--- a/data/SGF.MI.xlsx
+++ b/data/SGF.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>198623</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>2.06500005722046</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>2.02999997138977</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>2.04500007629395</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SGF.MI.xlsx
+++ b/data/SGF.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>139549</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>2.08500003814697</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>2.0550000667572</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>2.0550000667572</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SGF.MI.xlsx
+++ b/data/SGF.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>150820</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>2.07500004768372</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>2.02999997138977</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>2.02999997138977</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>2.04999995231628</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SGF.MI.xlsx
+++ b/data/SGF.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>197137</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>2.10999989509583</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>2.08999991416931</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SGF.MI.xlsx
+++ b/data/SGF.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>133665</v>
+        <v>96208</v>
       </c>
       <c r="C2715" t="n">
-        <v>2.08500003814697</v>
+        <v>2.125</v>
       </c>
       <c r="D2715" t="n">
-        <v>2.04500007629395</v>
+        <v>2.07999992370605</v>
       </c>
       <c r="E2715" t="n">
-        <v>2.0699999332428</v>
+        <v>2.11999988555908</v>
       </c>
       <c r="F2715" t="n">
-        <v>2.07999992370605</v>
+        <v>2.09500002861023</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>155743</v>
+        <v>133665</v>
       </c>
       <c r="C2716" t="n">
-        <v>2.07500004768372</v>
+        <v>2.08500003814697</v>
       </c>
       <c r="D2716" t="n">
-        <v>2.03500008583069</v>
+        <v>2.04500007629395</v>
       </c>
       <c r="E2716" t="n">
-        <v>2.07500004768372</v>
+        <v>2.0699999332428</v>
       </c>
       <c r="F2716" t="n">
-        <v>2.03999996185303</v>
+        <v>2.07999992370605</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>198594</v>
+        <v>155743</v>
       </c>
       <c r="C2717" t="n">
-        <v>2.10500001907349</v>
+        <v>2.07500004768372</v>
       </c>
       <c r="D2717" t="n">
-        <v>2.01999998092651</v>
+        <v>2.03500008583069</v>
       </c>
       <c r="E2717" t="n">
-        <v>2.01999998092651</v>
+        <v>2.07500004768372</v>
       </c>
       <c r="F2717" t="n">
-        <v>2.0699999332428</v>
+        <v>2.03999996185303</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>88030</v>
+        <v>198594</v>
       </c>
       <c r="C2718" t="n">
-        <v>2.09500002861023</v>
+        <v>2.10500001907349</v>
       </c>
       <c r="D2718" t="n">
-        <v>2.04999995231628</v>
+        <v>2.01999998092651</v>
       </c>
       <c r="E2718" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="F2718" t="n">
         <v>2.0699999332428</v>
-      </c>
-      <c r="F2718" t="n">
-        <v>2.05999994277954</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,19 +62888,19 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>198623</v>
+        <v>88030</v>
       </c>
       <c r="C2719" t="n">
-        <v>2.06500005722046</v>
+        <v>2.09500002861023</v>
       </c>
       <c r="D2719" t="n">
-        <v>2.02999997138977</v>
+        <v>2.04999995231628</v>
       </c>
       <c r="E2719" t="n">
-        <v>2.04500007629395</v>
+        <v>2.0699999332428</v>
       </c>
       <c r="F2719" t="n">
         <v>2.05999994277954</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>139549</v>
+        <v>198623</v>
       </c>
       <c r="C2720" t="n">
-        <v>2.08500003814697</v>
+        <v>2.06500005722046</v>
       </c>
       <c r="D2720" t="n">
-        <v>2.03999996185303</v>
+        <v>2.02999997138977</v>
       </c>
       <c r="E2720" t="n">
-        <v>2.0550000667572</v>
+        <v>2.04500007629395</v>
       </c>
       <c r="F2720" t="n">
-        <v>2.0550000667572</v>
+        <v>2.05999994277954</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>150820</v>
+        <v>139549</v>
       </c>
       <c r="C2721" t="n">
-        <v>2.07500004768372</v>
+        <v>2.08500003814697</v>
       </c>
       <c r="D2721" t="n">
-        <v>2.02999997138977</v>
+        <v>2.03999996185303</v>
       </c>
       <c r="E2721" t="n">
-        <v>2.02999997138977</v>
+        <v>2.0550000667572</v>
       </c>
       <c r="F2721" t="n">
-        <v>2.04999995231628</v>
+        <v>2.0550000667572</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>197137</v>
+        <v>150820</v>
       </c>
       <c r="C2722" t="n">
-        <v>2.10999989509583</v>
+        <v>2.07500004768372</v>
       </c>
       <c r="D2722" t="n">
-        <v>2.05999994277954</v>
+        <v>2.02999997138977</v>
       </c>
       <c r="E2722" t="n">
-        <v>2.05999994277954</v>
+        <v>2.02999997138977</v>
       </c>
       <c r="F2722" t="n">
-        <v>2.08999991416931</v>
+        <v>2.04999995231628</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>181673</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>2.09500002861023</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>2.04999995231628</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>2.08500003814697</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>2.06500005722046</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SGF.MI.xlsx
+++ b/data/SGF.MI.xlsx
@@ -499,7 +499,7 @@
         <v>1.93299996852875</v>
       </c>
       <c r="G5" t="n">
-        <v>1.18554711341858</v>
+        <v>1.18554699420929</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G8" t="n">
-        <v>1.17389392852783</v>
+        <v>1.17389404773712</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G9" t="n">
-        <v>1.15058791637421</v>
+        <v>1.15058779716492</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G10" t="n">
-        <v>1.12850832939148</v>
+        <v>1.12850844860077</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G13" t="n">
-        <v>1.09293568134308</v>
+        <v>1.09293580055237</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>1.00891089439392</v>
+        <v>1.00891101360321</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>1.77400004863739</v>
       </c>
       <c r="G18" t="n">
-        <v>1.08802926540375</v>
+        <v>1.08802914619446</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G27" t="n">
-        <v>0.841474652290344</v>
+        <v>0.841474711894989</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>1.42400002479553</v>
       </c>
       <c r="G29" t="n">
-        <v>0.873367249965668</v>
+        <v>0.873367309570312</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G30" t="n">
-        <v>0.858647644519806</v>
+        <v>0.858647584915161</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G32" t="n">
-        <v>0.981311500072479</v>
+        <v>0.981311559677124</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G33" t="n">
-        <v>0.950645565986633</v>
+        <v>0.950645625591278</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>1.56099998950958</v>
       </c>
       <c r="G34" t="n">
-        <v>0.957392036914825</v>
+        <v>0.95739209651947</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G35" t="n">
-        <v>0.941445708274841</v>
+        <v>0.941445767879486</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>1.50399994850159</v>
       </c>
       <c r="G36" t="n">
-        <v>0.922432839870453</v>
+        <v>0.922432899475098</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G37" t="n">
-        <v>0.96291196346283</v>
+        <v>0.962912023067474</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G38" t="n">
-        <v>0.941445708274841</v>
+        <v>0.941445767879486</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>1.52699995040894</v>
       </c>
       <c r="G41" t="n">
-        <v>0.936539232730865</v>
+        <v>0.936539173126221</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>1.5789999961853</v>
       </c>
       <c r="G44" t="n">
-        <v>0.968431890010834</v>
+        <v>0.968431770801544</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G49" t="n">
-        <v>1.00891089439392</v>
+        <v>1.00891101360321</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G53" t="n">
-        <v>0.960458695888519</v>
+        <v>0.960458636283875</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>1.58299994468689</v>
       </c>
       <c r="G54" t="n">
-        <v>0.970885157585144</v>
+        <v>0.970885097980499</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G55" t="n">
-        <v>0.956165492534637</v>
+        <v>0.956165432929993</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G57" t="n">
-        <v>0.926112711429596</v>
+        <v>0.926112830638885</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>1.4210000038147</v>
       </c>
       <c r="G59" t="n">
-        <v>0.871527314186096</v>
+        <v>0.871527373790741</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G60" t="n">
-        <v>0.853741109371185</v>
+        <v>0.853741049766541</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>1.34300005435944</v>
       </c>
       <c r="G61" t="n">
-        <v>0.823688447475433</v>
+        <v>0.823688387870789</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G66" t="n">
-        <v>0.815715193748474</v>
+        <v>0.815715253353119</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G67" t="n">
-        <v>0.818781852722168</v>
+        <v>0.818781912326813</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G68" t="n">
-        <v>0.79424911737442</v>
+        <v>0.794249057769775</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G69" t="n">
-        <v>0.832888185977936</v>
+        <v>0.832888305187225</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G70" t="n">
-        <v>0.849447786808014</v>
+        <v>0.849447846412659</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>1.38300001621246</v>
       </c>
       <c r="G71" t="n">
-        <v>0.848221182823181</v>
+        <v>0.848221242427826</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>1.43299996852875</v>
       </c>
       <c r="G73" t="n">
-        <v>0.878887176513672</v>
+        <v>0.878887116909027</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G76" t="n">
-        <v>0.852514386177063</v>
+        <v>0.852514445781708</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>1.43099999427795</v>
       </c>
       <c r="G77" t="n">
-        <v>0.877660572528839</v>
+        <v>0.877660512924194</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G78" t="n">
-        <v>0.875207304954529</v>
+        <v>0.875207245349884</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>1.42299997806549</v>
       </c>
       <c r="G79" t="n">
-        <v>0.872754037380219</v>
+        <v>0.872753977775574</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G81" t="n">
-        <v>0.868460714817047</v>
+        <v>0.868460774421692</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G83" t="n">
-        <v>0.943285644054413</v>
+        <v>0.943285763263702</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G84" t="n">
-        <v>0.977631628513336</v>
+        <v>0.977631688117981</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G85" t="n">
-        <v>0.99357795715332</v>
+        <v>0.993578016757965</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G86" t="n">
-        <v>0.951258897781372</v>
+        <v>0.951258957386017</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G87" t="n">
-        <v>0.951258897781372</v>
+        <v>0.951258957386017</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G88" t="n">
-        <v>0.951258897781372</v>
+        <v>0.951258957386017</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G89" t="n">
-        <v>0.951258897781372</v>
+        <v>0.951258957386017</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>1.50100004673004</v>
       </c>
       <c r="G90" t="n">
-        <v>0.920592963695526</v>
+        <v>0.920592904090881</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G93" t="n">
-        <v>0.978245079517365</v>
+        <v>0.97824501991272</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G94" t="n">
-        <v>0.992351412773132</v>
+        <v>0.992351353168488</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G95" t="n">
-        <v>1.00216448307037</v>
+        <v>1.00216436386108</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>1.6710000038147</v>
       </c>
       <c r="G96" t="n">
-        <v>1.02485716342926</v>
+        <v>1.02485728263855</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G98" t="n">
-        <v>0.943285644054413</v>
+        <v>0.943285763263702</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G99" t="n">
-        <v>0.935312569141388</v>
+        <v>0.935312628746033</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G102" t="n">
-        <v>1.0242440700531</v>
+        <v>1.02424395084381</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G103" t="n">
-        <v>1.09170913696289</v>
+        <v>1.0917090177536</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G110" t="n">
-        <v>0.999711215496063</v>
+        <v>0.999711155891418</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G111" t="n">
-        <v>1.00707101821899</v>
+        <v>1.0070708990097</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>1.625</v>
       </c>
       <c r="G112" t="n">
-        <v>0.996644616127014</v>
+        <v>0.996644556522369</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>1.60099995136261</v>
       </c>
       <c r="G113" t="n">
-        <v>0.981924831867218</v>
+        <v>0.981924891471863</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G114" t="n">
-        <v>0.935312569141388</v>
+        <v>0.935312628746033</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>1.39300000667572</v>
       </c>
       <c r="G115" t="n">
-        <v>0.854354321956635</v>
+        <v>0.854354381561279</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G116" t="n">
-        <v>0.806515455245972</v>
+        <v>0.806515514850616</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G119" t="n">
-        <v>0.792409062385559</v>
+        <v>0.792409121990204</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>1.36899995803833</v>
       </c>
       <c r="G120" t="n">
-        <v>0.839634716510773</v>
+        <v>0.839634656906128</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G121" t="n">
-        <v>0.880727112293243</v>
+        <v>0.880727171897888</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G122" t="n">
-        <v>0.875207304954529</v>
+        <v>0.875207245349884</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G123" t="n">
-        <v>0.880113780498505</v>
+        <v>0.880113840103149</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G124" t="n">
-        <v>0.812648713588715</v>
+        <v>0.81264865398407</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>1.25699996948242</v>
       </c>
       <c r="G127" t="n">
-        <v>0.770942866802216</v>
+        <v>0.77094292640686</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G128" t="n">
-        <v>0.806515455245972</v>
+        <v>0.806515514850616</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>1.30900001525879</v>
       </c>
       <c r="G129" t="n">
-        <v>0.802835583686829</v>
+        <v>0.802835524082184</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G131" t="n">
-        <v>0.725557208061218</v>
+        <v>0.725557267665863</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G132" t="n">
-        <v>0.71145087480545</v>
+        <v>0.711450815200806</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G133" t="n">
-        <v>0.713904142379761</v>
+        <v>0.713904201984406</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G135" t="n">
-        <v>0.771556198596954</v>
+        <v>0.771556258201599</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>1.30299997329712</v>
       </c>
       <c r="G136" t="n">
-        <v>0.799155533313751</v>
+        <v>0.799155652523041</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G137" t="n">
-        <v>0.803448855876923</v>
+        <v>0.803448796272278</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G140" t="n">
-        <v>0.858647644519806</v>
+        <v>0.858647584915161</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G141" t="n">
-        <v>0.851287841796875</v>
+        <v>0.85128778219223</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G142" t="n">
-        <v>0.861100971698761</v>
+        <v>0.861100912094116</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G148" t="n">
-        <v>0.935312569141388</v>
+        <v>0.935312628746033</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G149" t="n">
-        <v>0.932246029376984</v>
+        <v>0.932245969772339</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G150" t="n">
-        <v>0.935925900936127</v>
+        <v>0.935925960540771</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.54900002479553</v>
       </c>
       <c r="G152" t="n">
-        <v>0.950032234191895</v>
+        <v>0.950032293796539</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G153" t="n">
-        <v>0.956778824329376</v>
+        <v>0.956778764724731</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G156" t="n">
-        <v>1.00707101821899</v>
+        <v>1.0070708990097</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G158" t="n">
-        <v>1.0242440700531</v>
+        <v>1.02424395084381</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>1.66100001335144</v>
       </c>
       <c r="G162" t="n">
-        <v>1.01872408390045</v>
+        <v>1.01872396469116</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G163" t="n">
-        <v>1.00461769104004</v>
+        <v>1.00461781024933</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>1.66100001335144</v>
       </c>
       <c r="G164" t="n">
-        <v>1.01872408390045</v>
+        <v>1.01872396469116</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G165" t="n">
-        <v>1.03651034832001</v>
+        <v>1.0365104675293</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G166" t="n">
-        <v>1.03896355628967</v>
+        <v>1.03896367549896</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G169" t="n">
-        <v>1.0549099445343</v>
+        <v>1.05491006374359</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G170" t="n">
-        <v>1.0457102060318</v>
+        <v>1.04571008682251</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G172" t="n">
-        <v>1.02363073825836</v>
+        <v>1.02363061904907</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>1.66700005531311</v>
       </c>
       <c r="G173" t="n">
-        <v>1.02240407466888</v>
+        <v>1.02240395545959</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>1.75800001621246</v>
       </c>
       <c r="G174" t="n">
-        <v>1.07821607589722</v>
+        <v>1.07821619510651</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G176" t="n">
-        <v>1.09170913696289</v>
+        <v>1.0917090177536</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G179" t="n">
-        <v>1.0825092792511</v>
+        <v>1.08250939846039</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G181" t="n">
-        <v>1.06472301483154</v>
+        <v>1.06472289562225</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G184" t="n">
-        <v>1.0549099445343</v>
+        <v>1.05491006374359</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>1.77400004863739</v>
       </c>
       <c r="G187" t="n">
-        <v>1.08802926540375</v>
+        <v>1.08802914619446</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G189" t="n">
-        <v>1.09170913696289</v>
+        <v>1.0917090177536</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G191" t="n">
-        <v>1.1101086139679</v>
+        <v>1.11010873317719</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G194" t="n">
-        <v>1.09170913696289</v>
+        <v>1.0917090177536</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G195" t="n">
-        <v>1.09416234493256</v>
+        <v>1.09416246414185</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G199" t="n">
-        <v>1.10152220726013</v>
+        <v>1.10152232646942</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>1.79100000858307</v>
       </c>
       <c r="G201" t="n">
-        <v>1.09845554828644</v>
+        <v>1.09845566749573</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.76699995994568</v>
       </c>
       <c r="G202" t="n">
-        <v>1.08373606204987</v>
+        <v>1.08373594284058</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>1.79100000858307</v>
       </c>
       <c r="G205" t="n">
-        <v>1.09845554828644</v>
+        <v>1.09845566749573</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G208" t="n">
-        <v>1.10152220726013</v>
+        <v>1.10152232646942</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G209" t="n">
-        <v>1.12850832939148</v>
+        <v>1.12850844860077</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G210" t="n">
-        <v>1.18370711803436</v>
+        <v>1.18370699882507</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G211" t="n">
-        <v>1.23890590667725</v>
+        <v>1.23890578746796</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G213" t="n">
-        <v>1.23277258872986</v>
+        <v>1.23277270793915</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G215" t="n">
-        <v>1.26343858242035</v>
+        <v>1.26343870162964</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G217" t="n">
-        <v>1.28551805019379</v>
+        <v>1.28551816940308</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.07800006866455</v>
       </c>
       <c r="G221" t="n">
-        <v>1.27447855472565</v>
+        <v>1.27447843551636</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.07399988174438</v>
       </c>
       <c r="G223" t="n">
-        <v>1.27202498912811</v>
+        <v>1.2720251083374</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G225" t="n">
-        <v>1.31495749950409</v>
+        <v>1.31495761871338</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G226" t="n">
-        <v>1.32231724262238</v>
+        <v>1.32231712341309</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G230" t="n">
-        <v>1.32354402542114</v>
+        <v>1.32354390621185</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G236" t="n">
-        <v>1.28797125816345</v>
+        <v>1.28797137737274</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G237" t="n">
-        <v>1.28797125816345</v>
+        <v>1.28797137737274</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G241" t="n">
-        <v>1.3627964258194</v>
+        <v>1.36279654502869</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G242" t="n">
-        <v>1.4229017496109</v>
+        <v>1.42290163040161</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G243" t="n">
-        <v>1.43516826629639</v>
+        <v>1.4351681470871</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G245" t="n">
-        <v>1.4768739938736</v>
+        <v>1.47687387466431</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G249" t="n">
-        <v>1.47932708263397</v>
+        <v>1.47932732105255</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G251" t="n">
-        <v>1.50263333320618</v>
+        <v>1.50263345241547</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G254" t="n">
-        <v>1.4768739938736</v>
+        <v>1.47687387466431</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G255" t="n">
-        <v>1.44743454456329</v>
+        <v>1.447434425354</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G258" t="n">
-        <v>1.56396532058716</v>
+        <v>1.56396520137787</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G259" t="n">
-        <v>1.5799115896225</v>
+        <v>1.57991170883179</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G260" t="n">
-        <v>1.58113825321198</v>
+        <v>1.58113837242126</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G261" t="n">
-        <v>1.57009840011597</v>
+        <v>1.57009851932526</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G266" t="n">
-        <v>1.55169880390167</v>
+        <v>1.55169904232025</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G267" t="n">
-        <v>1.57009840011597</v>
+        <v>1.57009851932526</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G268" t="n">
-        <v>1.57868504524231</v>
+        <v>1.57868480682373</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G269" t="n">
-        <v>1.55660557746887</v>
+        <v>1.55660545825958</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.5</v>
       </c>
       <c r="G270" t="n">
-        <v>1.53329944610596</v>
+        <v>1.53329932689667</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G271" t="n">
-        <v>1.52593946456909</v>
+        <v>1.52593958377838</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.48600006103516</v>
       </c>
       <c r="G275" t="n">
-        <v>1.52471303939819</v>
+        <v>1.5247129201889</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G276" t="n">
-        <v>1.52593946456909</v>
+        <v>1.52593958377838</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G277" t="n">
-        <v>1.4768739938736</v>
+        <v>1.47687387466431</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G279" t="n">
-        <v>1.34930336475372</v>
+        <v>1.34930348396301</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G280" t="n">
-        <v>1.41676843166351</v>
+        <v>1.4167685508728</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G281" t="n">
-        <v>1.41308856010437</v>
+        <v>1.41308867931366</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G284" t="n">
-        <v>1.27079844474792</v>
+        <v>1.27079856395721</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.12400007247925</v>
       </c>
       <c r="G287" t="n">
-        <v>1.30269110202789</v>
+        <v>1.30269122123718</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.33599996566772</v>
       </c>
       <c r="G288" t="n">
-        <v>1.43271481990814</v>
+        <v>1.43271493911743</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G292" t="n">
-        <v>1.38732922077179</v>
+        <v>1.38732933998108</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G293" t="n">
-        <v>1.39959573745728</v>
+        <v>1.39959561824799</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G294" t="n">
-        <v>1.43394160270691</v>
+        <v>1.4339417219162</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G295" t="n">
-        <v>1.43394160270691</v>
+        <v>1.4339417219162</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G296" t="n">
-        <v>1.4106353521347</v>
+        <v>1.41063547134399</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.67199993133545</v>
       </c>
       <c r="G299" t="n">
-        <v>1.63879036903381</v>
+        <v>1.63879024982452</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G302" t="n">
-        <v>1.6694563627243</v>
+        <v>1.66945624351501</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G306" t="n">
-        <v>1.7540944814682</v>
+        <v>1.75409436225891</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>1.77862739562988</v>
+        <v>1.77862727642059</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G313" t="n">
-        <v>1.95526325702667</v>
+        <v>1.95526337623596</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G314" t="n">
-        <v>1.9356369972229</v>
+        <v>1.93563687801361</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G315" t="n">
-        <v>2.01046204566956</v>
+        <v>2.01046228408813</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G320" t="n">
-        <v>2.2974956035614</v>
+        <v>2.29749584197998</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G321" t="n">
-        <v>2.26928305625916</v>
+        <v>2.26928281784058</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G322" t="n">
-        <v>2.26805639266968</v>
+        <v>2.2680561542511</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G323" t="n">
-        <v>2.25701665878296</v>
+        <v>2.25701689720154</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>3.75600004196167</v>
       </c>
       <c r="G324" t="n">
-        <v>2.30362892150879</v>
+        <v>2.30362915992737</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G326" t="n">
-        <v>2.24843001365662</v>
+        <v>2.2484302520752</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G328" t="n">
-        <v>2.24843001365662</v>
+        <v>2.2484302520752</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G329" t="n">
-        <v>2.2778697013855</v>
+        <v>2.27786946296692</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G331" t="n">
-        <v>2.26805639266968</v>
+        <v>2.2680561542511</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G333" t="n">
-        <v>2.28277611732483</v>
+        <v>2.28277587890625</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G339" t="n">
-        <v>2.72681951522827</v>
+        <v>2.72681975364685</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>2.73540639877319</v>
+        <v>2.73540592193604</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G343" t="n">
-        <v>2.76607203483582</v>
+        <v>2.76607227325439</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G344" t="n">
-        <v>2.72927260398865</v>
+        <v>2.72927284240723</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>2.85193681716919</v>
+        <v>2.85193705558777</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G346" t="n">
-        <v>2.90590906143188</v>
+        <v>2.90590882301331</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G348" t="n">
-        <v>2.8899621963501</v>
+        <v>2.88996243476868</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>4.60799980163574</v>
       </c>
       <c r="G349" t="n">
-        <v>2.82617712020874</v>
+        <v>2.82617735862732</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G350" t="n">
-        <v>2.85684323310852</v>
+        <v>2.8568434715271</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>5.08500003814697</v>
       </c>
       <c r="G356" t="n">
-        <v>3.1187310218811</v>
+        <v>3.11873078346252</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G357" t="n">
-        <v>3.1463303565979</v>
+        <v>3.14633059501648</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G358" t="n">
-        <v>3.21379542350769</v>
+        <v>3.21379518508911</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G362" t="n">
-        <v>3.1463303565979</v>
+        <v>3.14633059501648</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>5.125</v>
       </c>
       <c r="G363" t="n">
-        <v>3.1432638168335</v>
+        <v>3.14326357841492</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G368" t="n">
-        <v>3.14019680023193</v>
+        <v>3.14019703865051</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G371" t="n">
-        <v>3.21072912216187</v>
+        <v>3.21072888374329</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G372" t="n">
-        <v>3.10953116416931</v>
+        <v>3.10953092575073</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>3.23219513893127</v>
+        <v>3.2321949005127</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G382" t="n">
-        <v>3.10953116416931</v>
+        <v>3.10953092575073</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G383" t="n">
-        <v>2.92553520202637</v>
+        <v>2.92553496360779</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>4.68400001525879</v>
       </c>
       <c r="G384" t="n">
-        <v>2.87278938293457</v>
+        <v>2.87278962135315</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.69199991226196</v>
       </c>
       <c r="G394" t="n">
-        <v>2.87769627571106</v>
+        <v>2.87769603729248</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G399" t="n">
-        <v>2.67898035049438</v>
+        <v>2.67898082733154</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G400" t="n">
-        <v>2.69860672950745</v>
+        <v>2.69860696792603</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>4.47800016403198</v>
       </c>
       <c r="G402" t="n">
-        <v>2.74644565582275</v>
+        <v>2.74644589424133</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>4.2480001449585</v>
       </c>
       <c r="G406" t="n">
-        <v>2.60538220405579</v>
+        <v>2.60538244247437</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>4.14200019836426</v>
       </c>
       <c r="G407" t="n">
-        <v>2.54037070274353</v>
+        <v>2.54037046432495</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G408" t="n">
-        <v>2.55631685256958</v>
+        <v>2.556316614151</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G409" t="n">
-        <v>2.5759425163269</v>
+        <v>2.57594275474548</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G410" t="n">
-        <v>2.5759425163269</v>
+        <v>2.57594275474548</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.27400016784668</v>
       </c>
       <c r="G412" t="n">
-        <v>2.62132859230042</v>
+        <v>2.62132883071899</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4.4520001411438</v>
       </c>
       <c r="G414" t="n">
-        <v>2.7304995059967</v>
+        <v>2.73049974441528</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>4.55800008773804</v>
       </c>
       <c r="G415" t="n">
-        <v>2.79551148414612</v>
+        <v>2.79551124572754</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G416" t="n">
-        <v>2.82127070426941</v>
+        <v>2.82127094268799</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>4.60400009155273</v>
       </c>
       <c r="G417" t="n">
-        <v>2.82372403144836</v>
+        <v>2.82372426986694</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G419" t="n">
-        <v>2.77588510513306</v>
+        <v>2.77588534355164</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G420" t="n">
-        <v>2.73540639877319</v>
+        <v>2.73540592193604</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>4.41800022125244</v>
       </c>
       <c r="G422" t="n">
-        <v>2.70964670181274</v>
+        <v>2.70964646339417</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>4.44399976730347</v>
       </c>
       <c r="G423" t="n">
-        <v>2.72559285163879</v>
+        <v>2.72559309005737</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G424" t="n">
-        <v>2.66794109344482</v>
+        <v>2.66794085502625</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>4.24599981307983</v>
       </c>
       <c r="G425" t="n">
-        <v>2.60415554046631</v>
+        <v>2.60415530204773</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G427" t="n">
-        <v>2.67898035049438</v>
+        <v>2.67898082733154</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G428" t="n">
-        <v>2.62991499900818</v>
+        <v>2.62991523742676</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>4.28200006484985</v>
       </c>
       <c r="G429" t="n">
-        <v>2.62623500823975</v>
+        <v>2.62623524665833</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>5</v>
       </c>
       <c r="G437" t="n">
-        <v>3.06659889221191</v>
+        <v>3.06659865379333</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>5</v>
       </c>
       <c r="G441" t="n">
-        <v>3.06659889221191</v>
+        <v>3.06659865379333</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G442" t="n">
-        <v>3.10033130645752</v>
+        <v>3.10033106803894</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>5.03499984741211</v>
       </c>
       <c r="G443" t="n">
-        <v>3.08806490898132</v>
+        <v>3.08806443214417</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>5</v>
       </c>
       <c r="G444" t="n">
-        <v>3.06659889221191</v>
+        <v>3.06659865379333</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G446" t="n">
-        <v>3.17699646949768</v>
+        <v>3.1769962310791</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>3.15552997589111</v>
+        <v>3.15553021430969</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.90199995040894</v>
       </c>
       <c r="G454" t="n">
-        <v>3.00649333000183</v>
+        <v>3.00649356842041</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>4.80600023269653</v>
       </c>
       <c r="G460" t="n">
-        <v>2.9476146697998</v>
+        <v>2.94761490821838</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G461" t="n">
-        <v>2.97214770317078</v>
+        <v>2.97214722633362</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>4.63199996948242</v>
       </c>
       <c r="G462" t="n">
-        <v>2.84089708328247</v>
+        <v>2.84089684486389</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G463" t="n">
-        <v>2.88260245323181</v>
+        <v>2.88260269165039</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G464" t="n">
-        <v>2.9010021686554</v>
+        <v>2.90100240707397</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G465" t="n">
-        <v>2.90590906143188</v>
+        <v>2.90590882301331</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G470" t="n">
-        <v>2.5759425163269</v>
+        <v>2.57594275474548</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G471" t="n">
-        <v>2.55631685256958</v>
+        <v>2.556316614151</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G476" t="n">
-        <v>2.47781181335449</v>
+        <v>2.47781157493591</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G477" t="n">
-        <v>2.43487930297852</v>
+        <v>2.43487954139709</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G481" t="n">
-        <v>2.26805639266968</v>
+        <v>2.2680561542511</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G482" t="n">
-        <v>2.34165477752686</v>
+        <v>2.34165501594543</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>3.86400008201599</v>
       </c>
       <c r="G483" t="n">
-        <v>2.36986756324768</v>
+        <v>2.3698673248291</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G486" t="n">
-        <v>2.58575582504272</v>
+        <v>2.5857560634613</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G489" t="n">
-        <v>2.42383933067322</v>
+        <v>2.4238395690918</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G490" t="n">
-        <v>2.44346570968628</v>
+        <v>2.44346594810486</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G491" t="n">
-        <v>2.66794109344482</v>
+        <v>2.66794085502625</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G492" t="n">
-        <v>2.63482141494751</v>
+        <v>2.63482189178467</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.25600004196167</v>
       </c>
       <c r="G494" t="n">
-        <v>2.61028861999512</v>
+        <v>2.6102888584137</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G496" t="n">
-        <v>2.53914356231689</v>
+        <v>2.53914380073547</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G501" t="n">
-        <v>2.38581395149231</v>
+        <v>2.38581371307373</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G502" t="n">
-        <v>2.33061504364014</v>
+        <v>2.33061480522156</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>3.94799995422363</v>
       </c>
       <c r="G504" t="n">
-        <v>2.42138648033142</v>
+        <v>2.42138624191284</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G505" t="n">
-        <v>2.39808011054993</v>
+        <v>2.39808034896851</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>3.95799994468689</v>
       </c>
       <c r="G513" t="n">
-        <v>2.42751932144165</v>
+        <v>2.42751955986023</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G516" t="n">
-        <v>2.51461100578308</v>
+        <v>2.5146107673645</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G517" t="n">
-        <v>2.5268771648407</v>
+        <v>2.52687740325928</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>4.18599987030029</v>
       </c>
       <c r="G519" t="n">
-        <v>2.56735610961914</v>
+        <v>2.56735634803772</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G521" t="n">
-        <v>2.62991499900818</v>
+        <v>2.62991523742676</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>4.21799993515015</v>
       </c>
       <c r="G523" t="n">
-        <v>2.5869824886322</v>
+        <v>2.58698272705078</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G532" t="n">
-        <v>2.45450568199158</v>
+        <v>2.454505443573</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>3.86400008201599</v>
       </c>
       <c r="G535" t="n">
-        <v>2.36986756324768</v>
+        <v>2.3698673248291</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G538" t="n">
-        <v>2.41647982597351</v>
+        <v>2.41647958755493</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>3.60599994659424</v>
       </c>
       <c r="G541" t="n">
-        <v>2.21163082122803</v>
+        <v>2.21163105964661</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G542" t="n">
-        <v>2.18341827392578</v>
+        <v>2.1834180355072</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G544" t="n">
-        <v>2.27541637420654</v>
+        <v>2.27541613578796</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G548" t="n">
-        <v>2.28400278091431</v>
+        <v>2.28400254249573</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G549" t="n">
-        <v>2.33061504364014</v>
+        <v>2.33061480522156</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G553" t="n">
-        <v>2.03008818626404</v>
+        <v>2.03008842468262</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>3.18600010871887</v>
       </c>
       <c r="G554" t="n">
-        <v>1.95403659343719</v>
+        <v>1.95403671264648</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G555" t="n">
-        <v>1.90129113197327</v>
+        <v>1.90129125118256</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G557" t="n">
-        <v>1.87921154499054</v>
+        <v>1.87921166419983</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>3.15799999237061</v>
       </c>
       <c r="G559" t="n">
-        <v>1.93686378002167</v>
+        <v>1.93686354160309</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>3.11800003051758</v>
       </c>
       <c r="G560" t="n">
-        <v>1.91233098506927</v>
+        <v>1.91233086585999</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>3.02600002288818</v>
       </c>
       <c r="G562" t="n">
-        <v>1.8559056520462</v>
+        <v>1.85590553283691</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G563" t="n">
-        <v>1.87798511981964</v>
+        <v>1.87798500061035</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G564" t="n">
-        <v>1.87921154499054</v>
+        <v>1.87921166419983</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G567" t="n">
-        <v>1.90129113197327</v>
+        <v>1.90129125118256</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G568" t="n">
-        <v>1.98715591430664</v>
+        <v>1.98715603351593</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>3.08200001716614</v>
       </c>
       <c r="G571" t="n">
-        <v>1.89025139808655</v>
+        <v>1.89025127887726</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G572" t="n">
-        <v>1.88657128810883</v>
+        <v>1.8865715265274</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G577" t="n">
-        <v>1.92091739177704</v>
+        <v>1.92091727256775</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G578" t="n">
-        <v>1.95649015903473</v>
+        <v>1.95649003982544</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>3.11800003051758</v>
       </c>
       <c r="G581" t="n">
-        <v>1.91233098506927</v>
+        <v>1.91233086585999</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>3.32399988174438</v>
       </c>
       <c r="G584" t="n">
-        <v>2.03867483139038</v>
+        <v>2.0386745929718</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G588" t="n">
-        <v>1.96262300014496</v>
+        <v>1.96262311935425</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G589" t="n">
-        <v>2.03008818626404</v>
+        <v>2.03008842468262</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G591" t="n">
-        <v>1.9712096452713</v>
+        <v>1.97120976448059</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G593" t="n">
-        <v>1.9773428440094</v>
+        <v>1.97734272480011</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>3.25399994850159</v>
       </c>
       <c r="G594" t="n">
-        <v>1.99574255943298</v>
+        <v>1.99574244022369</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G595" t="n">
-        <v>2.08283376693726</v>
+        <v>2.08283352851868</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G599" t="n">
-        <v>1.99942243099213</v>
+        <v>1.99942231178284</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G600" t="n">
-        <v>2.02640819549561</v>
+        <v>2.02640843391418</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G601" t="n">
-        <v>1.9712096452713</v>
+        <v>1.97120976448059</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G602" t="n">
-        <v>1.96017003059387</v>
+        <v>1.96016979217529</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>3.15199995040894</v>
       </c>
       <c r="G603" t="n">
-        <v>1.93318390846252</v>
+        <v>1.93318378925323</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G604" t="n">
-        <v>1.93441033363342</v>
+        <v>1.93441045284271</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>3.08200001716614</v>
       </c>
       <c r="G605" t="n">
-        <v>1.89025139808655</v>
+        <v>1.89025127887726</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>3.13800001144409</v>
       </c>
       <c r="G606" t="n">
-        <v>1.92459726333618</v>
+        <v>1.92459750175476</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G608" t="n">
-        <v>1.88411831855774</v>
+        <v>1.88411819934845</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>3.13599991798401</v>
       </c>
       <c r="G609" t="n">
-        <v>1.92337071895599</v>
+        <v>1.9233705997467</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G612" t="n">
-        <v>1.87921154499054</v>
+        <v>1.87921166419983</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G616" t="n">
-        <v>1.7663608789444</v>
+        <v>1.76636075973511</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G618" t="n">
-        <v>1.86939871311188</v>
+        <v>1.86939859390259</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G619" t="n">
-        <v>1.87307846546173</v>
+        <v>1.87307834625244</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G620" t="n">
-        <v>1.93441033363342</v>
+        <v>1.93441045284271</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>3.08400011062622</v>
       </c>
       <c r="G621" t="n">
-        <v>1.89147806167603</v>
+        <v>1.89147818088531</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G624" t="n">
-        <v>1.87062513828278</v>
+        <v>1.87062525749207</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G630" t="n">
-        <v>1.80193328857422</v>
+        <v>1.80193340778351</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>2.86400008201599</v>
       </c>
       <c r="G632" t="n">
-        <v>1.75654768943787</v>
+        <v>1.75654780864716</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G633" t="n">
-        <v>1.66822969913483</v>
+        <v>1.66822981834412</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G634" t="n">
-        <v>1.63756370544434</v>
+        <v>1.63756382465363</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G635" t="n">
-        <v>1.63020396232605</v>
+        <v>1.63020384311676</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G636" t="n">
-        <v>1.57009840011597</v>
+        <v>1.57009851932526</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G638" t="n">
-        <v>1.5492457151413</v>
+        <v>1.54924583435059</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G639" t="n">
-        <v>1.55169880390167</v>
+        <v>1.55169904232025</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G640" t="n">
-        <v>1.56273877620697</v>
+        <v>1.56273865699768</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.68600010871887</v>
       </c>
       <c r="G641" t="n">
-        <v>1.64737689495087</v>
+        <v>1.64737677574158</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G642" t="n">
-        <v>1.63143038749695</v>
+        <v>1.63143050670624</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.75799989700317</v>
       </c>
       <c r="G643" t="n">
-        <v>1.69153571128845</v>
+        <v>1.69153583049774</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.66400003433228</v>
       </c>
       <c r="G645" t="n">
-        <v>1.63388383388519</v>
+        <v>1.6338837146759</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G646" t="n">
-        <v>1.60567116737366</v>
+        <v>1.60567104816437</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G647" t="n">
-        <v>1.59217810630798</v>
+        <v>1.59217798709869</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G650" t="n">
-        <v>1.72956156730652</v>
+        <v>1.72956168651581</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.78600001335144</v>
       </c>
       <c r="G651" t="n">
-        <v>1.70870864391327</v>
+        <v>1.70870876312256</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.71399998664856</v>
       </c>
       <c r="G652" t="n">
-        <v>1.66454982757568</v>
+        <v>1.66454970836639</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G653" t="n">
-        <v>1.63143038749695</v>
+        <v>1.63143050670624</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G658" t="n">
-        <v>1.29287791252136</v>
+        <v>1.29287803173065</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G660" t="n">
-        <v>1.29287791252136</v>
+        <v>1.29287803173065</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G662" t="n">
-        <v>1.26957178115845</v>
+        <v>1.26957190036774</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G663" t="n">
-        <v>1.27815842628479</v>
+        <v>1.2781583070755</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G666" t="n">
-        <v>1.25853216648102</v>
+        <v>1.25853204727173</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G668" t="n">
-        <v>1.20946645736694</v>
+        <v>1.20946657657623</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G669" t="n">
-        <v>1.20517337322235</v>
+        <v>1.20517325401306</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G673" t="n">
-        <v>1.28551805019379</v>
+        <v>1.28551816940308</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>1.98099994659424</v>
       </c>
       <c r="G674" t="n">
-        <v>1.21498644351959</v>
+        <v>1.2149863243103</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G677" t="n">
-        <v>1.23154604434967</v>
+        <v>1.23154592514038</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>2.04800009727478</v>
       </c>
       <c r="G682" t="n">
-        <v>1.25607895851135</v>
+        <v>1.25607883930206</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G683" t="n">
-        <v>1.22602605819702</v>
+        <v>1.22602617740631</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2</v>
       </c>
       <c r="G687" t="n">
-        <v>1.22663950920105</v>
+        <v>1.22663938999176</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>1.97899997234344</v>
       </c>
       <c r="G688" t="n">
-        <v>1.21375966072083</v>
+        <v>1.21375977993011</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G690" t="n">
-        <v>1.21191966533661</v>
+        <v>1.2119197845459</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2</v>
       </c>
       <c r="G691" t="n">
-        <v>1.22663950920105</v>
+        <v>1.22663938999176</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G692" t="n">
-        <v>1.24381256103516</v>
+        <v>1.24381244182587</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G693" t="n">
-        <v>1.24381256103516</v>
+        <v>1.24381244182587</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G694" t="n">
-        <v>1.26343858242035</v>
+        <v>1.26343870162964</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G695" t="n">
-        <v>1.29533123970032</v>
+        <v>1.29533135890961</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G696" t="n">
-        <v>1.31741070747375</v>
+        <v>1.31741094589233</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G698" t="n">
-        <v>1.24381256103516</v>
+        <v>1.24381244182587</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G703" t="n">
-        <v>1.17389392852783</v>
+        <v>1.17389404773712</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G708" t="n">
-        <v>1.08434915542603</v>
+        <v>1.08434927463531</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>1.68700003623962</v>
       </c>
       <c r="G710" t="n">
-        <v>1.03467035293579</v>
+        <v>1.03467047214508</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G711" t="n">
-        <v>1.05552315711975</v>
+        <v>1.05552327632904</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>1.625</v>
       </c>
       <c r="G715" t="n">
-        <v>0.996644616127014</v>
+        <v>0.996644556522369</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G717" t="n">
-        <v>0.984991431236267</v>
+        <v>0.984991550445557</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>1.49300003051758</v>
       </c>
       <c r="G719" t="n">
-        <v>0.915686368942261</v>
+        <v>0.915686428546906</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>1.5110000371933</v>
       </c>
       <c r="G720" t="n">
-        <v>0.926726102828979</v>
+        <v>0.926726162433624</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G722" t="n">
-        <v>0.951258897781372</v>
+        <v>0.951258957386017</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>1.57599997520447</v>
       </c>
       <c r="G723" t="n">
-        <v>0.966591954231262</v>
+        <v>0.966591894626617</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>1.59300005435944</v>
       </c>
       <c r="G725" t="n">
-        <v>0.977018296718597</v>
+        <v>0.977018356323242</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G726" t="n">
-        <v>0.980085015296936</v>
+        <v>0.980084896087646</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G728" t="n">
-        <v>0.96291196346283</v>
+        <v>0.962912023067474</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G729" t="n">
-        <v>0.992351412773132</v>
+        <v>0.992351353168488</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>1.57200002670288</v>
       </c>
       <c r="G730" t="n">
-        <v>0.964138686656952</v>
+        <v>0.964138567447662</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>1.53299999237061</v>
       </c>
       <c r="G731" t="n">
-        <v>0.940219223499298</v>
+        <v>0.940219163894653</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>1.50100004673004</v>
       </c>
       <c r="G734" t="n">
-        <v>0.920592963695526</v>
+        <v>0.920592904090881</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G740" t="n">
-        <v>0.875820517539978</v>
+        <v>0.875820577144623</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>1.53299999237061</v>
       </c>
       <c r="G742" t="n">
-        <v>0.940219223499298</v>
+        <v>0.940219163894653</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G743" t="n">
-        <v>0.956778824329376</v>
+        <v>0.956778764724731</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G744" t="n">
-        <v>0.94451242685318</v>
+        <v>0.94451230764389</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G745" t="n">
-        <v>0.941445708274841</v>
+        <v>0.941445767879486</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G747" t="n">
-        <v>0.967205166816711</v>
+        <v>0.967205226421356</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G748" t="n">
-        <v>0.956165492534637</v>
+        <v>0.956165432929993</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>1.4539999961853</v>
       </c>
       <c r="G753" t="n">
-        <v>0.891766905784607</v>
+        <v>0.891766965389252</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>1.48699998855591</v>
       </c>
       <c r="G754" t="n">
-        <v>0.912006378173828</v>
+        <v>0.912006437778473</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G755" t="n">
-        <v>0.875207304954529</v>
+        <v>0.875207245349884</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>1.37899994850159</v>
       </c>
       <c r="G757" t="n">
-        <v>0.845767855644226</v>
+        <v>0.845767915248871</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G759" t="n">
-        <v>0.849447786808014</v>
+        <v>0.849447846412659</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G761" t="n">
-        <v>0.864780783653259</v>
+        <v>0.864780843257904</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G762" t="n">
-        <v>0.864780783653259</v>
+        <v>0.864780843257904</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>1.43099999427795</v>
       </c>
       <c r="G763" t="n">
-        <v>0.877660572528839</v>
+        <v>0.877660512924194</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>1.45700001716614</v>
       </c>
       <c r="G764" t="n">
-        <v>0.893606901168823</v>
+        <v>0.893606841564178</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G767" t="n">
-        <v>0.951258897781372</v>
+        <v>0.951258957386017</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G768" t="n">
-        <v>0.951872289180756</v>
+        <v>0.951872229576111</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>1.60699999332428</v>
       </c>
       <c r="G769" t="n">
-        <v>0.985604822635651</v>
+        <v>0.985604882240295</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>1.61300003528595</v>
       </c>
       <c r="G771" t="n">
-        <v>0.989284753799438</v>
+        <v>0.989284694194794</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G773" t="n">
-        <v>0.94451242685318</v>
+        <v>0.94451230764389</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G775" t="n">
-        <v>0.982538282871246</v>
+        <v>0.982538223266602</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G776" t="n">
-        <v>0.99357795715332</v>
+        <v>0.993578016757965</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G778" t="n">
-        <v>0.940832495689392</v>
+        <v>0.940832436084747</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G781" t="n">
-        <v>0.984991431236267</v>
+        <v>0.984991550445557</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G784" t="n">
-        <v>1.06472301483154</v>
+        <v>1.06472289562225</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G785" t="n">
-        <v>1.12237501144409</v>
+        <v>1.12237513065338</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>1.7039999961853</v>
       </c>
       <c r="G789" t="n">
-        <v>1.04509687423706</v>
+        <v>1.04509675502777</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>1.625</v>
       </c>
       <c r="G790" t="n">
-        <v>0.996644616127014</v>
+        <v>0.996644556522369</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G791" t="n">
-        <v>0.972111821174622</v>
+        <v>0.972111761569977</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G794" t="n">
-        <v>1.0549099445343</v>
+        <v>1.05491006374359</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>1.71300005912781</v>
       </c>
       <c r="G795" t="n">
-        <v>1.05061662197113</v>
+        <v>1.05061674118042</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G796" t="n">
-        <v>1.06901633739471</v>
+        <v>1.06901621818542</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G797" t="n">
-        <v>1.05552315711975</v>
+        <v>1.05552327632904</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G799" t="n">
-        <v>1.06901633739471</v>
+        <v>1.06901621818542</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G800" t="n">
-        <v>1.0395770072937</v>
+        <v>1.03957688808441</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>1.56900000572205</v>
       </c>
       <c r="G804" t="n">
-        <v>0.962298631668091</v>
+        <v>0.96229875087738</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>1.56700003147125</v>
       </c>
       <c r="G805" t="n">
-        <v>0.961072027683258</v>
+        <v>0.961072087287903</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>1.5789999961853</v>
       </c>
       <c r="G806" t="n">
-        <v>0.968431890010834</v>
+        <v>0.968431770801544</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G810" t="n">
-        <v>0.921206295490265</v>
+        <v>0.921206176280975</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G817" t="n">
-        <v>0.926112711429596</v>
+        <v>0.926112830638885</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>1.54100000858307</v>
       </c>
       <c r="G818" t="n">
-        <v>0.945125699043274</v>
+        <v>0.945125639438629</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G819" t="n">
-        <v>0.945739030838013</v>
+        <v>0.945739090442657</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>1.50100004673004</v>
       </c>
       <c r="G825" t="n">
-        <v>0.920592963695526</v>
+        <v>0.920592904090881</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>1.53699994087219</v>
       </c>
       <c r="G826" t="n">
-        <v>0.942672491073608</v>
+        <v>0.942672431468964</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>1.59300005435944</v>
       </c>
       <c r="G827" t="n">
-        <v>0.977018296718597</v>
+        <v>0.977018356323242</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G828" t="n">
-        <v>0.960458695888519</v>
+        <v>0.960458636283875</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>1.66100001335144</v>
       </c>
       <c r="G830" t="n">
-        <v>1.01872408390045</v>
+        <v>1.01872396469116</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G833" t="n">
-        <v>0.96291196346283</v>
+        <v>0.962912023067474</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G834" t="n">
-        <v>0.96291196346283</v>
+        <v>0.962912023067474</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G837" t="n">
-        <v>0.96291196346283</v>
+        <v>0.962912023067474</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G839" t="n">
-        <v>0.977631628513336</v>
+        <v>0.977631688117981</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>1.5789999961853</v>
       </c>
       <c r="G842" t="n">
-        <v>0.968431890010834</v>
+        <v>0.968431770801544</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G843" t="n">
-        <v>0.953098833560944</v>
+        <v>0.953098893165588</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G845" t="n">
-        <v>0.902806639671326</v>
+        <v>0.90280669927597</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G847" t="n">
-        <v>0.852514386177063</v>
+        <v>0.852514445781708</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G849" t="n">
-        <v>0.840248048305511</v>
+        <v>0.840247988700867</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.27799999713898</v>
       </c>
       <c r="G852" t="n">
-        <v>0.783822596073151</v>
+        <v>0.783822655677795</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G854" t="n">
-        <v>0.731077134609222</v>
+        <v>0.731077075004578</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>1.18700003623962</v>
       </c>
       <c r="G855" t="n">
-        <v>0.728010535240173</v>
+        <v>0.728010594844818</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G856" t="n">
-        <v>0.743343591690063</v>
+        <v>0.743343472480774</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G859" t="n">
-        <v>0.696117877960205</v>
+        <v>0.69611781835556</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G861" t="n">
-        <v>0.705317676067352</v>
+        <v>0.705317735671997</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>1.13100004196167</v>
       </c>
       <c r="G863" t="n">
-        <v>0.693664610385895</v>
+        <v>0.69366466999054</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G870" t="n">
-        <v>0.722490549087524</v>
+        <v>0.722490608692169</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G871" t="n">
-        <v>0.716970801353455</v>
+        <v>0.716970860958099</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G872" t="n">
-        <v>0.705317676067352</v>
+        <v>0.705317735671997</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G873" t="n">
-        <v>0.709610939025879</v>
+        <v>0.709610879421234</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G874" t="n">
-        <v>0.716970801353455</v>
+        <v>0.716970860958099</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G875" t="n">
-        <v>0.72187739610672</v>
+        <v>0.721877336502075</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>1.1710000038147</v>
       </c>
       <c r="G876" t="n">
-        <v>0.718197345733643</v>
+        <v>0.718197405338287</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G878" t="n">
-        <v>0.720650613307953</v>
+        <v>0.720650672912598</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G880" t="n">
-        <v>0.722490549087524</v>
+        <v>0.722490608692169</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G882" t="n">
-        <v>0.753156721591949</v>
+        <v>0.753156661987305</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G883" t="n">
-        <v>0.745183527469635</v>
+        <v>0.74518346786499</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G884" t="n">
-        <v>0.745183527469635</v>
+        <v>0.74518346786499</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>1.21599996089935</v>
       </c>
       <c r="G885" t="n">
-        <v>0.745796799659729</v>
+        <v>0.745796740055084</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>1.22099995613098</v>
       </c>
       <c r="G886" t="n">
-        <v>0.748863339424133</v>
+        <v>0.748863399028778</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.24300003051758</v>
       </c>
       <c r="G887" t="n">
-        <v>0.762356519699097</v>
+        <v>0.762356460094452</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>1.24699997901917</v>
       </c>
       <c r="G888" t="n">
-        <v>0.764809668064117</v>
+        <v>0.764809727668762</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G892" t="n">
-        <v>0.775849401950836</v>
+        <v>0.775849521160126</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.25</v>
       </c>
       <c r="G894" t="n">
-        <v>0.766649723052979</v>
+        <v>0.766649663448334</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G895" t="n">
-        <v>0.761743128299713</v>
+        <v>0.761743068695068</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G897" t="n">
-        <v>0.763583064079285</v>
+        <v>0.763583123683929</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>1.24699997901917</v>
       </c>
       <c r="G898" t="n">
-        <v>0.764809668064117</v>
+        <v>0.764809727668762</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>1.21099996566772</v>
       </c>
       <c r="G900" t="n">
-        <v>0.74273020029068</v>
+        <v>0.742730140686035</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G901" t="n">
-        <v>0.753156721591949</v>
+        <v>0.753156661987305</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G903" t="n">
-        <v>0.753156721591949</v>
+        <v>0.753156661987305</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G905" t="n">
-        <v>0.788729190826416</v>
+        <v>0.788729131221771</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G906" t="n">
-        <v>0.806515455245972</v>
+        <v>0.806515514850616</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G909" t="n">
-        <v>0.781982660293579</v>
+        <v>0.781982600688934</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>1.25</v>
       </c>
       <c r="G910" t="n">
-        <v>0.766649723052979</v>
+        <v>0.766649663448334</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>1.21099996566772</v>
       </c>
       <c r="G911" t="n">
-        <v>0.74273020029068</v>
+        <v>0.742730140686035</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>1.21099996566772</v>
       </c>
       <c r="G912" t="n">
-        <v>0.74273020029068</v>
+        <v>0.742730140686035</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G913" t="n">
-        <v>0.724943935871124</v>
+        <v>0.724943995475769</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G914" t="n">
-        <v>0.732303738594055</v>
+        <v>0.7323037981987</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G921" t="n">
-        <v>0.732303738594055</v>
+        <v>0.7323037981987</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.21099996566772</v>
       </c>
       <c r="G923" t="n">
-        <v>0.74273020029068</v>
+        <v>0.742730140686035</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G924" t="n">
-        <v>0.745183527469635</v>
+        <v>0.74518346786499</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G926" t="n">
-        <v>0.792409062385559</v>
+        <v>0.792409121990204</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G927" t="n">
-        <v>0.781982660293579</v>
+        <v>0.781982600688934</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>1.25</v>
       </c>
       <c r="G929" t="n">
-        <v>0.766649723052979</v>
+        <v>0.766649663448334</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G931" t="n">
-        <v>0.788729190826416</v>
+        <v>0.788729131221771</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>1.25</v>
       </c>
       <c r="G932" t="n">
-        <v>0.766649723052979</v>
+        <v>0.766649663448334</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G935" t="n">
-        <v>0.763583064079285</v>
+        <v>0.763583123683929</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G940" t="n">
-        <v>0.849447786808014</v>
+        <v>0.849447846412659</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G941" t="n">
-        <v>0.834114849567413</v>
+        <v>0.834114909172058</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G942" t="n">
-        <v>0.834114849567413</v>
+        <v>0.834114909172058</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G944" t="n">
-        <v>0.832888185977936</v>
+        <v>0.832888305187225</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G946" t="n">
-        <v>0.840248048305511</v>
+        <v>0.840247988700867</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G947" t="n">
-        <v>0.829208254814148</v>
+        <v>0.829208314418793</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>1.27600002288818</v>
       </c>
       <c r="G948" t="n">
-        <v>0.782595992088318</v>
+        <v>0.782596051692963</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>1.26300001144409</v>
       </c>
       <c r="G949" t="n">
-        <v>0.774622857570648</v>
+        <v>0.774622917175293</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G950" t="n">
-        <v>0.754383265972137</v>
+        <v>0.754383206367493</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>1.23099994659424</v>
       </c>
       <c r="G951" t="n">
-        <v>0.754996538162231</v>
+        <v>0.754996597766876</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G952" t="n">
-        <v>0.761743128299713</v>
+        <v>0.761743068695068</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>1.20099997520447</v>
       </c>
       <c r="G955" t="n">
-        <v>0.736597061157227</v>
+        <v>0.736597001552582</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>1.18599998950958</v>
       </c>
       <c r="G956" t="n">
-        <v>0.72739714384079</v>
+        <v>0.727397203445435</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G961" t="n">
-        <v>0.754383265972137</v>
+        <v>0.754383206367493</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G962" t="n">
-        <v>0.775849401950836</v>
+        <v>0.775849521160126</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G963" t="n">
-        <v>0.780142605304718</v>
+        <v>0.780142664909363</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>1.29900002479553</v>
       </c>
       <c r="G966" t="n">
-        <v>0.796702265739441</v>
+        <v>0.796702325344086</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G968" t="n">
-        <v>0.771556198596954</v>
+        <v>0.771556258201599</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G971" t="n">
-        <v>0.781982660293579</v>
+        <v>0.781982600688934</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G972" t="n">
-        <v>0.834114849567413</v>
+        <v>0.834114909172058</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G981" t="n">
-        <v>0.981311500072479</v>
+        <v>0.981311559677124</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G982" t="n">
-        <v>0.94451242685318</v>
+        <v>0.94451230764389</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G984" t="n">
-        <v>0.961685359477997</v>
+        <v>0.961685299873352</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G986" t="n">
-        <v>0.931019306182861</v>
+        <v>0.931019365787506</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G988" t="n">
-        <v>0.875820517539978</v>
+        <v>0.875820577144623</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G991" t="n">
-        <v>0.863554239273071</v>
+        <v>0.863554120063782</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>1.53100001811981</v>
       </c>
       <c r="G994" t="n">
-        <v>0.938992559909821</v>
+        <v>0.938992500305176</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>1.52699995040894</v>
       </c>
       <c r="G996" t="n">
-        <v>0.936539232730865</v>
+        <v>0.936539173126221</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>1.49300003051758</v>
       </c>
       <c r="G997" t="n">
-        <v>0.915686368942261</v>
+        <v>0.915686428546906</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G998" t="n">
-        <v>0.935312569141388</v>
+        <v>0.935312628746033</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1004" t="n">
-        <v>0.96291196346283</v>
+        <v>0.962912023067474</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.04141688346863</v>
+        <v>1.04141676425934</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G1007" t="n">
-        <v>1.05122995376587</v>
+        <v>1.05123007297516</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.0395770072937</v>
+        <v>1.03957688808441</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.01933741569519</v>
+        <v>1.0193372964859</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>1.63900005817413</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.00523102283478</v>
+        <v>1.00523114204407</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.00277781486511</v>
+        <v>1.00277769565582</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1014" t="n">
-        <v>0.980085015296936</v>
+        <v>0.980084896087646</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1015" t="n">
-        <v>0.980085015296936</v>
+        <v>0.980084896087646</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>1.57599997520447</v>
       </c>
       <c r="G1017" t="n">
-        <v>0.966591954231262</v>
+        <v>0.966591894626617</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1018" t="n">
-        <v>0.94451242685318</v>
+        <v>0.94451230764389</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1020" t="n">
-        <v>0.956778824329376</v>
+        <v>0.956778764724731</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1022" t="n">
-        <v>0.965978682041168</v>
+        <v>0.965978562831879</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G1023" t="n">
-        <v>0.967205166816711</v>
+        <v>0.967205226421356</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1025" t="n">
-        <v>0.980085015296936</v>
+        <v>0.980084896087646</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G1027" t="n">
-        <v>0.906486630439758</v>
+        <v>0.906486511230469</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1028" t="n">
-        <v>0.864780783653259</v>
+        <v>0.864780843257904</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1029" t="n">
-        <v>0.858647644519806</v>
+        <v>0.858647584915161</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1031" t="n">
-        <v>0.815715193748474</v>
+        <v>0.815715253353119</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G1033" t="n">
-        <v>0.767876327037811</v>
+        <v>0.767876267433167</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>1.26699995994568</v>
       </c>
       <c r="G1034" t="n">
-        <v>0.777076125144958</v>
+        <v>0.777076065540314</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G1038" t="n">
-        <v>0.781982660293579</v>
+        <v>0.781982600688934</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>1.2940000295639</v>
       </c>
       <c r="G1039" t="n">
-        <v>0.793635785579681</v>
+        <v>0.793635725975037</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G1046" t="n">
-        <v>0.806515455245972</v>
+        <v>0.806515514850616</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>1.30200004577637</v>
       </c>
       <c r="G1047" t="n">
-        <v>0.798542320728302</v>
+        <v>0.798542380332947</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1050" t="n">
-        <v>0.803448855876923</v>
+        <v>0.803448796272278</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>1.28699994087219</v>
       </c>
       <c r="G1052" t="n">
-        <v>0.789342522621155</v>
+        <v>0.789342403411865</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G1055" t="n">
-        <v>0.70899760723114</v>
+        <v>0.708997666835785</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>1.13699996471405</v>
       </c>
       <c r="G1056" t="n">
-        <v>0.697344481945038</v>
+        <v>0.697344541549683</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>1.07299995422363</v>
       </c>
       <c r="G1057" t="n">
-        <v>0.658092021942139</v>
+        <v>0.658092081546783</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>1.04299998283386</v>
       </c>
       <c r="G1058" t="n">
-        <v>0.639692425727844</v>
+        <v>0.639692485332489</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>0.972500026226044</v>
       </c>
       <c r="G1060" t="n">
-        <v>0.596453487873077</v>
+        <v>0.596453428268433</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.572227299213409</v>
+        <v>0.572227358818054</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.49678897857666</v>
+        <v>0.496789008378983</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.451403319835663</v>
+        <v>0.451403349637985</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>0.726999998092651</v>
       </c>
       <c r="G1068" t="n">
-        <v>0.445883452892303</v>
+        <v>0.445883482694626</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.47225621342659</v>
+        <v>0.472256153821945</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.461216419935226</v>
+        <v>0.461216449737549</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.474709451198578</v>
+        <v>0.4747094810009</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.49065575003624</v>
+        <v>0.490655779838562</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>0.816999971866608</v>
       </c>
       <c r="G1074" t="n">
-        <v>0.501082241535187</v>
+        <v>0.501082181930542</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.469802886247635</v>
+        <v>0.469802916049957</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1077" t="n">
-        <v>0.417057424783707</v>
+        <v>0.417057454586029</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>0.679000020027161</v>
       </c>
       <c r="G1078" t="n">
-        <v>0.416444092988968</v>
+        <v>0.416444152593613</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1080" t="n">
-        <v>0.394977897405624</v>
+        <v>0.394977927207947</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>0.679000020027161</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.416444092988968</v>
+        <v>0.416444152593613</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.434230357408524</v>
+        <v>0.434230387210846</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.49678897857666</v>
+        <v>0.496789008378983</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>0.816999971866608</v>
       </c>
       <c r="G1089" t="n">
-        <v>0.501082241535187</v>
+        <v>0.501082181930542</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>0.915000021457672</v>
       </c>
       <c r="G1093" t="n">
-        <v>0.561187505722046</v>
+        <v>0.561187565326691</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>0.880999982357025</v>
       </c>
       <c r="G1096" t="n">
-        <v>0.540334641933441</v>
+        <v>0.540334701538086</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G1100" t="n">
-        <v>0.51212203502655</v>
+        <v>0.512121975421906</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.506602048873901</v>
+        <v>0.506602108478546</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>0.83899998664856</v>
       </c>
       <c r="G1105" t="n">
-        <v>0.514575183391571</v>
+        <v>0.514575242996216</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>0.830999970436096</v>
       </c>
       <c r="G1108" t="n">
-        <v>0.509668707847595</v>
+        <v>0.50966864824295</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>0.820999979972839</v>
       </c>
       <c r="G1109" t="n">
-        <v>0.503535509109497</v>
+        <v>0.503535449504852</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>0.848999977111816</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.520708441734314</v>
+        <v>0.520708382129669</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1118" t="n">
-        <v>0.545854568481445</v>
+        <v>0.545854508876801</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G1122" t="n">
-        <v>0.61086642742157</v>
+        <v>0.610866487026215</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1124" t="n">
-        <v>0.643985629081726</v>
+        <v>0.643985688686371</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>1.07400000095367</v>
       </c>
       <c r="G1125" t="n">
-        <v>0.658705353736877</v>
+        <v>0.658705472946167</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>1</v>
       </c>
       <c r="G1126" t="n">
-        <v>0.613319754600525</v>
+        <v>0.61331969499588</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G1127" t="n">
-        <v>0.61086642742157</v>
+        <v>0.610866487026215</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1130" t="n">
-        <v>0.56916069984436</v>
+        <v>0.569160640239716</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>0.85699999332428</v>
       </c>
       <c r="G1138" t="n">
-        <v>0.525614976882935</v>
+        <v>0.525615036487579</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1140" t="n">
-        <v>0.527454972267151</v>
+        <v>0.527455031871796</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>0.85699999332428</v>
       </c>
       <c r="G1143" t="n">
-        <v>0.525614976882935</v>
+        <v>0.525615036487579</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>0.845000028610229</v>
       </c>
       <c r="G1146" t="n">
-        <v>0.518255174160004</v>
+        <v>0.518255233764648</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1147" t="n">
-        <v>0.528681635856628</v>
+        <v>0.528681576251984</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>0.83899998664856</v>
       </c>
       <c r="G1148" t="n">
-        <v>0.514575183391571</v>
+        <v>0.514575242996216</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1149" t="n">
-        <v>0.52254843711853</v>
+        <v>0.522548377513885</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>0.859000027179718</v>
       </c>
       <c r="G1150" t="n">
-        <v>0.526841700077057</v>
+        <v>0.526841640472412</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1151" t="n">
-        <v>0.534814834594727</v>
+        <v>0.534814774990082</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.555054306983948</v>
+        <v>0.555054366588593</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1156" t="n">
-        <v>0.542174577713013</v>
+        <v>0.542174637317657</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1157" t="n">
-        <v>0.545854568481445</v>
+        <v>0.545854508876801</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1158" t="n">
-        <v>0.545854568481445</v>
+        <v>0.545854508876801</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>0.879000008106232</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.539108037948608</v>
+        <v>0.539108097553253</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.542174577713013</v>
+        <v>0.542174637317657</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>0.879000008106232</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.539108037948608</v>
+        <v>0.539108097553253</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>0.890999972820282</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.546467840671539</v>
+        <v>0.546467900276184</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.56425416469574</v>
+        <v>0.564254224300385</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1167" t="n">
-        <v>0.575293958187103</v>
+        <v>0.575293898582458</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>0.907000005245209</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.55628103017807</v>
+        <v>0.556280970573425</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.567320764064789</v>
+        <v>0.567320704460144</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G1171" t="n">
-        <v>0.604733228683472</v>
+        <v>0.604733288288116</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.582653760910034</v>
+        <v>0.582653701305389</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>0.939000010490417</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.575907230377197</v>
+        <v>0.575907289981842</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>0.930999994277954</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.571000695228577</v>
+        <v>0.571000635623932</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>0.962999999523163</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.590626955032349</v>
+        <v>0.590626895427704</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>0.962999999523163</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.590626955032349</v>
+        <v>0.590626895427704</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>0.964999973773956</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.591853559017181</v>
+        <v>0.591853499412537</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.588786900043488</v>
+        <v>0.588786959648132</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.587560296058655</v>
+        <v>0.5875603556633</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.578973829746246</v>
+        <v>0.578973770141602</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.56916069984436</v>
+        <v>0.569160640239716</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>0.902999997138977</v>
       </c>
       <c r="G1186" t="n">
-        <v>0.55382776260376</v>
+        <v>0.553827702999115</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.572227299213409</v>
+        <v>0.572227358818054</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.547081172466278</v>
+        <v>0.547081232070923</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>0.939000010490417</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.575907230377197</v>
+        <v>0.575907289981842</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.56916069984436</v>
+        <v>0.569160640239716</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.56916069984436</v>
+        <v>0.569160640239716</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.59246689081192</v>
+        <v>0.592466831207275</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>0.89300000667572</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.547694563865662</v>
+        <v>0.547694504261017</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.555667698383331</v>
+        <v>0.555667638778687</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G1204" t="n">
-        <v>0.555054306983948</v>
+        <v>0.555054366588593</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>0.91100001335144</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.558734357357025</v>
+        <v>0.55873429775238</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.572227299213409</v>
+        <v>0.572227358818054</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.571614027023315</v>
+        <v>0.571613967418671</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.566707491874695</v>
+        <v>0.56670743227005</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G1219" t="n">
-        <v>0.566707491874695</v>
+        <v>0.56670743227005</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G1220" t="n">
-        <v>0.566707491874695</v>
+        <v>0.56670743227005</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G1224" t="n">
-        <v>0.597373366355896</v>
+        <v>0.597373425960541</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.565480768680573</v>
+        <v>0.565480828285217</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.572227299213409</v>
+        <v>0.572227358818054</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>0.967000007629395</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.593080163002014</v>
+        <v>0.593080222606659</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.588786900043488</v>
+        <v>0.588786959648132</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.619452953338623</v>
+        <v>0.619452893733978</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.680784940719604</v>
+        <v>0.68078488111496</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>1.15799999237061</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.710224270820618</v>
+        <v>0.710224211215973</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1243" t="n">
-        <v>0.71145087480545</v>
+        <v>0.711450815200806</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G1245" t="n">
-        <v>0.70899760723114</v>
+        <v>0.708997666835785</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1247" t="n">
-        <v>0.788729190826416</v>
+        <v>0.788729131221771</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.775236189365387</v>
+        <v>0.775236248970032</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G1250" t="n">
-        <v>0.780142605304718</v>
+        <v>0.780142664909363</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1252" t="n">
-        <v>0.754383265972137</v>
+        <v>0.754383206367493</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>1.25</v>
       </c>
       <c r="G1253" t="n">
-        <v>0.766649723052979</v>
+        <v>0.766649663448334</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.743343591690063</v>
+        <v>0.743343472480774</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.739663541316986</v>
+        <v>0.739663660526276</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1262" t="n">
-        <v>0.759289860725403</v>
+        <v>0.759289920330048</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.723717272281647</v>
+        <v>0.723717212677002</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.723717272281647</v>
+        <v>0.723717212677002</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1270" t="n">
-        <v>0.724943935871124</v>
+        <v>0.724943995475769</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1272" t="n">
-        <v>0.743343591690063</v>
+        <v>0.743343472480774</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G1273" t="n">
-        <v>0.737210273742676</v>
+        <v>0.737210333347321</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.761743128299713</v>
+        <v>0.761743068695068</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1281" t="n">
-        <v>0.720037400722504</v>
+        <v>0.720037341117859</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G1282" t="n">
-        <v>0.713904142379761</v>
+        <v>0.713904201984406</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1283" t="n">
-        <v>0.717584133148193</v>
+        <v>0.717584073543549</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1285" t="n">
-        <v>0.723717272281647</v>
+        <v>0.723717212677002</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G1288" t="n">
-        <v>0.706544280052185</v>
+        <v>0.70654433965683</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>1.14800000190735</v>
       </c>
       <c r="G1289" t="n">
-        <v>0.70409107208252</v>
+        <v>0.704091012477875</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G1291" t="n">
-        <v>0.688144743442535</v>
+        <v>0.688144683837891</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1293" t="n">
-        <v>0.693051278591156</v>
+        <v>0.693051338195801</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.70899760723114</v>
+        <v>0.708997666835785</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.720037400722504</v>
+        <v>0.720037341117859</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1299" t="n">
-        <v>0.743343591690063</v>
+        <v>0.743343472480774</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1304" t="n">
-        <v>0.759289860725403</v>
+        <v>0.759289920330048</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1306" t="n">
-        <v>0.762969732284546</v>
+        <v>0.762969791889191</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G1310" t="n">
-        <v>0.794862329959869</v>
+        <v>0.794862389564514</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>1.32200002670288</v>
       </c>
       <c r="G1312" t="n">
-        <v>0.810808777809143</v>
+        <v>0.810808718204498</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1314" t="n">
-        <v>0.824301719665527</v>
+        <v>0.824301660060883</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.803448855876923</v>
+        <v>0.803448796272278</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1320" t="n">
-        <v>0.792409062385559</v>
+        <v>0.792409121990204</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1321" t="n">
-        <v>0.815715193748474</v>
+        <v>0.815715253353119</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G1323" t="n">
-        <v>0.841474652290344</v>
+        <v>0.841474711894989</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1324" t="n">
-        <v>0.858647644519806</v>
+        <v>0.858647584915161</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1325" t="n">
-        <v>0.858647644519806</v>
+        <v>0.858647584915161</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>1.38399994373322</v>
       </c>
       <c r="G1326" t="n">
-        <v>0.84883451461792</v>
+        <v>0.848834455013275</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G1327" t="n">
-        <v>0.829208254814148</v>
+        <v>0.829208314418793</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1328" t="n">
-        <v>0.840248048305511</v>
+        <v>0.840247988700867</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1334" t="n">
-        <v>0.851287841796875</v>
+        <v>0.85128778219223</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1335" t="n">
-        <v>0.834114849567413</v>
+        <v>0.834114909172058</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1341" t="n">
-        <v>0.834114849567413</v>
+        <v>0.834114909172058</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G1342" t="n">
-        <v>0.841474652290344</v>
+        <v>0.841474711894989</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1345" t="n">
-        <v>0.815715193748474</v>
+        <v>0.815715253353119</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1347" t="n">
-        <v>0.803448855876923</v>
+        <v>0.803448796272278</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G1349" t="n">
-        <v>0.853741109371185</v>
+        <v>0.853741049766541</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1351" t="n">
-        <v>0.8770472407341</v>
+        <v>0.877047181129456</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1355" t="n">
-        <v>0.864780783653259</v>
+        <v>0.864780843257904</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G1356" t="n">
-        <v>0.880727112293243</v>
+        <v>0.880727171897888</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>1.44599997997284</v>
       </c>
       <c r="G1359" t="n">
-        <v>0.886860370635986</v>
+        <v>0.886860251426697</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>1.42599999904633</v>
       </c>
       <c r="G1360" t="n">
-        <v>0.87459397315979</v>
+        <v>0.874593913555145</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G1361" t="n">
-        <v>0.875820517539978</v>
+        <v>0.875820577144623</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1362" t="n">
-        <v>0.851287841796875</v>
+        <v>0.85128778219223</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1364" t="n">
-        <v>0.863554239273071</v>
+        <v>0.863554120063782</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1365" t="n">
-        <v>0.863554239273071</v>
+        <v>0.863554120063782</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1368" t="n">
-        <v>0.834114849567413</v>
+        <v>0.834114909172058</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1373" t="n">
-        <v>0.834114849567413</v>
+        <v>0.834114909172058</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G1374" t="n">
-        <v>0.861100971698761</v>
+        <v>0.861100912094116</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1375" t="n">
-        <v>0.863554239273071</v>
+        <v>0.863554120063782</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G1376" t="n">
-        <v>0.861100971698761</v>
+        <v>0.861100912094116</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1377" t="n">
-        <v>0.866007506847382</v>
+        <v>0.866007447242737</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G1381" t="n">
-        <v>0.940832495689392</v>
+        <v>0.940832436084747</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G1383" t="n">
-        <v>0.915073037147522</v>
+        <v>0.915073096752167</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1385" t="n">
-        <v>0.96291196346283</v>
+        <v>0.962912023067474</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G1386" t="n">
-        <v>0.945739030838013</v>
+        <v>0.945739090442657</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G1389" t="n">
-        <v>0.921206295490265</v>
+        <v>0.921206176280975</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G1394" t="n">
-        <v>0.861100971698761</v>
+        <v>0.861100912094116</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G1395" t="n">
-        <v>0.861100971698761</v>
+        <v>0.861100912094116</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1396" t="n">
-        <v>0.840248048305511</v>
+        <v>0.840247988700867</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1400" t="n">
-        <v>0.82062178850174</v>
+        <v>0.820621848106384</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>1.27600002288818</v>
       </c>
       <c r="G1402" t="n">
-        <v>0.782595992088318</v>
+        <v>0.782596051692963</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G1403" t="n">
-        <v>0.794862329959869</v>
+        <v>0.794862389564514</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>1.29799997806549</v>
       </c>
       <c r="G1404" t="n">
-        <v>0.796089053153992</v>
+        <v>0.796088993549347</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1406" t="n">
-        <v>0.785049200057983</v>
+        <v>0.785049259662628</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1408" t="n">
-        <v>0.754383265972137</v>
+        <v>0.754383206367493</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1409" t="n">
-        <v>0.723717272281647</v>
+        <v>0.723717212677002</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G1410" t="n">
-        <v>0.737210273742676</v>
+        <v>0.737210333347321</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1414" t="n">
-        <v>0.858647644519806</v>
+        <v>0.858647584915161</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1415" t="n">
-        <v>0.866007506847382</v>
+        <v>0.866007447242737</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.852514386177063</v>
+        <v>0.852514445781708</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G1417" t="n">
-        <v>0.850061118602753</v>
+        <v>0.850061178207397</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1423" t="n">
-        <v>0.851287841796875</v>
+        <v>0.85128778219223</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G1424" t="n">
-        <v>0.850061118602753</v>
+        <v>0.850061178207397</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G1425" t="n">
-        <v>0.857420980930328</v>
+        <v>0.857421040534973</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1426" t="n">
-        <v>0.858647644519806</v>
+        <v>0.858647584915161</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1427" t="n">
-        <v>0.864780783653259</v>
+        <v>0.864780843257904</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>1.42599999904633</v>
       </c>
       <c r="G1430" t="n">
-        <v>0.87459397315979</v>
+        <v>0.874593913555145</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>1.43400001525879</v>
       </c>
       <c r="G1431" t="n">
-        <v>0.879500508308411</v>
+        <v>0.879500567913055</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G1432" t="n">
-        <v>0.853741109371185</v>
+        <v>0.853741049766541</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1438" t="n">
-        <v>0.852514386177063</v>
+        <v>0.852514445781708</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>1.42400002479553</v>
       </c>
       <c r="G1439" t="n">
-        <v>0.873367249965668</v>
+        <v>0.873367309570312</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1440" t="n">
-        <v>0.858647644519806</v>
+        <v>0.858647584915161</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G1441" t="n">
-        <v>0.857420980930328</v>
+        <v>0.857421040534973</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1443" t="n">
-        <v>0.866007506847382</v>
+        <v>0.866007447242737</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1444" t="n">
-        <v>0.852514386177063</v>
+        <v>0.852514445781708</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G1445" t="n">
-        <v>0.850061118602753</v>
+        <v>0.850061178207397</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G1447" t="n">
-        <v>0.82307505607605</v>
+        <v>0.823075115680695</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G1451" t="n">
-        <v>0.82307505607605</v>
+        <v>0.823075115680695</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>1.27600002288818</v>
       </c>
       <c r="G1454" t="n">
-        <v>0.782595992088318</v>
+        <v>0.782596051692963</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>1.33200001716614</v>
       </c>
       <c r="G1459" t="n">
-        <v>0.816941916942596</v>
+        <v>0.816941857337952</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1461" t="n">
-        <v>0.803448855876923</v>
+        <v>0.803448796272278</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>1.29799997806549</v>
       </c>
       <c r="G1462" t="n">
-        <v>0.796089053153992</v>
+        <v>0.796088993549347</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1463" t="n">
-        <v>0.785049200057983</v>
+        <v>0.785049259662628</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1464" t="n">
-        <v>0.788729190826416</v>
+        <v>0.788729131221771</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1465" t="n">
-        <v>0.792409062385559</v>
+        <v>0.792409121990204</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1466" t="n">
-        <v>0.781369388103485</v>
+        <v>0.78136932849884</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>1.30200004577637</v>
       </c>
       <c r="G1468" t="n">
-        <v>0.798542320728302</v>
+        <v>0.798542380332947</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1469" t="n">
-        <v>0.788729190826416</v>
+        <v>0.788729131221771</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1470" t="n">
-        <v>0.809582054615021</v>
+        <v>0.809582114219666</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1471" t="n">
-        <v>0.815715193748474</v>
+        <v>0.815715253353119</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1473" t="n">
-        <v>0.834114849567413</v>
+        <v>0.834114909172058</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1474" t="n">
-        <v>0.840248048305511</v>
+        <v>0.840247988700867</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G1475" t="n">
-        <v>0.829208254814148</v>
+        <v>0.829208314418793</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1476" t="n">
-        <v>0.824301719665527</v>
+        <v>0.824301660060883</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1477" t="n">
-        <v>0.856194376945496</v>
+        <v>0.85619443655014</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1478" t="n">
-        <v>0.851287841796875</v>
+        <v>0.85128778219223</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1479" t="n">
-        <v>0.883180439472198</v>
+        <v>0.883180379867554</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>1.44799995422363</v>
       </c>
       <c r="G1480" t="n">
-        <v>0.888086915016174</v>
+        <v>0.888086974620819</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G1481" t="n">
-        <v>0.850061118602753</v>
+        <v>0.850061178207397</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1482" t="n">
-        <v>0.840248048305511</v>
+        <v>0.840247988700867</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1483" t="n">
-        <v>0.840248048305511</v>
+        <v>0.840247988700867</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1484" t="n">
-        <v>0.840248048305511</v>
+        <v>0.840247988700867</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1486" t="n">
-        <v>0.824301719665527</v>
+        <v>0.824301660060883</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G1487" t="n">
-        <v>0.819395184516907</v>
+        <v>0.819395124912262</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1489" t="n">
-        <v>0.824301719665527</v>
+        <v>0.824301660060883</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>1.29799997806549</v>
       </c>
       <c r="G1492" t="n">
-        <v>0.796089053153992</v>
+        <v>0.796088993549347</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1494" t="n">
-        <v>0.824301719665527</v>
+        <v>0.824301660060883</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G1495" t="n">
-        <v>0.82307505607605</v>
+        <v>0.823075115680695</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>1.33200001716614</v>
       </c>
       <c r="G1497" t="n">
-        <v>0.816941916942596</v>
+        <v>0.816941857337952</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1499" t="n">
-        <v>0.809582054615021</v>
+        <v>0.809582114219666</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>1.2940000295639</v>
       </c>
       <c r="G1502" t="n">
-        <v>0.793635785579681</v>
+        <v>0.793635725975037</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1506" t="n">
-        <v>0.743343591690063</v>
+        <v>0.743343472480774</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G1509" t="n">
-        <v>0.722490549087524</v>
+        <v>0.722490608692169</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1512" t="n">
-        <v>0.743343591690063</v>
+        <v>0.743343472480774</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1513" t="n">
-        <v>0.743343591690063</v>
+        <v>0.743343472480774</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>1.18599998950958</v>
       </c>
       <c r="G1515" t="n">
-        <v>0.72739714384079</v>
+        <v>0.727397203445435</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>1.21599996089935</v>
       </c>
       <c r="G1517" t="n">
-        <v>0.745796799659729</v>
+        <v>0.745796740055084</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G1518" t="n">
-        <v>0.731077134609222</v>
+        <v>0.731077075004578</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G1520" t="n">
-        <v>0.738436996936798</v>
+        <v>0.738436937332153</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G1521" t="n">
-        <v>0.731077134609222</v>
+        <v>0.731077075004578</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1522" t="n">
-        <v>0.724943935871124</v>
+        <v>0.724943995475769</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1524" t="n">
-        <v>0.723717272281647</v>
+        <v>0.723717212677002</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1525" t="n">
-        <v>0.723717272281647</v>
+        <v>0.723717212677002</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1526" t="n">
-        <v>0.724943935871124</v>
+        <v>0.724943995475769</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G1530" t="n">
-        <v>0.758063197135925</v>
+        <v>0.758063137531281</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1532" t="n">
-        <v>0.781369388103485</v>
+        <v>0.78136932849884</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G1533" t="n">
-        <v>0.780142605304718</v>
+        <v>0.780142664909363</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1536" t="n">
-        <v>0.788729190826416</v>
+        <v>0.788729131221771</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1538" t="n">
-        <v>0.771556198596954</v>
+        <v>0.771556258201599</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1539" t="n">
-        <v>0.762969732284546</v>
+        <v>0.762969791889191</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1540" t="n">
-        <v>0.775236189365387</v>
+        <v>0.775236248970032</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G1542" t="n">
-        <v>0.731077134609222</v>
+        <v>0.731077075004578</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1547" t="n">
-        <v>0.732303738594055</v>
+        <v>0.7323037981987</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1550" t="n">
-        <v>0.754383265972137</v>
+        <v>0.754383206367493</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1554" t="n">
-        <v>0.739663541316986</v>
+        <v>0.739663660526276</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1557" t="n">
-        <v>0.71145087480545</v>
+        <v>0.711450815200806</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1558" t="n">
-        <v>0.720037400722504</v>
+        <v>0.720037341117859</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>1.14800000190735</v>
       </c>
       <c r="G1562" t="n">
-        <v>0.70409107208252</v>
+        <v>0.704091012477875</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G1563" t="n">
-        <v>0.696731269359589</v>
+        <v>0.696731209754944</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1564" t="n">
-        <v>0.705317676067352</v>
+        <v>0.705317735671997</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>1.06200003623962</v>
       </c>
       <c r="G1565" t="n">
-        <v>0.651345551013947</v>
+        <v>0.651345610618591</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>1.12399995326996</v>
       </c>
       <c r="G1567" t="n">
-        <v>0.689371347427368</v>
+        <v>0.689371407032013</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1568" t="n">
-        <v>0.631719291210175</v>
+        <v>0.631719350814819</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1571" t="n">
-        <v>0.517641842365265</v>
+        <v>0.51764190196991</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>0.788999974727631</v>
       </c>
       <c r="G1572" t="n">
-        <v>0.483909249305725</v>
+        <v>0.483909219503403</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1573" t="n">
-        <v>0.480842679738998</v>
+        <v>0.480842649936676</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G1574" t="n">
-        <v>0.52009516954422</v>
+        <v>0.520095109939575</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>0.802999973297119</v>
       </c>
       <c r="G1575" t="n">
-        <v>0.492495715618134</v>
+        <v>0.492495775222778</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>0.814999997615814</v>
       </c>
       <c r="G1578" t="n">
-        <v>0.499855607748032</v>
+        <v>0.499855577945709</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>0.897000014781952</v>
       </c>
       <c r="G1582" t="n">
-        <v>0.550147831439972</v>
+        <v>0.550147771835327</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>0.879000008106232</v>
       </c>
       <c r="G1584" t="n">
-        <v>0.539108037948608</v>
+        <v>0.539108097553253</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1586" t="n">
-        <v>0.534814834594727</v>
+        <v>0.534814774990082</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G1588" t="n">
-        <v>0.565480768680573</v>
+        <v>0.565480828285217</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>0.890999972820282</v>
       </c>
       <c r="G1589" t="n">
-        <v>0.546467840671539</v>
+        <v>0.546467900276184</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1596" t="n">
-        <v>0.510281980037689</v>
+        <v>0.510282039642334</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1598" t="n">
-        <v>0.517641842365265</v>
+        <v>0.51764190196991</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1599" t="n">
-        <v>0.528681635856628</v>
+        <v>0.528681576251984</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1602" t="n">
-        <v>0.56425416469574</v>
+        <v>0.564254224300385</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>0.859000027179718</v>
       </c>
       <c r="G1609" t="n">
-        <v>0.526841700077057</v>
+        <v>0.526841640472412</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>0.869000017642975</v>
       </c>
       <c r="G1611" t="n">
-        <v>0.532974898815155</v>
+        <v>0.53297483921051</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>0.830999970436096</v>
       </c>
       <c r="G1613" t="n">
-        <v>0.509668707847595</v>
+        <v>0.50966864824295</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1614" t="n">
-        <v>0.517641842365265</v>
+        <v>0.51764190196991</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1615" t="n">
-        <v>0.509055376052856</v>
+        <v>0.509055316448212</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G1617" t="n">
-        <v>0.52009516954422</v>
+        <v>0.520095109939575</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1618" t="n">
-        <v>0.509055376052856</v>
+        <v>0.509055316448212</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1619" t="n">
-        <v>0.509055376052856</v>
+        <v>0.509055316448212</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G1620" t="n">
-        <v>0.519481778144836</v>
+        <v>0.519481837749481</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1621" t="n">
-        <v>0.527454972267151</v>
+        <v>0.527455031871796</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>0.869000017642975</v>
       </c>
       <c r="G1625" t="n">
-        <v>0.532974898815155</v>
+        <v>0.53297483921051</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1626" t="n">
-        <v>0.527454972267151</v>
+        <v>0.527455031871796</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1629" t="n">
-        <v>0.572227299213409</v>
+        <v>0.572227358818054</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>0.950999975204468</v>
       </c>
       <c r="G1630" t="n">
-        <v>0.583267033100128</v>
+        <v>0.583267092704773</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G1631" t="n">
-        <v>0.574067234992981</v>
+        <v>0.574067294597626</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G1633" t="n">
-        <v>0.647665619850159</v>
+        <v>0.647665679454803</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1634" t="n">
-        <v>0.619452953338623</v>
+        <v>0.619452893733978</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G1637" t="n">
-        <v>0.628039479255676</v>
+        <v>0.628039419651031</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1638" t="n">
-        <v>0.619452953338623</v>
+        <v>0.619452893733978</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1640" t="n">
-        <v>0.545854568481445</v>
+        <v>0.545854508876801</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>0.89300000667572</v>
       </c>
       <c r="G1642" t="n">
-        <v>0.547694563865662</v>
+        <v>0.547694504261017</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>0.869000017642975</v>
       </c>
       <c r="G1644" t="n">
-        <v>0.532974898815155</v>
+        <v>0.53297483921051</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>0.887000024318695</v>
       </c>
       <c r="G1646" t="n">
-        <v>0.544014632701874</v>
+        <v>0.544014573097229</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G1648" t="n">
-        <v>0.547081172466278</v>
+        <v>0.547081232070923</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1652" t="n">
-        <v>0.527454972267151</v>
+        <v>0.527455031871796</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G1655" t="n">
-        <v>0.51212203502655</v>
+        <v>0.512121975421906</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>0.788999974727631</v>
       </c>
       <c r="G1657" t="n">
-        <v>0.483909249305725</v>
+        <v>0.483909219503403</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>0.83899998664856</v>
       </c>
       <c r="G1659" t="n">
-        <v>0.514575183391571</v>
+        <v>0.514575242996216</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1660" t="n">
-        <v>0.509055376052856</v>
+        <v>0.509055316448212</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1664" t="n">
-        <v>0.482069343328476</v>
+        <v>0.482069283723831</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>0.785000026226044</v>
       </c>
       <c r="G1665" t="n">
-        <v>0.481455981731415</v>
+        <v>0.481456011533737</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1668" t="n">
-        <v>0.480842679738998</v>
+        <v>0.480842649936676</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1669" t="n">
-        <v>0.509055376052856</v>
+        <v>0.509055316448212</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>0.930999994277954</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.571000695228577</v>
+        <v>0.571000635623932</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>0.922999978065491</v>
       </c>
       <c r="G1673" t="n">
-        <v>0.566094100475311</v>
+        <v>0.566094160079956</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>0.915000021457672</v>
       </c>
       <c r="G1674" t="n">
-        <v>0.561187505722046</v>
+        <v>0.561187565326691</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>0.915000021457672</v>
       </c>
       <c r="G1675" t="n">
-        <v>0.561187505722046</v>
+        <v>0.561187565326691</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G1676" t="n">
-        <v>0.566707491874695</v>
+        <v>0.56670743227005</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>0.922999978065491</v>
       </c>
       <c r="G1678" t="n">
-        <v>0.566094100475311</v>
+        <v>0.566094160079956</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>0.890999972820282</v>
       </c>
       <c r="G1680" t="n">
-        <v>0.546467840671539</v>
+        <v>0.546467900276184</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>0.880999982357025</v>
       </c>
       <c r="G1686" t="n">
-        <v>0.540334641933441</v>
+        <v>0.540334701538086</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>0.887000024318695</v>
       </c>
       <c r="G1691" t="n">
-        <v>0.544014632701874</v>
+        <v>0.544014573097229</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.527454972267151</v>
+        <v>0.527455031871796</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1698" t="n">
-        <v>0.509055376052856</v>
+        <v>0.509055316448212</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1699" t="n">
-        <v>0.506602048873901</v>
+        <v>0.506602108478546</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1701" t="n">
-        <v>0.49065575003624</v>
+        <v>0.490655779838562</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1702" t="n">
-        <v>0.485749244689941</v>
+        <v>0.485749214887619</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1703" t="n">
-        <v>0.485749244689941</v>
+        <v>0.485749214887619</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>0.809000015258789</v>
       </c>
       <c r="G1704" t="n">
-        <v>0.496175706386566</v>
+        <v>0.496175676584244</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1705" t="n">
-        <v>0.484522551298141</v>
+        <v>0.484522610902786</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1708" t="n">
-        <v>0.474709451198578</v>
+        <v>0.4747094810009</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1709" t="n">
-        <v>0.474709451198578</v>
+        <v>0.4747094810009</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1710" t="n">
-        <v>0.47225621342659</v>
+        <v>0.472256153821945</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G1711" t="n">
-        <v>0.456923216581345</v>
+        <v>0.456923186779022</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1712" t="n">
-        <v>0.453243315219879</v>
+        <v>0.453243255615234</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1713" t="n">
-        <v>0.436683624982834</v>
+        <v>0.436683654785156</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1715" t="n">
-        <v>0.437910258769989</v>
+        <v>0.437910288572311</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G1717" t="n">
-        <v>0.43239039182663</v>
+        <v>0.432390421628952</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>0.712999999523163</v>
       </c>
       <c r="G1719" t="n">
-        <v>0.437296986579895</v>
+        <v>0.437296956777573</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G1720" t="n">
-        <v>0.43852362036705</v>
+        <v>0.438523590564728</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1722" t="n">
-        <v>0.428097188472748</v>
+        <v>0.42809721827507</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1723" t="n">
-        <v>0.429323822259903</v>
+        <v>0.429323792457581</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1724" t="n">
-        <v>0.414604127407074</v>
+        <v>0.414604157209396</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>0.66100001335144</v>
       </c>
       <c r="G1725" t="n">
-        <v>0.405404388904572</v>
+        <v>0.405404359102249</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1726" t="n">
-        <v>0.417057424783707</v>
+        <v>0.417057454586029</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1728" t="n">
-        <v>0.429323822259903</v>
+        <v>0.429323792457581</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1729" t="n">
-        <v>0.431777119636536</v>
+        <v>0.431777060031891</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1731" t="n">
-        <v>0.433003753423691</v>
+        <v>0.433003723621368</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1732" t="n">
-        <v>0.49065575003624</v>
+        <v>0.490655779838562</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1733" t="n">
-        <v>0.527454972267151</v>
+        <v>0.527455031871796</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>0.859000027179718</v>
       </c>
       <c r="G1747" t="n">
-        <v>0.526841700077057</v>
+        <v>0.526841640472412</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G1749" t="n">
-        <v>0.586333692073822</v>
+        <v>0.586333632469177</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1750" t="n">
-        <v>0.575293958187103</v>
+        <v>0.575293898582458</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G1751" t="n">
-        <v>0.567320764064789</v>
+        <v>0.567320704460144</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1754" t="n">
-        <v>0.542174577713013</v>
+        <v>0.542174637317657</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1756" t="n">
-        <v>0.525001704692841</v>
+        <v>0.525001645088196</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1759" t="n">
-        <v>0.534814834594727</v>
+        <v>0.534814774990082</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1761" t="n">
-        <v>0.545854568481445</v>
+        <v>0.545854508876801</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1764" t="n">
-        <v>0.525001704692841</v>
+        <v>0.525001645088196</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G1765" t="n">
-        <v>0.519481778144836</v>
+        <v>0.519481837749481</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G1766" t="n">
-        <v>0.519481778144836</v>
+        <v>0.519481837749481</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>0.845000028610229</v>
       </c>
       <c r="G1768" t="n">
-        <v>0.518255174160004</v>
+        <v>0.518255233764648</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1772" t="n">
-        <v>0.528681635856628</v>
+        <v>0.528681576251984</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1773" t="n">
-        <v>0.527454972267151</v>
+        <v>0.527455031871796</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G1778" t="n">
-        <v>0.567934036254883</v>
+        <v>0.567934095859528</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1781" t="n">
-        <v>0.575293958187103</v>
+        <v>0.575293898582458</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>0.950999975204468</v>
       </c>
       <c r="G1787" t="n">
-        <v>0.583267033100128</v>
+        <v>0.583267092704773</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1790" t="n">
-        <v>0.619452953338623</v>
+        <v>0.619452893733978</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1794" t="n">
-        <v>0.674651682376862</v>
+        <v>0.674651741981506</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1795" t="n">
-        <v>0.680784940719604</v>
+        <v>0.68078488111496</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1797" t="n">
-        <v>0.673425078392029</v>
+        <v>0.673425018787384</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>1.09200000762939</v>
       </c>
       <c r="G1798" t="n">
-        <v>0.669745087623596</v>
+        <v>0.669745206832886</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1799" t="n">
-        <v>0.674651682376862</v>
+        <v>0.674651741981506</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1801" t="n">
-        <v>0.674651682376862</v>
+        <v>0.674651741981506</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1802" t="n">
-        <v>0.680784940719604</v>
+        <v>0.68078488111496</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1803" t="n">
-        <v>0.680784940719604</v>
+        <v>0.68078488111496</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1804" t="n">
-        <v>0.680784940719604</v>
+        <v>0.68078488111496</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G1805" t="n">
-        <v>0.688144743442535</v>
+        <v>0.688144683837891</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1808" t="n">
-        <v>0.720037400722504</v>
+        <v>0.720037341117859</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1810" t="n">
-        <v>0.723717272281647</v>
+        <v>0.723717212677002</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1812" t="n">
-        <v>0.732303738594055</v>
+        <v>0.7323037981987</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1814" t="n">
-        <v>0.743343591690063</v>
+        <v>0.743343472480774</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1820" t="n">
-        <v>0.724943935871124</v>
+        <v>0.724943995475769</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G1821" t="n">
-        <v>0.753156721591949</v>
+        <v>0.753156661987305</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>1.11800003051758</v>
       </c>
       <c r="G1822" t="n">
-        <v>0.68569153547287</v>
+        <v>0.685691475868225</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1826" t="n">
-        <v>0.680784940719604</v>
+        <v>0.68078488111496</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1827" t="n">
-        <v>0.680784940719604</v>
+        <v>0.68078488111496</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G1828" t="n">
-        <v>0.688144743442535</v>
+        <v>0.688144683837891</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1831" t="n">
-        <v>0.680784940719604</v>
+        <v>0.68078488111496</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1834" t="n">
-        <v>0.680784940719604</v>
+        <v>0.68078488111496</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1835" t="n">
-        <v>0.643985629081726</v>
+        <v>0.643985688686371</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G1836" t="n">
-        <v>0.628039479255676</v>
+        <v>0.628039419651031</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G1838" t="n">
-        <v>0.647665619850159</v>
+        <v>0.647665679454803</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1839" t="n">
-        <v>0.673425078392029</v>
+        <v>0.673425018787384</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1840" t="n">
-        <v>0.705317676067352</v>
+        <v>0.705317735671997</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1841" t="n">
-        <v>0.705317676067352</v>
+        <v>0.705317735671997</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G1843" t="n">
-        <v>0.696731269359589</v>
+        <v>0.696731209754944</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>1.11800003051758</v>
       </c>
       <c r="G1845" t="n">
-        <v>0.68569153547287</v>
+        <v>0.685691475868225</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1846" t="n">
-        <v>0.680784940719604</v>
+        <v>0.68078488111496</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>1.12399995326996</v>
       </c>
       <c r="G1848" t="n">
-        <v>0.689371347427368</v>
+        <v>0.689371407032013</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G1853" t="n">
-        <v>0.70899760723114</v>
+        <v>0.708997666835785</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1856" t="n">
-        <v>0.754383265972137</v>
+        <v>0.754383206367493</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1857" t="n">
-        <v>0.743343591690063</v>
+        <v>0.743343472480774</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>1.21599996089935</v>
       </c>
       <c r="G1858" t="n">
-        <v>0.745796799659729</v>
+        <v>0.745796740055084</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1860" t="n">
-        <v>0.732303738594055</v>
+        <v>0.7323037981987</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1861" t="n">
-        <v>0.723717272281647</v>
+        <v>0.723717212677002</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>1.18599998950958</v>
       </c>
       <c r="G1862" t="n">
-        <v>0.72739714384079</v>
+        <v>0.727397203445435</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G1864" t="n">
-        <v>0.753156721591949</v>
+        <v>0.753156661987305</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G1865" t="n">
-        <v>0.753156721591949</v>
+        <v>0.753156661987305</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1867" t="n">
-        <v>0.724943935871124</v>
+        <v>0.724943995475769</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -48937,7 +48937,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G1868" t="n">
-        <v>0.706544280052185</v>
+        <v>0.70654433965683</v>
       </c>
       <c r="H1868" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1869" t="n">
-        <v>0.717584133148193</v>
+        <v>0.717584073543549</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G1871" t="n">
-        <v>0.696731269359589</v>
+        <v>0.696731209754944</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G1872" t="n">
-        <v>0.713904142379761</v>
+        <v>0.713904201984406</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1873" t="n">
-        <v>0.71145087480545</v>
+        <v>0.711450815200806</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1874" t="n">
-        <v>0.71145087480545</v>
+        <v>0.711450815200806</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>1.15400004386902</v>
       </c>
       <c r="G1875" t="n">
-        <v>0.707771003246307</v>
+        <v>0.707770943641663</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>1.15400004386902</v>
       </c>
       <c r="G1876" t="n">
-        <v>0.707771003246307</v>
+        <v>0.707770943641663</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1877" t="n">
-        <v>0.705317676067352</v>
+        <v>0.705317735671997</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>1.15400004386902</v>
       </c>
       <c r="G1878" t="n">
-        <v>0.707771003246307</v>
+        <v>0.707770943641663</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1879" t="n">
-        <v>0.71145087480545</v>
+        <v>0.711450815200806</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G1882" t="n">
-        <v>0.688144743442535</v>
+        <v>0.688144683837891</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1883" t="n">
-        <v>0.705317676067352</v>
+        <v>0.705317735671997</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.688144743442535</v>
+        <v>0.688144683837891</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49405,7 +49405,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.673425078392029</v>
+        <v>0.673425018787384</v>
       </c>
       <c r="H1886" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.700411140918732</v>
+        <v>0.700411081314087</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1891" t="n">
-        <v>0.71145087480545</v>
+        <v>0.711450815200806</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49561,7 +49561,7 @@
         <v>1.15799999237061</v>
       </c>
       <c r="G1892" t="n">
-        <v>0.710224270820618</v>
+        <v>0.710224211215973</v>
       </c>
       <c r="H1892" t="s">
         <v>8</v>
@@ -49613,7 +49613,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G1894" t="n">
-        <v>0.716357409954071</v>
+        <v>0.716357469558716</v>
       </c>
       <c r="H1894" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1895" t="n">
-        <v>0.717584133148193</v>
+        <v>0.717584073543549</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49665,7 +49665,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1896" t="n">
-        <v>0.720037400722504</v>
+        <v>0.720037341117859</v>
       </c>
       <c r="H1896" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1899" t="n">
-        <v>0.717584133148193</v>
+        <v>0.717584073543549</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49769,7 +49769,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1900" t="n">
-        <v>0.720037400722504</v>
+        <v>0.720037341117859</v>
       </c>
       <c r="H1900" t="s">
         <v>8</v>
@@ -49847,7 +49847,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G1903" t="n">
-        <v>0.716357409954071</v>
+        <v>0.716357469558716</v>
       </c>
       <c r="H1903" t="s">
         <v>8</v>
@@ -49899,7 +49899,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1905" t="n">
-        <v>0.717584133148193</v>
+        <v>0.717584073543549</v>
       </c>
       <c r="H1905" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1906" t="n">
-        <v>0.717584133148193</v>
+        <v>0.717584073543549</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1910" t="n">
-        <v>0.754383265972137</v>
+        <v>0.754383206367493</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50107,7 +50107,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G1913" t="n">
-        <v>0.753156721591949</v>
+        <v>0.753156661987305</v>
       </c>
       <c r="H1913" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1914" t="n">
-        <v>0.759289860725403</v>
+        <v>0.759289920330048</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50185,7 +50185,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G1916" t="n">
-        <v>0.767876327037811</v>
+        <v>0.767876267433167</v>
       </c>
       <c r="H1916" t="s">
         <v>8</v>
@@ -50211,7 +50211,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1917" t="n">
-        <v>0.775236189365387</v>
+        <v>0.775236248970032</v>
       </c>
       <c r="H1917" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>1.28799998760223</v>
       </c>
       <c r="G1919" t="n">
-        <v>0.789955794811249</v>
+        <v>0.789955854415894</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1921" t="n">
-        <v>0.781369388103485</v>
+        <v>0.78136932849884</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50445,7 +50445,7 @@
         <v>1.28799998760223</v>
       </c>
       <c r="G1926" t="n">
-        <v>0.789955794811249</v>
+        <v>0.789955854415894</v>
       </c>
       <c r="H1926" t="s">
         <v>8</v>
@@ -50471,7 +50471,7 @@
         <v>1.31200003623962</v>
       </c>
       <c r="G1927" t="n">
-        <v>0.8046755194664</v>
+        <v>0.804675459861755</v>
       </c>
       <c r="H1927" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G1929" t="n">
-        <v>0.819395184516907</v>
+        <v>0.819395124912262</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1931" t="n">
-        <v>0.781369388103485</v>
+        <v>0.78136932849884</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50601,7 +50601,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1932" t="n">
-        <v>0.775236189365387</v>
+        <v>0.775236248970032</v>
       </c>
       <c r="H1932" t="s">
         <v>8</v>
@@ -50653,7 +50653,7 @@
         <v>1.21599996089935</v>
       </c>
       <c r="G1934" t="n">
-        <v>0.745796799659729</v>
+        <v>0.745796740055084</v>
       </c>
       <c r="H1934" t="s">
         <v>8</v>
@@ -50757,7 +50757,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1938" t="n">
-        <v>0.759289860725403</v>
+        <v>0.759289920330048</v>
       </c>
       <c r="H1938" t="s">
         <v>8</v>
@@ -50809,7 +50809,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G1940" t="n">
-        <v>0.767876327037811</v>
+        <v>0.767876267433167</v>
       </c>
       <c r="H1940" t="s">
         <v>8</v>
@@ -50835,7 +50835,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1941" t="n">
-        <v>0.781369388103485</v>
+        <v>0.78136932849884</v>
       </c>
       <c r="H1941" t="s">
         <v>8</v>
@@ -50913,7 +50913,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G1944" t="n">
-        <v>0.753156721591949</v>
+        <v>0.753156661987305</v>
       </c>
       <c r="H1944" t="s">
         <v>8</v>
@@ -50991,7 +50991,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G1947" t="n">
-        <v>0.758063197135925</v>
+        <v>0.758063137531281</v>
       </c>
       <c r="H1947" t="s">
         <v>8</v>
@@ -51017,7 +51017,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G1948" t="n">
-        <v>0.780142605304718</v>
+        <v>0.780142664909363</v>
       </c>
       <c r="H1948" t="s">
         <v>8</v>
@@ -51069,7 +51069,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1950" t="n">
-        <v>0.785049200057983</v>
+        <v>0.785049259662628</v>
       </c>
       <c r="H1950" t="s">
         <v>8</v>
@@ -51147,7 +51147,7 @@
         <v>1.27600002288818</v>
       </c>
       <c r="G1953" t="n">
-        <v>0.782595992088318</v>
+        <v>0.782596051692963</v>
       </c>
       <c r="H1953" t="s">
         <v>8</v>
@@ -51173,7 +51173,7 @@
         <v>1.27600002288818</v>
       </c>
       <c r="G1954" t="n">
-        <v>0.782595992088318</v>
+        <v>0.782596051692963</v>
       </c>
       <c r="H1954" t="s">
         <v>8</v>
@@ -51199,7 +51199,7 @@
         <v>1.28799998760223</v>
       </c>
       <c r="G1955" t="n">
-        <v>0.789955794811249</v>
+        <v>0.789955854415894</v>
       </c>
       <c r="H1955" t="s">
         <v>8</v>
@@ -51225,7 +51225,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1956" t="n">
-        <v>0.785049200057983</v>
+        <v>0.785049259662628</v>
       </c>
       <c r="H1956" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1958" t="n">
-        <v>0.775236189365387</v>
+        <v>0.775236248970032</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51303,7 +51303,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1959" t="n">
-        <v>0.775236189365387</v>
+        <v>0.775236248970032</v>
       </c>
       <c r="H1959" t="s">
         <v>8</v>
@@ -51329,7 +51329,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1960" t="n">
-        <v>0.781369388103485</v>
+        <v>0.78136932849884</v>
       </c>
       <c r="H1960" t="s">
         <v>8</v>
@@ -51433,7 +51433,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G1964" t="n">
-        <v>0.794862329959869</v>
+        <v>0.794862389564514</v>
       </c>
       <c r="H1964" t="s">
         <v>8</v>
@@ -51485,7 +51485,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G1966" t="n">
-        <v>0.850061118602753</v>
+        <v>0.850061178207397</v>
       </c>
       <c r="H1966" t="s">
         <v>8</v>
@@ -51511,7 +51511,7 @@
         <v>1.42599999904633</v>
       </c>
       <c r="G1967" t="n">
-        <v>0.87459397315979</v>
+        <v>0.874593913555145</v>
       </c>
       <c r="H1967" t="s">
         <v>8</v>
@@ -51537,7 +51537,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1968" t="n">
-        <v>0.889313697814941</v>
+        <v>0.889313638210297</v>
       </c>
       <c r="H1968" t="s">
         <v>8</v>
@@ -51641,7 +51641,7 @@
         <v>1.46399998664856</v>
       </c>
       <c r="G1972" t="n">
-        <v>0.897900104522705</v>
+        <v>0.89790004491806</v>
       </c>
       <c r="H1972" t="s">
         <v>8</v>
@@ -51693,7 +51693,7 @@
         <v>1.50399994850159</v>
       </c>
       <c r="G1974" t="n">
-        <v>0.922432839870453</v>
+        <v>0.922432899475098</v>
       </c>
       <c r="H1974" t="s">
         <v>8</v>
@@ -51719,7 +51719,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1975" t="n">
-        <v>0.931019306182861</v>
+        <v>0.931019365787506</v>
       </c>
       <c r="H1975" t="s">
         <v>8</v>
@@ -51745,7 +51745,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1976" t="n">
-        <v>0.926112711429596</v>
+        <v>0.926112830638885</v>
       </c>
       <c r="H1976" t="s">
         <v>8</v>
@@ -51849,7 +51849,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G1980" t="n">
-        <v>1.04141688346863</v>
+        <v>1.04141676425934</v>
       </c>
       <c r="H1980" t="s">
         <v>8</v>
@@ -51901,7 +51901,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G1982" t="n">
-        <v>1.00707101821899</v>
+        <v>1.0070708990097</v>
       </c>
       <c r="H1982" t="s">
         <v>8</v>
@@ -51927,7 +51927,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1983" t="n">
-        <v>0.999711215496063</v>
+        <v>0.999711155891418</v>
       </c>
       <c r="H1983" t="s">
         <v>8</v>
@@ -52083,7 +52083,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1989" t="n">
-        <v>0.99357795715332</v>
+        <v>0.993578016757965</v>
       </c>
       <c r="H1989" t="s">
         <v>8</v>
@@ -52161,7 +52161,7 @@
         <v>1.54799997806549</v>
       </c>
       <c r="G1992" t="n">
-        <v>0.949418902397156</v>
+        <v>0.949418962001801</v>
       </c>
       <c r="H1992" t="s">
         <v>8</v>
@@ -52187,7 +52187,7 @@
         <v>1.54799997806549</v>
       </c>
       <c r="G1993" t="n">
-        <v>0.949418902397156</v>
+        <v>0.949418962001801</v>
       </c>
       <c r="H1993" t="s">
         <v>8</v>
@@ -52239,7 +52239,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1995" t="n">
-        <v>0.956778824329376</v>
+        <v>0.956778764724731</v>
       </c>
       <c r="H1995" t="s">
         <v>8</v>
@@ -52265,7 +52265,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G1996" t="n">
-        <v>0.951872289180756</v>
+        <v>0.951872229576111</v>
       </c>
       <c r="H1996" t="s">
         <v>8</v>
@@ -52291,7 +52291,7 @@
         <v>1.57799994945526</v>
       </c>
       <c r="G1997" t="n">
-        <v>0.96781849861145</v>
+        <v>0.967818439006805</v>
       </c>
       <c r="H1997" t="s">
         <v>8</v>
@@ -52369,7 +52369,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G2000" t="n">
-        <v>0.950645565986633</v>
+        <v>0.950645625591278</v>
       </c>
       <c r="H2000" t="s">
         <v>8</v>
@@ -52395,7 +52395,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G2001" t="n">
-        <v>0.950645565986633</v>
+        <v>0.950645625591278</v>
       </c>
       <c r="H2001" t="s">
         <v>8</v>
@@ -52421,7 +52421,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G2002" t="n">
-        <v>0.953098833560944</v>
+        <v>0.953098893165588</v>
       </c>
       <c r="H2002" t="s">
         <v>8</v>
@@ -52447,7 +52447,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G2003" t="n">
-        <v>0.980085015296936</v>
+        <v>0.980084896087646</v>
       </c>
       <c r="H2003" t="s">
         <v>8</v>
@@ -52499,7 +52499,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G2005" t="n">
-        <v>0.999711215496063</v>
+        <v>0.999711155891418</v>
       </c>
       <c r="H2005" t="s">
         <v>8</v>
@@ -52525,7 +52525,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G2006" t="n">
-        <v>0.999711215496063</v>
+        <v>0.999711155891418</v>
       </c>
       <c r="H2006" t="s">
         <v>8</v>
@@ -52577,7 +52577,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G2008" t="n">
-        <v>1.00461769104004</v>
+        <v>1.00461781024933</v>
       </c>
       <c r="H2008" t="s">
         <v>8</v>
@@ -52629,7 +52629,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2010" t="n">
-        <v>0.99357795715332</v>
+        <v>0.993578016757965</v>
       </c>
       <c r="H2010" t="s">
         <v>8</v>
@@ -52785,7 +52785,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G2016" t="n">
-        <v>0.9886714220047</v>
+        <v>0.988671362400055</v>
       </c>
       <c r="H2016" t="s">
         <v>8</v>
@@ -52811,7 +52811,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G2017" t="n">
-        <v>0.96291196346283</v>
+        <v>0.962912023067474</v>
       </c>
       <c r="H2017" t="s">
         <v>8</v>
@@ -52915,7 +52915,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G2021" t="n">
-        <v>1.11501526832581</v>
+        <v>1.11501514911652</v>
       </c>
       <c r="H2021" t="s">
         <v>8</v>
@@ -52993,7 +52993,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G2024" t="n">
-        <v>1.13341498374939</v>
+        <v>1.1334148645401</v>
       </c>
       <c r="H2024" t="s">
         <v>8</v>
@@ -53019,7 +53019,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G2025" t="n">
-        <v>1.14813446998596</v>
+        <v>1.14813458919525</v>
       </c>
       <c r="H2025" t="s">
         <v>8</v>
@@ -53045,7 +53045,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G2026" t="n">
-        <v>1.15181446075439</v>
+        <v>1.15181457996368</v>
       </c>
       <c r="H2026" t="s">
         <v>8</v>
@@ -53175,7 +53175,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2031" t="n">
-        <v>1.26957178115845</v>
+        <v>1.26957190036774</v>
       </c>
       <c r="H2031" t="s">
         <v>8</v>
@@ -53227,7 +53227,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2033" t="n">
-        <v>1.23277258872986</v>
+        <v>1.23277270793915</v>
       </c>
       <c r="H2033" t="s">
         <v>8</v>
@@ -53253,7 +53253,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2034" t="n">
-        <v>1.23890590667725</v>
+        <v>1.23890578746796</v>
       </c>
       <c r="H2034" t="s">
         <v>8</v>
@@ -53357,7 +53357,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2038" t="n">
-        <v>1.20823991298676</v>
+        <v>1.20823979377747</v>
       </c>
       <c r="H2038" t="s">
         <v>8</v>
@@ -53409,7 +53409,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G2040" t="n">
-        <v>1.18493378162384</v>
+        <v>1.18493366241455</v>
       </c>
       <c r="H2040" t="s">
         <v>8</v>
@@ -53435,7 +53435,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2041" t="n">
-        <v>1.17757380008698</v>
+        <v>1.17757391929626</v>
       </c>
       <c r="H2041" t="s">
         <v>8</v>
@@ -53513,7 +53513,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G2044" t="n">
-        <v>1.22173285484314</v>
+        <v>1.22173297405243</v>
       </c>
       <c r="H2044" t="s">
         <v>8</v>
@@ -53539,7 +53539,7 @@
         <v>2</v>
       </c>
       <c r="G2045" t="n">
-        <v>1.22663950920105</v>
+        <v>1.22663938999176</v>
       </c>
       <c r="H2045" t="s">
         <v>8</v>
@@ -53565,7 +53565,7 @@
         <v>2</v>
       </c>
       <c r="G2046" t="n">
-        <v>1.22663950920105</v>
+        <v>1.22663938999176</v>
       </c>
       <c r="H2046" t="s">
         <v>8</v>
@@ -53643,7 +53643,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2049" t="n">
-        <v>1.18370711803436</v>
+        <v>1.18370699882507</v>
       </c>
       <c r="H2049" t="s">
         <v>8</v>
@@ -53669,7 +53669,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G2050" t="n">
-        <v>1.14322805404663</v>
+        <v>1.14322793483734</v>
       </c>
       <c r="H2050" t="s">
         <v>8</v>
@@ -53721,7 +53721,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G2052" t="n">
-        <v>1.14445459842682</v>
+        <v>1.14445471763611</v>
       </c>
       <c r="H2052" t="s">
         <v>8</v>
@@ -53773,7 +53773,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G2054" t="n">
-        <v>1.13832139968872</v>
+        <v>1.13832128047943</v>
       </c>
       <c r="H2054" t="s">
         <v>8</v>
@@ -53825,7 +53825,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G2056" t="n">
-        <v>1.13832139968872</v>
+        <v>1.13832128047943</v>
       </c>
       <c r="H2056" t="s">
         <v>8</v>
@@ -53851,7 +53851,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G2057" t="n">
-        <v>1.14200139045715</v>
+        <v>1.14200127124786</v>
       </c>
       <c r="H2057" t="s">
         <v>8</v>
@@ -53877,7 +53877,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G2058" t="n">
-        <v>1.15181446075439</v>
+        <v>1.15181457996368</v>
       </c>
       <c r="H2058" t="s">
         <v>8</v>
@@ -53903,7 +53903,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2059" t="n">
-        <v>1.13464152812958</v>
+        <v>1.13464140892029</v>
       </c>
       <c r="H2059" t="s">
         <v>8</v>
@@ -53955,7 +53955,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2061" t="n">
-        <v>1.13464152812958</v>
+        <v>1.13464140892029</v>
       </c>
       <c r="H2061" t="s">
         <v>8</v>
@@ -54033,7 +54033,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2064" t="n">
-        <v>1.12850832939148</v>
+        <v>1.12850844860077</v>
       </c>
       <c r="H2064" t="s">
         <v>8</v>
@@ -54085,7 +54085,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G2066" t="n">
-        <v>1.15794765949249</v>
+        <v>1.1579475402832</v>
       </c>
       <c r="H2066" t="s">
         <v>8</v>
@@ -54111,7 +54111,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2067" t="n">
-        <v>1.16530752182007</v>
+        <v>1.16530740261078</v>
       </c>
       <c r="H2067" t="s">
         <v>8</v>
@@ -54293,7 +54293,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G2074" t="n">
-        <v>1.22173285484314</v>
+        <v>1.22173297405243</v>
       </c>
       <c r="H2074" t="s">
         <v>8</v>
@@ -54319,7 +54319,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2075" t="n">
-        <v>1.25730550289154</v>
+        <v>1.25730538368225</v>
       </c>
       <c r="H2075" t="s">
         <v>8</v>
@@ -54345,7 +54345,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G2076" t="n">
-        <v>1.70502877235413</v>
+        <v>1.70502889156342</v>
       </c>
       <c r="H2076" t="s">
         <v>8</v>
@@ -54371,7 +54371,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G2077" t="n">
-        <v>1.71729528903961</v>
+        <v>1.71729516983032</v>
       </c>
       <c r="H2077" t="s">
         <v>8</v>
@@ -54397,7 +54397,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G2078" t="n">
-        <v>1.81849300861359</v>
+        <v>1.8184928894043</v>
       </c>
       <c r="H2078" t="s">
         <v>8</v>
@@ -54423,7 +54423,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2079" t="n">
-        <v>1.94422364234924</v>
+        <v>1.94422352313995</v>
       </c>
       <c r="H2079" t="s">
         <v>8</v>
@@ -54449,7 +54449,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G2080" t="n">
-        <v>1.89822471141815</v>
+        <v>1.89822459220886</v>
       </c>
       <c r="H2080" t="s">
         <v>8</v>
@@ -54553,7 +54553,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G2084" t="n">
-        <v>1.79702687263489</v>
+        <v>1.7970267534256</v>
       </c>
       <c r="H2084" t="s">
         <v>8</v>
@@ -54605,7 +54605,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G2086" t="n">
-        <v>1.7448947429657</v>
+        <v>1.74489462375641</v>
       </c>
       <c r="H2086" t="s">
         <v>8</v>
@@ -54631,7 +54631,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G2087" t="n">
-        <v>1.84302592277527</v>
+        <v>1.84302580356598</v>
       </c>
       <c r="H2087" t="s">
         <v>8</v>
@@ -54683,7 +54683,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2089" t="n">
-        <v>1.90129113197327</v>
+        <v>1.90129125118256</v>
       </c>
       <c r="H2089" t="s">
         <v>8</v>
@@ -54709,7 +54709,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2090" t="n">
-        <v>1.90129113197327</v>
+        <v>1.90129125118256</v>
       </c>
       <c r="H2090" t="s">
         <v>8</v>
@@ -54735,7 +54735,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2091" t="n">
-        <v>1.91355764865875</v>
+        <v>1.91355752944946</v>
       </c>
       <c r="H2091" t="s">
         <v>8</v>
@@ -54865,7 +54865,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G2096" t="n">
-        <v>1.92889034748077</v>
+        <v>1.92889046669006</v>
       </c>
       <c r="H2096" t="s">
         <v>8</v>
@@ -54891,7 +54891,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2097" t="n">
-        <v>1.99942243099213</v>
+        <v>1.99942231178284</v>
       </c>
       <c r="H2097" t="s">
         <v>8</v>
@@ -54943,7 +54943,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G2099" t="n">
-        <v>1.95955657958984</v>
+        <v>1.95955646038055</v>
       </c>
       <c r="H2099" t="s">
         <v>8</v>
@@ -55021,7 +55021,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2102" t="n">
-        <v>1.93809020519257</v>
+        <v>1.93809044361115</v>
       </c>
       <c r="H2102" t="s">
         <v>8</v>
@@ -55125,7 +55125,7 @@
         <v>3.25</v>
       </c>
       <c r="G2106" t="n">
-        <v>1.99328923225403</v>
+        <v>1.99328911304474</v>
       </c>
       <c r="H2106" t="s">
         <v>8</v>
@@ -55151,7 +55151,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2107" t="n">
-        <v>2.00555562973022</v>
+        <v>2.00555539131165</v>
       </c>
       <c r="H2107" t="s">
         <v>8</v>
@@ -55177,7 +55177,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G2108" t="n">
-        <v>1.95342326164246</v>
+        <v>1.95342338085175</v>
       </c>
       <c r="H2108" t="s">
         <v>8</v>
@@ -55203,7 +55203,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G2109" t="n">
-        <v>1.95342326164246</v>
+        <v>1.95342338085175</v>
       </c>
       <c r="H2109" t="s">
         <v>8</v>
@@ -55229,7 +55229,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G2110" t="n">
-        <v>1.92889034748077</v>
+        <v>1.92889046669006</v>
       </c>
       <c r="H2110" t="s">
         <v>8</v>
@@ -55255,7 +55255,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2111" t="n">
-        <v>1.92582392692566</v>
+        <v>1.92582404613495</v>
       </c>
       <c r="H2111" t="s">
         <v>8</v>
@@ -55307,7 +55307,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2113" t="n">
-        <v>1.88902485370636</v>
+        <v>1.88902461528778</v>
       </c>
       <c r="H2113" t="s">
         <v>8</v>
@@ -55333,7 +55333,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2114" t="n">
-        <v>1.88902485370636</v>
+        <v>1.88902461528778</v>
       </c>
       <c r="H2114" t="s">
         <v>8</v>
@@ -55463,7 +55463,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G2119" t="n">
-        <v>1.8062264919281</v>
+        <v>1.80622661113739</v>
       </c>
       <c r="H2119" t="s">
         <v>8</v>
@@ -55489,7 +55489,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G2120" t="n">
-        <v>1.76942753791809</v>
+        <v>1.7694274187088</v>
       </c>
       <c r="H2120" t="s">
         <v>8</v>
@@ -55515,7 +55515,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G2121" t="n">
-        <v>1.76022756099701</v>
+        <v>1.7602276802063</v>
       </c>
       <c r="H2121" t="s">
         <v>8</v>
@@ -55541,7 +55541,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G2122" t="n">
-        <v>1.81849300861359</v>
+        <v>1.8184928894043</v>
       </c>
       <c r="H2122" t="s">
         <v>8</v>
@@ -55593,7 +55593,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G2124" t="n">
-        <v>2.0125093460083</v>
+        <v>2.01250958442688</v>
       </c>
       <c r="H2124" t="s">
         <v>8</v>
@@ -55619,7 +55619,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G2125" t="n">
-        <v>1.96318316459656</v>
+        <v>1.96318304538727</v>
       </c>
       <c r="H2125" t="s">
         <v>8</v>
@@ -55671,7 +55671,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G2127" t="n">
-        <v>1.79218554496765</v>
+        <v>1.79218566417694</v>
       </c>
       <c r="H2127" t="s">
         <v>8</v>
@@ -55801,7 +55801,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G2132" t="n">
-        <v>1.83164668083191</v>
+        <v>1.8316468000412</v>
       </c>
       <c r="H2132" t="s">
         <v>8</v>
@@ -55879,7 +55879,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G2135" t="n">
-        <v>1.79218554496765</v>
+        <v>1.79218566417694</v>
       </c>
       <c r="H2135" t="s">
         <v>8</v>
@@ -55905,7 +55905,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G2136" t="n">
-        <v>1.79218554496765</v>
+        <v>1.79218566417694</v>
       </c>
       <c r="H2136" t="s">
         <v>8</v>
@@ -55957,7 +55957,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G2138" t="n">
-        <v>1.95660626888275</v>
+        <v>1.95660638809204</v>
       </c>
       <c r="H2138" t="s">
         <v>8</v>
@@ -55983,7 +55983,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G2139" t="n">
-        <v>1.95002961158752</v>
+        <v>1.95002949237823</v>
       </c>
       <c r="H2139" t="s">
         <v>8</v>
@@ -56009,7 +56009,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G2140" t="n">
-        <v>1.92043387889862</v>
+        <v>1.92043375968933</v>
       </c>
       <c r="H2140" t="s">
         <v>8</v>
@@ -56035,7 +56035,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G2141" t="n">
-        <v>1.93358755111694</v>
+        <v>1.93358743190765</v>
       </c>
       <c r="H2141" t="s">
         <v>8</v>
@@ -56061,7 +56061,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G2142" t="n">
-        <v>1.92372226715088</v>
+        <v>1.92372214794159</v>
       </c>
       <c r="H2142" t="s">
         <v>8</v>
@@ -56113,7 +56113,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G2144" t="n">
-        <v>1.90728032588959</v>
+        <v>1.9072802066803</v>
       </c>
       <c r="H2144" t="s">
         <v>8</v>
@@ -56165,7 +56165,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G2146" t="n">
-        <v>1.91385698318481</v>
+        <v>1.9138571023941</v>
       </c>
       <c r="H2146" t="s">
         <v>8</v>
@@ -56191,7 +56191,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G2147" t="n">
-        <v>1.91056859493256</v>
+        <v>1.91056847572327</v>
       </c>
       <c r="H2147" t="s">
         <v>8</v>
@@ -56217,7 +56217,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G2148" t="n">
-        <v>1.91056859493256</v>
+        <v>1.91056847572327</v>
       </c>
       <c r="H2148" t="s">
         <v>8</v>
@@ -56243,7 +56243,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G2149" t="n">
-        <v>1.91714537143707</v>
+        <v>1.91714549064636</v>
       </c>
       <c r="H2149" t="s">
         <v>8</v>
@@ -56295,7 +56295,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G2151" t="n">
-        <v>1.87110769748688</v>
+        <v>1.87110757827759</v>
       </c>
       <c r="H2151" t="s">
         <v>8</v>
@@ -56373,7 +56373,7 @@
         <v>3</v>
       </c>
       <c r="G2154" t="n">
-        <v>1.97304844856262</v>
+        <v>1.97304832935333</v>
       </c>
       <c r="H2154" t="s">
         <v>8</v>
@@ -56607,7 +56607,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2163" t="n">
-        <v>2.22296786308289</v>
+        <v>2.22296810150146</v>
       </c>
       <c r="H2163" t="s">
         <v>8</v>
@@ -56633,7 +56633,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G2164" t="n">
-        <v>2.17692995071411</v>
+        <v>2.17693018913269</v>
       </c>
       <c r="H2164" t="s">
         <v>8</v>
@@ -56659,7 +56659,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G2165" t="n">
-        <v>2.20981431007385</v>
+        <v>2.20981407165527</v>
       </c>
       <c r="H2165" t="s">
         <v>8</v>
@@ -56685,7 +56685,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2166" t="n">
-        <v>2.22296786308289</v>
+        <v>2.22296810150146</v>
       </c>
       <c r="H2166" t="s">
         <v>8</v>
@@ -56763,7 +56763,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G2169" t="n">
-        <v>2.17692995071411</v>
+        <v>2.17693018913269</v>
       </c>
       <c r="H2169" t="s">
         <v>8</v>
@@ -71222,6 +71222,32 @@
         <v>2.13499999046326</v>
       </c>
       <c r="H2725" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>383405</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>2.15499997138977</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>2.10999989509583</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>2.15499997138977</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="H2726" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SGF.MI.xlsx
+++ b/data/SGF.MI.xlsx
@@ -71251,6 +71251,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>282243</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>2.04999995231628</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>2.08500003814697</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>2.08500003814697</v>
+      </c>
+      <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SGF.MI.xlsx
+++ b/data/SGF.MI.xlsx
@@ -447,7 +447,7 @@
         <v>2.00399994850159</v>
       </c>
       <c r="G3" t="n">
-        <v>1.22909271717072</v>
+        <v>1.22909259796143</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>1.91299998760223</v>
       </c>
       <c r="G6" t="n">
-        <v>1.17328059673309</v>
+        <v>1.17328071594238</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G9" t="n">
-        <v>1.15058779716492</v>
+        <v>1.15058791637421</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G10" t="n">
-        <v>1.12850844860077</v>
+        <v>1.12850832939148</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G13" t="n">
-        <v>1.09293580055237</v>
+        <v>1.09293568134308</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G24" t="n">
-        <v>1.01075088977814</v>
+        <v>1.01075100898743</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>1.50399994850159</v>
       </c>
       <c r="G36" t="n">
-        <v>0.922432899475098</v>
+        <v>0.922432839870453</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G37" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G39" t="n">
-        <v>0.924886167049408</v>
+        <v>0.924886226654053</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G40" t="n">
-        <v>0.910166442394257</v>
+        <v>0.910166501998901</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>1.52699995040894</v>
       </c>
       <c r="G41" t="n">
-        <v>0.936539173126221</v>
+        <v>0.93653929233551</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G42" t="n">
-        <v>0.87214070558548</v>
+        <v>0.872140645980835</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>1.5</v>
       </c>
       <c r="G43" t="n">
-        <v>0.919979572296143</v>
+        <v>0.919979512691498</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>1.5789999961853</v>
       </c>
       <c r="G44" t="n">
-        <v>0.968431770801544</v>
+        <v>0.968431890010834</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G48" t="n">
-        <v>1.0040043592453</v>
+        <v>1.00400447845459</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G57" t="n">
-        <v>0.926112830638885</v>
+        <v>0.92611289024353</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>1.5</v>
       </c>
       <c r="G58" t="n">
-        <v>0.919979572296143</v>
+        <v>0.919979512691498</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>1.4210000038147</v>
       </c>
       <c r="G59" t="n">
-        <v>0.871527373790741</v>
+        <v>0.871527314186096</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>1.34300005435944</v>
       </c>
       <c r="G61" t="n">
-        <v>0.823688387870789</v>
+        <v>0.823688447475433</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>1.40600001811981</v>
       </c>
       <c r="G62" t="n">
-        <v>0.862327516078949</v>
+        <v>0.862327575683594</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G67" t="n">
-        <v>0.818781912326813</v>
+        <v>0.818781852722168</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G69" t="n">
-        <v>0.832888305187225</v>
+        <v>0.832888245582581</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G70" t="n">
-        <v>0.849447846412659</v>
+        <v>0.849447786808014</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>1.38300001621246</v>
       </c>
       <c r="G71" t="n">
-        <v>0.848221242427826</v>
+        <v>0.848221182823181</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>1.43299996852875</v>
       </c>
       <c r="G73" t="n">
-        <v>0.878887116909027</v>
+        <v>0.878887236118317</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G75" t="n">
-        <v>0.895446836948395</v>
+        <v>0.89544677734375</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G76" t="n">
-        <v>0.852514445781708</v>
+        <v>0.852514386177063</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>1.43099999427795</v>
       </c>
       <c r="G77" t="n">
-        <v>0.877660512924194</v>
+        <v>0.877660572528839</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G78" t="n">
-        <v>0.875207245349884</v>
+        <v>0.875207364559174</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G80" t="n">
-        <v>0.87214070558548</v>
+        <v>0.872140645980835</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>1.5</v>
       </c>
       <c r="G82" t="n">
-        <v>0.919979572296143</v>
+        <v>0.919979512691498</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G85" t="n">
-        <v>0.993578016757965</v>
+        <v>0.993577897548676</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>1.50100004673004</v>
       </c>
       <c r="G90" t="n">
-        <v>0.920592904090881</v>
+        <v>0.920592963695526</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G91" t="n">
-        <v>0.938379168510437</v>
+        <v>0.938379287719727</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G95" t="n">
-        <v>1.00216436386108</v>
+        <v>1.00216448307037</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G102" t="n">
-        <v>1.02424395084381</v>
+        <v>1.02424383163452</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G108" t="n">
-        <v>1.03037714958191</v>
+        <v>1.03037703037262</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G111" t="n">
-        <v>1.0070708990097</v>
+        <v>1.00707101821899</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>1.36899995803833</v>
       </c>
       <c r="G120" t="n">
-        <v>0.839634656906128</v>
+        <v>0.839634716510773</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G121" t="n">
-        <v>0.880727171897888</v>
+        <v>0.880727112293243</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G122" t="n">
-        <v>0.875207245349884</v>
+        <v>0.875207364559174</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G123" t="n">
-        <v>0.880113840103149</v>
+        <v>0.880113780498505</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G132" t="n">
-        <v>0.711450815200806</v>
+        <v>0.71145087480545</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>1.30299997329712</v>
       </c>
       <c r="G136" t="n">
-        <v>0.799155652523041</v>
+        <v>0.799155592918396</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>1.40600001811981</v>
       </c>
       <c r="G143" t="n">
-        <v>0.862327516078949</v>
+        <v>0.862327575683594</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>1.38199996948242</v>
       </c>
       <c r="G144" t="n">
-        <v>0.847607791423798</v>
+        <v>0.847607851028442</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G146" t="n">
-        <v>0.884407103061676</v>
+        <v>0.884407043457031</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G149" t="n">
-        <v>0.932245969772339</v>
+        <v>0.932246029376984</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G151" t="n">
-        <v>0.907713234424591</v>
+        <v>0.907713174819946</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>1.62899994850159</v>
       </c>
       <c r="G155" t="n">
-        <v>0.999097764492035</v>
+        <v>0.99909782409668</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G156" t="n">
-        <v>1.0070708990097</v>
+        <v>1.00707101821899</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G158" t="n">
-        <v>1.02424395084381</v>
+        <v>1.02424383163452</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G160" t="n">
-        <v>1.03344368934631</v>
+        <v>1.0334438085556</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>1.66100001335144</v>
       </c>
       <c r="G162" t="n">
-        <v>1.01872396469116</v>
+        <v>1.01872408390045</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>1.66100001335144</v>
       </c>
       <c r="G164" t="n">
-        <v>1.01872396469116</v>
+        <v>1.01872408390045</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G168" t="n">
-        <v>1.03405702114105</v>
+        <v>1.03405714035034</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G169" t="n">
-        <v>1.05491006374359</v>
+        <v>1.0549099445343</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G170" t="n">
-        <v>1.04571008682251</v>
+        <v>1.0457102060318</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>1.77699995040894</v>
       </c>
       <c r="G177" t="n">
-        <v>1.08986914157867</v>
+        <v>1.08986902236938</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>1.73699998855591</v>
       </c>
       <c r="G180" t="n">
-        <v>1.06533634662628</v>
+        <v>1.06533622741699</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G184" t="n">
-        <v>1.05491006374359</v>
+        <v>1.0549099445343</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G186" t="n">
-        <v>1.0671763420105</v>
+        <v>1.06717622280121</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>1.78299999237061</v>
       </c>
       <c r="G190" t="n">
-        <v>1.09354913234711</v>
+        <v>1.09354901313782</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G195" t="n">
-        <v>1.09416246414185</v>
+        <v>1.09416234493256</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G198" t="n">
-        <v>1.09784233570099</v>
+        <v>1.0978422164917</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G199" t="n">
-        <v>1.10152232646942</v>
+        <v>1.10152220726013</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>1.09784233570099</v>
+        <v>1.0978422164917</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>1.79100000858307</v>
       </c>
       <c r="G201" t="n">
-        <v>1.09845566749573</v>
+        <v>1.09845554828644</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G204" t="n">
-        <v>1.10090899467468</v>
+        <v>1.10090887546539</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>1.79100000858307</v>
       </c>
       <c r="G205" t="n">
-        <v>1.09845566749573</v>
+        <v>1.09845554828644</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G207" t="n">
-        <v>1.10274887084961</v>
+        <v>1.1027489900589</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G208" t="n">
-        <v>1.10152232646942</v>
+        <v>1.10152220726013</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G209" t="n">
-        <v>1.12850844860077</v>
+        <v>1.12850832939148</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G211" t="n">
-        <v>1.23890578746796</v>
+        <v>1.23890590667725</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G213" t="n">
-        <v>1.23277270793915</v>
+        <v>1.23277258872986</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G215" t="n">
-        <v>1.26343870162964</v>
+        <v>1.26343858242035</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G218" t="n">
-        <v>1.26466536521912</v>
+        <v>1.26466524600983</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G224" t="n">
-        <v>1.30759763717651</v>
+        <v>1.3075977563858</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G226" t="n">
-        <v>1.32231712341309</v>
+        <v>1.32231724262238</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G229" t="n">
-        <v>1.33090376853943</v>
+        <v>1.33090388774872</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G232" t="n">
-        <v>1.30023777484894</v>
+        <v>1.30023765563965</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G233" t="n">
-        <v>1.29901123046875</v>
+        <v>1.29901111125946</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.09200000762939</v>
       </c>
       <c r="G238" t="n">
-        <v>1.28306496143341</v>
+        <v>1.28306484222412</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G240" t="n">
-        <v>1.30023777484894</v>
+        <v>1.30023765563965</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G241" t="n">
-        <v>1.36279654502869</v>
+        <v>1.3627964258194</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G242" t="n">
-        <v>1.42290163040161</v>
+        <v>1.4229017496109</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G245" t="n">
-        <v>1.47687387466431</v>
+        <v>1.4768739938736</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G249" t="n">
-        <v>1.47932732105255</v>
+        <v>1.47932720184326</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G251" t="n">
-        <v>1.50263345241547</v>
+        <v>1.50263333320618</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G252" t="n">
-        <v>1.49650025367737</v>
+        <v>1.49650013446808</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G254" t="n">
-        <v>1.47687387466431</v>
+        <v>1.4768739938736</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G255" t="n">
-        <v>1.447434425354</v>
+        <v>1.44743454456329</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G256" t="n">
-        <v>1.47810053825378</v>
+        <v>1.47810065746307</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G258" t="n">
-        <v>1.56396520137787</v>
+        <v>1.56396532058716</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G259" t="n">
-        <v>1.57991170883179</v>
+        <v>1.5799115896225</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G264" t="n">
-        <v>1.57377851009369</v>
+        <v>1.5737783908844</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G268" t="n">
-        <v>1.57868480682373</v>
+        <v>1.57868492603302</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G269" t="n">
-        <v>1.55660545825958</v>
+        <v>1.55660557746887</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G271" t="n">
-        <v>1.52593958377838</v>
+        <v>1.52593946456909</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G273" t="n">
-        <v>1.49527359008789</v>
+        <v>1.4952734708786</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G276" t="n">
-        <v>1.52593958377838</v>
+        <v>1.52593946456909</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G277" t="n">
-        <v>1.47687387466431</v>
+        <v>1.4768739938736</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.12400007247925</v>
       </c>
       <c r="G287" t="n">
-        <v>1.30269122123718</v>
+        <v>1.30269110202789</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G294" t="n">
-        <v>1.4339417219162</v>
+        <v>1.43394160270691</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G295" t="n">
-        <v>1.4339417219162</v>
+        <v>1.43394160270691</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G297" t="n">
-        <v>1.39591574668884</v>
+        <v>1.39591562747955</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G298" t="n">
-        <v>1.46338093280792</v>
+        <v>1.46338081359863</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G300" t="n">
-        <v>1.65718972682953</v>
+        <v>1.65718984603882</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G305" t="n">
-        <v>1.79825341701508</v>
+        <v>1.79825329780579</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G306" t="n">
-        <v>1.75409436225891</v>
+        <v>1.7540944814682</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G307" t="n">
-        <v>1.79089367389679</v>
+        <v>1.7908935546875</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G308" t="n">
-        <v>1.77740061283112</v>
+        <v>1.77740049362183</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>1.77862727642059</v>
+        <v>1.7786271572113</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G310" t="n">
-        <v>1.79089367389679</v>
+        <v>1.7908935546875</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G311" t="n">
-        <v>1.80316007137299</v>
+        <v>1.8031599521637</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G312" t="n">
-        <v>1.82523953914642</v>
+        <v>1.82523965835571</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G314" t="n">
-        <v>1.93563687801361</v>
+        <v>1.93563711643219</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G317" t="n">
-        <v>2.152752161026</v>
+        <v>2.15275239944458</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.60199999809265</v>
       </c>
       <c r="G318" t="n">
-        <v>2.20917773246765</v>
+        <v>2.20917797088623</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>3.75</v>
       </c>
       <c r="G319" t="n">
-        <v>2.29994893074036</v>
+        <v>2.29994916915894</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G323" t="n">
-        <v>2.25701689720154</v>
+        <v>2.25701665878296</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>3.75600004196167</v>
       </c>
       <c r="G324" t="n">
-        <v>2.30362915992737</v>
+        <v>2.30362892150879</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G326" t="n">
-        <v>2.2484302520752</v>
+        <v>2.24843001365662</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G328" t="n">
-        <v>2.2484302520752</v>
+        <v>2.24843001365662</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G332" t="n">
-        <v>2.20181798934937</v>
+        <v>2.20181775093079</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G333" t="n">
-        <v>2.28277587890625</v>
+        <v>2.28277611732483</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>2.85193705558777</v>
+        <v>2.85193681716919</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G348" t="n">
-        <v>2.88996243476868</v>
+        <v>2.88996267318726</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G350" t="n">
-        <v>2.8568434715271</v>
+        <v>2.85684323310852</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>4.72399997711182</v>
       </c>
       <c r="G351" t="n">
-        <v>2.89732265472412</v>
+        <v>2.89732241630554</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G354" t="n">
-        <v>2.99300050735474</v>
+        <v>2.99300026893616</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>5.08500003814697</v>
       </c>
       <c r="G356" t="n">
-        <v>3.11873078346252</v>
+        <v>3.1187310218811</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G357" t="n">
-        <v>3.14633059501648</v>
+        <v>3.1463303565979</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G360" t="n">
-        <v>3.17392992973328</v>
+        <v>3.1739296913147</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G361" t="n">
-        <v>3.18619608879089</v>
+        <v>3.18619585037231</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G362" t="n">
-        <v>3.14633059501648</v>
+        <v>3.1463303565979</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G364" t="n">
-        <v>3.28432703018188</v>
+        <v>3.28432726860046</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G365" t="n">
-        <v>3.18926239013672</v>
+        <v>3.1892626285553</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G370" t="n">
-        <v>2.99300050735474</v>
+        <v>2.99300026893616</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G372" t="n">
-        <v>3.10953092575073</v>
+        <v>3.10953116416931</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G373" t="n">
-        <v>3.03470587730408</v>
+        <v>3.03470611572266</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>3.17392992973328</v>
+        <v>3.1739296913147</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>3.2321949005127</v>
+        <v>3.23219513893127</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>4.93400001525879</v>
       </c>
       <c r="G381" t="n">
-        <v>3.02611947059631</v>
+        <v>3.02611970901489</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G382" t="n">
-        <v>3.10953092575073</v>
+        <v>3.10953116416931</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.50600004196167</v>
       </c>
       <c r="G390" t="n">
-        <v>2.76361870765686</v>
+        <v>2.76361894607544</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>4.72399997711182</v>
       </c>
       <c r="G391" t="n">
-        <v>2.89732265472412</v>
+        <v>2.89732241630554</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G395" t="n">
-        <v>2.91081523895264</v>
+        <v>2.91081547737122</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G401" t="n">
-        <v>2.62746167182922</v>
+        <v>2.6274619102478</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>4.47800016403198</v>
       </c>
       <c r="G402" t="n">
-        <v>2.74644589424133</v>
+        <v>2.74644565582275</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G405" t="n">
-        <v>2.62500858306885</v>
+        <v>2.62500882148743</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>4.2480001449585</v>
       </c>
       <c r="G406" t="n">
-        <v>2.60538244247437</v>
+        <v>2.60538220405579</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G408" t="n">
-        <v>2.556316614151</v>
+        <v>2.55631685256958</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>4.64799976348877</v>
       </c>
       <c r="G413" t="n">
-        <v>2.85071015357971</v>
+        <v>2.85070991516113</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4.4520001411438</v>
       </c>
       <c r="G414" t="n">
-        <v>2.73049974441528</v>
+        <v>2.7304995059967</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>4.41800022125244</v>
       </c>
       <c r="G422" t="n">
-        <v>2.70964646339417</v>
+        <v>2.70964670181274</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>4.44399976730347</v>
       </c>
       <c r="G423" t="n">
-        <v>2.72559309005737</v>
+        <v>2.72559285163879</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G424" t="n">
-        <v>2.66794085502625</v>
+        <v>2.66794061660767</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G434" t="n">
-        <v>3.05065226554871</v>
+        <v>3.05065250396729</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G439" t="n">
-        <v>3.17086291313171</v>
+        <v>3.17086315155029</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>5.03499984741211</v>
       </c>
       <c r="G443" t="n">
-        <v>3.08806443214417</v>
+        <v>3.08806467056274</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>5.06500005722046</v>
       </c>
       <c r="G445" t="n">
-        <v>3.10646462440491</v>
+        <v>3.10646438598633</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>3.15553021430969</v>
+        <v>3.15552997589111</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.90199995040894</v>
       </c>
       <c r="G454" t="n">
-        <v>3.00649356842041</v>
+        <v>3.00649333000183</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G457" t="n">
-        <v>2.99300050735474</v>
+        <v>2.99300026893616</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>4.80600023269653</v>
       </c>
       <c r="G460" t="n">
-        <v>2.94761490821838</v>
+        <v>2.9476146697998</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G461" t="n">
-        <v>2.97214722633362</v>
+        <v>2.9721474647522</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>4.63199996948242</v>
       </c>
       <c r="G462" t="n">
-        <v>2.84089684486389</v>
+        <v>2.84089708328247</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G467" t="n">
-        <v>2.65567445755005</v>
+        <v>2.65567421913147</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G471" t="n">
-        <v>2.556316614151</v>
+        <v>2.55631685256958</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>4.26399993896484</v>
       </c>
       <c r="G473" t="n">
-        <v>2.61519527435303</v>
+        <v>2.61519551277161</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G476" t="n">
-        <v>2.47781157493591</v>
+        <v>2.47781181335449</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G477" t="n">
-        <v>2.43487954139709</v>
+        <v>2.43487930297852</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>3.86400008201599</v>
       </c>
       <c r="G483" t="n">
-        <v>2.3698673248291</v>
+        <v>2.36986756324768</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G491" t="n">
-        <v>2.66794085502625</v>
+        <v>2.66794061660767</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G492" t="n">
-        <v>2.63482189178467</v>
+        <v>2.63482165336609</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G496" t="n">
-        <v>2.53914380073547</v>
+        <v>2.53914356231689</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G497" t="n">
-        <v>2.62500858306885</v>
+        <v>2.62500882148743</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G499" t="n">
-        <v>2.60047554969788</v>
+        <v>2.6004753112793</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G500" t="n">
-        <v>2.5366907119751</v>
+        <v>2.53669047355652</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G505" t="n">
-        <v>2.39808034896851</v>
+        <v>2.39808011054993</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G506" t="n">
-        <v>2.43242597579956</v>
+        <v>2.43242621421814</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G507" t="n">
-        <v>2.47903823852539</v>
+        <v>2.47903847694397</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G511" t="n">
-        <v>2.45941233634949</v>
+        <v>2.45941209793091</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G517" t="n">
-        <v>2.52687740325928</v>
+        <v>2.5268771648407</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G522" t="n">
-        <v>2.62746167182922</v>
+        <v>2.6274619102478</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G527" t="n">
-        <v>2.65567445755005</v>
+        <v>2.65567421913147</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G531" t="n">
-        <v>2.60047554969788</v>
+        <v>2.6004753112793</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G533" t="n">
-        <v>2.46799874305725</v>
+        <v>2.46799850463867</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>3.86400008201599</v>
       </c>
       <c r="G535" t="n">
-        <v>2.3698673248291</v>
+        <v>2.36986756324768</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G537" t="n">
-        <v>2.35269451141357</v>
+        <v>2.35269474983215</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G538" t="n">
-        <v>2.41647958755493</v>
+        <v>2.41647982597351</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G540" t="n">
-        <v>2.20181798934937</v>
+        <v>2.20181775093079</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G544" t="n">
-        <v>2.27541613578796</v>
+        <v>2.27541637420654</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G548" t="n">
-        <v>2.28400254249573</v>
+        <v>2.28400278091431</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G550" t="n">
-        <v>2.24965691566467</v>
+        <v>2.24965667724609</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G556" t="n">
-        <v>1.84609246253967</v>
+        <v>1.84609234333038</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>3.15799999237061</v>
       </c>
       <c r="G559" t="n">
-        <v>1.93686354160309</v>
+        <v>1.93686378002167</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G561" t="n">
-        <v>1.84609246253967</v>
+        <v>1.84609234333038</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G563" t="n">
-        <v>1.87798500061035</v>
+        <v>1.87798523902893</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G568" t="n">
-        <v>1.98715603351593</v>
+        <v>1.98715579509735</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>3.08200001716614</v>
       </c>
       <c r="G571" t="n">
-        <v>1.89025127887726</v>
+        <v>1.89025151729584</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G573" t="n">
-        <v>1.81542646884918</v>
+        <v>1.81542634963989</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>3.37199997901917</v>
       </c>
       <c r="G585" t="n">
-        <v>2.0681140422821</v>
+        <v>2.06811428070068</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G595" t="n">
-        <v>2.08283352851868</v>
+        <v>2.08283376693726</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G602" t="n">
-        <v>1.96016979217529</v>
+        <v>1.96017003059387</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>3.08200001716614</v>
       </c>
       <c r="G605" t="n">
-        <v>1.89025127887726</v>
+        <v>1.89025151729584</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>3.13800001144409</v>
       </c>
       <c r="G606" t="n">
-        <v>1.92459750175476</v>
+        <v>1.92459726333618</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G614" t="n">
-        <v>1.77985382080078</v>
+        <v>1.77985394001007</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>3.05599999427795</v>
       </c>
       <c r="G617" t="n">
-        <v>1.87430500984192</v>
+        <v>1.8743052482605</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G618" t="n">
-        <v>1.86939859390259</v>
+        <v>1.86939883232117</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G619" t="n">
-        <v>1.87307834625244</v>
+        <v>1.87307858467102</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G623" t="n">
-        <v>1.84609246253967</v>
+        <v>1.84609234333038</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G625" t="n">
-        <v>1.84609246253967</v>
+        <v>1.84609234333038</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>3.01200008392334</v>
       </c>
       <c r="G627" t="n">
-        <v>1.84731912612915</v>
+        <v>1.84731900691986</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G628" t="n">
-        <v>1.80316007137299</v>
+        <v>1.8031599521637</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G630" t="n">
-        <v>1.80193340778351</v>
+        <v>1.80193328857422</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G633" t="n">
-        <v>1.66822981834412</v>
+        <v>1.66822969913483</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G634" t="n">
-        <v>1.63756382465363</v>
+        <v>1.63756370544434</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G638" t="n">
-        <v>1.54924583435059</v>
+        <v>1.5492457151413</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G640" t="n">
-        <v>1.56273865699768</v>
+        <v>1.56273877620697</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.68600010871887</v>
       </c>
       <c r="G641" t="n">
-        <v>1.64737677574158</v>
+        <v>1.64737689495087</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G648" t="n">
-        <v>1.57377851009369</v>
+        <v>1.5737783908844</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G650" t="n">
-        <v>1.72956168651581</v>
+        <v>1.72956156730652</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.71399998664856</v>
       </c>
       <c r="G652" t="n">
-        <v>1.66454970836639</v>
+        <v>1.66454982757568</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G662" t="n">
-        <v>1.26957190036774</v>
+        <v>1.26957178115845</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G663" t="n">
-        <v>1.2781583070755</v>
+        <v>1.27815842628479</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.1340000629425</v>
       </c>
       <c r="G664" t="n">
-        <v>1.30882430076599</v>
+        <v>1.30882441997528</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G667" t="n">
-        <v>1.23645269870758</v>
+        <v>1.23645257949829</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>2.00399994850159</v>
       </c>
       <c r="G676" t="n">
-        <v>1.22909271717072</v>
+        <v>1.22909259796143</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G684" t="n">
-        <v>1.23522591590881</v>
+        <v>1.23522579669952</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.00399994850159</v>
       </c>
       <c r="G685" t="n">
-        <v>1.22909271717072</v>
+        <v>1.22909259796143</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>1.98300004005432</v>
       </c>
       <c r="G689" t="n">
-        <v>1.21621298789978</v>
+        <v>1.21621310710907</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G692" t="n">
-        <v>1.24381244182587</v>
+        <v>1.24381256103516</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G693" t="n">
-        <v>1.24381244182587</v>
+        <v>1.24381256103516</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G694" t="n">
-        <v>1.26343870162964</v>
+        <v>1.26343858242035</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G696" t="n">
-        <v>1.31741094589233</v>
+        <v>1.31741082668304</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G697" t="n">
-        <v>1.30023777484894</v>
+        <v>1.30023765563965</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G698" t="n">
-        <v>1.24381244182587</v>
+        <v>1.24381256103516</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G708" t="n">
-        <v>1.08434927463531</v>
+        <v>1.0843493938446</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>1.7389999628067</v>
       </c>
       <c r="G709" t="n">
-        <v>1.06656301021576</v>
+        <v>1.06656289100647</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G714" t="n">
-        <v>1.02792394161224</v>
+        <v>1.02792382240295</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G717" t="n">
-        <v>0.984991550445557</v>
+        <v>0.984991431236267</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>1.49300003051758</v>
       </c>
       <c r="G719" t="n">
-        <v>0.915686428546906</v>
+        <v>0.915686368942261</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>1.5110000371933</v>
       </c>
       <c r="G720" t="n">
-        <v>0.926726162433624</v>
+        <v>0.926726222038269</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G726" t="n">
-        <v>0.980084896087646</v>
+        <v>0.980085015296936</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G727" t="n">
-        <v>0.958618760108948</v>
+        <v>0.958618640899658</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G728" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G732" t="n">
-        <v>0.907713234424591</v>
+        <v>0.907713174819946</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>1.50100004673004</v>
       </c>
       <c r="G734" t="n">
-        <v>0.920592904090881</v>
+        <v>0.920592963695526</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G735" t="n">
-        <v>0.924886167049408</v>
+        <v>0.924886226654053</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G736" t="n">
-        <v>0.895446836948395</v>
+        <v>0.89544677734375</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G738" t="n">
-        <v>0.867847442626953</v>
+        <v>0.867847383022308</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G741" t="n">
-        <v>0.884407103061676</v>
+        <v>0.884407043457031</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G744" t="n">
-        <v>0.94451230764389</v>
+        <v>0.94451242685318</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G746" t="n">
-        <v>0.938379168510437</v>
+        <v>0.938379287719727</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>1.557000041008</v>
       </c>
       <c r="G749" t="n">
-        <v>0.954938888549805</v>
+        <v>0.954938769340515</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G750" t="n">
-        <v>0.901580035686493</v>
+        <v>0.901579976081848</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>1.48699998855591</v>
       </c>
       <c r="G754" t="n">
-        <v>0.912006437778473</v>
+        <v>0.912006497383118</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G755" t="n">
-        <v>0.875207245349884</v>
+        <v>0.875207364559174</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G758" t="n">
-        <v>0.837181448936462</v>
+        <v>0.837181389331818</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G759" t="n">
-        <v>0.849447846412659</v>
+        <v>0.849447786808014</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G760" t="n">
-        <v>0.837181448936462</v>
+        <v>0.837181389331818</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G761" t="n">
-        <v>0.864780843257904</v>
+        <v>0.864780783653259</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G762" t="n">
-        <v>0.864780843257904</v>
+        <v>0.864780783653259</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>1.43099999427795</v>
       </c>
       <c r="G763" t="n">
-        <v>0.877660512924194</v>
+        <v>0.877660572528839</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>1.45700001716614</v>
       </c>
       <c r="G764" t="n">
-        <v>0.893606841564178</v>
+        <v>0.893606901168823</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G765" t="n">
-        <v>0.911393105983734</v>
+        <v>0.911393046379089</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G773" t="n">
-        <v>0.94451230764389</v>
+        <v>0.94451242685318</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G776" t="n">
-        <v>0.993578016757965</v>
+        <v>0.993577897548676</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G778" t="n">
-        <v>0.940832436084747</v>
+        <v>0.940832555294037</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>1.5</v>
       </c>
       <c r="G779" t="n">
-        <v>0.919979572296143</v>
+        <v>0.919979512691498</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G781" t="n">
-        <v>0.984991550445557</v>
+        <v>0.984991431236267</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G788" t="n">
-        <v>1.03221714496613</v>
+        <v>1.03221702575684</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>1.7039999961853</v>
       </c>
       <c r="G789" t="n">
-        <v>1.04509675502777</v>
+        <v>1.04509687423706</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G791" t="n">
-        <v>0.972111761569977</v>
+        <v>0.972111880779266</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G794" t="n">
-        <v>1.05491006374359</v>
+        <v>1.0549099445343</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G796" t="n">
-        <v>1.06901621818542</v>
+        <v>1.06901633739471</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G799" t="n">
-        <v>1.06901621818542</v>
+        <v>1.06901633739471</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G800" t="n">
-        <v>1.03957688808441</v>
+        <v>1.0395770072937</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G803" t="n">
-        <v>1.02792394161224</v>
+        <v>1.02792382240295</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>1.56900000572205</v>
       </c>
       <c r="G804" t="n">
-        <v>0.96229875087738</v>
+        <v>0.962298631668091</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>1.56700003147125</v>
       </c>
       <c r="G805" t="n">
-        <v>0.961072087287903</v>
+        <v>0.961071968078613</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>1.5789999961853</v>
       </c>
       <c r="G806" t="n">
-        <v>0.968431770801544</v>
+        <v>0.968431890010834</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>1.50600004196167</v>
       </c>
       <c r="G814" t="n">
-        <v>0.923659563064575</v>
+        <v>0.92365950345993</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G815" t="n">
-        <v>0.928566098213196</v>
+        <v>0.928566157817841</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G816" t="n">
-        <v>0.923046231269836</v>
+        <v>0.923046171665192</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G817" t="n">
-        <v>0.926112830638885</v>
+        <v>0.92611289024353</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>1.54100000858307</v>
       </c>
       <c r="G818" t="n">
-        <v>0.945125639438629</v>
+        <v>0.945125758647919</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.47300004959106</v>
       </c>
       <c r="G822" t="n">
-        <v>0.903420031070709</v>
+        <v>0.903419971466064</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G823" t="n">
-        <v>0.899126708507538</v>
+        <v>0.899126648902893</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>1.50100004673004</v>
       </c>
       <c r="G825" t="n">
-        <v>0.920592904090881</v>
+        <v>0.920592963695526</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>1.66100001335144</v>
       </c>
       <c r="G830" t="n">
-        <v>1.01872396469116</v>
+        <v>1.01872408390045</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>1.66299998760223</v>
       </c>
       <c r="G831" t="n">
-        <v>1.01995074748993</v>
+        <v>1.01995062828064</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G833" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G834" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G837" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>1.5789999961853</v>
       </c>
       <c r="G842" t="n">
-        <v>0.968431770801544</v>
+        <v>0.968431890010834</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G845" t="n">
-        <v>0.90280669927597</v>
+        <v>0.902806639671326</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G847" t="n">
-        <v>0.852514445781708</v>
+        <v>0.852514386177063</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G849" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.27799999713898</v>
       </c>
       <c r="G852" t="n">
-        <v>0.783822655677795</v>
+        <v>0.783822596073151</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G854" t="n">
-        <v>0.731077075004578</v>
+        <v>0.731077134609222</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G856" t="n">
-        <v>0.743343472480774</v>
+        <v>0.743343532085419</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>1.192999958992</v>
       </c>
       <c r="G857" t="n">
-        <v>0.731690466403961</v>
+        <v>0.731690406799316</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G859" t="n">
-        <v>0.69611781835556</v>
+        <v>0.696117877960205</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>1.17900002002716</v>
       </c>
       <c r="G864" t="n">
-        <v>0.723103940486908</v>
+        <v>0.723104000091553</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>1.17900002002716</v>
       </c>
       <c r="G867" t="n">
-        <v>0.723103940486908</v>
+        <v>0.723104000091553</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G870" t="n">
-        <v>0.722490608692169</v>
+        <v>0.722490668296814</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G871" t="n">
-        <v>0.716970860958099</v>
+        <v>0.716970801353455</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G874" t="n">
-        <v>0.716970860958099</v>
+        <v>0.716970801353455</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G875" t="n">
-        <v>0.721877336502075</v>
+        <v>0.72187739610672</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G880" t="n">
-        <v>0.722490608692169</v>
+        <v>0.722490668296814</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>1.22099995613098</v>
       </c>
       <c r="G886" t="n">
-        <v>0.748863399028778</v>
+        <v>0.748863339424133</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>1.25300002098083</v>
       </c>
       <c r="G891" t="n">
-        <v>0.76848965883255</v>
+        <v>0.768489599227905</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G895" t="n">
-        <v>0.761743068695068</v>
+        <v>0.761743128299713</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>1.25300002098083</v>
       </c>
       <c r="G896" t="n">
-        <v>0.76848965883255</v>
+        <v>0.768489599227905</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G897" t="n">
-        <v>0.763583123683929</v>
+        <v>0.763583064079285</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>1.21700000762939</v>
       </c>
       <c r="G902" t="n">
-        <v>0.746410071849823</v>
+        <v>0.746410131454468</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G905" t="n">
-        <v>0.788729131221771</v>
+        <v>0.788729190826416</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G907" t="n">
-        <v>0.813261985778809</v>
+        <v>0.813261926174164</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G909" t="n">
-        <v>0.781982600688934</v>
+        <v>0.781982660293579</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G914" t="n">
-        <v>0.7323037981987</v>
+        <v>0.732303738594055</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>1.17900002002716</v>
       </c>
       <c r="G916" t="n">
-        <v>0.723103940486908</v>
+        <v>0.723104000091553</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>1.192999958992</v>
       </c>
       <c r="G918" t="n">
-        <v>0.731690466403961</v>
+        <v>0.731690406799316</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G920" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G921" t="n">
-        <v>0.7323037981987</v>
+        <v>0.732303738594055</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>1.18099999427795</v>
       </c>
       <c r="G922" t="n">
-        <v>0.72433066368103</v>
+        <v>0.724330604076385</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G927" t="n">
-        <v>0.781982600688934</v>
+        <v>0.781982660293579</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G931" t="n">
-        <v>0.788729131221771</v>
+        <v>0.788729190826416</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>1.23699998855591</v>
       </c>
       <c r="G934" t="n">
-        <v>0.758676469326019</v>
+        <v>0.758676528930664</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G935" t="n">
-        <v>0.763583123683929</v>
+        <v>0.763583064079285</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G938" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>1.33700001239777</v>
       </c>
       <c r="G939" t="n">
-        <v>0.820008516311646</v>
+        <v>0.820008456707001</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G940" t="n">
-        <v>0.849447846412659</v>
+        <v>0.849447786808014</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G941" t="n">
-        <v>0.834114909172058</v>
+        <v>0.834114849567413</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G942" t="n">
-        <v>0.834114909172058</v>
+        <v>0.834114849567413</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G943" t="n">
-        <v>0.837181448936462</v>
+        <v>0.837181389331818</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G944" t="n">
-        <v>0.832888305187225</v>
+        <v>0.832888245582581</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G946" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>1.27600002288818</v>
       </c>
       <c r="G948" t="n">
-        <v>0.782596051692963</v>
+        <v>0.782595992088318</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>1.26300001144409</v>
       </c>
       <c r="G949" t="n">
-        <v>0.774622917175293</v>
+        <v>0.774622857570648</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G950" t="n">
-        <v>0.754383206367493</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>1.23099994659424</v>
       </c>
       <c r="G951" t="n">
-        <v>0.754996597766876</v>
+        <v>0.754996538162231</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G952" t="n">
-        <v>0.761743068695068</v>
+        <v>0.761743128299713</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G957" t="n">
-        <v>0.733530402183533</v>
+        <v>0.733530342578888</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G958" t="n">
-        <v>0.739050269126892</v>
+        <v>0.739050328731537</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G961" t="n">
-        <v>0.754383206367493</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G965" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>1.29900002479553</v>
       </c>
       <c r="G966" t="n">
-        <v>0.796702325344086</v>
+        <v>0.79670238494873</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>1.25300002098083</v>
       </c>
       <c r="G967" t="n">
-        <v>0.76848965883255</v>
+        <v>0.768489599227905</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>1.25100004673004</v>
       </c>
       <c r="G970" t="n">
-        <v>0.767263054847717</v>
+        <v>0.767262995243073</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G971" t="n">
-        <v>0.781982600688934</v>
+        <v>0.781982660293579</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G972" t="n">
-        <v>0.834114909172058</v>
+        <v>0.834114849567413</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G982" t="n">
-        <v>0.94451230764389</v>
+        <v>0.94451242685318</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G983" t="n">
-        <v>0.937152504920959</v>
+        <v>0.937152624130249</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>1.44900000095367</v>
       </c>
       <c r="G989" t="n">
-        <v>0.888700306415558</v>
+        <v>0.888700246810913</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G990" t="n">
-        <v>0.87214070558548</v>
+        <v>0.872140645980835</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G991" t="n">
-        <v>0.863554120063782</v>
+        <v>0.863554179668427</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G992" t="n">
-        <v>0.884407103061676</v>
+        <v>0.884407043457031</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>1.5</v>
       </c>
       <c r="G993" t="n">
-        <v>0.919979572296143</v>
+        <v>0.919979512691498</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>1.53100001811981</v>
       </c>
       <c r="G994" t="n">
-        <v>0.938992500305176</v>
+        <v>0.938992619514465</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G995" t="n">
-        <v>0.954325556755066</v>
+        <v>0.954325437545776</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>1.52699995040894</v>
       </c>
       <c r="G996" t="n">
-        <v>0.936539173126221</v>
+        <v>0.93653929233551</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>1.49300003051758</v>
       </c>
       <c r="G997" t="n">
-        <v>0.915686428546906</v>
+        <v>0.915686368942261</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1000" t="n">
-        <v>0.928566098213196</v>
+        <v>0.928566157817841</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1004" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.04141676425934</v>
+        <v>1.04141688346863</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1006" t="n">
-        <v>1.03344368934631</v>
+        <v>1.0334438085556</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.03957688808441</v>
+        <v>1.0395770072937</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.00277769565582</v>
+        <v>1.00277781486511</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1014" t="n">
-        <v>0.980084896087646</v>
+        <v>0.980085015296936</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1015" t="n">
-        <v>0.980084896087646</v>
+        <v>0.980085015296936</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1018" t="n">
-        <v>0.94451230764389</v>
+        <v>0.94451242685318</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G1019" t="n">
-        <v>0.958618760108948</v>
+        <v>0.958618640899658</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1025" t="n">
-        <v>0.980084896087646</v>
+        <v>0.980085015296936</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G1027" t="n">
-        <v>0.906486511230469</v>
+        <v>0.906486570835114</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1028" t="n">
-        <v>0.864780843257904</v>
+        <v>0.864780783653259</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1032" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G1038" t="n">
-        <v>0.781982600688934</v>
+        <v>0.781982660293579</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>1.2940000295639</v>
       </c>
       <c r="G1039" t="n">
-        <v>0.793635725975037</v>
+        <v>0.793635785579681</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>1.33700001239777</v>
       </c>
       <c r="G1045" t="n">
-        <v>0.820008516311646</v>
+        <v>0.820008456707001</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>1.30200004577637</v>
       </c>
       <c r="G1047" t="n">
-        <v>0.798542380332947</v>
+        <v>0.798542320728302</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G1048" t="n">
-        <v>0.814488589763641</v>
+        <v>0.814488530158997</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1049" t="n">
-        <v>0.813261985778809</v>
+        <v>0.813261926174164</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>1.28699994087219</v>
       </c>
       <c r="G1052" t="n">
-        <v>0.789342403411865</v>
+        <v>0.78934246301651</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>1.192999958992</v>
       </c>
       <c r="G1053" t="n">
-        <v>0.731690466403961</v>
+        <v>0.731690406799316</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G1055" t="n">
-        <v>0.708997666835785</v>
+        <v>0.70899760723114</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>1.13699996471405</v>
       </c>
       <c r="G1056" t="n">
-        <v>0.697344541549683</v>
+        <v>0.697344481945038</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.496789008378983</v>
+        <v>0.496788948774338</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.451403349637985</v>
+        <v>0.451403319835663</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.472256153821945</v>
+        <v>0.47225621342659</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.461216449737549</v>
+        <v>0.461216419935226</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>0.816999971866608</v>
       </c>
       <c r="G1074" t="n">
-        <v>0.501082181930542</v>
+        <v>0.501082241535187</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>0.732999980449677</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.449563354253769</v>
+        <v>0.449563324451447</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1077" t="n">
-        <v>0.417057454586029</v>
+        <v>0.417057424783707</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>0.679000020027161</v>
       </c>
       <c r="G1078" t="n">
-        <v>0.416444152593613</v>
+        <v>0.41644412279129</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1080" t="n">
-        <v>0.394977927207947</v>
+        <v>0.394977897405624</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>0.679000020027161</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.416444152593613</v>
+        <v>0.41644412279129</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>0.901000022888184</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.552601099014282</v>
+        <v>0.552601158618927</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.496789008378983</v>
+        <v>0.496788948774338</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>0.816999971866608</v>
       </c>
       <c r="G1089" t="n">
-        <v>0.501082181930542</v>
+        <v>0.501082241535187</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1095" t="n">
-        <v>0.533588171005249</v>
+        <v>0.533588111400604</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1098" t="n">
-        <v>0.533588171005249</v>
+        <v>0.533588111400604</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G1099" t="n">
-        <v>0.536041438579559</v>
+        <v>0.536041498184204</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G1100" t="n">
-        <v>0.512121975421906</v>
+        <v>0.512121915817261</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1104" t="n">
-        <v>0.518868505954742</v>
+        <v>0.518868565559387</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1107" t="n">
-        <v>0.518868505954742</v>
+        <v>0.518868565559387</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>0.820999979972839</v>
       </c>
       <c r="G1109" t="n">
-        <v>0.503535449504852</v>
+        <v>0.503535509109497</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>0.848999977111816</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.520708382129669</v>
+        <v>0.520708441734314</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.491882383823395</v>
+        <v>0.49188244342804</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1116" t="n">
-        <v>0.518868505954742</v>
+        <v>0.518868565559387</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>1.07400000095367</v>
       </c>
       <c r="G1125" t="n">
-        <v>0.658705472946167</v>
+        <v>0.658705413341522</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>0.949000000953674</v>
       </c>
       <c r="G1129" t="n">
-        <v>0.582040429115295</v>
+        <v>0.582040369510651</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1130" t="n">
-        <v>0.569160640239716</v>
+        <v>0.56916069984436</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>0.876999974250793</v>
       </c>
       <c r="G1134" t="n">
-        <v>0.537881374359131</v>
+        <v>0.537881433963776</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>0.842999994754791</v>
       </c>
       <c r="G1139" t="n">
-        <v>0.517028510570526</v>
+        <v>0.517028570175171</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1140" t="n">
-        <v>0.527455031871796</v>
+        <v>0.527454972267151</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.516415238380432</v>
+        <v>0.516415178775787</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1147" t="n">
-        <v>0.528681576251984</v>
+        <v>0.528681635856628</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1149" t="n">
-        <v>0.522548377513885</v>
+        <v>0.52254843711853</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>0.859000027179718</v>
       </c>
       <c r="G1150" t="n">
-        <v>0.526841640472412</v>
+        <v>0.526841700077057</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1151" t="n">
-        <v>0.534814774990082</v>
+        <v>0.534814834594727</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1155" t="n">
-        <v>0.53849470615387</v>
+        <v>0.538494765758514</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1156" t="n">
-        <v>0.542174637317657</v>
+        <v>0.542174696922302</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.542174637317657</v>
+        <v>0.542174696922302</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>0.890999972820282</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.546467900276184</v>
+        <v>0.546467840671539</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.564254224300385</v>
+        <v>0.56425416469574</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1167" t="n">
-        <v>0.575293898582458</v>
+        <v>0.575293958187103</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>0.939000010490417</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.575907289981842</v>
+        <v>0.575907230377197</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>0.930999994277954</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.571000635623932</v>
+        <v>0.571000695228577</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.569160640239716</v>
+        <v>0.56916069984436</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>0.902999997138977</v>
       </c>
       <c r="G1186" t="n">
-        <v>0.553827702999115</v>
+        <v>0.55382776260376</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>0.916999995708466</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.562414228916168</v>
+        <v>0.562414169311523</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.547081232070923</v>
+        <v>0.547081172466278</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>0.939000010490417</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.575907289981842</v>
+        <v>0.575907230377197</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.569160640239716</v>
+        <v>0.56916069984436</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.569160640239716</v>
+        <v>0.56916069984436</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.592466831207275</v>
+        <v>0.59246689081192</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.555667638778687</v>
+        <v>0.555667698383331</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>0.944999992847443</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.579587161540985</v>
+        <v>0.57958710193634</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>0.958999991416931</v>
       </c>
       <c r="G1213" t="n">
-        <v>0.588173627853394</v>
+        <v>0.588173687458038</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.565480828285217</v>
+        <v>0.565480768680573</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>0.916999995708466</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.562414228916168</v>
+        <v>0.562414169311523</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>0.944999992847443</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.579587161540985</v>
+        <v>0.57958710193634</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>0.967000007629395</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.593080222606659</v>
+        <v>0.593080163002014</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.619452893733978</v>
+        <v>0.619452953338623</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>1.15799999237061</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.710224211215973</v>
+        <v>0.710224270820618</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1243" t="n">
-        <v>0.711450815200806</v>
+        <v>0.71145087480545</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.697957873344421</v>
+        <v>0.697957813739777</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G1245" t="n">
-        <v>0.708997666835785</v>
+        <v>0.70899760723114</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1247" t="n">
-        <v>0.788729131221771</v>
+        <v>0.788729190826416</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1249" t="n">
-        <v>0.821848511695862</v>
+        <v>0.821848452091217</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1252" t="n">
-        <v>0.754383206367493</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.743343472480774</v>
+        <v>0.743343532085419</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.739663660526276</v>
+        <v>0.739663600921631</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1262" t="n">
-        <v>0.759289920330048</v>
+        <v>0.759289860725403</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.712677538394928</v>
+        <v>0.712677478790283</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.723717212677002</v>
+        <v>0.723717272281647</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.723717212677002</v>
+        <v>0.723717272281647</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1272" t="n">
-        <v>0.743343472480774</v>
+        <v>0.743343532085419</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.761743068695068</v>
+        <v>0.761743128299713</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1277" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1279" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1285" t="n">
-        <v>0.723717212677002</v>
+        <v>0.723717272281647</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G1286" t="n">
-        <v>0.702864468097687</v>
+        <v>0.702864408493042</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1287" t="n">
-        <v>0.712677538394928</v>
+        <v>0.712677478790283</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>1.14800000190735</v>
       </c>
       <c r="G1289" t="n">
-        <v>0.704091012477875</v>
+        <v>0.70409107208252</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G1291" t="n">
-        <v>0.688144683837891</v>
+        <v>0.688144743442535</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.708997666835785</v>
+        <v>0.70899760723114</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1299" t="n">
-        <v>0.743343472480774</v>
+        <v>0.743343532085419</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1301" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1304" t="n">
-        <v>0.759289920330048</v>
+        <v>0.759289860725403</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1306" t="n">
-        <v>0.762969791889191</v>
+        <v>0.762969732284546</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1314" t="n">
-        <v>0.824301660060883</v>
+        <v>0.824301719665527</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1318" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1328" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1329" t="n">
-        <v>0.813261985778809</v>
+        <v>0.813261926174164</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1330" t="n">
-        <v>0.843927979469299</v>
+        <v>0.843928039073944</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1333" t="n">
-        <v>0.813261985778809</v>
+        <v>0.813261926174164</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1335" t="n">
-        <v>0.834114909172058</v>
+        <v>0.834114849567413</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1338" t="n">
-        <v>0.813261985778809</v>
+        <v>0.813261926174164</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1340" t="n">
-        <v>0.843927979469299</v>
+        <v>0.843928039073944</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1341" t="n">
-        <v>0.834114909172058</v>
+        <v>0.834114849567413</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G1343" t="n">
-        <v>0.842701256275177</v>
+        <v>0.842701315879822</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G1344" t="n">
-        <v>0.842701256275177</v>
+        <v>0.842701315879822</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1351" t="n">
-        <v>0.877047181129456</v>
+        <v>0.8770472407341</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1354" t="n">
-        <v>0.890540242195129</v>
+        <v>0.890540301799774</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1355" t="n">
-        <v>0.864780843257904</v>
+        <v>0.864780783653259</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G1356" t="n">
-        <v>0.880727171897888</v>
+        <v>0.880727112293243</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1357" t="n">
-        <v>0.890540242195129</v>
+        <v>0.890540301799774</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G1358" t="n">
-        <v>0.87214070558548</v>
+        <v>0.872140645980835</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1364" t="n">
-        <v>0.863554120063782</v>
+        <v>0.863554179668427</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1365" t="n">
-        <v>0.863554120063782</v>
+        <v>0.863554179668427</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1366" t="n">
-        <v>0.843927979469299</v>
+        <v>0.843928039073944</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1368" t="n">
-        <v>0.834114909172058</v>
+        <v>0.834114849567413</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1373" t="n">
-        <v>0.834114909172058</v>
+        <v>0.834114849567413</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1375" t="n">
-        <v>0.863554120063782</v>
+        <v>0.863554179668427</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G1379" t="n">
-        <v>0.912619769573212</v>
+        <v>0.912619829177856</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>1.5</v>
       </c>
       <c r="G1380" t="n">
-        <v>0.919979572296143</v>
+        <v>0.919979512691498</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G1381" t="n">
-        <v>0.940832436084747</v>
+        <v>0.940832555294037</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G1382" t="n">
-        <v>0.929792761802673</v>
+        <v>0.929792702198029</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G1383" t="n">
-        <v>0.915073096752167</v>
+        <v>0.915073037147522</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1385" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>1.5</v>
       </c>
       <c r="G1387" t="n">
-        <v>0.919979572296143</v>
+        <v>0.919979512691498</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1388" t="n">
-        <v>0.890540242195129</v>
+        <v>0.890540301799774</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1391" t="n">
-        <v>0.890540242195129</v>
+        <v>0.890540301799774</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G1392" t="n">
-        <v>0.884407103061676</v>
+        <v>0.884407043457031</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G1393" t="n">
-        <v>0.884407103061676</v>
+        <v>0.884407043457031</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1396" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>1.27600002288818</v>
       </c>
       <c r="G1402" t="n">
-        <v>0.782596051692963</v>
+        <v>0.782595992088318</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1408" t="n">
-        <v>0.754383206367493</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1409" t="n">
-        <v>0.723717212677002</v>
+        <v>0.723717272281647</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.852514445781708</v>
+        <v>0.852514386177063</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1427" t="n">
-        <v>0.864780843257904</v>
+        <v>0.864780783653259</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G1428" t="n">
-        <v>0.899126708507538</v>
+        <v>0.899126648902893</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G1435" t="n">
-        <v>0.842701256275177</v>
+        <v>0.842701315879822</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1437" t="n">
-        <v>0.843927979469299</v>
+        <v>0.843928039073944</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1438" t="n">
-        <v>0.852514445781708</v>
+        <v>0.852514386177063</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1444" t="n">
-        <v>0.852514445781708</v>
+        <v>0.852514386177063</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1453" t="n">
-        <v>0.813261985778809</v>
+        <v>0.813261926174164</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>1.27600002288818</v>
       </c>
       <c r="G1454" t="n">
-        <v>0.782596051692963</v>
+        <v>0.782595992088318</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1455" t="n">
-        <v>0.772782862186432</v>
+        <v>0.772782921791077</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1456" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1458" t="n">
-        <v>0.813261985778809</v>
+        <v>0.813261926174164</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1464" t="n">
-        <v>0.788729131221771</v>
+        <v>0.788729190826416</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1466" t="n">
-        <v>0.78136932849884</v>
+        <v>0.781369388103485</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>1.30200004577637</v>
       </c>
       <c r="G1468" t="n">
-        <v>0.798542380332947</v>
+        <v>0.798542320728302</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1469" t="n">
-        <v>0.788729131221771</v>
+        <v>0.788729190826416</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1473" t="n">
-        <v>0.834114909172058</v>
+        <v>0.834114849567413</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1474" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1476" t="n">
-        <v>0.824301660060883</v>
+        <v>0.824301719665527</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1477" t="n">
-        <v>0.85619443655014</v>
+        <v>0.856194376945496</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>1.44799995422363</v>
       </c>
       <c r="G1480" t="n">
-        <v>0.888086974620819</v>
+        <v>0.888086915016174</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1482" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1483" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1484" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1486" t="n">
-        <v>0.824301660060883</v>
+        <v>0.824301719665527</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1489" t="n">
-        <v>0.824301660060883</v>
+        <v>0.824301719665527</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1493" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1494" t="n">
-        <v>0.824301660060883</v>
+        <v>0.824301719665527</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1496" t="n">
-        <v>0.821848511695862</v>
+        <v>0.821848452091217</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1498" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1501" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>1.2940000295639</v>
       </c>
       <c r="G1502" t="n">
-        <v>0.793635725975037</v>
+        <v>0.793635785579681</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1505" t="n">
-        <v>0.735983729362488</v>
+        <v>0.735983669757843</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1506" t="n">
-        <v>0.743343472480774</v>
+        <v>0.743343532085419</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G1507" t="n">
-        <v>0.733530402183533</v>
+        <v>0.733530342578888</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G1509" t="n">
-        <v>0.722490608692169</v>
+        <v>0.722490668296814</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1511" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1512" t="n">
-        <v>0.743343472480774</v>
+        <v>0.743343532085419</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1513" t="n">
-        <v>0.743343472480774</v>
+        <v>0.743343532085419</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1514" t="n">
-        <v>0.735983729362488</v>
+        <v>0.735983669757843</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1516" t="n">
-        <v>0.735983729362488</v>
+        <v>0.735983669757843</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G1518" t="n">
-        <v>0.731077075004578</v>
+        <v>0.731077134609222</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G1520" t="n">
-        <v>0.738436937332153</v>
+        <v>0.738436996936798</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G1521" t="n">
-        <v>0.731077075004578</v>
+        <v>0.731077134609222</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1524" t="n">
-        <v>0.723717212677002</v>
+        <v>0.723717272281647</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1525" t="n">
-        <v>0.723717212677002</v>
+        <v>0.723717272281647</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1532" t="n">
-        <v>0.78136932849884</v>
+        <v>0.781369388103485</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>1.26199996471405</v>
       </c>
       <c r="G1534" t="n">
-        <v>0.774009466171265</v>
+        <v>0.774009525775909</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1536" t="n">
-        <v>0.788729131221771</v>
+        <v>0.788729190826416</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1537" t="n">
-        <v>0.772782862186432</v>
+        <v>0.772782921791077</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1539" t="n">
-        <v>0.762969791889191</v>
+        <v>0.762969732284546</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G1542" t="n">
-        <v>0.731077075004578</v>
+        <v>0.731077134609222</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1544" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1547" t="n">
-        <v>0.7323037981987</v>
+        <v>0.732303738594055</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1548" t="n">
-        <v>0.735983729362488</v>
+        <v>0.735983669757843</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1549" t="n">
-        <v>0.735983729362488</v>
+        <v>0.735983669757843</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1550" t="n">
-        <v>0.754383206367493</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1554" t="n">
-        <v>0.739663660526276</v>
+        <v>0.739663600921631</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1557" t="n">
-        <v>0.711450815200806</v>
+        <v>0.71145087480545</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1561" t="n">
-        <v>0.712677538394928</v>
+        <v>0.712677478790283</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>1.14800000190735</v>
       </c>
       <c r="G1562" t="n">
-        <v>0.704091012477875</v>
+        <v>0.70409107208252</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>1.06200003623962</v>
       </c>
       <c r="G1565" t="n">
-        <v>0.651345610618591</v>
+        <v>0.651345551013947</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>1.12399995326996</v>
       </c>
       <c r="G1567" t="n">
-        <v>0.689371407032013</v>
+        <v>0.689371347427368</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1568" t="n">
-        <v>0.631719350814819</v>
+        <v>0.631719291210175</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>0.788999974727631</v>
       </c>
       <c r="G1572" t="n">
-        <v>0.483909219503403</v>
+        <v>0.483909279108047</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>0.802999973297119</v>
       </c>
       <c r="G1575" t="n">
-        <v>0.492495775222778</v>
+        <v>0.492495715618134</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1579" t="n">
-        <v>0.53849470615387</v>
+        <v>0.538494765758514</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1586" t="n">
-        <v>0.534814774990082</v>
+        <v>0.534814834594727</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G1588" t="n">
-        <v>0.565480828285217</v>
+        <v>0.565480768680573</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>0.890999972820282</v>
       </c>
       <c r="G1589" t="n">
-        <v>0.546467900276184</v>
+        <v>0.546467840671539</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G1593" t="n">
-        <v>0.536041438579559</v>
+        <v>0.536041498184204</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1596" t="n">
-        <v>0.510282039642334</v>
+        <v>0.510281980037689</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1597" t="n">
-        <v>0.515188574790955</v>
+        <v>0.51518851518631</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1599" t="n">
-        <v>0.528681576251984</v>
+        <v>0.528681635856628</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1602" t="n">
-        <v>0.564254224300385</v>
+        <v>0.56425416469574</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G1604" t="n">
-        <v>0.577747225761414</v>
+        <v>0.577747166156769</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G1605" t="n">
-        <v>0.577747225761414</v>
+        <v>0.577747166156769</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>0.859000027179718</v>
       </c>
       <c r="G1609" t="n">
-        <v>0.526841640472412</v>
+        <v>0.526841700077057</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1610" t="n">
-        <v>0.533588171005249</v>
+        <v>0.533588111400604</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1621" t="n">
-        <v>0.527455031871796</v>
+        <v>0.527454972267151</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1622" t="n">
-        <v>0.533588171005249</v>
+        <v>0.533588111400604</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1626" t="n">
-        <v>0.527455031871796</v>
+        <v>0.527454972267151</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>0.950999975204468</v>
       </c>
       <c r="G1630" t="n">
-        <v>0.583267092704773</v>
+        <v>0.583267033100128</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1634" t="n">
-        <v>0.619452893733978</v>
+        <v>0.619452953338623</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1638" t="n">
-        <v>0.619452893733978</v>
+        <v>0.619452953338623</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1643" t="n">
-        <v>0.533588171005249</v>
+        <v>0.533588111400604</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>0.898999989032745</v>
       </c>
       <c r="G1645" t="n">
-        <v>0.551374435424805</v>
+        <v>0.551374495029449</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G1648" t="n">
-        <v>0.547081232070923</v>
+        <v>0.547081172466278</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>0.898999989032745</v>
       </c>
       <c r="G1649" t="n">
-        <v>0.551374435424805</v>
+        <v>0.551374495029449</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1651" t="n">
-        <v>0.533588171005249</v>
+        <v>0.533588111400604</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1652" t="n">
-        <v>0.527455031871796</v>
+        <v>0.527454972267151</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G1655" t="n">
-        <v>0.512121975421906</v>
+        <v>0.512121915817261</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>0.788999974727631</v>
       </c>
       <c r="G1657" t="n">
-        <v>0.483909219503403</v>
+        <v>0.483909279108047</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>0.785000026226044</v>
       </c>
       <c r="G1665" t="n">
-        <v>0.481456011533737</v>
+        <v>0.481455981731415</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>0.930999994277954</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.571000635623932</v>
+        <v>0.571000695228577</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>0.922999978065491</v>
       </c>
       <c r="G1673" t="n">
-        <v>0.566094160079956</v>
+        <v>0.566094100475311</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>0.922999978065491</v>
       </c>
       <c r="G1678" t="n">
-        <v>0.566094160079956</v>
+        <v>0.566094100475311</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>0.890999972820282</v>
       </c>
       <c r="G1680" t="n">
-        <v>0.546467900276184</v>
+        <v>0.546467840671539</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G1682" t="n">
-        <v>0.548921167850494</v>
+        <v>0.54892110824585</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>0.898999989032745</v>
       </c>
       <c r="G1687" t="n">
-        <v>0.551374435424805</v>
+        <v>0.551374495029449</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1688" t="n">
-        <v>0.53849470615387</v>
+        <v>0.538494765758514</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>0.898999989032745</v>
       </c>
       <c r="G1690" t="n">
-        <v>0.551374435424805</v>
+        <v>0.551374495029449</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>0.870999991893768</v>
       </c>
       <c r="G1693" t="n">
-        <v>0.534201443195343</v>
+        <v>0.534201502799988</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.527455031871796</v>
+        <v>0.527454972267151</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1696" t="n">
-        <v>0.515188574790955</v>
+        <v>0.51518851518631</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1702" t="n">
-        <v>0.485749214887619</v>
+        <v>0.485749274492264</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1703" t="n">
-        <v>0.485749214887619</v>
+        <v>0.485749274492264</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1706" t="n">
-        <v>0.486975878477097</v>
+        <v>0.486975908279419</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1710" t="n">
-        <v>0.472256153821945</v>
+        <v>0.47225621342659</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1712" t="n">
-        <v>0.453243255615234</v>
+        <v>0.453243285417557</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1716" t="n">
-        <v>0.447723418474197</v>
+        <v>0.447723388671875</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G1717" t="n">
-        <v>0.432390421628952</v>
+        <v>0.43239039182663</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G1720" t="n">
-        <v>0.438523590564728</v>
+        <v>0.43852362036705</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1722" t="n">
-        <v>0.42809721827507</v>
+        <v>0.428097188472748</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1726" t="n">
-        <v>0.417057454586029</v>
+        <v>0.417057424783707</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>0.686999976634979</v>
       </c>
       <c r="G1727" t="n">
-        <v>0.421350628137589</v>
+        <v>0.421350657939911</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1729" t="n">
-        <v>0.431777060031891</v>
+        <v>0.431777089834213</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1733" t="n">
-        <v>0.527455031871796</v>
+        <v>0.527454972267151</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>0.842999994754791</v>
       </c>
       <c r="G1737" t="n">
-        <v>0.517028510570526</v>
+        <v>0.517028570175171</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1744" t="n">
-        <v>0.513961970806122</v>
+        <v>0.513961911201477</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1745" t="n">
-        <v>0.515188574790955</v>
+        <v>0.51518851518631</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1746" t="n">
-        <v>0.515188574790955</v>
+        <v>0.51518851518631</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>0.859000027179718</v>
       </c>
       <c r="G1747" t="n">
-        <v>0.526841640472412</v>
+        <v>0.526841700077057</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G1749" t="n">
-        <v>0.586333632469177</v>
+        <v>0.586333692073822</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1750" t="n">
-        <v>0.575293898582458</v>
+        <v>0.575293958187103</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1754" t="n">
-        <v>0.542174637317657</v>
+        <v>0.542174696922302</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1756" t="n">
-        <v>0.525001645088196</v>
+        <v>0.525001704692841</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1759" t="n">
-        <v>0.534814774990082</v>
+        <v>0.534814834594727</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1764" t="n">
-        <v>0.525001645088196</v>
+        <v>0.525001704692841</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1769" t="n">
-        <v>0.518868505954742</v>
+        <v>0.518868565559387</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1772" t="n">
-        <v>0.528681576251984</v>
+        <v>0.528681635856628</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1773" t="n">
-        <v>0.527455031871796</v>
+        <v>0.527454972267151</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1774" t="n">
-        <v>0.533588171005249</v>
+        <v>0.533588111400604</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G1777" t="n">
-        <v>0.577747225761414</v>
+        <v>0.577747166156769</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G1778" t="n">
-        <v>0.567934095859528</v>
+        <v>0.567934036254883</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1781" t="n">
-        <v>0.575293898582458</v>
+        <v>0.575293958187103</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G1785" t="n">
-        <v>0.577747225761414</v>
+        <v>0.577747166156769</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>0.944999992847443</v>
       </c>
       <c r="G1786" t="n">
-        <v>0.579587161540985</v>
+        <v>0.57958710193634</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>0.950999975204468</v>
       </c>
       <c r="G1787" t="n">
-        <v>0.583267092704773</v>
+        <v>0.583267033100128</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1790" t="n">
-        <v>0.619452893733978</v>
+        <v>0.619452953338623</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>1.0460000038147</v>
       </c>
       <c r="G1791" t="n">
-        <v>0.641532480716705</v>
+        <v>0.641532421112061</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1792" t="n">
-        <v>0.656252145767212</v>
+        <v>0.656252205371857</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1795" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1797" t="n">
-        <v>0.673425018787384</v>
+        <v>0.673425078392029</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1802" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1803" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1804" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G1805" t="n">
-        <v>0.688144683837891</v>
+        <v>0.688144743442535</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G1807" t="n">
-        <v>0.702864468097687</v>
+        <v>0.702864408493042</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1810" t="n">
-        <v>0.723717212677002</v>
+        <v>0.723717272281647</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1812" t="n">
-        <v>0.7323037981987</v>
+        <v>0.732303738594055</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1814" t="n">
-        <v>0.743343472480774</v>
+        <v>0.743343532085419</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1815" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>1.11800003051758</v>
       </c>
       <c r="G1822" t="n">
-        <v>0.685691475868225</v>
+        <v>0.68569141626358</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1826" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1827" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G1828" t="n">
-        <v>0.688144683837891</v>
+        <v>0.688144743442535</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1831" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1834" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1839" t="n">
-        <v>0.673425018787384</v>
+        <v>0.673425078392029</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>1.11800003051758</v>
       </c>
       <c r="G1845" t="n">
-        <v>0.685691475868225</v>
+        <v>0.68569141626358</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1846" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>1.12399995326996</v>
       </c>
       <c r="G1848" t="n">
-        <v>0.689371407032013</v>
+        <v>0.689371347427368</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1849" t="n">
-        <v>0.686918079853058</v>
+        <v>0.686918139457703</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G1850" t="n">
-        <v>0.697957873344421</v>
+        <v>0.697957813739777</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1851" t="n">
-        <v>0.686918079853058</v>
+        <v>0.686918139457703</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1852" t="n">
-        <v>0.686918079853058</v>
+        <v>0.686918139457703</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G1853" t="n">
-        <v>0.708997666835785</v>
+        <v>0.70899760723114</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1856" t="n">
-        <v>0.754383206367493</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1857" t="n">
-        <v>0.743343472480774</v>
+        <v>0.743343532085419</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1860" t="n">
-        <v>0.7323037981987</v>
+        <v>0.732303738594055</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1861" t="n">
-        <v>0.723717212677002</v>
+        <v>0.723717272281647</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1873" t="n">
-        <v>0.711450815200806</v>
+        <v>0.71145087480545</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1874" t="n">
-        <v>0.711450815200806</v>
+        <v>0.71145087480545</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>1.15400004386902</v>
       </c>
       <c r="G1875" t="n">
-        <v>0.707770943641663</v>
+        <v>0.707771003246307</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>1.15400004386902</v>
       </c>
       <c r="G1876" t="n">
-        <v>0.707770943641663</v>
+        <v>0.707771003246307</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>1.15400004386902</v>
       </c>
       <c r="G1878" t="n">
-        <v>0.707770943641663</v>
+        <v>0.707771003246307</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1879" t="n">
-        <v>0.711450815200806</v>
+        <v>0.71145087480545</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G1882" t="n">
-        <v>0.688144683837891</v>
+        <v>0.688144743442535</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.688144683837891</v>
+        <v>0.688144743442535</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49379,7 +49379,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.686918079853058</v>
+        <v>0.686918139457703</v>
       </c>
       <c r="H1885" t="s">
         <v>8</v>
@@ -49405,7 +49405,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.673425018787384</v>
+        <v>0.673425078392029</v>
       </c>
       <c r="H1886" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1891" t="n">
-        <v>0.711450815200806</v>
+        <v>0.71145087480545</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49561,7 +49561,7 @@
         <v>1.15799999237061</v>
       </c>
       <c r="G1892" t="n">
-        <v>0.710224211215973</v>
+        <v>0.710224270820618</v>
       </c>
       <c r="H1892" t="s">
         <v>8</v>
@@ -50003,7 +50003,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1909" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1909" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1910" t="n">
-        <v>0.754383206367493</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1914" t="n">
-        <v>0.759289920330048</v>
+        <v>0.759289860725403</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>1.28799998760223</v>
       </c>
       <c r="G1919" t="n">
-        <v>0.789955854415894</v>
+        <v>0.789955794811249</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1920" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1921" t="n">
-        <v>0.78136932849884</v>
+        <v>0.781369388103485</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50367,7 +50367,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1923" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1923" t="s">
         <v>8</v>
@@ -50393,7 +50393,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1924" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1924" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1925" t="n">
-        <v>0.821848511695862</v>
+        <v>0.821848452091217</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50445,7 +50445,7 @@
         <v>1.28799998760223</v>
       </c>
       <c r="G1926" t="n">
-        <v>0.789955854415894</v>
+        <v>0.789955794811249</v>
       </c>
       <c r="H1926" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1931" t="n">
-        <v>0.78136932849884</v>
+        <v>0.781369388103485</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50705,7 +50705,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1936" t="n">
-        <v>0.735983729362488</v>
+        <v>0.735983669757843</v>
       </c>
       <c r="H1936" t="s">
         <v>8</v>
@@ -50757,7 +50757,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1938" t="n">
-        <v>0.759289920330048</v>
+        <v>0.759289860725403</v>
       </c>
       <c r="H1938" t="s">
         <v>8</v>
@@ -50835,7 +50835,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1941" t="n">
-        <v>0.78136932849884</v>
+        <v>0.781369388103485</v>
       </c>
       <c r="H1941" t="s">
         <v>8</v>
@@ -50887,7 +50887,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1943" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1943" t="s">
         <v>8</v>
@@ -51121,7 +51121,7 @@
         <v>1.26199996471405</v>
       </c>
       <c r="G1952" t="n">
-        <v>0.774009466171265</v>
+        <v>0.774009525775909</v>
       </c>
       <c r="H1952" t="s">
         <v>8</v>
@@ -51147,7 +51147,7 @@
         <v>1.27600002288818</v>
       </c>
       <c r="G1953" t="n">
-        <v>0.782596051692963</v>
+        <v>0.782595992088318</v>
       </c>
       <c r="H1953" t="s">
         <v>8</v>
@@ -51173,7 +51173,7 @@
         <v>1.27600002288818</v>
       </c>
       <c r="G1954" t="n">
-        <v>0.782596051692963</v>
+        <v>0.782595992088318</v>
       </c>
       <c r="H1954" t="s">
         <v>8</v>
@@ -51199,7 +51199,7 @@
         <v>1.28799998760223</v>
       </c>
       <c r="G1955" t="n">
-        <v>0.789955854415894</v>
+        <v>0.789955794811249</v>
       </c>
       <c r="H1955" t="s">
         <v>8</v>
@@ -51251,7 +51251,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1957" t="n">
-        <v>0.772782862186432</v>
+        <v>0.772782921791077</v>
       </c>
       <c r="H1957" t="s">
         <v>8</v>
@@ -51329,7 +51329,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1960" t="n">
-        <v>0.78136932849884</v>
+        <v>0.781369388103485</v>
       </c>
       <c r="H1960" t="s">
         <v>8</v>
@@ -51459,7 +51459,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1965" t="n">
-        <v>0.821848511695862</v>
+        <v>0.821848452091217</v>
       </c>
       <c r="H1965" t="s">
         <v>8</v>
@@ -51537,7 +51537,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1968" t="n">
-        <v>0.889313638210297</v>
+        <v>0.889313578605652</v>
       </c>
       <c r="H1968" t="s">
         <v>8</v>
@@ -51563,7 +51563,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G1969" t="n">
-        <v>0.924886167049408</v>
+        <v>0.924886226654053</v>
       </c>
       <c r="H1969" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1971" t="n">
-        <v>0.907713234424591</v>
+        <v>0.907713174819946</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51641,7 +51641,7 @@
         <v>1.46399998664856</v>
       </c>
       <c r="G1972" t="n">
-        <v>0.89790004491806</v>
+        <v>0.897900104522705</v>
       </c>
       <c r="H1972" t="s">
         <v>8</v>
@@ -51667,7 +51667,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G1973" t="n">
-        <v>0.912619769573212</v>
+        <v>0.912619829177856</v>
       </c>
       <c r="H1973" t="s">
         <v>8</v>
@@ -51693,7 +51693,7 @@
         <v>1.50399994850159</v>
       </c>
       <c r="G1974" t="n">
-        <v>0.922432899475098</v>
+        <v>0.922432839870453</v>
       </c>
       <c r="H1974" t="s">
         <v>8</v>
@@ -51745,7 +51745,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1976" t="n">
-        <v>0.926112830638885</v>
+        <v>0.92611289024353</v>
       </c>
       <c r="H1976" t="s">
         <v>8</v>
@@ -51771,7 +51771,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1977" t="n">
-        <v>0.928566098213196</v>
+        <v>0.928566157817841</v>
       </c>
       <c r="H1977" t="s">
         <v>8</v>
@@ -51823,7 +51823,7 @@
         <v>1.58800005912781</v>
       </c>
       <c r="G1979" t="n">
-        <v>0.973951756954193</v>
+        <v>0.973951816558838</v>
       </c>
       <c r="H1979" t="s">
         <v>8</v>
@@ -51849,7 +51849,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G1980" t="n">
-        <v>1.04141676425934</v>
+        <v>1.04141688346863</v>
       </c>
       <c r="H1980" t="s">
         <v>8</v>
@@ -51875,7 +51875,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G1981" t="n">
-        <v>1.02792394161224</v>
+        <v>1.02792382240295</v>
       </c>
       <c r="H1981" t="s">
         <v>8</v>
@@ -51901,7 +51901,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G1982" t="n">
-        <v>1.0070708990097</v>
+        <v>1.00707101821899</v>
       </c>
       <c r="H1982" t="s">
         <v>8</v>
@@ -52083,7 +52083,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1989" t="n">
-        <v>0.993578016757965</v>
+        <v>0.993577897548676</v>
       </c>
       <c r="H1989" t="s">
         <v>8</v>
@@ -52213,7 +52213,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1994" t="n">
-        <v>0.937152504920959</v>
+        <v>0.937152624130249</v>
       </c>
       <c r="H1994" t="s">
         <v>8</v>
@@ -52291,7 +52291,7 @@
         <v>1.57799994945526</v>
       </c>
       <c r="G1997" t="n">
-        <v>0.967818439006805</v>
+        <v>0.967818558216095</v>
       </c>
       <c r="H1997" t="s">
         <v>8</v>
@@ -52343,7 +52343,7 @@
         <v>1.5</v>
       </c>
       <c r="G1999" t="n">
-        <v>0.919979572296143</v>
+        <v>0.919979512691498</v>
       </c>
       <c r="H1999" t="s">
         <v>8</v>
@@ -52447,7 +52447,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G2003" t="n">
-        <v>0.980084896087646</v>
+        <v>0.980085015296936</v>
       </c>
       <c r="H2003" t="s">
         <v>8</v>
@@ -52473,7 +52473,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G2004" t="n">
-        <v>1.01075088977814</v>
+        <v>1.01075100898743</v>
       </c>
       <c r="H2004" t="s">
         <v>8</v>
@@ -52629,7 +52629,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2010" t="n">
-        <v>0.993578016757965</v>
+        <v>0.993577897548676</v>
       </c>
       <c r="H2010" t="s">
         <v>8</v>
@@ -52681,7 +52681,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G2012" t="n">
-        <v>0.98376476764679</v>
+        <v>0.983764886856079</v>
       </c>
       <c r="H2012" t="s">
         <v>8</v>
@@ -52733,7 +52733,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G2014" t="n">
-        <v>0.98376476764679</v>
+        <v>0.983764886856079</v>
       </c>
       <c r="H2014" t="s">
         <v>8</v>
@@ -52811,7 +52811,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G2017" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H2017" t="s">
         <v>8</v>
@@ -52915,7 +52915,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G2021" t="n">
-        <v>1.11501514911652</v>
+        <v>1.11501526832581</v>
       </c>
       <c r="H2021" t="s">
         <v>8</v>
@@ -53045,7 +53045,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G2026" t="n">
-        <v>1.15181457996368</v>
+        <v>1.15181446075439</v>
       </c>
       <c r="H2026" t="s">
         <v>8</v>
@@ -53175,7 +53175,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2031" t="n">
-        <v>1.26957190036774</v>
+        <v>1.26957178115845</v>
       </c>
       <c r="H2031" t="s">
         <v>8</v>
@@ -53227,7 +53227,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2033" t="n">
-        <v>1.23277270793915</v>
+        <v>1.23277258872986</v>
       </c>
       <c r="H2033" t="s">
         <v>8</v>
@@ -53253,7 +53253,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2034" t="n">
-        <v>1.23890578746796</v>
+        <v>1.23890590667725</v>
       </c>
       <c r="H2034" t="s">
         <v>8</v>
@@ -53331,7 +53331,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G2037" t="n">
-        <v>1.22970616817474</v>
+        <v>1.22970604896545</v>
       </c>
       <c r="H2037" t="s">
         <v>8</v>
@@ -53357,7 +53357,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2038" t="n">
-        <v>1.20823979377747</v>
+        <v>1.20823991298676</v>
       </c>
       <c r="H2038" t="s">
         <v>8</v>
@@ -53409,7 +53409,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G2040" t="n">
-        <v>1.18493366241455</v>
+        <v>1.18493378162384</v>
       </c>
       <c r="H2040" t="s">
         <v>8</v>
@@ -53773,7 +53773,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G2054" t="n">
-        <v>1.13832128047943</v>
+        <v>1.13832139968872</v>
       </c>
       <c r="H2054" t="s">
         <v>8</v>
@@ -53825,7 +53825,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G2056" t="n">
-        <v>1.13832128047943</v>
+        <v>1.13832139968872</v>
       </c>
       <c r="H2056" t="s">
         <v>8</v>
@@ -53851,7 +53851,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G2057" t="n">
-        <v>1.14200127124786</v>
+        <v>1.14200139045715</v>
       </c>
       <c r="H2057" t="s">
         <v>8</v>
@@ -53877,7 +53877,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G2058" t="n">
-        <v>1.15181457996368</v>
+        <v>1.15181446075439</v>
       </c>
       <c r="H2058" t="s">
         <v>8</v>
@@ -53929,7 +53929,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G2060" t="n">
-        <v>1.10274887084961</v>
+        <v>1.1027489900589</v>
       </c>
       <c r="H2060" t="s">
         <v>8</v>
@@ -54033,7 +54033,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2064" t="n">
-        <v>1.12850844860077</v>
+        <v>1.12850832939148</v>
       </c>
       <c r="H2064" t="s">
         <v>8</v>
@@ -54345,7 +54345,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G2076" t="n">
-        <v>1.70502889156342</v>
+        <v>1.70502877235413</v>
       </c>
       <c r="H2076" t="s">
         <v>8</v>
@@ -54423,7 +54423,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2079" t="n">
-        <v>1.94422352313995</v>
+        <v>1.94422376155853</v>
       </c>
       <c r="H2079" t="s">
         <v>8</v>
@@ -54475,7 +54475,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G2081" t="n">
-        <v>1.87675833702087</v>
+        <v>1.87675857543945</v>
       </c>
       <c r="H2081" t="s">
         <v>8</v>
@@ -54527,7 +54527,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G2083" t="n">
-        <v>1.83075940608978</v>
+        <v>1.83075928688049</v>
       </c>
       <c r="H2083" t="s">
         <v>8</v>
@@ -54553,7 +54553,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G2084" t="n">
-        <v>1.7970267534256</v>
+        <v>1.79702687263489</v>
       </c>
       <c r="H2084" t="s">
         <v>8</v>
@@ -54657,7 +54657,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G2088" t="n">
-        <v>1.83689260482788</v>
+        <v>1.83689248561859</v>
       </c>
       <c r="H2088" t="s">
         <v>8</v>
@@ -55151,7 +55151,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2107" t="n">
-        <v>2.00555539131165</v>
+        <v>2.00555562973022</v>
       </c>
       <c r="H2107" t="s">
         <v>8</v>
@@ -55177,7 +55177,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G2108" t="n">
-        <v>1.95342338085175</v>
+        <v>1.95342314243317</v>
       </c>
       <c r="H2108" t="s">
         <v>8</v>
@@ -55203,7 +55203,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G2109" t="n">
-        <v>1.95342338085175</v>
+        <v>1.95342314243317</v>
       </c>
       <c r="H2109" t="s">
         <v>8</v>
@@ -55255,7 +55255,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2111" t="n">
-        <v>1.92582404613495</v>
+        <v>1.92582392692566</v>
       </c>
       <c r="H2111" t="s">
         <v>8</v>
@@ -55307,7 +55307,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2113" t="n">
-        <v>1.88902461528778</v>
+        <v>1.88902485370636</v>
       </c>
       <c r="H2113" t="s">
         <v>8</v>
@@ -55333,7 +55333,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2114" t="n">
-        <v>1.88902461528778</v>
+        <v>1.88902485370636</v>
       </c>
       <c r="H2114" t="s">
         <v>8</v>
@@ -55385,7 +55385,7 @@
         <v>3</v>
       </c>
       <c r="G2116" t="n">
-        <v>1.83995914459229</v>
+        <v>1.839959025383</v>
       </c>
       <c r="H2116" t="s">
         <v>8</v>
@@ -55463,7 +55463,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G2119" t="n">
-        <v>1.80622661113739</v>
+        <v>1.8062264919281</v>
       </c>
       <c r="H2119" t="s">
         <v>8</v>
@@ -55489,7 +55489,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G2120" t="n">
-        <v>1.7694274187088</v>
+        <v>1.76942729949951</v>
       </c>
       <c r="H2120" t="s">
         <v>8</v>
@@ -55515,7 +55515,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G2121" t="n">
-        <v>1.7602276802063</v>
+        <v>1.76022756099701</v>
       </c>
       <c r="H2121" t="s">
         <v>8</v>
@@ -71274,6 +71274,32 @@
         <v>2.08500003814697</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>165363</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>2.08500003814697</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>2.02999997138977</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SGF.MI.xlsx
+++ b/data/SGF.MI.xlsx
@@ -447,7 +447,7 @@
         <v>2.00399994850159</v>
       </c>
       <c r="G3" t="n">
-        <v>1.22909259796143</v>
+        <v>1.22909271717072</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>1.93299996852875</v>
       </c>
       <c r="G5" t="n">
-        <v>1.18554699420929</v>
+        <v>1.18554711341858</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>1.91299998760223</v>
       </c>
       <c r="G6" t="n">
-        <v>1.17328071594238</v>
+        <v>1.17328059673309</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G8" t="n">
-        <v>1.17389404773712</v>
+        <v>1.17389392852783</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>1.00891101360321</v>
+        <v>1.00891089439392</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>1.77400004863739</v>
       </c>
       <c r="G18" t="n">
-        <v>1.08802914619446</v>
+        <v>1.08802926540375</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G24" t="n">
-        <v>1.01075100898743</v>
+        <v>1.01075088977814</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G27" t="n">
-        <v>0.841474711894989</v>
+        <v>0.841474652290344</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>1.42400002479553</v>
       </c>
       <c r="G29" t="n">
-        <v>0.873367309570312</v>
+        <v>0.873367249965668</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G30" t="n">
-        <v>0.858647584915161</v>
+        <v>0.858647644519806</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G32" t="n">
-        <v>0.981311559677124</v>
+        <v>0.981311500072479</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G33" t="n">
-        <v>0.950645625591278</v>
+        <v>0.950645565986633</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>1.56099998950958</v>
       </c>
       <c r="G34" t="n">
-        <v>0.95739209651947</v>
+        <v>0.957392036914825</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G35" t="n">
-        <v>0.941445767879486</v>
+        <v>0.941445708274841</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G38" t="n">
-        <v>0.941445767879486</v>
+        <v>0.941445708274841</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G39" t="n">
-        <v>0.924886226654053</v>
+        <v>0.924886167049408</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G40" t="n">
-        <v>0.910166501998901</v>
+        <v>0.910166442394257</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>1.52699995040894</v>
       </c>
       <c r="G41" t="n">
-        <v>0.93653929233551</v>
+        <v>0.936539232730865</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G42" t="n">
-        <v>0.872140645980835</v>
+        <v>0.87214070558548</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>1.5</v>
       </c>
       <c r="G43" t="n">
-        <v>0.919979512691498</v>
+        <v>0.919979572296143</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G48" t="n">
-        <v>1.00400447845459</v>
+        <v>1.0040043592453</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G49" t="n">
-        <v>1.00891101360321</v>
+        <v>1.00891089439392</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G53" t="n">
-        <v>0.960458636283875</v>
+        <v>0.960458695888519</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>1.58299994468689</v>
       </c>
       <c r="G54" t="n">
-        <v>0.970885097980499</v>
+        <v>0.970885157585144</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G55" t="n">
-        <v>0.956165432929993</v>
+        <v>0.956165492534637</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G57" t="n">
-        <v>0.92611289024353</v>
+        <v>0.926112711429596</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>1.5</v>
       </c>
       <c r="G58" t="n">
-        <v>0.919979512691498</v>
+        <v>0.919979572296143</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G60" t="n">
-        <v>0.853741049766541</v>
+        <v>0.853741109371185</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>1.40600001811981</v>
       </c>
       <c r="G62" t="n">
-        <v>0.862327575683594</v>
+        <v>0.862327516078949</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G66" t="n">
-        <v>0.815715253353119</v>
+        <v>0.815715193748474</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G68" t="n">
-        <v>0.794249057769775</v>
+        <v>0.79424911737442</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G69" t="n">
-        <v>0.832888245582581</v>
+        <v>0.832888185977936</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>1.43299996852875</v>
       </c>
       <c r="G73" t="n">
-        <v>0.878887236118317</v>
+        <v>0.878887176513672</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G75" t="n">
-        <v>0.89544677734375</v>
+        <v>0.895446836948395</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G78" t="n">
-        <v>0.875207364559174</v>
+        <v>0.875207304954529</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>1.42299997806549</v>
       </c>
       <c r="G79" t="n">
-        <v>0.872753977775574</v>
+        <v>0.872754037380219</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G80" t="n">
-        <v>0.872140645980835</v>
+        <v>0.87214070558548</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G81" t="n">
-        <v>0.868460774421692</v>
+        <v>0.868460714817047</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>1.5</v>
       </c>
       <c r="G82" t="n">
-        <v>0.919979512691498</v>
+        <v>0.919979572296143</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G83" t="n">
-        <v>0.943285763263702</v>
+        <v>0.943285644054413</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G84" t="n">
-        <v>0.977631688117981</v>
+        <v>0.977631628513336</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G85" t="n">
-        <v>0.993577897548676</v>
+        <v>0.99357795715332</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G86" t="n">
-        <v>0.951258957386017</v>
+        <v>0.951258897781372</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G87" t="n">
-        <v>0.951258957386017</v>
+        <v>0.951258897781372</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G88" t="n">
-        <v>0.951258957386017</v>
+        <v>0.951258897781372</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G89" t="n">
-        <v>0.951258957386017</v>
+        <v>0.951258897781372</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G91" t="n">
-        <v>0.938379287719727</v>
+        <v>0.938379168510437</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G93" t="n">
-        <v>0.97824501991272</v>
+        <v>0.978245079517365</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G94" t="n">
-        <v>0.992351353168488</v>
+        <v>0.992351412773132</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>1.6710000038147</v>
       </c>
       <c r="G96" t="n">
-        <v>1.02485728263855</v>
+        <v>1.02485716342926</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G98" t="n">
-        <v>0.943285763263702</v>
+        <v>0.943285644054413</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G99" t="n">
-        <v>0.935312628746033</v>
+        <v>0.935312569141388</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G102" t="n">
-        <v>1.02424383163452</v>
+        <v>1.0242440700531</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G103" t="n">
-        <v>1.0917090177536</v>
+        <v>1.09170913696289</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G108" t="n">
-        <v>1.03037703037262</v>
+        <v>1.03037714958191</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G110" t="n">
-        <v>0.999711155891418</v>
+        <v>0.999711215496063</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>1.625</v>
       </c>
       <c r="G112" t="n">
-        <v>0.996644556522369</v>
+        <v>0.996644616127014</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>1.60099995136261</v>
       </c>
       <c r="G113" t="n">
-        <v>0.981924891471863</v>
+        <v>0.981924831867218</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G114" t="n">
-        <v>0.935312628746033</v>
+        <v>0.935312569141388</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>1.39300000667572</v>
       </c>
       <c r="G115" t="n">
-        <v>0.854354381561279</v>
+        <v>0.854354321956635</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G116" t="n">
-        <v>0.806515514850616</v>
+        <v>0.806515455245972</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G119" t="n">
-        <v>0.792409121990204</v>
+        <v>0.792409062385559</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G122" t="n">
-        <v>0.875207364559174</v>
+        <v>0.875207304954529</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G124" t="n">
-        <v>0.81264865398407</v>
+        <v>0.812648713588715</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>1.25699996948242</v>
       </c>
       <c r="G127" t="n">
-        <v>0.77094292640686</v>
+        <v>0.770942866802216</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G128" t="n">
-        <v>0.806515514850616</v>
+        <v>0.806515455245972</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>1.30900001525879</v>
       </c>
       <c r="G129" t="n">
-        <v>0.802835524082184</v>
+        <v>0.802835583686829</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G131" t="n">
-        <v>0.725557267665863</v>
+        <v>0.725557208061218</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G133" t="n">
-        <v>0.713904201984406</v>
+        <v>0.713904142379761</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G135" t="n">
-        <v>0.771556258201599</v>
+        <v>0.771556198596954</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>1.30299997329712</v>
       </c>
       <c r="G136" t="n">
-        <v>0.799155592918396</v>
+        <v>0.799155533313751</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G137" t="n">
-        <v>0.803448796272278</v>
+        <v>0.803448855876923</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G140" t="n">
-        <v>0.858647584915161</v>
+        <v>0.858647644519806</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G141" t="n">
-        <v>0.85128778219223</v>
+        <v>0.851287841796875</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G142" t="n">
-        <v>0.861100912094116</v>
+        <v>0.861100971698761</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>1.40600001811981</v>
       </c>
       <c r="G143" t="n">
-        <v>0.862327575683594</v>
+        <v>0.862327516078949</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>1.38199996948242</v>
       </c>
       <c r="G144" t="n">
-        <v>0.847607851028442</v>
+        <v>0.847607791423798</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G146" t="n">
-        <v>0.884407043457031</v>
+        <v>0.884407103061676</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G148" t="n">
-        <v>0.935312628746033</v>
+        <v>0.935312569141388</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G150" t="n">
-        <v>0.935925960540771</v>
+        <v>0.935925900936127</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G151" t="n">
-        <v>0.907713174819946</v>
+        <v>0.907713234424591</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.54900002479553</v>
       </c>
       <c r="G152" t="n">
-        <v>0.950032293796539</v>
+        <v>0.950032234191895</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G153" t="n">
-        <v>0.956778764724731</v>
+        <v>0.956778824329376</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>1.62899994850159</v>
       </c>
       <c r="G155" t="n">
-        <v>0.99909782409668</v>
+        <v>0.999097764492035</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G158" t="n">
-        <v>1.02424383163452</v>
+        <v>1.0242440700531</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G160" t="n">
-        <v>1.0334438085556</v>
+        <v>1.03344368934631</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G163" t="n">
-        <v>1.00461781024933</v>
+        <v>1.00461769104004</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G165" t="n">
-        <v>1.0365104675293</v>
+        <v>1.03651034832001</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G166" t="n">
-        <v>1.03896367549896</v>
+        <v>1.03896355628967</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G168" t="n">
-        <v>1.03405714035034</v>
+        <v>1.03405702114105</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G172" t="n">
-        <v>1.02363061904907</v>
+        <v>1.02363073825836</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>1.66700005531311</v>
       </c>
       <c r="G173" t="n">
-        <v>1.02240395545959</v>
+        <v>1.02240407466888</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>1.75800001621246</v>
       </c>
       <c r="G174" t="n">
-        <v>1.07821619510651</v>
+        <v>1.07821607589722</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G176" t="n">
-        <v>1.0917090177536</v>
+        <v>1.09170913696289</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>1.77699995040894</v>
       </c>
       <c r="G177" t="n">
-        <v>1.08986902236938</v>
+        <v>1.08986914157867</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G179" t="n">
-        <v>1.08250939846039</v>
+        <v>1.0825092792511</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>1.73699998855591</v>
       </c>
       <c r="G180" t="n">
-        <v>1.06533622741699</v>
+        <v>1.06533634662628</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G181" t="n">
-        <v>1.06472289562225</v>
+        <v>1.06472301483154</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G186" t="n">
-        <v>1.06717622280121</v>
+        <v>1.0671763420105</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>1.77400004863739</v>
       </c>
       <c r="G187" t="n">
-        <v>1.08802914619446</v>
+        <v>1.08802926540375</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G189" t="n">
-        <v>1.0917090177536</v>
+        <v>1.09170913696289</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>1.78299999237061</v>
       </c>
       <c r="G190" t="n">
-        <v>1.09354901313782</v>
+        <v>1.09354913234711</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G191" t="n">
-        <v>1.11010873317719</v>
+        <v>1.1101086139679</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G194" t="n">
-        <v>1.0917090177536</v>
+        <v>1.09170913696289</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G198" t="n">
-        <v>1.0978422164917</v>
+        <v>1.09784233570099</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>1.0978422164917</v>
+        <v>1.09784233570099</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.76699995994568</v>
       </c>
       <c r="G202" t="n">
-        <v>1.08373594284058</v>
+        <v>1.08373606204987</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G204" t="n">
-        <v>1.10090887546539</v>
+        <v>1.10090899467468</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G207" t="n">
-        <v>1.1027489900589</v>
+        <v>1.10274887084961</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G210" t="n">
-        <v>1.18370699882507</v>
+        <v>1.18370711803436</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G217" t="n">
-        <v>1.28551816940308</v>
+        <v>1.28551805019379</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G218" t="n">
-        <v>1.26466524600983</v>
+        <v>1.26466536521912</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.07800006866455</v>
       </c>
       <c r="G221" t="n">
-        <v>1.27447843551636</v>
+        <v>1.27447855472565</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.07399988174438</v>
       </c>
       <c r="G223" t="n">
-        <v>1.2720251083374</v>
+        <v>1.27202498912811</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G224" t="n">
-        <v>1.3075977563858</v>
+        <v>1.30759763717651</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G225" t="n">
-        <v>1.31495761871338</v>
+        <v>1.31495749950409</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G229" t="n">
-        <v>1.33090388774872</v>
+        <v>1.33090376853943</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G230" t="n">
-        <v>1.32354390621185</v>
+        <v>1.32354402542114</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G232" t="n">
-        <v>1.30023765563965</v>
+        <v>1.30023777484894</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G233" t="n">
-        <v>1.29901111125946</v>
+        <v>1.29901123046875</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G236" t="n">
-        <v>1.28797137737274</v>
+        <v>1.28797125816345</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G237" t="n">
-        <v>1.28797137737274</v>
+        <v>1.28797125816345</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.09200000762939</v>
       </c>
       <c r="G238" t="n">
-        <v>1.28306484222412</v>
+        <v>1.28306496143341</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G240" t="n">
-        <v>1.30023765563965</v>
+        <v>1.30023777484894</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G243" t="n">
-        <v>1.4351681470871</v>
+        <v>1.43516826629639</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G249" t="n">
-        <v>1.47932720184326</v>
+        <v>1.47932708263397</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G252" t="n">
-        <v>1.49650013446808</v>
+        <v>1.49650025367737</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G256" t="n">
-        <v>1.47810065746307</v>
+        <v>1.47810053825378</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G260" t="n">
-        <v>1.58113837242126</v>
+        <v>1.58113825321198</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G261" t="n">
-        <v>1.57009851932526</v>
+        <v>1.57009840011597</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G264" t="n">
-        <v>1.5737783908844</v>
+        <v>1.57377851009369</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G266" t="n">
-        <v>1.55169904232025</v>
+        <v>1.55169880390167</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G267" t="n">
-        <v>1.57009851932526</v>
+        <v>1.57009840011597</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G268" t="n">
-        <v>1.57868492603302</v>
+        <v>1.57868504524231</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.5</v>
       </c>
       <c r="G270" t="n">
-        <v>1.53329932689667</v>
+        <v>1.53329944610596</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G273" t="n">
-        <v>1.4952734708786</v>
+        <v>1.49527359008789</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.48600006103516</v>
       </c>
       <c r="G275" t="n">
-        <v>1.5247129201889</v>
+        <v>1.52471303939819</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G279" t="n">
-        <v>1.34930348396301</v>
+        <v>1.34930336475372</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G280" t="n">
-        <v>1.4167685508728</v>
+        <v>1.41676843166351</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G281" t="n">
-        <v>1.41308867931366</v>
+        <v>1.41308856010437</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G284" t="n">
-        <v>1.27079856395721</v>
+        <v>1.27079844474792</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.33599996566772</v>
       </c>
       <c r="G288" t="n">
-        <v>1.43271493911743</v>
+        <v>1.43271481990814</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G292" t="n">
-        <v>1.38732933998108</v>
+        <v>1.38732922077179</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G293" t="n">
-        <v>1.39959561824799</v>
+        <v>1.39959573745728</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G296" t="n">
-        <v>1.41063547134399</v>
+        <v>1.4106353521347</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G297" t="n">
-        <v>1.39591562747955</v>
+        <v>1.39591574668884</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G298" t="n">
-        <v>1.46338081359863</v>
+        <v>1.46338093280792</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.67199993133545</v>
       </c>
       <c r="G299" t="n">
-        <v>1.63879024982452</v>
+        <v>1.63879036903381</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G300" t="n">
-        <v>1.65718984603882</v>
+        <v>1.65718972682953</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G302" t="n">
-        <v>1.66945624351501</v>
+        <v>1.6694563627243</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G305" t="n">
-        <v>1.79825329780579</v>
+        <v>1.79825341701508</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G307" t="n">
-        <v>1.7908935546875</v>
+        <v>1.79089367389679</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G308" t="n">
-        <v>1.77740049362183</v>
+        <v>1.77740061283112</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>1.7786271572113</v>
+        <v>1.77862739562988</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G310" t="n">
-        <v>1.7908935546875</v>
+        <v>1.79089367389679</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G311" t="n">
-        <v>1.8031599521637</v>
+        <v>1.80316007137299</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G312" t="n">
-        <v>1.82523965835571</v>
+        <v>1.82523953914642</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G313" t="n">
-        <v>1.95526337623596</v>
+        <v>1.95526325702667</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G314" t="n">
-        <v>1.93563711643219</v>
+        <v>1.9356369972229</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G315" t="n">
-        <v>2.01046228408813</v>
+        <v>2.01046204566956</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G317" t="n">
-        <v>2.15275239944458</v>
+        <v>2.152752161026</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.60199999809265</v>
       </c>
       <c r="G318" t="n">
-        <v>2.20917797088623</v>
+        <v>2.20917773246765</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>3.75</v>
       </c>
       <c r="G319" t="n">
-        <v>2.29994916915894</v>
+        <v>2.29994893074036</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G320" t="n">
-        <v>2.29749584197998</v>
+        <v>2.2974956035614</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G321" t="n">
-        <v>2.26928281784058</v>
+        <v>2.26928305625916</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G322" t="n">
-        <v>2.2680561542511</v>
+        <v>2.26805639266968</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G329" t="n">
-        <v>2.27786946296692</v>
+        <v>2.2778697013855</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G331" t="n">
-        <v>2.2680561542511</v>
+        <v>2.26805639266968</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G332" t="n">
-        <v>2.20181775093079</v>
+        <v>2.20181798934937</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G339" t="n">
-        <v>2.72681975364685</v>
+        <v>2.72681951522827</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>2.73540592193604</v>
+        <v>2.73540639877319</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G343" t="n">
-        <v>2.76607227325439</v>
+        <v>2.76607203483582</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G344" t="n">
-        <v>2.72927284240723</v>
+        <v>2.72927260398865</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G346" t="n">
-        <v>2.90590882301331</v>
+        <v>2.90590906143188</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G348" t="n">
-        <v>2.88996267318726</v>
+        <v>2.8899621963501</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>4.60799980163574</v>
       </c>
       <c r="G349" t="n">
-        <v>2.82617735862732</v>
+        <v>2.82617712020874</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>4.72399997711182</v>
       </c>
       <c r="G351" t="n">
-        <v>2.89732241630554</v>
+        <v>2.89732265472412</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G354" t="n">
-        <v>2.99300026893616</v>
+        <v>2.99300050735474</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G358" t="n">
-        <v>3.21379518508911</v>
+        <v>3.21379542350769</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G360" t="n">
-        <v>3.1739296913147</v>
+        <v>3.17392992973328</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G361" t="n">
-        <v>3.18619585037231</v>
+        <v>3.18619608879089</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>5.125</v>
       </c>
       <c r="G363" t="n">
-        <v>3.14326357841492</v>
+        <v>3.1432638168335</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G364" t="n">
-        <v>3.28432726860046</v>
+        <v>3.28432703018188</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G365" t="n">
-        <v>3.1892626285553</v>
+        <v>3.18926239013672</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G368" t="n">
-        <v>3.14019703865051</v>
+        <v>3.14019680023193</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G370" t="n">
-        <v>2.99300026893616</v>
+        <v>2.99300050735474</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G371" t="n">
-        <v>3.21072888374329</v>
+        <v>3.21072912216187</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G373" t="n">
-        <v>3.03470611572266</v>
+        <v>3.03470587730408</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>3.1739296913147</v>
+        <v>3.17392992973328</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>4.93400001525879</v>
       </c>
       <c r="G381" t="n">
-        <v>3.02611970901489</v>
+        <v>3.02611947059631</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G383" t="n">
-        <v>2.92553496360779</v>
+        <v>2.92553520202637</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>4.68400001525879</v>
       </c>
       <c r="G384" t="n">
-        <v>2.87278962135315</v>
+        <v>2.87278938293457</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.50600004196167</v>
       </c>
       <c r="G390" t="n">
-        <v>2.76361894607544</v>
+        <v>2.76361870765686</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>4.72399997711182</v>
       </c>
       <c r="G391" t="n">
-        <v>2.89732241630554</v>
+        <v>2.89732265472412</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.69199991226196</v>
       </c>
       <c r="G394" t="n">
-        <v>2.87769603729248</v>
+        <v>2.87769627571106</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G395" t="n">
-        <v>2.91081547737122</v>
+        <v>2.91081523895264</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G399" t="n">
-        <v>2.67898082733154</v>
+        <v>2.67898035049438</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G400" t="n">
-        <v>2.69860696792603</v>
+        <v>2.69860672950745</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G401" t="n">
-        <v>2.6274619102478</v>
+        <v>2.62746167182922</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G405" t="n">
-        <v>2.62500882148743</v>
+        <v>2.62500858306885</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>4.14200019836426</v>
       </c>
       <c r="G407" t="n">
-        <v>2.54037046432495</v>
+        <v>2.54037070274353</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G409" t="n">
-        <v>2.57594275474548</v>
+        <v>2.5759425163269</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G410" t="n">
-        <v>2.57594275474548</v>
+        <v>2.5759425163269</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.27400016784668</v>
       </c>
       <c r="G412" t="n">
-        <v>2.62132883071899</v>
+        <v>2.62132859230042</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>4.64799976348877</v>
       </c>
       <c r="G413" t="n">
-        <v>2.85070991516113</v>
+        <v>2.85071015357971</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>4.55800008773804</v>
       </c>
       <c r="G415" t="n">
-        <v>2.79551124572754</v>
+        <v>2.79551148414612</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G416" t="n">
-        <v>2.82127094268799</v>
+        <v>2.82127070426941</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>4.60400009155273</v>
       </c>
       <c r="G417" t="n">
-        <v>2.82372426986694</v>
+        <v>2.82372403144836</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G419" t="n">
-        <v>2.77588534355164</v>
+        <v>2.77588510513306</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G420" t="n">
-        <v>2.73540592193604</v>
+        <v>2.73540639877319</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G424" t="n">
-        <v>2.66794061660767</v>
+        <v>2.66794109344482</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>4.24599981307983</v>
       </c>
       <c r="G425" t="n">
-        <v>2.60415530204773</v>
+        <v>2.60415554046631</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G427" t="n">
-        <v>2.67898082733154</v>
+        <v>2.67898035049438</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G428" t="n">
-        <v>2.62991523742676</v>
+        <v>2.62991499900818</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>4.28200006484985</v>
       </c>
       <c r="G429" t="n">
-        <v>2.62623524665833</v>
+        <v>2.62623500823975</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G434" t="n">
-        <v>3.05065250396729</v>
+        <v>3.05065226554871</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>5</v>
       </c>
       <c r="G437" t="n">
-        <v>3.06659865379333</v>
+        <v>3.06659889221191</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G439" t="n">
-        <v>3.17086315155029</v>
+        <v>3.17086291313171</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>5</v>
       </c>
       <c r="G441" t="n">
-        <v>3.06659865379333</v>
+        <v>3.06659889221191</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G442" t="n">
-        <v>3.10033106803894</v>
+        <v>3.10033130645752</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>5.03499984741211</v>
       </c>
       <c r="G443" t="n">
-        <v>3.08806467056274</v>
+        <v>3.08806490898132</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>5</v>
       </c>
       <c r="G444" t="n">
-        <v>3.06659865379333</v>
+        <v>3.06659889221191</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>5.06500005722046</v>
       </c>
       <c r="G445" t="n">
-        <v>3.10646438598633</v>
+        <v>3.10646462440491</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G446" t="n">
-        <v>3.1769962310791</v>
+        <v>3.17699646949768</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G457" t="n">
-        <v>2.99300026893616</v>
+        <v>2.99300050735474</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G461" t="n">
-        <v>2.9721474647522</v>
+        <v>2.97214770317078</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G463" t="n">
-        <v>2.88260269165039</v>
+        <v>2.88260245323181</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G464" t="n">
-        <v>2.90100240707397</v>
+        <v>2.9010021686554</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G465" t="n">
-        <v>2.90590882301331</v>
+        <v>2.90590906143188</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G467" t="n">
-        <v>2.65567421913147</v>
+        <v>2.65567445755005</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G470" t="n">
-        <v>2.57594275474548</v>
+        <v>2.5759425163269</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>4.26399993896484</v>
       </c>
       <c r="G473" t="n">
-        <v>2.61519551277161</v>
+        <v>2.61519527435303</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G481" t="n">
-        <v>2.2680561542511</v>
+        <v>2.26805639266968</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G482" t="n">
-        <v>2.34165501594543</v>
+        <v>2.34165477752686</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G486" t="n">
-        <v>2.5857560634613</v>
+        <v>2.58575582504272</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G489" t="n">
-        <v>2.4238395690918</v>
+        <v>2.42383933067322</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G490" t="n">
-        <v>2.44346594810486</v>
+        <v>2.44346570968628</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G491" t="n">
-        <v>2.66794061660767</v>
+        <v>2.66794109344482</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G492" t="n">
-        <v>2.63482165336609</v>
+        <v>2.63482141494751</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.25600004196167</v>
       </c>
       <c r="G494" t="n">
-        <v>2.6102888584137</v>
+        <v>2.61028861999512</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G497" t="n">
-        <v>2.62500882148743</v>
+        <v>2.62500858306885</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G499" t="n">
-        <v>2.6004753112793</v>
+        <v>2.60047554969788</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G500" t="n">
-        <v>2.53669047355652</v>
+        <v>2.5366907119751</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G501" t="n">
-        <v>2.38581371307373</v>
+        <v>2.38581395149231</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G502" t="n">
-        <v>2.33061480522156</v>
+        <v>2.33061504364014</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>3.94799995422363</v>
       </c>
       <c r="G504" t="n">
-        <v>2.42138624191284</v>
+        <v>2.42138648033142</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G506" t="n">
-        <v>2.43242621421814</v>
+        <v>2.43242597579956</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G507" t="n">
-        <v>2.47903847694397</v>
+        <v>2.47903823852539</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G511" t="n">
-        <v>2.45941209793091</v>
+        <v>2.45941233634949</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>3.95799994468689</v>
       </c>
       <c r="G513" t="n">
-        <v>2.42751955986023</v>
+        <v>2.42751932144165</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G516" t="n">
-        <v>2.5146107673645</v>
+        <v>2.51461100578308</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>4.18599987030029</v>
       </c>
       <c r="G519" t="n">
-        <v>2.56735634803772</v>
+        <v>2.56735610961914</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G521" t="n">
-        <v>2.62991523742676</v>
+        <v>2.62991499900818</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G522" t="n">
-        <v>2.6274619102478</v>
+        <v>2.62746167182922</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>4.21799993515015</v>
       </c>
       <c r="G523" t="n">
-        <v>2.58698272705078</v>
+        <v>2.5869824886322</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G527" t="n">
-        <v>2.65567421913147</v>
+        <v>2.65567445755005</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G531" t="n">
-        <v>2.6004753112793</v>
+        <v>2.60047554969788</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G532" t="n">
-        <v>2.454505443573</v>
+        <v>2.45450568199158</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G533" t="n">
-        <v>2.46799850463867</v>
+        <v>2.46799874305725</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G537" t="n">
-        <v>2.35269474983215</v>
+        <v>2.35269451141357</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G540" t="n">
-        <v>2.20181775093079</v>
+        <v>2.20181798934937</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>3.60599994659424</v>
       </c>
       <c r="G541" t="n">
-        <v>2.21163105964661</v>
+        <v>2.21163082122803</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G542" t="n">
-        <v>2.1834180355072</v>
+        <v>2.18341827392578</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G549" t="n">
-        <v>2.33061480522156</v>
+        <v>2.33061504364014</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G550" t="n">
-        <v>2.24965667724609</v>
+        <v>2.24965691566467</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G553" t="n">
-        <v>2.03008842468262</v>
+        <v>2.03008818626404</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>3.18600010871887</v>
       </c>
       <c r="G554" t="n">
-        <v>1.95403671264648</v>
+        <v>1.95403659343719</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G555" t="n">
-        <v>1.90129125118256</v>
+        <v>1.90129113197327</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G556" t="n">
-        <v>1.84609234333038</v>
+        <v>1.84609246253967</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G557" t="n">
-        <v>1.87921166419983</v>
+        <v>1.87921154499054</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>3.11800003051758</v>
       </c>
       <c r="G560" t="n">
-        <v>1.91233086585999</v>
+        <v>1.91233098506927</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G561" t="n">
-        <v>1.84609234333038</v>
+        <v>1.84609246253967</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>3.02600002288818</v>
       </c>
       <c r="G562" t="n">
-        <v>1.85590553283691</v>
+        <v>1.8559056520462</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G563" t="n">
-        <v>1.87798523902893</v>
+        <v>1.87798511981964</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G564" t="n">
-        <v>1.87921166419983</v>
+        <v>1.87921154499054</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G567" t="n">
-        <v>1.90129125118256</v>
+        <v>1.90129113197327</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G568" t="n">
-        <v>1.98715579509735</v>
+        <v>1.98715591430664</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>3.08200001716614</v>
       </c>
       <c r="G571" t="n">
-        <v>1.89025151729584</v>
+        <v>1.89025139808655</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G572" t="n">
-        <v>1.8865715265274</v>
+        <v>1.88657128810883</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G573" t="n">
-        <v>1.81542634963989</v>
+        <v>1.81542646884918</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G577" t="n">
-        <v>1.92091727256775</v>
+        <v>1.92091739177704</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G578" t="n">
-        <v>1.95649003982544</v>
+        <v>1.95649015903473</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>3.11800003051758</v>
       </c>
       <c r="G581" t="n">
-        <v>1.91233086585999</v>
+        <v>1.91233098506927</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>3.32399988174438</v>
       </c>
       <c r="G584" t="n">
-        <v>2.0386745929718</v>
+        <v>2.03867483139038</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>3.37199997901917</v>
       </c>
       <c r="G585" t="n">
-        <v>2.06811428070068</v>
+        <v>2.0681140422821</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G588" t="n">
-        <v>1.96262311935425</v>
+        <v>1.96262300014496</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G589" t="n">
-        <v>2.03008842468262</v>
+        <v>2.03008818626404</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G591" t="n">
-        <v>1.97120976448059</v>
+        <v>1.9712096452713</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G593" t="n">
-        <v>1.97734272480011</v>
+        <v>1.9773428440094</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>3.25399994850159</v>
       </c>
       <c r="G594" t="n">
-        <v>1.99574244022369</v>
+        <v>1.99574255943298</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G599" t="n">
-        <v>1.99942231178284</v>
+        <v>1.99942243099213</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G600" t="n">
-        <v>2.02640843391418</v>
+        <v>2.02640819549561</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G601" t="n">
-        <v>1.97120976448059</v>
+        <v>1.9712096452713</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>3.15199995040894</v>
       </c>
       <c r="G603" t="n">
-        <v>1.93318378925323</v>
+        <v>1.93318390846252</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G604" t="n">
-        <v>1.93441045284271</v>
+        <v>1.93441033363342</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>3.08200001716614</v>
       </c>
       <c r="G605" t="n">
-        <v>1.89025151729584</v>
+        <v>1.89025139808655</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G608" t="n">
-        <v>1.88411819934845</v>
+        <v>1.88411831855774</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>3.13599991798401</v>
       </c>
       <c r="G609" t="n">
-        <v>1.9233705997467</v>
+        <v>1.92337071895599</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G612" t="n">
-        <v>1.87921166419983</v>
+        <v>1.87921154499054</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G614" t="n">
-        <v>1.77985394001007</v>
+        <v>1.77985382080078</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G616" t="n">
-        <v>1.76636075973511</v>
+        <v>1.7663608789444</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>3.05599999427795</v>
       </c>
       <c r="G617" t="n">
-        <v>1.8743052482605</v>
+        <v>1.87430500984192</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G618" t="n">
-        <v>1.86939883232117</v>
+        <v>1.86939871311188</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G619" t="n">
-        <v>1.87307858467102</v>
+        <v>1.87307846546173</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G620" t="n">
-        <v>1.93441045284271</v>
+        <v>1.93441033363342</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>3.08400011062622</v>
       </c>
       <c r="G621" t="n">
-        <v>1.89147818088531</v>
+        <v>1.89147806167603</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G623" t="n">
-        <v>1.84609234333038</v>
+        <v>1.84609246253967</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G624" t="n">
-        <v>1.87062525749207</v>
+        <v>1.87062513828278</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G625" t="n">
-        <v>1.84609234333038</v>
+        <v>1.84609246253967</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>3.01200008392334</v>
       </c>
       <c r="G627" t="n">
-        <v>1.84731900691986</v>
+        <v>1.84731912612915</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G628" t="n">
-        <v>1.8031599521637</v>
+        <v>1.80316007137299</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>2.86400008201599</v>
       </c>
       <c r="G632" t="n">
-        <v>1.75654780864716</v>
+        <v>1.75654768943787</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G635" t="n">
-        <v>1.63020384311676</v>
+        <v>1.63020396232605</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G636" t="n">
-        <v>1.57009851932526</v>
+        <v>1.57009840011597</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G639" t="n">
-        <v>1.55169904232025</v>
+        <v>1.55169880390167</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G642" t="n">
-        <v>1.63143050670624</v>
+        <v>1.63143038749695</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.75799989700317</v>
       </c>
       <c r="G643" t="n">
-        <v>1.69153583049774</v>
+        <v>1.69153571128845</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.66400003433228</v>
       </c>
       <c r="G645" t="n">
-        <v>1.6338837146759</v>
+        <v>1.63388383388519</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G646" t="n">
-        <v>1.60567104816437</v>
+        <v>1.60567116737366</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G647" t="n">
-        <v>1.59217798709869</v>
+        <v>1.59217810630798</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G648" t="n">
-        <v>1.5737783908844</v>
+        <v>1.57377851009369</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.78600001335144</v>
       </c>
       <c r="G651" t="n">
-        <v>1.70870876312256</v>
+        <v>1.70870864391327</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G653" t="n">
-        <v>1.63143050670624</v>
+        <v>1.63143038749695</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G658" t="n">
-        <v>1.29287803173065</v>
+        <v>1.29287791252136</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G660" t="n">
-        <v>1.29287803173065</v>
+        <v>1.29287791252136</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.1340000629425</v>
       </c>
       <c r="G664" t="n">
-        <v>1.30882441997528</v>
+        <v>1.30882430076599</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G666" t="n">
-        <v>1.25853204727173</v>
+        <v>1.25853216648102</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G667" t="n">
-        <v>1.23645257949829</v>
+        <v>1.23645269870758</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G668" t="n">
-        <v>1.20946657657623</v>
+        <v>1.20946645736694</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G669" t="n">
-        <v>1.20517325401306</v>
+        <v>1.20517337322235</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G673" t="n">
-        <v>1.28551816940308</v>
+        <v>1.28551805019379</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>1.98099994659424</v>
       </c>
       <c r="G674" t="n">
-        <v>1.2149863243103</v>
+        <v>1.21498644351959</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>2.00399994850159</v>
       </c>
       <c r="G676" t="n">
-        <v>1.22909259796143</v>
+        <v>1.22909271717072</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G677" t="n">
-        <v>1.23154592514038</v>
+        <v>1.23154604434967</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>2.04800009727478</v>
       </c>
       <c r="G682" t="n">
-        <v>1.25607883930206</v>
+        <v>1.25607895851135</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G683" t="n">
-        <v>1.22602617740631</v>
+        <v>1.22602605819702</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G684" t="n">
-        <v>1.23522579669952</v>
+        <v>1.23522591590881</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.00399994850159</v>
       </c>
       <c r="G685" t="n">
-        <v>1.22909259796143</v>
+        <v>1.22909271717072</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2</v>
       </c>
       <c r="G687" t="n">
-        <v>1.22663938999176</v>
+        <v>1.22663950920105</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>1.97899997234344</v>
       </c>
       <c r="G688" t="n">
-        <v>1.21375977993011</v>
+        <v>1.21375966072083</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>1.98300004005432</v>
       </c>
       <c r="G689" t="n">
-        <v>1.21621310710907</v>
+        <v>1.21621298789978</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G690" t="n">
-        <v>1.2119197845459</v>
+        <v>1.21191966533661</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2</v>
       </c>
       <c r="G691" t="n">
-        <v>1.22663938999176</v>
+        <v>1.22663950920105</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G695" t="n">
-        <v>1.29533135890961</v>
+        <v>1.29533123970032</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G696" t="n">
-        <v>1.31741082668304</v>
+        <v>1.31741070747375</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G697" t="n">
-        <v>1.30023765563965</v>
+        <v>1.30023777484894</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G703" t="n">
-        <v>1.17389404773712</v>
+        <v>1.17389392852783</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G708" t="n">
-        <v>1.0843493938446</v>
+        <v>1.08434915542603</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>1.7389999628067</v>
       </c>
       <c r="G709" t="n">
-        <v>1.06656289100647</v>
+        <v>1.06656301021576</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>1.68700003623962</v>
       </c>
       <c r="G710" t="n">
-        <v>1.03467047214508</v>
+        <v>1.03467035293579</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G711" t="n">
-        <v>1.05552327632904</v>
+        <v>1.05552315711975</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G714" t="n">
-        <v>1.02792382240295</v>
+        <v>1.02792394161224</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>1.625</v>
       </c>
       <c r="G715" t="n">
-        <v>0.996644556522369</v>
+        <v>0.996644616127014</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>1.5110000371933</v>
       </c>
       <c r="G720" t="n">
-        <v>0.926726222038269</v>
+        <v>0.926726102828979</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G722" t="n">
-        <v>0.951258957386017</v>
+        <v>0.951258897781372</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>1.57599997520447</v>
       </c>
       <c r="G723" t="n">
-        <v>0.966591894626617</v>
+        <v>0.966591954231262</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>1.59300005435944</v>
       </c>
       <c r="G725" t="n">
-        <v>0.977018356323242</v>
+        <v>0.977018296718597</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G727" t="n">
-        <v>0.958618640899658</v>
+        <v>0.958618760108948</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G729" t="n">
-        <v>0.992351353168488</v>
+        <v>0.992351412773132</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>1.57200002670288</v>
       </c>
       <c r="G730" t="n">
-        <v>0.964138567447662</v>
+        <v>0.964138686656952</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>1.53299999237061</v>
       </c>
       <c r="G731" t="n">
-        <v>0.940219163894653</v>
+        <v>0.940219223499298</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G732" t="n">
-        <v>0.907713174819946</v>
+        <v>0.907713234424591</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G735" t="n">
-        <v>0.924886226654053</v>
+        <v>0.924886167049408</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G736" t="n">
-        <v>0.89544677734375</v>
+        <v>0.895446836948395</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G738" t="n">
-        <v>0.867847383022308</v>
+        <v>0.867847442626953</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G740" t="n">
-        <v>0.875820577144623</v>
+        <v>0.875820517539978</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G741" t="n">
-        <v>0.884407043457031</v>
+        <v>0.884407103061676</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>1.53299999237061</v>
       </c>
       <c r="G742" t="n">
-        <v>0.940219163894653</v>
+        <v>0.940219223499298</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G743" t="n">
-        <v>0.956778764724731</v>
+        <v>0.956778824329376</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G745" t="n">
-        <v>0.941445767879486</v>
+        <v>0.941445708274841</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G746" t="n">
-        <v>0.938379287719727</v>
+        <v>0.938379168510437</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G747" t="n">
-        <v>0.967205226421356</v>
+        <v>0.967205166816711</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G748" t="n">
-        <v>0.956165432929993</v>
+        <v>0.956165492534637</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>1.557000041008</v>
       </c>
       <c r="G749" t="n">
-        <v>0.954938769340515</v>
+        <v>0.954938888549805</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G750" t="n">
-        <v>0.901579976081848</v>
+        <v>0.901580035686493</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>1.4539999961853</v>
       </c>
       <c r="G753" t="n">
-        <v>0.891766965389252</v>
+        <v>0.891766905784607</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>1.48699998855591</v>
       </c>
       <c r="G754" t="n">
-        <v>0.912006497383118</v>
+        <v>0.912006378173828</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G755" t="n">
-        <v>0.875207364559174</v>
+        <v>0.875207304954529</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>1.37899994850159</v>
       </c>
       <c r="G757" t="n">
-        <v>0.845767915248871</v>
+        <v>0.845767855644226</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G758" t="n">
-        <v>0.837181389331818</v>
+        <v>0.837181448936462</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G760" t="n">
-        <v>0.837181389331818</v>
+        <v>0.837181448936462</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G765" t="n">
-        <v>0.911393046379089</v>
+        <v>0.911393105983734</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G767" t="n">
-        <v>0.951258957386017</v>
+        <v>0.951258897781372</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G768" t="n">
-        <v>0.951872229576111</v>
+        <v>0.951872289180756</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>1.60699999332428</v>
       </c>
       <c r="G769" t="n">
-        <v>0.985604882240295</v>
+        <v>0.985604822635651</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>1.61300003528595</v>
       </c>
       <c r="G771" t="n">
-        <v>0.989284694194794</v>
+        <v>0.989284753799438</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G775" t="n">
-        <v>0.982538223266602</v>
+        <v>0.982538282871246</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G776" t="n">
-        <v>0.993577897548676</v>
+        <v>0.99357795715332</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G778" t="n">
-        <v>0.940832555294037</v>
+        <v>0.940832495689392</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>1.5</v>
       </c>
       <c r="G779" t="n">
-        <v>0.919979512691498</v>
+        <v>0.919979572296143</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G784" t="n">
-        <v>1.06472289562225</v>
+        <v>1.06472301483154</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G785" t="n">
-        <v>1.12237513065338</v>
+        <v>1.12237501144409</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G788" t="n">
-        <v>1.03221702575684</v>
+        <v>1.03221714496613</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>1.625</v>
       </c>
       <c r="G790" t="n">
-        <v>0.996644556522369</v>
+        <v>0.996644616127014</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G791" t="n">
-        <v>0.972111880779266</v>
+        <v>0.972111821174622</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>1.71300005912781</v>
       </c>
       <c r="G795" t="n">
-        <v>1.05061674118042</v>
+        <v>1.05061662197113</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G797" t="n">
-        <v>1.05552327632904</v>
+        <v>1.05552315711975</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G803" t="n">
-        <v>1.02792382240295</v>
+        <v>1.02792394161224</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>1.56700003147125</v>
       </c>
       <c r="G805" t="n">
-        <v>0.961071968078613</v>
+        <v>0.961072027683258</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G810" t="n">
-        <v>0.921206176280975</v>
+        <v>0.921206295490265</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>1.50600004196167</v>
       </c>
       <c r="G814" t="n">
-        <v>0.92365950345993</v>
+        <v>0.923659563064575</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G815" t="n">
-        <v>0.928566157817841</v>
+        <v>0.928566098213196</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G816" t="n">
-        <v>0.923046171665192</v>
+        <v>0.923046231269836</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G817" t="n">
-        <v>0.92611289024353</v>
+        <v>0.926112711429596</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>1.54100000858307</v>
       </c>
       <c r="G818" t="n">
-        <v>0.945125758647919</v>
+        <v>0.945125699043274</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G819" t="n">
-        <v>0.945739090442657</v>
+        <v>0.945739030838013</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.47300004959106</v>
       </c>
       <c r="G822" t="n">
-        <v>0.903419971466064</v>
+        <v>0.903420031070709</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G823" t="n">
-        <v>0.899126648902893</v>
+        <v>0.899126708507538</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>1.53699994087219</v>
       </c>
       <c r="G826" t="n">
-        <v>0.942672431468964</v>
+        <v>0.942672491073608</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>1.59300005435944</v>
       </c>
       <c r="G827" t="n">
-        <v>0.977018356323242</v>
+        <v>0.977018296718597</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G828" t="n">
-        <v>0.960458636283875</v>
+        <v>0.960458695888519</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>1.66299998760223</v>
       </c>
       <c r="G831" t="n">
-        <v>1.01995062828064</v>
+        <v>1.01995074748993</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G839" t="n">
-        <v>0.977631688117981</v>
+        <v>0.977631628513336</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G843" t="n">
-        <v>0.953098893165588</v>
+        <v>0.953098833560944</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>1.18700003623962</v>
       </c>
       <c r="G855" t="n">
-        <v>0.728010594844818</v>
+        <v>0.728010535240173</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G856" t="n">
-        <v>0.743343532085419</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>1.192999958992</v>
       </c>
       <c r="G857" t="n">
-        <v>0.731690406799316</v>
+        <v>0.731690466403961</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G861" t="n">
-        <v>0.705317735671997</v>
+        <v>0.705317676067352</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>1.13100004196167</v>
       </c>
       <c r="G863" t="n">
-        <v>0.69366466999054</v>
+        <v>0.693664610385895</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>1.17900002002716</v>
       </c>
       <c r="G864" t="n">
-        <v>0.723104000091553</v>
+        <v>0.723103940486908</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>1.17900002002716</v>
       </c>
       <c r="G867" t="n">
-        <v>0.723104000091553</v>
+        <v>0.723103940486908</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G870" t="n">
-        <v>0.722490668296814</v>
+        <v>0.722490549087524</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G872" t="n">
-        <v>0.705317735671997</v>
+        <v>0.705317676067352</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G873" t="n">
-        <v>0.709610879421234</v>
+        <v>0.709610939025879</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>1.1710000038147</v>
       </c>
       <c r="G876" t="n">
-        <v>0.718197405338287</v>
+        <v>0.718197345733643</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G878" t="n">
-        <v>0.720650672912598</v>
+        <v>0.720650613307953</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G880" t="n">
-        <v>0.722490668296814</v>
+        <v>0.722490549087524</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G882" t="n">
-        <v>0.753156661987305</v>
+        <v>0.753156721591949</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G883" t="n">
-        <v>0.74518346786499</v>
+        <v>0.745183527469635</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G884" t="n">
-        <v>0.74518346786499</v>
+        <v>0.745183527469635</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>1.21599996089935</v>
       </c>
       <c r="G885" t="n">
-        <v>0.745796740055084</v>
+        <v>0.745796799659729</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.24300003051758</v>
       </c>
       <c r="G887" t="n">
-        <v>0.762356460094452</v>
+        <v>0.762356519699097</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>1.24699997901917</v>
       </c>
       <c r="G888" t="n">
-        <v>0.764809727668762</v>
+        <v>0.764809668064117</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>1.25300002098083</v>
       </c>
       <c r="G891" t="n">
-        <v>0.768489599227905</v>
+        <v>0.76848965883255</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G892" t="n">
-        <v>0.775849521160126</v>
+        <v>0.775849401950836</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.25</v>
       </c>
       <c r="G894" t="n">
-        <v>0.766649663448334</v>
+        <v>0.766649723052979</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>1.25300002098083</v>
       </c>
       <c r="G896" t="n">
-        <v>0.768489599227905</v>
+        <v>0.76848965883255</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>1.24699997901917</v>
       </c>
       <c r="G898" t="n">
-        <v>0.764809727668762</v>
+        <v>0.764809668064117</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>1.21099996566772</v>
       </c>
       <c r="G900" t="n">
-        <v>0.742730140686035</v>
+        <v>0.74273020029068</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G901" t="n">
-        <v>0.753156661987305</v>
+        <v>0.753156721591949</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>1.21700000762939</v>
       </c>
       <c r="G902" t="n">
-        <v>0.746410131454468</v>
+        <v>0.746410071849823</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G903" t="n">
-        <v>0.753156661987305</v>
+        <v>0.753156721591949</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G906" t="n">
-        <v>0.806515514850616</v>
+        <v>0.806515455245972</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G907" t="n">
-        <v>0.813261926174164</v>
+        <v>0.813261985778809</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>1.25</v>
       </c>
       <c r="G910" t="n">
-        <v>0.766649663448334</v>
+        <v>0.766649723052979</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>1.21099996566772</v>
       </c>
       <c r="G911" t="n">
-        <v>0.742730140686035</v>
+        <v>0.74273020029068</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>1.21099996566772</v>
       </c>
       <c r="G912" t="n">
-        <v>0.742730140686035</v>
+        <v>0.74273020029068</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G913" t="n">
-        <v>0.724943995475769</v>
+        <v>0.724943935871124</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>1.17900002002716</v>
       </c>
       <c r="G916" t="n">
-        <v>0.723104000091553</v>
+        <v>0.723103940486908</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>1.192999958992</v>
       </c>
       <c r="G918" t="n">
-        <v>0.731690406799316</v>
+        <v>0.731690466403961</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G920" t="n">
-        <v>0.748250067234039</v>
+        <v>0.748250126838684</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>1.18099999427795</v>
       </c>
       <c r="G922" t="n">
-        <v>0.724330604076385</v>
+        <v>0.72433066368103</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.21099996566772</v>
       </c>
       <c r="G923" t="n">
-        <v>0.742730140686035</v>
+        <v>0.74273020029068</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G924" t="n">
-        <v>0.74518346786499</v>
+        <v>0.745183527469635</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G926" t="n">
-        <v>0.792409121990204</v>
+        <v>0.792409062385559</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>1.25</v>
       </c>
       <c r="G929" t="n">
-        <v>0.766649663448334</v>
+        <v>0.766649723052979</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>1.25</v>
       </c>
       <c r="G932" t="n">
-        <v>0.766649663448334</v>
+        <v>0.766649723052979</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>1.23699998855591</v>
       </c>
       <c r="G934" t="n">
-        <v>0.758676528930664</v>
+        <v>0.758676469326019</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G938" t="n">
-        <v>0.797315657138824</v>
+        <v>0.79731559753418</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>1.33700001239777</v>
       </c>
       <c r="G939" t="n">
-        <v>0.820008456707001</v>
+        <v>0.820008516311646</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G943" t="n">
-        <v>0.837181389331818</v>
+        <v>0.837181448936462</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G944" t="n">
-        <v>0.832888245582581</v>
+        <v>0.832888185977936</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G947" t="n">
-        <v>0.829208314418793</v>
+        <v>0.829208254814148</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>1.20099997520447</v>
       </c>
       <c r="G955" t="n">
-        <v>0.736597001552582</v>
+        <v>0.736597061157227</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>1.18599998950958</v>
       </c>
       <c r="G956" t="n">
-        <v>0.727397203445435</v>
+        <v>0.72739714384079</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G957" t="n">
-        <v>0.733530342578888</v>
+        <v>0.733530402183533</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G958" t="n">
-        <v>0.739050328731537</v>
+        <v>0.739050269126892</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G962" t="n">
-        <v>0.775849521160126</v>
+        <v>0.775849401950836</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G963" t="n">
-        <v>0.780142664909363</v>
+        <v>0.780142605304718</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G965" t="n">
-        <v>0.797315657138824</v>
+        <v>0.79731559753418</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>1.29900002479553</v>
       </c>
       <c r="G966" t="n">
-        <v>0.79670238494873</v>
+        <v>0.796702265739441</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>1.25300002098083</v>
       </c>
       <c r="G967" t="n">
-        <v>0.768489599227905</v>
+        <v>0.76848965883255</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G968" t="n">
-        <v>0.771556258201599</v>
+        <v>0.771556198596954</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>1.25100004673004</v>
       </c>
       <c r="G970" t="n">
-        <v>0.767262995243073</v>
+        <v>0.767263054847717</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G981" t="n">
-        <v>0.981311559677124</v>
+        <v>0.981311500072479</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G983" t="n">
-        <v>0.937152624130249</v>
+        <v>0.937152504920959</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G984" t="n">
-        <v>0.961685299873352</v>
+        <v>0.961685359477997</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G986" t="n">
-        <v>0.931019365787506</v>
+        <v>0.931019306182861</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G988" t="n">
-        <v>0.875820577144623</v>
+        <v>0.875820517539978</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>1.44900000095367</v>
       </c>
       <c r="G989" t="n">
-        <v>0.888700246810913</v>
+        <v>0.888700306415558</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G990" t="n">
-        <v>0.872140645980835</v>
+        <v>0.87214070558548</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G991" t="n">
-        <v>0.863554179668427</v>
+        <v>0.863554239273071</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G992" t="n">
-        <v>0.884407043457031</v>
+        <v>0.884407103061676</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>1.5</v>
       </c>
       <c r="G993" t="n">
-        <v>0.919979512691498</v>
+        <v>0.919979572296143</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>1.53100001811981</v>
       </c>
       <c r="G994" t="n">
-        <v>0.938992619514465</v>
+        <v>0.938992559909821</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G995" t="n">
-        <v>0.954325437545776</v>
+        <v>0.954325556755066</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>1.52699995040894</v>
       </c>
       <c r="G996" t="n">
-        <v>0.93653929233551</v>
+        <v>0.936539232730865</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G998" t="n">
-        <v>0.935312628746033</v>
+        <v>0.935312569141388</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1000" t="n">
-        <v>0.928566157817841</v>
+        <v>0.928566098213196</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1006" t="n">
-        <v>1.0334438085556</v>
+        <v>1.03344368934631</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G1007" t="n">
-        <v>1.05123007297516</v>
+        <v>1.05122995376587</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.0193372964859</v>
+        <v>1.01933741569519</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>1.63900005817413</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.00523114204407</v>
+        <v>1.00523102283478</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>1.57599997520447</v>
       </c>
       <c r="G1017" t="n">
-        <v>0.966591894626617</v>
+        <v>0.966591954231262</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G1019" t="n">
-        <v>0.958618640899658</v>
+        <v>0.958618760108948</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1020" t="n">
-        <v>0.956778764724731</v>
+        <v>0.956778824329376</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1022" t="n">
-        <v>0.965978562831879</v>
+        <v>0.965978682041168</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G1023" t="n">
-        <v>0.967205226421356</v>
+        <v>0.967205166816711</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G1027" t="n">
-        <v>0.906486570835114</v>
+        <v>0.906486630439758</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1029" t="n">
-        <v>0.858647584915161</v>
+        <v>0.858647644519806</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1031" t="n">
-        <v>0.815715253353119</v>
+        <v>0.815715193748474</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1032" t="n">
-        <v>0.797315657138824</v>
+        <v>0.79731559753418</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G1033" t="n">
-        <v>0.767876267433167</v>
+        <v>0.767876327037811</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>1.26699995994568</v>
       </c>
       <c r="G1034" t="n">
-        <v>0.777076065540314</v>
+        <v>0.777076125144958</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>1.33700001239777</v>
       </c>
       <c r="G1045" t="n">
-        <v>0.820008456707001</v>
+        <v>0.820008516311646</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G1046" t="n">
-        <v>0.806515514850616</v>
+        <v>0.806515455245972</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G1048" t="n">
-        <v>0.814488530158997</v>
+        <v>0.814488589763641</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1049" t="n">
-        <v>0.813261926174164</v>
+        <v>0.813261985778809</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1050" t="n">
-        <v>0.803448796272278</v>
+        <v>0.803448855876923</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>1.28699994087219</v>
       </c>
       <c r="G1052" t="n">
-        <v>0.78934246301651</v>
+        <v>0.789342522621155</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>1.192999958992</v>
       </c>
       <c r="G1053" t="n">
-        <v>0.731690406799316</v>
+        <v>0.731690466403961</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>1.07299995422363</v>
       </c>
       <c r="G1057" t="n">
-        <v>0.658092081546783</v>
+        <v>0.658092021942139</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>1.04299998283386</v>
       </c>
       <c r="G1058" t="n">
-        <v>0.639692485332489</v>
+        <v>0.639692425727844</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>0.972500026226044</v>
       </c>
       <c r="G1060" t="n">
-        <v>0.596453428268433</v>
+        <v>0.596453487873077</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.572227358818054</v>
+        <v>0.572227299213409</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.496788948774338</v>
+        <v>0.49678897857666</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>0.726999998092651</v>
       </c>
       <c r="G1068" t="n">
-        <v>0.445883482694626</v>
+        <v>0.445883452892303</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.4747094810009</v>
+        <v>0.474709451198578</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.490655779838562</v>
+        <v>0.49065575003624</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.469802916049957</v>
+        <v>0.469802886247635</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>0.732999980449677</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.449563324451447</v>
+        <v>0.449563354253769</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>0.679000020027161</v>
       </c>
       <c r="G1078" t="n">
-        <v>0.41644412279129</v>
+        <v>0.416444092988968</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>0.679000020027161</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.41644412279129</v>
+        <v>0.416444092988968</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.434230387210846</v>
+        <v>0.434230357408524</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>0.901000022888184</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.552601158618927</v>
+        <v>0.552601099014282</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.496788948774338</v>
+        <v>0.49678897857666</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>0.915000021457672</v>
       </c>
       <c r="G1093" t="n">
-        <v>0.561187565326691</v>
+        <v>0.561187505722046</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1095" t="n">
-        <v>0.533588111400604</v>
+        <v>0.533588171005249</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>0.880999982357025</v>
       </c>
       <c r="G1096" t="n">
-        <v>0.540334701538086</v>
+        <v>0.540334641933441</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1098" t="n">
-        <v>0.533588111400604</v>
+        <v>0.533588171005249</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G1099" t="n">
-        <v>0.536041498184204</v>
+        <v>0.536041438579559</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G1100" t="n">
-        <v>0.512121915817261</v>
+        <v>0.51212203502655</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.506602108478546</v>
+        <v>0.506602048873901</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1104" t="n">
-        <v>0.518868565559387</v>
+        <v>0.518868505954742</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>0.83899998664856</v>
       </c>
       <c r="G1105" t="n">
-        <v>0.514575242996216</v>
+        <v>0.514575183391571</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1107" t="n">
-        <v>0.518868565559387</v>
+        <v>0.518868505954742</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>0.830999970436096</v>
       </c>
       <c r="G1108" t="n">
-        <v>0.50966864824295</v>
+        <v>0.509668707847595</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.49188244342804</v>
+        <v>0.491882383823395</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1116" t="n">
-        <v>0.518868565559387</v>
+        <v>0.518868505954742</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1118" t="n">
-        <v>0.545854508876801</v>
+        <v>0.545854568481445</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G1122" t="n">
-        <v>0.610866487026215</v>
+        <v>0.61086642742157</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1124" t="n">
-        <v>0.643985688686371</v>
+        <v>0.643985629081726</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>1.07400000095367</v>
       </c>
       <c r="G1125" t="n">
-        <v>0.658705413341522</v>
+        <v>0.658705353736877</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>1</v>
       </c>
       <c r="G1126" t="n">
-        <v>0.61331969499588</v>
+        <v>0.613319754600525</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G1127" t="n">
-        <v>0.610866487026215</v>
+        <v>0.61086642742157</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>0.949000000953674</v>
       </c>
       <c r="G1129" t="n">
-        <v>0.582040369510651</v>
+        <v>0.582040429115295</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>0.876999974250793</v>
       </c>
       <c r="G1134" t="n">
-        <v>0.537881433963776</v>
+        <v>0.537881374359131</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>0.85699999332428</v>
       </c>
       <c r="G1138" t="n">
-        <v>0.525615036487579</v>
+        <v>0.525614976882935</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>0.842999994754791</v>
       </c>
       <c r="G1139" t="n">
-        <v>0.517028570175171</v>
+        <v>0.517028510570526</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>0.85699999332428</v>
       </c>
       <c r="G1143" t="n">
-        <v>0.525615036487579</v>
+        <v>0.525614976882935</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.516415178775787</v>
+        <v>0.516415238380432</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>0.845000028610229</v>
       </c>
       <c r="G1146" t="n">
-        <v>0.518255233764648</v>
+        <v>0.518255174160004</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>0.83899998664856</v>
       </c>
       <c r="G1148" t="n">
-        <v>0.514575242996216</v>
+        <v>0.514575183391571</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.555054366588593</v>
+        <v>0.555054306983948</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1155" t="n">
-        <v>0.538494765758514</v>
+        <v>0.53849470615387</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1156" t="n">
-        <v>0.542174696922302</v>
+        <v>0.542174577713013</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1157" t="n">
-        <v>0.545854508876801</v>
+        <v>0.545854568481445</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1158" t="n">
-        <v>0.545854508876801</v>
+        <v>0.545854568481445</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>0.879000008106232</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.539108097553253</v>
+        <v>0.539108037948608</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.542174696922302</v>
+        <v>0.542174577713013</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>0.879000008106232</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.539108097553253</v>
+        <v>0.539108037948608</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>0.907000005245209</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.556280970573425</v>
+        <v>0.55628103017807</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.567320704460144</v>
+        <v>0.567320764064789</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G1171" t="n">
-        <v>0.604733288288116</v>
+        <v>0.604733228683472</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.582653701305389</v>
+        <v>0.582653760910034</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>0.962999999523163</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.590626895427704</v>
+        <v>0.590626955032349</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>0.962999999523163</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.590626895427704</v>
+        <v>0.590626955032349</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>0.964999973773956</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.591853499412537</v>
+        <v>0.591853559017181</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.588786959648132</v>
+        <v>0.588786900043488</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.5875603556633</v>
+        <v>0.587560296058655</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.578973770141602</v>
+        <v>0.578973829746246</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.572227358818054</v>
+        <v>0.572227299213409</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>0.916999995708466</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.562414169311523</v>
+        <v>0.562414228916168</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>0.89300000667572</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.547694504261017</v>
+        <v>0.547694563865662</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G1204" t="n">
-        <v>0.555054366588593</v>
+        <v>0.555054306983948</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>0.91100001335144</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.55873429775238</v>
+        <v>0.558734357357025</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.572227358818054</v>
+        <v>0.572227299213409</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>0.944999992847443</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.57958710193634</v>
+        <v>0.579587161540985</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>0.958999991416931</v>
       </c>
       <c r="G1213" t="n">
-        <v>0.588173687458038</v>
+        <v>0.588173627853394</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.571613967418671</v>
+        <v>0.571614027023315</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.56670743227005</v>
+        <v>0.566707491874695</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G1219" t="n">
-        <v>0.56670743227005</v>
+        <v>0.566707491874695</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G1220" t="n">
-        <v>0.56670743227005</v>
+        <v>0.566707491874695</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G1224" t="n">
-        <v>0.597373425960541</v>
+        <v>0.597373366355896</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>0.916999995708466</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.562414169311523</v>
+        <v>0.562414228916168</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.572227358818054</v>
+        <v>0.572227299213409</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>0.944999992847443</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.57958710193634</v>
+        <v>0.579587161540985</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.588786959648132</v>
+        <v>0.588786900043488</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.697957813739777</v>
+        <v>0.697957873344421</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.775236248970032</v>
+        <v>0.775236189365387</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1249" t="n">
-        <v>0.821848452091217</v>
+        <v>0.821848511695862</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G1250" t="n">
-        <v>0.780142664909363</v>
+        <v>0.780142605304718</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>1.25</v>
       </c>
       <c r="G1253" t="n">
-        <v>0.766649663448334</v>
+        <v>0.766649723052979</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.743343532085419</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.739663600921631</v>
+        <v>0.739663541316986</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.748250067234039</v>
+        <v>0.748250126838684</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.712677478790283</v>
+        <v>0.712677538394928</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1270" t="n">
-        <v>0.724943995475769</v>
+        <v>0.724943935871124</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1272" t="n">
-        <v>0.743343532085419</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G1273" t="n">
-        <v>0.737210333347321</v>
+        <v>0.737210273742676</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1277" t="n">
-        <v>0.748250067234039</v>
+        <v>0.748250126838684</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1279" t="n">
-        <v>0.748250067234039</v>
+        <v>0.748250126838684</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1281" t="n">
-        <v>0.720037341117859</v>
+        <v>0.720037400722504</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G1282" t="n">
-        <v>0.713904201984406</v>
+        <v>0.713904142379761</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1283" t="n">
-        <v>0.717584073543549</v>
+        <v>0.717584133148193</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G1286" t="n">
-        <v>0.702864408493042</v>
+        <v>0.702864468097687</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1287" t="n">
-        <v>0.712677478790283</v>
+        <v>0.712677538394928</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G1288" t="n">
-        <v>0.70654433965683</v>
+        <v>0.706544280052185</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1293" t="n">
-        <v>0.693051338195801</v>
+        <v>0.693051278591156</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.720037341117859</v>
+        <v>0.720037400722504</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1299" t="n">
-        <v>0.743343532085419</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1301" t="n">
-        <v>0.748250067234039</v>
+        <v>0.748250126838684</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.797315657138824</v>
+        <v>0.79731559753418</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G1310" t="n">
-        <v>0.794862389564514</v>
+        <v>0.794862329959869</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>1.32200002670288</v>
       </c>
       <c r="G1312" t="n">
-        <v>0.810808718204498</v>
+        <v>0.810808777809143</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.803448796272278</v>
+        <v>0.803448855876923</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1318" t="n">
-        <v>0.797315657138824</v>
+        <v>0.79731559753418</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1320" t="n">
-        <v>0.792409121990204</v>
+        <v>0.792409062385559</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1321" t="n">
-        <v>0.815715253353119</v>
+        <v>0.815715193748474</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G1323" t="n">
-        <v>0.841474711894989</v>
+        <v>0.841474652290344</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1324" t="n">
-        <v>0.858647584915161</v>
+        <v>0.858647644519806</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1325" t="n">
-        <v>0.858647584915161</v>
+        <v>0.858647644519806</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>1.38399994373322</v>
       </c>
       <c r="G1326" t="n">
-        <v>0.848834455013275</v>
+        <v>0.84883451461792</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G1327" t="n">
-        <v>0.829208314418793</v>
+        <v>0.829208254814148</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1329" t="n">
-        <v>0.813261926174164</v>
+        <v>0.813261985778809</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1330" t="n">
-        <v>0.843928039073944</v>
+        <v>0.843927979469299</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1333" t="n">
-        <v>0.813261926174164</v>
+        <v>0.813261985778809</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1334" t="n">
-        <v>0.85128778219223</v>
+        <v>0.851287841796875</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1338" t="n">
-        <v>0.813261926174164</v>
+        <v>0.813261985778809</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1340" t="n">
-        <v>0.843928039073944</v>
+        <v>0.843927979469299</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G1342" t="n">
-        <v>0.841474711894989</v>
+        <v>0.841474652290344</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G1343" t="n">
-        <v>0.842701315879822</v>
+        <v>0.842701256275177</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G1344" t="n">
-        <v>0.842701315879822</v>
+        <v>0.842701256275177</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1345" t="n">
-        <v>0.815715253353119</v>
+        <v>0.815715193748474</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1347" t="n">
-        <v>0.803448796272278</v>
+        <v>0.803448855876923</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G1349" t="n">
-        <v>0.853741049766541</v>
+        <v>0.853741109371185</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1354" t="n">
-        <v>0.890540301799774</v>
+        <v>0.890540242195129</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1357" t="n">
-        <v>0.890540301799774</v>
+        <v>0.890540242195129</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G1358" t="n">
-        <v>0.872140645980835</v>
+        <v>0.87214070558548</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>1.44599997997284</v>
       </c>
       <c r="G1359" t="n">
-        <v>0.886860251426697</v>
+        <v>0.886860370635986</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>1.42599999904633</v>
       </c>
       <c r="G1360" t="n">
-        <v>0.874593913555145</v>
+        <v>0.87459397315979</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G1361" t="n">
-        <v>0.875820577144623</v>
+        <v>0.875820517539978</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1362" t="n">
-        <v>0.85128778219223</v>
+        <v>0.851287841796875</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1364" t="n">
-        <v>0.863554179668427</v>
+        <v>0.863554239273071</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1365" t="n">
-        <v>0.863554179668427</v>
+        <v>0.863554239273071</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1366" t="n">
-        <v>0.843928039073944</v>
+        <v>0.843927979469299</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G1374" t="n">
-        <v>0.861100912094116</v>
+        <v>0.861100971698761</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1375" t="n">
-        <v>0.863554179668427</v>
+        <v>0.863554239273071</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G1376" t="n">
-        <v>0.861100912094116</v>
+        <v>0.861100971698761</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1377" t="n">
-        <v>0.866007447242737</v>
+        <v>0.866007506847382</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G1379" t="n">
-        <v>0.912619829177856</v>
+        <v>0.912619769573212</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>1.5</v>
       </c>
       <c r="G1380" t="n">
-        <v>0.919979512691498</v>
+        <v>0.919979572296143</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G1381" t="n">
-        <v>0.940832555294037</v>
+        <v>0.940832495689392</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G1382" t="n">
-        <v>0.929792702198029</v>
+        <v>0.929792761802673</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G1386" t="n">
-        <v>0.945739090442657</v>
+        <v>0.945739030838013</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>1.5</v>
       </c>
       <c r="G1387" t="n">
-        <v>0.919979512691498</v>
+        <v>0.919979572296143</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1388" t="n">
-        <v>0.890540301799774</v>
+        <v>0.890540242195129</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G1389" t="n">
-        <v>0.921206176280975</v>
+        <v>0.921206295490265</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1391" t="n">
-        <v>0.890540301799774</v>
+        <v>0.890540242195129</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G1392" t="n">
-        <v>0.884407043457031</v>
+        <v>0.884407103061676</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G1393" t="n">
-        <v>0.884407043457031</v>
+        <v>0.884407103061676</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G1394" t="n">
-        <v>0.861100912094116</v>
+        <v>0.861100971698761</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G1395" t="n">
-        <v>0.861100912094116</v>
+        <v>0.861100971698761</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1400" t="n">
-        <v>0.820621848106384</v>
+        <v>0.82062178850174</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G1403" t="n">
-        <v>0.794862389564514</v>
+        <v>0.794862329959869</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>1.29799997806549</v>
       </c>
       <c r="G1404" t="n">
-        <v>0.796088993549347</v>
+        <v>0.796089053153992</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1406" t="n">
-        <v>0.785049259662628</v>
+        <v>0.785049200057983</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G1410" t="n">
-        <v>0.737210333347321</v>
+        <v>0.737210273742676</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1414" t="n">
-        <v>0.858647584915161</v>
+        <v>0.858647644519806</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1415" t="n">
-        <v>0.866007447242737</v>
+        <v>0.866007506847382</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G1417" t="n">
-        <v>0.850061178207397</v>
+        <v>0.850061118602753</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1423" t="n">
-        <v>0.85128778219223</v>
+        <v>0.851287841796875</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G1424" t="n">
-        <v>0.850061178207397</v>
+        <v>0.850061118602753</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G1425" t="n">
-        <v>0.857421040534973</v>
+        <v>0.857420980930328</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1426" t="n">
-        <v>0.858647584915161</v>
+        <v>0.858647644519806</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G1428" t="n">
-        <v>0.899126648902893</v>
+        <v>0.899126708507538</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>1.42599999904633</v>
       </c>
       <c r="G1430" t="n">
-        <v>0.874593913555145</v>
+        <v>0.87459397315979</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>1.43400001525879</v>
       </c>
       <c r="G1431" t="n">
-        <v>0.879500567913055</v>
+        <v>0.879500508308411</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G1432" t="n">
-        <v>0.853741049766541</v>
+        <v>0.853741109371185</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G1435" t="n">
-        <v>0.842701315879822</v>
+        <v>0.842701256275177</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1437" t="n">
-        <v>0.843928039073944</v>
+        <v>0.843927979469299</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>1.42400002479553</v>
       </c>
       <c r="G1439" t="n">
-        <v>0.873367309570312</v>
+        <v>0.873367249965668</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1440" t="n">
-        <v>0.858647584915161</v>
+        <v>0.858647644519806</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G1441" t="n">
-        <v>0.857421040534973</v>
+        <v>0.857420980930328</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1443" t="n">
-        <v>0.866007447242737</v>
+        <v>0.866007506847382</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G1445" t="n">
-        <v>0.850061178207397</v>
+        <v>0.850061118602753</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G1447" t="n">
-        <v>0.823075115680695</v>
+        <v>0.82307505607605</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G1451" t="n">
-        <v>0.823075115680695</v>
+        <v>0.82307505607605</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1453" t="n">
-        <v>0.813261926174164</v>
+        <v>0.813261985778809</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1455" t="n">
-        <v>0.772782921791077</v>
+        <v>0.772782862186432</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1456" t="n">
-        <v>0.797315657138824</v>
+        <v>0.79731559753418</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1458" t="n">
-        <v>0.813261926174164</v>
+        <v>0.813261985778809</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>1.33200001716614</v>
       </c>
       <c r="G1459" t="n">
-        <v>0.816941857337952</v>
+        <v>0.816941916942596</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1461" t="n">
-        <v>0.803448796272278</v>
+        <v>0.803448855876923</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>1.29799997806549</v>
       </c>
       <c r="G1462" t="n">
-        <v>0.796088993549347</v>
+        <v>0.796089053153992</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1463" t="n">
-        <v>0.785049259662628</v>
+        <v>0.785049200057983</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1465" t="n">
-        <v>0.792409121990204</v>
+        <v>0.792409062385559</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1470" t="n">
-        <v>0.809582114219666</v>
+        <v>0.809582054615021</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1471" t="n">
-        <v>0.815715253353119</v>
+        <v>0.815715193748474</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G1475" t="n">
-        <v>0.829208314418793</v>
+        <v>0.829208254814148</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1478" t="n">
-        <v>0.85128778219223</v>
+        <v>0.851287841796875</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1479" t="n">
-        <v>0.883180379867554</v>
+        <v>0.883180439472198</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G1481" t="n">
-        <v>0.850061178207397</v>
+        <v>0.850061118602753</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G1487" t="n">
-        <v>0.819395124912262</v>
+        <v>0.819395184516907</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>1.29799997806549</v>
       </c>
       <c r="G1492" t="n">
-        <v>0.796088993549347</v>
+        <v>0.796089053153992</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1493" t="n">
-        <v>0.797315657138824</v>
+        <v>0.79731559753418</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G1495" t="n">
-        <v>0.823075115680695</v>
+        <v>0.82307505607605</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1496" t="n">
-        <v>0.821848452091217</v>
+        <v>0.821848511695862</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>1.33200001716614</v>
       </c>
       <c r="G1497" t="n">
-        <v>0.816941857337952</v>
+        <v>0.816941916942596</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1498" t="n">
-        <v>0.797315657138824</v>
+        <v>0.79731559753418</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1499" t="n">
-        <v>0.809582114219666</v>
+        <v>0.809582054615021</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1501" t="n">
-        <v>0.797315657138824</v>
+        <v>0.79731559753418</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1505" t="n">
-        <v>0.735983669757843</v>
+        <v>0.735983729362488</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1506" t="n">
-        <v>0.743343532085419</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G1507" t="n">
-        <v>0.733530342578888</v>
+        <v>0.733530402183533</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G1509" t="n">
-        <v>0.722490668296814</v>
+        <v>0.722490549087524</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1511" t="n">
-        <v>0.748250067234039</v>
+        <v>0.748250126838684</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1512" t="n">
-        <v>0.743343532085419</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1513" t="n">
-        <v>0.743343532085419</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1514" t="n">
-        <v>0.735983669757843</v>
+        <v>0.735983729362488</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>1.18599998950958</v>
       </c>
       <c r="G1515" t="n">
-        <v>0.727397203445435</v>
+        <v>0.72739714384079</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1516" t="n">
-        <v>0.735983669757843</v>
+        <v>0.735983729362488</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>1.21599996089935</v>
       </c>
       <c r="G1517" t="n">
-        <v>0.745796740055084</v>
+        <v>0.745796799659729</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1522" t="n">
-        <v>0.724943995475769</v>
+        <v>0.724943935871124</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1526" t="n">
-        <v>0.724943995475769</v>
+        <v>0.724943935871124</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G1530" t="n">
-        <v>0.758063137531281</v>
+        <v>0.758063197135925</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G1533" t="n">
-        <v>0.780142664909363</v>
+        <v>0.780142605304718</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>1.26199996471405</v>
       </c>
       <c r="G1534" t="n">
-        <v>0.774009525775909</v>
+        <v>0.774009466171265</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1537" t="n">
-        <v>0.772782921791077</v>
+        <v>0.772782862186432</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1538" t="n">
-        <v>0.771556258201599</v>
+        <v>0.771556198596954</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1540" t="n">
-        <v>0.775236248970032</v>
+        <v>0.775236189365387</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1544" t="n">
-        <v>0.748250067234039</v>
+        <v>0.748250126838684</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1548" t="n">
-        <v>0.735983669757843</v>
+        <v>0.735983729362488</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1549" t="n">
-        <v>0.735983669757843</v>
+        <v>0.735983729362488</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1554" t="n">
-        <v>0.739663600921631</v>
+        <v>0.739663541316986</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1558" t="n">
-        <v>0.720037341117859</v>
+        <v>0.720037400722504</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1561" t="n">
-        <v>0.712677478790283</v>
+        <v>0.712677538394928</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G1563" t="n">
-        <v>0.696731209754944</v>
+        <v>0.696731269359589</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1564" t="n">
-        <v>0.705317735671997</v>
+        <v>0.705317676067352</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1571" t="n">
-        <v>0.51764190196991</v>
+        <v>0.517641842365265</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>0.788999974727631</v>
       </c>
       <c r="G1572" t="n">
-        <v>0.483909279108047</v>
+        <v>0.483909249305725</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1573" t="n">
-        <v>0.480842649936676</v>
+        <v>0.480842679738998</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G1574" t="n">
-        <v>0.520095109939575</v>
+        <v>0.52009516954422</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>0.814999997615814</v>
       </c>
       <c r="G1578" t="n">
-        <v>0.499855577945709</v>
+        <v>0.499855607748032</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1579" t="n">
-        <v>0.538494765758514</v>
+        <v>0.53849470615387</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>0.897000014781952</v>
       </c>
       <c r="G1582" t="n">
-        <v>0.550147771835327</v>
+        <v>0.550147831439972</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>0.879000008106232</v>
       </c>
       <c r="G1584" t="n">
-        <v>0.539108097553253</v>
+        <v>0.539108037948608</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G1593" t="n">
-        <v>0.536041498184204</v>
+        <v>0.536041438579559</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1597" t="n">
-        <v>0.51518851518631</v>
+        <v>0.515188574790955</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1598" t="n">
-        <v>0.51764190196991</v>
+        <v>0.517641842365265</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G1604" t="n">
-        <v>0.577747166156769</v>
+        <v>0.577747225761414</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G1605" t="n">
-        <v>0.577747166156769</v>
+        <v>0.577747225761414</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1610" t="n">
-        <v>0.533588111400604</v>
+        <v>0.533588171005249</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>0.869000017642975</v>
       </c>
       <c r="G1611" t="n">
-        <v>0.53297483921051</v>
+        <v>0.532974898815155</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>0.830999970436096</v>
       </c>
       <c r="G1613" t="n">
-        <v>0.50966864824295</v>
+        <v>0.509668707847595</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1614" t="n">
-        <v>0.51764190196991</v>
+        <v>0.517641842365265</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1615" t="n">
-        <v>0.509055316448212</v>
+        <v>0.509055376052856</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G1617" t="n">
-        <v>0.520095109939575</v>
+        <v>0.52009516954422</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1618" t="n">
-        <v>0.509055316448212</v>
+        <v>0.509055376052856</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1619" t="n">
-        <v>0.509055316448212</v>
+        <v>0.509055376052856</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G1620" t="n">
-        <v>0.519481837749481</v>
+        <v>0.519481778144836</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1622" t="n">
-        <v>0.533588111400604</v>
+        <v>0.533588171005249</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>0.869000017642975</v>
       </c>
       <c r="G1625" t="n">
-        <v>0.53297483921051</v>
+        <v>0.532974898815155</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1629" t="n">
-        <v>0.572227358818054</v>
+        <v>0.572227299213409</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G1631" t="n">
-        <v>0.574067294597626</v>
+        <v>0.574067234992981</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G1633" t="n">
-        <v>0.647665679454803</v>
+        <v>0.647665619850159</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G1637" t="n">
-        <v>0.628039419651031</v>
+        <v>0.628039479255676</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1640" t="n">
-        <v>0.545854508876801</v>
+        <v>0.545854568481445</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>0.89300000667572</v>
       </c>
       <c r="G1642" t="n">
-        <v>0.547694504261017</v>
+        <v>0.547694563865662</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1643" t="n">
-        <v>0.533588111400604</v>
+        <v>0.533588171005249</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>0.869000017642975</v>
       </c>
       <c r="G1644" t="n">
-        <v>0.53297483921051</v>
+        <v>0.532974898815155</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>0.898999989032745</v>
       </c>
       <c r="G1645" t="n">
-        <v>0.551374495029449</v>
+        <v>0.551374435424805</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>0.887000024318695</v>
       </c>
       <c r="G1646" t="n">
-        <v>0.544014573097229</v>
+        <v>0.544014632701874</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>0.898999989032745</v>
       </c>
       <c r="G1649" t="n">
-        <v>0.551374495029449</v>
+        <v>0.551374435424805</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1651" t="n">
-        <v>0.533588111400604</v>
+        <v>0.533588171005249</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G1655" t="n">
-        <v>0.512121915817261</v>
+        <v>0.51212203502655</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>0.788999974727631</v>
       </c>
       <c r="G1657" t="n">
-        <v>0.483909279108047</v>
+        <v>0.483909249305725</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>0.83899998664856</v>
       </c>
       <c r="G1659" t="n">
-        <v>0.514575242996216</v>
+        <v>0.514575183391571</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1660" t="n">
-        <v>0.509055316448212</v>
+        <v>0.509055376052856</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1664" t="n">
-        <v>0.482069283723831</v>
+        <v>0.482069343328476</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1668" t="n">
-        <v>0.480842649936676</v>
+        <v>0.480842679738998</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1669" t="n">
-        <v>0.509055316448212</v>
+        <v>0.509055376052856</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>0.915000021457672</v>
       </c>
       <c r="G1674" t="n">
-        <v>0.561187565326691</v>
+        <v>0.561187505722046</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>0.915000021457672</v>
       </c>
       <c r="G1675" t="n">
-        <v>0.561187565326691</v>
+        <v>0.561187505722046</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G1676" t="n">
-        <v>0.56670743227005</v>
+        <v>0.566707491874695</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G1682" t="n">
-        <v>0.54892110824585</v>
+        <v>0.548921167850494</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>0.880999982357025</v>
       </c>
       <c r="G1686" t="n">
-        <v>0.540334701538086</v>
+        <v>0.540334641933441</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>0.898999989032745</v>
       </c>
       <c r="G1687" t="n">
-        <v>0.551374495029449</v>
+        <v>0.551374435424805</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1688" t="n">
-        <v>0.538494765758514</v>
+        <v>0.53849470615387</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>0.898999989032745</v>
       </c>
       <c r="G1690" t="n">
-        <v>0.551374495029449</v>
+        <v>0.551374435424805</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>0.887000024318695</v>
       </c>
       <c r="G1691" t="n">
-        <v>0.544014573097229</v>
+        <v>0.544014632701874</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>0.870999991893768</v>
       </c>
       <c r="G1693" t="n">
-        <v>0.534201502799988</v>
+        <v>0.534201443195343</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1696" t="n">
-        <v>0.51518851518631</v>
+        <v>0.515188574790955</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1698" t="n">
-        <v>0.509055316448212</v>
+        <v>0.509055376052856</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1699" t="n">
-        <v>0.506602108478546</v>
+        <v>0.506602048873901</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1701" t="n">
-        <v>0.490655779838562</v>
+        <v>0.49065575003624</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1702" t="n">
-        <v>0.485749274492264</v>
+        <v>0.485749244689941</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1703" t="n">
-        <v>0.485749274492264</v>
+        <v>0.485749244689941</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>0.809000015258789</v>
       </c>
       <c r="G1704" t="n">
-        <v>0.496175676584244</v>
+        <v>0.496175706386566</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1705" t="n">
-        <v>0.484522610902786</v>
+        <v>0.484522551298141</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1706" t="n">
-        <v>0.486975908279419</v>
+        <v>0.486975878477097</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1708" t="n">
-        <v>0.4747094810009</v>
+        <v>0.474709451198578</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1709" t="n">
-        <v>0.4747094810009</v>
+        <v>0.474709451198578</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G1711" t="n">
-        <v>0.456923186779022</v>
+        <v>0.456923216581345</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1712" t="n">
-        <v>0.453243285417557</v>
+        <v>0.453243315219879</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1713" t="n">
-        <v>0.436683654785156</v>
+        <v>0.436683624982834</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1715" t="n">
-        <v>0.437910288572311</v>
+        <v>0.437910258769989</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1716" t="n">
-        <v>0.447723388671875</v>
+        <v>0.447723418474197</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>0.712999999523163</v>
       </c>
       <c r="G1719" t="n">
-        <v>0.437296956777573</v>
+        <v>0.437296986579895</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1723" t="n">
-        <v>0.429323792457581</v>
+        <v>0.429323822259903</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1724" t="n">
-        <v>0.414604157209396</v>
+        <v>0.414604127407074</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>0.66100001335144</v>
       </c>
       <c r="G1725" t="n">
-        <v>0.405404359102249</v>
+        <v>0.405404388904572</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>0.686999976634979</v>
       </c>
       <c r="G1727" t="n">
-        <v>0.421350657939911</v>
+        <v>0.421350628137589</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1728" t="n">
-        <v>0.429323792457581</v>
+        <v>0.429323822259903</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1729" t="n">
-        <v>0.431777089834213</v>
+        <v>0.431777119636536</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1731" t="n">
-        <v>0.433003723621368</v>
+        <v>0.433003753423691</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1732" t="n">
-        <v>0.490655779838562</v>
+        <v>0.49065575003624</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>0.842999994754791</v>
       </c>
       <c r="G1737" t="n">
-        <v>0.517028570175171</v>
+        <v>0.517028510570526</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1744" t="n">
-        <v>0.513961911201477</v>
+        <v>0.513961970806122</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1745" t="n">
-        <v>0.51518851518631</v>
+        <v>0.515188574790955</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1746" t="n">
-        <v>0.51518851518631</v>
+        <v>0.515188574790955</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G1751" t="n">
-        <v>0.567320704460144</v>
+        <v>0.567320764064789</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1754" t="n">
-        <v>0.542174696922302</v>
+        <v>0.542174577713013</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1761" t="n">
-        <v>0.545854508876801</v>
+        <v>0.545854568481445</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G1765" t="n">
-        <v>0.519481837749481</v>
+        <v>0.519481778144836</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G1766" t="n">
-        <v>0.519481837749481</v>
+        <v>0.519481778144836</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>0.845000028610229</v>
       </c>
       <c r="G1768" t="n">
-        <v>0.518255233764648</v>
+        <v>0.518255174160004</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1769" t="n">
-        <v>0.518868565559387</v>
+        <v>0.518868505954742</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1774" t="n">
-        <v>0.533588111400604</v>
+        <v>0.533588171005249</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G1777" t="n">
-        <v>0.577747166156769</v>
+        <v>0.577747225761414</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G1785" t="n">
-        <v>0.577747166156769</v>
+        <v>0.577747225761414</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>0.944999992847443</v>
       </c>
       <c r="G1786" t="n">
-        <v>0.57958710193634</v>
+        <v>0.579587161540985</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>1.0460000038147</v>
       </c>
       <c r="G1791" t="n">
-        <v>0.641532421112061</v>
+        <v>0.641532480716705</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1792" t="n">
-        <v>0.656252205371857</v>
+        <v>0.656252145767212</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1794" t="n">
-        <v>0.674651741981506</v>
+        <v>0.674651682376862</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>1.09200000762939</v>
       </c>
       <c r="G1798" t="n">
-        <v>0.669745206832886</v>
+        <v>0.669745087623596</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1799" t="n">
-        <v>0.674651741981506</v>
+        <v>0.674651682376862</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1801" t="n">
-        <v>0.674651741981506</v>
+        <v>0.674651682376862</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G1807" t="n">
-        <v>0.702864408493042</v>
+        <v>0.702864468097687</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1808" t="n">
-        <v>0.720037341117859</v>
+        <v>0.720037400722504</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1814" t="n">
-        <v>0.743343532085419</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1815" t="n">
-        <v>0.748250067234039</v>
+        <v>0.748250126838684</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1820" t="n">
-        <v>0.724943995475769</v>
+        <v>0.724943935871124</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G1821" t="n">
-        <v>0.753156661987305</v>
+        <v>0.753156721591949</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>1.11800003051758</v>
       </c>
       <c r="G1822" t="n">
-        <v>0.68569141626358</v>
+        <v>0.68569153547287</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1835" t="n">
-        <v>0.643985688686371</v>
+        <v>0.643985629081726</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G1836" t="n">
-        <v>0.628039419651031</v>
+        <v>0.628039479255676</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G1838" t="n">
-        <v>0.647665679454803</v>
+        <v>0.647665619850159</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1840" t="n">
-        <v>0.705317735671997</v>
+        <v>0.705317676067352</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1841" t="n">
-        <v>0.705317735671997</v>
+        <v>0.705317676067352</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G1843" t="n">
-        <v>0.696731209754944</v>
+        <v>0.696731269359589</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>1.11800003051758</v>
       </c>
       <c r="G1845" t="n">
-        <v>0.68569141626358</v>
+        <v>0.68569153547287</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1849" t="n">
-        <v>0.686918139457703</v>
+        <v>0.686918079853058</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G1850" t="n">
-        <v>0.697957813739777</v>
+        <v>0.697957873344421</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1851" t="n">
-        <v>0.686918139457703</v>
+        <v>0.686918079853058</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1852" t="n">
-        <v>0.686918139457703</v>
+        <v>0.686918079853058</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1857" t="n">
-        <v>0.743343532085419</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>1.21599996089935</v>
       </c>
       <c r="G1858" t="n">
-        <v>0.745796740055084</v>
+        <v>0.745796799659729</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>1.18599998950958</v>
       </c>
       <c r="G1862" t="n">
-        <v>0.727397203445435</v>
+        <v>0.72739714384079</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G1864" t="n">
-        <v>0.753156661987305</v>
+        <v>0.753156721591949</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G1865" t="n">
-        <v>0.753156661987305</v>
+        <v>0.753156721591949</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1867" t="n">
-        <v>0.724943995475769</v>
+        <v>0.724943935871124</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -48937,7 +48937,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G1868" t="n">
-        <v>0.70654433965683</v>
+        <v>0.706544280052185</v>
       </c>
       <c r="H1868" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1869" t="n">
-        <v>0.717584073543549</v>
+        <v>0.717584133148193</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G1871" t="n">
-        <v>0.696731209754944</v>
+        <v>0.696731269359589</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G1872" t="n">
-        <v>0.713904201984406</v>
+        <v>0.713904142379761</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1877" t="n">
-        <v>0.705317735671997</v>
+        <v>0.705317676067352</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1883" t="n">
-        <v>0.705317735671997</v>
+        <v>0.705317676067352</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49379,7 +49379,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.686918139457703</v>
+        <v>0.686918079853058</v>
       </c>
       <c r="H1885" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.700411081314087</v>
+        <v>0.700411140918732</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49613,7 +49613,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G1894" t="n">
-        <v>0.716357469558716</v>
+        <v>0.716357409954071</v>
       </c>
       <c r="H1894" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1895" t="n">
-        <v>0.717584073543549</v>
+        <v>0.717584133148193</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49665,7 +49665,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1896" t="n">
-        <v>0.720037341117859</v>
+        <v>0.720037400722504</v>
       </c>
       <c r="H1896" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1899" t="n">
-        <v>0.717584073543549</v>
+        <v>0.717584133148193</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49769,7 +49769,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1900" t="n">
-        <v>0.720037341117859</v>
+        <v>0.720037400722504</v>
       </c>
       <c r="H1900" t="s">
         <v>8</v>
@@ -49847,7 +49847,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G1903" t="n">
-        <v>0.716357469558716</v>
+        <v>0.716357409954071</v>
       </c>
       <c r="H1903" t="s">
         <v>8</v>
@@ -49899,7 +49899,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1905" t="n">
-        <v>0.717584073543549</v>
+        <v>0.717584133148193</v>
       </c>
       <c r="H1905" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1906" t="n">
-        <v>0.717584073543549</v>
+        <v>0.717584133148193</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50003,7 +50003,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1909" t="n">
-        <v>0.748250067234039</v>
+        <v>0.748250126838684</v>
       </c>
       <c r="H1909" t="s">
         <v>8</v>
@@ -50107,7 +50107,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G1913" t="n">
-        <v>0.753156661987305</v>
+        <v>0.753156721591949</v>
       </c>
       <c r="H1913" t="s">
         <v>8</v>
@@ -50185,7 +50185,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G1916" t="n">
-        <v>0.767876267433167</v>
+        <v>0.767876327037811</v>
       </c>
       <c r="H1916" t="s">
         <v>8</v>
@@ -50211,7 +50211,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1917" t="n">
-        <v>0.775236248970032</v>
+        <v>0.775236189365387</v>
       </c>
       <c r="H1917" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1920" t="n">
-        <v>0.797315657138824</v>
+        <v>0.79731559753418</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50367,7 +50367,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1923" t="n">
-        <v>0.797315657138824</v>
+        <v>0.79731559753418</v>
       </c>
       <c r="H1923" t="s">
         <v>8</v>
@@ -50393,7 +50393,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1924" t="n">
-        <v>0.797315657138824</v>
+        <v>0.79731559753418</v>
       </c>
       <c r="H1924" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1925" t="n">
-        <v>0.821848452091217</v>
+        <v>0.821848511695862</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50471,7 +50471,7 @@
         <v>1.31200003623962</v>
       </c>
       <c r="G1927" t="n">
-        <v>0.804675459861755</v>
+        <v>0.8046755194664</v>
       </c>
       <c r="H1927" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G1929" t="n">
-        <v>0.819395124912262</v>
+        <v>0.819395184516907</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50601,7 +50601,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1932" t="n">
-        <v>0.775236248970032</v>
+        <v>0.775236189365387</v>
       </c>
       <c r="H1932" t="s">
         <v>8</v>
@@ -50653,7 +50653,7 @@
         <v>1.21599996089935</v>
       </c>
       <c r="G1934" t="n">
-        <v>0.745796740055084</v>
+        <v>0.745796799659729</v>
       </c>
       <c r="H1934" t="s">
         <v>8</v>
@@ -50705,7 +50705,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1936" t="n">
-        <v>0.735983669757843</v>
+        <v>0.735983729362488</v>
       </c>
       <c r="H1936" t="s">
         <v>8</v>
@@ -50809,7 +50809,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G1940" t="n">
-        <v>0.767876267433167</v>
+        <v>0.767876327037811</v>
       </c>
       <c r="H1940" t="s">
         <v>8</v>
@@ -50887,7 +50887,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1943" t="n">
-        <v>0.748250067234039</v>
+        <v>0.748250126838684</v>
       </c>
       <c r="H1943" t="s">
         <v>8</v>
@@ -50913,7 +50913,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G1944" t="n">
-        <v>0.753156661987305</v>
+        <v>0.753156721591949</v>
       </c>
       <c r="H1944" t="s">
         <v>8</v>
@@ -50991,7 +50991,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G1947" t="n">
-        <v>0.758063137531281</v>
+        <v>0.758063197135925</v>
       </c>
       <c r="H1947" t="s">
         <v>8</v>
@@ -51017,7 +51017,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G1948" t="n">
-        <v>0.780142664909363</v>
+        <v>0.780142605304718</v>
       </c>
       <c r="H1948" t="s">
         <v>8</v>
@@ -51069,7 +51069,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1950" t="n">
-        <v>0.785049259662628</v>
+        <v>0.785049200057983</v>
       </c>
       <c r="H1950" t="s">
         <v>8</v>
@@ -51121,7 +51121,7 @@
         <v>1.26199996471405</v>
       </c>
       <c r="G1952" t="n">
-        <v>0.774009525775909</v>
+        <v>0.774009466171265</v>
       </c>
       <c r="H1952" t="s">
         <v>8</v>
@@ -51225,7 +51225,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1956" t="n">
-        <v>0.785049259662628</v>
+        <v>0.785049200057983</v>
       </c>
       <c r="H1956" t="s">
         <v>8</v>
@@ -51251,7 +51251,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1957" t="n">
-        <v>0.772782921791077</v>
+        <v>0.772782862186432</v>
       </c>
       <c r="H1957" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1958" t="n">
-        <v>0.775236248970032</v>
+        <v>0.775236189365387</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51303,7 +51303,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1959" t="n">
-        <v>0.775236248970032</v>
+        <v>0.775236189365387</v>
       </c>
       <c r="H1959" t="s">
         <v>8</v>
@@ -51433,7 +51433,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G1964" t="n">
-        <v>0.794862389564514</v>
+        <v>0.794862329959869</v>
       </c>
       <c r="H1964" t="s">
         <v>8</v>
@@ -51459,7 +51459,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1965" t="n">
-        <v>0.821848452091217</v>
+        <v>0.821848511695862</v>
       </c>
       <c r="H1965" t="s">
         <v>8</v>
@@ -51485,7 +51485,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G1966" t="n">
-        <v>0.850061178207397</v>
+        <v>0.850061118602753</v>
       </c>
       <c r="H1966" t="s">
         <v>8</v>
@@ -51511,7 +51511,7 @@
         <v>1.42599999904633</v>
       </c>
       <c r="G1967" t="n">
-        <v>0.874593913555145</v>
+        <v>0.87459397315979</v>
       </c>
       <c r="H1967" t="s">
         <v>8</v>
@@ -51537,7 +51537,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1968" t="n">
-        <v>0.889313578605652</v>
+        <v>0.889313697814941</v>
       </c>
       <c r="H1968" t="s">
         <v>8</v>
@@ -51563,7 +51563,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G1969" t="n">
-        <v>0.924886226654053</v>
+        <v>0.924886167049408</v>
       </c>
       <c r="H1969" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1971" t="n">
-        <v>0.907713174819946</v>
+        <v>0.907713234424591</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51667,7 +51667,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G1973" t="n">
-        <v>0.912619829177856</v>
+        <v>0.912619769573212</v>
       </c>
       <c r="H1973" t="s">
         <v>8</v>
@@ -51719,7 +51719,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1975" t="n">
-        <v>0.931019365787506</v>
+        <v>0.931019306182861</v>
       </c>
       <c r="H1975" t="s">
         <v>8</v>
@@ -51745,7 +51745,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1976" t="n">
-        <v>0.92611289024353</v>
+        <v>0.926112711429596</v>
       </c>
       <c r="H1976" t="s">
         <v>8</v>
@@ -51771,7 +51771,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1977" t="n">
-        <v>0.928566157817841</v>
+        <v>0.928566098213196</v>
       </c>
       <c r="H1977" t="s">
         <v>8</v>
@@ -51823,7 +51823,7 @@
         <v>1.58800005912781</v>
       </c>
       <c r="G1979" t="n">
-        <v>0.973951816558838</v>
+        <v>0.973951756954193</v>
       </c>
       <c r="H1979" t="s">
         <v>8</v>
@@ -51875,7 +51875,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G1981" t="n">
-        <v>1.02792382240295</v>
+        <v>1.02792394161224</v>
       </c>
       <c r="H1981" t="s">
         <v>8</v>
@@ -51927,7 +51927,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1983" t="n">
-        <v>0.999711155891418</v>
+        <v>0.999711215496063</v>
       </c>
       <c r="H1983" t="s">
         <v>8</v>
@@ -52083,7 +52083,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1989" t="n">
-        <v>0.993577897548676</v>
+        <v>0.99357795715332</v>
       </c>
       <c r="H1989" t="s">
         <v>8</v>
@@ -52161,7 +52161,7 @@
         <v>1.54799997806549</v>
       </c>
       <c r="G1992" t="n">
-        <v>0.949418962001801</v>
+        <v>0.949418902397156</v>
       </c>
       <c r="H1992" t="s">
         <v>8</v>
@@ -52187,7 +52187,7 @@
         <v>1.54799997806549</v>
       </c>
       <c r="G1993" t="n">
-        <v>0.949418962001801</v>
+        <v>0.949418902397156</v>
       </c>
       <c r="H1993" t="s">
         <v>8</v>
@@ -52213,7 +52213,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1994" t="n">
-        <v>0.937152624130249</v>
+        <v>0.937152504920959</v>
       </c>
       <c r="H1994" t="s">
         <v>8</v>
@@ -52239,7 +52239,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1995" t="n">
-        <v>0.956778764724731</v>
+        <v>0.956778824329376</v>
       </c>
       <c r="H1995" t="s">
         <v>8</v>
@@ -52265,7 +52265,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G1996" t="n">
-        <v>0.951872229576111</v>
+        <v>0.951872289180756</v>
       </c>
       <c r="H1996" t="s">
         <v>8</v>
@@ -52291,7 +52291,7 @@
         <v>1.57799994945526</v>
       </c>
       <c r="G1997" t="n">
-        <v>0.967818558216095</v>
+        <v>0.96781849861145</v>
       </c>
       <c r="H1997" t="s">
         <v>8</v>
@@ -52343,7 +52343,7 @@
         <v>1.5</v>
       </c>
       <c r="G1999" t="n">
-        <v>0.919979512691498</v>
+        <v>0.919979572296143</v>
       </c>
       <c r="H1999" t="s">
         <v>8</v>
@@ -52369,7 +52369,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G2000" t="n">
-        <v>0.950645625591278</v>
+        <v>0.950645565986633</v>
       </c>
       <c r="H2000" t="s">
         <v>8</v>
@@ -52395,7 +52395,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G2001" t="n">
-        <v>0.950645625591278</v>
+        <v>0.950645565986633</v>
       </c>
       <c r="H2001" t="s">
         <v>8</v>
@@ -52421,7 +52421,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G2002" t="n">
-        <v>0.953098893165588</v>
+        <v>0.953098833560944</v>
       </c>
       <c r="H2002" t="s">
         <v>8</v>
@@ -52473,7 +52473,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G2004" t="n">
-        <v>1.01075100898743</v>
+        <v>1.01075088977814</v>
       </c>
       <c r="H2004" t="s">
         <v>8</v>
@@ -52499,7 +52499,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G2005" t="n">
-        <v>0.999711155891418</v>
+        <v>0.999711215496063</v>
       </c>
       <c r="H2005" t="s">
         <v>8</v>
@@ -52525,7 +52525,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G2006" t="n">
-        <v>0.999711155891418</v>
+        <v>0.999711215496063</v>
       </c>
       <c r="H2006" t="s">
         <v>8</v>
@@ -52577,7 +52577,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G2008" t="n">
-        <v>1.00461781024933</v>
+        <v>1.00461769104004</v>
       </c>
       <c r="H2008" t="s">
         <v>8</v>
@@ -52629,7 +52629,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2010" t="n">
-        <v>0.993577897548676</v>
+        <v>0.99357795715332</v>
       </c>
       <c r="H2010" t="s">
         <v>8</v>
@@ -52681,7 +52681,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G2012" t="n">
-        <v>0.983764886856079</v>
+        <v>0.98376476764679</v>
       </c>
       <c r="H2012" t="s">
         <v>8</v>
@@ -52733,7 +52733,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G2014" t="n">
-        <v>0.983764886856079</v>
+        <v>0.98376476764679</v>
       </c>
       <c r="H2014" t="s">
         <v>8</v>
@@ -52785,7 +52785,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G2016" t="n">
-        <v>0.988671362400055</v>
+        <v>0.9886714220047</v>
       </c>
       <c r="H2016" t="s">
         <v>8</v>
@@ -52993,7 +52993,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G2024" t="n">
-        <v>1.1334148645401</v>
+        <v>1.13341498374939</v>
       </c>
       <c r="H2024" t="s">
         <v>8</v>
@@ -53019,7 +53019,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G2025" t="n">
-        <v>1.14813458919525</v>
+        <v>1.14813446998596</v>
       </c>
       <c r="H2025" t="s">
         <v>8</v>
@@ -53331,7 +53331,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G2037" t="n">
-        <v>1.22970604896545</v>
+        <v>1.22970616817474</v>
       </c>
       <c r="H2037" t="s">
         <v>8</v>
@@ -53435,7 +53435,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2041" t="n">
-        <v>1.17757391929626</v>
+        <v>1.17757380008698</v>
       </c>
       <c r="H2041" t="s">
         <v>8</v>
@@ -53513,7 +53513,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G2044" t="n">
-        <v>1.22173297405243</v>
+        <v>1.22173285484314</v>
       </c>
       <c r="H2044" t="s">
         <v>8</v>
@@ -53539,7 +53539,7 @@
         <v>2</v>
       </c>
       <c r="G2045" t="n">
-        <v>1.22663938999176</v>
+        <v>1.22663950920105</v>
       </c>
       <c r="H2045" t="s">
         <v>8</v>
@@ -53565,7 +53565,7 @@
         <v>2</v>
       </c>
       <c r="G2046" t="n">
-        <v>1.22663938999176</v>
+        <v>1.22663950920105</v>
       </c>
       <c r="H2046" t="s">
         <v>8</v>
@@ -53643,7 +53643,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2049" t="n">
-        <v>1.18370699882507</v>
+        <v>1.18370711803436</v>
       </c>
       <c r="H2049" t="s">
         <v>8</v>
@@ -53669,7 +53669,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G2050" t="n">
-        <v>1.14322793483734</v>
+        <v>1.14322805404663</v>
       </c>
       <c r="H2050" t="s">
         <v>8</v>
@@ -53721,7 +53721,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G2052" t="n">
-        <v>1.14445471763611</v>
+        <v>1.14445459842682</v>
       </c>
       <c r="H2052" t="s">
         <v>8</v>
@@ -53903,7 +53903,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2059" t="n">
-        <v>1.13464140892029</v>
+        <v>1.13464152812958</v>
       </c>
       <c r="H2059" t="s">
         <v>8</v>
@@ -53929,7 +53929,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G2060" t="n">
-        <v>1.1027489900589</v>
+        <v>1.10274887084961</v>
       </c>
       <c r="H2060" t="s">
         <v>8</v>
@@ -53955,7 +53955,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2061" t="n">
-        <v>1.13464140892029</v>
+        <v>1.13464152812958</v>
       </c>
       <c r="H2061" t="s">
         <v>8</v>
@@ -54085,7 +54085,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G2066" t="n">
-        <v>1.1579475402832</v>
+        <v>1.15794765949249</v>
       </c>
       <c r="H2066" t="s">
         <v>8</v>
@@ -54111,7 +54111,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2067" t="n">
-        <v>1.16530740261078</v>
+        <v>1.16530752182007</v>
       </c>
       <c r="H2067" t="s">
         <v>8</v>
@@ -54293,7 +54293,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G2074" t="n">
-        <v>1.22173297405243</v>
+        <v>1.22173285484314</v>
       </c>
       <c r="H2074" t="s">
         <v>8</v>
@@ -54319,7 +54319,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2075" t="n">
-        <v>1.25730538368225</v>
+        <v>1.25730550289154</v>
       </c>
       <c r="H2075" t="s">
         <v>8</v>
@@ -54371,7 +54371,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G2077" t="n">
-        <v>1.71729516983032</v>
+        <v>1.71729528903961</v>
       </c>
       <c r="H2077" t="s">
         <v>8</v>
@@ -54397,7 +54397,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G2078" t="n">
-        <v>1.8184928894043</v>
+        <v>1.81849300861359</v>
       </c>
       <c r="H2078" t="s">
         <v>8</v>
@@ -54423,7 +54423,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2079" t="n">
-        <v>1.94422376155853</v>
+        <v>1.94422364234924</v>
       </c>
       <c r="H2079" t="s">
         <v>8</v>
@@ -54449,7 +54449,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G2080" t="n">
-        <v>1.89822459220886</v>
+        <v>1.89822471141815</v>
       </c>
       <c r="H2080" t="s">
         <v>8</v>
@@ -54475,7 +54475,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G2081" t="n">
-        <v>1.87675857543945</v>
+        <v>1.87675833702087</v>
       </c>
       <c r="H2081" t="s">
         <v>8</v>
@@ -54527,7 +54527,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G2083" t="n">
-        <v>1.83075928688049</v>
+        <v>1.83075940608978</v>
       </c>
       <c r="H2083" t="s">
         <v>8</v>
@@ -54605,7 +54605,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G2086" t="n">
-        <v>1.74489462375641</v>
+        <v>1.7448947429657</v>
       </c>
       <c r="H2086" t="s">
         <v>8</v>
@@ -54631,7 +54631,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G2087" t="n">
-        <v>1.84302580356598</v>
+        <v>1.84302592277527</v>
       </c>
       <c r="H2087" t="s">
         <v>8</v>
@@ -54657,7 +54657,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G2088" t="n">
-        <v>1.83689248561859</v>
+        <v>1.83689260482788</v>
       </c>
       <c r="H2088" t="s">
         <v>8</v>
@@ -54683,7 +54683,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2089" t="n">
-        <v>1.90129125118256</v>
+        <v>1.90129113197327</v>
       </c>
       <c r="H2089" t="s">
         <v>8</v>
@@ -54709,7 +54709,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2090" t="n">
-        <v>1.90129125118256</v>
+        <v>1.90129113197327</v>
       </c>
       <c r="H2090" t="s">
         <v>8</v>
@@ -54735,7 +54735,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2091" t="n">
-        <v>1.91355752944946</v>
+        <v>1.91355764865875</v>
       </c>
       <c r="H2091" t="s">
         <v>8</v>
@@ -54865,7 +54865,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G2096" t="n">
-        <v>1.92889046669006</v>
+        <v>1.92889034748077</v>
       </c>
       <c r="H2096" t="s">
         <v>8</v>
@@ -54891,7 +54891,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2097" t="n">
-        <v>1.99942231178284</v>
+        <v>1.99942243099213</v>
       </c>
       <c r="H2097" t="s">
         <v>8</v>
@@ -54943,7 +54943,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G2099" t="n">
-        <v>1.95955646038055</v>
+        <v>1.95955657958984</v>
       </c>
       <c r="H2099" t="s">
         <v>8</v>
@@ -55021,7 +55021,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2102" t="n">
-        <v>1.93809044361115</v>
+        <v>1.93809020519257</v>
       </c>
       <c r="H2102" t="s">
         <v>8</v>
@@ -55125,7 +55125,7 @@
         <v>3.25</v>
       </c>
       <c r="G2106" t="n">
-        <v>1.99328911304474</v>
+        <v>1.99328923225403</v>
       </c>
       <c r="H2106" t="s">
         <v>8</v>
@@ -55177,7 +55177,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G2108" t="n">
-        <v>1.95342314243317</v>
+        <v>1.95342326164246</v>
       </c>
       <c r="H2108" t="s">
         <v>8</v>
@@ -55203,7 +55203,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G2109" t="n">
-        <v>1.95342314243317</v>
+        <v>1.95342326164246</v>
       </c>
       <c r="H2109" t="s">
         <v>8</v>
@@ -55229,7 +55229,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G2110" t="n">
-        <v>1.92889046669006</v>
+        <v>1.92889034748077</v>
       </c>
       <c r="H2110" t="s">
         <v>8</v>
@@ -55385,7 +55385,7 @@
         <v>3</v>
       </c>
       <c r="G2116" t="n">
-        <v>1.839959025383</v>
+        <v>1.83995914459229</v>
       </c>
       <c r="H2116" t="s">
         <v>8</v>
@@ -55489,7 +55489,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G2120" t="n">
-        <v>1.76942729949951</v>
+        <v>1.76942753791809</v>
       </c>
       <c r="H2120" t="s">
         <v>8</v>
@@ -55541,7 +55541,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G2122" t="n">
-        <v>1.8184928894043</v>
+        <v>1.81849300861359</v>
       </c>
       <c r="H2122" t="s">
         <v>8</v>
@@ -55593,7 +55593,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G2124" t="n">
-        <v>2.01250958442688</v>
+        <v>2.0125093460083</v>
       </c>
       <c r="H2124" t="s">
         <v>8</v>
@@ -55619,7 +55619,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G2125" t="n">
-        <v>1.96318304538727</v>
+        <v>1.96318316459656</v>
       </c>
       <c r="H2125" t="s">
         <v>8</v>
@@ -55671,7 +55671,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G2127" t="n">
-        <v>1.79218566417694</v>
+        <v>1.79218554496765</v>
       </c>
       <c r="H2127" t="s">
         <v>8</v>
@@ -55801,7 +55801,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G2132" t="n">
-        <v>1.8316468000412</v>
+        <v>1.83164668083191</v>
       </c>
       <c r="H2132" t="s">
         <v>8</v>
@@ -55879,7 +55879,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G2135" t="n">
-        <v>1.79218566417694</v>
+        <v>1.79218554496765</v>
       </c>
       <c r="H2135" t="s">
         <v>8</v>
@@ -55905,7 +55905,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G2136" t="n">
-        <v>1.79218566417694</v>
+        <v>1.79218554496765</v>
       </c>
       <c r="H2136" t="s">
         <v>8</v>
@@ -55957,7 +55957,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G2138" t="n">
-        <v>1.95660638809204</v>
+        <v>1.95660626888275</v>
       </c>
       <c r="H2138" t="s">
         <v>8</v>
@@ -55983,7 +55983,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G2139" t="n">
-        <v>1.95002949237823</v>
+        <v>1.95002961158752</v>
       </c>
       <c r="H2139" t="s">
         <v>8</v>
@@ -56009,7 +56009,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G2140" t="n">
-        <v>1.92043375968933</v>
+        <v>1.92043387889862</v>
       </c>
       <c r="H2140" t="s">
         <v>8</v>
@@ -56035,7 +56035,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G2141" t="n">
-        <v>1.93358743190765</v>
+        <v>1.93358755111694</v>
       </c>
       <c r="H2141" t="s">
         <v>8</v>
@@ -56061,7 +56061,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G2142" t="n">
-        <v>1.92372214794159</v>
+        <v>1.92372226715088</v>
       </c>
       <c r="H2142" t="s">
         <v>8</v>
@@ -56113,7 +56113,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G2144" t="n">
-        <v>1.9072802066803</v>
+        <v>1.90728032588959</v>
       </c>
       <c r="H2144" t="s">
         <v>8</v>
@@ -56165,7 +56165,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G2146" t="n">
-        <v>1.9138571023941</v>
+        <v>1.91385698318481</v>
       </c>
       <c r="H2146" t="s">
         <v>8</v>
@@ -56191,7 +56191,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G2147" t="n">
-        <v>1.91056847572327</v>
+        <v>1.91056859493256</v>
       </c>
       <c r="H2147" t="s">
         <v>8</v>
@@ -56217,7 +56217,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G2148" t="n">
-        <v>1.91056847572327</v>
+        <v>1.91056859493256</v>
       </c>
       <c r="H2148" t="s">
         <v>8</v>
@@ -56243,7 +56243,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G2149" t="n">
-        <v>1.91714549064636</v>
+        <v>1.91714537143707</v>
       </c>
       <c r="H2149" t="s">
         <v>8</v>
@@ -56295,7 +56295,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G2151" t="n">
-        <v>1.87110757827759</v>
+        <v>1.87110769748688</v>
       </c>
       <c r="H2151" t="s">
         <v>8</v>
@@ -56373,7 +56373,7 @@
         <v>3</v>
       </c>
       <c r="G2154" t="n">
-        <v>1.97304832935333</v>
+        <v>1.97304844856262</v>
       </c>
       <c r="H2154" t="s">
         <v>8</v>
@@ -56607,7 +56607,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2163" t="n">
-        <v>2.22296810150146</v>
+        <v>2.22296786308289</v>
       </c>
       <c r="H2163" t="s">
         <v>8</v>
@@ -56633,7 +56633,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G2164" t="n">
-        <v>2.17693018913269</v>
+        <v>2.17692995071411</v>
       </c>
       <c r="H2164" t="s">
         <v>8</v>
@@ -56659,7 +56659,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G2165" t="n">
-        <v>2.20981407165527</v>
+        <v>2.20981431007385</v>
       </c>
       <c r="H2165" t="s">
         <v>8</v>
@@ -56685,7 +56685,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2166" t="n">
-        <v>2.22296810150146</v>
+        <v>2.22296786308289</v>
       </c>
       <c r="H2166" t="s">
         <v>8</v>
@@ -56763,7 +56763,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G2169" t="n">
-        <v>2.17693018913269</v>
+        <v>2.17692995071411</v>
       </c>
       <c r="H2169" t="s">
         <v>8</v>
@@ -71288,7 +71288,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="D2728" t="n">
-        <v>2.02999997138977</v>
+        <v>2.01999998092651</v>
       </c>
       <c r="E2728" t="n">
         <v>2.05999994277954</v>
@@ -71300,6 +71300,32 @@
         <v>2.01999998092651</v>
       </c>
       <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>175893</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>2.02999997138977</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>2.04500007629395</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>2.04500007629395</v>
+      </c>
+      <c r="H2729" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SGF.MI.xlsx
+++ b/data/SGF.MI.xlsx
@@ -447,7 +447,7 @@
         <v>2.00399994850159</v>
       </c>
       <c r="G3" t="n">
-        <v>1.22909271717072</v>
+        <v>1.22909259796143</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>1.91299998760223</v>
       </c>
       <c r="G6" t="n">
-        <v>1.17328059673309</v>
+        <v>1.17328071594238</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G8" t="n">
-        <v>1.17389392852783</v>
+        <v>1.17389404773712</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G9" t="n">
-        <v>1.15058779716492</v>
+        <v>1.15058791637421</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G12" t="n">
-        <v>1.05613648891449</v>
+        <v>1.05613660812378</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G13" t="n">
-        <v>1.09293580055237</v>
+        <v>1.09293568134308</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>1.00891089439392</v>
+        <v>1.00891101360321</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>1.75699996948242</v>
       </c>
       <c r="G19" t="n">
-        <v>1.07760286331177</v>
+        <v>1.07760274410248</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G21" t="n">
-        <v>1.05613648891449</v>
+        <v>1.05613660812378</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>1.72800004482269</v>
       </c>
       <c r="G22" t="n">
-        <v>1.05981647968292</v>
+        <v>1.05981659889221</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G24" t="n">
-        <v>1.01075088977814</v>
+        <v>1.01075100898743</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G31" t="n">
-        <v>0.916913032531738</v>
+        <v>0.916912972927094</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G32" t="n">
-        <v>0.981311619281769</v>
+        <v>0.981311559677124</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G33" t="n">
-        <v>0.950645565986633</v>
+        <v>0.950645625591278</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>1.56099998950958</v>
       </c>
       <c r="G34" t="n">
-        <v>0.957392156124115</v>
+        <v>0.95739209651947</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G35" t="n">
-        <v>0.941445827484131</v>
+        <v>0.941445767879486</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>1.50399994850159</v>
       </c>
       <c r="G36" t="n">
-        <v>0.922432899475098</v>
+        <v>0.922432839870453</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G37" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G38" t="n">
-        <v>0.941445827484131</v>
+        <v>0.941445767879486</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G39" t="n">
-        <v>0.924886167049408</v>
+        <v>0.924886226654053</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G40" t="n">
-        <v>0.910166442394257</v>
+        <v>0.910166501998901</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>1.52699995040894</v>
       </c>
       <c r="G41" t="n">
-        <v>0.936539173126221</v>
+        <v>0.93653929233551</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G42" t="n">
-        <v>0.872140765190125</v>
+        <v>0.872140645980835</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>1.5</v>
       </c>
       <c r="G43" t="n">
-        <v>0.919979631900787</v>
+        <v>0.919979512691498</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>1.5789999961853</v>
       </c>
       <c r="G44" t="n">
-        <v>0.968431770801544</v>
+        <v>0.968431890010834</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G45" t="n">
-        <v>1.0426436662674</v>
+        <v>1.04264354705811</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G48" t="n">
-        <v>1.0040043592453</v>
+        <v>1.00400447845459</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G49" t="n">
-        <v>1.00891089439392</v>
+        <v>1.00891101360321</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>1.54700005054474</v>
       </c>
       <c r="G50" t="n">
-        <v>0.948805689811707</v>
+        <v>0.948805630207062</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G51" t="n">
-        <v>0.986218214035034</v>
+        <v>0.986218154430389</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G53" t="n">
-        <v>0.960458695888519</v>
+        <v>0.960458636283875</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>1.58299994468689</v>
       </c>
       <c r="G54" t="n">
-        <v>0.970885157585144</v>
+        <v>0.970885097980499</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G57" t="n">
-        <v>0.926112830638885</v>
+        <v>0.92611289024353</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>1.5</v>
       </c>
       <c r="G58" t="n">
-        <v>0.919979631900787</v>
+        <v>0.919979512691498</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>1.4210000038147</v>
       </c>
       <c r="G59" t="n">
-        <v>0.871527373790741</v>
+        <v>0.871527314186096</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>1.34300005435944</v>
       </c>
       <c r="G61" t="n">
-        <v>0.823688387870789</v>
+        <v>0.823688447475433</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G63" t="n">
-        <v>0.86723405122757</v>
+        <v>0.867234110832214</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>1.34599995613098</v>
       </c>
       <c r="G65" t="n">
-        <v>0.825528383255005</v>
+        <v>0.82552832365036</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G66" t="n">
-        <v>0.815715312957764</v>
+        <v>0.815715253353119</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G67" t="n">
-        <v>0.818781912326813</v>
+        <v>0.818781852722168</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G68" t="n">
-        <v>0.79424911737442</v>
+        <v>0.794249057769775</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G70" t="n">
-        <v>0.849447846412659</v>
+        <v>0.849447786808014</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>1.43299996852875</v>
       </c>
       <c r="G73" t="n">
-        <v>0.878887116909027</v>
+        <v>0.878887236118317</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G75" t="n">
-        <v>0.895446836948395</v>
+        <v>0.89544677734375</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G76" t="n">
-        <v>0.852514445781708</v>
+        <v>0.852514386177063</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>1.43099999427795</v>
       </c>
       <c r="G77" t="n">
-        <v>0.877660512924194</v>
+        <v>0.877660572528839</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G78" t="n">
-        <v>0.875207245349884</v>
+        <v>0.875207364559174</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>1.42299997806549</v>
       </c>
       <c r="G79" t="n">
-        <v>0.872754037380219</v>
+        <v>0.872753977775574</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G80" t="n">
-        <v>0.872140765190125</v>
+        <v>0.872140645980835</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>1.5</v>
       </c>
       <c r="G82" t="n">
-        <v>0.919979631900787</v>
+        <v>0.919979512691498</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G83" t="n">
-        <v>0.943285703659058</v>
+        <v>0.943285763263702</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G84" t="n">
-        <v>0.977631628513336</v>
+        <v>0.977631688117981</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G85" t="n">
-        <v>0.99357795715332</v>
+        <v>0.993577897548676</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G86" t="n">
-        <v>0.951258897781372</v>
+        <v>0.951258957386017</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G87" t="n">
-        <v>0.951258897781372</v>
+        <v>0.951258957386017</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G88" t="n">
-        <v>0.951258897781372</v>
+        <v>0.951258957386017</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G89" t="n">
-        <v>0.951258897781372</v>
+        <v>0.951258957386017</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>1.50100004673004</v>
       </c>
       <c r="G90" t="n">
-        <v>0.920592904090881</v>
+        <v>0.920592963695526</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G91" t="n">
-        <v>0.938379228115082</v>
+        <v>0.938379287719727</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>1.54700005054474</v>
       </c>
       <c r="G92" t="n">
-        <v>0.948805689811707</v>
+        <v>0.948805630207062</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G93" t="n">
-        <v>0.978244960308075</v>
+        <v>0.97824501991272</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G94" t="n">
-        <v>0.992351412773132</v>
+        <v>0.992351353168488</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G98" t="n">
-        <v>0.943285703659058</v>
+        <v>0.943285763263702</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G100" t="n">
-        <v>0.927339375019073</v>
+        <v>0.927339434623718</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G101" t="n">
-        <v>0.953712165355682</v>
+        <v>0.953712105751038</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G102" t="n">
-        <v>1.02424395084381</v>
+        <v>1.02424383163452</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G103" t="n">
-        <v>1.09170913696289</v>
+        <v>1.0917090177536</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G105" t="n">
-        <v>1.12360167503357</v>
+        <v>1.12360179424286</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G107" t="n">
-        <v>1.0426436662674</v>
+        <v>1.04264354705811</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G108" t="n">
-        <v>1.03037714958191</v>
+        <v>1.03037703037262</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G111" t="n">
-        <v>1.0070708990097</v>
+        <v>1.00707101821899</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>1.39300000667572</v>
       </c>
       <c r="G115" t="n">
-        <v>0.854354441165924</v>
+        <v>0.854354381561279</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>1.36899995803833</v>
       </c>
       <c r="G120" t="n">
-        <v>0.839634656906128</v>
+        <v>0.839634716510773</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G122" t="n">
-        <v>0.875207245349884</v>
+        <v>0.875207364559174</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>1.24800002574921</v>
       </c>
       <c r="G125" t="n">
-        <v>0.765423059463501</v>
+        <v>0.765422999858856</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>1.30900001525879</v>
       </c>
       <c r="G129" t="n">
-        <v>0.802835583686829</v>
+        <v>0.802835524082184</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G131" t="n">
-        <v>0.725557208061218</v>
+        <v>0.725557267665863</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G137" t="n">
-        <v>0.803448855876923</v>
+        <v>0.803448796272278</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G141" t="n">
-        <v>0.851287841796875</v>
+        <v>0.85128778219223</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G146" t="n">
-        <v>0.884407103061676</v>
+        <v>0.884407043457031</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G149" t="n">
-        <v>0.932245969772339</v>
+        <v>0.932246029376984</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G151" t="n">
-        <v>0.907713294029236</v>
+        <v>0.907713174819946</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G156" t="n">
-        <v>1.0070708990097</v>
+        <v>1.00707101821899</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G158" t="n">
-        <v>1.02424395084381</v>
+        <v>1.02424383163452</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G159" t="n">
-        <v>1.01749753952026</v>
+        <v>1.01749742031097</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G160" t="n">
-        <v>1.03344368934631</v>
+        <v>1.0334438085556</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G167" t="n">
-        <v>1.0273106098175</v>
+        <v>1.02731049060822</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G168" t="n">
-        <v>1.03405702114105</v>
+        <v>1.03405714035034</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G172" t="n">
-        <v>1.02363073825836</v>
+        <v>1.02363061904907</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>1.75800001621246</v>
       </c>
       <c r="G174" t="n">
-        <v>1.07821607589722</v>
+        <v>1.07821619510651</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G176" t="n">
-        <v>1.09170913696289</v>
+        <v>1.0917090177536</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>1.77699995040894</v>
       </c>
       <c r="G177" t="n">
-        <v>1.08986914157867</v>
+        <v>1.08986902236938</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G179" t="n">
-        <v>1.0825092792511</v>
+        <v>1.08250939846039</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>1.73699998855591</v>
       </c>
       <c r="G180" t="n">
-        <v>1.06533634662628</v>
+        <v>1.06533622741699</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G181" t="n">
-        <v>1.06472301483154</v>
+        <v>1.06472289562225</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G182" t="n">
-        <v>1.06410980224609</v>
+        <v>1.0641096830368</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>1.64600002765656</v>
       </c>
       <c r="G183" t="n">
-        <v>1.00952422618866</v>
+        <v>1.00952434539795</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>1.68900001049042</v>
       </c>
       <c r="G185" t="n">
-        <v>1.03589701652527</v>
+        <v>1.03589713573456</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G186" t="n">
-        <v>1.0671763420105</v>
+        <v>1.06717622280121</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G189" t="n">
-        <v>1.09170913696289</v>
+        <v>1.0917090177536</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G191" t="n">
-        <v>1.1101086139679</v>
+        <v>1.11010873317719</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G192" t="n">
-        <v>1.1039754152298</v>
+        <v>1.10397553443909</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G193" t="n">
-        <v>1.1039754152298</v>
+        <v>1.10397553443909</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G194" t="n">
-        <v>1.09170913696289</v>
+        <v>1.0917090177536</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G195" t="n">
-        <v>1.09416246414185</v>
+        <v>1.09416234493256</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G197" t="n">
-        <v>1.1039754152298</v>
+        <v>1.10397553443909</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G198" t="n">
-        <v>1.09784233570099</v>
+        <v>1.0978422164917</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G199" t="n">
-        <v>1.10152232646942</v>
+        <v>1.10152220726013</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>1.09784233570099</v>
+        <v>1.0978422164917</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>1.79100000858307</v>
       </c>
       <c r="G201" t="n">
-        <v>1.09845566749573</v>
+        <v>1.09845554828644</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>1.79100000858307</v>
       </c>
       <c r="G205" t="n">
-        <v>1.09845566749573</v>
+        <v>1.09845554828644</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G207" t="n">
-        <v>1.10274887084961</v>
+        <v>1.1027489900589</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G208" t="n">
-        <v>1.10152232646942</v>
+        <v>1.10152220726013</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G210" t="n">
-        <v>1.18370711803436</v>
+        <v>1.18370699882507</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G211" t="n">
-        <v>1.23890578746796</v>
+        <v>1.23890590667725</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G213" t="n">
-        <v>1.23277270793915</v>
+        <v>1.23277258872986</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G215" t="n">
-        <v>1.26343870162964</v>
+        <v>1.26343858242035</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G216" t="n">
-        <v>1.22050619125366</v>
+        <v>1.22050631046295</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G218" t="n">
-        <v>1.26466536521912</v>
+        <v>1.26466524600983</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G220" t="n">
-        <v>1.24503898620605</v>
+        <v>1.24503910541534</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G225" t="n">
-        <v>1.31495749950409</v>
+        <v>1.31495761871338</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G229" t="n">
-        <v>1.33090376853943</v>
+        <v>1.33090388774872</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G232" t="n">
-        <v>1.30023777484894</v>
+        <v>1.30023765563965</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G233" t="n">
-        <v>1.29901123046875</v>
+        <v>1.29901111125946</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.09200000762939</v>
       </c>
       <c r="G238" t="n">
-        <v>1.28306496143341</v>
+        <v>1.28306484222412</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G240" t="n">
-        <v>1.30023777484894</v>
+        <v>1.30023765563965</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G245" t="n">
-        <v>1.47687387466431</v>
+        <v>1.4768739938736</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G247" t="n">
-        <v>1.45970106124878</v>
+        <v>1.45970094203949</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G251" t="n">
-        <v>1.50263345241547</v>
+        <v>1.50263333320618</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G252" t="n">
-        <v>1.49650025367737</v>
+        <v>1.49650013446808</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G254" t="n">
-        <v>1.47687387466431</v>
+        <v>1.4768739938736</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G255" t="n">
-        <v>1.447434425354</v>
+        <v>1.44743454456329</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G256" t="n">
-        <v>1.47810053825378</v>
+        <v>1.47810065746307</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G259" t="n">
-        <v>1.57991170883179</v>
+        <v>1.5799115896225</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G263" t="n">
-        <v>1.53943240642548</v>
+        <v>1.53943252563477</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G264" t="n">
-        <v>1.57377851009369</v>
+        <v>1.5737783908844</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G266" t="n">
-        <v>1.55169880390167</v>
+        <v>1.55169904232025</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G268" t="n">
-        <v>1.57868480682373</v>
+        <v>1.57868492603302</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G271" t="n">
-        <v>1.52593958377838</v>
+        <v>1.52593946456909</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G272" t="n">
-        <v>1.51367318630219</v>
+        <v>1.5136730670929</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G274" t="n">
-        <v>1.530846118927</v>
+        <v>1.53084599971771</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G276" t="n">
-        <v>1.52593958377838</v>
+        <v>1.52593946456909</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G277" t="n">
-        <v>1.47687387466431</v>
+        <v>1.4768739938736</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G280" t="n">
-        <v>1.41676867008209</v>
+        <v>1.4167685508728</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G284" t="n">
-        <v>1.27079844474792</v>
+        <v>1.27079856395721</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.12400007247925</v>
       </c>
       <c r="G287" t="n">
-        <v>1.30269122123718</v>
+        <v>1.30269110202789</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G297" t="n">
-        <v>1.39591574668884</v>
+        <v>1.39591562747955</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.67199993133545</v>
       </c>
       <c r="G299" t="n">
-        <v>1.63879036903381</v>
+        <v>1.63879024982452</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G305" t="n">
-        <v>1.79825341701508</v>
+        <v>1.79825329780579</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G306" t="n">
-        <v>1.75409436225891</v>
+        <v>1.7540944814682</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G307" t="n">
-        <v>1.79089367389679</v>
+        <v>1.7908935546875</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G308" t="n">
-        <v>1.77740061283112</v>
+        <v>1.77740049362183</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G310" t="n">
-        <v>1.79089367389679</v>
+        <v>1.7908935546875</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G311" t="n">
-        <v>1.80316007137299</v>
+        <v>1.8031599521637</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G312" t="n">
-        <v>1.82523953914642</v>
+        <v>1.82523965835571</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G313" t="n">
-        <v>1.95526325702667</v>
+        <v>1.95526337623596</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G314" t="n">
-        <v>1.9356369972229</v>
+        <v>1.93563711643219</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G316" t="n">
-        <v>2.08528733253479</v>
+        <v>2.08528709411621</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G317" t="n">
-        <v>2.152752161026</v>
+        <v>2.15275239944458</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.60199999809265</v>
       </c>
       <c r="G318" t="n">
-        <v>2.20917773246765</v>
+        <v>2.20917797088623</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>3.75</v>
       </c>
       <c r="G319" t="n">
-        <v>2.29994893074036</v>
+        <v>2.29994916915894</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G322" t="n">
-        <v>2.26805639266968</v>
+        <v>2.2680561542511</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G326" t="n">
-        <v>2.2484302520752</v>
+        <v>2.24843001365662</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G328" t="n">
-        <v>2.2484302520752</v>
+        <v>2.24843001365662</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G331" t="n">
-        <v>2.26805639266968</v>
+        <v>2.2680561542511</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G333" t="n">
-        <v>2.28277587890625</v>
+        <v>2.28277611732483</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G334" t="n">
-        <v>2.33920121192932</v>
+        <v>2.3392014503479</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G336" t="n">
-        <v>2.44101238250732</v>
+        <v>2.4410126209259</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.71799993515015</v>
       </c>
       <c r="G340" t="n">
-        <v>2.89364218711853</v>
+        <v>2.89364242553711</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G343" t="n">
-        <v>2.76607203483582</v>
+        <v>2.76607227325439</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G344" t="n">
-        <v>2.72927260398865</v>
+        <v>2.72927284240723</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G347" t="n">
-        <v>2.93780159950256</v>
+        <v>2.93780136108398</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G348" t="n">
-        <v>2.88996243476868</v>
+        <v>2.88996267318726</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>4.72399997711182</v>
       </c>
       <c r="G351" t="n">
-        <v>2.89732265472412</v>
+        <v>2.89732241630554</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G353" t="n">
-        <v>2.79796457290649</v>
+        <v>2.79796433448792</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G354" t="n">
-        <v>2.99300050735474</v>
+        <v>2.99300026893616</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>5.08500003814697</v>
       </c>
       <c r="G356" t="n">
-        <v>3.11873078346252</v>
+        <v>3.1187310218811</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G358" t="n">
-        <v>3.21379542350769</v>
+        <v>3.21379518508911</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G361" t="n">
-        <v>3.18619608879089</v>
+        <v>3.18619585037231</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>5.125</v>
       </c>
       <c r="G363" t="n">
-        <v>3.1432638168335</v>
+        <v>3.14326357841492</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G365" t="n">
-        <v>3.18926239013672</v>
+        <v>3.1892626285553</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G370" t="n">
-        <v>2.99300050735474</v>
+        <v>2.99300026893616</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G371" t="n">
-        <v>3.21072864532471</v>
+        <v>3.21072888374329</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G373" t="n">
-        <v>3.03470587730408</v>
+        <v>3.03470611572266</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>3.2321949005127</v>
+        <v>3.23219513893127</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G380" t="n">
-        <v>3.18312931060791</v>
+        <v>3.18312954902649</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G383" t="n">
-        <v>2.92553520202637</v>
+        <v>2.92553496360779</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>4.5</v>
       </c>
       <c r="G386" t="n">
-        <v>2.75993871688843</v>
+        <v>2.75993895530701</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.50600004196167</v>
       </c>
       <c r="G390" t="n">
-        <v>2.76361870765686</v>
+        <v>2.76361894607544</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>4.72399997711182</v>
       </c>
       <c r="G391" t="n">
-        <v>2.89732265472412</v>
+        <v>2.89732241630554</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>4.71799993515015</v>
       </c>
       <c r="G392" t="n">
-        <v>2.89364218711853</v>
+        <v>2.89364242553711</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>4.71799993515015</v>
       </c>
       <c r="G393" t="n">
-        <v>2.89364218711853</v>
+        <v>2.89364242553711</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.69199991226196</v>
       </c>
       <c r="G394" t="n">
-        <v>2.8776957988739</v>
+        <v>2.87769603729248</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G395" t="n">
-        <v>2.91081523895264</v>
+        <v>2.91081547737122</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>4.62599992752075</v>
       </c>
       <c r="G397" t="n">
-        <v>2.83721733093262</v>
+        <v>2.83721709251404</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>4.51599979400635</v>
       </c>
       <c r="G398" t="n">
-        <v>2.76975154876709</v>
+        <v>2.76975178718567</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G401" t="n">
-        <v>2.62746167182922</v>
+        <v>2.6274619102478</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>4.47800016403198</v>
       </c>
       <c r="G402" t="n">
-        <v>2.74644589424133</v>
+        <v>2.74644565582275</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G403" t="n">
-        <v>2.69492721557617</v>
+        <v>2.69492697715759</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G405" t="n">
-        <v>2.62500858306885</v>
+        <v>2.62500882148743</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>4.2480001449585</v>
       </c>
       <c r="G406" t="n">
-        <v>2.60538244247437</v>
+        <v>2.60538220405579</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.27400016784668</v>
       </c>
       <c r="G412" t="n">
-        <v>2.62132859230042</v>
+        <v>2.62132883071899</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>4.64799976348877</v>
       </c>
       <c r="G413" t="n">
-        <v>2.85071015357971</v>
+        <v>2.85070991516113</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>4.55800008773804</v>
       </c>
       <c r="G415" t="n">
-        <v>2.79551148414612</v>
+        <v>2.79551124572754</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G419" t="n">
-        <v>2.77588510513306</v>
+        <v>2.77588534355164</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>4.41800022125244</v>
       </c>
       <c r="G422" t="n">
-        <v>2.70964646339417</v>
+        <v>2.70964670181274</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G424" t="n">
-        <v>2.66794085502625</v>
+        <v>2.66794061660767</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G428" t="n">
-        <v>2.62991499900818</v>
+        <v>2.62991523742676</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.62200021743774</v>
       </c>
       <c r="G433" t="n">
-        <v>2.83476424217224</v>
+        <v>2.83476400375366</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G434" t="n">
-        <v>3.05065226554871</v>
+        <v>3.05065250396729</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G438" t="n">
-        <v>3.0727322101593</v>
+        <v>3.07273197174072</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G439" t="n">
-        <v>3.17086291313171</v>
+        <v>3.17086315155029</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>5.06500005722046</v>
       </c>
       <c r="G445" t="n">
-        <v>3.10646462440491</v>
+        <v>3.10646438598633</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G446" t="n">
-        <v>3.17699646949768</v>
+        <v>3.1769962310791</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>3.15553021430969</v>
+        <v>3.15552997589111</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G450" t="n">
-        <v>3.12486386299133</v>
+        <v>3.12486410140991</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G451" t="n">
-        <v>3.12486386299133</v>
+        <v>3.12486410140991</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>4.95599985122681</v>
       </c>
       <c r="G453" t="n">
-        <v>3.03961277008057</v>
+        <v>3.03961253166199</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>4.93800020217896</v>
       </c>
       <c r="G456" t="n">
-        <v>3.02857279777527</v>
+        <v>3.02857303619385</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G457" t="n">
-        <v>2.99300050735474</v>
+        <v>2.99300026893616</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>4.80600023269653</v>
       </c>
       <c r="G460" t="n">
-        <v>2.94761490821838</v>
+        <v>2.9476146697998</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>4.63199996948242</v>
       </c>
       <c r="G462" t="n">
-        <v>2.84089684486389</v>
+        <v>2.84089708328247</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G464" t="n">
-        <v>2.90100264549255</v>
+        <v>2.90100240707397</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G466" t="n">
-        <v>2.67407393455505</v>
+        <v>2.67407417297363</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G467" t="n">
-        <v>2.65567445755005</v>
+        <v>2.65567421913147</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G468" t="n">
-        <v>2.56490302085876</v>
+        <v>2.56490325927734</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G472" t="n">
-        <v>2.67407393455505</v>
+        <v>2.67407417297363</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G476" t="n">
-        <v>2.47781157493591</v>
+        <v>2.47781181335449</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G481" t="n">
-        <v>2.26805639266968</v>
+        <v>2.2680561542511</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G482" t="n">
-        <v>2.34165477752686</v>
+        <v>2.34165501594543</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>3.86400008201599</v>
       </c>
       <c r="G483" t="n">
-        <v>2.3698673248291</v>
+        <v>2.36986756324768</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G485" t="n">
-        <v>2.49375796318054</v>
+        <v>2.49375820159912</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G491" t="n">
-        <v>2.66794085502625</v>
+        <v>2.66794061660767</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>4.23199987411499</v>
       </c>
       <c r="G493" t="n">
-        <v>2.59556913375854</v>
+        <v>2.59556889533997</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.25600004196167</v>
       </c>
       <c r="G494" t="n">
-        <v>2.61028861999512</v>
+        <v>2.6102888584137</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G497" t="n">
-        <v>2.62500858306885</v>
+        <v>2.62500882148743</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G499" t="n">
-        <v>2.60047554969788</v>
+        <v>2.6004753112793</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G502" t="n">
-        <v>2.33061504364014</v>
+        <v>2.33061480522156</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G505" t="n">
-        <v>2.39808034896851</v>
+        <v>2.39808011054993</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G507" t="n">
-        <v>2.47903823852539</v>
+        <v>2.47903847694397</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G511" t="n">
-        <v>2.45941233634949</v>
+        <v>2.45941209793091</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G514" t="n">
-        <v>2.54527711868286</v>
+        <v>2.54527688026428</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G515" t="n">
-        <v>2.54527711868286</v>
+        <v>2.54527688026428</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G517" t="n">
-        <v>2.52687740325928</v>
+        <v>2.5268771648407</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G521" t="n">
-        <v>2.62991499900818</v>
+        <v>2.62991523742676</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G522" t="n">
-        <v>2.62746167182922</v>
+        <v>2.6274619102478</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>4.21799993515015</v>
       </c>
       <c r="G523" t="n">
-        <v>2.5869824886322</v>
+        <v>2.58698272705078</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G527" t="n">
-        <v>2.65567445755005</v>
+        <v>2.65567421913147</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G528" t="n">
-        <v>2.59311604499817</v>
+        <v>2.59311580657959</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G531" t="n">
-        <v>2.60047554969788</v>
+        <v>2.6004753112793</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G533" t="n">
-        <v>2.46799874305725</v>
+        <v>2.46799850463867</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>3.86400008201599</v>
       </c>
       <c r="G535" t="n">
-        <v>2.3698673248291</v>
+        <v>2.36986756324768</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G536" t="n">
-        <v>2.32325530052185</v>
+        <v>2.32325506210327</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G537" t="n">
-        <v>2.35269451141357</v>
+        <v>2.35269474983215</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G542" t="n">
-        <v>2.18341827392578</v>
+        <v>2.1834180355072</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G543" t="n">
-        <v>2.32325530052185</v>
+        <v>2.32325506210327</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G544" t="n">
-        <v>2.27541613578796</v>
+        <v>2.27541637420654</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G548" t="n">
-        <v>2.28400254249573</v>
+        <v>2.28400278091431</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G549" t="n">
-        <v>2.33061504364014</v>
+        <v>2.33061480522156</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G550" t="n">
-        <v>2.24965691566467</v>
+        <v>2.24965667724609</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>3.41199994087219</v>
       </c>
       <c r="G552" t="n">
-        <v>2.09264707565308</v>
+        <v>2.0926468372345</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G553" t="n">
-        <v>2.03008818626404</v>
+        <v>2.03008842468262</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G555" t="n">
-        <v>1.90129113197327</v>
+        <v>1.90129125118256</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G556" t="n">
-        <v>1.84609246253967</v>
+        <v>1.84609234333038</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G557" t="n">
-        <v>1.87921154499054</v>
+        <v>1.87921166419983</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>3.15799999237061</v>
       </c>
       <c r="G559" t="n">
-        <v>1.93686354160309</v>
+        <v>1.93686378002167</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G561" t="n">
-        <v>1.84609246253967</v>
+        <v>1.84609234333038</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G563" t="n">
-        <v>1.87798511981964</v>
+        <v>1.87798523902893</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G564" t="n">
-        <v>1.87921154499054</v>
+        <v>1.87921166419983</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G566" t="n">
-        <v>1.86571872234344</v>
+        <v>1.86571860313416</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G567" t="n">
-        <v>1.90129113197327</v>
+        <v>1.90129125118256</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G568" t="n">
-        <v>1.98715591430664</v>
+        <v>1.98715579509735</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G570" t="n">
-        <v>1.86571872234344</v>
+        <v>1.86571860313416</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>3.08200001716614</v>
       </c>
       <c r="G571" t="n">
-        <v>1.89025139808655</v>
+        <v>1.89025151729584</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G572" t="n">
-        <v>1.88657140731812</v>
+        <v>1.8865715265274</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G573" t="n">
-        <v>1.81542658805847</v>
+        <v>1.81542634963989</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G577" t="n">
-        <v>1.92091739177704</v>
+        <v>1.92091727256775</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G578" t="n">
-        <v>1.95648992061615</v>
+        <v>1.95649003982544</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>3.12800002098083</v>
       </c>
       <c r="G579" t="n">
-        <v>1.91846406459808</v>
+        <v>1.91846418380737</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>3.14800000190735</v>
       </c>
       <c r="G582" t="n">
-        <v>1.93073058128357</v>
+        <v>1.93073046207428</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>3.32399988174438</v>
       </c>
       <c r="G584" t="n">
-        <v>2.03867483139038</v>
+        <v>2.0386745929718</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>3.37199997901917</v>
       </c>
       <c r="G585" t="n">
-        <v>2.0681140422821</v>
+        <v>2.06811428070068</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G587" t="n">
-        <v>1.99083590507507</v>
+        <v>1.99083578586578</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G588" t="n">
-        <v>1.96262323856354</v>
+        <v>1.96262311935425</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G589" t="n">
-        <v>2.03008818626404</v>
+        <v>2.03008842468262</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G591" t="n">
-        <v>1.9712096452713</v>
+        <v>1.97120976448059</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G593" t="n">
-        <v>1.9773428440094</v>
+        <v>1.97734272480011</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>3.33599996566772</v>
       </c>
       <c r="G596" t="n">
-        <v>2.04603481292725</v>
+        <v>2.04603457450867</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G601" t="n">
-        <v>1.9712096452713</v>
+        <v>1.97120976448059</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G602" t="n">
-        <v>1.96016991138458</v>
+        <v>1.96017003059387</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>3.08200001716614</v>
       </c>
       <c r="G605" t="n">
-        <v>1.89025139808655</v>
+        <v>1.89025151729584</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>3.10599994659424</v>
       </c>
       <c r="G607" t="n">
-        <v>1.90497088432312</v>
+        <v>1.90497100353241</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G608" t="n">
-        <v>1.88411831855774</v>
+        <v>1.88411819934845</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G612" t="n">
-        <v>1.87921154499054</v>
+        <v>1.87921166419983</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G614" t="n">
-        <v>1.77985370159149</v>
+        <v>1.77985394001007</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G615" t="n">
-        <v>1.74182784557343</v>
+        <v>1.74182796478271</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>3.05599999427795</v>
       </c>
       <c r="G617" t="n">
-        <v>1.87430500984192</v>
+        <v>1.8743052482605</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G618" t="n">
-        <v>1.86939871311188</v>
+        <v>1.86939883232117</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G619" t="n">
-        <v>1.87307834625244</v>
+        <v>1.87307858467102</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G622" t="n">
-        <v>1.82155978679657</v>
+        <v>1.82155966758728</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G623" t="n">
-        <v>1.84609246253967</v>
+        <v>1.84609234333038</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G625" t="n">
-        <v>1.84609246253967</v>
+        <v>1.84609234333038</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G628" t="n">
-        <v>1.80316007137299</v>
+        <v>1.8031599521637</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G630" t="n">
-        <v>1.80193340778351</v>
+        <v>1.80193328857422</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G634" t="n">
-        <v>1.63756382465363</v>
+        <v>1.63756370544434</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G639" t="n">
-        <v>1.55169880390167</v>
+        <v>1.55169904232025</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.68600010871887</v>
       </c>
       <c r="G641" t="n">
-        <v>1.64737677574158</v>
+        <v>1.64737689495087</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G642" t="n">
-        <v>1.63143062591553</v>
+        <v>1.63143050670624</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.75799989700317</v>
       </c>
       <c r="G643" t="n">
-        <v>1.69153571128845</v>
+        <v>1.69153583049774</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.66400003433228</v>
       </c>
       <c r="G645" t="n">
-        <v>1.63388359546661</v>
+        <v>1.6338837146759</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G646" t="n">
-        <v>1.60567116737366</v>
+        <v>1.60567104816437</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G648" t="n">
-        <v>1.57377851009369</v>
+        <v>1.5737783908844</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.78600001335144</v>
       </c>
       <c r="G651" t="n">
-        <v>1.70870888233185</v>
+        <v>1.70870876312256</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.71399998664856</v>
       </c>
       <c r="G652" t="n">
-        <v>1.66454970836639</v>
+        <v>1.66454982757568</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G653" t="n">
-        <v>1.63143062591553</v>
+        <v>1.63143050670624</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.1340000629425</v>
       </c>
       <c r="G664" t="n">
-        <v>1.30882430076599</v>
+        <v>1.30882441997528</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G667" t="n">
-        <v>1.23645269870758</v>
+        <v>1.23645257949829</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>2.00399994850159</v>
       </c>
       <c r="G676" t="n">
-        <v>1.22909271717072</v>
+        <v>1.22909259796143</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>2.04800009727478</v>
       </c>
       <c r="G682" t="n">
-        <v>1.25607895851135</v>
+        <v>1.25607883930206</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G683" t="n">
-        <v>1.22602605819702</v>
+        <v>1.22602617740631</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G684" t="n">
-        <v>1.23522591590881</v>
+        <v>1.23522579669952</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.00399994850159</v>
       </c>
       <c r="G685" t="n">
-        <v>1.22909271717072</v>
+        <v>1.22909259796143</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G686" t="n">
-        <v>1.24503898620605</v>
+        <v>1.24503910541534</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2</v>
       </c>
       <c r="G687" t="n">
-        <v>1.22663950920105</v>
+        <v>1.22663938999176</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2</v>
       </c>
       <c r="G691" t="n">
-        <v>1.22663950920105</v>
+        <v>1.22663938999176</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G692" t="n">
-        <v>1.24381244182587</v>
+        <v>1.24381256103516</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G693" t="n">
-        <v>1.24381244182587</v>
+        <v>1.24381256103516</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G694" t="n">
-        <v>1.26343870162964</v>
+        <v>1.26343858242035</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G695" t="n">
-        <v>1.29533123970032</v>
+        <v>1.29533135890961</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G697" t="n">
-        <v>1.30023777484894</v>
+        <v>1.30023765563965</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G698" t="n">
-        <v>1.24381244182587</v>
+        <v>1.24381256103516</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G703" t="n">
-        <v>1.17389392852783</v>
+        <v>1.17389404773712</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>1.92299997806549</v>
       </c>
       <c r="G705" t="n">
-        <v>1.17941379547119</v>
+        <v>1.17941391468048</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G706" t="n">
-        <v>1.13709485530853</v>
+        <v>1.13709473609924</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G708" t="n">
-        <v>1.08434927463531</v>
+        <v>1.0843493938446</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>1.7389999628067</v>
       </c>
       <c r="G709" t="n">
-        <v>1.06656301021576</v>
+        <v>1.06656289100647</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G716" t="n">
-        <v>0.976405084133148</v>
+        <v>0.976405024528503</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G717" t="n">
-        <v>0.984991490840912</v>
+        <v>0.984991431236267</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G718" t="n">
-        <v>0.910779893398285</v>
+        <v>0.91077983379364</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>1.5110000371933</v>
       </c>
       <c r="G720" t="n">
-        <v>0.926726102828979</v>
+        <v>0.926726222038269</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>1.49399995803833</v>
       </c>
       <c r="G721" t="n">
-        <v>0.916299641132355</v>
+        <v>0.916299700737</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G722" t="n">
-        <v>0.951258897781372</v>
+        <v>0.951258957386017</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G724" t="n">
-        <v>0.965365290641785</v>
+        <v>0.96536523103714</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G726" t="n">
-        <v>0.980084955692291</v>
+        <v>0.980085015296936</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G727" t="n">
-        <v>0.958618700504303</v>
+        <v>0.958618640899658</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G728" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G729" t="n">
-        <v>0.992351412773132</v>
+        <v>0.992351353168488</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>1.57200002670288</v>
       </c>
       <c r="G730" t="n">
-        <v>0.964138627052307</v>
+        <v>0.964138567447662</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>1.53299999237061</v>
       </c>
       <c r="G731" t="n">
-        <v>0.940219104290009</v>
+        <v>0.940219163894653</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G732" t="n">
-        <v>0.907713294029236</v>
+        <v>0.907713174819946</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>1.50100004673004</v>
       </c>
       <c r="G734" t="n">
-        <v>0.920592904090881</v>
+        <v>0.920592963695526</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G735" t="n">
-        <v>0.924886167049408</v>
+        <v>0.924886226654053</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G736" t="n">
-        <v>0.895446836948395</v>
+        <v>0.89544677734375</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G737" t="n">
-        <v>0.902193248271942</v>
+        <v>0.902193307876587</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G738" t="n">
-        <v>0.867847442626953</v>
+        <v>0.867847383022308</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G740" t="n">
-        <v>0.875820636749268</v>
+        <v>0.875820577144623</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G741" t="n">
-        <v>0.884407103061676</v>
+        <v>0.884407043457031</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>1.53299999237061</v>
       </c>
       <c r="G742" t="n">
-        <v>0.940219104290009</v>
+        <v>0.940219163894653</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G744" t="n">
-        <v>0.944512367248535</v>
+        <v>0.94451242685318</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G745" t="n">
-        <v>0.941445827484131</v>
+        <v>0.941445767879486</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G746" t="n">
-        <v>0.938379228115082</v>
+        <v>0.938379287719727</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>1.557000041008</v>
       </c>
       <c r="G749" t="n">
-        <v>0.954938888549805</v>
+        <v>0.954938769340515</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G750" t="n">
-        <v>0.901580035686493</v>
+        <v>0.901579976081848</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G752" t="n">
-        <v>0.870913922786713</v>
+        <v>0.870913982391357</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>1.48699998855591</v>
       </c>
       <c r="G754" t="n">
-        <v>0.912006437778473</v>
+        <v>0.912006497383118</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G755" t="n">
-        <v>0.875207245349884</v>
+        <v>0.875207364559174</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G756" t="n">
-        <v>0.859874308109283</v>
+        <v>0.859874248504639</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>1.37899994850159</v>
       </c>
       <c r="G757" t="n">
-        <v>0.845767855644226</v>
+        <v>0.845767915248871</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G758" t="n">
-        <v>0.837181448936462</v>
+        <v>0.837181389331818</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G759" t="n">
-        <v>0.849447846412659</v>
+        <v>0.849447786808014</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G760" t="n">
-        <v>0.837181448936462</v>
+        <v>0.837181389331818</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>1.43099999427795</v>
       </c>
       <c r="G763" t="n">
-        <v>0.877660512924194</v>
+        <v>0.877660572528839</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>1.45700001716614</v>
       </c>
       <c r="G764" t="n">
-        <v>0.893606841564178</v>
+        <v>0.893606901168823</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G767" t="n">
-        <v>0.951258897781372</v>
+        <v>0.951258957386017</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G768" t="n">
-        <v>0.951872289180756</v>
+        <v>0.951872229576111</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>1.60699999332428</v>
       </c>
       <c r="G769" t="n">
-        <v>0.985604822635651</v>
+        <v>0.985604882240295</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>1.61300003528595</v>
       </c>
       <c r="G771" t="n">
-        <v>0.989284813404083</v>
+        <v>0.989284694194794</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G773" t="n">
-        <v>0.944512367248535</v>
+        <v>0.94451242685318</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G776" t="n">
-        <v>0.99357795715332</v>
+        <v>0.993577897548676</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G777" t="n">
-        <v>0.986218214035034</v>
+        <v>0.986218154430389</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G778" t="n">
-        <v>0.940832495689392</v>
+        <v>0.940832555294037</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>1.5</v>
       </c>
       <c r="G779" t="n">
-        <v>0.919979631900787</v>
+        <v>0.919979512691498</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G781" t="n">
-        <v>0.984991490840912</v>
+        <v>0.984991431236267</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G784" t="n">
-        <v>1.06472301483154</v>
+        <v>1.06472289562225</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G788" t="n">
-        <v>1.03221714496613</v>
+        <v>1.03221702575684</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>1.7039999961853</v>
       </c>
       <c r="G789" t="n">
-        <v>1.04509675502777</v>
+        <v>1.04509687423706</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G791" t="n">
-        <v>0.972111761569977</v>
+        <v>0.972111880779266</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>1.59700000286102</v>
       </c>
       <c r="G792" t="n">
-        <v>0.979471623897552</v>
+        <v>0.979471564292908</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G796" t="n">
-        <v>1.06901621818542</v>
+        <v>1.06901633739471</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G798" t="n">
-        <v>1.0426436662674</v>
+        <v>1.04264354705811</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G799" t="n">
-        <v>1.06901621818542</v>
+        <v>1.06901633739471</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>1.56700003147125</v>
       </c>
       <c r="G805" t="n">
-        <v>0.961072087287903</v>
+        <v>0.961071968078613</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>1.5789999961853</v>
       </c>
       <c r="G806" t="n">
-        <v>0.968431770801544</v>
+        <v>0.968431890010834</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>1.49399995803833</v>
       </c>
       <c r="G812" t="n">
-        <v>0.916299641132355</v>
+        <v>0.916299700737</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G815" t="n">
-        <v>0.928566098213196</v>
+        <v>0.928566157817841</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G816" t="n">
-        <v>0.923046231269836</v>
+        <v>0.923046171665192</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G817" t="n">
-        <v>0.926112830638885</v>
+        <v>0.92611289024353</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>1.54100000858307</v>
       </c>
       <c r="G818" t="n">
-        <v>0.945125699043274</v>
+        <v>0.945125758647919</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.47300004959106</v>
       </c>
       <c r="G822" t="n">
-        <v>0.903420031070709</v>
+        <v>0.903419971466064</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G823" t="n">
-        <v>0.899126708507538</v>
+        <v>0.899126648902893</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>1.50100004673004</v>
       </c>
       <c r="G825" t="n">
-        <v>0.920592904090881</v>
+        <v>0.920592963695526</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>1.53699994087219</v>
       </c>
       <c r="G826" t="n">
-        <v>0.942672371864319</v>
+        <v>0.942672431468964</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G828" t="n">
-        <v>0.960458695888519</v>
+        <v>0.960458636283875</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>1.66299998760223</v>
       </c>
       <c r="G831" t="n">
-        <v>1.01995074748993</v>
+        <v>1.01995062828064</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G833" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G834" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>1.55299997329712</v>
       </c>
       <c r="G835" t="n">
-        <v>0.95248544216156</v>
+        <v>0.952485501766205</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G836" t="n">
-        <v>0.965365290641785</v>
+        <v>0.96536523103714</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G837" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G839" t="n">
-        <v>0.977631628513336</v>
+        <v>0.977631688117981</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>1.5789999961853</v>
       </c>
       <c r="G842" t="n">
-        <v>0.968431770801544</v>
+        <v>0.968431890010834</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G845" t="n">
-        <v>0.90280669927597</v>
+        <v>0.902806639671326</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G846" t="n">
-        <v>0.86723405122757</v>
+        <v>0.867234110832214</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G847" t="n">
-        <v>0.852514445781708</v>
+        <v>0.852514386177063</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G849" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.27799999713898</v>
       </c>
       <c r="G852" t="n">
-        <v>0.783822655677795</v>
+        <v>0.783822596073151</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G860" t="n">
-        <v>0.718810796737671</v>
+        <v>0.718810737133026</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>1.17900002002716</v>
       </c>
       <c r="G864" t="n">
-        <v>0.723103940486908</v>
+        <v>0.723104000091553</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G866" t="n">
-        <v>0.72985053062439</v>
+        <v>0.729850471019745</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>1.17900002002716</v>
       </c>
       <c r="G867" t="n">
-        <v>0.723103940486908</v>
+        <v>0.723104000091553</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G870" t="n">
-        <v>0.722490608692169</v>
+        <v>0.722490668296814</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G873" t="n">
-        <v>0.709610939025879</v>
+        <v>0.709610879421234</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G879" t="n">
-        <v>0.718810796737671</v>
+        <v>0.718810737133026</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G880" t="n">
-        <v>0.722490608692169</v>
+        <v>0.722490668296814</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>1.24699997901917</v>
       </c>
       <c r="G888" t="n">
-        <v>0.764809668064117</v>
+        <v>0.764809727668762</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G890" t="n">
-        <v>0.770329535007477</v>
+        <v>0.770329594612122</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>1.25300002098083</v>
       </c>
       <c r="G891" t="n">
-        <v>0.76848965883255</v>
+        <v>0.768489599227905</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G892" t="n">
-        <v>0.775849401950836</v>
+        <v>0.775849521160126</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G895" t="n">
-        <v>0.761743068695068</v>
+        <v>0.761743128299713</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>1.25300002098083</v>
       </c>
       <c r="G896" t="n">
-        <v>0.76848965883255</v>
+        <v>0.768489599227905</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>1.24699997901917</v>
       </c>
       <c r="G898" t="n">
-        <v>0.764809668064117</v>
+        <v>0.764809727668762</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G899" t="n">
-        <v>0.756836593151093</v>
+        <v>0.756836533546448</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G905" t="n">
-        <v>0.788729131221771</v>
+        <v>0.788729190826416</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G907" t="n">
-        <v>0.813262045383453</v>
+        <v>0.813261926174164</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G914" t="n">
-        <v>0.7323037981987</v>
+        <v>0.732303738594055</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G915" t="n">
-        <v>0.721264064311981</v>
+        <v>0.721264004707336</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>1.17900002002716</v>
       </c>
       <c r="G916" t="n">
-        <v>0.723103940486908</v>
+        <v>0.723104000091553</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G917" t="n">
-        <v>0.726170539855957</v>
+        <v>0.726170599460602</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G920" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G921" t="n">
-        <v>0.7323037981987</v>
+        <v>0.732303738594055</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>1.18099999427795</v>
       </c>
       <c r="G922" t="n">
-        <v>0.72433066368103</v>
+        <v>0.724330604076385</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G925" t="n">
-        <v>0.750703275203705</v>
+        <v>0.75070333480835</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G928" t="n">
-        <v>0.770329535007477</v>
+        <v>0.770329594612122</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G931" t="n">
-        <v>0.788729131221771</v>
+        <v>0.788729190826416</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>1.23699998855591</v>
       </c>
       <c r="G934" t="n">
-        <v>0.758676469326019</v>
+        <v>0.758676528930664</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G938" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G940" t="n">
-        <v>0.849447846412659</v>
+        <v>0.849447786808014</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G943" t="n">
-        <v>0.837181448936462</v>
+        <v>0.837181389331818</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G946" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G947" t="n">
-        <v>0.829208254814148</v>
+        <v>0.829208314418793</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G950" t="n">
-        <v>0.754383206367493</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>1.23099994659424</v>
       </c>
       <c r="G951" t="n">
-        <v>0.754996597766876</v>
+        <v>0.754996538162231</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G952" t="n">
-        <v>0.761743068695068</v>
+        <v>0.761743128299713</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G957" t="n">
-        <v>0.733530402183533</v>
+        <v>0.733530342578888</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G958" t="n">
-        <v>0.739050269126892</v>
+        <v>0.739050328731537</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G960" t="n">
-        <v>0.756836593151093</v>
+        <v>0.756836533546448</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G961" t="n">
-        <v>0.754383206367493</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G962" t="n">
-        <v>0.775849401950836</v>
+        <v>0.775849521160126</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G965" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>1.29900002479553</v>
       </c>
       <c r="G966" t="n">
-        <v>0.796702325344086</v>
+        <v>0.79670238494873</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>1.25300002098083</v>
       </c>
       <c r="G967" t="n">
-        <v>0.76848965883255</v>
+        <v>0.768489599227905</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G969" t="n">
-        <v>0.769102931022644</v>
+        <v>0.769102871417999</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>1.25100004673004</v>
       </c>
       <c r="G970" t="n">
-        <v>0.767263054847717</v>
+        <v>0.767262995243073</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G976" t="n">
-        <v>0.859874308109283</v>
+        <v>0.859874248504639</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G977" t="n">
-        <v>0.845154583454132</v>
+        <v>0.845154643058777</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G978" t="n">
-        <v>0.910779893398285</v>
+        <v>0.91077983379364</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G979" t="n">
-        <v>0.953712165355682</v>
+        <v>0.953712105751038</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G981" t="n">
-        <v>0.981311619281769</v>
+        <v>0.981311559677124</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G982" t="n">
-        <v>0.944512367248535</v>
+        <v>0.94451242685318</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G983" t="n">
-        <v>0.937152504920959</v>
+        <v>0.937152624130249</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G988" t="n">
-        <v>0.875820636749268</v>
+        <v>0.875820577144623</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>1.44900000095367</v>
       </c>
       <c r="G989" t="n">
-        <v>0.888700306415558</v>
+        <v>0.888700246810913</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G990" t="n">
-        <v>0.872140765190125</v>
+        <v>0.872140645980835</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G992" t="n">
-        <v>0.884407103061676</v>
+        <v>0.884407043457031</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>1.5</v>
       </c>
       <c r="G993" t="n">
-        <v>0.919979631900787</v>
+        <v>0.919979512691498</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>1.53100001811981</v>
       </c>
       <c r="G994" t="n">
-        <v>0.938992559909821</v>
+        <v>0.938992619514465</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G995" t="n">
-        <v>0.954325556755066</v>
+        <v>0.954325437545776</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>1.52699995040894</v>
       </c>
       <c r="G996" t="n">
-        <v>0.936539173126221</v>
+        <v>0.93653929233551</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G999" t="n">
-        <v>0.918753027915955</v>
+        <v>0.91875296831131</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1000" t="n">
-        <v>0.928566098213196</v>
+        <v>0.928566157817841</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G1001" t="n">
-        <v>0.916913032531738</v>
+        <v>0.916912972927094</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G1002" t="n">
-        <v>0.918753027915955</v>
+        <v>0.91875296831131</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G1003" t="n">
-        <v>0.918753027915955</v>
+        <v>0.91875296831131</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1004" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1006" t="n">
-        <v>1.03344368934631</v>
+        <v>1.0334438085556</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.01933741569519</v>
+        <v>1.0193372964859</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.00277769565582</v>
+        <v>1.00277781486511</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1014" t="n">
-        <v>0.980084955692291</v>
+        <v>0.980085015296936</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1015" t="n">
-        <v>0.980084955692291</v>
+        <v>0.980085015296936</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G1016" t="n">
-        <v>0.986218214035034</v>
+        <v>0.986218154430389</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1018" t="n">
-        <v>0.944512367248535</v>
+        <v>0.94451242685318</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G1019" t="n">
-        <v>0.958618700504303</v>
+        <v>0.958618640899658</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1022" t="n">
-        <v>0.965978622436523</v>
+        <v>0.965978562831879</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>1.58899998664856</v>
       </c>
       <c r="G1024" t="n">
-        <v>0.974565029144287</v>
+        <v>0.974565088748932</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1025" t="n">
-        <v>0.980084955692291</v>
+        <v>0.980085015296936</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>1.58700001239777</v>
       </c>
       <c r="G1026" t="n">
-        <v>0.973338484764099</v>
+        <v>0.973338425159454</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>1.36699998378754</v>
       </c>
       <c r="G1030" t="n">
-        <v>0.83840811252594</v>
+        <v>0.838408052921295</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1031" t="n">
-        <v>0.815715312957764</v>
+        <v>0.815715253353119</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1032" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G1033" t="n">
-        <v>0.767876327037811</v>
+        <v>0.767876267433167</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>1.32099997997284</v>
       </c>
       <c r="G1035" t="n">
-        <v>0.810195446014404</v>
+        <v>0.81019538640976</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>1.2940000295639</v>
       </c>
       <c r="G1039" t="n">
-        <v>0.793635725975037</v>
+        <v>0.793635785579681</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G1040" t="n">
-        <v>0.79976898431778</v>
+        <v>0.799768924713135</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G1048" t="n">
-        <v>0.814488589763641</v>
+        <v>0.814488530158997</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1049" t="n">
-        <v>0.813262045383453</v>
+        <v>0.813261926174164</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1050" t="n">
-        <v>0.803448855876923</v>
+        <v>0.803448796272278</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>1.28699994087219</v>
       </c>
       <c r="G1052" t="n">
-        <v>0.789342403411865</v>
+        <v>0.78934246301651</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G1054" t="n">
-        <v>0.721264064311981</v>
+        <v>0.721264004707336</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G1055" t="n">
-        <v>0.708997666835785</v>
+        <v>0.70899760723114</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>1.13699996471405</v>
       </c>
       <c r="G1056" t="n">
-        <v>0.697344541549683</v>
+        <v>0.697344481945038</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>0.942499995231628</v>
       </c>
       <c r="G1061" t="n">
-        <v>0.578053891658783</v>
+        <v>0.578053832054138</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.572227299213409</v>
+        <v>0.572227358818054</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.49678897857666</v>
+        <v>0.496788948774338</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.451403349637985</v>
+        <v>0.451403319835663</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.472256183624268</v>
+        <v>0.47225621342659</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.461216449737549</v>
+        <v>0.461216419935226</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>0.806999981403351</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.494948983192444</v>
+        <v>0.494949012994766</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.490655809640884</v>
+        <v>0.490655779838562</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.469802886247635</v>
+        <v>0.469802916049957</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>0.732999980449677</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.449563354253769</v>
+        <v>0.449563324451447</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.39988449215889</v>
+        <v>0.399884462356567</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1080" t="n">
-        <v>0.394977927207947</v>
+        <v>0.394977897405624</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.488202542066574</v>
+        <v>0.488202512264252</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>0.901000022888184</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.552601099014282</v>
+        <v>0.552601158618927</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.49678897857666</v>
+        <v>0.496788948774338</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>0.852999985218048</v>
       </c>
       <c r="G1090" t="n">
-        <v>0.523161768913269</v>
+        <v>0.523161709308624</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G1094" t="n">
-        <v>0.559347629547119</v>
+        <v>0.559347569942474</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1095" t="n">
-        <v>0.533588171005249</v>
+        <v>0.533588111400604</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1097" t="n">
-        <v>0.543401300907135</v>
+        <v>0.54340124130249</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1098" t="n">
-        <v>0.533588171005249</v>
+        <v>0.533588111400604</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G1099" t="n">
-        <v>0.536041438579559</v>
+        <v>0.536041498184204</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G1100" t="n">
-        <v>0.512121975421906</v>
+        <v>0.512121915817261</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1104" t="n">
-        <v>0.518868505954742</v>
+        <v>0.518868565559387</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1107" t="n">
-        <v>0.518868505954742</v>
+        <v>0.518868565559387</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>0.830999970436096</v>
       </c>
       <c r="G1108" t="n">
-        <v>0.509668707847595</v>
+        <v>0.50966864824295</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>0.820999979972839</v>
       </c>
       <c r="G1109" t="n">
-        <v>0.503535449504852</v>
+        <v>0.503535509109497</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.493109107017517</v>
+        <v>0.493109077215195</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.491882383823395</v>
+        <v>0.49188244342804</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1116" t="n">
-        <v>0.518868505954742</v>
+        <v>0.518868565559387</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1117" t="n">
-        <v>0.551987707614899</v>
+        <v>0.551987767219543</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1118" t="n">
-        <v>0.545854568481445</v>
+        <v>0.545854508876801</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1123" t="n">
-        <v>0.637852549552917</v>
+        <v>0.637852489948273</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>1</v>
       </c>
       <c r="G1126" t="n">
-        <v>0.613319754600525</v>
+        <v>0.61331969499588</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>0.949000000953674</v>
       </c>
       <c r="G1129" t="n">
-        <v>0.582040429115295</v>
+        <v>0.582040369510651</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1132" t="n">
-        <v>0.551987707614899</v>
+        <v>0.551987767219543</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1133" t="n">
-        <v>0.544627964496613</v>
+        <v>0.544627904891968</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>0.876999974250793</v>
       </c>
       <c r="G1134" t="n">
-        <v>0.537881374359131</v>
+        <v>0.537881433963776</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1135" t="n">
-        <v>0.544627964496613</v>
+        <v>0.544627904891968</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1136" t="n">
-        <v>0.544627964496613</v>
+        <v>0.544627904891968</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1137" t="n">
-        <v>0.521321833133698</v>
+        <v>0.521321773529053</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>0.842999994754791</v>
       </c>
       <c r="G1139" t="n">
-        <v>0.517028510570526</v>
+        <v>0.517028570175171</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.516415238380432</v>
+        <v>0.516415178775787</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>0.837000012397766</v>
       </c>
       <c r="G1145" t="n">
-        <v>0.513348639011383</v>
+        <v>0.513348579406738</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1147" t="n">
-        <v>0.528681576251984</v>
+        <v>0.528681635856628</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1149" t="n">
-        <v>0.522548377513885</v>
+        <v>0.52254843711853</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>0.859000027179718</v>
       </c>
       <c r="G1150" t="n">
-        <v>0.526841640472412</v>
+        <v>0.526841700077057</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.555054306983948</v>
+        <v>0.555054366588593</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1155" t="n">
-        <v>0.53849470615387</v>
+        <v>0.538494765758514</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1156" t="n">
-        <v>0.542174637317657</v>
+        <v>0.542174696922302</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1157" t="n">
-        <v>0.545854568481445</v>
+        <v>0.545854508876801</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1158" t="n">
-        <v>0.545854568481445</v>
+        <v>0.545854508876801</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>0.879000008106232</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.539108037948608</v>
+        <v>0.539108097553253</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1160" t="n">
-        <v>0.544627964496613</v>
+        <v>0.544627904891968</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1162" t="n">
-        <v>0.551987707614899</v>
+        <v>0.551987767219543</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.542174637317657</v>
+        <v>0.542174696922302</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>0.879000008106232</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.539108037948608</v>
+        <v>0.539108097553253</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>0.890999972820282</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.546467900276184</v>
+        <v>0.546467840671539</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1167" t="n">
-        <v>0.575293898582458</v>
+        <v>0.575293958187103</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.582653760910034</v>
+        <v>0.582653701305389</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>0.930999994277954</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.571000635623932</v>
+        <v>0.571000695228577</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>0.964999973773956</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.591853559017181</v>
+        <v>0.591853499412537</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.588786900043488</v>
+        <v>0.588786959648132</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.578973829746246</v>
+        <v>0.578973770141602</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.559347629547119</v>
+        <v>0.559347569942474</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>0.902999997138977</v>
       </c>
       <c r="G1186" t="n">
-        <v>0.553827702999115</v>
+        <v>0.55382776260376</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.572227299213409</v>
+        <v>0.572227358818054</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>0.916999995708466</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.562414228916168</v>
+        <v>0.562414169311523</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.547081232070923</v>
+        <v>0.547081172466278</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.592466831207275</v>
+        <v>0.59246689081192</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G1199" t="n">
-        <v>0.561800837516785</v>
+        <v>0.561800897121429</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.551987707614899</v>
+        <v>0.551987767219543</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G1204" t="n">
-        <v>0.555054306983948</v>
+        <v>0.555054366588593</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.572227299213409</v>
+        <v>0.572227358818054</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>0.944999992847443</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.579587161540985</v>
+        <v>0.57958710193634</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>0.958999991416931</v>
       </c>
       <c r="G1213" t="n">
-        <v>0.588173627853394</v>
+        <v>0.588173687458038</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>0.953000009059906</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.58449375629425</v>
+        <v>0.584493696689606</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.571614027023315</v>
+        <v>0.571613967418671</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.544627964496613</v>
+        <v>0.544627904891968</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>0.916999995708466</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.562414228916168</v>
+        <v>0.562414169311523</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.572227299213409</v>
+        <v>0.572227358818054</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>0.944999992847443</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.579587161540985</v>
+        <v>0.57958710193634</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>0.967000007629395</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.593080222606659</v>
+        <v>0.593080163002014</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.588786900043488</v>
+        <v>0.588786959648132</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.619452893733978</v>
+        <v>0.619452953338623</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.648892283439636</v>
+        <v>0.648892223834991</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>1.15799999237061</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.710224211215973</v>
+        <v>0.710224270820618</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.697957873344421</v>
+        <v>0.697957813739777</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G1245" t="n">
-        <v>0.708997666835785</v>
+        <v>0.70899760723114</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1246" t="n">
-        <v>0.726170539855957</v>
+        <v>0.726170599460602</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1247" t="n">
-        <v>0.788729131221771</v>
+        <v>0.788729190826416</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1249" t="n">
-        <v>0.821848511695862</v>
+        <v>0.821848452091217</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1252" t="n">
-        <v>0.754383206367493</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G1254" t="n">
-        <v>0.756836593151093</v>
+        <v>0.756836533546448</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1256" t="n">
-        <v>0.769102931022644</v>
+        <v>0.769102871417999</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1262" t="n">
-        <v>0.759289920330048</v>
+        <v>0.759289860725403</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1263" t="n">
-        <v>0.764196395874023</v>
+        <v>0.764196455478668</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.712677538394928</v>
+        <v>0.712677478790283</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.723717212677002</v>
+        <v>0.723717272281647</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.723717212677002</v>
+        <v>0.723717272281647</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G1273" t="n">
-        <v>0.737210392951965</v>
+        <v>0.737210333347321</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.761743068695068</v>
+        <v>0.761743128299713</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1277" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1279" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G1280" t="n">
-        <v>0.728623807430267</v>
+        <v>0.728623867034912</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1285" t="n">
-        <v>0.723717212677002</v>
+        <v>0.723717272281647</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1287" t="n">
-        <v>0.712677538394928</v>
+        <v>0.712677478790283</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.708997666835785</v>
+        <v>0.70899760723114</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G1298" t="n">
-        <v>0.750703275203705</v>
+        <v>0.75070333480835</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1301" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1302" t="n">
-        <v>0.769102931022644</v>
+        <v>0.769102871417999</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1304" t="n">
-        <v>0.759289920330048</v>
+        <v>0.759289860725403</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1305" t="n">
-        <v>0.764196395874023</v>
+        <v>0.764196455478668</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1306" t="n">
-        <v>0.762969791889191</v>
+        <v>0.762969732284546</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>1.24800002574921</v>
       </c>
       <c r="G1307" t="n">
-        <v>0.765423059463501</v>
+        <v>0.765422999858856</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1308" t="n">
-        <v>0.769102931022644</v>
+        <v>0.769102871417999</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>1.34599995613098</v>
       </c>
       <c r="G1311" t="n">
-        <v>0.825528383255005</v>
+        <v>0.82552832365036</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1314" t="n">
-        <v>0.824301660060883</v>
+        <v>0.824301719665527</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.803448855876923</v>
+        <v>0.803448796272278</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1317" t="n">
-        <v>0.769102931022644</v>
+        <v>0.769102871417999</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1318" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1321" t="n">
-        <v>0.815715312957764</v>
+        <v>0.815715253353119</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1322" t="n">
-        <v>0.835341513156891</v>
+        <v>0.835341453552246</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G1327" t="n">
-        <v>0.829208254814148</v>
+        <v>0.829208314418793</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1328" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1329" t="n">
-        <v>0.813262045383453</v>
+        <v>0.813261926174164</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1330" t="n">
-        <v>0.843927979469299</v>
+        <v>0.843928039073944</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1331" t="n">
-        <v>0.837794840335846</v>
+        <v>0.837794780731201</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1333" t="n">
-        <v>0.813262045383453</v>
+        <v>0.813261926174164</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1334" t="n">
-        <v>0.851287841796875</v>
+        <v>0.85128778219223</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1338" t="n">
-        <v>0.813262045383453</v>
+        <v>0.813261926174164</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1340" t="n">
-        <v>0.843927979469299</v>
+        <v>0.843928039073944</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G1343" t="n">
-        <v>0.842701256275177</v>
+        <v>0.842701315879822</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G1344" t="n">
-        <v>0.842701256275177</v>
+        <v>0.842701315879822</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1345" t="n">
-        <v>0.815715312957764</v>
+        <v>0.815715253353119</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1347" t="n">
-        <v>0.803448855876923</v>
+        <v>0.803448796272278</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1350" t="n">
-        <v>0.870913922786713</v>
+        <v>0.870913982391357</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1351" t="n">
-        <v>0.877047181129456</v>
+        <v>0.8770472407341</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G1353" t="n">
-        <v>0.86723405122757</v>
+        <v>0.867234110832214</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1354" t="n">
-        <v>0.890540242195129</v>
+        <v>0.890540301799774</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1357" t="n">
-        <v>0.890540242195129</v>
+        <v>0.890540301799774</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G1358" t="n">
-        <v>0.872140765190125</v>
+        <v>0.872140645980835</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G1361" t="n">
-        <v>0.875820636749268</v>
+        <v>0.875820577144623</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1362" t="n">
-        <v>0.851287841796875</v>
+        <v>0.85128778219223</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1366" t="n">
-        <v>0.843927979469299</v>
+        <v>0.843928039073944</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1367" t="n">
-        <v>0.835341513156891</v>
+        <v>0.835341453552246</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1369" t="n">
-        <v>0.837794840335846</v>
+        <v>0.837794780731201</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G1371" t="n">
-        <v>0.826754987239838</v>
+        <v>0.826755046844482</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G1372" t="n">
-        <v>0.826754987239838</v>
+        <v>0.826755046844482</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1378" t="n">
-        <v>0.870913922786713</v>
+        <v>0.870913982391357</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G1379" t="n">
-        <v>0.912619769573212</v>
+        <v>0.912619829177856</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>1.5</v>
       </c>
       <c r="G1380" t="n">
-        <v>0.919979631900787</v>
+        <v>0.919979512691498</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G1381" t="n">
-        <v>0.940832495689392</v>
+        <v>0.940832555294037</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G1382" t="n">
-        <v>0.929792761802673</v>
+        <v>0.929792702198029</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>1.49399995803833</v>
       </c>
       <c r="G1384" t="n">
-        <v>0.916299641132355</v>
+        <v>0.916299700737</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1385" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>1.5</v>
       </c>
       <c r="G1387" t="n">
-        <v>0.919979631900787</v>
+        <v>0.919979512691498</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1388" t="n">
-        <v>0.890540242195129</v>
+        <v>0.890540301799774</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1391" t="n">
-        <v>0.890540242195129</v>
+        <v>0.890540301799774</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G1392" t="n">
-        <v>0.884407103061676</v>
+        <v>0.884407043457031</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G1393" t="n">
-        <v>0.884407103061676</v>
+        <v>0.884407043457031</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1396" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1397" t="n">
-        <v>0.835341513156891</v>
+        <v>0.835341453552246</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1400" t="n">
-        <v>0.82062178850174</v>
+        <v>0.820621848106384</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1408" t="n">
-        <v>0.754383206367493</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1409" t="n">
-        <v>0.723717212677002</v>
+        <v>0.723717272281647</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G1410" t="n">
-        <v>0.737210392951965</v>
+        <v>0.737210333347321</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1411" t="n">
-        <v>0.769102931022644</v>
+        <v>0.769102871417999</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.852514445781708</v>
+        <v>0.852514386177063</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1419" t="n">
-        <v>0.835341513156891</v>
+        <v>0.835341453552246</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G1422" t="n">
-        <v>0.845154583454132</v>
+        <v>0.845154643058777</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1423" t="n">
-        <v>0.851287841796875</v>
+        <v>0.85128778219223</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G1428" t="n">
-        <v>0.899126708507538</v>
+        <v>0.899126648902893</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>1.43400001525879</v>
       </c>
       <c r="G1431" t="n">
-        <v>0.879500508308411</v>
+        <v>0.879500567913055</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G1435" t="n">
-        <v>0.842701256275177</v>
+        <v>0.842701315879822</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1437" t="n">
-        <v>0.843927979469299</v>
+        <v>0.843928039073944</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1438" t="n">
-        <v>0.852514445781708</v>
+        <v>0.852514386177063</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1442" t="n">
-        <v>0.870913922786713</v>
+        <v>0.870913982391357</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1444" t="n">
-        <v>0.852514445781708</v>
+        <v>0.852514386177063</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1446" t="n">
-        <v>0.837794840335846</v>
+        <v>0.837794780731201</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G1447" t="n">
-        <v>0.82307505607605</v>
+        <v>0.823075115680695</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>1.34599995613098</v>
       </c>
       <c r="G1450" t="n">
-        <v>0.825528383255005</v>
+        <v>0.82552832365036</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G1451" t="n">
-        <v>0.82307505607605</v>
+        <v>0.823075115680695</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1453" t="n">
-        <v>0.813262045383453</v>
+        <v>0.813261926174164</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1455" t="n">
-        <v>0.772782802581787</v>
+        <v>0.772782921791077</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1456" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1458" t="n">
-        <v>0.813262045383453</v>
+        <v>0.813261926174164</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>1.33200001716614</v>
       </c>
       <c r="G1459" t="n">
-        <v>0.816941797733307</v>
+        <v>0.816941857337952</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G1460" t="n">
-        <v>0.79976898431778</v>
+        <v>0.799768924713135</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1461" t="n">
-        <v>0.803448855876923</v>
+        <v>0.803448796272278</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1464" t="n">
-        <v>0.788729131221771</v>
+        <v>0.788729190826416</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1469" t="n">
-        <v>0.788729131221771</v>
+        <v>0.788729190826416</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1470" t="n">
-        <v>0.80958217382431</v>
+        <v>0.809582114219666</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1471" t="n">
-        <v>0.815715312957764</v>
+        <v>0.815715253353119</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>1.34599995613098</v>
       </c>
       <c r="G1472" t="n">
-        <v>0.825528383255005</v>
+        <v>0.82552832365036</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1474" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G1475" t="n">
-        <v>0.829208254814148</v>
+        <v>0.829208314418793</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1476" t="n">
-        <v>0.824301660060883</v>
+        <v>0.824301719665527</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1477" t="n">
-        <v>0.85619443655014</v>
+        <v>0.856194376945496</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1478" t="n">
-        <v>0.851287841796875</v>
+        <v>0.85128778219223</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>1.44799995422363</v>
       </c>
       <c r="G1480" t="n">
-        <v>0.888086974620819</v>
+        <v>0.888086915016174</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1482" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1483" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1484" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>1.34599995613098</v>
       </c>
       <c r="G1485" t="n">
-        <v>0.825528383255005</v>
+        <v>0.82552832365036</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1486" t="n">
-        <v>0.824301660060883</v>
+        <v>0.824301719665527</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G1487" t="n">
-        <v>0.819395184516907</v>
+        <v>0.819395124912262</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1489" t="n">
-        <v>0.824301660060883</v>
+        <v>0.824301719665527</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1493" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1494" t="n">
-        <v>0.824301660060883</v>
+        <v>0.824301719665527</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G1495" t="n">
-        <v>0.82307505607605</v>
+        <v>0.823075115680695</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1496" t="n">
-        <v>0.821848511695862</v>
+        <v>0.821848452091217</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>1.33200001716614</v>
       </c>
       <c r="G1497" t="n">
-        <v>0.816941797733307</v>
+        <v>0.816941857337952</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1498" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1499" t="n">
-        <v>0.80958217382431</v>
+        <v>0.809582114219666</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G1500" t="n">
-        <v>0.79976898431778</v>
+        <v>0.799768924713135</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1501" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>1.2940000295639</v>
       </c>
       <c r="G1502" t="n">
-        <v>0.793635725975037</v>
+        <v>0.793635785579681</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1505" t="n">
-        <v>0.735983729362488</v>
+        <v>0.735983669757843</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G1507" t="n">
-        <v>0.733530402183533</v>
+        <v>0.733530342578888</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G1508" t="n">
-        <v>0.728623807430267</v>
+        <v>0.728623867034912</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G1509" t="n">
-        <v>0.722490608692169</v>
+        <v>0.722490668296814</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1511" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1514" t="n">
-        <v>0.735983729362488</v>
+        <v>0.735983669757843</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1516" t="n">
-        <v>0.735983729362488</v>
+        <v>0.735983669757843</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G1519" t="n">
-        <v>0.728623807430267</v>
+        <v>0.728623867034912</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G1520" t="n">
-        <v>0.738436937332153</v>
+        <v>0.738436996936798</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1523" t="n">
-        <v>0.726170539855957</v>
+        <v>0.726170599460602</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1524" t="n">
-        <v>0.723717212677002</v>
+        <v>0.723717272281647</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1525" t="n">
-        <v>0.723717212677002</v>
+        <v>0.723717272281647</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G1527" t="n">
-        <v>0.750703275203705</v>
+        <v>0.75070333480835</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G1531" t="n">
-        <v>0.750703275203705</v>
+        <v>0.75070333480835</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>1.26199996471405</v>
       </c>
       <c r="G1534" t="n">
-        <v>0.774009466171265</v>
+        <v>0.774009525775909</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1536" t="n">
-        <v>0.788729131221771</v>
+        <v>0.788729190826416</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1537" t="n">
-        <v>0.772782802581787</v>
+        <v>0.772782921791077</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1539" t="n">
-        <v>0.762969791889191</v>
+        <v>0.762969732284546</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G1541" t="n">
-        <v>0.756836593151093</v>
+        <v>0.756836533546448</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1543" t="n">
-        <v>0.72985053062439</v>
+        <v>0.729850471019745</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1544" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G1546" t="n">
-        <v>0.728623807430267</v>
+        <v>0.728623867034912</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1547" t="n">
-        <v>0.7323037981987</v>
+        <v>0.732303738594055</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1548" t="n">
-        <v>0.735983729362488</v>
+        <v>0.735983669757843</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1549" t="n">
-        <v>0.735983729362488</v>
+        <v>0.735983669757843</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1550" t="n">
-        <v>0.754383206367493</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1552" t="n">
-        <v>0.726170539855957</v>
+        <v>0.726170599460602</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G1555" t="n">
-        <v>0.721264064311981</v>
+        <v>0.721264004707336</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G1556" t="n">
-        <v>0.728623807430267</v>
+        <v>0.728623867034912</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G1559" t="n">
-        <v>0.728623807430267</v>
+        <v>0.728623867034912</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1561" t="n">
-        <v>0.712677538394928</v>
+        <v>0.712677478790283</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>1.06200003623962</v>
       </c>
       <c r="G1565" t="n">
-        <v>0.651345610618591</v>
+        <v>0.651345551013947</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>1.12399995326996</v>
       </c>
       <c r="G1567" t="n">
-        <v>0.689371407032013</v>
+        <v>0.689371347427368</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1568" t="n">
-        <v>0.631719350814819</v>
+        <v>0.631719291210175</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1571" t="n">
-        <v>0.517641842365265</v>
+        <v>0.51764190196991</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>0.788999974727631</v>
       </c>
       <c r="G1572" t="n">
-        <v>0.483909249305725</v>
+        <v>0.483909279108047</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>0.802999973297119</v>
       </c>
       <c r="G1575" t="n">
-        <v>0.492495745420456</v>
+        <v>0.492495715618134</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>0.823000013828278</v>
       </c>
       <c r="G1576" t="n">
-        <v>0.50476211309433</v>
+        <v>0.504762172698975</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1579" t="n">
-        <v>0.53849470615387</v>
+        <v>0.538494765758514</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>0.879000008106232</v>
       </c>
       <c r="G1584" t="n">
-        <v>0.539108037948608</v>
+        <v>0.539108097553253</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>0.890999972820282</v>
       </c>
       <c r="G1589" t="n">
-        <v>0.546467900276184</v>
+        <v>0.546467840671539</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G1593" t="n">
-        <v>0.536041438579559</v>
+        <v>0.536041498184204</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>0.861000001430511</v>
       </c>
       <c r="G1594" t="n">
-        <v>0.528068244457245</v>
+        <v>0.52806830406189</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>0.837000012397766</v>
       </c>
       <c r="G1595" t="n">
-        <v>0.513348639011383</v>
+        <v>0.513348579406738</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1596" t="n">
-        <v>0.510282039642334</v>
+        <v>0.510281980037689</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1597" t="n">
-        <v>0.515188574790955</v>
+        <v>0.51518851518631</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1598" t="n">
-        <v>0.517641842365265</v>
+        <v>0.51764190196991</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1599" t="n">
-        <v>0.528681576251984</v>
+        <v>0.528681635856628</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G1600" t="n">
-        <v>0.529908239841461</v>
+        <v>0.529908299446106</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>0.861000001430511</v>
       </c>
       <c r="G1608" t="n">
-        <v>0.528068244457245</v>
+        <v>0.52806830406189</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>0.859000027179718</v>
       </c>
       <c r="G1609" t="n">
-        <v>0.526841640472412</v>
+        <v>0.526841700077057</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1610" t="n">
-        <v>0.533588171005249</v>
+        <v>0.533588111400604</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>0.830999970436096</v>
       </c>
       <c r="G1613" t="n">
-        <v>0.509668707847595</v>
+        <v>0.50966864824295</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1614" t="n">
-        <v>0.517641842365265</v>
+        <v>0.51764190196991</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1615" t="n">
-        <v>0.509055376052856</v>
+        <v>0.509055316448212</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1618" t="n">
-        <v>0.509055376052856</v>
+        <v>0.509055316448212</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1619" t="n">
-        <v>0.509055376052856</v>
+        <v>0.509055316448212</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1622" t="n">
-        <v>0.533588171005249</v>
+        <v>0.533588111400604</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G1624" t="n">
-        <v>0.529908239841461</v>
+        <v>0.529908299446106</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1629" t="n">
-        <v>0.572227299213409</v>
+        <v>0.572227358818054</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G1633" t="n">
-        <v>0.647665619850159</v>
+        <v>0.647665679454803</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1634" t="n">
-        <v>0.619452893733978</v>
+        <v>0.619452953338623</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G1637" t="n">
-        <v>0.628039479255676</v>
+        <v>0.628039419651031</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1638" t="n">
-        <v>0.619452893733978</v>
+        <v>0.619452953338623</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1640" t="n">
-        <v>0.545854568481445</v>
+        <v>0.545854508876801</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1643" t="n">
-        <v>0.533588171005249</v>
+        <v>0.533588111400604</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>0.898999989032745</v>
       </c>
       <c r="G1645" t="n">
-        <v>0.551374435424805</v>
+        <v>0.551374495029449</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G1648" t="n">
-        <v>0.547081232070923</v>
+        <v>0.547081172466278</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>0.898999989032745</v>
       </c>
       <c r="G1649" t="n">
-        <v>0.551374435424805</v>
+        <v>0.551374495029449</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1651" t="n">
-        <v>0.533588171005249</v>
+        <v>0.533588111400604</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G1655" t="n">
-        <v>0.512121975421906</v>
+        <v>0.512121915817261</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>0.788999974727631</v>
       </c>
       <c r="G1657" t="n">
-        <v>0.483909249305725</v>
+        <v>0.483909279108047</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G1658" t="n">
-        <v>0.511508703231812</v>
+        <v>0.511508643627167</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1660" t="n">
-        <v>0.509055376052856</v>
+        <v>0.509055316448212</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1661" t="n">
-        <v>0.488202542066574</v>
+        <v>0.488202512264252</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1662" t="n">
-        <v>0.488202542066574</v>
+        <v>0.488202512264252</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1663" t="n">
-        <v>0.479616016149521</v>
+        <v>0.479616045951843</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1664" t="n">
-        <v>0.482069313526154</v>
+        <v>0.482069283723831</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>0.785000026226044</v>
       </c>
       <c r="G1665" t="n">
-        <v>0.481456011533737</v>
+        <v>0.481455981731415</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>0.787000000476837</v>
       </c>
       <c r="G1666" t="n">
-        <v>0.482682645320892</v>
+        <v>0.48268261551857</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1669" t="n">
-        <v>0.509055376052856</v>
+        <v>0.509055316448212</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>0.861000001430511</v>
       </c>
       <c r="G1670" t="n">
-        <v>0.528068244457245</v>
+        <v>0.52806830406189</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G1671" t="n">
-        <v>0.559347629547119</v>
+        <v>0.559347569942474</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>0.930999994277954</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.571000635623932</v>
+        <v>0.571000695228577</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>0.890999972820282</v>
       </c>
       <c r="G1680" t="n">
-        <v>0.546467900276184</v>
+        <v>0.546467840671539</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G1682" t="n">
-        <v>0.548921167850494</v>
+        <v>0.54892110824585</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1683" t="n">
-        <v>0.551987707614899</v>
+        <v>0.551987767219543</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G1684" t="n">
-        <v>0.5483078956604</v>
+        <v>0.548307836055756</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>0.898999989032745</v>
       </c>
       <c r="G1687" t="n">
-        <v>0.551374435424805</v>
+        <v>0.551374495029449</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1688" t="n">
-        <v>0.53849470615387</v>
+        <v>0.538494765758514</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>0.898999989032745</v>
       </c>
       <c r="G1690" t="n">
-        <v>0.551374435424805</v>
+        <v>0.551374495029449</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1696" t="n">
-        <v>0.515188574790955</v>
+        <v>0.51518851518631</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1698" t="n">
-        <v>0.509055376052856</v>
+        <v>0.509055316448212</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1701" t="n">
-        <v>0.490655809640884</v>
+        <v>0.490655779838562</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1702" t="n">
-        <v>0.485749214887619</v>
+        <v>0.485749274492264</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1703" t="n">
-        <v>0.485749214887619</v>
+        <v>0.485749274492264</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>0.809000015258789</v>
       </c>
       <c r="G1704" t="n">
-        <v>0.496175706386566</v>
+        <v>0.496175676584244</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1706" t="n">
-        <v>0.486975878477097</v>
+        <v>0.486975908279419</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1710" t="n">
-        <v>0.472256183624268</v>
+        <v>0.47225621342659</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G1711" t="n">
-        <v>0.456923216581345</v>
+        <v>0.456923186779022</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1714" t="n">
-        <v>0.435456961393356</v>
+        <v>0.435456991195679</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1715" t="n">
-        <v>0.437910318374634</v>
+        <v>0.437910288572311</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1716" t="n">
-        <v>0.447723418474197</v>
+        <v>0.447723388671875</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1718" t="n">
-        <v>0.435456961393356</v>
+        <v>0.435456991195679</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G1720" t="n">
-        <v>0.438523590564728</v>
+        <v>0.43852362036705</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1722" t="n">
-        <v>0.42809721827507</v>
+        <v>0.428097188472748</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1724" t="n">
-        <v>0.414604127407074</v>
+        <v>0.414604157209396</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>0.686999976634979</v>
       </c>
       <c r="G1727" t="n">
-        <v>0.421350628137589</v>
+        <v>0.421350657939911</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1732" t="n">
-        <v>0.490655809640884</v>
+        <v>0.490655779838562</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1734" t="n">
-        <v>0.544627964496613</v>
+        <v>0.544627904891968</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>0.842999994754791</v>
       </c>
       <c r="G1737" t="n">
-        <v>0.517028510570526</v>
+        <v>0.517028570175171</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>0.837000012397766</v>
       </c>
       <c r="G1738" t="n">
-        <v>0.513348639011383</v>
+        <v>0.513348579406738</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>0.837000012397766</v>
       </c>
       <c r="G1741" t="n">
-        <v>0.513348639011383</v>
+        <v>0.513348579406738</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1745" t="n">
-        <v>0.515188574790955</v>
+        <v>0.51518851518631</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1746" t="n">
-        <v>0.515188574790955</v>
+        <v>0.51518851518631</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>0.859000027179718</v>
       </c>
       <c r="G1747" t="n">
-        <v>0.526841640472412</v>
+        <v>0.526841700077057</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G1749" t="n">
-        <v>0.586333632469177</v>
+        <v>0.586333692073822</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1750" t="n">
-        <v>0.575293898582458</v>
+        <v>0.575293958187103</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1754" t="n">
-        <v>0.542174637317657</v>
+        <v>0.542174696922302</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1756" t="n">
-        <v>0.525001645088196</v>
+        <v>0.525001704692841</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1761" t="n">
-        <v>0.545854568481445</v>
+        <v>0.545854508876801</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1764" t="n">
-        <v>0.525001645088196</v>
+        <v>0.525001704692841</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1769" t="n">
-        <v>0.518868505954742</v>
+        <v>0.518868565559387</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G1770" t="n">
-        <v>0.529908239841461</v>
+        <v>0.529908299446106</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G1771" t="n">
-        <v>0.529908239841461</v>
+        <v>0.529908299446106</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1772" t="n">
-        <v>0.528681576251984</v>
+        <v>0.528681635856628</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1774" t="n">
-        <v>0.533588171005249</v>
+        <v>0.533588111400604</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G1778" t="n">
-        <v>0.567934095859528</v>
+        <v>0.567934036254883</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1781" t="n">
-        <v>0.575293898582458</v>
+        <v>0.575293958187103</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>0.944999992847443</v>
       </c>
       <c r="G1786" t="n">
-        <v>0.579587161540985</v>
+        <v>0.57958710193634</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46883,7 +46883,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G1789" t="n">
-        <v>0.624359488487244</v>
+        <v>0.624359548091888</v>
       </c>
       <c r="H1789" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1790" t="n">
-        <v>0.619452893733978</v>
+        <v>0.619452953338623</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>1.0460000038147</v>
       </c>
       <c r="G1791" t="n">
-        <v>0.641532480716705</v>
+        <v>0.641532421112061</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1792" t="n">
-        <v>0.656252145767212</v>
+        <v>0.656252205371857</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1795" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1802" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1803" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1804" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G1809" t="n">
-        <v>0.721264064311981</v>
+        <v>0.721264004707336</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1810" t="n">
-        <v>0.723717212677002</v>
+        <v>0.723717272281647</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G1811" t="n">
-        <v>0.721264064311981</v>
+        <v>0.721264004707336</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1812" t="n">
-        <v>0.7323037981987</v>
+        <v>0.732303738594055</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1813" t="n">
-        <v>0.726170539855957</v>
+        <v>0.726170599460602</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1815" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1819" t="n">
-        <v>0.726170539855957</v>
+        <v>0.726170599460602</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>1.11800003051758</v>
       </c>
       <c r="G1822" t="n">
-        <v>0.68569153547287</v>
+        <v>0.68569141626358</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>1.12800002098083</v>
       </c>
       <c r="G1823" t="n">
-        <v>0.691824615001678</v>
+        <v>0.691824674606323</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1824" t="n">
-        <v>0.668518483638763</v>
+        <v>0.668518543243408</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1826" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1827" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1831" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1834" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G1836" t="n">
-        <v>0.628039479255676</v>
+        <v>0.628039419651031</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G1838" t="n">
-        <v>0.647665619850159</v>
+        <v>0.647665679454803</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>1.11800003051758</v>
       </c>
       <c r="G1845" t="n">
-        <v>0.68569153547287</v>
+        <v>0.68569141626358</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1846" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>1.12399995326996</v>
       </c>
       <c r="G1848" t="n">
-        <v>0.689371407032013</v>
+        <v>0.689371347427368</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1849" t="n">
-        <v>0.686918079853058</v>
+        <v>0.686918139457703</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G1850" t="n">
-        <v>0.697957873344421</v>
+        <v>0.697957813739777</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1851" t="n">
-        <v>0.686918079853058</v>
+        <v>0.686918139457703</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1852" t="n">
-        <v>0.686918079853058</v>
+        <v>0.686918139457703</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G1853" t="n">
-        <v>0.708997666835785</v>
+        <v>0.70899760723114</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1856" t="n">
-        <v>0.754383206367493</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1860" t="n">
-        <v>0.7323037981987</v>
+        <v>0.732303738594055</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1861" t="n">
-        <v>0.723717212677002</v>
+        <v>0.723717272281647</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>1.15400004386902</v>
       </c>
       <c r="G1875" t="n">
-        <v>0.707770943641663</v>
+        <v>0.707771003246307</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>1.15400004386902</v>
       </c>
       <c r="G1876" t="n">
-        <v>0.707770943641663</v>
+        <v>0.707771003246307</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>1.15400004386902</v>
       </c>
       <c r="G1878" t="n">
-        <v>0.707770943641663</v>
+        <v>0.707771003246307</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49379,7 +49379,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.686918079853058</v>
+        <v>0.686918139457703</v>
       </c>
       <c r="H1885" t="s">
         <v>8</v>
@@ -49561,7 +49561,7 @@
         <v>1.15799999237061</v>
       </c>
       <c r="G1892" t="n">
-        <v>0.710224211215973</v>
+        <v>0.710224270820618</v>
       </c>
       <c r="H1892" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G1893" t="n">
-        <v>0.721264064311981</v>
+        <v>0.721264004707336</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G1897" t="n">
-        <v>0.718810796737671</v>
+        <v>0.718810737133026</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G1898" t="n">
-        <v>0.721264064311981</v>
+        <v>0.721264004707336</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49795,7 +49795,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G1901" t="n">
-        <v>0.721264064311981</v>
+        <v>0.721264004707336</v>
       </c>
       <c r="H1901" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G1902" t="n">
-        <v>0.721264064311981</v>
+        <v>0.721264004707336</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -49873,7 +49873,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G1904" t="n">
-        <v>0.721264064311981</v>
+        <v>0.721264004707336</v>
       </c>
       <c r="H1904" t="s">
         <v>8</v>
@@ -50003,7 +50003,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1909" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1909" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1910" t="n">
-        <v>0.754383206367493</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50081,7 +50081,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1912" t="n">
-        <v>0.764196395874023</v>
+        <v>0.764196455478668</v>
       </c>
       <c r="H1912" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1914" t="n">
-        <v>0.759289920330048</v>
+        <v>0.759289860725403</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1915" t="n">
-        <v>0.764196395874023</v>
+        <v>0.764196455478668</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50185,7 +50185,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G1916" t="n">
-        <v>0.767876327037811</v>
+        <v>0.767876267433167</v>
       </c>
       <c r="H1916" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>1.28799998760223</v>
       </c>
       <c r="G1919" t="n">
-        <v>0.789955854415894</v>
+        <v>0.789955794811249</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1920" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50367,7 +50367,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1923" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1923" t="s">
         <v>8</v>
@@ -50393,7 +50393,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1924" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1924" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1925" t="n">
-        <v>0.821848511695862</v>
+        <v>0.821848452091217</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50445,7 +50445,7 @@
         <v>1.28799998760223</v>
       </c>
       <c r="G1926" t="n">
-        <v>0.789955854415894</v>
+        <v>0.789955794811249</v>
       </c>
       <c r="H1926" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G1929" t="n">
-        <v>0.819395184516907</v>
+        <v>0.819395124912262</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50549,7 +50549,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G1930" t="n">
-        <v>0.79976898431778</v>
+        <v>0.799768924713135</v>
       </c>
       <c r="H1930" t="s">
         <v>8</v>
@@ -50627,7 +50627,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G1933" t="n">
-        <v>0.750703275203705</v>
+        <v>0.75070333480835</v>
       </c>
       <c r="H1933" t="s">
         <v>8</v>
@@ -50705,7 +50705,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1936" t="n">
-        <v>0.735983729362488</v>
+        <v>0.735983669757843</v>
       </c>
       <c r="H1936" t="s">
         <v>8</v>
@@ -50757,7 +50757,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1938" t="n">
-        <v>0.759289920330048</v>
+        <v>0.759289860725403</v>
       </c>
       <c r="H1938" t="s">
         <v>8</v>
@@ -50809,7 +50809,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G1940" t="n">
-        <v>0.767876327037811</v>
+        <v>0.767876267433167</v>
       </c>
       <c r="H1940" t="s">
         <v>8</v>
@@ -50887,7 +50887,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1943" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1943" t="s">
         <v>8</v>
@@ -51121,7 +51121,7 @@
         <v>1.26199996471405</v>
       </c>
       <c r="G1952" t="n">
-        <v>0.774009466171265</v>
+        <v>0.774009525775909</v>
       </c>
       <c r="H1952" t="s">
         <v>8</v>
@@ -51199,7 +51199,7 @@
         <v>1.28799998760223</v>
       </c>
       <c r="G1955" t="n">
-        <v>0.789955854415894</v>
+        <v>0.789955794811249</v>
       </c>
       <c r="H1955" t="s">
         <v>8</v>
@@ -51251,7 +51251,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1957" t="n">
-        <v>0.772782802581787</v>
+        <v>0.772782921791077</v>
       </c>
       <c r="H1957" t="s">
         <v>8</v>
@@ -51407,7 +51407,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G1963" t="n">
-        <v>0.79976898431778</v>
+        <v>0.799768924713135</v>
       </c>
       <c r="H1963" t="s">
         <v>8</v>
@@ -51459,7 +51459,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1965" t="n">
-        <v>0.821848511695862</v>
+        <v>0.821848452091217</v>
       </c>
       <c r="H1965" t="s">
         <v>8</v>
@@ -51563,7 +51563,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G1969" t="n">
-        <v>0.924886167049408</v>
+        <v>0.924886226654053</v>
       </c>
       <c r="H1969" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1971" t="n">
-        <v>0.907713294029236</v>
+        <v>0.907713174819946</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51667,7 +51667,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G1973" t="n">
-        <v>0.912619769573212</v>
+        <v>0.912619829177856</v>
       </c>
       <c r="H1973" t="s">
         <v>8</v>
@@ -51693,7 +51693,7 @@
         <v>1.50399994850159</v>
       </c>
       <c r="G1974" t="n">
-        <v>0.922432899475098</v>
+        <v>0.922432839870453</v>
       </c>
       <c r="H1974" t="s">
         <v>8</v>
@@ -51745,7 +51745,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1976" t="n">
-        <v>0.926112830638885</v>
+        <v>0.92611289024353</v>
       </c>
       <c r="H1976" t="s">
         <v>8</v>
@@ -51771,7 +51771,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1977" t="n">
-        <v>0.928566098213196</v>
+        <v>0.928566157817841</v>
       </c>
       <c r="H1977" t="s">
         <v>8</v>
@@ -51797,7 +51797,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G1978" t="n">
-        <v>0.958005487918854</v>
+        <v>0.958005428314209</v>
       </c>
       <c r="H1978" t="s">
         <v>8</v>
@@ -51823,7 +51823,7 @@
         <v>1.58800005912781</v>
       </c>
       <c r="G1979" t="n">
-        <v>0.973951756954193</v>
+        <v>0.973951816558838</v>
       </c>
       <c r="H1979" t="s">
         <v>8</v>
@@ -51901,7 +51901,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G1982" t="n">
-        <v>1.0070708990097</v>
+        <v>1.00707101821899</v>
       </c>
       <c r="H1982" t="s">
         <v>8</v>
@@ -51953,7 +51953,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1984" t="n">
-        <v>1.02301740646362</v>
+        <v>1.02301728725433</v>
       </c>
       <c r="H1984" t="s">
         <v>8</v>
@@ -52083,7 +52083,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1989" t="n">
-        <v>0.99357795715332</v>
+        <v>0.993577897548676</v>
       </c>
       <c r="H1989" t="s">
         <v>8</v>
@@ -52109,7 +52109,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G1990" t="n">
-        <v>0.986218214035034</v>
+        <v>0.986218154430389</v>
       </c>
       <c r="H1990" t="s">
         <v>8</v>
@@ -52213,7 +52213,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1994" t="n">
-        <v>0.937152504920959</v>
+        <v>0.937152624130249</v>
       </c>
       <c r="H1994" t="s">
         <v>8</v>
@@ -52265,7 +52265,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G1996" t="n">
-        <v>0.951872289180756</v>
+        <v>0.951872229576111</v>
       </c>
       <c r="H1996" t="s">
         <v>8</v>
@@ -52291,7 +52291,7 @@
         <v>1.57799994945526</v>
       </c>
       <c r="G1997" t="n">
-        <v>0.96781849861145</v>
+        <v>0.967818558216095</v>
       </c>
       <c r="H1997" t="s">
         <v>8</v>
@@ -52317,7 +52317,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1998" t="n">
-        <v>0.965365290641785</v>
+        <v>0.96536523103714</v>
       </c>
       <c r="H1998" t="s">
         <v>8</v>
@@ -52343,7 +52343,7 @@
         <v>1.5</v>
       </c>
       <c r="G1999" t="n">
-        <v>0.919979631900787</v>
+        <v>0.919979512691498</v>
       </c>
       <c r="H1999" t="s">
         <v>8</v>
@@ -52369,7 +52369,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G2000" t="n">
-        <v>0.950645565986633</v>
+        <v>0.950645625591278</v>
       </c>
       <c r="H2000" t="s">
         <v>8</v>
@@ -52395,7 +52395,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G2001" t="n">
-        <v>0.950645565986633</v>
+        <v>0.950645625591278</v>
       </c>
       <c r="H2001" t="s">
         <v>8</v>
@@ -52447,7 +52447,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G2003" t="n">
-        <v>0.980084955692291</v>
+        <v>0.980085015296936</v>
       </c>
       <c r="H2003" t="s">
         <v>8</v>
@@ -52473,7 +52473,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G2004" t="n">
-        <v>1.01075088977814</v>
+        <v>1.01075100898743</v>
       </c>
       <c r="H2004" t="s">
         <v>8</v>
@@ -52629,7 +52629,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2010" t="n">
-        <v>0.99357795715332</v>
+        <v>0.993577897548676</v>
       </c>
       <c r="H2010" t="s">
         <v>8</v>
@@ -52681,7 +52681,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G2012" t="n">
-        <v>0.98376476764679</v>
+        <v>0.983764886856079</v>
       </c>
       <c r="H2012" t="s">
         <v>8</v>
@@ -52733,7 +52733,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G2014" t="n">
-        <v>0.98376476764679</v>
+        <v>0.983764886856079</v>
       </c>
       <c r="H2014" t="s">
         <v>8</v>
@@ -52785,7 +52785,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G2016" t="n">
-        <v>0.9886714220047</v>
+        <v>0.988671362400055</v>
       </c>
       <c r="H2016" t="s">
         <v>8</v>
@@ -52811,7 +52811,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G2017" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H2017" t="s">
         <v>8</v>
@@ -52941,7 +52941,7 @@
         <v>1.78799998760223</v>
       </c>
       <c r="G2022" t="n">
-        <v>1.0966157913208</v>
+        <v>1.09661567211151</v>
       </c>
       <c r="H2022" t="s">
         <v>8</v>
@@ -53071,7 +53071,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G2027" t="n">
-        <v>1.20087993144989</v>
+        <v>1.20088005065918</v>
       </c>
       <c r="H2027" t="s">
         <v>8</v>
@@ -53149,7 +53149,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G2030" t="n">
-        <v>1.26650536060333</v>
+        <v>1.26650524139404</v>
       </c>
       <c r="H2030" t="s">
         <v>8</v>
@@ -53227,7 +53227,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2033" t="n">
-        <v>1.23277270793915</v>
+        <v>1.23277258872986</v>
       </c>
       <c r="H2033" t="s">
         <v>8</v>
@@ -53253,7 +53253,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2034" t="n">
-        <v>1.23890578746796</v>
+        <v>1.23890590667725</v>
       </c>
       <c r="H2034" t="s">
         <v>8</v>
@@ -53279,7 +53279,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G2035" t="n">
-        <v>1.24197244644165</v>
+        <v>1.24197256565094</v>
       </c>
       <c r="H2035" t="s">
         <v>8</v>
@@ -53331,7 +53331,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G2037" t="n">
-        <v>1.22970616817474</v>
+        <v>1.22970604896545</v>
       </c>
       <c r="H2037" t="s">
         <v>8</v>
@@ -53409,7 +53409,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G2040" t="n">
-        <v>1.18493366241455</v>
+        <v>1.18493378162384</v>
       </c>
       <c r="H2040" t="s">
         <v>8</v>
@@ -53435,7 +53435,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2041" t="n">
-        <v>1.17757380008698</v>
+        <v>1.17757391929626</v>
       </c>
       <c r="H2041" t="s">
         <v>8</v>
@@ -53539,7 +53539,7 @@
         <v>2</v>
       </c>
       <c r="G2045" t="n">
-        <v>1.22663950920105</v>
+        <v>1.22663938999176</v>
       </c>
       <c r="H2045" t="s">
         <v>8</v>
@@ -53565,7 +53565,7 @@
         <v>2</v>
       </c>
       <c r="G2046" t="n">
-        <v>1.22663950920105</v>
+        <v>1.22663938999176</v>
       </c>
       <c r="H2046" t="s">
         <v>8</v>
@@ -53643,7 +53643,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2049" t="n">
-        <v>1.18370711803436</v>
+        <v>1.18370699882507</v>
       </c>
       <c r="H2049" t="s">
         <v>8</v>
@@ -53669,7 +53669,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G2050" t="n">
-        <v>1.14322805404663</v>
+        <v>1.14322793483734</v>
       </c>
       <c r="H2050" t="s">
         <v>8</v>
@@ -53721,7 +53721,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G2052" t="n">
-        <v>1.14445459842682</v>
+        <v>1.14445471763611</v>
       </c>
       <c r="H2052" t="s">
         <v>8</v>
@@ -53747,7 +53747,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G2053" t="n">
-        <v>1.13709485530853</v>
+        <v>1.13709473609924</v>
       </c>
       <c r="H2053" t="s">
         <v>8</v>
@@ -53851,7 +53851,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G2057" t="n">
-        <v>1.14200127124786</v>
+        <v>1.14200139045715</v>
       </c>
       <c r="H2057" t="s">
         <v>8</v>
@@ -53929,7 +53929,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G2060" t="n">
-        <v>1.10274887084961</v>
+        <v>1.1027489900589</v>
       </c>
       <c r="H2060" t="s">
         <v>8</v>
@@ -53981,7 +53981,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G2062" t="n">
-        <v>1.13709485530853</v>
+        <v>1.13709473609924</v>
       </c>
       <c r="H2062" t="s">
         <v>8</v>
@@ -54085,7 +54085,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G2066" t="n">
-        <v>1.15794765949249</v>
+        <v>1.1579475402832</v>
       </c>
       <c r="H2066" t="s">
         <v>8</v>
@@ -54111,7 +54111,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2067" t="n">
-        <v>1.16530752182007</v>
+        <v>1.16530740261078</v>
       </c>
       <c r="H2067" t="s">
         <v>8</v>
@@ -54163,7 +54163,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G2069" t="n">
-        <v>1.16162765026093</v>
+        <v>1.16162753105164</v>
       </c>
       <c r="H2069" t="s">
         <v>8</v>
@@ -54345,7 +54345,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G2076" t="n">
-        <v>1.70502889156342</v>
+        <v>1.70502877235413</v>
       </c>
       <c r="H2076" t="s">
         <v>8</v>
@@ -54423,7 +54423,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2079" t="n">
-        <v>1.94422352313995</v>
+        <v>1.94422376155853</v>
       </c>
       <c r="H2079" t="s">
         <v>8</v>
@@ -54449,7 +54449,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G2080" t="n">
-        <v>1.89822447299957</v>
+        <v>1.89822459220886</v>
       </c>
       <c r="H2080" t="s">
         <v>8</v>
@@ -54475,7 +54475,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G2081" t="n">
-        <v>1.87675845623016</v>
+        <v>1.87675857543945</v>
       </c>
       <c r="H2081" t="s">
         <v>8</v>
@@ -54579,7 +54579,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G2085" t="n">
-        <v>1.74182784557343</v>
+        <v>1.74182796478271</v>
       </c>
       <c r="H2085" t="s">
         <v>8</v>
@@ -54605,7 +54605,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G2086" t="n">
-        <v>1.7448947429657</v>
+        <v>1.74489462375641</v>
       </c>
       <c r="H2086" t="s">
         <v>8</v>
@@ -54657,7 +54657,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G2088" t="n">
-        <v>1.83689260482788</v>
+        <v>1.83689248561859</v>
       </c>
       <c r="H2088" t="s">
         <v>8</v>
@@ -54683,7 +54683,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2089" t="n">
-        <v>1.90129113197327</v>
+        <v>1.90129125118256</v>
       </c>
       <c r="H2089" t="s">
         <v>8</v>
@@ -54709,7 +54709,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2090" t="n">
-        <v>1.90129113197327</v>
+        <v>1.90129125118256</v>
       </c>
       <c r="H2090" t="s">
         <v>8</v>
@@ -54761,7 +54761,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G2092" t="n">
-        <v>1.90435767173767</v>
+        <v>1.90435779094696</v>
       </c>
       <c r="H2092" t="s">
         <v>8</v>
@@ -54865,7 +54865,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G2096" t="n">
-        <v>1.92889058589935</v>
+        <v>1.92889046669006</v>
       </c>
       <c r="H2096" t="s">
         <v>8</v>
@@ -54969,7 +54969,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G2100" t="n">
-        <v>1.92275738716125</v>
+        <v>1.92275750637054</v>
       </c>
       <c r="H2100" t="s">
         <v>8</v>
@@ -55047,7 +55047,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G2103" t="n">
-        <v>1.90435767173767</v>
+        <v>1.90435779094696</v>
       </c>
       <c r="H2103" t="s">
         <v>8</v>
@@ -55151,7 +55151,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2107" t="n">
-        <v>2.00555539131165</v>
+        <v>2.00555562973022</v>
       </c>
       <c r="H2107" t="s">
         <v>8</v>
@@ -55177,7 +55177,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G2108" t="n">
-        <v>1.95342350006104</v>
+        <v>1.95342314243317</v>
       </c>
       <c r="H2108" t="s">
         <v>8</v>
@@ -55203,7 +55203,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G2109" t="n">
-        <v>1.95342350006104</v>
+        <v>1.95342314243317</v>
       </c>
       <c r="H2109" t="s">
         <v>8</v>
@@ -55229,7 +55229,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G2110" t="n">
-        <v>1.92889058589935</v>
+        <v>1.92889046669006</v>
       </c>
       <c r="H2110" t="s">
         <v>8</v>
@@ -55255,7 +55255,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2111" t="n">
-        <v>1.92582404613495</v>
+        <v>1.92582392692566</v>
       </c>
       <c r="H2111" t="s">
         <v>8</v>
@@ -55281,7 +55281,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G2112" t="n">
-        <v>1.92275738716125</v>
+        <v>1.92275750637054</v>
       </c>
       <c r="H2112" t="s">
         <v>8</v>
@@ -55307,7 +55307,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2113" t="n">
-        <v>1.88902473449707</v>
+        <v>1.88902485370636</v>
       </c>
       <c r="H2113" t="s">
         <v>8</v>
@@ -55333,7 +55333,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2114" t="n">
-        <v>1.88902473449707</v>
+        <v>1.88902485370636</v>
       </c>
       <c r="H2114" t="s">
         <v>8</v>
@@ -55385,7 +55385,7 @@
         <v>3</v>
       </c>
       <c r="G2116" t="n">
-        <v>1.83995926380157</v>
+        <v>1.839959025383</v>
       </c>
       <c r="H2116" t="s">
         <v>8</v>
@@ -55411,7 +55411,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G2117" t="n">
-        <v>1.77249395847321</v>
+        <v>1.7724940776825</v>
       </c>
       <c r="H2117" t="s">
         <v>8</v>
@@ -55463,7 +55463,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G2119" t="n">
-        <v>1.80622661113739</v>
+        <v>1.8062264919281</v>
       </c>
       <c r="H2119" t="s">
         <v>8</v>
@@ -55489,7 +55489,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G2120" t="n">
-        <v>1.7694274187088</v>
+        <v>1.76942729949951</v>
       </c>
       <c r="H2120" t="s">
         <v>8</v>
@@ -55593,7 +55593,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G2124" t="n">
-        <v>2.0125093460083</v>
+        <v>2.01250958442688</v>
       </c>
       <c r="H2124" t="s">
         <v>8</v>
@@ -55619,7 +55619,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G2125" t="n">
-        <v>1.96318316459656</v>
+        <v>1.96318304538727</v>
       </c>
       <c r="H2125" t="s">
         <v>8</v>
@@ -55671,7 +55671,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G2127" t="n">
-        <v>1.79218554496765</v>
+        <v>1.79218566417694</v>
       </c>
       <c r="H2127" t="s">
         <v>8</v>
@@ -55801,7 +55801,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G2132" t="n">
-        <v>1.83164668083191</v>
+        <v>1.8316468000412</v>
       </c>
       <c r="H2132" t="s">
         <v>8</v>
@@ -55879,7 +55879,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G2135" t="n">
-        <v>1.79218554496765</v>
+        <v>1.79218566417694</v>
       </c>
       <c r="H2135" t="s">
         <v>8</v>
@@ -55905,7 +55905,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G2136" t="n">
-        <v>1.79218554496765</v>
+        <v>1.79218566417694</v>
       </c>
       <c r="H2136" t="s">
         <v>8</v>
@@ -55957,7 +55957,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G2138" t="n">
-        <v>1.95660626888275</v>
+        <v>1.95660638809204</v>
       </c>
       <c r="H2138" t="s">
         <v>8</v>
@@ -55983,7 +55983,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G2139" t="n">
-        <v>1.95002961158752</v>
+        <v>1.95002949237823</v>
       </c>
       <c r="H2139" t="s">
         <v>8</v>
@@ -56009,7 +56009,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G2140" t="n">
-        <v>1.92043387889862</v>
+        <v>1.92043375968933</v>
       </c>
       <c r="H2140" t="s">
         <v>8</v>
@@ -56035,7 +56035,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G2141" t="n">
-        <v>1.93358755111694</v>
+        <v>1.93358743190765</v>
       </c>
       <c r="H2141" t="s">
         <v>8</v>
@@ -56061,7 +56061,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G2142" t="n">
-        <v>1.92372226715088</v>
+        <v>1.92372214794159</v>
       </c>
       <c r="H2142" t="s">
         <v>8</v>
@@ -56113,7 +56113,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G2144" t="n">
-        <v>1.90728032588959</v>
+        <v>1.9072802066803</v>
       </c>
       <c r="H2144" t="s">
         <v>8</v>
@@ -56165,7 +56165,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G2146" t="n">
-        <v>1.91385698318481</v>
+        <v>1.9138571023941</v>
       </c>
       <c r="H2146" t="s">
         <v>8</v>
@@ -56191,7 +56191,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G2147" t="n">
-        <v>1.91056859493256</v>
+        <v>1.91056847572327</v>
       </c>
       <c r="H2147" t="s">
         <v>8</v>
@@ -56217,7 +56217,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G2148" t="n">
-        <v>1.91056859493256</v>
+        <v>1.91056847572327</v>
       </c>
       <c r="H2148" t="s">
         <v>8</v>
@@ -56243,7 +56243,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G2149" t="n">
-        <v>1.91714537143707</v>
+        <v>1.91714549064636</v>
       </c>
       <c r="H2149" t="s">
         <v>8</v>
@@ -56295,7 +56295,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G2151" t="n">
-        <v>1.87110769748688</v>
+        <v>1.87110757827759</v>
       </c>
       <c r="H2151" t="s">
         <v>8</v>
@@ -56373,7 +56373,7 @@
         <v>3</v>
       </c>
       <c r="G2154" t="n">
-        <v>1.97304844856262</v>
+        <v>1.97304832935333</v>
       </c>
       <c r="H2154" t="s">
         <v>8</v>
@@ -56607,7 +56607,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2163" t="n">
-        <v>2.22296786308289</v>
+        <v>2.22296810150146</v>
       </c>
       <c r="H2163" t="s">
         <v>8</v>
@@ -56633,7 +56633,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G2164" t="n">
-        <v>2.17692995071411</v>
+        <v>2.17693018913269</v>
       </c>
       <c r="H2164" t="s">
         <v>8</v>
@@ -56659,7 +56659,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G2165" t="n">
-        <v>2.20981431007385</v>
+        <v>2.20981407165527</v>
       </c>
       <c r="H2165" t="s">
         <v>8</v>
@@ -56685,7 +56685,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2166" t="n">
-        <v>2.22296786308289</v>
+        <v>2.22296810150146</v>
       </c>
       <c r="H2166" t="s">
         <v>8</v>
@@ -56763,7 +56763,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G2169" t="n">
-        <v>2.17692995071411</v>
+        <v>2.17693018913269</v>
       </c>
       <c r="H2169" t="s">
         <v>8</v>
@@ -71378,6 +71378,32 @@
         <v>2.01999998092651</v>
       </c>
       <c r="H2731" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>168924</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>2.07500004768372</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>2.02500009536743</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>2.04500007629395</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>2.03500008583069</v>
+      </c>
+      <c r="G2732" t="n">
+        <v>2.03500008583069</v>
+      </c>
+      <c r="H2732" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SGF.MI.xlsx
+++ b/data/SGF.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>2.02999997138977</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>2.05999994277954</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>174302</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>2.10999989509583</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>2.0699999332428</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>2.0699999332428</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SGF.MI.xlsx
+++ b/data/SGF.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>2.0699999332428</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>2.08999991416931</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>304097</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>2.03500008583069</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>2.07500004768372</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SGF.MI.xlsx
+++ b/data/SGF.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>2.07500004768372</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>2.0550000667572</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>503284</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>2.02999997138977</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>1.9539999961853</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>2.02999997138977</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SGF.MI.xlsx
+++ b/data/SGF.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>2.02999997138977</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>1.97599995136261</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>309968</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>2.01500010490417</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>1.98199999332428</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SGF.MI.xlsx
+++ b/data/SGF.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>583746</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>2.03500008583069</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>1.92999994754791</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>1.97399997711182</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>1.92999994754791</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SGF.MI.xlsx
+++ b/data/SGF.MI.xlsx
@@ -71667,6 +71667,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>966462</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>2.02999997138977</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>1.93599998950958</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>2.02500009536743</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>1.97399997711182</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>1.97399997711182</v>
+      </c>
+      <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SGF.MI.xlsx
+++ b/data/SGF.MI.xlsx
@@ -499,7 +499,7 @@
         <v>1.93299996852875</v>
       </c>
       <c r="G5" t="n">
-        <v>1.18554699420929</v>
+        <v>1.18554711341858</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G8" t="n">
-        <v>1.17389404773712</v>
+        <v>1.17389392852783</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G9" t="n">
-        <v>1.15058779716492</v>
+        <v>1.15058791637421</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G10" t="n">
-        <v>1.12850844860077</v>
+        <v>1.12850832939148</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G13" t="n">
-        <v>1.09293580055237</v>
+        <v>1.09293568134308</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>1.00891101360321</v>
+        <v>1.00891089439392</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>1.77400004863739</v>
       </c>
       <c r="G18" t="n">
-        <v>1.08802914619446</v>
+        <v>1.08802926540375</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G27" t="n">
-        <v>0.841474711894989</v>
+        <v>0.841474652290344</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>1.42400002479553</v>
       </c>
       <c r="G29" t="n">
-        <v>0.873367309570312</v>
+        <v>0.873367249965668</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G30" t="n">
-        <v>0.858647584915161</v>
+        <v>0.858647644519806</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G32" t="n">
-        <v>0.981311559677124</v>
+        <v>0.981311500072479</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G33" t="n">
-        <v>0.950645625591278</v>
+        <v>0.950645565986633</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>1.56099998950958</v>
       </c>
       <c r="G34" t="n">
-        <v>0.95739209651947</v>
+        <v>0.957392036914825</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G35" t="n">
-        <v>0.941445767879486</v>
+        <v>0.941445708274841</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>1.50399994850159</v>
       </c>
       <c r="G36" t="n">
-        <v>0.922432899475098</v>
+        <v>0.922432839870453</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G37" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G38" t="n">
-        <v>0.941445767879486</v>
+        <v>0.941445708274841</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>1.52699995040894</v>
       </c>
       <c r="G41" t="n">
-        <v>0.936539173126221</v>
+        <v>0.936539232730865</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>1.5789999961853</v>
       </c>
       <c r="G44" t="n">
-        <v>0.968431770801544</v>
+        <v>0.968431890010834</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G49" t="n">
-        <v>1.00891101360321</v>
+        <v>1.00891089439392</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G53" t="n">
-        <v>0.960458636283875</v>
+        <v>0.960458695888519</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>1.58299994468689</v>
       </c>
       <c r="G54" t="n">
-        <v>0.970885097980499</v>
+        <v>0.970885157585144</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G55" t="n">
-        <v>0.956165432929993</v>
+        <v>0.956165492534637</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G57" t="n">
-        <v>0.926112830638885</v>
+        <v>0.926112711429596</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>1.4210000038147</v>
       </c>
       <c r="G59" t="n">
-        <v>0.871527373790741</v>
+        <v>0.871527314186096</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G60" t="n">
-        <v>0.853741049766541</v>
+        <v>0.853741109371185</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>1.34300005435944</v>
       </c>
       <c r="G61" t="n">
-        <v>0.823688387870789</v>
+        <v>0.823688447475433</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G66" t="n">
-        <v>0.815715253353119</v>
+        <v>0.815715193748474</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G67" t="n">
-        <v>0.818781912326813</v>
+        <v>0.818781852722168</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G68" t="n">
-        <v>0.794249057769775</v>
+        <v>0.79424911737442</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G69" t="n">
-        <v>0.832888305187225</v>
+        <v>0.832888185977936</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G70" t="n">
-        <v>0.849447846412659</v>
+        <v>0.849447786808014</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>1.38300001621246</v>
       </c>
       <c r="G71" t="n">
-        <v>0.848221242427826</v>
+        <v>0.848221182823181</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>1.43299996852875</v>
       </c>
       <c r="G73" t="n">
-        <v>0.878887116909027</v>
+        <v>0.878887176513672</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G76" t="n">
-        <v>0.852514445781708</v>
+        <v>0.852514386177063</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>1.43099999427795</v>
       </c>
       <c r="G77" t="n">
-        <v>0.877660512924194</v>
+        <v>0.877660572528839</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G78" t="n">
-        <v>0.875207245349884</v>
+        <v>0.875207304954529</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>1.42299997806549</v>
       </c>
       <c r="G79" t="n">
-        <v>0.872753977775574</v>
+        <v>0.872754037380219</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G81" t="n">
-        <v>0.868460774421692</v>
+        <v>0.868460714817047</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G83" t="n">
-        <v>0.943285763263702</v>
+        <v>0.943285644054413</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G84" t="n">
-        <v>0.977631688117981</v>
+        <v>0.977631628513336</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G85" t="n">
-        <v>0.993578016757965</v>
+        <v>0.99357795715332</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G86" t="n">
-        <v>0.951258957386017</v>
+        <v>0.951258897781372</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G87" t="n">
-        <v>0.951258957386017</v>
+        <v>0.951258897781372</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G88" t="n">
-        <v>0.951258957386017</v>
+        <v>0.951258897781372</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G89" t="n">
-        <v>0.951258957386017</v>
+        <v>0.951258897781372</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>1.50100004673004</v>
       </c>
       <c r="G90" t="n">
-        <v>0.920592904090881</v>
+        <v>0.920592963695526</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G93" t="n">
-        <v>0.97824501991272</v>
+        <v>0.978245079517365</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G94" t="n">
-        <v>0.992351353168488</v>
+        <v>0.992351412773132</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G95" t="n">
-        <v>1.00216436386108</v>
+        <v>1.00216448307037</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>1.6710000038147</v>
       </c>
       <c r="G96" t="n">
-        <v>1.02485728263855</v>
+        <v>1.02485716342926</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G98" t="n">
-        <v>0.943285763263702</v>
+        <v>0.943285644054413</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G99" t="n">
-        <v>0.935312628746033</v>
+        <v>0.935312569141388</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G102" t="n">
-        <v>1.02424395084381</v>
+        <v>1.0242440700531</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G103" t="n">
-        <v>1.0917090177536</v>
+        <v>1.09170913696289</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G110" t="n">
-        <v>0.999711155891418</v>
+        <v>0.999711215496063</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G111" t="n">
-        <v>1.0070708990097</v>
+        <v>1.00707101821899</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>1.625</v>
       </c>
       <c r="G112" t="n">
-        <v>0.996644556522369</v>
+        <v>0.996644616127014</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>1.60099995136261</v>
       </c>
       <c r="G113" t="n">
-        <v>0.981924891471863</v>
+        <v>0.981924831867218</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G114" t="n">
-        <v>0.935312628746033</v>
+        <v>0.935312569141388</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>1.39300000667572</v>
       </c>
       <c r="G115" t="n">
-        <v>0.854354381561279</v>
+        <v>0.854354321956635</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G116" t="n">
-        <v>0.806515514850616</v>
+        <v>0.806515455245972</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G119" t="n">
-        <v>0.792409121990204</v>
+        <v>0.792409062385559</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>1.36899995803833</v>
       </c>
       <c r="G120" t="n">
-        <v>0.839634656906128</v>
+        <v>0.839634716510773</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G121" t="n">
-        <v>0.880727171897888</v>
+        <v>0.880727112293243</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G122" t="n">
-        <v>0.875207245349884</v>
+        <v>0.875207304954529</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G123" t="n">
-        <v>0.880113840103149</v>
+        <v>0.880113780498505</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G124" t="n">
-        <v>0.81264865398407</v>
+        <v>0.812648713588715</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>1.25699996948242</v>
       </c>
       <c r="G127" t="n">
-        <v>0.77094292640686</v>
+        <v>0.770942866802216</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G128" t="n">
-        <v>0.806515514850616</v>
+        <v>0.806515455245972</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>1.30900001525879</v>
       </c>
       <c r="G129" t="n">
-        <v>0.802835524082184</v>
+        <v>0.802835583686829</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G131" t="n">
-        <v>0.725557267665863</v>
+        <v>0.725557208061218</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G132" t="n">
-        <v>0.711450815200806</v>
+        <v>0.71145087480545</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G133" t="n">
-        <v>0.713904201984406</v>
+        <v>0.713904142379761</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G135" t="n">
-        <v>0.771556258201599</v>
+        <v>0.771556198596954</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>1.30299997329712</v>
       </c>
       <c r="G136" t="n">
-        <v>0.799155652523041</v>
+        <v>0.799155533313751</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G137" t="n">
-        <v>0.803448796272278</v>
+        <v>0.803448855876923</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G140" t="n">
-        <v>0.858647584915161</v>
+        <v>0.858647644519806</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G141" t="n">
-        <v>0.85128778219223</v>
+        <v>0.851287841796875</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G142" t="n">
-        <v>0.861100912094116</v>
+        <v>0.861100971698761</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G148" t="n">
-        <v>0.935312628746033</v>
+        <v>0.935312569141388</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G149" t="n">
-        <v>0.932245969772339</v>
+        <v>0.932246029376984</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G150" t="n">
-        <v>0.935925960540771</v>
+        <v>0.935925900936127</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.54900002479553</v>
       </c>
       <c r="G152" t="n">
-        <v>0.950032293796539</v>
+        <v>0.950032234191895</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G153" t="n">
-        <v>0.956778764724731</v>
+        <v>0.956778824329376</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G156" t="n">
-        <v>1.0070708990097</v>
+        <v>1.00707101821899</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G158" t="n">
-        <v>1.02424395084381</v>
+        <v>1.0242440700531</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>1.66100001335144</v>
       </c>
       <c r="G162" t="n">
-        <v>1.01872396469116</v>
+        <v>1.01872408390045</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G163" t="n">
-        <v>1.00461781024933</v>
+        <v>1.00461769104004</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>1.66100001335144</v>
       </c>
       <c r="G164" t="n">
-        <v>1.01872396469116</v>
+        <v>1.01872408390045</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G165" t="n">
-        <v>1.0365104675293</v>
+        <v>1.03651034832001</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G166" t="n">
-        <v>1.03896367549896</v>
+        <v>1.03896355628967</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G169" t="n">
-        <v>1.05491006374359</v>
+        <v>1.0549099445343</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G170" t="n">
-        <v>1.04571008682251</v>
+        <v>1.0457102060318</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G172" t="n">
-        <v>1.02363061904907</v>
+        <v>1.02363073825836</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>1.66700005531311</v>
       </c>
       <c r="G173" t="n">
-        <v>1.02240395545959</v>
+        <v>1.02240407466888</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>1.75800001621246</v>
       </c>
       <c r="G174" t="n">
-        <v>1.07821619510651</v>
+        <v>1.07821607589722</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G176" t="n">
-        <v>1.0917090177536</v>
+        <v>1.09170913696289</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G179" t="n">
-        <v>1.08250939846039</v>
+        <v>1.0825092792511</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G181" t="n">
-        <v>1.06472289562225</v>
+        <v>1.06472301483154</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G184" t="n">
-        <v>1.05491006374359</v>
+        <v>1.0549099445343</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>1.77400004863739</v>
       </c>
       <c r="G187" t="n">
-        <v>1.08802914619446</v>
+        <v>1.08802926540375</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G189" t="n">
-        <v>1.0917090177536</v>
+        <v>1.09170913696289</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G191" t="n">
-        <v>1.11010873317719</v>
+        <v>1.1101086139679</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G194" t="n">
-        <v>1.0917090177536</v>
+        <v>1.09170913696289</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G195" t="n">
-        <v>1.09416246414185</v>
+        <v>1.09416234493256</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G199" t="n">
-        <v>1.10152232646942</v>
+        <v>1.10152220726013</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>1.79100000858307</v>
       </c>
       <c r="G201" t="n">
-        <v>1.09845566749573</v>
+        <v>1.09845554828644</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.76699995994568</v>
       </c>
       <c r="G202" t="n">
-        <v>1.08373594284058</v>
+        <v>1.08373606204987</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>1.79100000858307</v>
       </c>
       <c r="G205" t="n">
-        <v>1.09845566749573</v>
+        <v>1.09845554828644</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G208" t="n">
-        <v>1.10152232646942</v>
+        <v>1.10152220726013</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G209" t="n">
-        <v>1.12850844860077</v>
+        <v>1.12850832939148</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G210" t="n">
-        <v>1.18370699882507</v>
+        <v>1.18370711803436</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G211" t="n">
-        <v>1.23890578746796</v>
+        <v>1.23890590667725</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G213" t="n">
-        <v>1.23277270793915</v>
+        <v>1.23277258872986</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G215" t="n">
-        <v>1.26343870162964</v>
+        <v>1.26343858242035</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G217" t="n">
-        <v>1.28551816940308</v>
+        <v>1.28551805019379</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.07800006866455</v>
       </c>
       <c r="G221" t="n">
-        <v>1.27447843551636</v>
+        <v>1.27447855472565</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.07399988174438</v>
       </c>
       <c r="G223" t="n">
-        <v>1.2720251083374</v>
+        <v>1.27202498912811</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G225" t="n">
-        <v>1.31495761871338</v>
+        <v>1.31495749950409</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G226" t="n">
-        <v>1.32231712341309</v>
+        <v>1.32231724262238</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G230" t="n">
-        <v>1.32354390621185</v>
+        <v>1.32354402542114</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G236" t="n">
-        <v>1.28797137737274</v>
+        <v>1.28797125816345</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G237" t="n">
-        <v>1.28797137737274</v>
+        <v>1.28797125816345</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G241" t="n">
-        <v>1.36279654502869</v>
+        <v>1.3627964258194</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G242" t="n">
-        <v>1.42290163040161</v>
+        <v>1.4229017496109</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G243" t="n">
-        <v>1.4351681470871</v>
+        <v>1.43516826629639</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G245" t="n">
-        <v>1.47687387466431</v>
+        <v>1.4768739938736</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G249" t="n">
-        <v>1.47932732105255</v>
+        <v>1.47932708263397</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G251" t="n">
-        <v>1.50263345241547</v>
+        <v>1.50263333320618</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G254" t="n">
-        <v>1.47687387466431</v>
+        <v>1.4768739938736</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G255" t="n">
-        <v>1.447434425354</v>
+        <v>1.44743454456329</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G258" t="n">
-        <v>1.56396520137787</v>
+        <v>1.56396532058716</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G259" t="n">
-        <v>1.57991170883179</v>
+        <v>1.5799115896225</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G260" t="n">
-        <v>1.58113837242126</v>
+        <v>1.58113825321198</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G261" t="n">
-        <v>1.57009851932526</v>
+        <v>1.57009840011597</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G266" t="n">
-        <v>1.55169904232025</v>
+        <v>1.55169880390167</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G267" t="n">
-        <v>1.57009851932526</v>
+        <v>1.57009840011597</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G268" t="n">
-        <v>1.57868480682373</v>
+        <v>1.57868504524231</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G269" t="n">
-        <v>1.55660545825958</v>
+        <v>1.55660557746887</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.5</v>
       </c>
       <c r="G270" t="n">
-        <v>1.53329932689667</v>
+        <v>1.53329944610596</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G271" t="n">
-        <v>1.52593958377838</v>
+        <v>1.52593946456909</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.48600006103516</v>
       </c>
       <c r="G275" t="n">
-        <v>1.5247129201889</v>
+        <v>1.52471303939819</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G276" t="n">
-        <v>1.52593958377838</v>
+        <v>1.52593946456909</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G277" t="n">
-        <v>1.47687387466431</v>
+        <v>1.4768739938736</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G279" t="n">
-        <v>1.34930348396301</v>
+        <v>1.34930336475372</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G280" t="n">
-        <v>1.4167685508728</v>
+        <v>1.41676843166351</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G281" t="n">
-        <v>1.41308867931366</v>
+        <v>1.41308856010437</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G284" t="n">
-        <v>1.27079856395721</v>
+        <v>1.27079844474792</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.12400007247925</v>
       </c>
       <c r="G287" t="n">
-        <v>1.30269122123718</v>
+        <v>1.30269110202789</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.33599996566772</v>
       </c>
       <c r="G288" t="n">
-        <v>1.43271493911743</v>
+        <v>1.43271481990814</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G292" t="n">
-        <v>1.38732933998108</v>
+        <v>1.38732922077179</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G293" t="n">
-        <v>1.39959561824799</v>
+        <v>1.39959573745728</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G294" t="n">
-        <v>1.4339417219162</v>
+        <v>1.43394160270691</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G295" t="n">
-        <v>1.4339417219162</v>
+        <v>1.43394160270691</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G296" t="n">
-        <v>1.41063547134399</v>
+        <v>1.4106353521347</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.67199993133545</v>
       </c>
       <c r="G299" t="n">
-        <v>1.63879024982452</v>
+        <v>1.63879036903381</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G302" t="n">
-        <v>1.66945624351501</v>
+        <v>1.6694563627243</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G306" t="n">
-        <v>1.75409436225891</v>
+        <v>1.7540944814682</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>1.77862727642059</v>
+        <v>1.77862739562988</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G313" t="n">
-        <v>1.95526337623596</v>
+        <v>1.95526325702667</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G314" t="n">
-        <v>1.93563687801361</v>
+        <v>1.9356369972229</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G315" t="n">
-        <v>2.01046228408813</v>
+        <v>2.01046204566956</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G320" t="n">
-        <v>2.29749584197998</v>
+        <v>2.2974956035614</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G321" t="n">
-        <v>2.26928281784058</v>
+        <v>2.26928305625916</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G322" t="n">
-        <v>2.2680561542511</v>
+        <v>2.26805639266968</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G323" t="n">
-        <v>2.25701689720154</v>
+        <v>2.25701665878296</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>3.75600004196167</v>
       </c>
       <c r="G324" t="n">
-        <v>2.30362915992737</v>
+        <v>2.30362892150879</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G326" t="n">
-        <v>2.2484302520752</v>
+        <v>2.24843001365662</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G328" t="n">
-        <v>2.2484302520752</v>
+        <v>2.24843001365662</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G329" t="n">
-        <v>2.27786946296692</v>
+        <v>2.2778697013855</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G331" t="n">
-        <v>2.2680561542511</v>
+        <v>2.26805639266968</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G333" t="n">
-        <v>2.28277587890625</v>
+        <v>2.28277611732483</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G339" t="n">
-        <v>2.72681975364685</v>
+        <v>2.72681951522827</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>2.73540592193604</v>
+        <v>2.73540639877319</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G343" t="n">
-        <v>2.76607227325439</v>
+        <v>2.76607203483582</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G344" t="n">
-        <v>2.72927284240723</v>
+        <v>2.72927260398865</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>2.85193705558777</v>
+        <v>2.85193681716919</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G346" t="n">
-        <v>2.90590882301331</v>
+        <v>2.90590906143188</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G348" t="n">
-        <v>2.88996243476868</v>
+        <v>2.8899621963501</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>4.60799980163574</v>
       </c>
       <c r="G349" t="n">
-        <v>2.82617735862732</v>
+        <v>2.82617712020874</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G350" t="n">
-        <v>2.8568434715271</v>
+        <v>2.85684323310852</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>5.08500003814697</v>
       </c>
       <c r="G356" t="n">
-        <v>3.11873078346252</v>
+        <v>3.1187310218811</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G357" t="n">
-        <v>3.14633059501648</v>
+        <v>3.1463303565979</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G358" t="n">
-        <v>3.21379518508911</v>
+        <v>3.21379542350769</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G362" t="n">
-        <v>3.14633059501648</v>
+        <v>3.1463303565979</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>5.125</v>
       </c>
       <c r="G363" t="n">
-        <v>3.14326357841492</v>
+        <v>3.1432638168335</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G368" t="n">
-        <v>3.14019703865051</v>
+        <v>3.14019680023193</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G371" t="n">
-        <v>3.21072888374329</v>
+        <v>3.21072912216187</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G372" t="n">
-        <v>3.10953092575073</v>
+        <v>3.10953116416931</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>3.2321949005127</v>
+        <v>3.23219513893127</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G382" t="n">
-        <v>3.10953092575073</v>
+        <v>3.10953116416931</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G383" t="n">
-        <v>2.92553496360779</v>
+        <v>2.92553520202637</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>4.68400001525879</v>
       </c>
       <c r="G384" t="n">
-        <v>2.87278962135315</v>
+        <v>2.87278938293457</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.69199991226196</v>
       </c>
       <c r="G394" t="n">
-        <v>2.87769603729248</v>
+        <v>2.87769627571106</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G399" t="n">
-        <v>2.67898082733154</v>
+        <v>2.67898035049438</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G400" t="n">
-        <v>2.69860696792603</v>
+        <v>2.69860672950745</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>4.47800016403198</v>
       </c>
       <c r="G402" t="n">
-        <v>2.74644589424133</v>
+        <v>2.74644565582275</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>4.2480001449585</v>
       </c>
       <c r="G406" t="n">
-        <v>2.60538244247437</v>
+        <v>2.60538220405579</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>4.14200019836426</v>
       </c>
       <c r="G407" t="n">
-        <v>2.54037046432495</v>
+        <v>2.54037070274353</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G408" t="n">
-        <v>2.556316614151</v>
+        <v>2.55631685256958</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G409" t="n">
-        <v>2.57594275474548</v>
+        <v>2.5759425163269</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G410" t="n">
-        <v>2.57594275474548</v>
+        <v>2.5759425163269</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.27400016784668</v>
       </c>
       <c r="G412" t="n">
-        <v>2.62132883071899</v>
+        <v>2.62132859230042</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4.4520001411438</v>
       </c>
       <c r="G414" t="n">
-        <v>2.73049974441528</v>
+        <v>2.7304995059967</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>4.55800008773804</v>
       </c>
       <c r="G415" t="n">
-        <v>2.79551124572754</v>
+        <v>2.79551148414612</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G416" t="n">
-        <v>2.82127094268799</v>
+        <v>2.82127070426941</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>4.60400009155273</v>
       </c>
       <c r="G417" t="n">
-        <v>2.82372426986694</v>
+        <v>2.82372403144836</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G419" t="n">
-        <v>2.77588534355164</v>
+        <v>2.77588510513306</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G420" t="n">
-        <v>2.73540592193604</v>
+        <v>2.73540639877319</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>4.41800022125244</v>
       </c>
       <c r="G422" t="n">
-        <v>2.70964646339417</v>
+        <v>2.70964670181274</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>4.44399976730347</v>
       </c>
       <c r="G423" t="n">
-        <v>2.72559309005737</v>
+        <v>2.72559285163879</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G424" t="n">
-        <v>2.66794085502625</v>
+        <v>2.66794109344482</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>4.24599981307983</v>
       </c>
       <c r="G425" t="n">
-        <v>2.60415530204773</v>
+        <v>2.60415554046631</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G427" t="n">
-        <v>2.67898082733154</v>
+        <v>2.67898035049438</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G428" t="n">
-        <v>2.62991523742676</v>
+        <v>2.62991499900818</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>4.28200006484985</v>
       </c>
       <c r="G429" t="n">
-        <v>2.62623524665833</v>
+        <v>2.62623500823975</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>5</v>
       </c>
       <c r="G437" t="n">
-        <v>3.06659865379333</v>
+        <v>3.06659889221191</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>5</v>
       </c>
       <c r="G441" t="n">
-        <v>3.06659865379333</v>
+        <v>3.06659889221191</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G442" t="n">
-        <v>3.10033106803894</v>
+        <v>3.10033130645752</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>5.03499984741211</v>
       </c>
       <c r="G443" t="n">
-        <v>3.08806443214417</v>
+        <v>3.08806490898132</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>5</v>
       </c>
       <c r="G444" t="n">
-        <v>3.06659865379333</v>
+        <v>3.06659889221191</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G446" t="n">
-        <v>3.1769962310791</v>
+        <v>3.17699646949768</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>3.15553021430969</v>
+        <v>3.15552997589111</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.90199995040894</v>
       </c>
       <c r="G454" t="n">
-        <v>3.00649356842041</v>
+        <v>3.00649333000183</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>4.80600023269653</v>
       </c>
       <c r="G460" t="n">
-        <v>2.94761490821838</v>
+        <v>2.9476146697998</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G461" t="n">
-        <v>2.97214722633362</v>
+        <v>2.97214770317078</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>4.63199996948242</v>
       </c>
       <c r="G462" t="n">
-        <v>2.84089684486389</v>
+        <v>2.84089708328247</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G463" t="n">
-        <v>2.88260269165039</v>
+        <v>2.88260245323181</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G464" t="n">
-        <v>2.90100240707397</v>
+        <v>2.9010021686554</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G465" t="n">
-        <v>2.90590882301331</v>
+        <v>2.90590906143188</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G470" t="n">
-        <v>2.57594275474548</v>
+        <v>2.5759425163269</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G471" t="n">
-        <v>2.556316614151</v>
+        <v>2.55631685256958</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G476" t="n">
-        <v>2.47781157493591</v>
+        <v>2.47781181335449</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G477" t="n">
-        <v>2.43487954139709</v>
+        <v>2.43487930297852</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G481" t="n">
-        <v>2.2680561542511</v>
+        <v>2.26805639266968</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G482" t="n">
-        <v>2.34165501594543</v>
+        <v>2.34165477752686</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>3.86400008201599</v>
       </c>
       <c r="G483" t="n">
-        <v>2.3698673248291</v>
+        <v>2.36986756324768</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G486" t="n">
-        <v>2.5857560634613</v>
+        <v>2.58575582504272</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G489" t="n">
-        <v>2.4238395690918</v>
+        <v>2.42383933067322</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G490" t="n">
-        <v>2.44346594810486</v>
+        <v>2.44346570968628</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G491" t="n">
-        <v>2.66794085502625</v>
+        <v>2.66794109344482</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G492" t="n">
-        <v>2.63482189178467</v>
+        <v>2.63482141494751</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.25600004196167</v>
       </c>
       <c r="G494" t="n">
-        <v>2.6102888584137</v>
+        <v>2.61028861999512</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G496" t="n">
-        <v>2.53914380073547</v>
+        <v>2.53914356231689</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G501" t="n">
-        <v>2.38581371307373</v>
+        <v>2.38581395149231</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G502" t="n">
-        <v>2.33061480522156</v>
+        <v>2.33061504364014</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>3.94799995422363</v>
       </c>
       <c r="G504" t="n">
-        <v>2.42138624191284</v>
+        <v>2.42138648033142</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G505" t="n">
-        <v>2.39808034896851</v>
+        <v>2.39808011054993</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>3.95799994468689</v>
       </c>
       <c r="G513" t="n">
-        <v>2.42751955986023</v>
+        <v>2.42751932144165</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G516" t="n">
-        <v>2.5146107673645</v>
+        <v>2.51461100578308</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G517" t="n">
-        <v>2.52687740325928</v>
+        <v>2.5268771648407</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>4.18599987030029</v>
       </c>
       <c r="G519" t="n">
-        <v>2.56735634803772</v>
+        <v>2.56735610961914</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G521" t="n">
-        <v>2.62991523742676</v>
+        <v>2.62991499900818</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>4.21799993515015</v>
       </c>
       <c r="G523" t="n">
-        <v>2.58698272705078</v>
+        <v>2.5869824886322</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G532" t="n">
-        <v>2.454505443573</v>
+        <v>2.45450568199158</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>3.86400008201599</v>
       </c>
       <c r="G535" t="n">
-        <v>2.3698673248291</v>
+        <v>2.36986756324768</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G538" t="n">
-        <v>2.41647958755493</v>
+        <v>2.41647982597351</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>3.60599994659424</v>
       </c>
       <c r="G541" t="n">
-        <v>2.21163105964661</v>
+        <v>2.21163082122803</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G542" t="n">
-        <v>2.1834180355072</v>
+        <v>2.18341827392578</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G544" t="n">
-        <v>2.27541613578796</v>
+        <v>2.27541637420654</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G548" t="n">
-        <v>2.28400254249573</v>
+        <v>2.28400278091431</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G549" t="n">
-        <v>2.33061480522156</v>
+        <v>2.33061504364014</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G553" t="n">
-        <v>2.03008842468262</v>
+        <v>2.03008818626404</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>3.18600010871887</v>
       </c>
       <c r="G554" t="n">
-        <v>1.95403671264648</v>
+        <v>1.95403659343719</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G555" t="n">
-        <v>1.90129125118256</v>
+        <v>1.90129113197327</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G557" t="n">
-        <v>1.87921166419983</v>
+        <v>1.87921154499054</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>3.15799999237061</v>
       </c>
       <c r="G559" t="n">
-        <v>1.93686354160309</v>
+        <v>1.93686378002167</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>3.11800003051758</v>
       </c>
       <c r="G560" t="n">
-        <v>1.91233086585999</v>
+        <v>1.91233098506927</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>3.02600002288818</v>
       </c>
       <c r="G562" t="n">
-        <v>1.85590553283691</v>
+        <v>1.8559056520462</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G563" t="n">
-        <v>1.87798500061035</v>
+        <v>1.87798511981964</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G564" t="n">
-        <v>1.87921166419983</v>
+        <v>1.87921154499054</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G567" t="n">
-        <v>1.90129125118256</v>
+        <v>1.90129113197327</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G568" t="n">
-        <v>1.98715603351593</v>
+        <v>1.98715591430664</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>3.08200001716614</v>
       </c>
       <c r="G571" t="n">
-        <v>1.89025127887726</v>
+        <v>1.89025139808655</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G572" t="n">
-        <v>1.8865715265274</v>
+        <v>1.88657128810883</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G577" t="n">
-        <v>1.92091727256775</v>
+        <v>1.92091739177704</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G578" t="n">
-        <v>1.95649003982544</v>
+        <v>1.95649015903473</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>3.11800003051758</v>
       </c>
       <c r="G581" t="n">
-        <v>1.91233086585999</v>
+        <v>1.91233098506927</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>3.32399988174438</v>
       </c>
       <c r="G584" t="n">
-        <v>2.0386745929718</v>
+        <v>2.03867483139038</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G588" t="n">
-        <v>1.96262311935425</v>
+        <v>1.96262300014496</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G589" t="n">
-        <v>2.03008842468262</v>
+        <v>2.03008818626404</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G591" t="n">
-        <v>1.97120976448059</v>
+        <v>1.9712096452713</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G593" t="n">
-        <v>1.97734272480011</v>
+        <v>1.9773428440094</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>3.25399994850159</v>
       </c>
       <c r="G594" t="n">
-        <v>1.99574244022369</v>
+        <v>1.99574255943298</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G595" t="n">
-        <v>2.08283352851868</v>
+        <v>2.08283376693726</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G599" t="n">
-        <v>1.99942231178284</v>
+        <v>1.99942243099213</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G600" t="n">
-        <v>2.02640843391418</v>
+        <v>2.02640819549561</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G601" t="n">
-        <v>1.97120976448059</v>
+        <v>1.9712096452713</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G602" t="n">
-        <v>1.96016979217529</v>
+        <v>1.96017003059387</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>3.15199995040894</v>
       </c>
       <c r="G603" t="n">
-        <v>1.93318378925323</v>
+        <v>1.93318390846252</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G604" t="n">
-        <v>1.93441045284271</v>
+        <v>1.93441033363342</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>3.08200001716614</v>
       </c>
       <c r="G605" t="n">
-        <v>1.89025127887726</v>
+        <v>1.89025139808655</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>3.13800001144409</v>
       </c>
       <c r="G606" t="n">
-        <v>1.92459750175476</v>
+        <v>1.92459726333618</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G608" t="n">
-        <v>1.88411819934845</v>
+        <v>1.88411831855774</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>3.13599991798401</v>
       </c>
       <c r="G609" t="n">
-        <v>1.9233705997467</v>
+        <v>1.92337071895599</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G612" t="n">
-        <v>1.87921166419983</v>
+        <v>1.87921154499054</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G616" t="n">
-        <v>1.76636075973511</v>
+        <v>1.7663608789444</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G618" t="n">
-        <v>1.86939859390259</v>
+        <v>1.86939871311188</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G619" t="n">
-        <v>1.87307834625244</v>
+        <v>1.87307846546173</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G620" t="n">
-        <v>1.93441045284271</v>
+        <v>1.93441033363342</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>3.08400011062622</v>
       </c>
       <c r="G621" t="n">
-        <v>1.89147818088531</v>
+        <v>1.89147806167603</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G624" t="n">
-        <v>1.87062525749207</v>
+        <v>1.87062513828278</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G630" t="n">
-        <v>1.80193340778351</v>
+        <v>1.80193328857422</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>2.86400008201599</v>
       </c>
       <c r="G632" t="n">
-        <v>1.75654780864716</v>
+        <v>1.75654768943787</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G633" t="n">
-        <v>1.66822981834412</v>
+        <v>1.66822969913483</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G634" t="n">
-        <v>1.63756382465363</v>
+        <v>1.63756370544434</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G635" t="n">
-        <v>1.63020384311676</v>
+        <v>1.63020396232605</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G636" t="n">
-        <v>1.57009851932526</v>
+        <v>1.57009840011597</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G638" t="n">
-        <v>1.54924583435059</v>
+        <v>1.5492457151413</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G639" t="n">
-        <v>1.55169904232025</v>
+        <v>1.55169880390167</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G640" t="n">
-        <v>1.56273865699768</v>
+        <v>1.56273877620697</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.68600010871887</v>
       </c>
       <c r="G641" t="n">
-        <v>1.64737677574158</v>
+        <v>1.64737689495087</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G642" t="n">
-        <v>1.63143050670624</v>
+        <v>1.63143038749695</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.75799989700317</v>
       </c>
       <c r="G643" t="n">
-        <v>1.69153583049774</v>
+        <v>1.69153571128845</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.66400003433228</v>
       </c>
       <c r="G645" t="n">
-        <v>1.6338837146759</v>
+        <v>1.63388383388519</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G646" t="n">
-        <v>1.60567104816437</v>
+        <v>1.60567116737366</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G647" t="n">
-        <v>1.59217798709869</v>
+        <v>1.59217810630798</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G650" t="n">
-        <v>1.72956168651581</v>
+        <v>1.72956156730652</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.78600001335144</v>
       </c>
       <c r="G651" t="n">
-        <v>1.70870876312256</v>
+        <v>1.70870864391327</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.71399998664856</v>
       </c>
       <c r="G652" t="n">
-        <v>1.66454970836639</v>
+        <v>1.66454982757568</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G653" t="n">
-        <v>1.63143050670624</v>
+        <v>1.63143038749695</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G658" t="n">
-        <v>1.29287803173065</v>
+        <v>1.29287791252136</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G660" t="n">
-        <v>1.29287803173065</v>
+        <v>1.29287791252136</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G662" t="n">
-        <v>1.26957190036774</v>
+        <v>1.26957178115845</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G663" t="n">
-        <v>1.2781583070755</v>
+        <v>1.27815842628479</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G666" t="n">
-        <v>1.25853204727173</v>
+        <v>1.25853216648102</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G668" t="n">
-        <v>1.20946657657623</v>
+        <v>1.20946645736694</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G669" t="n">
-        <v>1.20517325401306</v>
+        <v>1.20517337322235</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G673" t="n">
-        <v>1.28551816940308</v>
+        <v>1.28551805019379</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>1.98099994659424</v>
       </c>
       <c r="G674" t="n">
-        <v>1.2149863243103</v>
+        <v>1.21498644351959</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G677" t="n">
-        <v>1.23154592514038</v>
+        <v>1.23154604434967</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>2.04800009727478</v>
       </c>
       <c r="G682" t="n">
-        <v>1.25607883930206</v>
+        <v>1.25607895851135</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G683" t="n">
-        <v>1.22602617740631</v>
+        <v>1.22602605819702</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2</v>
       </c>
       <c r="G687" t="n">
-        <v>1.22663938999176</v>
+        <v>1.22663950920105</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>1.97899997234344</v>
       </c>
       <c r="G688" t="n">
-        <v>1.21375977993011</v>
+        <v>1.21375966072083</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G690" t="n">
-        <v>1.2119197845459</v>
+        <v>1.21191966533661</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2</v>
       </c>
       <c r="G691" t="n">
-        <v>1.22663938999176</v>
+        <v>1.22663950920105</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G692" t="n">
-        <v>1.24381244182587</v>
+        <v>1.24381256103516</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G693" t="n">
-        <v>1.24381244182587</v>
+        <v>1.24381256103516</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G694" t="n">
-        <v>1.26343870162964</v>
+        <v>1.26343858242035</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G695" t="n">
-        <v>1.29533135890961</v>
+        <v>1.29533123970032</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G696" t="n">
-        <v>1.31741094589233</v>
+        <v>1.31741070747375</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G698" t="n">
-        <v>1.24381244182587</v>
+        <v>1.24381256103516</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G703" t="n">
-        <v>1.17389404773712</v>
+        <v>1.17389392852783</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G708" t="n">
-        <v>1.08434927463531</v>
+        <v>1.08434915542603</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>1.68700003623962</v>
       </c>
       <c r="G710" t="n">
-        <v>1.03467047214508</v>
+        <v>1.03467035293579</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G711" t="n">
-        <v>1.05552327632904</v>
+        <v>1.05552315711975</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>1.625</v>
       </c>
       <c r="G715" t="n">
-        <v>0.996644556522369</v>
+        <v>0.996644616127014</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G717" t="n">
-        <v>0.984991550445557</v>
+        <v>0.984991431236267</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>1.49300003051758</v>
       </c>
       <c r="G719" t="n">
-        <v>0.915686428546906</v>
+        <v>0.915686368942261</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>1.5110000371933</v>
       </c>
       <c r="G720" t="n">
-        <v>0.926726162433624</v>
+        <v>0.926726102828979</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G722" t="n">
-        <v>0.951258957386017</v>
+        <v>0.951258897781372</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>1.57599997520447</v>
       </c>
       <c r="G723" t="n">
-        <v>0.966591894626617</v>
+        <v>0.966591954231262</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>1.59300005435944</v>
       </c>
       <c r="G725" t="n">
-        <v>0.977018356323242</v>
+        <v>0.977018296718597</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G726" t="n">
-        <v>0.980084896087646</v>
+        <v>0.980085015296936</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G728" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G729" t="n">
-        <v>0.992351353168488</v>
+        <v>0.992351412773132</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>1.57200002670288</v>
       </c>
       <c r="G730" t="n">
-        <v>0.964138567447662</v>
+        <v>0.964138686656952</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>1.53299999237061</v>
       </c>
       <c r="G731" t="n">
-        <v>0.940219163894653</v>
+        <v>0.940219223499298</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>1.50100004673004</v>
       </c>
       <c r="G734" t="n">
-        <v>0.920592904090881</v>
+        <v>0.920592963695526</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G740" t="n">
-        <v>0.875820577144623</v>
+        <v>0.875820517539978</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>1.53299999237061</v>
       </c>
       <c r="G742" t="n">
-        <v>0.940219163894653</v>
+        <v>0.940219223499298</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G743" t="n">
-        <v>0.956778764724731</v>
+        <v>0.956778824329376</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G744" t="n">
-        <v>0.94451230764389</v>
+        <v>0.94451242685318</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G745" t="n">
-        <v>0.941445767879486</v>
+        <v>0.941445708274841</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G747" t="n">
-        <v>0.967205226421356</v>
+        <v>0.967205166816711</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G748" t="n">
-        <v>0.956165432929993</v>
+        <v>0.956165492534637</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>1.4539999961853</v>
       </c>
       <c r="G753" t="n">
-        <v>0.891766965389252</v>
+        <v>0.891766905784607</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>1.48699998855591</v>
       </c>
       <c r="G754" t="n">
-        <v>0.912006437778473</v>
+        <v>0.912006378173828</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G755" t="n">
-        <v>0.875207245349884</v>
+        <v>0.875207304954529</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>1.37899994850159</v>
       </c>
       <c r="G757" t="n">
-        <v>0.845767915248871</v>
+        <v>0.845767855644226</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G759" t="n">
-        <v>0.849447846412659</v>
+        <v>0.849447786808014</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G761" t="n">
-        <v>0.864780843257904</v>
+        <v>0.864780783653259</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G762" t="n">
-        <v>0.864780843257904</v>
+        <v>0.864780783653259</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>1.43099999427795</v>
       </c>
       <c r="G763" t="n">
-        <v>0.877660512924194</v>
+        <v>0.877660572528839</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>1.45700001716614</v>
       </c>
       <c r="G764" t="n">
-        <v>0.893606841564178</v>
+        <v>0.893606901168823</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G767" t="n">
-        <v>0.951258957386017</v>
+        <v>0.951258897781372</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G768" t="n">
-        <v>0.951872229576111</v>
+        <v>0.951872289180756</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>1.60699999332428</v>
       </c>
       <c r="G769" t="n">
-        <v>0.985604882240295</v>
+        <v>0.985604822635651</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>1.61300003528595</v>
       </c>
       <c r="G771" t="n">
-        <v>0.989284694194794</v>
+        <v>0.989284753799438</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G773" t="n">
-        <v>0.94451230764389</v>
+        <v>0.94451242685318</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G775" t="n">
-        <v>0.982538223266602</v>
+        <v>0.982538282871246</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G776" t="n">
-        <v>0.993578016757965</v>
+        <v>0.99357795715332</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G778" t="n">
-        <v>0.940832436084747</v>
+        <v>0.940832495689392</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G781" t="n">
-        <v>0.984991550445557</v>
+        <v>0.984991431236267</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G784" t="n">
-        <v>1.06472289562225</v>
+        <v>1.06472301483154</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G785" t="n">
-        <v>1.12237513065338</v>
+        <v>1.12237501144409</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>1.7039999961853</v>
       </c>
       <c r="G789" t="n">
-        <v>1.04509675502777</v>
+        <v>1.04509687423706</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>1.625</v>
       </c>
       <c r="G790" t="n">
-        <v>0.996644556522369</v>
+        <v>0.996644616127014</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G791" t="n">
-        <v>0.972111761569977</v>
+        <v>0.972111821174622</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G794" t="n">
-        <v>1.05491006374359</v>
+        <v>1.0549099445343</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>1.71300005912781</v>
       </c>
       <c r="G795" t="n">
-        <v>1.05061674118042</v>
+        <v>1.05061662197113</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G796" t="n">
-        <v>1.06901621818542</v>
+        <v>1.06901633739471</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G797" t="n">
-        <v>1.05552327632904</v>
+        <v>1.05552315711975</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G799" t="n">
-        <v>1.06901621818542</v>
+        <v>1.06901633739471</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G800" t="n">
-        <v>1.03957688808441</v>
+        <v>1.0395770072937</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>1.56900000572205</v>
       </c>
       <c r="G804" t="n">
-        <v>0.96229875087738</v>
+        <v>0.962298631668091</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>1.56700003147125</v>
       </c>
       <c r="G805" t="n">
-        <v>0.961072087287903</v>
+        <v>0.961072027683258</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>1.5789999961853</v>
       </c>
       <c r="G806" t="n">
-        <v>0.968431770801544</v>
+        <v>0.968431890010834</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G810" t="n">
-        <v>0.921206176280975</v>
+        <v>0.921206295490265</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G817" t="n">
-        <v>0.926112830638885</v>
+        <v>0.926112711429596</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>1.54100000858307</v>
       </c>
       <c r="G818" t="n">
-        <v>0.945125639438629</v>
+        <v>0.945125699043274</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G819" t="n">
-        <v>0.945739090442657</v>
+        <v>0.945739030838013</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>1.50100004673004</v>
       </c>
       <c r="G825" t="n">
-        <v>0.920592904090881</v>
+        <v>0.920592963695526</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>1.53699994087219</v>
       </c>
       <c r="G826" t="n">
-        <v>0.942672431468964</v>
+        <v>0.942672491073608</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>1.59300005435944</v>
       </c>
       <c r="G827" t="n">
-        <v>0.977018356323242</v>
+        <v>0.977018296718597</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G828" t="n">
-        <v>0.960458636283875</v>
+        <v>0.960458695888519</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>1.66100001335144</v>
       </c>
       <c r="G830" t="n">
-        <v>1.01872396469116</v>
+        <v>1.01872408390045</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G833" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G834" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G837" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G839" t="n">
-        <v>0.977631688117981</v>
+        <v>0.977631628513336</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>1.5789999961853</v>
       </c>
       <c r="G842" t="n">
-        <v>0.968431770801544</v>
+        <v>0.968431890010834</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G843" t="n">
-        <v>0.953098893165588</v>
+        <v>0.953098833560944</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G845" t="n">
-        <v>0.90280669927597</v>
+        <v>0.902806639671326</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G847" t="n">
-        <v>0.852514445781708</v>
+        <v>0.852514386177063</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G849" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.27799999713898</v>
       </c>
       <c r="G852" t="n">
-        <v>0.783822655677795</v>
+        <v>0.783822596073151</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G854" t="n">
-        <v>0.731077075004578</v>
+        <v>0.731077134609222</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>1.18700003623962</v>
       </c>
       <c r="G855" t="n">
-        <v>0.728010594844818</v>
+        <v>0.728010535240173</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G856" t="n">
-        <v>0.743343472480774</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G859" t="n">
-        <v>0.69611781835556</v>
+        <v>0.696117877960205</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G861" t="n">
-        <v>0.705317735671997</v>
+        <v>0.705317676067352</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>1.13100004196167</v>
       </c>
       <c r="G863" t="n">
-        <v>0.69366466999054</v>
+        <v>0.693664610385895</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G870" t="n">
-        <v>0.722490608692169</v>
+        <v>0.722490549087524</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G871" t="n">
-        <v>0.716970860958099</v>
+        <v>0.716970801353455</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G872" t="n">
-        <v>0.705317735671997</v>
+        <v>0.705317676067352</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G873" t="n">
-        <v>0.709610879421234</v>
+        <v>0.709610939025879</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G874" t="n">
-        <v>0.716970860958099</v>
+        <v>0.716970801353455</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G875" t="n">
-        <v>0.721877336502075</v>
+        <v>0.72187739610672</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>1.1710000038147</v>
       </c>
       <c r="G876" t="n">
-        <v>0.718197405338287</v>
+        <v>0.718197345733643</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G878" t="n">
-        <v>0.720650672912598</v>
+        <v>0.720650613307953</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G880" t="n">
-        <v>0.722490608692169</v>
+        <v>0.722490549087524</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G882" t="n">
-        <v>0.753156661987305</v>
+        <v>0.753156721591949</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G883" t="n">
-        <v>0.74518346786499</v>
+        <v>0.745183527469635</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G884" t="n">
-        <v>0.74518346786499</v>
+        <v>0.745183527469635</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>1.21599996089935</v>
       </c>
       <c r="G885" t="n">
-        <v>0.745796740055084</v>
+        <v>0.745796799659729</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>1.22099995613098</v>
       </c>
       <c r="G886" t="n">
-        <v>0.748863399028778</v>
+        <v>0.748863339424133</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.24300003051758</v>
       </c>
       <c r="G887" t="n">
-        <v>0.762356460094452</v>
+        <v>0.762356519699097</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>1.24699997901917</v>
       </c>
       <c r="G888" t="n">
-        <v>0.764809727668762</v>
+        <v>0.764809668064117</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G892" t="n">
-        <v>0.775849521160126</v>
+        <v>0.775849401950836</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.25</v>
       </c>
       <c r="G894" t="n">
-        <v>0.766649663448334</v>
+        <v>0.766649723052979</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G895" t="n">
-        <v>0.761743068695068</v>
+        <v>0.761743128299713</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G897" t="n">
-        <v>0.763583123683929</v>
+        <v>0.763583064079285</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>1.24699997901917</v>
       </c>
       <c r="G898" t="n">
-        <v>0.764809727668762</v>
+        <v>0.764809668064117</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>1.21099996566772</v>
       </c>
       <c r="G900" t="n">
-        <v>0.742730140686035</v>
+        <v>0.74273020029068</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G901" t="n">
-        <v>0.753156661987305</v>
+        <v>0.753156721591949</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G903" t="n">
-        <v>0.753156661987305</v>
+        <v>0.753156721591949</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G905" t="n">
-        <v>0.788729131221771</v>
+        <v>0.788729190826416</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G906" t="n">
-        <v>0.806515514850616</v>
+        <v>0.806515455245972</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G909" t="n">
-        <v>0.781982600688934</v>
+        <v>0.781982660293579</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>1.25</v>
       </c>
       <c r="G910" t="n">
-        <v>0.766649663448334</v>
+        <v>0.766649723052979</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>1.21099996566772</v>
       </c>
       <c r="G911" t="n">
-        <v>0.742730140686035</v>
+        <v>0.74273020029068</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>1.21099996566772</v>
       </c>
       <c r="G912" t="n">
-        <v>0.742730140686035</v>
+        <v>0.74273020029068</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G913" t="n">
-        <v>0.724943995475769</v>
+        <v>0.724943935871124</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G914" t="n">
-        <v>0.7323037981987</v>
+        <v>0.732303738594055</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G921" t="n">
-        <v>0.7323037981987</v>
+        <v>0.732303738594055</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.21099996566772</v>
       </c>
       <c r="G923" t="n">
-        <v>0.742730140686035</v>
+        <v>0.74273020029068</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G924" t="n">
-        <v>0.74518346786499</v>
+        <v>0.745183527469635</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G926" t="n">
-        <v>0.792409121990204</v>
+        <v>0.792409062385559</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G927" t="n">
-        <v>0.781982600688934</v>
+        <v>0.781982660293579</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>1.25</v>
       </c>
       <c r="G929" t="n">
-        <v>0.766649663448334</v>
+        <v>0.766649723052979</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G931" t="n">
-        <v>0.788729131221771</v>
+        <v>0.788729190826416</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>1.25</v>
       </c>
       <c r="G932" t="n">
-        <v>0.766649663448334</v>
+        <v>0.766649723052979</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G935" t="n">
-        <v>0.763583123683929</v>
+        <v>0.763583064079285</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G940" t="n">
-        <v>0.849447846412659</v>
+        <v>0.849447786808014</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G941" t="n">
-        <v>0.834114909172058</v>
+        <v>0.834114849567413</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G942" t="n">
-        <v>0.834114909172058</v>
+        <v>0.834114849567413</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G944" t="n">
-        <v>0.832888305187225</v>
+        <v>0.832888185977936</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G946" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G947" t="n">
-        <v>0.829208314418793</v>
+        <v>0.829208254814148</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>1.27600002288818</v>
       </c>
       <c r="G948" t="n">
-        <v>0.782596051692963</v>
+        <v>0.782595992088318</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>1.26300001144409</v>
       </c>
       <c r="G949" t="n">
-        <v>0.774622917175293</v>
+        <v>0.774622857570648</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G950" t="n">
-        <v>0.754383206367493</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>1.23099994659424</v>
       </c>
       <c r="G951" t="n">
-        <v>0.754996597766876</v>
+        <v>0.754996538162231</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G952" t="n">
-        <v>0.761743068695068</v>
+        <v>0.761743128299713</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>1.20099997520447</v>
       </c>
       <c r="G955" t="n">
-        <v>0.736597001552582</v>
+        <v>0.736597061157227</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>1.18599998950958</v>
       </c>
       <c r="G956" t="n">
-        <v>0.727397203445435</v>
+        <v>0.72739714384079</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G961" t="n">
-        <v>0.754383206367493</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G962" t="n">
-        <v>0.775849521160126</v>
+        <v>0.775849401950836</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G963" t="n">
-        <v>0.780142664909363</v>
+        <v>0.780142605304718</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>1.29900002479553</v>
       </c>
       <c r="G966" t="n">
-        <v>0.796702325344086</v>
+        <v>0.796702265739441</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G968" t="n">
-        <v>0.771556258201599</v>
+        <v>0.771556198596954</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G971" t="n">
-        <v>0.781982600688934</v>
+        <v>0.781982660293579</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G972" t="n">
-        <v>0.834114909172058</v>
+        <v>0.834114849567413</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G981" t="n">
-        <v>0.981311559677124</v>
+        <v>0.981311500072479</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G982" t="n">
-        <v>0.94451230764389</v>
+        <v>0.94451242685318</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G984" t="n">
-        <v>0.961685299873352</v>
+        <v>0.961685359477997</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G986" t="n">
-        <v>0.931019365787506</v>
+        <v>0.931019306182861</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G988" t="n">
-        <v>0.875820577144623</v>
+        <v>0.875820517539978</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G991" t="n">
-        <v>0.863554120063782</v>
+        <v>0.863554239273071</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>1.53100001811981</v>
       </c>
       <c r="G994" t="n">
-        <v>0.938992500305176</v>
+        <v>0.938992559909821</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>1.52699995040894</v>
       </c>
       <c r="G996" t="n">
-        <v>0.936539173126221</v>
+        <v>0.936539232730865</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>1.49300003051758</v>
       </c>
       <c r="G997" t="n">
-        <v>0.915686428546906</v>
+        <v>0.915686368942261</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G998" t="n">
-        <v>0.935312628746033</v>
+        <v>0.935312569141388</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1004" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.04141676425934</v>
+        <v>1.04141688346863</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G1007" t="n">
-        <v>1.05123007297516</v>
+        <v>1.05122995376587</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.03957688808441</v>
+        <v>1.0395770072937</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.0193372964859</v>
+        <v>1.01933741569519</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>1.63900005817413</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.00523114204407</v>
+        <v>1.00523102283478</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.00277769565582</v>
+        <v>1.00277781486511</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1014" t="n">
-        <v>0.980084896087646</v>
+        <v>0.980085015296936</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1015" t="n">
-        <v>0.980084896087646</v>
+        <v>0.980085015296936</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>1.57599997520447</v>
       </c>
       <c r="G1017" t="n">
-        <v>0.966591894626617</v>
+        <v>0.966591954231262</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1018" t="n">
-        <v>0.94451230764389</v>
+        <v>0.94451242685318</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1020" t="n">
-        <v>0.956778764724731</v>
+        <v>0.956778824329376</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1022" t="n">
-        <v>0.965978562831879</v>
+        <v>0.965978682041168</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G1023" t="n">
-        <v>0.967205226421356</v>
+        <v>0.967205166816711</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1025" t="n">
-        <v>0.980084896087646</v>
+        <v>0.980085015296936</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G1027" t="n">
-        <v>0.906486511230469</v>
+        <v>0.906486630439758</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1028" t="n">
-        <v>0.864780843257904</v>
+        <v>0.864780783653259</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1029" t="n">
-        <v>0.858647584915161</v>
+        <v>0.858647644519806</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1031" t="n">
-        <v>0.815715253353119</v>
+        <v>0.815715193748474</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G1033" t="n">
-        <v>0.767876267433167</v>
+        <v>0.767876327037811</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>1.26699995994568</v>
       </c>
       <c r="G1034" t="n">
-        <v>0.777076065540314</v>
+        <v>0.777076125144958</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G1038" t="n">
-        <v>0.781982600688934</v>
+        <v>0.781982660293579</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>1.2940000295639</v>
       </c>
       <c r="G1039" t="n">
-        <v>0.793635725975037</v>
+        <v>0.793635785579681</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G1046" t="n">
-        <v>0.806515514850616</v>
+        <v>0.806515455245972</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>1.30200004577637</v>
       </c>
       <c r="G1047" t="n">
-        <v>0.798542380332947</v>
+        <v>0.798542320728302</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1050" t="n">
-        <v>0.803448796272278</v>
+        <v>0.803448855876923</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>1.28699994087219</v>
       </c>
       <c r="G1052" t="n">
-        <v>0.789342403411865</v>
+        <v>0.789342522621155</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G1055" t="n">
-        <v>0.708997666835785</v>
+        <v>0.70899760723114</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>1.13699996471405</v>
       </c>
       <c r="G1056" t="n">
-        <v>0.697344541549683</v>
+        <v>0.697344481945038</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>1.07299995422363</v>
       </c>
       <c r="G1057" t="n">
-        <v>0.658092081546783</v>
+        <v>0.658092021942139</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>1.04299998283386</v>
       </c>
       <c r="G1058" t="n">
-        <v>0.639692485332489</v>
+        <v>0.639692425727844</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>0.972500026226044</v>
       </c>
       <c r="G1060" t="n">
-        <v>0.596453428268433</v>
+        <v>0.596453487873077</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.572227358818054</v>
+        <v>0.572227299213409</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.496789008378983</v>
+        <v>0.49678897857666</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.451403349637985</v>
+        <v>0.451403319835663</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>0.726999998092651</v>
       </c>
       <c r="G1068" t="n">
-        <v>0.445883482694626</v>
+        <v>0.445883452892303</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.472256153821945</v>
+        <v>0.47225621342659</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.461216449737549</v>
+        <v>0.461216419935226</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.4747094810009</v>
+        <v>0.474709451198578</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.490655779838562</v>
+        <v>0.49065575003624</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>0.816999971866608</v>
       </c>
       <c r="G1074" t="n">
-        <v>0.501082181930542</v>
+        <v>0.501082241535187</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.469802916049957</v>
+        <v>0.469802886247635</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1077" t="n">
-        <v>0.417057454586029</v>
+        <v>0.417057424783707</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>0.679000020027161</v>
       </c>
       <c r="G1078" t="n">
-        <v>0.416444152593613</v>
+        <v>0.416444092988968</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1080" t="n">
-        <v>0.394977927207947</v>
+        <v>0.394977897405624</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>0.679000020027161</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.416444152593613</v>
+        <v>0.416444092988968</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.434230387210846</v>
+        <v>0.434230357408524</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.496789008378983</v>
+        <v>0.49678897857666</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>0.816999971866608</v>
       </c>
       <c r="G1089" t="n">
-        <v>0.501082181930542</v>
+        <v>0.501082241535187</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>0.915000021457672</v>
       </c>
       <c r="G1093" t="n">
-        <v>0.561187565326691</v>
+        <v>0.561187505722046</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>0.880999982357025</v>
       </c>
       <c r="G1096" t="n">
-        <v>0.540334701538086</v>
+        <v>0.540334641933441</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G1100" t="n">
-        <v>0.512121975421906</v>
+        <v>0.51212203502655</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.506602108478546</v>
+        <v>0.506602048873901</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>0.83899998664856</v>
       </c>
       <c r="G1105" t="n">
-        <v>0.514575242996216</v>
+        <v>0.514575183391571</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>0.830999970436096</v>
       </c>
       <c r="G1108" t="n">
-        <v>0.50966864824295</v>
+        <v>0.509668707847595</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>0.820999979972839</v>
       </c>
       <c r="G1109" t="n">
-        <v>0.503535449504852</v>
+        <v>0.503535509109497</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>0.848999977111816</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.520708382129669</v>
+        <v>0.520708441734314</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1118" t="n">
-        <v>0.545854508876801</v>
+        <v>0.545854568481445</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G1122" t="n">
-        <v>0.610866487026215</v>
+        <v>0.61086642742157</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1124" t="n">
-        <v>0.643985688686371</v>
+        <v>0.643985629081726</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>1.07400000095367</v>
       </c>
       <c r="G1125" t="n">
-        <v>0.658705472946167</v>
+        <v>0.658705353736877</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>1</v>
       </c>
       <c r="G1126" t="n">
-        <v>0.61331969499588</v>
+        <v>0.613319754600525</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G1127" t="n">
-        <v>0.610866487026215</v>
+        <v>0.61086642742157</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1130" t="n">
-        <v>0.569160640239716</v>
+        <v>0.56916069984436</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>0.85699999332428</v>
       </c>
       <c r="G1138" t="n">
-        <v>0.525615036487579</v>
+        <v>0.525614976882935</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1140" t="n">
-        <v>0.527455031871796</v>
+        <v>0.527454972267151</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>0.85699999332428</v>
       </c>
       <c r="G1143" t="n">
-        <v>0.525615036487579</v>
+        <v>0.525614976882935</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>0.845000028610229</v>
       </c>
       <c r="G1146" t="n">
-        <v>0.518255233764648</v>
+        <v>0.518255174160004</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1147" t="n">
-        <v>0.528681576251984</v>
+        <v>0.528681635856628</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>0.83899998664856</v>
       </c>
       <c r="G1148" t="n">
-        <v>0.514575242996216</v>
+        <v>0.514575183391571</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1149" t="n">
-        <v>0.522548377513885</v>
+        <v>0.52254843711853</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>0.859000027179718</v>
       </c>
       <c r="G1150" t="n">
-        <v>0.526841640472412</v>
+        <v>0.526841700077057</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1151" t="n">
-        <v>0.534814774990082</v>
+        <v>0.534814834594727</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.555054366588593</v>
+        <v>0.555054306983948</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1156" t="n">
-        <v>0.542174637317657</v>
+        <v>0.542174577713013</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1157" t="n">
-        <v>0.545854508876801</v>
+        <v>0.545854568481445</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1158" t="n">
-        <v>0.545854508876801</v>
+        <v>0.545854568481445</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>0.879000008106232</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.539108097553253</v>
+        <v>0.539108037948608</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.542174637317657</v>
+        <v>0.542174577713013</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>0.879000008106232</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.539108097553253</v>
+        <v>0.539108037948608</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>0.890999972820282</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.546467900276184</v>
+        <v>0.546467840671539</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.564254224300385</v>
+        <v>0.56425416469574</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1167" t="n">
-        <v>0.575293898582458</v>
+        <v>0.575293958187103</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>0.907000005245209</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.556280970573425</v>
+        <v>0.55628103017807</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.567320704460144</v>
+        <v>0.567320764064789</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G1171" t="n">
-        <v>0.604733288288116</v>
+        <v>0.604733228683472</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.582653701305389</v>
+        <v>0.582653760910034</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>0.939000010490417</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.575907289981842</v>
+        <v>0.575907230377197</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>0.930999994277954</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.571000635623932</v>
+        <v>0.571000695228577</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>0.962999999523163</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.590626895427704</v>
+        <v>0.590626955032349</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>0.962999999523163</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.590626895427704</v>
+        <v>0.590626955032349</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>0.964999973773956</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.591853499412537</v>
+        <v>0.591853559017181</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.588786959648132</v>
+        <v>0.588786900043488</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.5875603556633</v>
+        <v>0.587560296058655</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.578973770141602</v>
+        <v>0.578973829746246</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.569160640239716</v>
+        <v>0.56916069984436</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>0.902999997138977</v>
       </c>
       <c r="G1186" t="n">
-        <v>0.553827702999115</v>
+        <v>0.55382776260376</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.572227358818054</v>
+        <v>0.572227299213409</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.547081232070923</v>
+        <v>0.547081172466278</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>0.939000010490417</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.575907289981842</v>
+        <v>0.575907230377197</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.569160640239716</v>
+        <v>0.56916069984436</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.569160640239716</v>
+        <v>0.56916069984436</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.592466831207275</v>
+        <v>0.59246689081192</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>0.89300000667572</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.547694504261017</v>
+        <v>0.547694563865662</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.555667638778687</v>
+        <v>0.555667698383331</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G1204" t="n">
-        <v>0.555054366588593</v>
+        <v>0.555054306983948</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>0.91100001335144</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.55873429775238</v>
+        <v>0.558734357357025</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.572227358818054</v>
+        <v>0.572227299213409</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.571613967418671</v>
+        <v>0.571614027023315</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.56670743227005</v>
+        <v>0.566707491874695</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G1219" t="n">
-        <v>0.56670743227005</v>
+        <v>0.566707491874695</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G1220" t="n">
-        <v>0.56670743227005</v>
+        <v>0.566707491874695</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G1224" t="n">
-        <v>0.597373425960541</v>
+        <v>0.597373366355896</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.565480828285217</v>
+        <v>0.565480768680573</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.572227358818054</v>
+        <v>0.572227299213409</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>0.967000007629395</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.593080222606659</v>
+        <v>0.593080163002014</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.588786959648132</v>
+        <v>0.588786900043488</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.619452893733978</v>
+        <v>0.619452953338623</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>1.15799999237061</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.710224211215973</v>
+        <v>0.710224270820618</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1243" t="n">
-        <v>0.711450815200806</v>
+        <v>0.71145087480545</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G1245" t="n">
-        <v>0.708997666835785</v>
+        <v>0.70899760723114</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1247" t="n">
-        <v>0.788729131221771</v>
+        <v>0.788729190826416</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.775236248970032</v>
+        <v>0.775236189365387</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G1250" t="n">
-        <v>0.780142664909363</v>
+        <v>0.780142605304718</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1252" t="n">
-        <v>0.754383206367493</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>1.25</v>
       </c>
       <c r="G1253" t="n">
-        <v>0.766649663448334</v>
+        <v>0.766649723052979</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.743343472480774</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.739663660526276</v>
+        <v>0.739663541316986</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1262" t="n">
-        <v>0.759289920330048</v>
+        <v>0.759289860725403</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.723717212677002</v>
+        <v>0.723717272281647</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.723717212677002</v>
+        <v>0.723717272281647</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1270" t="n">
-        <v>0.724943995475769</v>
+        <v>0.724943935871124</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1272" t="n">
-        <v>0.743343472480774</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G1273" t="n">
-        <v>0.737210333347321</v>
+        <v>0.737210273742676</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.761743068695068</v>
+        <v>0.761743128299713</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1281" t="n">
-        <v>0.720037341117859</v>
+        <v>0.720037400722504</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G1282" t="n">
-        <v>0.713904201984406</v>
+        <v>0.713904142379761</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1283" t="n">
-        <v>0.717584073543549</v>
+        <v>0.717584133148193</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1285" t="n">
-        <v>0.723717212677002</v>
+        <v>0.723717272281647</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G1288" t="n">
-        <v>0.70654433965683</v>
+        <v>0.706544280052185</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>1.14800000190735</v>
       </c>
       <c r="G1289" t="n">
-        <v>0.704091012477875</v>
+        <v>0.70409107208252</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G1291" t="n">
-        <v>0.688144683837891</v>
+        <v>0.688144743442535</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1293" t="n">
-        <v>0.693051338195801</v>
+        <v>0.693051278591156</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.708997666835785</v>
+        <v>0.70899760723114</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.720037341117859</v>
+        <v>0.720037400722504</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1299" t="n">
-        <v>0.743343472480774</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1304" t="n">
-        <v>0.759289920330048</v>
+        <v>0.759289860725403</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1306" t="n">
-        <v>0.762969791889191</v>
+        <v>0.762969732284546</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G1310" t="n">
-        <v>0.794862389564514</v>
+        <v>0.794862329959869</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>1.32200002670288</v>
       </c>
       <c r="G1312" t="n">
-        <v>0.810808718204498</v>
+        <v>0.810808777809143</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1314" t="n">
-        <v>0.824301660060883</v>
+        <v>0.824301719665527</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.803448796272278</v>
+        <v>0.803448855876923</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1320" t="n">
-        <v>0.792409121990204</v>
+        <v>0.792409062385559</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1321" t="n">
-        <v>0.815715253353119</v>
+        <v>0.815715193748474</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G1323" t="n">
-        <v>0.841474711894989</v>
+        <v>0.841474652290344</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1324" t="n">
-        <v>0.858647584915161</v>
+        <v>0.858647644519806</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1325" t="n">
-        <v>0.858647584915161</v>
+        <v>0.858647644519806</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>1.38399994373322</v>
       </c>
       <c r="G1326" t="n">
-        <v>0.848834455013275</v>
+        <v>0.84883451461792</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G1327" t="n">
-        <v>0.829208314418793</v>
+        <v>0.829208254814148</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1328" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1334" t="n">
-        <v>0.85128778219223</v>
+        <v>0.851287841796875</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1335" t="n">
-        <v>0.834114909172058</v>
+        <v>0.834114849567413</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1341" t="n">
-        <v>0.834114909172058</v>
+        <v>0.834114849567413</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G1342" t="n">
-        <v>0.841474711894989</v>
+        <v>0.841474652290344</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1345" t="n">
-        <v>0.815715253353119</v>
+        <v>0.815715193748474</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1347" t="n">
-        <v>0.803448796272278</v>
+        <v>0.803448855876923</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G1349" t="n">
-        <v>0.853741049766541</v>
+        <v>0.853741109371185</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1351" t="n">
-        <v>0.877047181129456</v>
+        <v>0.8770472407341</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1355" t="n">
-        <v>0.864780843257904</v>
+        <v>0.864780783653259</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G1356" t="n">
-        <v>0.880727171897888</v>
+        <v>0.880727112293243</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>1.44599997997284</v>
       </c>
       <c r="G1359" t="n">
-        <v>0.886860251426697</v>
+        <v>0.886860370635986</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>1.42599999904633</v>
       </c>
       <c r="G1360" t="n">
-        <v>0.874593913555145</v>
+        <v>0.87459397315979</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G1361" t="n">
-        <v>0.875820577144623</v>
+        <v>0.875820517539978</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1362" t="n">
-        <v>0.85128778219223</v>
+        <v>0.851287841796875</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1364" t="n">
-        <v>0.863554120063782</v>
+        <v>0.863554239273071</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1365" t="n">
-        <v>0.863554120063782</v>
+        <v>0.863554239273071</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1368" t="n">
-        <v>0.834114909172058</v>
+        <v>0.834114849567413</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1373" t="n">
-        <v>0.834114909172058</v>
+        <v>0.834114849567413</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G1374" t="n">
-        <v>0.861100912094116</v>
+        <v>0.861100971698761</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1375" t="n">
-        <v>0.863554120063782</v>
+        <v>0.863554239273071</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G1376" t="n">
-        <v>0.861100912094116</v>
+        <v>0.861100971698761</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1377" t="n">
-        <v>0.866007447242737</v>
+        <v>0.866007506847382</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G1381" t="n">
-        <v>0.940832436084747</v>
+        <v>0.940832495689392</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G1383" t="n">
-        <v>0.915073096752167</v>
+        <v>0.915073037147522</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1385" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G1386" t="n">
-        <v>0.945739090442657</v>
+        <v>0.945739030838013</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G1389" t="n">
-        <v>0.921206176280975</v>
+        <v>0.921206295490265</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G1394" t="n">
-        <v>0.861100912094116</v>
+        <v>0.861100971698761</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G1395" t="n">
-        <v>0.861100912094116</v>
+        <v>0.861100971698761</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1396" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1400" t="n">
-        <v>0.820621848106384</v>
+        <v>0.82062178850174</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>1.27600002288818</v>
       </c>
       <c r="G1402" t="n">
-        <v>0.782596051692963</v>
+        <v>0.782595992088318</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G1403" t="n">
-        <v>0.794862389564514</v>
+        <v>0.794862329959869</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>1.29799997806549</v>
       </c>
       <c r="G1404" t="n">
-        <v>0.796088993549347</v>
+        <v>0.796089053153992</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1406" t="n">
-        <v>0.785049259662628</v>
+        <v>0.785049200057983</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1408" t="n">
-        <v>0.754383206367493</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1409" t="n">
-        <v>0.723717212677002</v>
+        <v>0.723717272281647</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G1410" t="n">
-        <v>0.737210333347321</v>
+        <v>0.737210273742676</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1414" t="n">
-        <v>0.858647584915161</v>
+        <v>0.858647644519806</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1415" t="n">
-        <v>0.866007447242737</v>
+        <v>0.866007506847382</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.852514445781708</v>
+        <v>0.852514386177063</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G1417" t="n">
-        <v>0.850061178207397</v>
+        <v>0.850061118602753</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1423" t="n">
-        <v>0.85128778219223</v>
+        <v>0.851287841796875</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G1424" t="n">
-        <v>0.850061178207397</v>
+        <v>0.850061118602753</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G1425" t="n">
-        <v>0.857421040534973</v>
+        <v>0.857420980930328</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1426" t="n">
-        <v>0.858647584915161</v>
+        <v>0.858647644519806</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1427" t="n">
-        <v>0.864780843257904</v>
+        <v>0.864780783653259</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>1.42599999904633</v>
       </c>
       <c r="G1430" t="n">
-        <v>0.874593913555145</v>
+        <v>0.87459397315979</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>1.43400001525879</v>
       </c>
       <c r="G1431" t="n">
-        <v>0.879500567913055</v>
+        <v>0.879500508308411</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G1432" t="n">
-        <v>0.853741049766541</v>
+        <v>0.853741109371185</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1438" t="n">
-        <v>0.852514445781708</v>
+        <v>0.852514386177063</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>1.42400002479553</v>
       </c>
       <c r="G1439" t="n">
-        <v>0.873367309570312</v>
+        <v>0.873367249965668</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1440" t="n">
-        <v>0.858647584915161</v>
+        <v>0.858647644519806</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G1441" t="n">
-        <v>0.857421040534973</v>
+        <v>0.857420980930328</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1443" t="n">
-        <v>0.866007447242737</v>
+        <v>0.866007506847382</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1444" t="n">
-        <v>0.852514445781708</v>
+        <v>0.852514386177063</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G1445" t="n">
-        <v>0.850061178207397</v>
+        <v>0.850061118602753</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G1447" t="n">
-        <v>0.823075115680695</v>
+        <v>0.82307505607605</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G1451" t="n">
-        <v>0.823075115680695</v>
+        <v>0.82307505607605</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>1.27600002288818</v>
       </c>
       <c r="G1454" t="n">
-        <v>0.782596051692963</v>
+        <v>0.782595992088318</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>1.33200001716614</v>
       </c>
       <c r="G1459" t="n">
-        <v>0.816941857337952</v>
+        <v>0.816941916942596</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1461" t="n">
-        <v>0.803448796272278</v>
+        <v>0.803448855876923</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>1.29799997806549</v>
       </c>
       <c r="G1462" t="n">
-        <v>0.796088993549347</v>
+        <v>0.796089053153992</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1463" t="n">
-        <v>0.785049259662628</v>
+        <v>0.785049200057983</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1464" t="n">
-        <v>0.788729131221771</v>
+        <v>0.788729190826416</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1465" t="n">
-        <v>0.792409121990204</v>
+        <v>0.792409062385559</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1466" t="n">
-        <v>0.78136932849884</v>
+        <v>0.781369388103485</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>1.30200004577637</v>
       </c>
       <c r="G1468" t="n">
-        <v>0.798542380332947</v>
+        <v>0.798542320728302</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1469" t="n">
-        <v>0.788729131221771</v>
+        <v>0.788729190826416</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1470" t="n">
-        <v>0.809582114219666</v>
+        <v>0.809582054615021</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1471" t="n">
-        <v>0.815715253353119</v>
+        <v>0.815715193748474</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1473" t="n">
-        <v>0.834114909172058</v>
+        <v>0.834114849567413</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1474" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G1475" t="n">
-        <v>0.829208314418793</v>
+        <v>0.829208254814148</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1476" t="n">
-        <v>0.824301660060883</v>
+        <v>0.824301719665527</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1477" t="n">
-        <v>0.85619443655014</v>
+        <v>0.856194376945496</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1478" t="n">
-        <v>0.85128778219223</v>
+        <v>0.851287841796875</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1479" t="n">
-        <v>0.883180379867554</v>
+        <v>0.883180439472198</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>1.44799995422363</v>
       </c>
       <c r="G1480" t="n">
-        <v>0.888086974620819</v>
+        <v>0.888086915016174</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G1481" t="n">
-        <v>0.850061178207397</v>
+        <v>0.850061118602753</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1482" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1483" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1484" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1486" t="n">
-        <v>0.824301660060883</v>
+        <v>0.824301719665527</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G1487" t="n">
-        <v>0.819395124912262</v>
+        <v>0.819395184516907</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1489" t="n">
-        <v>0.824301660060883</v>
+        <v>0.824301719665527</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>1.29799997806549</v>
       </c>
       <c r="G1492" t="n">
-        <v>0.796088993549347</v>
+        <v>0.796089053153992</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1494" t="n">
-        <v>0.824301660060883</v>
+        <v>0.824301719665527</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G1495" t="n">
-        <v>0.823075115680695</v>
+        <v>0.82307505607605</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>1.33200001716614</v>
       </c>
       <c r="G1497" t="n">
-        <v>0.816941857337952</v>
+        <v>0.816941916942596</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1499" t="n">
-        <v>0.809582114219666</v>
+        <v>0.809582054615021</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>1.2940000295639</v>
       </c>
       <c r="G1502" t="n">
-        <v>0.793635725975037</v>
+        <v>0.793635785579681</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1506" t="n">
-        <v>0.743343472480774</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G1509" t="n">
-        <v>0.722490608692169</v>
+        <v>0.722490549087524</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1512" t="n">
-        <v>0.743343472480774</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1513" t="n">
-        <v>0.743343472480774</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>1.18599998950958</v>
       </c>
       <c r="G1515" t="n">
-        <v>0.727397203445435</v>
+        <v>0.72739714384079</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>1.21599996089935</v>
       </c>
       <c r="G1517" t="n">
-        <v>0.745796740055084</v>
+        <v>0.745796799659729</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G1518" t="n">
-        <v>0.731077075004578</v>
+        <v>0.731077134609222</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G1520" t="n">
-        <v>0.738436937332153</v>
+        <v>0.738436996936798</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G1521" t="n">
-        <v>0.731077075004578</v>
+        <v>0.731077134609222</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1522" t="n">
-        <v>0.724943995475769</v>
+        <v>0.724943935871124</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1524" t="n">
-        <v>0.723717212677002</v>
+        <v>0.723717272281647</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1525" t="n">
-        <v>0.723717212677002</v>
+        <v>0.723717272281647</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1526" t="n">
-        <v>0.724943995475769</v>
+        <v>0.724943935871124</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G1530" t="n">
-        <v>0.758063137531281</v>
+        <v>0.758063197135925</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1532" t="n">
-        <v>0.78136932849884</v>
+        <v>0.781369388103485</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G1533" t="n">
-        <v>0.780142664909363</v>
+        <v>0.780142605304718</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1536" t="n">
-        <v>0.788729131221771</v>
+        <v>0.788729190826416</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1538" t="n">
-        <v>0.771556258201599</v>
+        <v>0.771556198596954</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1539" t="n">
-        <v>0.762969791889191</v>
+        <v>0.762969732284546</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1540" t="n">
-        <v>0.775236248970032</v>
+        <v>0.775236189365387</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G1542" t="n">
-        <v>0.731077075004578</v>
+        <v>0.731077134609222</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1547" t="n">
-        <v>0.7323037981987</v>
+        <v>0.732303738594055</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1550" t="n">
-        <v>0.754383206367493</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1554" t="n">
-        <v>0.739663660526276</v>
+        <v>0.739663541316986</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1557" t="n">
-        <v>0.711450815200806</v>
+        <v>0.71145087480545</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1558" t="n">
-        <v>0.720037341117859</v>
+        <v>0.720037400722504</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>1.14800000190735</v>
       </c>
       <c r="G1562" t="n">
-        <v>0.704091012477875</v>
+        <v>0.70409107208252</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G1563" t="n">
-        <v>0.696731209754944</v>
+        <v>0.696731269359589</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1564" t="n">
-        <v>0.705317735671997</v>
+        <v>0.705317676067352</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>1.06200003623962</v>
       </c>
       <c r="G1565" t="n">
-        <v>0.651345610618591</v>
+        <v>0.651345551013947</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>1.12399995326996</v>
       </c>
       <c r="G1567" t="n">
-        <v>0.689371407032013</v>
+        <v>0.689371347427368</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1568" t="n">
-        <v>0.631719350814819</v>
+        <v>0.631719291210175</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1571" t="n">
-        <v>0.51764190196991</v>
+        <v>0.517641842365265</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>0.788999974727631</v>
       </c>
       <c r="G1572" t="n">
-        <v>0.483909219503403</v>
+        <v>0.483909249305725</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1573" t="n">
-        <v>0.480842649936676</v>
+        <v>0.480842679738998</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G1574" t="n">
-        <v>0.520095109939575</v>
+        <v>0.52009516954422</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>0.802999973297119</v>
       </c>
       <c r="G1575" t="n">
-        <v>0.492495775222778</v>
+        <v>0.492495715618134</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>0.814999997615814</v>
       </c>
       <c r="G1578" t="n">
-        <v>0.499855577945709</v>
+        <v>0.499855607748032</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>0.897000014781952</v>
       </c>
       <c r="G1582" t="n">
-        <v>0.550147771835327</v>
+        <v>0.550147831439972</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>0.879000008106232</v>
       </c>
       <c r="G1584" t="n">
-        <v>0.539108097553253</v>
+        <v>0.539108037948608</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1586" t="n">
-        <v>0.534814774990082</v>
+        <v>0.534814834594727</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G1588" t="n">
-        <v>0.565480828285217</v>
+        <v>0.565480768680573</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>0.890999972820282</v>
       </c>
       <c r="G1589" t="n">
-        <v>0.546467900276184</v>
+        <v>0.546467840671539</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1596" t="n">
-        <v>0.510282039642334</v>
+        <v>0.510281980037689</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1598" t="n">
-        <v>0.51764190196991</v>
+        <v>0.517641842365265</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1599" t="n">
-        <v>0.528681576251984</v>
+        <v>0.528681635856628</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1602" t="n">
-        <v>0.564254224300385</v>
+        <v>0.56425416469574</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>0.859000027179718</v>
       </c>
       <c r="G1609" t="n">
-        <v>0.526841640472412</v>
+        <v>0.526841700077057</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>0.869000017642975</v>
       </c>
       <c r="G1611" t="n">
-        <v>0.53297483921051</v>
+        <v>0.532974898815155</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>0.830999970436096</v>
       </c>
       <c r="G1613" t="n">
-        <v>0.50966864824295</v>
+        <v>0.509668707847595</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1614" t="n">
-        <v>0.51764190196991</v>
+        <v>0.517641842365265</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1615" t="n">
-        <v>0.509055316448212</v>
+        <v>0.509055376052856</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G1617" t="n">
-        <v>0.520095109939575</v>
+        <v>0.52009516954422</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1618" t="n">
-        <v>0.509055316448212</v>
+        <v>0.509055376052856</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1619" t="n">
-        <v>0.509055316448212</v>
+        <v>0.509055376052856</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G1620" t="n">
-        <v>0.519481837749481</v>
+        <v>0.519481778144836</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1621" t="n">
-        <v>0.527455031871796</v>
+        <v>0.527454972267151</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>0.869000017642975</v>
       </c>
       <c r="G1625" t="n">
-        <v>0.53297483921051</v>
+        <v>0.532974898815155</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1626" t="n">
-        <v>0.527455031871796</v>
+        <v>0.527454972267151</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1629" t="n">
-        <v>0.572227358818054</v>
+        <v>0.572227299213409</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>0.950999975204468</v>
       </c>
       <c r="G1630" t="n">
-        <v>0.583267092704773</v>
+        <v>0.583267033100128</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G1631" t="n">
-        <v>0.574067294597626</v>
+        <v>0.574067234992981</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G1633" t="n">
-        <v>0.647665679454803</v>
+        <v>0.647665619850159</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1634" t="n">
-        <v>0.619452893733978</v>
+        <v>0.619452953338623</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G1637" t="n">
-        <v>0.628039419651031</v>
+        <v>0.628039479255676</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1638" t="n">
-        <v>0.619452893733978</v>
+        <v>0.619452953338623</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1640" t="n">
-        <v>0.545854508876801</v>
+        <v>0.545854568481445</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>0.89300000667572</v>
       </c>
       <c r="G1642" t="n">
-        <v>0.547694504261017</v>
+        <v>0.547694563865662</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>0.869000017642975</v>
       </c>
       <c r="G1644" t="n">
-        <v>0.53297483921051</v>
+        <v>0.532974898815155</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>0.887000024318695</v>
       </c>
       <c r="G1646" t="n">
-        <v>0.544014573097229</v>
+        <v>0.544014632701874</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G1648" t="n">
-        <v>0.547081232070923</v>
+        <v>0.547081172466278</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1652" t="n">
-        <v>0.527455031871796</v>
+        <v>0.527454972267151</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G1655" t="n">
-        <v>0.512121975421906</v>
+        <v>0.51212203502655</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>0.788999974727631</v>
       </c>
       <c r="G1657" t="n">
-        <v>0.483909219503403</v>
+        <v>0.483909249305725</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>0.83899998664856</v>
       </c>
       <c r="G1659" t="n">
-        <v>0.514575242996216</v>
+        <v>0.514575183391571</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1660" t="n">
-        <v>0.509055316448212</v>
+        <v>0.509055376052856</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1664" t="n">
-        <v>0.482069283723831</v>
+        <v>0.482069343328476</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>0.785000026226044</v>
       </c>
       <c r="G1665" t="n">
-        <v>0.481456011533737</v>
+        <v>0.481455981731415</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1668" t="n">
-        <v>0.480842649936676</v>
+        <v>0.480842679738998</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1669" t="n">
-        <v>0.509055316448212</v>
+        <v>0.509055376052856</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>0.930999994277954</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.571000635623932</v>
+        <v>0.571000695228577</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>0.922999978065491</v>
       </c>
       <c r="G1673" t="n">
-        <v>0.566094160079956</v>
+        <v>0.566094100475311</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>0.915000021457672</v>
       </c>
       <c r="G1674" t="n">
-        <v>0.561187565326691</v>
+        <v>0.561187505722046</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>0.915000021457672</v>
       </c>
       <c r="G1675" t="n">
-        <v>0.561187565326691</v>
+        <v>0.561187505722046</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G1676" t="n">
-        <v>0.56670743227005</v>
+        <v>0.566707491874695</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>0.922999978065491</v>
       </c>
       <c r="G1678" t="n">
-        <v>0.566094160079956</v>
+        <v>0.566094100475311</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>0.890999972820282</v>
       </c>
       <c r="G1680" t="n">
-        <v>0.546467900276184</v>
+        <v>0.546467840671539</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>0.880999982357025</v>
       </c>
       <c r="G1686" t="n">
-        <v>0.540334701538086</v>
+        <v>0.540334641933441</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>0.887000024318695</v>
       </c>
       <c r="G1691" t="n">
-        <v>0.544014573097229</v>
+        <v>0.544014632701874</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.527455031871796</v>
+        <v>0.527454972267151</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1698" t="n">
-        <v>0.509055316448212</v>
+        <v>0.509055376052856</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1699" t="n">
-        <v>0.506602108478546</v>
+        <v>0.506602048873901</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1701" t="n">
-        <v>0.490655779838562</v>
+        <v>0.49065575003624</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1702" t="n">
-        <v>0.485749214887619</v>
+        <v>0.485749244689941</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1703" t="n">
-        <v>0.485749214887619</v>
+        <v>0.485749244689941</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>0.809000015258789</v>
       </c>
       <c r="G1704" t="n">
-        <v>0.496175676584244</v>
+        <v>0.496175706386566</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1705" t="n">
-        <v>0.484522610902786</v>
+        <v>0.484522551298141</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1708" t="n">
-        <v>0.4747094810009</v>
+        <v>0.474709451198578</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1709" t="n">
-        <v>0.4747094810009</v>
+        <v>0.474709451198578</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1710" t="n">
-        <v>0.472256153821945</v>
+        <v>0.47225621342659</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G1711" t="n">
-        <v>0.456923186779022</v>
+        <v>0.456923216581345</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1712" t="n">
-        <v>0.453243255615234</v>
+        <v>0.453243315219879</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1713" t="n">
-        <v>0.436683654785156</v>
+        <v>0.436683624982834</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1715" t="n">
-        <v>0.437910288572311</v>
+        <v>0.437910258769989</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G1717" t="n">
-        <v>0.432390421628952</v>
+        <v>0.43239039182663</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>0.712999999523163</v>
       </c>
       <c r="G1719" t="n">
-        <v>0.437296956777573</v>
+        <v>0.437296986579895</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G1720" t="n">
-        <v>0.438523590564728</v>
+        <v>0.43852362036705</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1722" t="n">
-        <v>0.42809721827507</v>
+        <v>0.428097188472748</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1723" t="n">
-        <v>0.429323792457581</v>
+        <v>0.429323822259903</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1724" t="n">
-        <v>0.414604157209396</v>
+        <v>0.414604127407074</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>0.66100001335144</v>
       </c>
       <c r="G1725" t="n">
-        <v>0.405404359102249</v>
+        <v>0.405404388904572</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1726" t="n">
-        <v>0.417057454586029</v>
+        <v>0.417057424783707</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1728" t="n">
-        <v>0.429323792457581</v>
+        <v>0.429323822259903</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1729" t="n">
-        <v>0.431777060031891</v>
+        <v>0.431777119636536</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1731" t="n">
-        <v>0.433003723621368</v>
+        <v>0.433003753423691</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1732" t="n">
-        <v>0.490655779838562</v>
+        <v>0.49065575003624</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1733" t="n">
-        <v>0.527455031871796</v>
+        <v>0.527454972267151</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>0.859000027179718</v>
       </c>
       <c r="G1747" t="n">
-        <v>0.526841640472412</v>
+        <v>0.526841700077057</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G1749" t="n">
-        <v>0.586333632469177</v>
+        <v>0.586333692073822</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1750" t="n">
-        <v>0.575293898582458</v>
+        <v>0.575293958187103</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G1751" t="n">
-        <v>0.567320704460144</v>
+        <v>0.567320764064789</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1754" t="n">
-        <v>0.542174637317657</v>
+        <v>0.542174577713013</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1756" t="n">
-        <v>0.525001645088196</v>
+        <v>0.525001704692841</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1759" t="n">
-        <v>0.534814774990082</v>
+        <v>0.534814834594727</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1761" t="n">
-        <v>0.545854508876801</v>
+        <v>0.545854568481445</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1764" t="n">
-        <v>0.525001645088196</v>
+        <v>0.525001704692841</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G1765" t="n">
-        <v>0.519481837749481</v>
+        <v>0.519481778144836</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G1766" t="n">
-        <v>0.519481837749481</v>
+        <v>0.519481778144836</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>0.845000028610229</v>
       </c>
       <c r="G1768" t="n">
-        <v>0.518255233764648</v>
+        <v>0.518255174160004</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1772" t="n">
-        <v>0.528681576251984</v>
+        <v>0.528681635856628</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1773" t="n">
-        <v>0.527455031871796</v>
+        <v>0.527454972267151</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G1778" t="n">
-        <v>0.567934095859528</v>
+        <v>0.567934036254883</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1781" t="n">
-        <v>0.575293898582458</v>
+        <v>0.575293958187103</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>0.950999975204468</v>
       </c>
       <c r="G1787" t="n">
-        <v>0.583267092704773</v>
+        <v>0.583267033100128</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1790" t="n">
-        <v>0.619452893733978</v>
+        <v>0.619452953338623</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1794" t="n">
-        <v>0.674651741981506</v>
+        <v>0.674651682376862</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1795" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1797" t="n">
-        <v>0.673425018787384</v>
+        <v>0.673425078392029</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>1.09200000762939</v>
       </c>
       <c r="G1798" t="n">
-        <v>0.669745206832886</v>
+        <v>0.669745087623596</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1799" t="n">
-        <v>0.674651741981506</v>
+        <v>0.674651682376862</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1801" t="n">
-        <v>0.674651741981506</v>
+        <v>0.674651682376862</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1802" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1803" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1804" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G1805" t="n">
-        <v>0.688144683837891</v>
+        <v>0.688144743442535</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1808" t="n">
-        <v>0.720037341117859</v>
+        <v>0.720037400722504</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1810" t="n">
-        <v>0.723717212677002</v>
+        <v>0.723717272281647</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1812" t="n">
-        <v>0.7323037981987</v>
+        <v>0.732303738594055</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1814" t="n">
-        <v>0.743343472480774</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1820" t="n">
-        <v>0.724943995475769</v>
+        <v>0.724943935871124</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G1821" t="n">
-        <v>0.753156661987305</v>
+        <v>0.753156721591949</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>1.11800003051758</v>
       </c>
       <c r="G1822" t="n">
-        <v>0.685691475868225</v>
+        <v>0.68569153547287</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1826" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1827" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G1828" t="n">
-        <v>0.688144683837891</v>
+        <v>0.688144743442535</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1831" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1834" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1835" t="n">
-        <v>0.643985688686371</v>
+        <v>0.643985629081726</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G1836" t="n">
-        <v>0.628039419651031</v>
+        <v>0.628039479255676</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G1838" t="n">
-        <v>0.647665679454803</v>
+        <v>0.647665619850159</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1839" t="n">
-        <v>0.673425018787384</v>
+        <v>0.673425078392029</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1840" t="n">
-        <v>0.705317735671997</v>
+        <v>0.705317676067352</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1841" t="n">
-        <v>0.705317735671997</v>
+        <v>0.705317676067352</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G1843" t="n">
-        <v>0.696731209754944</v>
+        <v>0.696731269359589</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>1.11800003051758</v>
       </c>
       <c r="G1845" t="n">
-        <v>0.685691475868225</v>
+        <v>0.68569153547287</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1846" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>1.12399995326996</v>
       </c>
       <c r="G1848" t="n">
-        <v>0.689371407032013</v>
+        <v>0.689371347427368</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G1853" t="n">
-        <v>0.708997666835785</v>
+        <v>0.70899760723114</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1856" t="n">
-        <v>0.754383206367493</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1857" t="n">
-        <v>0.743343472480774</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>1.21599996089935</v>
       </c>
       <c r="G1858" t="n">
-        <v>0.745796740055084</v>
+        <v>0.745796799659729</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1860" t="n">
-        <v>0.7323037981987</v>
+        <v>0.732303738594055</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1861" t="n">
-        <v>0.723717212677002</v>
+        <v>0.723717272281647</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>1.18599998950958</v>
       </c>
       <c r="G1862" t="n">
-        <v>0.727397203445435</v>
+        <v>0.72739714384079</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G1864" t="n">
-        <v>0.753156661987305</v>
+        <v>0.753156721591949</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G1865" t="n">
-        <v>0.753156661987305</v>
+        <v>0.753156721591949</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1867" t="n">
-        <v>0.724943995475769</v>
+        <v>0.724943935871124</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -48937,7 +48937,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G1868" t="n">
-        <v>0.70654433965683</v>
+        <v>0.706544280052185</v>
       </c>
       <c r="H1868" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1869" t="n">
-        <v>0.717584073543549</v>
+        <v>0.717584133148193</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G1871" t="n">
-        <v>0.696731209754944</v>
+        <v>0.696731269359589</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G1872" t="n">
-        <v>0.713904201984406</v>
+        <v>0.713904142379761</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1873" t="n">
-        <v>0.711450815200806</v>
+        <v>0.71145087480545</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1874" t="n">
-        <v>0.711450815200806</v>
+        <v>0.71145087480545</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>1.15400004386902</v>
       </c>
       <c r="G1875" t="n">
-        <v>0.707770943641663</v>
+        <v>0.707771003246307</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>1.15400004386902</v>
       </c>
       <c r="G1876" t="n">
-        <v>0.707770943641663</v>
+        <v>0.707771003246307</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1877" t="n">
-        <v>0.705317735671997</v>
+        <v>0.705317676067352</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>1.15400004386902</v>
       </c>
       <c r="G1878" t="n">
-        <v>0.707770943641663</v>
+        <v>0.707771003246307</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1879" t="n">
-        <v>0.711450815200806</v>
+        <v>0.71145087480545</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G1882" t="n">
-        <v>0.688144683837891</v>
+        <v>0.688144743442535</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1883" t="n">
-        <v>0.705317735671997</v>
+        <v>0.705317676067352</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.688144683837891</v>
+        <v>0.688144743442535</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49405,7 +49405,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.673425018787384</v>
+        <v>0.673425078392029</v>
       </c>
       <c r="H1886" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.700411081314087</v>
+        <v>0.700411140918732</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1891" t="n">
-        <v>0.711450815200806</v>
+        <v>0.71145087480545</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49561,7 +49561,7 @@
         <v>1.15799999237061</v>
       </c>
       <c r="G1892" t="n">
-        <v>0.710224211215973</v>
+        <v>0.710224270820618</v>
       </c>
       <c r="H1892" t="s">
         <v>8</v>
@@ -49613,7 +49613,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G1894" t="n">
-        <v>0.716357469558716</v>
+        <v>0.716357409954071</v>
       </c>
       <c r="H1894" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1895" t="n">
-        <v>0.717584073543549</v>
+        <v>0.717584133148193</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49665,7 +49665,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1896" t="n">
-        <v>0.720037341117859</v>
+        <v>0.720037400722504</v>
       </c>
       <c r="H1896" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1899" t="n">
-        <v>0.717584073543549</v>
+        <v>0.717584133148193</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49769,7 +49769,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1900" t="n">
-        <v>0.720037341117859</v>
+        <v>0.720037400722504</v>
       </c>
       <c r="H1900" t="s">
         <v>8</v>
@@ -49847,7 +49847,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G1903" t="n">
-        <v>0.716357469558716</v>
+        <v>0.716357409954071</v>
       </c>
       <c r="H1903" t="s">
         <v>8</v>
@@ -49899,7 +49899,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1905" t="n">
-        <v>0.717584073543549</v>
+        <v>0.717584133148193</v>
       </c>
       <c r="H1905" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1906" t="n">
-        <v>0.717584073543549</v>
+        <v>0.717584133148193</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1910" t="n">
-        <v>0.754383206367493</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50107,7 +50107,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G1913" t="n">
-        <v>0.753156661987305</v>
+        <v>0.753156721591949</v>
       </c>
       <c r="H1913" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1914" t="n">
-        <v>0.759289920330048</v>
+        <v>0.759289860725403</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50185,7 +50185,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G1916" t="n">
-        <v>0.767876267433167</v>
+        <v>0.767876327037811</v>
       </c>
       <c r="H1916" t="s">
         <v>8</v>
@@ -50211,7 +50211,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1917" t="n">
-        <v>0.775236248970032</v>
+        <v>0.775236189365387</v>
       </c>
       <c r="H1917" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>1.28799998760223</v>
       </c>
       <c r="G1919" t="n">
-        <v>0.789955854415894</v>
+        <v>0.789955794811249</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1921" t="n">
-        <v>0.78136932849884</v>
+        <v>0.781369388103485</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50445,7 +50445,7 @@
         <v>1.28799998760223</v>
       </c>
       <c r="G1926" t="n">
-        <v>0.789955854415894</v>
+        <v>0.789955794811249</v>
       </c>
       <c r="H1926" t="s">
         <v>8</v>
@@ -50471,7 +50471,7 @@
         <v>1.31200003623962</v>
       </c>
       <c r="G1927" t="n">
-        <v>0.804675459861755</v>
+        <v>0.8046755194664</v>
       </c>
       <c r="H1927" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G1929" t="n">
-        <v>0.819395124912262</v>
+        <v>0.819395184516907</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1931" t="n">
-        <v>0.78136932849884</v>
+        <v>0.781369388103485</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50601,7 +50601,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1932" t="n">
-        <v>0.775236248970032</v>
+        <v>0.775236189365387</v>
       </c>
       <c r="H1932" t="s">
         <v>8</v>
@@ -50653,7 +50653,7 @@
         <v>1.21599996089935</v>
       </c>
       <c r="G1934" t="n">
-        <v>0.745796740055084</v>
+        <v>0.745796799659729</v>
       </c>
       <c r="H1934" t="s">
         <v>8</v>
@@ -50757,7 +50757,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1938" t="n">
-        <v>0.759289920330048</v>
+        <v>0.759289860725403</v>
       </c>
       <c r="H1938" t="s">
         <v>8</v>
@@ -50809,7 +50809,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G1940" t="n">
-        <v>0.767876267433167</v>
+        <v>0.767876327037811</v>
       </c>
       <c r="H1940" t="s">
         <v>8</v>
@@ -50835,7 +50835,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1941" t="n">
-        <v>0.78136932849884</v>
+        <v>0.781369388103485</v>
       </c>
       <c r="H1941" t="s">
         <v>8</v>
@@ -50913,7 +50913,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G1944" t="n">
-        <v>0.753156661987305</v>
+        <v>0.753156721591949</v>
       </c>
       <c r="H1944" t="s">
         <v>8</v>
@@ -50991,7 +50991,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G1947" t="n">
-        <v>0.758063137531281</v>
+        <v>0.758063197135925</v>
       </c>
       <c r="H1947" t="s">
         <v>8</v>
@@ -51017,7 +51017,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G1948" t="n">
-        <v>0.780142664909363</v>
+        <v>0.780142605304718</v>
       </c>
       <c r="H1948" t="s">
         <v>8</v>
@@ -51069,7 +51069,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1950" t="n">
-        <v>0.785049259662628</v>
+        <v>0.785049200057983</v>
       </c>
       <c r="H1950" t="s">
         <v>8</v>
@@ -51147,7 +51147,7 @@
         <v>1.27600002288818</v>
       </c>
       <c r="G1953" t="n">
-        <v>0.782596051692963</v>
+        <v>0.782595992088318</v>
       </c>
       <c r="H1953" t="s">
         <v>8</v>
@@ -51173,7 +51173,7 @@
         <v>1.27600002288818</v>
       </c>
       <c r="G1954" t="n">
-        <v>0.782596051692963</v>
+        <v>0.782595992088318</v>
       </c>
       <c r="H1954" t="s">
         <v>8</v>
@@ -51199,7 +51199,7 @@
         <v>1.28799998760223</v>
       </c>
       <c r="G1955" t="n">
-        <v>0.789955854415894</v>
+        <v>0.789955794811249</v>
       </c>
       <c r="H1955" t="s">
         <v>8</v>
@@ -51225,7 +51225,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1956" t="n">
-        <v>0.785049259662628</v>
+        <v>0.785049200057983</v>
       </c>
       <c r="H1956" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1958" t="n">
-        <v>0.775236248970032</v>
+        <v>0.775236189365387</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51303,7 +51303,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1959" t="n">
-        <v>0.775236248970032</v>
+        <v>0.775236189365387</v>
       </c>
       <c r="H1959" t="s">
         <v>8</v>
@@ -51329,7 +51329,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1960" t="n">
-        <v>0.78136932849884</v>
+        <v>0.781369388103485</v>
       </c>
       <c r="H1960" t="s">
         <v>8</v>
@@ -51433,7 +51433,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G1964" t="n">
-        <v>0.794862389564514</v>
+        <v>0.794862329959869</v>
       </c>
       <c r="H1964" t="s">
         <v>8</v>
@@ -51485,7 +51485,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G1966" t="n">
-        <v>0.850061178207397</v>
+        <v>0.850061118602753</v>
       </c>
       <c r="H1966" t="s">
         <v>8</v>
@@ -51511,7 +51511,7 @@
         <v>1.42599999904633</v>
       </c>
       <c r="G1967" t="n">
-        <v>0.874593913555145</v>
+        <v>0.87459397315979</v>
       </c>
       <c r="H1967" t="s">
         <v>8</v>
@@ -51537,7 +51537,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1968" t="n">
-        <v>0.889313638210297</v>
+        <v>0.889313697814941</v>
       </c>
       <c r="H1968" t="s">
         <v>8</v>
@@ -51641,7 +51641,7 @@
         <v>1.46399998664856</v>
       </c>
       <c r="G1972" t="n">
-        <v>0.89790004491806</v>
+        <v>0.897900104522705</v>
       </c>
       <c r="H1972" t="s">
         <v>8</v>
@@ -51693,7 +51693,7 @@
         <v>1.50399994850159</v>
       </c>
       <c r="G1974" t="n">
-        <v>0.922432899475098</v>
+        <v>0.922432839870453</v>
       </c>
       <c r="H1974" t="s">
         <v>8</v>
@@ -51719,7 +51719,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1975" t="n">
-        <v>0.931019365787506</v>
+        <v>0.931019306182861</v>
       </c>
       <c r="H1975" t="s">
         <v>8</v>
@@ -51745,7 +51745,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1976" t="n">
-        <v>0.926112830638885</v>
+        <v>0.926112711429596</v>
       </c>
       <c r="H1976" t="s">
         <v>8</v>
@@ -51849,7 +51849,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G1980" t="n">
-        <v>1.04141676425934</v>
+        <v>1.04141688346863</v>
       </c>
       <c r="H1980" t="s">
         <v>8</v>
@@ -51901,7 +51901,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G1982" t="n">
-        <v>1.0070708990097</v>
+        <v>1.00707101821899</v>
       </c>
       <c r="H1982" t="s">
         <v>8</v>
@@ -51927,7 +51927,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1983" t="n">
-        <v>0.999711155891418</v>
+        <v>0.999711215496063</v>
       </c>
       <c r="H1983" t="s">
         <v>8</v>
@@ -52083,7 +52083,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1989" t="n">
-        <v>0.993578016757965</v>
+        <v>0.99357795715332</v>
       </c>
       <c r="H1989" t="s">
         <v>8</v>
@@ -52161,7 +52161,7 @@
         <v>1.54799997806549</v>
       </c>
       <c r="G1992" t="n">
-        <v>0.949418962001801</v>
+        <v>0.949418902397156</v>
       </c>
       <c r="H1992" t="s">
         <v>8</v>
@@ -52187,7 +52187,7 @@
         <v>1.54799997806549</v>
       </c>
       <c r="G1993" t="n">
-        <v>0.949418962001801</v>
+        <v>0.949418902397156</v>
       </c>
       <c r="H1993" t="s">
         <v>8</v>
@@ -52239,7 +52239,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1995" t="n">
-        <v>0.956778764724731</v>
+        <v>0.956778824329376</v>
       </c>
       <c r="H1995" t="s">
         <v>8</v>
@@ -52265,7 +52265,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G1996" t="n">
-        <v>0.951872229576111</v>
+        <v>0.951872289180756</v>
       </c>
       <c r="H1996" t="s">
         <v>8</v>
@@ -52291,7 +52291,7 @@
         <v>1.57799994945526</v>
       </c>
       <c r="G1997" t="n">
-        <v>0.967818439006805</v>
+        <v>0.96781849861145</v>
       </c>
       <c r="H1997" t="s">
         <v>8</v>
@@ -52369,7 +52369,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G2000" t="n">
-        <v>0.950645625591278</v>
+        <v>0.950645565986633</v>
       </c>
       <c r="H2000" t="s">
         <v>8</v>
@@ -52395,7 +52395,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G2001" t="n">
-        <v>0.950645625591278</v>
+        <v>0.950645565986633</v>
       </c>
       <c r="H2001" t="s">
         <v>8</v>
@@ -52421,7 +52421,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G2002" t="n">
-        <v>0.953098893165588</v>
+        <v>0.953098833560944</v>
       </c>
       <c r="H2002" t="s">
         <v>8</v>
@@ -52447,7 +52447,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G2003" t="n">
-        <v>0.980084896087646</v>
+        <v>0.980085015296936</v>
       </c>
       <c r="H2003" t="s">
         <v>8</v>
@@ -52499,7 +52499,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G2005" t="n">
-        <v>0.999711155891418</v>
+        <v>0.999711215496063</v>
       </c>
       <c r="H2005" t="s">
         <v>8</v>
@@ -52525,7 +52525,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G2006" t="n">
-        <v>0.999711155891418</v>
+        <v>0.999711215496063</v>
       </c>
       <c r="H2006" t="s">
         <v>8</v>
@@ -52577,7 +52577,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G2008" t="n">
-        <v>1.00461781024933</v>
+        <v>1.00461769104004</v>
       </c>
       <c r="H2008" t="s">
         <v>8</v>
@@ -52629,7 +52629,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2010" t="n">
-        <v>0.993578016757965</v>
+        <v>0.99357795715332</v>
       </c>
       <c r="H2010" t="s">
         <v>8</v>
@@ -52785,7 +52785,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G2016" t="n">
-        <v>0.988671362400055</v>
+        <v>0.9886714220047</v>
       </c>
       <c r="H2016" t="s">
         <v>8</v>
@@ -52811,7 +52811,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G2017" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H2017" t="s">
         <v>8</v>
@@ -52915,7 +52915,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G2021" t="n">
-        <v>1.11501514911652</v>
+        <v>1.11501526832581</v>
       </c>
       <c r="H2021" t="s">
         <v>8</v>
@@ -52993,7 +52993,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G2024" t="n">
-        <v>1.1334148645401</v>
+        <v>1.13341498374939</v>
       </c>
       <c r="H2024" t="s">
         <v>8</v>
@@ -53019,7 +53019,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G2025" t="n">
-        <v>1.14813458919525</v>
+        <v>1.14813446998596</v>
       </c>
       <c r="H2025" t="s">
         <v>8</v>
@@ -53045,7 +53045,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G2026" t="n">
-        <v>1.15181457996368</v>
+        <v>1.15181446075439</v>
       </c>
       <c r="H2026" t="s">
         <v>8</v>
@@ -53175,7 +53175,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2031" t="n">
-        <v>1.26957190036774</v>
+        <v>1.26957178115845</v>
       </c>
       <c r="H2031" t="s">
         <v>8</v>
@@ -53227,7 +53227,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2033" t="n">
-        <v>1.23277270793915</v>
+        <v>1.23277258872986</v>
       </c>
       <c r="H2033" t="s">
         <v>8</v>
@@ -53253,7 +53253,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2034" t="n">
-        <v>1.23890578746796</v>
+        <v>1.23890590667725</v>
       </c>
       <c r="H2034" t="s">
         <v>8</v>
@@ -53357,7 +53357,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2038" t="n">
-        <v>1.20823979377747</v>
+        <v>1.20823991298676</v>
       </c>
       <c r="H2038" t="s">
         <v>8</v>
@@ -53409,7 +53409,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G2040" t="n">
-        <v>1.18493366241455</v>
+        <v>1.18493378162384</v>
       </c>
       <c r="H2040" t="s">
         <v>8</v>
@@ -53435,7 +53435,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2041" t="n">
-        <v>1.17757391929626</v>
+        <v>1.17757380008698</v>
       </c>
       <c r="H2041" t="s">
         <v>8</v>
@@ -53513,7 +53513,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G2044" t="n">
-        <v>1.22173297405243</v>
+        <v>1.22173285484314</v>
       </c>
       <c r="H2044" t="s">
         <v>8</v>
@@ -53539,7 +53539,7 @@
         <v>2</v>
       </c>
       <c r="G2045" t="n">
-        <v>1.22663938999176</v>
+        <v>1.22663950920105</v>
       </c>
       <c r="H2045" t="s">
         <v>8</v>
@@ -53565,7 +53565,7 @@
         <v>2</v>
       </c>
       <c r="G2046" t="n">
-        <v>1.22663938999176</v>
+        <v>1.22663950920105</v>
       </c>
       <c r="H2046" t="s">
         <v>8</v>
@@ -53643,7 +53643,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2049" t="n">
-        <v>1.18370699882507</v>
+        <v>1.18370711803436</v>
       </c>
       <c r="H2049" t="s">
         <v>8</v>
@@ -53669,7 +53669,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G2050" t="n">
-        <v>1.14322793483734</v>
+        <v>1.14322805404663</v>
       </c>
       <c r="H2050" t="s">
         <v>8</v>
@@ -53721,7 +53721,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G2052" t="n">
-        <v>1.14445471763611</v>
+        <v>1.14445459842682</v>
       </c>
       <c r="H2052" t="s">
         <v>8</v>
@@ -53773,7 +53773,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G2054" t="n">
-        <v>1.13832128047943</v>
+        <v>1.13832139968872</v>
       </c>
       <c r="H2054" t="s">
         <v>8</v>
@@ -53825,7 +53825,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G2056" t="n">
-        <v>1.13832128047943</v>
+        <v>1.13832139968872</v>
       </c>
       <c r="H2056" t="s">
         <v>8</v>
@@ -53851,7 +53851,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G2057" t="n">
-        <v>1.14200127124786</v>
+        <v>1.14200139045715</v>
       </c>
       <c r="H2057" t="s">
         <v>8</v>
@@ -53877,7 +53877,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G2058" t="n">
-        <v>1.15181457996368</v>
+        <v>1.15181446075439</v>
       </c>
       <c r="H2058" t="s">
         <v>8</v>
@@ -53903,7 +53903,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2059" t="n">
-        <v>1.13464140892029</v>
+        <v>1.13464152812958</v>
       </c>
       <c r="H2059" t="s">
         <v>8</v>
@@ -53955,7 +53955,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2061" t="n">
-        <v>1.13464140892029</v>
+        <v>1.13464152812958</v>
       </c>
       <c r="H2061" t="s">
         <v>8</v>
@@ -54033,7 +54033,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2064" t="n">
-        <v>1.12850844860077</v>
+        <v>1.12850832939148</v>
       </c>
       <c r="H2064" t="s">
         <v>8</v>
@@ -54085,7 +54085,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G2066" t="n">
-        <v>1.1579475402832</v>
+        <v>1.15794765949249</v>
       </c>
       <c r="H2066" t="s">
         <v>8</v>
@@ -54111,7 +54111,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2067" t="n">
-        <v>1.16530740261078</v>
+        <v>1.16530752182007</v>
       </c>
       <c r="H2067" t="s">
         <v>8</v>
@@ -54293,7 +54293,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G2074" t="n">
-        <v>1.22173297405243</v>
+        <v>1.22173285484314</v>
       </c>
       <c r="H2074" t="s">
         <v>8</v>
@@ -54319,7 +54319,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2075" t="n">
-        <v>1.25730538368225</v>
+        <v>1.25730550289154</v>
       </c>
       <c r="H2075" t="s">
         <v>8</v>
@@ -54345,7 +54345,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G2076" t="n">
-        <v>1.70502889156342</v>
+        <v>1.70502877235413</v>
       </c>
       <c r="H2076" t="s">
         <v>8</v>
@@ -54371,7 +54371,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G2077" t="n">
-        <v>1.71729516983032</v>
+        <v>1.71729528903961</v>
       </c>
       <c r="H2077" t="s">
         <v>8</v>
@@ -54397,7 +54397,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G2078" t="n">
-        <v>1.8184928894043</v>
+        <v>1.81849300861359</v>
       </c>
       <c r="H2078" t="s">
         <v>8</v>
@@ -54423,7 +54423,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2079" t="n">
-        <v>1.94422352313995</v>
+        <v>1.94422364234924</v>
       </c>
       <c r="H2079" t="s">
         <v>8</v>
@@ -54449,7 +54449,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G2080" t="n">
-        <v>1.89822459220886</v>
+        <v>1.89822471141815</v>
       </c>
       <c r="H2080" t="s">
         <v>8</v>
@@ -54553,7 +54553,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G2084" t="n">
-        <v>1.7970267534256</v>
+        <v>1.79702687263489</v>
       </c>
       <c r="H2084" t="s">
         <v>8</v>
@@ -54605,7 +54605,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G2086" t="n">
-        <v>1.74489462375641</v>
+        <v>1.7448947429657</v>
       </c>
       <c r="H2086" t="s">
         <v>8</v>
@@ -54631,7 +54631,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G2087" t="n">
-        <v>1.84302580356598</v>
+        <v>1.84302592277527</v>
       </c>
       <c r="H2087" t="s">
         <v>8</v>
@@ -54683,7 +54683,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2089" t="n">
-        <v>1.90129125118256</v>
+        <v>1.90129113197327</v>
       </c>
       <c r="H2089" t="s">
         <v>8</v>
@@ -54709,7 +54709,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2090" t="n">
-        <v>1.90129125118256</v>
+        <v>1.90129113197327</v>
       </c>
       <c r="H2090" t="s">
         <v>8</v>
@@ -54735,7 +54735,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2091" t="n">
-        <v>1.91355752944946</v>
+        <v>1.91355764865875</v>
       </c>
       <c r="H2091" t="s">
         <v>8</v>
@@ -54865,7 +54865,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G2096" t="n">
-        <v>1.92889046669006</v>
+        <v>1.92889034748077</v>
       </c>
       <c r="H2096" t="s">
         <v>8</v>
@@ -54891,7 +54891,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2097" t="n">
-        <v>1.99942231178284</v>
+        <v>1.99942243099213</v>
       </c>
       <c r="H2097" t="s">
         <v>8</v>
@@ -54943,7 +54943,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G2099" t="n">
-        <v>1.95955646038055</v>
+        <v>1.95955657958984</v>
       </c>
       <c r="H2099" t="s">
         <v>8</v>
@@ -55021,7 +55021,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2102" t="n">
-        <v>1.93809044361115</v>
+        <v>1.93809020519257</v>
       </c>
       <c r="H2102" t="s">
         <v>8</v>
@@ -55125,7 +55125,7 @@
         <v>3.25</v>
       </c>
       <c r="G2106" t="n">
-        <v>1.99328911304474</v>
+        <v>1.99328923225403</v>
       </c>
       <c r="H2106" t="s">
         <v>8</v>
@@ -55151,7 +55151,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2107" t="n">
-        <v>2.00555539131165</v>
+        <v>2.00555562973022</v>
       </c>
       <c r="H2107" t="s">
         <v>8</v>
@@ -55177,7 +55177,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G2108" t="n">
-        <v>1.95342338085175</v>
+        <v>1.95342326164246</v>
       </c>
       <c r="H2108" t="s">
         <v>8</v>
@@ -55203,7 +55203,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G2109" t="n">
-        <v>1.95342338085175</v>
+        <v>1.95342326164246</v>
       </c>
       <c r="H2109" t="s">
         <v>8</v>
@@ -55229,7 +55229,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G2110" t="n">
-        <v>1.92889046669006</v>
+        <v>1.92889034748077</v>
       </c>
       <c r="H2110" t="s">
         <v>8</v>
@@ -55255,7 +55255,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2111" t="n">
-        <v>1.92582404613495</v>
+        <v>1.92582392692566</v>
       </c>
       <c r="H2111" t="s">
         <v>8</v>
@@ -55307,7 +55307,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2113" t="n">
-        <v>1.88902461528778</v>
+        <v>1.88902485370636</v>
       </c>
       <c r="H2113" t="s">
         <v>8</v>
@@ -55333,7 +55333,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2114" t="n">
-        <v>1.88902461528778</v>
+        <v>1.88902485370636</v>
       </c>
       <c r="H2114" t="s">
         <v>8</v>
@@ -55463,7 +55463,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G2119" t="n">
-        <v>1.80622661113739</v>
+        <v>1.8062264919281</v>
       </c>
       <c r="H2119" t="s">
         <v>8</v>
@@ -55489,7 +55489,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G2120" t="n">
-        <v>1.7694274187088</v>
+        <v>1.76942753791809</v>
       </c>
       <c r="H2120" t="s">
         <v>8</v>
@@ -55515,7 +55515,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G2121" t="n">
-        <v>1.7602276802063</v>
+        <v>1.76022756099701</v>
       </c>
       <c r="H2121" t="s">
         <v>8</v>
@@ -55541,7 +55541,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G2122" t="n">
-        <v>1.8184928894043</v>
+        <v>1.81849300861359</v>
       </c>
       <c r="H2122" t="s">
         <v>8</v>
@@ -55593,7 +55593,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G2124" t="n">
-        <v>2.01250958442688</v>
+        <v>2.0125093460083</v>
       </c>
       <c r="H2124" t="s">
         <v>8</v>
@@ -55619,7 +55619,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G2125" t="n">
-        <v>1.96318304538727</v>
+        <v>1.96318316459656</v>
       </c>
       <c r="H2125" t="s">
         <v>8</v>
@@ -55671,7 +55671,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G2127" t="n">
-        <v>1.79218566417694</v>
+        <v>1.79218554496765</v>
       </c>
       <c r="H2127" t="s">
         <v>8</v>
@@ -55801,7 +55801,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G2132" t="n">
-        <v>1.8316468000412</v>
+        <v>1.83164668083191</v>
       </c>
       <c r="H2132" t="s">
         <v>8</v>
@@ -55879,7 +55879,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G2135" t="n">
-        <v>1.79218566417694</v>
+        <v>1.79218554496765</v>
       </c>
       <c r="H2135" t="s">
         <v>8</v>
@@ -55905,7 +55905,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G2136" t="n">
-        <v>1.79218566417694</v>
+        <v>1.79218554496765</v>
       </c>
       <c r="H2136" t="s">
         <v>8</v>
@@ -55957,7 +55957,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G2138" t="n">
-        <v>1.95660638809204</v>
+        <v>1.95660626888275</v>
       </c>
       <c r="H2138" t="s">
         <v>8</v>
@@ -55983,7 +55983,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G2139" t="n">
-        <v>1.95002949237823</v>
+        <v>1.95002961158752</v>
       </c>
       <c r="H2139" t="s">
         <v>8</v>
@@ -56009,7 +56009,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G2140" t="n">
-        <v>1.92043375968933</v>
+        <v>1.92043387889862</v>
       </c>
       <c r="H2140" t="s">
         <v>8</v>
@@ -56035,7 +56035,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G2141" t="n">
-        <v>1.93358743190765</v>
+        <v>1.93358755111694</v>
       </c>
       <c r="H2141" t="s">
         <v>8</v>
@@ -56061,7 +56061,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G2142" t="n">
-        <v>1.92372214794159</v>
+        <v>1.92372226715088</v>
       </c>
       <c r="H2142" t="s">
         <v>8</v>
@@ -56113,7 +56113,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G2144" t="n">
-        <v>1.9072802066803</v>
+        <v>1.90728032588959</v>
       </c>
       <c r="H2144" t="s">
         <v>8</v>
@@ -56165,7 +56165,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G2146" t="n">
-        <v>1.9138571023941</v>
+        <v>1.91385698318481</v>
       </c>
       <c r="H2146" t="s">
         <v>8</v>
@@ -56191,7 +56191,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G2147" t="n">
-        <v>1.91056847572327</v>
+        <v>1.91056859493256</v>
       </c>
       <c r="H2147" t="s">
         <v>8</v>
@@ -56217,7 +56217,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G2148" t="n">
-        <v>1.91056847572327</v>
+        <v>1.91056859493256</v>
       </c>
       <c r="H2148" t="s">
         <v>8</v>
@@ -56243,7 +56243,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G2149" t="n">
-        <v>1.91714549064636</v>
+        <v>1.91714537143707</v>
       </c>
       <c r="H2149" t="s">
         <v>8</v>
@@ -56295,7 +56295,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G2151" t="n">
-        <v>1.87110757827759</v>
+        <v>1.87110769748688</v>
       </c>
       <c r="H2151" t="s">
         <v>8</v>
@@ -56373,7 +56373,7 @@
         <v>3</v>
       </c>
       <c r="G2154" t="n">
-        <v>1.97304832935333</v>
+        <v>1.97304844856262</v>
       </c>
       <c r="H2154" t="s">
         <v>8</v>
@@ -56607,7 +56607,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2163" t="n">
-        <v>2.22296810150146</v>
+        <v>2.22296786308289</v>
       </c>
       <c r="H2163" t="s">
         <v>8</v>
@@ -56633,7 +56633,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G2164" t="n">
-        <v>2.17693018913269</v>
+        <v>2.17692995071411</v>
       </c>
       <c r="H2164" t="s">
         <v>8</v>
@@ -56659,7 +56659,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G2165" t="n">
-        <v>2.20981407165527</v>
+        <v>2.20981431007385</v>
       </c>
       <c r="H2165" t="s">
         <v>8</v>
@@ -56685,7 +56685,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2166" t="n">
-        <v>2.22296810150146</v>
+        <v>2.22296786308289</v>
       </c>
       <c r="H2166" t="s">
         <v>8</v>
@@ -56763,7 +56763,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G2169" t="n">
-        <v>2.17693018913269</v>
+        <v>2.17692995071411</v>
       </c>
       <c r="H2169" t="s">
         <v>8</v>
@@ -71672,7 +71672,7 @@
         <v>46310.2916666667</v>
       </c>
       <c r="B2743" t="n">
-        <v>966462</v>
+        <v>975658</v>
       </c>
       <c r="C2743" t="n">
         <v>2.02999997138977</v>
@@ -71690,6 +71690,32 @@
         <v>1.97399997711182</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>475815</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>1.98199999332428</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>1.98199999332428</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>1.98599994182587</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>1.98599994182587</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SGF.MI.xlsx
+++ b/data/SGF.MI.xlsx
@@ -456,7 +456,7 @@
         <v>2.00399994850159</v>
       </c>
       <c r="G3" t="n">
-        <v>1.22909271717072</v>
+        <v>1.22909259796143</v>
       </c>
       <c r="H3" t="n">
         <v>161308</v>
@@ -514,7 +514,7 @@
         <v>1.93299996852875</v>
       </c>
       <c r="G5" t="n">
-        <v>1.18554699420929</v>
+        <v>1.18554711341858</v>
       </c>
       <c r="H5" t="n">
         <v>335985</v>
@@ -601,7 +601,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G8" t="n">
-        <v>1.17389404773712</v>
+        <v>1.17389392852783</v>
       </c>
       <c r="H8" t="n">
         <v>255301</v>
@@ -630,7 +630,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G9" t="n">
-        <v>1.15058779716492</v>
+        <v>1.15058791637421</v>
       </c>
       <c r="H9" t="n">
         <v>230740</v>
@@ -659,7 +659,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G10" t="n">
-        <v>1.12850844860077</v>
+        <v>1.12850832939148</v>
       </c>
       <c r="H10" t="n">
         <v>270591</v>
@@ -688,7 +688,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G11" t="n">
-        <v>1.08557593822479</v>
+        <v>1.0855758190155</v>
       </c>
       <c r="H11" t="n">
         <v>331594</v>
@@ -746,7 +746,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G13" t="n">
-        <v>1.09293580055237</v>
+        <v>1.09293568134308</v>
       </c>
       <c r="H13" t="n">
         <v>294153</v>
@@ -775,7 +775,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>1.00891101360321</v>
+        <v>1.00891089439392</v>
       </c>
       <c r="H14" t="n">
         <v>229916</v>
@@ -833,7 +833,7 @@
         <v>1.7610000371933</v>
       </c>
       <c r="G16" t="n">
-        <v>1.08005607128143</v>
+        <v>1.08005595207214</v>
       </c>
       <c r="H16" t="n">
         <v>396007</v>
@@ -891,7 +891,7 @@
         <v>1.77400004863739</v>
       </c>
       <c r="G18" t="n">
-        <v>1.08802914619446</v>
+        <v>1.08802926540375</v>
       </c>
       <c r="H18" t="n">
         <v>242295</v>
@@ -949,7 +949,7 @@
         <v>1.692999958992</v>
       </c>
       <c r="G20" t="n">
-        <v>1.03835034370422</v>
+        <v>1.03835022449493</v>
       </c>
       <c r="H20" t="n">
         <v>324056</v>
@@ -1065,7 +1065,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G24" t="n">
-        <v>1.01075088977814</v>
+        <v>1.01075100898743</v>
       </c>
       <c r="H24" t="n">
         <v>327325</v>
@@ -1152,7 +1152,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G27" t="n">
-        <v>0.841474711894989</v>
+        <v>0.841474652290344</v>
       </c>
       <c r="H27" t="n">
         <v>327658</v>
@@ -1268,7 +1268,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G31" t="n">
-        <v>0.916912972927094</v>
+        <v>0.916913032531738</v>
       </c>
       <c r="H31" t="n">
         <v>204119</v>
@@ -1297,7 +1297,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G32" t="n">
-        <v>0.981311559677124</v>
+        <v>0.981311500072479</v>
       </c>
       <c r="H32" t="n">
         <v>168307</v>
@@ -1326,7 +1326,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G33" t="n">
-        <v>0.950645625591278</v>
+        <v>0.950645565986633</v>
       </c>
       <c r="H33" t="n">
         <v>252019</v>
@@ -1355,7 +1355,7 @@
         <v>1.56099998950958</v>
       </c>
       <c r="G34" t="n">
-        <v>0.95739209651947</v>
+        <v>0.957392156124115</v>
       </c>
       <c r="H34" t="n">
         <v>320159</v>
@@ -1384,7 +1384,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G35" t="n">
-        <v>0.941445767879486</v>
+        <v>0.941445708274841</v>
       </c>
       <c r="H35" t="n">
         <v>350921</v>
@@ -1413,7 +1413,7 @@
         <v>1.50399994850159</v>
       </c>
       <c r="G36" t="n">
-        <v>0.922432899475098</v>
+        <v>0.922432839870453</v>
       </c>
       <c r="H36" t="n">
         <v>200666</v>
@@ -1442,7 +1442,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G37" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H37" t="n">
         <v>274788</v>
@@ -1471,7 +1471,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G38" t="n">
-        <v>0.941445767879486</v>
+        <v>0.941445708274841</v>
       </c>
       <c r="H38" t="n">
         <v>449707</v>
@@ -1529,7 +1529,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G40" t="n">
-        <v>0.910166442394257</v>
+        <v>0.910166501998901</v>
       </c>
       <c r="H40" t="n">
         <v>482847</v>
@@ -1558,7 +1558,7 @@
         <v>1.52699995040894</v>
       </c>
       <c r="G41" t="n">
-        <v>0.936539173126221</v>
+        <v>0.936539232730865</v>
       </c>
       <c r="H41" t="n">
         <v>374615</v>
@@ -1616,7 +1616,7 @@
         <v>1.5</v>
       </c>
       <c r="G43" t="n">
-        <v>0.919979572296143</v>
+        <v>0.919979512691498</v>
       </c>
       <c r="H43" t="n">
         <v>841811</v>
@@ -1645,7 +1645,7 @@
         <v>1.5789999961853</v>
       </c>
       <c r="G44" t="n">
-        <v>0.968431770801544</v>
+        <v>0.968431830406189</v>
       </c>
       <c r="H44" t="n">
         <v>563184</v>
@@ -1790,7 +1790,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G49" t="n">
-        <v>1.00891101360321</v>
+        <v>1.00891089439392</v>
       </c>
       <c r="H49" t="n">
         <v>192494</v>
@@ -1906,7 +1906,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G53" t="n">
-        <v>0.960458636283875</v>
+        <v>0.960458695888519</v>
       </c>
       <c r="H53" t="n">
         <v>389718</v>
@@ -1935,7 +1935,7 @@
         <v>1.58299994468689</v>
       </c>
       <c r="G54" t="n">
-        <v>0.970885097980499</v>
+        <v>0.970885038375854</v>
       </c>
       <c r="H54" t="n">
         <v>320346</v>
@@ -1964,7 +1964,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G55" t="n">
-        <v>0.956165432929993</v>
+        <v>0.956165492534637</v>
       </c>
       <c r="H55" t="n">
         <v>282072</v>
@@ -2051,7 +2051,7 @@
         <v>1.5</v>
       </c>
       <c r="G58" t="n">
-        <v>0.919979572296143</v>
+        <v>0.919979512691498</v>
       </c>
       <c r="H58" t="n">
         <v>214751</v>
@@ -2109,7 +2109,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G60" t="n">
-        <v>0.853741049766541</v>
+        <v>0.853741109371185</v>
       </c>
       <c r="H60" t="n">
         <v>330575</v>
@@ -2138,7 +2138,7 @@
         <v>1.34300005435944</v>
       </c>
       <c r="G61" t="n">
-        <v>0.823688387870789</v>
+        <v>0.823688447475433</v>
       </c>
       <c r="H61" t="n">
         <v>330707</v>
@@ -2167,7 +2167,7 @@
         <v>1.40600001811981</v>
       </c>
       <c r="G62" t="n">
-        <v>0.862327516078949</v>
+        <v>0.862327575683594</v>
       </c>
       <c r="H62" t="n">
         <v>445947</v>
@@ -2312,7 +2312,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G67" t="n">
-        <v>0.818781912326813</v>
+        <v>0.818781852722168</v>
       </c>
       <c r="H67" t="n">
         <v>147823</v>
@@ -2370,7 +2370,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G69" t="n">
-        <v>0.832888305187225</v>
+        <v>0.832888185977936</v>
       </c>
       <c r="H69" t="n">
         <v>207067</v>
@@ -2428,7 +2428,7 @@
         <v>1.38300001621246</v>
       </c>
       <c r="G71" t="n">
-        <v>0.848221242427826</v>
+        <v>0.848221182823181</v>
       </c>
       <c r="H71" t="n">
         <v>161956</v>
@@ -2486,7 +2486,7 @@
         <v>1.43299996852875</v>
       </c>
       <c r="G73" t="n">
-        <v>0.878887116909027</v>
+        <v>0.878887236118317</v>
       </c>
       <c r="H73" t="n">
         <v>194805</v>
@@ -2544,7 +2544,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G75" t="n">
-        <v>0.895446836948395</v>
+        <v>0.89544677734375</v>
       </c>
       <c r="H75" t="n">
         <v>124767</v>
@@ -2573,7 +2573,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G76" t="n">
-        <v>0.852514445781708</v>
+        <v>0.852514386177063</v>
       </c>
       <c r="H76" t="n">
         <v>774434</v>
@@ -2631,7 +2631,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G78" t="n">
-        <v>0.875207245349884</v>
+        <v>0.875207304954529</v>
       </c>
       <c r="H78" t="n">
         <v>207294</v>
@@ -2660,7 +2660,7 @@
         <v>1.42299997806549</v>
       </c>
       <c r="G79" t="n">
-        <v>0.872753977775574</v>
+        <v>0.872754037380219</v>
       </c>
       <c r="H79" t="n">
         <v>99483</v>
@@ -2747,7 +2747,7 @@
         <v>1.5</v>
       </c>
       <c r="G82" t="n">
-        <v>0.919979572296143</v>
+        <v>0.919979512691498</v>
       </c>
       <c r="H82" t="n">
         <v>823016</v>
@@ -2805,7 +2805,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G84" t="n">
-        <v>0.977631688117981</v>
+        <v>0.977631628513336</v>
       </c>
       <c r="H84" t="n">
         <v>875820</v>
@@ -2834,7 +2834,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G85" t="n">
-        <v>0.993578016757965</v>
+        <v>0.99357795715332</v>
       </c>
       <c r="H85" t="n">
         <v>550524</v>
@@ -2979,7 +2979,7 @@
         <v>1.50100004673004</v>
       </c>
       <c r="G90" t="n">
-        <v>0.920592904090881</v>
+        <v>0.920592963695526</v>
       </c>
       <c r="H90" t="n">
         <v>157165</v>
@@ -3008,7 +3008,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G91" t="n">
-        <v>0.938379168510437</v>
+        <v>0.938379287719727</v>
       </c>
       <c r="H91" t="n">
         <v>93150</v>
@@ -3066,7 +3066,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G93" t="n">
-        <v>0.97824501991272</v>
+        <v>0.978245079517365</v>
       </c>
       <c r="H93" t="n">
         <v>347619</v>
@@ -3095,7 +3095,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G94" t="n">
-        <v>0.992351353168488</v>
+        <v>0.992351412773132</v>
       </c>
       <c r="H94" t="n">
         <v>320086</v>
@@ -3124,7 +3124,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G95" t="n">
-        <v>1.00216436386108</v>
+        <v>1.00216448307037</v>
       </c>
       <c r="H95" t="n">
         <v>110841</v>
@@ -3240,7 +3240,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G99" t="n">
-        <v>0.935312628746033</v>
+        <v>0.935312569141388</v>
       </c>
       <c r="H99" t="n">
         <v>196453</v>
@@ -3356,7 +3356,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G103" t="n">
-        <v>1.0917090177536</v>
+        <v>1.09170913696289</v>
       </c>
       <c r="H103" t="n">
         <v>2561297</v>
@@ -3501,7 +3501,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G108" t="n">
-        <v>1.03037714958191</v>
+        <v>1.03037703037262</v>
       </c>
       <c r="H108" t="n">
         <v>290532</v>
@@ -3559,7 +3559,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G110" t="n">
-        <v>0.999711155891418</v>
+        <v>0.999711096286774</v>
       </c>
       <c r="H110" t="n">
         <v>236211</v>
@@ -3588,7 +3588,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G111" t="n">
-        <v>1.0070708990097</v>
+        <v>1.00707101821899</v>
       </c>
       <c r="H111" t="n">
         <v>230111</v>
@@ -3617,7 +3617,7 @@
         <v>1.625</v>
       </c>
       <c r="G112" t="n">
-        <v>0.996644556522369</v>
+        <v>0.996644616127014</v>
       </c>
       <c r="H112" t="n">
         <v>276657</v>
@@ -3646,7 +3646,7 @@
         <v>1.60099995136261</v>
       </c>
       <c r="G113" t="n">
-        <v>0.981924891471863</v>
+        <v>0.981924831867218</v>
       </c>
       <c r="H113" t="n">
         <v>124731</v>
@@ -3675,7 +3675,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G114" t="n">
-        <v>0.935312628746033</v>
+        <v>0.935312569141388</v>
       </c>
       <c r="H114" t="n">
         <v>354806</v>
@@ -3820,7 +3820,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G119" t="n">
-        <v>0.792409121990204</v>
+        <v>0.792409062385559</v>
       </c>
       <c r="H119" t="n">
         <v>527410</v>
@@ -3878,7 +3878,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G121" t="n">
-        <v>0.880727171897888</v>
+        <v>0.880727112293243</v>
       </c>
       <c r="H121" t="n">
         <v>394406</v>
@@ -3907,7 +3907,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G122" t="n">
-        <v>0.875207245349884</v>
+        <v>0.875207304954529</v>
       </c>
       <c r="H122" t="n">
         <v>340422</v>
@@ -3936,7 +3936,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G123" t="n">
-        <v>0.880113840103149</v>
+        <v>0.880113780498505</v>
       </c>
       <c r="H123" t="n">
         <v>209882</v>
@@ -4110,7 +4110,7 @@
         <v>1.30900001525879</v>
       </c>
       <c r="G129" t="n">
-        <v>0.802835524082184</v>
+        <v>0.802835583686829</v>
       </c>
       <c r="H129" t="n">
         <v>198549</v>
@@ -4197,7 +4197,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G132" t="n">
-        <v>0.711450815200806</v>
+        <v>0.71145087480545</v>
       </c>
       <c r="H132" t="n">
         <v>436842</v>
@@ -4284,7 +4284,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G135" t="n">
-        <v>0.771556258201599</v>
+        <v>0.771556198596954</v>
       </c>
       <c r="H135" t="n">
         <v>325977</v>
@@ -4313,7 +4313,7 @@
         <v>1.30299997329712</v>
       </c>
       <c r="G136" t="n">
-        <v>0.799155652523041</v>
+        <v>0.799155592918396</v>
       </c>
       <c r="H136" t="n">
         <v>418971</v>
@@ -4458,7 +4458,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G141" t="n">
-        <v>0.85128778219223</v>
+        <v>0.851287841796875</v>
       </c>
       <c r="H141" t="n">
         <v>149242</v>
@@ -4516,7 +4516,7 @@
         <v>1.40600001811981</v>
       </c>
       <c r="G143" t="n">
-        <v>0.862327516078949</v>
+        <v>0.862327575683594</v>
       </c>
       <c r="H143" t="n">
         <v>70858</v>
@@ -4545,7 +4545,7 @@
         <v>1.38199996948242</v>
       </c>
       <c r="G144" t="n">
-        <v>0.847607791423798</v>
+        <v>0.847607851028442</v>
       </c>
       <c r="H144" t="n">
         <v>99538</v>
@@ -4603,7 +4603,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G146" t="n">
-        <v>0.884407103061676</v>
+        <v>0.884407043457031</v>
       </c>
       <c r="H146" t="n">
         <v>428209</v>
@@ -4661,7 +4661,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G148" t="n">
-        <v>0.935312628746033</v>
+        <v>0.935312569141388</v>
       </c>
       <c r="H148" t="n">
         <v>421354</v>
@@ -4690,7 +4690,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G149" t="n">
-        <v>0.932245969772339</v>
+        <v>0.932246029376984</v>
       </c>
       <c r="H149" t="n">
         <v>325924</v>
@@ -4719,7 +4719,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G150" t="n">
-        <v>0.935925960540771</v>
+        <v>0.935925900936127</v>
       </c>
       <c r="H150" t="n">
         <v>228664</v>
@@ -4748,7 +4748,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G151" t="n">
-        <v>0.907713234424591</v>
+        <v>0.907713174819946</v>
       </c>
       <c r="H151" t="n">
         <v>331548</v>
@@ -4777,7 +4777,7 @@
         <v>1.54900002479553</v>
       </c>
       <c r="G152" t="n">
-        <v>0.950032293796539</v>
+        <v>0.950032234191895</v>
       </c>
       <c r="H152" t="n">
         <v>547010</v>
@@ -4806,7 +4806,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G153" t="n">
-        <v>0.956778764724731</v>
+        <v>0.956778824329376</v>
       </c>
       <c r="H153" t="n">
         <v>149124</v>
@@ -4893,7 +4893,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G156" t="n">
-        <v>1.0070708990097</v>
+        <v>1.00707101821899</v>
       </c>
       <c r="H156" t="n">
         <v>68730</v>
@@ -5067,7 +5067,7 @@
         <v>1.66100001335144</v>
       </c>
       <c r="G162" t="n">
-        <v>1.01872396469116</v>
+        <v>1.01872420310974</v>
       </c>
       <c r="H162" t="n">
         <v>160844</v>
@@ -5096,7 +5096,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G163" t="n">
-        <v>1.00461781024933</v>
+        <v>1.00461769104004</v>
       </c>
       <c r="H163" t="n">
         <v>76999</v>
@@ -5125,7 +5125,7 @@
         <v>1.66100001335144</v>
       </c>
       <c r="G164" t="n">
-        <v>1.01872396469116</v>
+        <v>1.01872420310974</v>
       </c>
       <c r="H164" t="n">
         <v>78461</v>
@@ -5183,7 +5183,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G166" t="n">
-        <v>1.03896367549896</v>
+        <v>1.03896355628967</v>
       </c>
       <c r="H166" t="n">
         <v>150712</v>
@@ -5270,7 +5270,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G169" t="n">
-        <v>1.05491006374359</v>
+        <v>1.0549099445343</v>
       </c>
       <c r="H169" t="n">
         <v>262531</v>
@@ -5299,7 +5299,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G170" t="n">
-        <v>1.04571008682251</v>
+        <v>1.0457102060318</v>
       </c>
       <c r="H170" t="n">
         <v>255988</v>
@@ -5357,7 +5357,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G172" t="n">
-        <v>1.02363061904907</v>
+        <v>1.02363073825836</v>
       </c>
       <c r="H172" t="n">
         <v>236960</v>
@@ -5473,7 +5473,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G176" t="n">
-        <v>1.0917090177536</v>
+        <v>1.09170913696289</v>
       </c>
       <c r="H176" t="n">
         <v>233304</v>
@@ -5502,7 +5502,7 @@
         <v>1.77699995040894</v>
       </c>
       <c r="G177" t="n">
-        <v>1.08986914157867</v>
+        <v>1.08986902236938</v>
       </c>
       <c r="H177" t="n">
         <v>220355</v>
@@ -5618,7 +5618,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G181" t="n">
-        <v>1.06472289562225</v>
+        <v>1.06472301483154</v>
       </c>
       <c r="H181" t="n">
         <v>121177</v>
@@ -5647,7 +5647,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G182" t="n">
-        <v>1.0641096830368</v>
+        <v>1.06410980224609</v>
       </c>
       <c r="H182" t="n">
         <v>104640</v>
@@ -5705,7 +5705,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G184" t="n">
-        <v>1.05491006374359</v>
+        <v>1.0549099445343</v>
       </c>
       <c r="H184" t="n">
         <v>297503</v>
@@ -5734,7 +5734,7 @@
         <v>1.68900001049042</v>
       </c>
       <c r="G185" t="n">
-        <v>1.03589713573456</v>
+        <v>1.03589701652527</v>
       </c>
       <c r="H185" t="n">
         <v>97005</v>
@@ -5763,7 +5763,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G186" t="n">
-        <v>1.0671763420105</v>
+        <v>1.06717622280121</v>
       </c>
       <c r="H186" t="n">
         <v>130158</v>
@@ -5792,7 +5792,7 @@
         <v>1.77400004863739</v>
       </c>
       <c r="G187" t="n">
-        <v>1.08802914619446</v>
+        <v>1.08802926540375</v>
       </c>
       <c r="H187" t="n">
         <v>705957</v>
@@ -5850,7 +5850,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G189" t="n">
-        <v>1.0917090177536</v>
+        <v>1.09170913696289</v>
       </c>
       <c r="H189" t="n">
         <v>140051</v>
@@ -5879,7 +5879,7 @@
         <v>1.78299999237061</v>
       </c>
       <c r="G190" t="n">
-        <v>1.09354913234711</v>
+        <v>1.09354901313782</v>
       </c>
       <c r="H190" t="n">
         <v>136706</v>
@@ -5908,7 +5908,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G191" t="n">
-        <v>1.11010873317719</v>
+        <v>1.1101086139679</v>
       </c>
       <c r="H191" t="n">
         <v>193032</v>
@@ -5995,7 +5995,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G194" t="n">
-        <v>1.0917090177536</v>
+        <v>1.09170913696289</v>
       </c>
       <c r="H194" t="n">
         <v>147290</v>
@@ -6024,7 +6024,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G195" t="n">
-        <v>1.09416246414185</v>
+        <v>1.09416234493256</v>
       </c>
       <c r="H195" t="n">
         <v>227267</v>
@@ -6111,7 +6111,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G198" t="n">
-        <v>1.09784233570099</v>
+        <v>1.0978422164917</v>
       </c>
       <c r="H198" t="n">
         <v>97852</v>
@@ -6140,7 +6140,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G199" t="n">
-        <v>1.10152232646942</v>
+        <v>1.10152220726013</v>
       </c>
       <c r="H199" t="n">
         <v>60811</v>
@@ -6169,7 +6169,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>1.09784233570099</v>
+        <v>1.0978422164917</v>
       </c>
       <c r="H200" t="n">
         <v>71260</v>
@@ -6198,7 +6198,7 @@
         <v>1.79100000858307</v>
       </c>
       <c r="G201" t="n">
-        <v>1.09845566749573</v>
+        <v>1.09845554828644</v>
       </c>
       <c r="H201" t="n">
         <v>108906</v>
@@ -6314,7 +6314,7 @@
         <v>1.79100000858307</v>
       </c>
       <c r="G205" t="n">
-        <v>1.09845566749573</v>
+        <v>1.09845554828644</v>
       </c>
       <c r="H205" t="n">
         <v>130768</v>
@@ -6401,7 +6401,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G208" t="n">
-        <v>1.10152232646942</v>
+        <v>1.10152220726013</v>
       </c>
       <c r="H208" t="n">
         <v>71337</v>
@@ -6430,7 +6430,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G209" t="n">
-        <v>1.12850844860077</v>
+        <v>1.12850832939148</v>
       </c>
       <c r="H209" t="n">
         <v>499157</v>
@@ -6488,7 +6488,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G211" t="n">
-        <v>1.23890578746796</v>
+        <v>1.23890590667725</v>
       </c>
       <c r="H211" t="n">
         <v>1398955</v>
@@ -6546,7 +6546,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G213" t="n">
-        <v>1.23277270793915</v>
+        <v>1.23277258872986</v>
       </c>
       <c r="H213" t="n">
         <v>488691</v>
@@ -6604,7 +6604,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G215" t="n">
-        <v>1.26343870162964</v>
+        <v>1.26343858242035</v>
       </c>
       <c r="H215" t="n">
         <v>414877</v>
@@ -6633,7 +6633,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G216" t="n">
-        <v>1.22050631046295</v>
+        <v>1.22050619125366</v>
       </c>
       <c r="H216" t="n">
         <v>490241</v>
@@ -6691,7 +6691,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G218" t="n">
-        <v>1.26466536521912</v>
+        <v>1.26466524600983</v>
       </c>
       <c r="H218" t="n">
         <v>379339</v>
@@ -6807,7 +6807,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G222" t="n">
-        <v>1.24135911464691</v>
+        <v>1.24135899543762</v>
       </c>
       <c r="H222" t="n">
         <v>447289</v>
@@ -6836,7 +6836,7 @@
         <v>2.07399988174438</v>
       </c>
       <c r="G223" t="n">
-        <v>1.2720251083374</v>
+        <v>1.27202498912811</v>
       </c>
       <c r="H223" t="n">
         <v>256250</v>
@@ -6865,7 +6865,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G224" t="n">
-        <v>1.30759763717651</v>
+        <v>1.3075977563858</v>
       </c>
       <c r="H224" t="n">
         <v>602971</v>
@@ -6894,7 +6894,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G225" t="n">
-        <v>1.31495761871338</v>
+        <v>1.31495749950409</v>
       </c>
       <c r="H225" t="n">
         <v>292475</v>
@@ -6923,7 +6923,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G226" t="n">
-        <v>1.32231712341309</v>
+        <v>1.32231724262238</v>
       </c>
       <c r="H226" t="n">
         <v>577745</v>
@@ -6952,7 +6952,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G227" t="n">
-        <v>1.32477068901062</v>
+        <v>1.32477080821991</v>
       </c>
       <c r="H227" t="n">
         <v>203471</v>
@@ -6981,7 +6981,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G228" t="n">
-        <v>1.32477068901062</v>
+        <v>1.32477080821991</v>
       </c>
       <c r="H228" t="n">
         <v>299354</v>
@@ -7010,7 +7010,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G229" t="n">
-        <v>1.33090376853943</v>
+        <v>1.33090388774872</v>
       </c>
       <c r="H229" t="n">
         <v>710066</v>
@@ -7213,7 +7213,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G236" t="n">
-        <v>1.28797137737274</v>
+        <v>1.28797125816345</v>
       </c>
       <c r="H236" t="n">
         <v>205772</v>
@@ -7242,7 +7242,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G237" t="n">
-        <v>1.28797137737274</v>
+        <v>1.28797125816345</v>
       </c>
       <c r="H237" t="n">
         <v>141863</v>
@@ -7271,7 +7271,7 @@
         <v>2.09200000762939</v>
       </c>
       <c r="G238" t="n">
-        <v>1.28306496143341</v>
+        <v>1.28306484222412</v>
       </c>
       <c r="H238" t="n">
         <v>268785</v>
@@ -7358,7 +7358,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G241" t="n">
-        <v>1.36279654502869</v>
+        <v>1.3627964258194</v>
       </c>
       <c r="H241" t="n">
         <v>824205</v>
@@ -7387,7 +7387,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G242" t="n">
-        <v>1.42290163040161</v>
+        <v>1.4229017496109</v>
       </c>
       <c r="H242" t="n">
         <v>556866</v>
@@ -7532,7 +7532,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G247" t="n">
-        <v>1.45970094203949</v>
+        <v>1.45970106124878</v>
       </c>
       <c r="H247" t="n">
         <v>391093</v>
@@ -7590,7 +7590,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G249" t="n">
-        <v>1.47932732105255</v>
+        <v>1.47932708263397</v>
       </c>
       <c r="H249" t="n">
         <v>163664</v>
@@ -7648,7 +7648,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G251" t="n">
-        <v>1.50263345241547</v>
+        <v>1.50263333320618</v>
       </c>
       <c r="H251" t="n">
         <v>163694</v>
@@ -7677,7 +7677,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G252" t="n">
-        <v>1.49650025367737</v>
+        <v>1.49650013446808</v>
       </c>
       <c r="H252" t="n">
         <v>188904</v>
@@ -7764,7 +7764,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G255" t="n">
-        <v>1.447434425354</v>
+        <v>1.44743454456329</v>
       </c>
       <c r="H255" t="n">
         <v>237678</v>
@@ -7793,7 +7793,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G256" t="n">
-        <v>1.47810053825378</v>
+        <v>1.47810065746307</v>
       </c>
       <c r="H256" t="n">
         <v>141019</v>
@@ -7851,7 +7851,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G258" t="n">
-        <v>1.56396520137787</v>
+        <v>1.56396532058716</v>
       </c>
       <c r="H258" t="n">
         <v>345212</v>
@@ -7880,7 +7880,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G259" t="n">
-        <v>1.57991170883179</v>
+        <v>1.5799115896225</v>
       </c>
       <c r="H259" t="n">
         <v>412317</v>
@@ -8025,7 +8025,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G264" t="n">
-        <v>1.57377851009369</v>
+        <v>1.5737783908844</v>
       </c>
       <c r="H264" t="n">
         <v>102370</v>
@@ -8083,7 +8083,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G266" t="n">
-        <v>1.55169904232025</v>
+        <v>1.55169892311096</v>
       </c>
       <c r="H266" t="n">
         <v>242727</v>
@@ -8141,7 +8141,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G268" t="n">
-        <v>1.57868480682373</v>
+        <v>1.57868492603302</v>
       </c>
       <c r="H268" t="n">
         <v>126004</v>
@@ -8170,7 +8170,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G269" t="n">
-        <v>1.55660545825958</v>
+        <v>1.55660557746887</v>
       </c>
       <c r="H269" t="n">
         <v>102959</v>
@@ -8199,7 +8199,7 @@
         <v>2.5</v>
       </c>
       <c r="G270" t="n">
-        <v>1.53329932689667</v>
+        <v>1.53329944610596</v>
       </c>
       <c r="H270" t="n">
         <v>124510</v>
@@ -8228,7 +8228,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G271" t="n">
-        <v>1.52593958377838</v>
+        <v>1.5259393453598</v>
       </c>
       <c r="H271" t="n">
         <v>154741</v>
@@ -8373,7 +8373,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G276" t="n">
-        <v>1.52593958377838</v>
+        <v>1.5259393453598</v>
       </c>
       <c r="H276" t="n">
         <v>121968</v>
@@ -8518,7 +8518,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G281" t="n">
-        <v>1.41308867931366</v>
+        <v>1.41308856010437</v>
       </c>
       <c r="H281" t="n">
         <v>67393</v>
@@ -8605,7 +8605,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G284" t="n">
-        <v>1.27079856395721</v>
+        <v>1.27079844474792</v>
       </c>
       <c r="H284" t="n">
         <v>532104</v>
@@ -8750,7 +8750,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G289" t="n">
-        <v>1.40940892696381</v>
+        <v>1.40940880775452</v>
       </c>
       <c r="H289" t="n">
         <v>287135</v>
@@ -8779,7 +8779,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G290" t="n">
-        <v>1.39100909233093</v>
+        <v>1.39100897312164</v>
       </c>
       <c r="H290" t="n">
         <v>208243</v>
@@ -8895,7 +8895,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G294" t="n">
-        <v>1.4339417219162</v>
+        <v>1.43394160270691</v>
       </c>
       <c r="H294" t="n">
         <v>298331</v>
@@ -8924,7 +8924,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G295" t="n">
-        <v>1.4339417219162</v>
+        <v>1.43394160270691</v>
       </c>
       <c r="H295" t="n">
         <v>262571</v>
@@ -8953,7 +8953,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G296" t="n">
-        <v>1.41063547134399</v>
+        <v>1.4106353521347</v>
       </c>
       <c r="H296" t="n">
         <v>197826</v>
@@ -8982,7 +8982,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G297" t="n">
-        <v>1.39591574668884</v>
+        <v>1.39591562747955</v>
       </c>
       <c r="H297" t="n">
         <v>195070</v>
@@ -9011,7 +9011,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G298" t="n">
-        <v>1.46338093280792</v>
+        <v>1.46338081359863</v>
       </c>
       <c r="H298" t="n">
         <v>234364</v>
@@ -9069,7 +9069,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G300" t="n">
-        <v>1.65718972682953</v>
+        <v>1.65718984603882</v>
       </c>
       <c r="H300" t="n">
         <v>1429043</v>
@@ -9214,7 +9214,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G305" t="n">
-        <v>1.79825341701508</v>
+        <v>1.79825329780579</v>
       </c>
       <c r="H305" t="n">
         <v>673534</v>
@@ -9243,7 +9243,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G306" t="n">
-        <v>1.75409436225891</v>
+        <v>1.7540944814682</v>
       </c>
       <c r="H306" t="n">
         <v>548849</v>
@@ -9272,7 +9272,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G307" t="n">
-        <v>1.79089367389679</v>
+        <v>1.7908935546875</v>
       </c>
       <c r="H307" t="n">
         <v>670021</v>
@@ -9301,7 +9301,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G308" t="n">
-        <v>1.77740061283112</v>
+        <v>1.77740049362183</v>
       </c>
       <c r="H308" t="n">
         <v>520725</v>
@@ -9359,7 +9359,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G310" t="n">
-        <v>1.79089367389679</v>
+        <v>1.7908935546875</v>
       </c>
       <c r="H310" t="n">
         <v>165055</v>
@@ -9388,7 +9388,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G311" t="n">
-        <v>1.80316007137299</v>
+        <v>1.8031599521637</v>
       </c>
       <c r="H311" t="n">
         <v>257588</v>
@@ -9417,7 +9417,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G312" t="n">
-        <v>1.82523953914642</v>
+        <v>1.82523965835571</v>
       </c>
       <c r="H312" t="n">
         <v>318543</v>
@@ -9446,7 +9446,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G313" t="n">
-        <v>1.95526337623596</v>
+        <v>1.95526325702667</v>
       </c>
       <c r="H313" t="n">
         <v>926523</v>
@@ -9475,7 +9475,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G314" t="n">
-        <v>1.93563687801361</v>
+        <v>1.9356369972229</v>
       </c>
       <c r="H314" t="n">
         <v>1008378</v>
@@ -9591,7 +9591,7 @@
         <v>3.60199999809265</v>
       </c>
       <c r="G318" t="n">
-        <v>2.20917773246765</v>
+        <v>2.20917797088623</v>
       </c>
       <c r="H318" t="n">
         <v>1002453</v>
@@ -9620,7 +9620,7 @@
         <v>3.75</v>
       </c>
       <c r="G319" t="n">
-        <v>2.29994893074036</v>
+        <v>2.29994916915894</v>
       </c>
       <c r="H319" t="n">
         <v>632837</v>
@@ -9649,7 +9649,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G320" t="n">
-        <v>2.29749584197998</v>
+        <v>2.2974956035614</v>
       </c>
       <c r="H320" t="n">
         <v>576179</v>
@@ -9678,7 +9678,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G321" t="n">
-        <v>2.26928281784058</v>
+        <v>2.26928305625916</v>
       </c>
       <c r="H321" t="n">
         <v>427642</v>
@@ -9707,7 +9707,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G322" t="n">
-        <v>2.2680561542511</v>
+        <v>2.26805639266968</v>
       </c>
       <c r="H322" t="n">
         <v>763540</v>
@@ -9736,7 +9736,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G323" t="n">
-        <v>2.25701689720154</v>
+        <v>2.25701665878296</v>
       </c>
       <c r="H323" t="n">
         <v>420141</v>
@@ -9765,7 +9765,7 @@
         <v>3.75600004196167</v>
       </c>
       <c r="G324" t="n">
-        <v>2.30362915992737</v>
+        <v>2.30362892150879</v>
       </c>
       <c r="H324" t="n">
         <v>585886</v>
@@ -9823,7 +9823,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G326" t="n">
-        <v>2.2484302520752</v>
+        <v>2.24843001365662</v>
       </c>
       <c r="H326" t="n">
         <v>356043</v>
@@ -9881,7 +9881,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G328" t="n">
-        <v>2.2484302520752</v>
+        <v>2.24843001365662</v>
       </c>
       <c r="H328" t="n">
         <v>167124</v>
@@ -9968,7 +9968,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G331" t="n">
-        <v>2.2680561542511</v>
+        <v>2.26805639266968</v>
       </c>
       <c r="H331" t="n">
         <v>213985</v>
@@ -10026,7 +10026,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G333" t="n">
-        <v>2.28277587890625</v>
+        <v>2.28277611732483</v>
       </c>
       <c r="H333" t="n">
         <v>285695</v>
@@ -10055,7 +10055,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G334" t="n">
-        <v>2.3392014503479</v>
+        <v>2.33920121192932</v>
       </c>
       <c r="H334" t="n">
         <v>497655</v>
@@ -10113,7 +10113,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G336" t="n">
-        <v>2.4410126209259</v>
+        <v>2.44101238250732</v>
       </c>
       <c r="H336" t="n">
         <v>688744</v>
@@ -10287,7 +10287,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>2.73540592193604</v>
+        <v>2.73540616035461</v>
       </c>
       <c r="H342" t="n">
         <v>1177654</v>
@@ -10345,7 +10345,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G344" t="n">
-        <v>2.72927284240723</v>
+        <v>2.72927260398865</v>
       </c>
       <c r="H344" t="n">
         <v>500433</v>
@@ -10374,7 +10374,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>2.85193705558777</v>
+        <v>2.85193681716919</v>
       </c>
       <c r="H345" t="n">
         <v>553581</v>
@@ -10432,7 +10432,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G347" t="n">
-        <v>2.93780136108398</v>
+        <v>2.93780159950256</v>
       </c>
       <c r="H347" t="n">
         <v>302332</v>
@@ -10490,7 +10490,7 @@
         <v>4.60799980163574</v>
       </c>
       <c r="G349" t="n">
-        <v>2.82617735862732</v>
+        <v>2.82617712020874</v>
       </c>
       <c r="H349" t="n">
         <v>339119</v>
@@ -10519,7 +10519,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G350" t="n">
-        <v>2.8568434715271</v>
+        <v>2.85684323310852</v>
       </c>
       <c r="H350" t="n">
         <v>230854</v>
@@ -10548,7 +10548,7 @@
         <v>4.72399997711182</v>
       </c>
       <c r="G351" t="n">
-        <v>2.89732265472412</v>
+        <v>2.89732241630554</v>
       </c>
       <c r="H351" t="n">
         <v>476496</v>
@@ -10635,7 +10635,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G354" t="n">
-        <v>2.99300050735474</v>
+        <v>2.99300026893616</v>
       </c>
       <c r="H354" t="n">
         <v>1271662</v>
@@ -10722,7 +10722,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G357" t="n">
-        <v>3.14633059501648</v>
+        <v>3.1463303565979</v>
       </c>
       <c r="H357" t="n">
         <v>584493</v>
@@ -10809,7 +10809,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G360" t="n">
-        <v>3.17392992973328</v>
+        <v>3.1739296913147</v>
       </c>
       <c r="H360" t="n">
         <v>342891</v>
@@ -10867,7 +10867,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G362" t="n">
-        <v>3.14633059501648</v>
+        <v>3.1463303565979</v>
       </c>
       <c r="H362" t="n">
         <v>1345063</v>
@@ -10896,7 +10896,7 @@
         <v>5.125</v>
       </c>
       <c r="G363" t="n">
-        <v>3.14326357841492</v>
+        <v>3.1432638168335</v>
       </c>
       <c r="H363" t="n">
         <v>592954</v>
@@ -10925,7 +10925,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G364" t="n">
-        <v>3.28432703018188</v>
+        <v>3.28432726860046</v>
       </c>
       <c r="H364" t="n">
         <v>536733</v>
@@ -10954,7 +10954,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G365" t="n">
-        <v>3.18926239013672</v>
+        <v>3.1892626285553</v>
       </c>
       <c r="H365" t="n">
         <v>330140</v>
@@ -11099,7 +11099,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G370" t="n">
-        <v>2.99300050735474</v>
+        <v>2.99300026893616</v>
       </c>
       <c r="H370" t="n">
         <v>709668</v>
@@ -11157,7 +11157,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G372" t="n">
-        <v>3.10953092575073</v>
+        <v>3.10953116416931</v>
       </c>
       <c r="H372" t="n">
         <v>943510</v>
@@ -11302,7 +11302,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>3.17392992973328</v>
+        <v>3.1739296913147</v>
       </c>
       <c r="H377" t="n">
         <v>294725</v>
@@ -11447,7 +11447,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G382" t="n">
-        <v>3.10953092575073</v>
+        <v>3.10953116416931</v>
       </c>
       <c r="H382" t="n">
         <v>568166</v>
@@ -11505,7 +11505,7 @@
         <v>4.68400001525879</v>
       </c>
       <c r="G384" t="n">
-        <v>2.87278962135315</v>
+        <v>2.87278938293457</v>
       </c>
       <c r="H384" t="n">
         <v>628468</v>
@@ -11708,7 +11708,7 @@
         <v>4.72399997711182</v>
       </c>
       <c r="G391" t="n">
-        <v>2.89732265472412</v>
+        <v>2.89732241630554</v>
       </c>
       <c r="H391" t="n">
         <v>894334</v>
@@ -11795,7 +11795,7 @@
         <v>4.69199991226196</v>
       </c>
       <c r="G394" t="n">
-        <v>2.87769603729248</v>
+        <v>2.87769627571106</v>
       </c>
       <c r="H394" t="n">
         <v>136890</v>
@@ -11824,7 +11824,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G395" t="n">
-        <v>2.91081523895264</v>
+        <v>2.91081547737122</v>
       </c>
       <c r="H395" t="n">
         <v>1325910</v>
@@ -11940,7 +11940,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G399" t="n">
-        <v>2.67898082733154</v>
+        <v>2.67898058891296</v>
       </c>
       <c r="H399" t="n">
         <v>762725</v>
@@ -12027,7 +12027,7 @@
         <v>4.47800016403198</v>
       </c>
       <c r="G402" t="n">
-        <v>2.74644589424133</v>
+        <v>2.74644565582275</v>
       </c>
       <c r="H402" t="n">
         <v>1187685</v>
@@ -12114,7 +12114,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G405" t="n">
-        <v>2.62500858306885</v>
+        <v>2.62500882148743</v>
       </c>
       <c r="H405" t="n">
         <v>480173</v>
@@ -12201,7 +12201,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G408" t="n">
-        <v>2.556316614151</v>
+        <v>2.55631685256958</v>
       </c>
       <c r="H408" t="n">
         <v>363869</v>
@@ -12230,7 +12230,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G409" t="n">
-        <v>2.57594275474548</v>
+        <v>2.5759425163269</v>
       </c>
       <c r="H409" t="n">
         <v>222579</v>
@@ -12259,7 +12259,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G410" t="n">
-        <v>2.57594275474548</v>
+        <v>2.5759425163269</v>
       </c>
       <c r="H410" t="n">
         <v>166188</v>
@@ -12317,7 +12317,7 @@
         <v>4.27400016784668</v>
       </c>
       <c r="G412" t="n">
-        <v>2.62132883071899</v>
+        <v>2.62132859230042</v>
       </c>
       <c r="H412" t="n">
         <v>485494</v>
@@ -12346,7 +12346,7 @@
         <v>4.64799976348877</v>
       </c>
       <c r="G413" t="n">
-        <v>2.85071015357971</v>
+        <v>2.85070991516113</v>
       </c>
       <c r="H413" t="n">
         <v>1542581</v>
@@ -12375,7 +12375,7 @@
         <v>4.4520001411438</v>
       </c>
       <c r="G414" t="n">
-        <v>2.73049974441528</v>
+        <v>2.7304995059967</v>
       </c>
       <c r="H414" t="n">
         <v>700794</v>
@@ -12404,7 +12404,7 @@
         <v>4.55800008773804</v>
       </c>
       <c r="G415" t="n">
-        <v>2.79551124572754</v>
+        <v>2.79551148414612</v>
       </c>
       <c r="H415" t="n">
         <v>440882</v>
@@ -12433,7 +12433,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G416" t="n">
-        <v>2.82127094268799</v>
+        <v>2.82127070426941</v>
       </c>
       <c r="H416" t="n">
         <v>398517</v>
@@ -12462,7 +12462,7 @@
         <v>4.60400009155273</v>
       </c>
       <c r="G417" t="n">
-        <v>2.82372426986694</v>
+        <v>2.82372403144836</v>
       </c>
       <c r="H417" t="n">
         <v>268282</v>
@@ -12491,7 +12491,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G418" t="n">
-        <v>2.79428482055664</v>
+        <v>2.79428505897522</v>
       </c>
       <c r="H418" t="n">
         <v>184142</v>
@@ -12549,7 +12549,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G420" t="n">
-        <v>2.73540592193604</v>
+        <v>2.73540616035461</v>
       </c>
       <c r="H420" t="n">
         <v>222228</v>
@@ -12607,7 +12607,7 @@
         <v>4.41800022125244</v>
       </c>
       <c r="G422" t="n">
-        <v>2.70964646339417</v>
+        <v>2.70964670181274</v>
       </c>
       <c r="H422" t="n">
         <v>269674</v>
@@ -12636,7 +12636,7 @@
         <v>4.44399976730347</v>
       </c>
       <c r="G423" t="n">
-        <v>2.72559309005737</v>
+        <v>2.72559285163879</v>
       </c>
       <c r="H423" t="n">
         <v>270668</v>
@@ -12694,7 +12694,7 @@
         <v>4.24599981307983</v>
       </c>
       <c r="G425" t="n">
-        <v>2.60415530204773</v>
+        <v>2.60415554046631</v>
       </c>
       <c r="H425" t="n">
         <v>469148</v>
@@ -12723,7 +12723,7 @@
         <v>4.23400020599365</v>
       </c>
       <c r="G426" t="n">
-        <v>2.59679579734802</v>
+        <v>2.5967960357666</v>
       </c>
       <c r="H426" t="n">
         <v>653160</v>
@@ -12752,7 +12752,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G427" t="n">
-        <v>2.67898082733154</v>
+        <v>2.67898058891296</v>
       </c>
       <c r="H427" t="n">
         <v>1331409</v>
@@ -12781,7 +12781,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G428" t="n">
-        <v>2.62991523742676</v>
+        <v>2.62991499900818</v>
       </c>
       <c r="H428" t="n">
         <v>528651</v>
@@ -12810,7 +12810,7 @@
         <v>4.28200006484985</v>
       </c>
       <c r="G429" t="n">
-        <v>2.62623524665833</v>
+        <v>2.62623500823975</v>
       </c>
       <c r="H429" t="n">
         <v>411427</v>
@@ -12984,7 +12984,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G435" t="n">
-        <v>3.06966543197632</v>
+        <v>3.06966519355774</v>
       </c>
       <c r="H435" t="n">
         <v>1556069</v>
@@ -13042,7 +13042,7 @@
         <v>5</v>
       </c>
       <c r="G437" t="n">
-        <v>3.06659865379333</v>
+        <v>3.06659889221191</v>
       </c>
       <c r="H437" t="n">
         <v>542060</v>
@@ -13071,7 +13071,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G438" t="n">
-        <v>3.07273197174072</v>
+        <v>3.0727322101593</v>
       </c>
       <c r="H438" t="n">
         <v>434258</v>
@@ -13100,7 +13100,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G439" t="n">
-        <v>3.17086291313171</v>
+        <v>3.17086315155029</v>
       </c>
       <c r="H439" t="n">
         <v>667518</v>
@@ -13158,7 +13158,7 @@
         <v>5</v>
       </c>
       <c r="G441" t="n">
-        <v>3.06659865379333</v>
+        <v>3.06659889221191</v>
       </c>
       <c r="H441" t="n">
         <v>837961</v>
@@ -13187,7 +13187,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G442" t="n">
-        <v>3.10033106803894</v>
+        <v>3.10033130645752</v>
       </c>
       <c r="H442" t="n">
         <v>607313</v>
@@ -13216,7 +13216,7 @@
         <v>5.03499984741211</v>
       </c>
       <c r="G443" t="n">
-        <v>3.08806443214417</v>
+        <v>3.08806467056274</v>
       </c>
       <c r="H443" t="n">
         <v>178529</v>
@@ -13245,7 +13245,7 @@
         <v>5</v>
       </c>
       <c r="G444" t="n">
-        <v>3.06659865379333</v>
+        <v>3.06659889221191</v>
       </c>
       <c r="H444" t="n">
         <v>685848</v>
@@ -13274,7 +13274,7 @@
         <v>5.06500005722046</v>
       </c>
       <c r="G445" t="n">
-        <v>3.10646462440491</v>
+        <v>3.10646438598633</v>
       </c>
       <c r="H445" t="n">
         <v>756719</v>
@@ -13361,7 +13361,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>3.15553021430969</v>
+        <v>3.15552997589111</v>
       </c>
       <c r="H448" t="n">
         <v>253394</v>
@@ -13535,7 +13535,7 @@
         <v>4.90199995040894</v>
       </c>
       <c r="G454" t="n">
-        <v>3.00649356842041</v>
+        <v>3.00649333000183</v>
       </c>
       <c r="H454" t="n">
         <v>249613</v>
@@ -13564,7 +13564,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G455" t="n">
-        <v>2.96233439445496</v>
+        <v>2.96233415603638</v>
       </c>
       <c r="H455" t="n">
         <v>503874</v>
@@ -13622,7 +13622,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G457" t="n">
-        <v>2.99300050735474</v>
+        <v>2.99300026893616</v>
       </c>
       <c r="H457" t="n">
         <v>279277</v>
@@ -13738,7 +13738,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G461" t="n">
-        <v>2.97214722633362</v>
+        <v>2.9721474647522</v>
       </c>
       <c r="H461" t="n">
         <v>182632</v>
@@ -13767,7 +13767,7 @@
         <v>4.63199996948242</v>
       </c>
       <c r="G462" t="n">
-        <v>2.84089684486389</v>
+        <v>2.84089708328247</v>
       </c>
       <c r="H462" t="n">
         <v>672804</v>
@@ -13912,7 +13912,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G467" t="n">
-        <v>2.65567445755005</v>
+        <v>2.65567421913147</v>
       </c>
       <c r="H467" t="n">
         <v>2274886</v>
@@ -13999,7 +13999,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G470" t="n">
-        <v>2.57594275474548</v>
+        <v>2.5759425163269</v>
       </c>
       <c r="H470" t="n">
         <v>671006</v>
@@ -14028,7 +14028,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G471" t="n">
-        <v>2.556316614151</v>
+        <v>2.55631685256958</v>
       </c>
       <c r="H471" t="n">
         <v>827622</v>
@@ -14086,7 +14086,7 @@
         <v>4.26399993896484</v>
       </c>
       <c r="G473" t="n">
-        <v>2.61519527435303</v>
+        <v>2.61519551277161</v>
       </c>
       <c r="H473" t="n">
         <v>1086537</v>
@@ -14173,7 +14173,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G476" t="n">
-        <v>2.47781157493591</v>
+        <v>2.47781181335449</v>
       </c>
       <c r="H476" t="n">
         <v>974146</v>
@@ -14202,7 +14202,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G477" t="n">
-        <v>2.43487954139709</v>
+        <v>2.43487930297852</v>
       </c>
       <c r="H477" t="n">
         <v>1127908</v>
@@ -14318,7 +14318,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G481" t="n">
-        <v>2.2680561542511</v>
+        <v>2.26805639266968</v>
       </c>
       <c r="H481" t="n">
         <v>919203</v>
@@ -14347,7 +14347,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G482" t="n">
-        <v>2.34165501594543</v>
+        <v>2.34165477752686</v>
       </c>
       <c r="H482" t="n">
         <v>702888</v>
@@ -14376,7 +14376,7 @@
         <v>3.86400008201599</v>
       </c>
       <c r="G483" t="n">
-        <v>2.3698673248291</v>
+        <v>2.36986756324768</v>
       </c>
       <c r="H483" t="n">
         <v>818536</v>
@@ -14434,7 +14434,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G485" t="n">
-        <v>2.49375820159912</v>
+        <v>2.49375796318054</v>
       </c>
       <c r="H485" t="n">
         <v>644388</v>
@@ -14637,7 +14637,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G492" t="n">
-        <v>2.63482189178467</v>
+        <v>2.63482141494751</v>
       </c>
       <c r="H492" t="n">
         <v>1627474</v>
@@ -14666,7 +14666,7 @@
         <v>4.23199987411499</v>
       </c>
       <c r="G493" t="n">
-        <v>2.59556889533997</v>
+        <v>2.59556913375854</v>
       </c>
       <c r="H493" t="n">
         <v>749802</v>
@@ -14695,7 +14695,7 @@
         <v>4.25600004196167</v>
       </c>
       <c r="G494" t="n">
-        <v>2.6102888584137</v>
+        <v>2.61028861999512</v>
       </c>
       <c r="H494" t="n">
         <v>274888</v>
@@ -14753,7 +14753,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G496" t="n">
-        <v>2.53914380073547</v>
+        <v>2.53914356231689</v>
       </c>
       <c r="H496" t="n">
         <v>526596</v>
@@ -14782,7 +14782,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G497" t="n">
-        <v>2.62500858306885</v>
+        <v>2.62500882148743</v>
       </c>
       <c r="H497" t="n">
         <v>426003</v>
@@ -14869,7 +14869,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G500" t="n">
-        <v>2.5366907119751</v>
+        <v>2.53669047355652</v>
       </c>
       <c r="H500" t="n">
         <v>652804</v>
@@ -15014,7 +15014,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G505" t="n">
-        <v>2.39808034896851</v>
+        <v>2.39808011054993</v>
       </c>
       <c r="H505" t="n">
         <v>447765</v>
@@ -15072,7 +15072,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G507" t="n">
-        <v>2.47903823852539</v>
+        <v>2.47903847694397</v>
       </c>
       <c r="H507" t="n">
         <v>419637</v>
@@ -15188,7 +15188,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G511" t="n">
-        <v>2.45941233634949</v>
+        <v>2.45941209793091</v>
       </c>
       <c r="H511" t="n">
         <v>303747</v>
@@ -15333,7 +15333,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G516" t="n">
-        <v>2.5146107673645</v>
+        <v>2.51461100578308</v>
       </c>
       <c r="H516" t="n">
         <v>279351</v>
@@ -15362,7 +15362,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G517" t="n">
-        <v>2.52687740325928</v>
+        <v>2.5268771648407</v>
       </c>
       <c r="H517" t="n">
         <v>467905</v>
@@ -15478,7 +15478,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G521" t="n">
-        <v>2.62991523742676</v>
+        <v>2.62991499900818</v>
       </c>
       <c r="H521" t="n">
         <v>220252</v>
@@ -15594,7 +15594,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G525" t="n">
-        <v>2.64954137802124</v>
+        <v>2.64954161643982</v>
       </c>
       <c r="H525" t="n">
         <v>531029</v>
@@ -15623,7 +15623,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G526" t="n">
-        <v>2.64954137802124</v>
+        <v>2.64954161643982</v>
       </c>
       <c r="H526" t="n">
         <v>459494</v>
@@ -15652,7 +15652,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G527" t="n">
-        <v>2.65567445755005</v>
+        <v>2.65567421913147</v>
       </c>
       <c r="H527" t="n">
         <v>263721</v>
@@ -15826,7 +15826,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G533" t="n">
-        <v>2.46799874305725</v>
+        <v>2.46799850463867</v>
       </c>
       <c r="H533" t="n">
         <v>422014</v>
@@ -15855,7 +15855,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G534" t="n">
-        <v>2.48271822929382</v>
+        <v>2.48271799087524</v>
       </c>
       <c r="H534" t="n">
         <v>309567</v>
@@ -15884,7 +15884,7 @@
         <v>3.86400008201599</v>
       </c>
       <c r="G535" t="n">
-        <v>2.3698673248291</v>
+        <v>2.36986756324768</v>
       </c>
       <c r="H535" t="n">
         <v>527548</v>
@@ -15942,7 +15942,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G537" t="n">
-        <v>2.35269451141357</v>
+        <v>2.35269474983215</v>
       </c>
       <c r="H537" t="n">
         <v>708296</v>
@@ -15971,7 +15971,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G538" t="n">
-        <v>2.41647958755493</v>
+        <v>2.41647982597351</v>
       </c>
       <c r="H538" t="n">
         <v>656258</v>
@@ -16058,7 +16058,7 @@
         <v>3.60599994659424</v>
       </c>
       <c r="G541" t="n">
-        <v>2.21163105964661</v>
+        <v>2.21163082122803</v>
       </c>
       <c r="H541" t="n">
         <v>539338</v>
@@ -16087,7 +16087,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G542" t="n">
-        <v>2.1834180355072</v>
+        <v>2.18341827392578</v>
       </c>
       <c r="H542" t="n">
         <v>383193</v>
@@ -16145,7 +16145,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G544" t="n">
-        <v>2.27541613578796</v>
+        <v>2.27541637420654</v>
       </c>
       <c r="H544" t="n">
         <v>202220</v>
@@ -16261,7 +16261,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G548" t="n">
-        <v>2.28400254249573</v>
+        <v>2.28400278091431</v>
       </c>
       <c r="H548" t="n">
         <v>586919</v>
@@ -16319,7 +16319,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G550" t="n">
-        <v>2.24965691566467</v>
+        <v>2.24965667724609</v>
       </c>
       <c r="H550" t="n">
         <v>1786585</v>
@@ -16435,7 +16435,7 @@
         <v>3.18600010871887</v>
       </c>
       <c r="G554" t="n">
-        <v>1.95403671264648</v>
+        <v>1.95403659343719</v>
       </c>
       <c r="H554" t="n">
         <v>1152409</v>
@@ -16464,7 +16464,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G555" t="n">
-        <v>1.90129125118256</v>
+        <v>1.90129113197327</v>
       </c>
       <c r="H555" t="n">
         <v>1443403</v>
@@ -16522,7 +16522,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G557" t="n">
-        <v>1.87921166419983</v>
+        <v>1.87921154499054</v>
       </c>
       <c r="H557" t="n">
         <v>843821</v>
@@ -16580,7 +16580,7 @@
         <v>3.15799999237061</v>
       </c>
       <c r="G559" t="n">
-        <v>1.93686354160309</v>
+        <v>1.93686366081238</v>
       </c>
       <c r="H559" t="n">
         <v>444170</v>
@@ -16609,7 +16609,7 @@
         <v>3.11800003051758</v>
       </c>
       <c r="G560" t="n">
-        <v>1.91233086585999</v>
+        <v>1.91233098506927</v>
       </c>
       <c r="H560" t="n">
         <v>430921</v>
@@ -16696,7 +16696,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G563" t="n">
-        <v>1.87798500061035</v>
+        <v>1.87798511981964</v>
       </c>
       <c r="H563" t="n">
         <v>1003231</v>
@@ -16725,7 +16725,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G564" t="n">
-        <v>1.87921166419983</v>
+        <v>1.87921154499054</v>
       </c>
       <c r="H564" t="n">
         <v>329963</v>
@@ -16812,7 +16812,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G567" t="n">
-        <v>1.90129125118256</v>
+        <v>1.90129113197327</v>
       </c>
       <c r="H567" t="n">
         <v>594160</v>
@@ -16841,7 +16841,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G568" t="n">
-        <v>1.98715603351593</v>
+        <v>1.98715591430664</v>
       </c>
       <c r="H568" t="n">
         <v>1455013</v>
@@ -16928,7 +16928,7 @@
         <v>3.08200001716614</v>
       </c>
       <c r="G571" t="n">
-        <v>1.89025127887726</v>
+        <v>1.89025139808655</v>
       </c>
       <c r="H571" t="n">
         <v>528910</v>
@@ -16986,7 +16986,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G573" t="n">
-        <v>1.81542646884918</v>
+        <v>1.81542634963989</v>
       </c>
       <c r="H573" t="n">
         <v>710644</v>
@@ -17102,7 +17102,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G577" t="n">
-        <v>1.92091727256775</v>
+        <v>1.92091739177704</v>
       </c>
       <c r="H577" t="n">
         <v>1128337</v>
@@ -17131,7 +17131,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G578" t="n">
-        <v>1.95649003982544</v>
+        <v>1.95649015903473</v>
       </c>
       <c r="H578" t="n">
         <v>584408</v>
@@ -17218,7 +17218,7 @@
         <v>3.11800003051758</v>
       </c>
       <c r="G581" t="n">
-        <v>1.91233086585999</v>
+        <v>1.91233098506927</v>
       </c>
       <c r="H581" t="n">
         <v>350643</v>
@@ -17247,7 +17247,7 @@
         <v>3.14800000190735</v>
       </c>
       <c r="G582" t="n">
-        <v>1.93073046207428</v>
+        <v>1.93073070049286</v>
       </c>
       <c r="H582" t="n">
         <v>436681</v>
@@ -17305,7 +17305,7 @@
         <v>3.32399988174438</v>
       </c>
       <c r="G584" t="n">
-        <v>2.0386745929718</v>
+        <v>2.03867483139038</v>
       </c>
       <c r="H584" t="n">
         <v>692299</v>
@@ -17421,7 +17421,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G588" t="n">
-        <v>1.96262311935425</v>
+        <v>1.96262300014496</v>
       </c>
       <c r="H588" t="n">
         <v>478776</v>
@@ -17508,7 +17508,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G591" t="n">
-        <v>1.97120976448059</v>
+        <v>1.9712096452713</v>
       </c>
       <c r="H591" t="n">
         <v>772312</v>
@@ -17566,7 +17566,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G593" t="n">
-        <v>1.97734272480011</v>
+        <v>1.9773428440094</v>
       </c>
       <c r="H593" t="n">
         <v>256523</v>
@@ -17595,7 +17595,7 @@
         <v>3.25399994850159</v>
       </c>
       <c r="G594" t="n">
-        <v>1.99574244022369</v>
+        <v>1.99574255943298</v>
       </c>
       <c r="H594" t="n">
         <v>241270</v>
@@ -17624,7 +17624,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G595" t="n">
-        <v>2.08283352851868</v>
+        <v>2.08283400535583</v>
       </c>
       <c r="H595" t="n">
         <v>902410</v>
@@ -17653,7 +17653,7 @@
         <v>3.33599996566772</v>
       </c>
       <c r="G596" t="n">
-        <v>2.04603457450867</v>
+        <v>2.04603481292725</v>
       </c>
       <c r="H596" t="n">
         <v>599907</v>
@@ -17740,7 +17740,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G599" t="n">
-        <v>1.99942231178284</v>
+        <v>1.99942219257355</v>
       </c>
       <c r="H599" t="n">
         <v>777043</v>
@@ -17769,7 +17769,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G600" t="n">
-        <v>2.02640843391418</v>
+        <v>2.02640819549561</v>
       </c>
       <c r="H600" t="n">
         <v>719661</v>
@@ -17798,7 +17798,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G601" t="n">
-        <v>1.97120976448059</v>
+        <v>1.9712096452713</v>
       </c>
       <c r="H601" t="n">
         <v>1259936</v>
@@ -17827,7 +17827,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G602" t="n">
-        <v>1.96016979217529</v>
+        <v>1.96017003059387</v>
       </c>
       <c r="H602" t="n">
         <v>1065883</v>
@@ -17856,7 +17856,7 @@
         <v>3.15199995040894</v>
       </c>
       <c r="G603" t="n">
-        <v>1.93318378925323</v>
+        <v>1.93318367004395</v>
       </c>
       <c r="H603" t="n">
         <v>745062</v>
@@ -17885,7 +17885,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G604" t="n">
-        <v>1.93441045284271</v>
+        <v>1.93441033363342</v>
       </c>
       <c r="H604" t="n">
         <v>347176</v>
@@ -17914,7 +17914,7 @@
         <v>3.08200001716614</v>
       </c>
       <c r="G605" t="n">
-        <v>1.89025127887726</v>
+        <v>1.89025139808655</v>
       </c>
       <c r="H605" t="n">
         <v>380241</v>
@@ -17943,7 +17943,7 @@
         <v>3.13800001144409</v>
       </c>
       <c r="G606" t="n">
-        <v>1.92459750175476</v>
+        <v>1.92459726333618</v>
       </c>
       <c r="H606" t="n">
         <v>423628</v>
@@ -18001,7 +18001,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G608" t="n">
-        <v>1.88411819934845</v>
+        <v>1.88411831855774</v>
       </c>
       <c r="H608" t="n">
         <v>255709</v>
@@ -18030,7 +18030,7 @@
         <v>3.13599991798401</v>
       </c>
       <c r="G609" t="n">
-        <v>1.9233705997467</v>
+        <v>1.92337071895599</v>
       </c>
       <c r="H609" t="n">
         <v>161247</v>
@@ -18117,7 +18117,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G612" t="n">
-        <v>1.87921166419983</v>
+        <v>1.87921154499054</v>
       </c>
       <c r="H612" t="n">
         <v>402149</v>
@@ -18233,7 +18233,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G616" t="n">
-        <v>1.76636075973511</v>
+        <v>1.7663608789444</v>
       </c>
       <c r="H616" t="n">
         <v>727846</v>
@@ -18291,7 +18291,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G618" t="n">
-        <v>1.86939859390259</v>
+        <v>1.86939871311188</v>
       </c>
       <c r="H618" t="n">
         <v>268999</v>
@@ -18320,7 +18320,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G619" t="n">
-        <v>1.87307834625244</v>
+        <v>1.87307846546173</v>
       </c>
       <c r="H619" t="n">
         <v>336325</v>
@@ -18349,7 +18349,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G620" t="n">
-        <v>1.93441045284271</v>
+        <v>1.93441033363342</v>
       </c>
       <c r="H620" t="n">
         <v>666111</v>
@@ -18378,7 +18378,7 @@
         <v>3.08400011062622</v>
       </c>
       <c r="G621" t="n">
-        <v>1.89147818088531</v>
+        <v>1.89147806167603</v>
       </c>
       <c r="H621" t="n">
         <v>497533</v>
@@ -18465,7 +18465,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G624" t="n">
-        <v>1.87062525749207</v>
+        <v>1.87062513828278</v>
       </c>
       <c r="H624" t="n">
         <v>269179</v>
@@ -18581,7 +18581,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G628" t="n">
-        <v>1.80316007137299</v>
+        <v>1.8031599521637</v>
       </c>
       <c r="H628" t="n">
         <v>337726</v>
@@ -18639,7 +18639,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G630" t="n">
-        <v>1.80193340778351</v>
+        <v>1.80193328857422</v>
       </c>
       <c r="H630" t="n">
         <v>413305</v>
@@ -18668,7 +18668,7 @@
         <v>2.87599992752075</v>
       </c>
       <c r="G631" t="n">
-        <v>1.76390755176544</v>
+        <v>1.76390743255615</v>
       </c>
       <c r="H631" t="n">
         <v>379228</v>
@@ -18726,7 +18726,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G633" t="n">
-        <v>1.66822981834412</v>
+        <v>1.66822969913483</v>
       </c>
       <c r="H633" t="n">
         <v>413144</v>
@@ -18755,7 +18755,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G634" t="n">
-        <v>1.63756382465363</v>
+        <v>1.63756370544434</v>
       </c>
       <c r="H634" t="n">
         <v>381605</v>
@@ -18784,7 +18784,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G635" t="n">
-        <v>1.63020384311676</v>
+        <v>1.63020396232605</v>
       </c>
       <c r="H635" t="n">
         <v>421592</v>
@@ -18871,7 +18871,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G638" t="n">
-        <v>1.54924583435059</v>
+        <v>1.5492457151413</v>
       </c>
       <c r="H638" t="n">
         <v>499767</v>
@@ -18900,7 +18900,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G639" t="n">
-        <v>1.55169904232025</v>
+        <v>1.55169892311096</v>
       </c>
       <c r="H639" t="n">
         <v>341019</v>
@@ -18929,7 +18929,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G640" t="n">
-        <v>1.56273865699768</v>
+        <v>1.56273877620697</v>
       </c>
       <c r="H640" t="n">
         <v>265395</v>
@@ -18958,7 +18958,7 @@
         <v>2.68600010871887</v>
       </c>
       <c r="G641" t="n">
-        <v>1.64737677574158</v>
+        <v>1.64737689495087</v>
       </c>
       <c r="H641" t="n">
         <v>510074</v>
@@ -19016,7 +19016,7 @@
         <v>2.75799989700317</v>
       </c>
       <c r="G643" t="n">
-        <v>1.69153583049774</v>
+        <v>1.69153571128845</v>
       </c>
       <c r="H643" t="n">
         <v>185397</v>
@@ -19103,7 +19103,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G646" t="n">
-        <v>1.60567104816437</v>
+        <v>1.60567116737366</v>
       </c>
       <c r="H646" t="n">
         <v>247013</v>
@@ -19161,7 +19161,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G648" t="n">
-        <v>1.57377851009369</v>
+        <v>1.5737783908844</v>
       </c>
       <c r="H648" t="n">
         <v>104635</v>
@@ -19190,7 +19190,7 @@
         <v>2.62800002098083</v>
       </c>
       <c r="G649" t="n">
-        <v>1.61180436611176</v>
+        <v>1.61180424690247</v>
       </c>
       <c r="H649" t="n">
         <v>203791</v>
@@ -19219,7 +19219,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G650" t="n">
-        <v>1.72956168651581</v>
+        <v>1.72956156730652</v>
       </c>
       <c r="H650" t="n">
         <v>751420</v>
@@ -19277,7 +19277,7 @@
         <v>2.71399998664856</v>
       </c>
       <c r="G652" t="n">
-        <v>1.66454970836639</v>
+        <v>1.66454982757568</v>
       </c>
       <c r="H652" t="n">
         <v>684291</v>
@@ -19538,7 +19538,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G661" t="n">
-        <v>1.24135911464691</v>
+        <v>1.24135899543762</v>
       </c>
       <c r="H661" t="n">
         <v>746110</v>
@@ -19567,7 +19567,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G662" t="n">
-        <v>1.26957190036774</v>
+        <v>1.26957178115845</v>
       </c>
       <c r="H662" t="n">
         <v>642114</v>
@@ -19596,7 +19596,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G663" t="n">
-        <v>1.2781583070755</v>
+        <v>1.27815842628479</v>
       </c>
       <c r="H663" t="n">
         <v>398421</v>
@@ -19973,7 +19973,7 @@
         <v>2.00399994850159</v>
       </c>
       <c r="G676" t="n">
-        <v>1.22909271717072</v>
+        <v>1.22909259796143</v>
       </c>
       <c r="H676" t="n">
         <v>261133</v>
@@ -20002,7 +20002,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G677" t="n">
-        <v>1.23154592514038</v>
+        <v>1.23154604434967</v>
       </c>
       <c r="H677" t="n">
         <v>290766</v>
@@ -20031,7 +20031,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G678" t="n">
-        <v>1.24749231338501</v>
+        <v>1.24749219417572</v>
       </c>
       <c r="H678" t="n">
         <v>430500</v>
@@ -20060,7 +20060,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G679" t="n">
-        <v>1.24749231338501</v>
+        <v>1.24749219417572</v>
       </c>
       <c r="H679" t="n">
         <v>198373</v>
@@ -20118,7 +20118,7 @@
         <v>2.00600004196167</v>
       </c>
       <c r="G681" t="n">
-        <v>1.23031938076019</v>
+        <v>1.23031949996948</v>
       </c>
       <c r="H681" t="n">
         <v>692504</v>
@@ -20234,7 +20234,7 @@
         <v>2.00399994850159</v>
       </c>
       <c r="G685" t="n">
-        <v>1.22909271717072</v>
+        <v>1.22909259796143</v>
       </c>
       <c r="H685" t="n">
         <v>716738</v>
@@ -20292,7 +20292,7 @@
         <v>2</v>
       </c>
       <c r="G687" t="n">
-        <v>1.22663938999176</v>
+        <v>1.22663950920105</v>
       </c>
       <c r="H687" t="n">
         <v>624287</v>
@@ -20408,7 +20408,7 @@
         <v>2</v>
       </c>
       <c r="G691" t="n">
-        <v>1.22663938999176</v>
+        <v>1.22663950920105</v>
       </c>
       <c r="H691" t="n">
         <v>605384</v>
@@ -20437,7 +20437,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G692" t="n">
-        <v>1.24381244182587</v>
+        <v>1.24381256103516</v>
       </c>
       <c r="H692" t="n">
         <v>607664</v>
@@ -20466,7 +20466,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G693" t="n">
-        <v>1.24381244182587</v>
+        <v>1.24381256103516</v>
       </c>
       <c r="H693" t="n">
         <v>615775</v>
@@ -20495,7 +20495,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G694" t="n">
-        <v>1.26343870162964</v>
+        <v>1.26343858242035</v>
       </c>
       <c r="H694" t="n">
         <v>729450</v>
@@ -20553,7 +20553,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G696" t="n">
-        <v>1.31741094589233</v>
+        <v>1.31741070747375</v>
       </c>
       <c r="H696" t="n">
         <v>1602595</v>
@@ -20611,7 +20611,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G698" t="n">
-        <v>1.24381244182587</v>
+        <v>1.24381256103516</v>
       </c>
       <c r="H698" t="n">
         <v>965266</v>
@@ -20669,7 +20669,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G700" t="n">
-        <v>1.24626576900482</v>
+        <v>1.24626564979553</v>
       </c>
       <c r="H700" t="n">
         <v>384853</v>
@@ -20756,7 +20756,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G703" t="n">
-        <v>1.17389404773712</v>
+        <v>1.17389392852783</v>
       </c>
       <c r="H703" t="n">
         <v>1026206</v>
@@ -20814,7 +20814,7 @@
         <v>1.92299997806549</v>
       </c>
       <c r="G705" t="n">
-        <v>1.17941391468048</v>
+        <v>1.17941379547119</v>
       </c>
       <c r="H705" t="n">
         <v>288525</v>
@@ -20959,7 +20959,7 @@
         <v>1.68700003623962</v>
       </c>
       <c r="G710" t="n">
-        <v>1.03467047214508</v>
+        <v>1.03467035293579</v>
       </c>
       <c r="H710" t="n">
         <v>398616</v>
@@ -21104,7 +21104,7 @@
         <v>1.625</v>
       </c>
       <c r="G715" t="n">
-        <v>0.996644556522369</v>
+        <v>0.996644616127014</v>
       </c>
       <c r="H715" t="n">
         <v>423729</v>
@@ -21162,7 +21162,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G717" t="n">
-        <v>0.984991550445557</v>
+        <v>0.984991431236267</v>
       </c>
       <c r="H717" t="n">
         <v>776455</v>
@@ -21220,7 +21220,7 @@
         <v>1.49300003051758</v>
       </c>
       <c r="G719" t="n">
-        <v>0.915686428546906</v>
+        <v>0.915686309337616</v>
       </c>
       <c r="H719" t="n">
         <v>735567</v>
@@ -21336,7 +21336,7 @@
         <v>1.57599997520447</v>
       </c>
       <c r="G723" t="n">
-        <v>0.966591894626617</v>
+        <v>0.966591835021973</v>
       </c>
       <c r="H723" t="n">
         <v>684711</v>
@@ -21365,7 +21365,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G724" t="n">
-        <v>0.96536523103714</v>
+        <v>0.965365350246429</v>
       </c>
       <c r="H724" t="n">
         <v>453862</v>
@@ -21394,7 +21394,7 @@
         <v>1.59300005435944</v>
       </c>
       <c r="G725" t="n">
-        <v>0.977018356323242</v>
+        <v>0.977018296718597</v>
       </c>
       <c r="H725" t="n">
         <v>492029</v>
@@ -21423,7 +21423,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G726" t="n">
-        <v>0.980084896087646</v>
+        <v>0.980085015296936</v>
       </c>
       <c r="H726" t="n">
         <v>625242</v>
@@ -21452,7 +21452,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G727" t="n">
-        <v>0.958618760108948</v>
+        <v>0.958618640899658</v>
       </c>
       <c r="H727" t="n">
         <v>253732</v>
@@ -21481,7 +21481,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G728" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H728" t="n">
         <v>546391</v>
@@ -21510,7 +21510,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G729" t="n">
-        <v>0.992351353168488</v>
+        <v>0.992351412773132</v>
       </c>
       <c r="H729" t="n">
         <v>763102</v>
@@ -21539,7 +21539,7 @@
         <v>1.57200002670288</v>
       </c>
       <c r="G730" t="n">
-        <v>0.964138567447662</v>
+        <v>0.964138627052307</v>
       </c>
       <c r="H730" t="n">
         <v>464016</v>
@@ -21568,7 +21568,7 @@
         <v>1.53299999237061</v>
       </c>
       <c r="G731" t="n">
-        <v>0.940219163894653</v>
+        <v>0.940219104290009</v>
       </c>
       <c r="H731" t="n">
         <v>257158</v>
@@ -21597,7 +21597,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G732" t="n">
-        <v>0.907713234424591</v>
+        <v>0.907713174819946</v>
       </c>
       <c r="H732" t="n">
         <v>497466</v>
@@ -21655,7 +21655,7 @@
         <v>1.50100004673004</v>
       </c>
       <c r="G734" t="n">
-        <v>0.920592904090881</v>
+        <v>0.920592963695526</v>
       </c>
       <c r="H734" t="n">
         <v>566523</v>
@@ -21713,7 +21713,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G736" t="n">
-        <v>0.895446836948395</v>
+        <v>0.89544677734375</v>
       </c>
       <c r="H736" t="n">
         <v>253922</v>
@@ -21771,7 +21771,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G738" t="n">
-        <v>0.867847442626953</v>
+        <v>0.867847383022308</v>
       </c>
       <c r="H738" t="n">
         <v>252282</v>
@@ -21858,7 +21858,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G741" t="n">
-        <v>0.884407103061676</v>
+        <v>0.884407043457031</v>
       </c>
       <c r="H741" t="n">
         <v>275350</v>
@@ -21887,7 +21887,7 @@
         <v>1.53299999237061</v>
       </c>
       <c r="G742" t="n">
-        <v>0.940219163894653</v>
+        <v>0.940219104290009</v>
       </c>
       <c r="H742" t="n">
         <v>982055</v>
@@ -21916,7 +21916,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G743" t="n">
-        <v>0.956778764724731</v>
+        <v>0.956778824329376</v>
       </c>
       <c r="H743" t="n">
         <v>500398</v>
@@ -21945,7 +21945,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G744" t="n">
-        <v>0.94451230764389</v>
+        <v>0.94451242685318</v>
       </c>
       <c r="H744" t="n">
         <v>249172</v>
@@ -21974,7 +21974,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G745" t="n">
-        <v>0.941445767879486</v>
+        <v>0.941445708274841</v>
       </c>
       <c r="H745" t="n">
         <v>656565</v>
@@ -22003,7 +22003,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G746" t="n">
-        <v>0.938379168510437</v>
+        <v>0.938379287719727</v>
       </c>
       <c r="H746" t="n">
         <v>1898728</v>
@@ -22032,7 +22032,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G747" t="n">
-        <v>0.967205226421356</v>
+        <v>0.967205166816711</v>
       </c>
       <c r="H747" t="n">
         <v>682019</v>
@@ -22061,7 +22061,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G748" t="n">
-        <v>0.956165432929993</v>
+        <v>0.956165492534637</v>
       </c>
       <c r="H748" t="n">
         <v>267818</v>
@@ -22090,7 +22090,7 @@
         <v>1.557000041008</v>
       </c>
       <c r="G749" t="n">
-        <v>0.954938888549805</v>
+        <v>0.954938769340515</v>
       </c>
       <c r="H749" t="n">
         <v>131447</v>
@@ -22119,7 +22119,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G750" t="n">
-        <v>0.901580035686493</v>
+        <v>0.901579976081848</v>
       </c>
       <c r="H750" t="n">
         <v>663241</v>
@@ -22235,7 +22235,7 @@
         <v>1.48699998855591</v>
       </c>
       <c r="G754" t="n">
-        <v>0.912006437778473</v>
+        <v>0.912006497383118</v>
       </c>
       <c r="H754" t="n">
         <v>459581</v>
@@ -22264,7 +22264,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G755" t="n">
-        <v>0.875207245349884</v>
+        <v>0.875207304954529</v>
       </c>
       <c r="H755" t="n">
         <v>856510</v>
@@ -22322,7 +22322,7 @@
         <v>1.37899994850159</v>
       </c>
       <c r="G757" t="n">
-        <v>0.845767915248871</v>
+        <v>0.845767855644226</v>
       </c>
       <c r="H757" t="n">
         <v>507600</v>
@@ -22351,7 +22351,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G758" t="n">
-        <v>0.837181448936462</v>
+        <v>0.837181389331818</v>
       </c>
       <c r="H758" t="n">
         <v>234713</v>
@@ -22409,7 +22409,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G760" t="n">
-        <v>0.837181448936462</v>
+        <v>0.837181389331818</v>
       </c>
       <c r="H760" t="n">
         <v>270071</v>
@@ -22438,7 +22438,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G761" t="n">
-        <v>0.864780843257904</v>
+        <v>0.864780783653259</v>
       </c>
       <c r="H761" t="n">
         <v>398789</v>
@@ -22467,7 +22467,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G762" t="n">
-        <v>0.864780843257904</v>
+        <v>0.864780783653259</v>
       </c>
       <c r="H762" t="n">
         <v>196803</v>
@@ -22525,7 +22525,7 @@
         <v>1.45700001716614</v>
       </c>
       <c r="G764" t="n">
-        <v>0.893606841564178</v>
+        <v>0.893606901168823</v>
       </c>
       <c r="H764" t="n">
         <v>309417</v>
@@ -22554,7 +22554,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G765" t="n">
-        <v>0.911393105983734</v>
+        <v>0.911392986774445</v>
       </c>
       <c r="H765" t="n">
         <v>318206</v>
@@ -22641,7 +22641,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G768" t="n">
-        <v>0.951872229576111</v>
+        <v>0.951872289180756</v>
       </c>
       <c r="H768" t="n">
         <v>554719</v>
@@ -22670,7 +22670,7 @@
         <v>1.60699999332428</v>
       </c>
       <c r="G769" t="n">
-        <v>0.985604882240295</v>
+        <v>0.985604822635651</v>
       </c>
       <c r="H769" t="n">
         <v>1218675</v>
@@ -22728,7 +22728,7 @@
         <v>1.61300003528595</v>
       </c>
       <c r="G771" t="n">
-        <v>0.989284694194794</v>
+        <v>0.989284753799438</v>
       </c>
       <c r="H771" t="n">
         <v>301683</v>
@@ -22786,7 +22786,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G773" t="n">
-        <v>0.94451230764389</v>
+        <v>0.94451242685318</v>
       </c>
       <c r="H773" t="n">
         <v>246426</v>
@@ -22844,7 +22844,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G775" t="n">
-        <v>0.982538223266602</v>
+        <v>0.982538282871246</v>
       </c>
       <c r="H775" t="n">
         <v>323658</v>
@@ -22873,7 +22873,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G776" t="n">
-        <v>0.993578016757965</v>
+        <v>0.99357795715332</v>
       </c>
       <c r="H776" t="n">
         <v>368874</v>
@@ -22931,7 +22931,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G778" t="n">
-        <v>0.940832436084747</v>
+        <v>0.940832495689392</v>
       </c>
       <c r="H778" t="n">
         <v>302240</v>
@@ -22960,7 +22960,7 @@
         <v>1.5</v>
       </c>
       <c r="G779" t="n">
-        <v>0.919979572296143</v>
+        <v>0.919979512691498</v>
       </c>
       <c r="H779" t="n">
         <v>307567</v>
@@ -23018,7 +23018,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G781" t="n">
-        <v>0.984991550445557</v>
+        <v>0.984991431236267</v>
       </c>
       <c r="H781" t="n">
         <v>583532</v>
@@ -23105,7 +23105,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G784" t="n">
-        <v>1.06472289562225</v>
+        <v>1.06472301483154</v>
       </c>
       <c r="H784" t="n">
         <v>414554</v>
@@ -23250,7 +23250,7 @@
         <v>1.7039999961853</v>
       </c>
       <c r="G789" t="n">
-        <v>1.04509675502777</v>
+        <v>1.04509687423706</v>
       </c>
       <c r="H789" t="n">
         <v>244962</v>
@@ -23279,7 +23279,7 @@
         <v>1.625</v>
       </c>
       <c r="G790" t="n">
-        <v>0.996644556522369</v>
+        <v>0.996644616127014</v>
       </c>
       <c r="H790" t="n">
         <v>694373</v>
@@ -23308,7 +23308,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G791" t="n">
-        <v>0.972111761569977</v>
+        <v>0.972111821174622</v>
       </c>
       <c r="H791" t="n">
         <v>381336</v>
@@ -23366,7 +23366,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G793" t="n">
-        <v>0.996031224727631</v>
+        <v>0.996031284332275</v>
       </c>
       <c r="H793" t="n">
         <v>454468</v>
@@ -23395,7 +23395,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G794" t="n">
-        <v>1.05491006374359</v>
+        <v>1.0549099445343</v>
       </c>
       <c r="H794" t="n">
         <v>592655</v>
@@ -23453,7 +23453,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G796" t="n">
-        <v>1.06901621818542</v>
+        <v>1.06901633739471</v>
       </c>
       <c r="H796" t="n">
         <v>268068</v>
@@ -23540,7 +23540,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G799" t="n">
-        <v>1.06901621818542</v>
+        <v>1.06901633739471</v>
       </c>
       <c r="H799" t="n">
         <v>234941</v>
@@ -23569,7 +23569,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G800" t="n">
-        <v>1.03957688808441</v>
+        <v>1.0395770072937</v>
       </c>
       <c r="H800" t="n">
         <v>181799</v>
@@ -23685,7 +23685,7 @@
         <v>1.56900000572205</v>
       </c>
       <c r="G804" t="n">
-        <v>0.96229875087738</v>
+        <v>0.962298631668091</v>
       </c>
       <c r="H804" t="n">
         <v>1000748</v>
@@ -23714,7 +23714,7 @@
         <v>1.56700003147125</v>
       </c>
       <c r="G805" t="n">
-        <v>0.961072087287903</v>
+        <v>0.961072027683258</v>
       </c>
       <c r="H805" t="n">
         <v>514716</v>
@@ -23743,7 +23743,7 @@
         <v>1.5789999961853</v>
       </c>
       <c r="G806" t="n">
-        <v>0.968431770801544</v>
+        <v>0.968431830406189</v>
       </c>
       <c r="H806" t="n">
         <v>380344</v>
@@ -23859,7 +23859,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G810" t="n">
-        <v>0.921206176280975</v>
+        <v>0.92120623588562</v>
       </c>
       <c r="H810" t="n">
         <v>897101</v>
@@ -24004,7 +24004,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G815" t="n">
-        <v>0.928566098213196</v>
+        <v>0.928566157817841</v>
       </c>
       <c r="H815" t="n">
         <v>528078</v>
@@ -24091,7 +24091,7 @@
         <v>1.54100000858307</v>
       </c>
       <c r="G818" t="n">
-        <v>0.945125639438629</v>
+        <v>0.945125699043274</v>
       </c>
       <c r="H818" t="n">
         <v>478848</v>
@@ -24120,7 +24120,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G819" t="n">
-        <v>0.945739090442657</v>
+        <v>0.945739030838013</v>
       </c>
       <c r="H819" t="n">
         <v>1308957</v>
@@ -24207,7 +24207,7 @@
         <v>1.47300004959106</v>
       </c>
       <c r="G822" t="n">
-        <v>0.903420031070709</v>
+        <v>0.903419971466064</v>
       </c>
       <c r="H822" t="n">
         <v>526975</v>
@@ -24236,7 +24236,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G823" t="n">
-        <v>0.899126708507538</v>
+        <v>0.899126648902893</v>
       </c>
       <c r="H823" t="n">
         <v>347418</v>
@@ -24294,7 +24294,7 @@
         <v>1.50100004673004</v>
       </c>
       <c r="G825" t="n">
-        <v>0.920592904090881</v>
+        <v>0.920592963695526</v>
       </c>
       <c r="H825" t="n">
         <v>216341</v>
@@ -24323,7 +24323,7 @@
         <v>1.53699994087219</v>
       </c>
       <c r="G826" t="n">
-        <v>0.942672431468964</v>
+        <v>0.942672491073608</v>
       </c>
       <c r="H826" t="n">
         <v>166399</v>
@@ -24352,7 +24352,7 @@
         <v>1.59300005435944</v>
       </c>
       <c r="G827" t="n">
-        <v>0.977018356323242</v>
+        <v>0.977018296718597</v>
       </c>
       <c r="H827" t="n">
         <v>400075</v>
@@ -24381,7 +24381,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G828" t="n">
-        <v>0.960458636283875</v>
+        <v>0.960458695888519</v>
       </c>
       <c r="H828" t="n">
         <v>496001</v>
@@ -24410,7 +24410,7 @@
         <v>1.65299999713898</v>
       </c>
       <c r="G829" t="n">
-        <v>1.01381754875183</v>
+        <v>1.01381742954254</v>
       </c>
       <c r="H829" t="n">
         <v>887503</v>
@@ -24439,7 +24439,7 @@
         <v>1.66100001335144</v>
       </c>
       <c r="G830" t="n">
-        <v>1.01872396469116</v>
+        <v>1.01872420310974</v>
       </c>
       <c r="H830" t="n">
         <v>270311</v>
@@ -24526,7 +24526,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G833" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H833" t="n">
         <v>950966</v>
@@ -24555,7 +24555,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G834" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H834" t="n">
         <v>272796</v>
@@ -24613,7 +24613,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G836" t="n">
-        <v>0.96536523103714</v>
+        <v>0.965365350246429</v>
       </c>
       <c r="H836" t="n">
         <v>290487</v>
@@ -24642,7 +24642,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G837" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H837" t="n">
         <v>135240</v>
@@ -24700,7 +24700,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G839" t="n">
-        <v>0.977631688117981</v>
+        <v>0.977631628513336</v>
       </c>
       <c r="H839" t="n">
         <v>557684</v>
@@ -24787,7 +24787,7 @@
         <v>1.5789999961853</v>
       </c>
       <c r="G842" t="n">
-        <v>0.968431770801544</v>
+        <v>0.968431830406189</v>
       </c>
       <c r="H842" t="n">
         <v>498110</v>
@@ -24816,7 +24816,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G843" t="n">
-        <v>0.953098893165588</v>
+        <v>0.953098952770233</v>
       </c>
       <c r="H843" t="n">
         <v>226537</v>
@@ -24874,7 +24874,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G845" t="n">
-        <v>0.90280669927597</v>
+        <v>0.902806639671326</v>
       </c>
       <c r="H845" t="n">
         <v>601706</v>
@@ -24932,7 +24932,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G847" t="n">
-        <v>0.852514445781708</v>
+        <v>0.852514386177063</v>
       </c>
       <c r="H847" t="n">
         <v>1230354</v>
@@ -24990,7 +24990,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G849" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H849" t="n">
         <v>747799</v>
@@ -25077,7 +25077,7 @@
         <v>1.27799999713898</v>
       </c>
       <c r="G852" t="n">
-        <v>0.783822655677795</v>
+        <v>0.783822596073151</v>
       </c>
       <c r="H852" t="n">
         <v>775169</v>
@@ -25135,7 +25135,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G854" t="n">
-        <v>0.731077075004578</v>
+        <v>0.731077134609222</v>
       </c>
       <c r="H854" t="n">
         <v>637617</v>
@@ -25193,7 +25193,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G856" t="n">
-        <v>0.743343472480774</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H856" t="n">
         <v>866584</v>
@@ -25222,7 +25222,7 @@
         <v>1.192999958992</v>
       </c>
       <c r="G857" t="n">
-        <v>0.731690466403961</v>
+        <v>0.731690406799316</v>
       </c>
       <c r="H857" t="n">
         <v>416974</v>
@@ -25280,7 +25280,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G859" t="n">
-        <v>0.69611781835556</v>
+        <v>0.69611793756485</v>
       </c>
       <c r="H859" t="n">
         <v>285309</v>
@@ -25309,7 +25309,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G860" t="n">
-        <v>0.718810737133026</v>
+        <v>0.718810796737671</v>
       </c>
       <c r="H860" t="n">
         <v>601635</v>
@@ -25338,7 +25338,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G861" t="n">
-        <v>0.705317735671997</v>
+        <v>0.705317676067352</v>
       </c>
       <c r="H861" t="n">
         <v>305816</v>
@@ -25367,7 +25367,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G862" t="n">
-        <v>0.69857120513916</v>
+        <v>0.698571264743805</v>
       </c>
       <c r="H862" t="n">
         <v>581824</v>
@@ -25425,7 +25425,7 @@
         <v>1.17900002002716</v>
       </c>
       <c r="G864" t="n">
-        <v>0.723103940486908</v>
+        <v>0.723104000091553</v>
       </c>
       <c r="H864" t="n">
         <v>869061</v>
@@ -25483,7 +25483,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G866" t="n">
-        <v>0.729850471019745</v>
+        <v>0.72985053062439</v>
       </c>
       <c r="H866" t="n">
         <v>419879</v>
@@ -25512,7 +25512,7 @@
         <v>1.17900002002716</v>
       </c>
       <c r="G867" t="n">
-        <v>0.723103940486908</v>
+        <v>0.723104000091553</v>
       </c>
       <c r="H867" t="n">
         <v>203797</v>
@@ -25570,7 +25570,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G869" t="n">
-        <v>0.69857120513916</v>
+        <v>0.698571264743805</v>
       </c>
       <c r="H869" t="n">
         <v>137746</v>
@@ -25628,7 +25628,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G871" t="n">
-        <v>0.716970860958099</v>
+        <v>0.716970801353455</v>
       </c>
       <c r="H871" t="n">
         <v>193491</v>
@@ -25657,7 +25657,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G872" t="n">
-        <v>0.705317735671997</v>
+        <v>0.705317676067352</v>
       </c>
       <c r="H872" t="n">
         <v>363288</v>
@@ -25686,7 +25686,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G873" t="n">
-        <v>0.709610879421234</v>
+        <v>0.709610939025879</v>
       </c>
       <c r="H873" t="n">
         <v>47164</v>
@@ -25715,7 +25715,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G874" t="n">
-        <v>0.716970860958099</v>
+        <v>0.716970801353455</v>
       </c>
       <c r="H874" t="n">
         <v>88623</v>
@@ -25744,7 +25744,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G875" t="n">
-        <v>0.721877336502075</v>
+        <v>0.72187739610672</v>
       </c>
       <c r="H875" t="n">
         <v>166052</v>
@@ -25773,7 +25773,7 @@
         <v>1.1710000038147</v>
       </c>
       <c r="G876" t="n">
-        <v>0.718197405338287</v>
+        <v>0.718197345733643</v>
       </c>
       <c r="H876" t="n">
         <v>98716</v>
@@ -25860,7 +25860,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G879" t="n">
-        <v>0.718810737133026</v>
+        <v>0.718810796737671</v>
       </c>
       <c r="H879" t="n">
         <v>103212</v>
@@ -25918,7 +25918,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G881" t="n">
-        <v>0.734757006168365</v>
+        <v>0.73475706577301</v>
       </c>
       <c r="H881" t="n">
         <v>166835</v>
@@ -26063,7 +26063,7 @@
         <v>1.22099995613098</v>
       </c>
       <c r="G886" t="n">
-        <v>0.748863399028778</v>
+        <v>0.748863339424133</v>
       </c>
       <c r="H886" t="n">
         <v>113419</v>
@@ -26121,7 +26121,7 @@
         <v>1.24699997901917</v>
       </c>
       <c r="G888" t="n">
-        <v>0.764809727668762</v>
+        <v>0.764809668064117</v>
       </c>
       <c r="H888" t="n">
         <v>84093</v>
@@ -26179,7 +26179,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G890" t="n">
-        <v>0.770329594612122</v>
+        <v>0.770329654216766</v>
       </c>
       <c r="H890" t="n">
         <v>248918</v>
@@ -26237,7 +26237,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G892" t="n">
-        <v>0.775849521160126</v>
+        <v>0.775849461555481</v>
       </c>
       <c r="H892" t="n">
         <v>153630</v>
@@ -26295,7 +26295,7 @@
         <v>1.25</v>
       </c>
       <c r="G894" t="n">
-        <v>0.766649663448334</v>
+        <v>0.766649723052979</v>
       </c>
       <c r="H894" t="n">
         <v>155968</v>
@@ -26324,7 +26324,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G895" t="n">
-        <v>0.761743068695068</v>
+        <v>0.761743128299713</v>
       </c>
       <c r="H895" t="n">
         <v>419752</v>
@@ -26382,7 +26382,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G897" t="n">
-        <v>0.763583123683929</v>
+        <v>0.763583064079285</v>
       </c>
       <c r="H897" t="n">
         <v>72706</v>
@@ -26411,7 +26411,7 @@
         <v>1.24699997901917</v>
       </c>
       <c r="G898" t="n">
-        <v>0.764809727668762</v>
+        <v>0.764809668064117</v>
       </c>
       <c r="H898" t="n">
         <v>106980</v>
@@ -26527,7 +26527,7 @@
         <v>1.21700000762939</v>
       </c>
       <c r="G902" t="n">
-        <v>0.746410071849823</v>
+        <v>0.746410131454468</v>
       </c>
       <c r="H902" t="n">
         <v>45869</v>
@@ -26614,7 +26614,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G905" t="n">
-        <v>0.788729131221771</v>
+        <v>0.788729190826416</v>
       </c>
       <c r="H905" t="n">
         <v>739169</v>
@@ -26730,7 +26730,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G909" t="n">
-        <v>0.781982600688934</v>
+        <v>0.781982660293579</v>
       </c>
       <c r="H909" t="n">
         <v>162522</v>
@@ -26759,7 +26759,7 @@
         <v>1.25</v>
       </c>
       <c r="G910" t="n">
-        <v>0.766649663448334</v>
+        <v>0.766649723052979</v>
       </c>
       <c r="H910" t="n">
         <v>92063</v>
@@ -26846,7 +26846,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G913" t="n">
-        <v>0.724943995475769</v>
+        <v>0.724943935871124</v>
       </c>
       <c r="H913" t="n">
         <v>255453</v>
@@ -26933,7 +26933,7 @@
         <v>1.17900002002716</v>
       </c>
       <c r="G916" t="n">
-        <v>0.723103940486908</v>
+        <v>0.723104000091553</v>
       </c>
       <c r="H916" t="n">
         <v>38025</v>
@@ -26991,7 +26991,7 @@
         <v>1.192999958992</v>
       </c>
       <c r="G918" t="n">
-        <v>0.731690466403961</v>
+        <v>0.731690406799316</v>
       </c>
       <c r="H918" t="n">
         <v>265819</v>
@@ -27049,7 +27049,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G920" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H920" t="n">
         <v>337846</v>
@@ -27107,7 +27107,7 @@
         <v>1.18099999427795</v>
       </c>
       <c r="G922" t="n">
-        <v>0.72433066368103</v>
+        <v>0.724330604076385</v>
       </c>
       <c r="H922" t="n">
         <v>22435</v>
@@ -27223,7 +27223,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G926" t="n">
-        <v>0.792409121990204</v>
+        <v>0.792409062385559</v>
       </c>
       <c r="H926" t="n">
         <v>543195</v>
@@ -27252,7 +27252,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G927" t="n">
-        <v>0.781982600688934</v>
+        <v>0.781982660293579</v>
       </c>
       <c r="H927" t="n">
         <v>211914</v>
@@ -27281,7 +27281,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G928" t="n">
-        <v>0.770329594612122</v>
+        <v>0.770329654216766</v>
       </c>
       <c r="H928" t="n">
         <v>147741</v>
@@ -27310,7 +27310,7 @@
         <v>1.25</v>
       </c>
       <c r="G929" t="n">
-        <v>0.766649663448334</v>
+        <v>0.766649723052979</v>
       </c>
       <c r="H929" t="n">
         <v>80356</v>
@@ -27368,7 +27368,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G931" t="n">
-        <v>0.788729131221771</v>
+        <v>0.788729190826416</v>
       </c>
       <c r="H931" t="n">
         <v>296798</v>
@@ -27397,7 +27397,7 @@
         <v>1.25</v>
       </c>
       <c r="G932" t="n">
-        <v>0.766649663448334</v>
+        <v>0.766649723052979</v>
       </c>
       <c r="H932" t="n">
         <v>209670</v>
@@ -27484,7 +27484,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G935" t="n">
-        <v>0.763583123683929</v>
+        <v>0.763583064079285</v>
       </c>
       <c r="H935" t="n">
         <v>149674</v>
@@ -27571,7 +27571,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G938" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H938" t="n">
         <v>317570</v>
@@ -27600,7 +27600,7 @@
         <v>1.33700001239777</v>
       </c>
       <c r="G939" t="n">
-        <v>0.820008516311646</v>
+        <v>0.820008456707001</v>
       </c>
       <c r="H939" t="n">
         <v>628585</v>
@@ -27658,7 +27658,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G941" t="n">
-        <v>0.834114909172058</v>
+        <v>0.834114849567413</v>
       </c>
       <c r="H941" t="n">
         <v>271769</v>
@@ -27687,7 +27687,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G942" t="n">
-        <v>0.834114909172058</v>
+        <v>0.834114849567413</v>
       </c>
       <c r="H942" t="n">
         <v>220189</v>
@@ -27716,7 +27716,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G943" t="n">
-        <v>0.837181448936462</v>
+        <v>0.837181389331818</v>
       </c>
       <c r="H943" t="n">
         <v>150974</v>
@@ -27745,7 +27745,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G944" t="n">
-        <v>0.832888305187225</v>
+        <v>0.832888185977936</v>
       </c>
       <c r="H944" t="n">
         <v>363471</v>
@@ -27803,7 +27803,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G946" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H946" t="n">
         <v>120742</v>
@@ -27861,7 +27861,7 @@
         <v>1.27600002288818</v>
       </c>
       <c r="G948" t="n">
-        <v>0.782596051692963</v>
+        <v>0.782595992088318</v>
       </c>
       <c r="H948" t="n">
         <v>282380</v>
@@ -27890,7 +27890,7 @@
         <v>1.26300001144409</v>
       </c>
       <c r="G949" t="n">
-        <v>0.774622917175293</v>
+        <v>0.774622857570648</v>
       </c>
       <c r="H949" t="n">
         <v>310968</v>
@@ -27919,7 +27919,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G950" t="n">
-        <v>0.754383206367493</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H950" t="n">
         <v>388069</v>
@@ -27948,7 +27948,7 @@
         <v>1.23099994659424</v>
       </c>
       <c r="G951" t="n">
-        <v>0.754996597766876</v>
+        <v>0.754996538162231</v>
       </c>
       <c r="H951" t="n">
         <v>184190</v>
@@ -27977,7 +27977,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G952" t="n">
-        <v>0.761743068695068</v>
+        <v>0.761743128299713</v>
       </c>
       <c r="H952" t="n">
         <v>112361</v>
@@ -28122,7 +28122,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G957" t="n">
-        <v>0.733530402183533</v>
+        <v>0.733530342578888</v>
       </c>
       <c r="H957" t="n">
         <v>98928</v>
@@ -28151,7 +28151,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G958" t="n">
-        <v>0.739050269126892</v>
+        <v>0.739050328731537</v>
       </c>
       <c r="H958" t="n">
         <v>114210</v>
@@ -28238,7 +28238,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G961" t="n">
-        <v>0.754383206367493</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H961" t="n">
         <v>137429</v>
@@ -28267,7 +28267,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G962" t="n">
-        <v>0.775849521160126</v>
+        <v>0.775849461555481</v>
       </c>
       <c r="H962" t="n">
         <v>214782</v>
@@ -28354,7 +28354,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G965" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H965" t="n">
         <v>236368</v>
@@ -28441,7 +28441,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G968" t="n">
-        <v>0.771556258201599</v>
+        <v>0.771556198596954</v>
       </c>
       <c r="H968" t="n">
         <v>106279</v>
@@ -28499,7 +28499,7 @@
         <v>1.25100004673004</v>
       </c>
       <c r="G970" t="n">
-        <v>0.767263054847717</v>
+        <v>0.767262995243073</v>
       </c>
       <c r="H970" t="n">
         <v>27949</v>
@@ -28528,7 +28528,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G971" t="n">
-        <v>0.781982600688934</v>
+        <v>0.781982660293579</v>
       </c>
       <c r="H971" t="n">
         <v>151642</v>
@@ -28557,7 +28557,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G972" t="n">
-        <v>0.834114909172058</v>
+        <v>0.834114849567413</v>
       </c>
       <c r="H972" t="n">
         <v>740480</v>
@@ -28818,7 +28818,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G981" t="n">
-        <v>0.981311559677124</v>
+        <v>0.981311500072479</v>
       </c>
       <c r="H981" t="n">
         <v>380709</v>
@@ -28847,7 +28847,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G982" t="n">
-        <v>0.94451230764389</v>
+        <v>0.94451242685318</v>
       </c>
       <c r="H982" t="n">
         <v>609647</v>
@@ -28905,7 +28905,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G984" t="n">
-        <v>0.961685299873352</v>
+        <v>0.961685359477997</v>
       </c>
       <c r="H984" t="n">
         <v>669708</v>
@@ -29050,7 +29050,7 @@
         <v>1.44900000095367</v>
       </c>
       <c r="G989" t="n">
-        <v>0.888700306415558</v>
+        <v>0.888700246810913</v>
       </c>
       <c r="H989" t="n">
         <v>370224</v>
@@ -29108,7 +29108,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G991" t="n">
-        <v>0.863554120063782</v>
+        <v>0.863554179668427</v>
       </c>
       <c r="H991" t="n">
         <v>202046</v>
@@ -29137,7 +29137,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G992" t="n">
-        <v>0.884407103061676</v>
+        <v>0.884407043457031</v>
       </c>
       <c r="H992" t="n">
         <v>245509</v>
@@ -29166,7 +29166,7 @@
         <v>1.5</v>
       </c>
       <c r="G993" t="n">
-        <v>0.919979572296143</v>
+        <v>0.919979512691498</v>
       </c>
       <c r="H993" t="n">
         <v>297589</v>
@@ -29195,7 +29195,7 @@
         <v>1.53100001811981</v>
       </c>
       <c r="G994" t="n">
-        <v>0.938992500305176</v>
+        <v>0.938992559909821</v>
       </c>
       <c r="H994" t="n">
         <v>412888</v>
@@ -29224,7 +29224,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G995" t="n">
-        <v>0.954325556755066</v>
+        <v>0.954325437545776</v>
       </c>
       <c r="H995" t="n">
         <v>364299</v>
@@ -29253,7 +29253,7 @@
         <v>1.52699995040894</v>
       </c>
       <c r="G996" t="n">
-        <v>0.936539173126221</v>
+        <v>0.936539232730865</v>
       </c>
       <c r="H996" t="n">
         <v>279676</v>
@@ -29282,7 +29282,7 @@
         <v>1.49300003051758</v>
       </c>
       <c r="G997" t="n">
-        <v>0.915686428546906</v>
+        <v>0.915686309337616</v>
       </c>
       <c r="H997" t="n">
         <v>223364</v>
@@ -29311,7 +29311,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G998" t="n">
-        <v>0.935312628746033</v>
+        <v>0.935312569141388</v>
       </c>
       <c r="H998" t="n">
         <v>1239866</v>
@@ -29340,7 +29340,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G999" t="n">
-        <v>0.91875296831131</v>
+        <v>0.918753027915955</v>
       </c>
       <c r="H999" t="n">
         <v>695778</v>
@@ -29369,7 +29369,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1000" t="n">
-        <v>0.928566098213196</v>
+        <v>0.928566157817841</v>
       </c>
       <c r="H1000" t="n">
         <v>238212</v>
@@ -29398,7 +29398,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G1001" t="n">
-        <v>0.916912972927094</v>
+        <v>0.916913032531738</v>
       </c>
       <c r="H1001" t="n">
         <v>566221</v>
@@ -29427,7 +29427,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G1002" t="n">
-        <v>0.91875296831131</v>
+        <v>0.918753027915955</v>
       </c>
       <c r="H1002" t="n">
         <v>198540</v>
@@ -29456,7 +29456,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G1003" t="n">
-        <v>0.91875296831131</v>
+        <v>0.918753027915955</v>
       </c>
       <c r="H1003" t="n">
         <v>784488</v>
@@ -29485,7 +29485,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1004" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H1004" t="n">
         <v>1240368</v>
@@ -29514,7 +29514,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.04141676425934</v>
+        <v>1.04141700267792</v>
       </c>
       <c r="H1005" t="n">
         <v>2397908</v>
@@ -29630,7 +29630,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.03957688808441</v>
+        <v>1.0395770072937</v>
       </c>
       <c r="H1009" t="n">
         <v>633161</v>
@@ -29659,7 +29659,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.0193372964859</v>
+        <v>1.01933741569519</v>
       </c>
       <c r="H1010" t="n">
         <v>906453</v>
@@ -29717,7 +29717,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.00277769565582</v>
+        <v>1.00277781486511</v>
       </c>
       <c r="H1012" t="n">
         <v>2587600</v>
@@ -29775,7 +29775,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1014" t="n">
-        <v>0.980084896087646</v>
+        <v>0.980085015296936</v>
       </c>
       <c r="H1014" t="n">
         <v>523079</v>
@@ -29804,7 +29804,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1015" t="n">
-        <v>0.980084896087646</v>
+        <v>0.980085015296936</v>
       </c>
       <c r="H1015" t="n">
         <v>426514</v>
@@ -29862,7 +29862,7 @@
         <v>1.57599997520447</v>
       </c>
       <c r="G1017" t="n">
-        <v>0.966591894626617</v>
+        <v>0.966591835021973</v>
       </c>
       <c r="H1017" t="n">
         <v>660847</v>
@@ -29891,7 +29891,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1018" t="n">
-        <v>0.94451230764389</v>
+        <v>0.94451242685318</v>
       </c>
       <c r="H1018" t="n">
         <v>455781</v>
@@ -29920,7 +29920,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G1019" t="n">
-        <v>0.958618760108948</v>
+        <v>0.958618640899658</v>
       </c>
       <c r="H1019" t="n">
         <v>288466</v>
@@ -29949,7 +29949,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1020" t="n">
-        <v>0.956778764724731</v>
+        <v>0.956778824329376</v>
       </c>
       <c r="H1020" t="n">
         <v>270776</v>
@@ -30007,7 +30007,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1022" t="n">
-        <v>0.965978562831879</v>
+        <v>0.965978682041168</v>
       </c>
       <c r="H1022" t="n">
         <v>372971</v>
@@ -30036,7 +30036,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G1023" t="n">
-        <v>0.967205226421356</v>
+        <v>0.967205166816711</v>
       </c>
       <c r="H1023" t="n">
         <v>273940</v>
@@ -30094,7 +30094,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1025" t="n">
-        <v>0.980084896087646</v>
+        <v>0.980085015296936</v>
       </c>
       <c r="H1025" t="n">
         <v>570459</v>
@@ -30123,7 +30123,7 @@
         <v>1.58700001239777</v>
       </c>
       <c r="G1026" t="n">
-        <v>0.973338425159454</v>
+        <v>0.973338305950165</v>
       </c>
       <c r="H1026" t="n">
         <v>768858</v>
@@ -30152,7 +30152,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G1027" t="n">
-        <v>0.906486511230469</v>
+        <v>0.906486630439758</v>
       </c>
       <c r="H1027" t="n">
         <v>1879056</v>
@@ -30181,7 +30181,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1028" t="n">
-        <v>0.864780843257904</v>
+        <v>0.864780783653259</v>
       </c>
       <c r="H1028" t="n">
         <v>1430254</v>
@@ -30239,7 +30239,7 @@
         <v>1.36699998378754</v>
       </c>
       <c r="G1030" t="n">
-        <v>0.838408052921295</v>
+        <v>0.83840811252594</v>
       </c>
       <c r="H1030" t="n">
         <v>744323</v>
@@ -30297,7 +30297,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1032" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1032" t="n">
         <v>989532</v>
@@ -30326,7 +30326,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G1033" t="n">
-        <v>0.767876267433167</v>
+        <v>0.767876327037811</v>
       </c>
       <c r="H1033" t="n">
         <v>878332</v>
@@ -30355,7 +30355,7 @@
         <v>1.26699995994568</v>
       </c>
       <c r="G1034" t="n">
-        <v>0.777076065540314</v>
+        <v>0.777076125144958</v>
       </c>
       <c r="H1034" t="n">
         <v>1684681</v>
@@ -30384,7 +30384,7 @@
         <v>1.32099997997284</v>
       </c>
       <c r="G1035" t="n">
-        <v>0.81019538640976</v>
+        <v>0.810195326805115</v>
       </c>
       <c r="H1035" t="n">
         <v>1370386</v>
@@ -30471,7 +30471,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G1038" t="n">
-        <v>0.781982600688934</v>
+        <v>0.781982660293579</v>
       </c>
       <c r="H1038" t="n">
         <v>221036</v>
@@ -30500,7 +30500,7 @@
         <v>1.2940000295639</v>
       </c>
       <c r="G1039" t="n">
-        <v>0.793635725975037</v>
+        <v>0.793635785579681</v>
       </c>
       <c r="H1039" t="n">
         <v>278799</v>
@@ -30529,7 +30529,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G1040" t="n">
-        <v>0.799768924713135</v>
+        <v>0.79976898431778</v>
       </c>
       <c r="H1040" t="n">
         <v>413001</v>
@@ -30674,7 +30674,7 @@
         <v>1.33700001239777</v>
       </c>
       <c r="G1045" t="n">
-        <v>0.820008516311646</v>
+        <v>0.820008456707001</v>
       </c>
       <c r="H1045" t="n">
         <v>582765</v>
@@ -30732,7 +30732,7 @@
         <v>1.30200004577637</v>
       </c>
       <c r="G1047" t="n">
-        <v>0.798542380332947</v>
+        <v>0.798542320728302</v>
       </c>
       <c r="H1047" t="n">
         <v>191360</v>
@@ -30761,7 +30761,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G1048" t="n">
-        <v>0.814488589763641</v>
+        <v>0.814488530158997</v>
       </c>
       <c r="H1048" t="n">
         <v>245739</v>
@@ -30877,7 +30877,7 @@
         <v>1.28699994087219</v>
       </c>
       <c r="G1052" t="n">
-        <v>0.789342403411865</v>
+        <v>0.78934246301651</v>
       </c>
       <c r="H1052" t="n">
         <v>394105</v>
@@ -30906,7 +30906,7 @@
         <v>1.192999958992</v>
       </c>
       <c r="G1053" t="n">
-        <v>0.731690466403961</v>
+        <v>0.731690406799316</v>
       </c>
       <c r="H1053" t="n">
         <v>919066</v>
@@ -30964,7 +30964,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G1055" t="n">
-        <v>0.708997666835785</v>
+        <v>0.70899760723114</v>
       </c>
       <c r="H1055" t="n">
         <v>894753</v>
@@ -30993,7 +30993,7 @@
         <v>1.13699996471405</v>
       </c>
       <c r="G1056" t="n">
-        <v>0.697344541549683</v>
+        <v>0.697344481945038</v>
       </c>
       <c r="H1056" t="n">
         <v>1009167</v>
@@ -31167,7 +31167,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.572227358818054</v>
+        <v>0.572227299213409</v>
       </c>
       <c r="H1062" t="n">
         <v>1024504</v>
@@ -31254,7 +31254,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.496789008378983</v>
+        <v>0.49678897857666</v>
       </c>
       <c r="H1065" t="n">
         <v>713971</v>
@@ -31312,7 +31312,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.451403349637985</v>
+        <v>0.451403319835663</v>
       </c>
       <c r="H1067" t="n">
         <v>964293</v>
@@ -31370,7 +31370,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.472256153821945</v>
+        <v>0.47225621342659</v>
       </c>
       <c r="H1069" t="n">
         <v>461033</v>
@@ -31399,7 +31399,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.461216449737549</v>
+        <v>0.461216419935226</v>
       </c>
       <c r="H1070" t="n">
         <v>387884</v>
@@ -31428,7 +31428,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.4747094810009</v>
+        <v>0.474709451198578</v>
       </c>
       <c r="H1071" t="n">
         <v>273830</v>
@@ -31486,7 +31486,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.490655779838562</v>
+        <v>0.49065575003624</v>
       </c>
       <c r="H1073" t="n">
         <v>143879</v>
@@ -31515,7 +31515,7 @@
         <v>0.816999971866608</v>
       </c>
       <c r="G1074" t="n">
-        <v>0.501082181930542</v>
+        <v>0.501082241535187</v>
       </c>
       <c r="H1074" t="n">
         <v>419852</v>
@@ -31544,7 +31544,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.469802916049957</v>
+        <v>0.469802886247635</v>
       </c>
       <c r="H1075" t="n">
         <v>576348</v>
@@ -31573,7 +31573,7 @@
         <v>0.732999980449677</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.449563354253769</v>
+        <v>0.449563324451447</v>
       </c>
       <c r="H1076" t="n">
         <v>402235</v>
@@ -31602,7 +31602,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1077" t="n">
-        <v>0.417057454586029</v>
+        <v>0.417057424783707</v>
       </c>
       <c r="H1077" t="n">
         <v>1092990</v>
@@ -31631,7 +31631,7 @@
         <v>0.679000020027161</v>
       </c>
       <c r="G1078" t="n">
-        <v>0.416444152593613</v>
+        <v>0.416444092988968</v>
       </c>
       <c r="H1078" t="n">
         <v>305317</v>
@@ -31660,7 +31660,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.399884462356567</v>
+        <v>0.39988449215889</v>
       </c>
       <c r="H1079" t="n">
         <v>1104968</v>
@@ -31689,7 +31689,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1080" t="n">
-        <v>0.394977927207947</v>
+        <v>0.394977897405624</v>
       </c>
       <c r="H1080" t="n">
         <v>603190</v>
@@ -31718,7 +31718,7 @@
         <v>0.679000020027161</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.416444152593613</v>
+        <v>0.416444092988968</v>
       </c>
       <c r="H1081" t="n">
         <v>566218</v>
@@ -31921,7 +31921,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.496789008378983</v>
+        <v>0.49678897857666</v>
       </c>
       <c r="H1088" t="n">
         <v>488572</v>
@@ -31950,7 +31950,7 @@
         <v>0.816999971866608</v>
       </c>
       <c r="G1089" t="n">
-        <v>0.501082181930542</v>
+        <v>0.501082241535187</v>
       </c>
       <c r="H1089" t="n">
         <v>179250</v>
@@ -32124,7 +32124,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1095" t="n">
-        <v>0.533588171005249</v>
+        <v>0.533588111400604</v>
       </c>
       <c r="H1095" t="n">
         <v>655537</v>
@@ -32153,7 +32153,7 @@
         <v>0.880999982357025</v>
       </c>
       <c r="G1096" t="n">
-        <v>0.540334701538086</v>
+        <v>0.540334641933441</v>
       </c>
       <c r="H1096" t="n">
         <v>135566</v>
@@ -32182,7 +32182,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1097" t="n">
-        <v>0.54340124130249</v>
+        <v>0.543401300907135</v>
       </c>
       <c r="H1097" t="n">
         <v>178955</v>
@@ -32211,7 +32211,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1098" t="n">
-        <v>0.533588171005249</v>
+        <v>0.533588111400604</v>
       </c>
       <c r="H1098" t="n">
         <v>299617</v>
@@ -32298,7 +32298,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.506602108478546</v>
+        <v>0.506602048873901</v>
       </c>
       <c r="H1101" t="n">
         <v>179925</v>
@@ -32327,7 +32327,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1102" t="n">
-        <v>0.504148840904236</v>
+        <v>0.504148781299591</v>
       </c>
       <c r="H1102" t="n">
         <v>84582</v>
@@ -32501,7 +32501,7 @@
         <v>0.830999970436096</v>
       </c>
       <c r="G1108" t="n">
-        <v>0.50966864824295</v>
+        <v>0.509668707847595</v>
       </c>
       <c r="H1108" t="n">
         <v>91813</v>
@@ -32530,7 +32530,7 @@
         <v>0.820999979972839</v>
       </c>
       <c r="G1109" t="n">
-        <v>0.503535449504852</v>
+        <v>0.503535509109497</v>
       </c>
       <c r="H1109" t="n">
         <v>54511</v>
@@ -32559,7 +32559,7 @@
         <v>0.848999977111816</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.520708382129669</v>
+        <v>0.520708501338959</v>
       </c>
       <c r="H1110" t="n">
         <v>181006</v>
@@ -32646,7 +32646,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.491882383823395</v>
+        <v>0.49188244342804</v>
       </c>
       <c r="H1113" t="n">
         <v>111204</v>
@@ -32791,7 +32791,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1118" t="n">
-        <v>0.545854508876801</v>
+        <v>0.545854568481445</v>
       </c>
       <c r="H1118" t="n">
         <v>579211</v>
@@ -32965,7 +32965,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1124" t="n">
-        <v>0.643985688686371</v>
+        <v>0.643985629081726</v>
       </c>
       <c r="H1124" t="n">
         <v>645259</v>
@@ -32994,7 +32994,7 @@
         <v>1.07400000095367</v>
       </c>
       <c r="G1125" t="n">
-        <v>0.658705472946167</v>
+        <v>0.658705353736877</v>
       </c>
       <c r="H1125" t="n">
         <v>626443</v>
@@ -33023,7 +33023,7 @@
         <v>1</v>
       </c>
       <c r="G1126" t="n">
-        <v>0.61331969499588</v>
+        <v>0.613319754600525</v>
       </c>
       <c r="H1126" t="n">
         <v>511212</v>
@@ -33139,7 +33139,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1130" t="n">
-        <v>0.569160640239716</v>
+        <v>0.56916069984436</v>
       </c>
       <c r="H1130" t="n">
         <v>331420</v>
@@ -33168,7 +33168,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G1131" t="n">
-        <v>0.554441034793854</v>
+        <v>0.554441094398499</v>
       </c>
       <c r="H1131" t="n">
         <v>721039</v>
@@ -33429,7 +33429,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1140" t="n">
-        <v>0.527455031871796</v>
+        <v>0.527454972267151</v>
       </c>
       <c r="H1140" t="n">
         <v>121230</v>
@@ -33487,7 +33487,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1142" t="n">
-        <v>0.504148840904236</v>
+        <v>0.504148781299591</v>
       </c>
       <c r="H1142" t="n">
         <v>275625</v>
@@ -33632,7 +33632,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1147" t="n">
-        <v>0.528681576251984</v>
+        <v>0.528681635856628</v>
       </c>
       <c r="H1147" t="n">
         <v>178410</v>
@@ -33690,7 +33690,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1149" t="n">
-        <v>0.522548377513885</v>
+        <v>0.52254843711853</v>
       </c>
       <c r="H1149" t="n">
         <v>155783</v>
@@ -33719,7 +33719,7 @@
         <v>0.859000027179718</v>
       </c>
       <c r="G1150" t="n">
-        <v>0.526841640472412</v>
+        <v>0.526841700077057</v>
       </c>
       <c r="H1150" t="n">
         <v>153721</v>
@@ -33748,7 +33748,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1151" t="n">
-        <v>0.534814774990082</v>
+        <v>0.534814834594727</v>
       </c>
       <c r="H1151" t="n">
         <v>157868</v>
@@ -33806,7 +33806,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.555054366588593</v>
+        <v>0.555054306983948</v>
       </c>
       <c r="H1153" t="n">
         <v>178213</v>
@@ -33835,7 +33835,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G1154" t="n">
-        <v>0.542787969112396</v>
+        <v>0.542787909507751</v>
       </c>
       <c r="H1154" t="n">
         <v>194414</v>
@@ -33864,7 +33864,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1155" t="n">
-        <v>0.53849470615387</v>
+        <v>0.538494765758514</v>
       </c>
       <c r="H1155" t="n">
         <v>65264</v>
@@ -33922,7 +33922,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1157" t="n">
-        <v>0.545854508876801</v>
+        <v>0.545854568481445</v>
       </c>
       <c r="H1157" t="n">
         <v>71533</v>
@@ -33951,7 +33951,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1158" t="n">
-        <v>0.545854508876801</v>
+        <v>0.545854568481445</v>
       </c>
       <c r="H1158" t="n">
         <v>127025</v>
@@ -34038,7 +34038,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G1161" t="n">
-        <v>0.542787969112396</v>
+        <v>0.542787909507751</v>
       </c>
       <c r="H1161" t="n">
         <v>343997</v>
@@ -34154,7 +34154,7 @@
         <v>0.890999972820282</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.546467900276184</v>
+        <v>0.546467840671539</v>
       </c>
       <c r="H1165" t="n">
         <v>169704</v>
@@ -34183,7 +34183,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.564254224300385</v>
+        <v>0.56425416469574</v>
       </c>
       <c r="H1166" t="n">
         <v>336489</v>
@@ -34212,7 +34212,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1167" t="n">
-        <v>0.575293898582458</v>
+        <v>0.575293958187103</v>
       </c>
       <c r="H1167" t="n">
         <v>167438</v>
@@ -34270,7 +34270,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.567320704460144</v>
+        <v>0.567320764064789</v>
       </c>
       <c r="H1169" t="n">
         <v>120442</v>
@@ -34444,7 +34444,7 @@
         <v>0.939000010490417</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.575907289981842</v>
+        <v>0.575907230377197</v>
       </c>
       <c r="H1175" t="n">
         <v>40579</v>
@@ -34473,7 +34473,7 @@
         <v>0.930999994277954</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.571000635623932</v>
+        <v>0.571000695228577</v>
       </c>
       <c r="H1176" t="n">
         <v>76615</v>
@@ -34502,7 +34502,7 @@
         <v>0.962999999523163</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.590626895427704</v>
+        <v>0.590626955032349</v>
       </c>
       <c r="H1177" t="n">
         <v>110900</v>
@@ -34531,7 +34531,7 @@
         <v>0.962999999523163</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.590626895427704</v>
+        <v>0.590626955032349</v>
       </c>
       <c r="H1178" t="n">
         <v>48968</v>
@@ -34618,7 +34618,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.588786959648132</v>
+        <v>0.588786900043488</v>
       </c>
       <c r="H1181" t="n">
         <v>72156</v>
@@ -34647,7 +34647,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.5875603556633</v>
+        <v>0.587560296058655</v>
       </c>
       <c r="H1182" t="n">
         <v>98391</v>
@@ -34676,7 +34676,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.578973770141602</v>
+        <v>0.578973829746246</v>
       </c>
       <c r="H1183" t="n">
         <v>46587</v>
@@ -34705,7 +34705,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.569160640239716</v>
+        <v>0.56916069984436</v>
       </c>
       <c r="H1184" t="n">
         <v>58272</v>
@@ -34792,7 +34792,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.576520562171936</v>
+        <v>0.576520502567291</v>
       </c>
       <c r="H1187" t="n">
         <v>133864</v>
@@ -34821,7 +34821,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.572227358818054</v>
+        <v>0.572227299213409</v>
       </c>
       <c r="H1188" t="n">
         <v>463536</v>
@@ -34879,7 +34879,7 @@
         <v>0.916999995708466</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.562414228916168</v>
+        <v>0.562414169311523</v>
       </c>
       <c r="H1190" t="n">
         <v>129939</v>
@@ -34908,7 +34908,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.547081232070923</v>
+        <v>0.547081172466278</v>
       </c>
       <c r="H1191" t="n">
         <v>73041</v>
@@ -34966,7 +34966,7 @@
         <v>0.939000010490417</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.575907289981842</v>
+        <v>0.575907230377197</v>
       </c>
       <c r="H1193" t="n">
         <v>92209</v>
@@ -34995,7 +34995,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.569160640239716</v>
+        <v>0.56916069984436</v>
       </c>
       <c r="H1194" t="n">
         <v>86844</v>
@@ -35082,7 +35082,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.569160640239716</v>
+        <v>0.56916069984436</v>
       </c>
       <c r="H1197" t="n">
         <v>170059</v>
@@ -35111,7 +35111,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.592466831207275</v>
+        <v>0.59246689081192</v>
       </c>
       <c r="H1198" t="n">
         <v>237851</v>
@@ -35169,7 +35169,7 @@
         <v>0.89300000667572</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.547694504261017</v>
+        <v>0.547694563865662</v>
       </c>
       <c r="H1200" t="n">
         <v>153127</v>
@@ -35227,7 +35227,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.555667638778687</v>
+        <v>0.555667698383331</v>
       </c>
       <c r="H1202" t="n">
         <v>97223</v>
@@ -35285,7 +35285,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G1204" t="n">
-        <v>0.555054366588593</v>
+        <v>0.555054306983948</v>
       </c>
       <c r="H1204" t="n">
         <v>55490</v>
@@ -35401,7 +35401,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.572227358818054</v>
+        <v>0.572227299213409</v>
       </c>
       <c r="H1208" t="n">
         <v>45202</v>
@@ -35459,7 +35459,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.576520562171936</v>
+        <v>0.576520502567291</v>
       </c>
       <c r="H1210" t="n">
         <v>31625</v>
@@ -35517,7 +35517,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1212" t="n">
-        <v>0.576520562171936</v>
+        <v>0.576520502567291</v>
       </c>
       <c r="H1212" t="n">
         <v>65395</v>
@@ -35546,7 +35546,7 @@
         <v>0.958999991416931</v>
       </c>
       <c r="G1213" t="n">
-        <v>0.588173627853394</v>
+        <v>0.588173687458038</v>
       </c>
       <c r="H1213" t="n">
         <v>77828</v>
@@ -35662,7 +35662,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.576520562171936</v>
+        <v>0.576520502567291</v>
       </c>
       <c r="H1217" t="n">
         <v>57725</v>
@@ -35894,7 +35894,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.576520562171936</v>
+        <v>0.576520502567291</v>
       </c>
       <c r="H1225" t="n">
         <v>611268</v>
@@ -35923,7 +35923,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.565480828285217</v>
+        <v>0.565480768680573</v>
       </c>
       <c r="H1226" t="n">
         <v>111837</v>
@@ -36039,7 +36039,7 @@
         <v>0.916999995708466</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.562414228916168</v>
+        <v>0.562414169311523</v>
       </c>
       <c r="H1230" t="n">
         <v>70429</v>
@@ -36068,7 +36068,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.572227358818054</v>
+        <v>0.572227299213409</v>
       </c>
       <c r="H1231" t="n">
         <v>77919</v>
@@ -36126,7 +36126,7 @@
         <v>0.967000007629395</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.593080222606659</v>
+        <v>0.593080163002014</v>
       </c>
       <c r="H1233" t="n">
         <v>53370</v>
@@ -36155,7 +36155,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.588786959648132</v>
+        <v>0.588786900043488</v>
       </c>
       <c r="H1234" t="n">
         <v>47192</v>
@@ -36184,7 +36184,7 @@
         <v>1.01600003242493</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.623132884502411</v>
+        <v>0.623132824897766</v>
       </c>
       <c r="H1235" t="n">
         <v>290003</v>
@@ -36213,7 +36213,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.619452893733978</v>
+        <v>0.619452953338623</v>
       </c>
       <c r="H1236" t="n">
         <v>126464</v>
@@ -36300,7 +36300,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.648892223834991</v>
+        <v>0.648892283439636</v>
       </c>
       <c r="H1239" t="n">
         <v>338804</v>
@@ -36358,7 +36358,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1241" t="n">
         <v>292213</v>
@@ -36387,7 +36387,7 @@
         <v>1.15799999237061</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.710224211215973</v>
+        <v>0.710224270820618</v>
       </c>
       <c r="H1242" t="n">
         <v>253980</v>
@@ -36416,7 +36416,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1243" t="n">
-        <v>0.711450815200806</v>
+        <v>0.71145087480545</v>
       </c>
       <c r="H1243" t="n">
         <v>241318</v>
@@ -36445,7 +36445,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.697957873344421</v>
+        <v>0.697957813739777</v>
       </c>
       <c r="H1244" t="n">
         <v>343735</v>
@@ -36474,7 +36474,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G1245" t="n">
-        <v>0.708997666835785</v>
+        <v>0.70899760723114</v>
       </c>
       <c r="H1245" t="n">
         <v>198309</v>
@@ -36532,7 +36532,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1247" t="n">
-        <v>0.788729131221771</v>
+        <v>0.788729190826416</v>
       </c>
       <c r="H1247" t="n">
         <v>694692</v>
@@ -36561,7 +36561,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.775236248970032</v>
+        <v>0.775236189365387</v>
       </c>
       <c r="H1248" t="n">
         <v>177276</v>
@@ -36677,7 +36677,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1252" t="n">
-        <v>0.754383206367493</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H1252" t="n">
         <v>109391</v>
@@ -36706,7 +36706,7 @@
         <v>1.25</v>
       </c>
       <c r="G1253" t="n">
-        <v>0.766649663448334</v>
+        <v>0.766649723052979</v>
       </c>
       <c r="H1253" t="n">
         <v>88845</v>
@@ -36880,7 +36880,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.743343472480774</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H1259" t="n">
         <v>192421</v>
@@ -36909,7 +36909,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.739663660526276</v>
+        <v>0.739663541316986</v>
       </c>
       <c r="H1260" t="n">
         <v>143028</v>
@@ -36938,7 +36938,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1261" t="n">
         <v>99221</v>
@@ -36967,7 +36967,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1262" t="n">
-        <v>0.759289920330048</v>
+        <v>0.759289860725403</v>
       </c>
       <c r="H1262" t="n">
         <v>121252</v>
@@ -37054,7 +37054,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.712677538394928</v>
+        <v>0.712677478790283</v>
       </c>
       <c r="H1265" t="n">
         <v>252252</v>
@@ -37083,7 +37083,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.723717212677002</v>
+        <v>0.723717272281647</v>
       </c>
       <c r="H1266" t="n">
         <v>113541</v>
@@ -37170,7 +37170,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.723717212677002</v>
+        <v>0.723717272281647</v>
       </c>
       <c r="H1269" t="n">
         <v>185115</v>
@@ -37199,7 +37199,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1270" t="n">
-        <v>0.724943995475769</v>
+        <v>0.724943935871124</v>
       </c>
       <c r="H1270" t="n">
         <v>100068</v>
@@ -37228,7 +37228,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.734757006168365</v>
+        <v>0.73475706577301</v>
       </c>
       <c r="H1271" t="n">
         <v>87758</v>
@@ -37257,7 +37257,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1272" t="n">
-        <v>0.743343472480774</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H1272" t="n">
         <v>66956</v>
@@ -37315,7 +37315,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.761743068695068</v>
+        <v>0.761743128299713</v>
       </c>
       <c r="H1274" t="n">
         <v>257120</v>
@@ -37402,7 +37402,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1277" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1277" t="n">
         <v>128905</v>
@@ -37460,7 +37460,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1279" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1279" t="n">
         <v>104631</v>
@@ -37518,7 +37518,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1281" t="n">
-        <v>0.720037341117859</v>
+        <v>0.720037400722504</v>
       </c>
       <c r="H1281" t="n">
         <v>71454</v>
@@ -37634,7 +37634,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1285" t="n">
-        <v>0.723717212677002</v>
+        <v>0.723717272281647</v>
       </c>
       <c r="H1285" t="n">
         <v>189558</v>
@@ -37692,7 +37692,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1287" t="n">
-        <v>0.712677538394928</v>
+        <v>0.712677478790283</v>
       </c>
       <c r="H1287" t="n">
         <v>89003</v>
@@ -37721,7 +37721,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G1288" t="n">
-        <v>0.70654433965683</v>
+        <v>0.706544280052185</v>
       </c>
       <c r="H1288" t="n">
         <v>55804</v>
@@ -37808,7 +37808,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G1291" t="n">
-        <v>0.688144683837891</v>
+        <v>0.688144743442535</v>
       </c>
       <c r="H1291" t="n">
         <v>82352</v>
@@ -37837,7 +37837,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.69059807062149</v>
+        <v>0.690598011016846</v>
       </c>
       <c r="H1292" t="n">
         <v>43018</v>
@@ -37866,7 +37866,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1293" t="n">
-        <v>0.693051338195801</v>
+        <v>0.693051278591156</v>
       </c>
       <c r="H1293" t="n">
         <v>114472</v>
@@ -37895,7 +37895,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.708997666835785</v>
+        <v>0.70899760723114</v>
       </c>
       <c r="H1294" t="n">
         <v>110214</v>
@@ -37924,7 +37924,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.720037341117859</v>
+        <v>0.720037400722504</v>
       </c>
       <c r="H1295" t="n">
         <v>130325</v>
@@ -38040,7 +38040,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1299" t="n">
-        <v>0.743343472480774</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H1299" t="n">
         <v>114513</v>
@@ -38098,7 +38098,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1301" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1301" t="n">
         <v>82491</v>
@@ -38185,7 +38185,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1304" t="n">
-        <v>0.759289920330048</v>
+        <v>0.759289860725403</v>
       </c>
       <c r="H1304" t="n">
         <v>121379</v>
@@ -38243,7 +38243,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1306" t="n">
-        <v>0.762969791889191</v>
+        <v>0.762969672679901</v>
       </c>
       <c r="H1306" t="n">
         <v>43432</v>
@@ -38330,7 +38330,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1309" t="n">
         <v>791184</v>
@@ -38475,7 +38475,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1314" t="n">
-        <v>0.824301660060883</v>
+        <v>0.824301719665527</v>
       </c>
       <c r="H1314" t="n">
         <v>64998</v>
@@ -38533,7 +38533,7 @@
         <v>1.31400001049042</v>
       </c>
       <c r="G1316" t="n">
-        <v>0.805902183055878</v>
+        <v>0.805902123451233</v>
       </c>
       <c r="H1316" t="n">
         <v>74558</v>
@@ -38591,7 +38591,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1318" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1318" t="n">
         <v>326078</v>
@@ -38649,7 +38649,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1320" t="n">
-        <v>0.792409121990204</v>
+        <v>0.792409062385559</v>
       </c>
       <c r="H1320" t="n">
         <v>90832</v>
@@ -38707,7 +38707,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1322" t="n">
-        <v>0.835341453552246</v>
+        <v>0.835341513156891</v>
       </c>
       <c r="H1322" t="n">
         <v>275179</v>
@@ -38736,7 +38736,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G1323" t="n">
-        <v>0.841474711894989</v>
+        <v>0.841474652290344</v>
       </c>
       <c r="H1323" t="n">
         <v>216478</v>
@@ -38823,7 +38823,7 @@
         <v>1.38399994373322</v>
       </c>
       <c r="G1326" t="n">
-        <v>0.848834455013275</v>
+        <v>0.84883451461792</v>
       </c>
       <c r="H1326" t="n">
         <v>212647</v>
@@ -38881,7 +38881,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1328" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H1328" t="n">
         <v>87547</v>
@@ -38968,7 +38968,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1331" t="n">
-        <v>0.837794780731201</v>
+        <v>0.837794840335846</v>
       </c>
       <c r="H1331" t="n">
         <v>112011</v>
@@ -39055,7 +39055,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1334" t="n">
-        <v>0.85128778219223</v>
+        <v>0.851287841796875</v>
       </c>
       <c r="H1334" t="n">
         <v>98128</v>
@@ -39084,7 +39084,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1335" t="n">
-        <v>0.834114909172058</v>
+        <v>0.834114849567413</v>
       </c>
       <c r="H1335" t="n">
         <v>166556</v>
@@ -39113,7 +39113,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1336" t="n">
-        <v>0.84638124704361</v>
+        <v>0.846381187438965</v>
       </c>
       <c r="H1336" t="n">
         <v>167091</v>
@@ -39258,7 +39258,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1341" t="n">
-        <v>0.834114909172058</v>
+        <v>0.834114849567413</v>
       </c>
       <c r="H1341" t="n">
         <v>71978</v>
@@ -39287,7 +39287,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G1342" t="n">
-        <v>0.841474711894989</v>
+        <v>0.841474652290344</v>
       </c>
       <c r="H1342" t="n">
         <v>68917</v>
@@ -39316,7 +39316,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G1343" t="n">
-        <v>0.842701256275177</v>
+        <v>0.842701315879822</v>
       </c>
       <c r="H1343" t="n">
         <v>92663</v>
@@ -39345,7 +39345,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G1344" t="n">
-        <v>0.842701256275177</v>
+        <v>0.842701315879822</v>
       </c>
       <c r="H1344" t="n">
         <v>50622</v>
@@ -39490,7 +39490,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G1349" t="n">
-        <v>0.853741049766541</v>
+        <v>0.853741109371185</v>
       </c>
       <c r="H1349" t="n">
         <v>1336786</v>
@@ -39548,7 +39548,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1351" t="n">
-        <v>0.877047181129456</v>
+        <v>0.8770472407341</v>
       </c>
       <c r="H1351" t="n">
         <v>713545</v>
@@ -39577,7 +39577,7 @@
         <v>1.43799996376038</v>
       </c>
       <c r="G1352" t="n">
-        <v>0.881953775882721</v>
+        <v>0.881953716278076</v>
       </c>
       <c r="H1352" t="n">
         <v>370355</v>
@@ -39664,7 +39664,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1355" t="n">
-        <v>0.864780843257904</v>
+        <v>0.864780783653259</v>
       </c>
       <c r="H1355" t="n">
         <v>325590</v>
@@ -39693,7 +39693,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G1356" t="n">
-        <v>0.880727171897888</v>
+        <v>0.880727112293243</v>
       </c>
       <c r="H1356" t="n">
         <v>136088</v>
@@ -39780,7 +39780,7 @@
         <v>1.44599997997284</v>
       </c>
       <c r="G1359" t="n">
-        <v>0.886860251426697</v>
+        <v>0.886860311031342</v>
       </c>
       <c r="H1359" t="n">
         <v>147778</v>
@@ -39867,7 +39867,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1362" t="n">
-        <v>0.85128778219223</v>
+        <v>0.851287841796875</v>
       </c>
       <c r="H1362" t="n">
         <v>179758</v>
@@ -39896,7 +39896,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1363" t="n">
-        <v>0.84638124704361</v>
+        <v>0.846381187438965</v>
       </c>
       <c r="H1363" t="n">
         <v>171352</v>
@@ -39925,7 +39925,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1364" t="n">
-        <v>0.863554120063782</v>
+        <v>0.863554179668427</v>
       </c>
       <c r="H1364" t="n">
         <v>135359</v>
@@ -39954,7 +39954,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1365" t="n">
-        <v>0.863554120063782</v>
+        <v>0.863554179668427</v>
       </c>
       <c r="H1365" t="n">
         <v>193569</v>
@@ -40012,7 +40012,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1367" t="n">
-        <v>0.835341453552246</v>
+        <v>0.835341513156891</v>
       </c>
       <c r="H1367" t="n">
         <v>176992</v>
@@ -40041,7 +40041,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1368" t="n">
-        <v>0.834114909172058</v>
+        <v>0.834114849567413</v>
       </c>
       <c r="H1368" t="n">
         <v>97652</v>
@@ -40070,7 +40070,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1369" t="n">
-        <v>0.837794780731201</v>
+        <v>0.837794840335846</v>
       </c>
       <c r="H1369" t="n">
         <v>104647</v>
@@ -40186,7 +40186,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1373" t="n">
-        <v>0.834114909172058</v>
+        <v>0.834114849567413</v>
       </c>
       <c r="H1373" t="n">
         <v>89066</v>
@@ -40244,7 +40244,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1375" t="n">
-        <v>0.863554120063782</v>
+        <v>0.863554179668427</v>
       </c>
       <c r="H1375" t="n">
         <v>321942</v>
@@ -40360,7 +40360,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G1379" t="n">
-        <v>0.912619769573212</v>
+        <v>0.912619829177856</v>
       </c>
       <c r="H1379" t="n">
         <v>464389</v>
@@ -40389,7 +40389,7 @@
         <v>1.5</v>
       </c>
       <c r="G1380" t="n">
-        <v>0.919979572296143</v>
+        <v>0.919979512691498</v>
       </c>
       <c r="H1380" t="n">
         <v>1413263</v>
@@ -40418,7 +40418,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G1381" t="n">
-        <v>0.940832436084747</v>
+        <v>0.940832495689392</v>
       </c>
       <c r="H1381" t="n">
         <v>367278</v>
@@ -40476,7 +40476,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G1383" t="n">
-        <v>0.915073096752167</v>
+        <v>0.915073037147522</v>
       </c>
       <c r="H1383" t="n">
         <v>263618</v>
@@ -40534,7 +40534,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1385" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H1385" t="n">
         <v>939739</v>
@@ -40563,7 +40563,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G1386" t="n">
-        <v>0.945739090442657</v>
+        <v>0.945739030838013</v>
       </c>
       <c r="H1386" t="n">
         <v>326723</v>
@@ -40592,7 +40592,7 @@
         <v>1.5</v>
       </c>
       <c r="G1387" t="n">
-        <v>0.919979572296143</v>
+        <v>0.919979512691498</v>
       </c>
       <c r="H1387" t="n">
         <v>365772</v>
@@ -40650,7 +40650,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G1389" t="n">
-        <v>0.921206176280975</v>
+        <v>0.92120623588562</v>
       </c>
       <c r="H1389" t="n">
         <v>395299</v>
@@ -40737,7 +40737,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G1392" t="n">
-        <v>0.884407103061676</v>
+        <v>0.884407043457031</v>
       </c>
       <c r="H1392" t="n">
         <v>141898</v>
@@ -40766,7 +40766,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G1393" t="n">
-        <v>0.884407103061676</v>
+        <v>0.884407043457031</v>
       </c>
       <c r="H1393" t="n">
         <v>64747</v>
@@ -40853,7 +40853,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1396" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H1396" t="n">
         <v>305258</v>
@@ -40882,7 +40882,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1397" t="n">
-        <v>0.835341453552246</v>
+        <v>0.835341513156891</v>
       </c>
       <c r="H1397" t="n">
         <v>217994</v>
@@ -41027,7 +41027,7 @@
         <v>1.27600002288818</v>
       </c>
       <c r="G1402" t="n">
-        <v>0.782596051692963</v>
+        <v>0.782595992088318</v>
       </c>
       <c r="H1402" t="n">
         <v>475228</v>
@@ -41201,7 +41201,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1408" t="n">
-        <v>0.754383206367493</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H1408" t="n">
         <v>366294</v>
@@ -41230,7 +41230,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1409" t="n">
-        <v>0.723717212677002</v>
+        <v>0.723717272281647</v>
       </c>
       <c r="H1409" t="n">
         <v>220777</v>
@@ -41433,7 +41433,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.852514445781708</v>
+        <v>0.852514386177063</v>
       </c>
       <c r="H1416" t="n">
         <v>491957</v>
@@ -41520,7 +41520,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1419" t="n">
-        <v>0.835341453552246</v>
+        <v>0.835341513156891</v>
       </c>
       <c r="H1419" t="n">
         <v>214498</v>
@@ -41549,7 +41549,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1420" t="n">
-        <v>0.84638124704361</v>
+        <v>0.846381187438965</v>
       </c>
       <c r="H1420" t="n">
         <v>163849</v>
@@ -41578,7 +41578,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1421" t="n">
-        <v>0.84638124704361</v>
+        <v>0.846381187438965</v>
       </c>
       <c r="H1421" t="n">
         <v>206853</v>
@@ -41636,7 +41636,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1423" t="n">
-        <v>0.85128778219223</v>
+        <v>0.851287841796875</v>
       </c>
       <c r="H1423" t="n">
         <v>61204</v>
@@ -41694,7 +41694,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G1425" t="n">
-        <v>0.857421040534973</v>
+        <v>0.857420980930328</v>
       </c>
       <c r="H1425" t="n">
         <v>391972</v>
@@ -41752,7 +41752,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1427" t="n">
-        <v>0.864780843257904</v>
+        <v>0.864780783653259</v>
       </c>
       <c r="H1427" t="n">
         <v>309661</v>
@@ -41781,7 +41781,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G1428" t="n">
-        <v>0.899126708507538</v>
+        <v>0.899126648902893</v>
       </c>
       <c r="H1428" t="n">
         <v>825243</v>
@@ -41868,7 +41868,7 @@
         <v>1.43400001525879</v>
       </c>
       <c r="G1431" t="n">
-        <v>0.879500567913055</v>
+        <v>0.879500508308411</v>
       </c>
       <c r="H1431" t="n">
         <v>165321</v>
@@ -41897,7 +41897,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G1432" t="n">
-        <v>0.853741049766541</v>
+        <v>0.853741109371185</v>
       </c>
       <c r="H1432" t="n">
         <v>367934</v>
@@ -41984,7 +41984,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G1435" t="n">
-        <v>0.842701256275177</v>
+        <v>0.842701315879822</v>
       </c>
       <c r="H1435" t="n">
         <v>133388</v>
@@ -42071,7 +42071,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1438" t="n">
-        <v>0.852514445781708</v>
+        <v>0.852514386177063</v>
       </c>
       <c r="H1438" t="n">
         <v>170931</v>
@@ -42158,7 +42158,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G1441" t="n">
-        <v>0.857421040534973</v>
+        <v>0.857420980930328</v>
       </c>
       <c r="H1441" t="n">
         <v>224445</v>
@@ -42245,7 +42245,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1444" t="n">
-        <v>0.852514445781708</v>
+        <v>0.852514386177063</v>
       </c>
       <c r="H1444" t="n">
         <v>122371</v>
@@ -42303,7 +42303,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1446" t="n">
-        <v>0.837794780731201</v>
+        <v>0.837794840335846</v>
       </c>
       <c r="H1446" t="n">
         <v>129072</v>
@@ -42332,7 +42332,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G1447" t="n">
-        <v>0.823075115680695</v>
+        <v>0.82307505607605</v>
       </c>
       <c r="H1447" t="n">
         <v>145648</v>
@@ -42448,7 +42448,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G1451" t="n">
-        <v>0.823075115680695</v>
+        <v>0.82307505607605</v>
       </c>
       <c r="H1451" t="n">
         <v>132905</v>
@@ -42477,7 +42477,7 @@
         <v>1.31400001049042</v>
       </c>
       <c r="G1452" t="n">
-        <v>0.805902183055878</v>
+        <v>0.805902123451233</v>
       </c>
       <c r="H1452" t="n">
         <v>244151</v>
@@ -42535,7 +42535,7 @@
         <v>1.27600002288818</v>
       </c>
       <c r="G1454" t="n">
-        <v>0.782596051692963</v>
+        <v>0.782595992088318</v>
       </c>
       <c r="H1454" t="n">
         <v>337653</v>
@@ -42564,7 +42564,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1455" t="n">
-        <v>0.772782862186432</v>
+        <v>0.772782921791077</v>
       </c>
       <c r="H1455" t="n">
         <v>167953</v>
@@ -42593,7 +42593,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1456" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1456" t="n">
         <v>154869</v>
@@ -42622,7 +42622,7 @@
         <v>1.31400001049042</v>
       </c>
       <c r="G1457" t="n">
-        <v>0.805902183055878</v>
+        <v>0.805902123451233</v>
       </c>
       <c r="H1457" t="n">
         <v>100821</v>
@@ -42709,7 +42709,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G1460" t="n">
-        <v>0.799768924713135</v>
+        <v>0.79976898431778</v>
       </c>
       <c r="H1460" t="n">
         <v>158559</v>
@@ -42825,7 +42825,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1464" t="n">
-        <v>0.788729131221771</v>
+        <v>0.788729190826416</v>
       </c>
       <c r="H1464" t="n">
         <v>91651</v>
@@ -42854,7 +42854,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1465" t="n">
-        <v>0.792409121990204</v>
+        <v>0.792409062385559</v>
       </c>
       <c r="H1465" t="n">
         <v>190594</v>
@@ -42883,7 +42883,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1466" t="n">
-        <v>0.78136932849884</v>
+        <v>0.781369388103485</v>
       </c>
       <c r="H1466" t="n">
         <v>128264</v>
@@ -42941,7 +42941,7 @@
         <v>1.30200004577637</v>
       </c>
       <c r="G1468" t="n">
-        <v>0.798542380332947</v>
+        <v>0.798542320728302</v>
       </c>
       <c r="H1468" t="n">
         <v>38231</v>
@@ -42970,7 +42970,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1469" t="n">
-        <v>0.788729131221771</v>
+        <v>0.788729190826416</v>
       </c>
       <c r="H1469" t="n">
         <v>41589</v>
@@ -42999,7 +42999,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1470" t="n">
-        <v>0.809582114219666</v>
+        <v>0.809582054615021</v>
       </c>
       <c r="H1470" t="n">
         <v>109019</v>
@@ -43086,7 +43086,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1473" t="n">
-        <v>0.834114909172058</v>
+        <v>0.834114849567413</v>
       </c>
       <c r="H1473" t="n">
         <v>128473</v>
@@ -43115,7 +43115,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1474" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H1474" t="n">
         <v>123829</v>
@@ -43173,7 +43173,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1476" t="n">
-        <v>0.824301660060883</v>
+        <v>0.824301719665527</v>
       </c>
       <c r="H1476" t="n">
         <v>93692</v>
@@ -43202,7 +43202,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1477" t="n">
-        <v>0.85619443655014</v>
+        <v>0.856194376945496</v>
       </c>
       <c r="H1477" t="n">
         <v>332826</v>
@@ -43231,7 +43231,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1478" t="n">
-        <v>0.85128778219223</v>
+        <v>0.851287841796875</v>
       </c>
       <c r="H1478" t="n">
         <v>1035445</v>
@@ -43260,7 +43260,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1479" t="n">
-        <v>0.883180379867554</v>
+        <v>0.883180439472198</v>
       </c>
       <c r="H1479" t="n">
         <v>900272</v>
@@ -43289,7 +43289,7 @@
         <v>1.44799995422363</v>
       </c>
       <c r="G1480" t="n">
-        <v>0.888086974620819</v>
+        <v>0.888086915016174</v>
       </c>
       <c r="H1480" t="n">
         <v>440724</v>
@@ -43347,7 +43347,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1482" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H1482" t="n">
         <v>185548</v>
@@ -43376,7 +43376,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1483" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H1483" t="n">
         <v>140243</v>
@@ -43405,7 +43405,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1484" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H1484" t="n">
         <v>295922</v>
@@ -43463,7 +43463,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1486" t="n">
-        <v>0.824301660060883</v>
+        <v>0.824301719665527</v>
       </c>
       <c r="H1486" t="n">
         <v>109288</v>
@@ -43550,7 +43550,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1489" t="n">
-        <v>0.824301660060883</v>
+        <v>0.824301719665527</v>
       </c>
       <c r="H1489" t="n">
         <v>73053</v>
@@ -43608,7 +43608,7 @@
         <v>1.31400001049042</v>
       </c>
       <c r="G1491" t="n">
-        <v>0.805902183055878</v>
+        <v>0.805902123451233</v>
       </c>
       <c r="H1491" t="n">
         <v>171192</v>
@@ -43666,7 +43666,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1493" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1493" t="n">
         <v>257678</v>
@@ -43695,7 +43695,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1494" t="n">
-        <v>0.824301660060883</v>
+        <v>0.824301719665527</v>
       </c>
       <c r="H1494" t="n">
         <v>265076</v>
@@ -43724,7 +43724,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G1495" t="n">
-        <v>0.823075115680695</v>
+        <v>0.82307505607605</v>
       </c>
       <c r="H1495" t="n">
         <v>151385</v>
@@ -43811,7 +43811,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1498" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1498" t="n">
         <v>352664</v>
@@ -43840,7 +43840,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1499" t="n">
-        <v>0.809582114219666</v>
+        <v>0.809582054615021</v>
       </c>
       <c r="H1499" t="n">
         <v>101101</v>
@@ -43869,7 +43869,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G1500" t="n">
-        <v>0.799768924713135</v>
+        <v>0.79976898431778</v>
       </c>
       <c r="H1500" t="n">
         <v>70839</v>
@@ -43898,7 +43898,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1501" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1501" t="n">
         <v>164805</v>
@@ -43927,7 +43927,7 @@
         <v>1.2940000295639</v>
       </c>
       <c r="G1502" t="n">
-        <v>0.793635725975037</v>
+        <v>0.793635785579681</v>
       </c>
       <c r="H1502" t="n">
         <v>60756</v>
@@ -44014,7 +44014,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1505" t="n">
-        <v>0.735983729362488</v>
+        <v>0.735983669757843</v>
       </c>
       <c r="H1505" t="n">
         <v>147647</v>
@@ -44043,7 +44043,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1506" t="n">
-        <v>0.743343472480774</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H1506" t="n">
         <v>53247</v>
@@ -44072,7 +44072,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G1507" t="n">
-        <v>0.733530402183533</v>
+        <v>0.733530342578888</v>
       </c>
       <c r="H1507" t="n">
         <v>126855</v>
@@ -44188,7 +44188,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1511" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1511" t="n">
         <v>77419</v>
@@ -44217,7 +44217,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1512" t="n">
-        <v>0.743343472480774</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H1512" t="n">
         <v>124927</v>
@@ -44246,7 +44246,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1513" t="n">
-        <v>0.743343472480774</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H1513" t="n">
         <v>67036</v>
@@ -44275,7 +44275,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1514" t="n">
-        <v>0.735983729362488</v>
+        <v>0.735983669757843</v>
       </c>
       <c r="H1514" t="n">
         <v>158378</v>
@@ -44333,7 +44333,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1516" t="n">
-        <v>0.735983729362488</v>
+        <v>0.735983669757843</v>
       </c>
       <c r="H1516" t="n">
         <v>141495</v>
@@ -44391,7 +44391,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G1518" t="n">
-        <v>0.731077075004578</v>
+        <v>0.731077134609222</v>
       </c>
       <c r="H1518" t="n">
         <v>149431</v>
@@ -44478,7 +44478,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G1521" t="n">
-        <v>0.731077075004578</v>
+        <v>0.731077134609222</v>
       </c>
       <c r="H1521" t="n">
         <v>202473</v>
@@ -44507,7 +44507,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1522" t="n">
-        <v>0.724943995475769</v>
+        <v>0.724943935871124</v>
       </c>
       <c r="H1522" t="n">
         <v>49440</v>
@@ -44565,7 +44565,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1524" t="n">
-        <v>0.723717212677002</v>
+        <v>0.723717272281647</v>
       </c>
       <c r="H1524" t="n">
         <v>102045</v>
@@ -44594,7 +44594,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1525" t="n">
-        <v>0.723717212677002</v>
+        <v>0.723717272281647</v>
       </c>
       <c r="H1525" t="n">
         <v>104761</v>
@@ -44623,7 +44623,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1526" t="n">
-        <v>0.724943995475769</v>
+        <v>0.724943935871124</v>
       </c>
       <c r="H1526" t="n">
         <v>112221</v>
@@ -44797,7 +44797,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1532" t="n">
-        <v>0.78136932849884</v>
+        <v>0.781369388103485</v>
       </c>
       <c r="H1532" t="n">
         <v>299326</v>
@@ -44913,7 +44913,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1536" t="n">
-        <v>0.788729131221771</v>
+        <v>0.788729190826416</v>
       </c>
       <c r="H1536" t="n">
         <v>27795</v>
@@ -44942,7 +44942,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1537" t="n">
-        <v>0.772782862186432</v>
+        <v>0.772782921791077</v>
       </c>
       <c r="H1537" t="n">
         <v>36607</v>
@@ -44971,7 +44971,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1538" t="n">
-        <v>0.771556258201599</v>
+        <v>0.771556198596954</v>
       </c>
       <c r="H1538" t="n">
         <v>69625</v>
@@ -45000,7 +45000,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1539" t="n">
-        <v>0.762969791889191</v>
+        <v>0.762969672679901</v>
       </c>
       <c r="H1539" t="n">
         <v>100515</v>
@@ -45029,7 +45029,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1540" t="n">
-        <v>0.775236248970032</v>
+        <v>0.775236189365387</v>
       </c>
       <c r="H1540" t="n">
         <v>42391</v>
@@ -45087,7 +45087,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G1542" t="n">
-        <v>0.731077075004578</v>
+        <v>0.731077134609222</v>
       </c>
       <c r="H1542" t="n">
         <v>150136</v>
@@ -45116,7 +45116,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1543" t="n">
-        <v>0.729850471019745</v>
+        <v>0.72985053062439</v>
       </c>
       <c r="H1543" t="n">
         <v>155144</v>
@@ -45145,7 +45145,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1544" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1544" t="n">
         <v>23434</v>
@@ -45261,7 +45261,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1548" t="n">
-        <v>0.735983729362488</v>
+        <v>0.735983669757843</v>
       </c>
       <c r="H1548" t="n">
         <v>66394</v>
@@ -45290,7 +45290,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1549" t="n">
-        <v>0.735983729362488</v>
+        <v>0.735983669757843</v>
       </c>
       <c r="H1549" t="n">
         <v>85697</v>
@@ -45319,7 +45319,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1550" t="n">
-        <v>0.754383206367493</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H1550" t="n">
         <v>123629</v>
@@ -45406,7 +45406,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G1553" t="n">
-        <v>0.734757006168365</v>
+        <v>0.73475706577301</v>
       </c>
       <c r="H1553" t="n">
         <v>104901</v>
@@ -45435,7 +45435,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1554" t="n">
-        <v>0.739663660526276</v>
+        <v>0.739663541316986</v>
       </c>
       <c r="H1554" t="n">
         <v>60612</v>
@@ -45522,7 +45522,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1557" t="n">
-        <v>0.711450815200806</v>
+        <v>0.71145087480545</v>
       </c>
       <c r="H1557" t="n">
         <v>96916</v>
@@ -45551,7 +45551,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1558" t="n">
-        <v>0.720037341117859</v>
+        <v>0.720037400722504</v>
       </c>
       <c r="H1558" t="n">
         <v>49443</v>
@@ -45638,7 +45638,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1561" t="n">
-        <v>0.712677538394928</v>
+        <v>0.712677478790283</v>
       </c>
       <c r="H1561" t="n">
         <v>157256</v>
@@ -45696,7 +45696,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G1563" t="n">
-        <v>0.696731209754944</v>
+        <v>0.696731269359589</v>
       </c>
       <c r="H1563" t="n">
         <v>80261</v>
@@ -45725,7 +45725,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1564" t="n">
-        <v>0.705317735671997</v>
+        <v>0.705317676067352</v>
       </c>
       <c r="H1564" t="n">
         <v>161119</v>
@@ -45812,7 +45812,7 @@
         <v>1.12399995326996</v>
       </c>
       <c r="G1567" t="n">
-        <v>0.689371407032013</v>
+        <v>0.689371347427368</v>
       </c>
       <c r="H1567" t="n">
         <v>302584</v>
@@ -45841,7 +45841,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1568" t="n">
-        <v>0.631719350814819</v>
+        <v>0.631719291210175</v>
       </c>
       <c r="H1568" t="n">
         <v>334873</v>
@@ -45928,7 +45928,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1571" t="n">
-        <v>0.51764190196991</v>
+        <v>0.517641842365265</v>
       </c>
       <c r="H1571" t="n">
         <v>472172</v>
@@ -45957,7 +45957,7 @@
         <v>0.788999974727631</v>
       </c>
       <c r="G1572" t="n">
-        <v>0.483909219503403</v>
+        <v>0.483909249305725</v>
       </c>
       <c r="H1572" t="n">
         <v>431253</v>
@@ -45986,7 +45986,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1573" t="n">
-        <v>0.480842649936676</v>
+        <v>0.480842679738998</v>
       </c>
       <c r="H1573" t="n">
         <v>174707</v>
@@ -46044,7 +46044,7 @@
         <v>0.802999973297119</v>
       </c>
       <c r="G1575" t="n">
-        <v>0.492495775222778</v>
+        <v>0.492495715618134</v>
       </c>
       <c r="H1575" t="n">
         <v>323492</v>
@@ -46102,7 +46102,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1577" t="n">
-        <v>0.504148840904236</v>
+        <v>0.504148781299591</v>
       </c>
       <c r="H1577" t="n">
         <v>133955</v>
@@ -46131,7 +46131,7 @@
         <v>0.814999997615814</v>
       </c>
       <c r="G1578" t="n">
-        <v>0.499855577945709</v>
+        <v>0.499855548143387</v>
       </c>
       <c r="H1578" t="n">
         <v>88927</v>
@@ -46160,7 +46160,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1579" t="n">
-        <v>0.53849470615387</v>
+        <v>0.538494765758514</v>
       </c>
       <c r="H1579" t="n">
         <v>227555</v>
@@ -46247,7 +46247,7 @@
         <v>0.897000014781952</v>
       </c>
       <c r="G1582" t="n">
-        <v>0.550147771835327</v>
+        <v>0.550147831439972</v>
       </c>
       <c r="H1582" t="n">
         <v>225480</v>
@@ -46363,7 +46363,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1586" t="n">
-        <v>0.534814774990082</v>
+        <v>0.534814834594727</v>
       </c>
       <c r="H1586" t="n">
         <v>186678</v>
@@ -46392,7 +46392,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G1587" t="n">
-        <v>0.542787969112396</v>
+        <v>0.542787909507751</v>
       </c>
       <c r="H1587" t="n">
         <v>140994</v>
@@ -46421,7 +46421,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G1588" t="n">
-        <v>0.565480828285217</v>
+        <v>0.565480768680573</v>
       </c>
       <c r="H1588" t="n">
         <v>228632</v>
@@ -46450,7 +46450,7 @@
         <v>0.890999972820282</v>
       </c>
       <c r="G1589" t="n">
-        <v>0.546467900276184</v>
+        <v>0.546467840671539</v>
       </c>
       <c r="H1589" t="n">
         <v>278270</v>
@@ -46479,7 +46479,7 @@
         <v>0.866999983787537</v>
       </c>
       <c r="G1590" t="n">
-        <v>0.531748175621033</v>
+        <v>0.531748235225677</v>
       </c>
       <c r="H1590" t="n">
         <v>167752</v>
@@ -46653,7 +46653,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1596" t="n">
-        <v>0.510282039642334</v>
+        <v>0.510281980037689</v>
       </c>
       <c r="H1596" t="n">
         <v>140867</v>
@@ -46682,7 +46682,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1597" t="n">
-        <v>0.515188574790955</v>
+        <v>0.51518851518631</v>
       </c>
       <c r="H1597" t="n">
         <v>250652</v>
@@ -46711,7 +46711,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1598" t="n">
-        <v>0.51764190196991</v>
+        <v>0.517641842365265</v>
       </c>
       <c r="H1598" t="n">
         <v>186829</v>
@@ -46740,7 +46740,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1599" t="n">
-        <v>0.528681576251984</v>
+        <v>0.528681635856628</v>
       </c>
       <c r="H1599" t="n">
         <v>99156</v>
@@ -46827,7 +46827,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1602" t="n">
-        <v>0.564254224300385</v>
+        <v>0.56425416469574</v>
       </c>
       <c r="H1602" t="n">
         <v>239240</v>
@@ -46885,7 +46885,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G1604" t="n">
-        <v>0.577747225761414</v>
+        <v>0.577747166156769</v>
       </c>
       <c r="H1604" t="n">
         <v>194467</v>
@@ -46914,7 +46914,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G1605" t="n">
-        <v>0.577747225761414</v>
+        <v>0.577747166156769</v>
       </c>
       <c r="H1605" t="n">
         <v>360098</v>
@@ -46943,7 +46943,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G1606" t="n">
-        <v>0.542787969112396</v>
+        <v>0.542787909507751</v>
       </c>
       <c r="H1606" t="n">
         <v>302675</v>
@@ -47030,7 +47030,7 @@
         <v>0.859000027179718</v>
       </c>
       <c r="G1609" t="n">
-        <v>0.526841640472412</v>
+        <v>0.526841700077057</v>
       </c>
       <c r="H1609" t="n">
         <v>270347</v>
@@ -47059,7 +47059,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1610" t="n">
-        <v>0.533588171005249</v>
+        <v>0.533588111400604</v>
       </c>
       <c r="H1610" t="n">
         <v>109591</v>
@@ -47088,7 +47088,7 @@
         <v>0.869000017642975</v>
       </c>
       <c r="G1611" t="n">
-        <v>0.53297483921051</v>
+        <v>0.532974898815155</v>
       </c>
       <c r="H1611" t="n">
         <v>108692</v>
@@ -47146,7 +47146,7 @@
         <v>0.830999970436096</v>
       </c>
       <c r="G1613" t="n">
-        <v>0.50966864824295</v>
+        <v>0.509668707847595</v>
       </c>
       <c r="H1613" t="n">
         <v>203802</v>
@@ -47175,7 +47175,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1614" t="n">
-        <v>0.51764190196991</v>
+        <v>0.517641842365265</v>
       </c>
       <c r="H1614" t="n">
         <v>160874</v>
@@ -47349,7 +47349,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G1620" t="n">
-        <v>0.519481837749481</v>
+        <v>0.519481778144836</v>
       </c>
       <c r="H1620" t="n">
         <v>106747</v>
@@ -47378,7 +47378,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1621" t="n">
-        <v>0.527455031871796</v>
+        <v>0.527454972267151</v>
       </c>
       <c r="H1621" t="n">
         <v>91565</v>
@@ -47407,7 +47407,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1622" t="n">
-        <v>0.533588171005249</v>
+        <v>0.533588111400604</v>
       </c>
       <c r="H1622" t="n">
         <v>114805</v>
@@ -47494,7 +47494,7 @@
         <v>0.869000017642975</v>
       </c>
       <c r="G1625" t="n">
-        <v>0.53297483921051</v>
+        <v>0.532974898815155</v>
       </c>
       <c r="H1625" t="n">
         <v>113355</v>
@@ -47523,7 +47523,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1626" t="n">
-        <v>0.527455031871796</v>
+        <v>0.527454972267151</v>
       </c>
       <c r="H1626" t="n">
         <v>36276</v>
@@ -47610,7 +47610,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1629" t="n">
-        <v>0.572227358818054</v>
+        <v>0.572227299213409</v>
       </c>
       <c r="H1629" t="n">
         <v>80085</v>
@@ -47639,7 +47639,7 @@
         <v>0.950999975204468</v>
       </c>
       <c r="G1630" t="n">
-        <v>0.583267092704773</v>
+        <v>0.583267033100128</v>
       </c>
       <c r="H1630" t="n">
         <v>88990</v>
@@ -47668,7 +47668,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G1631" t="n">
-        <v>0.574067294597626</v>
+        <v>0.574067234992981</v>
       </c>
       <c r="H1631" t="n">
         <v>117312</v>
@@ -47755,7 +47755,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1634" t="n">
-        <v>0.619452893733978</v>
+        <v>0.619452953338623</v>
       </c>
       <c r="H1634" t="n">
         <v>300388</v>
@@ -47813,7 +47813,7 @@
         <v>1.01600003242493</v>
       </c>
       <c r="G1636" t="n">
-        <v>0.623132884502411</v>
+        <v>0.623132824897766</v>
       </c>
       <c r="H1636" t="n">
         <v>85942</v>
@@ -47871,7 +47871,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1638" t="n">
-        <v>0.619452893733978</v>
+        <v>0.619452953338623</v>
       </c>
       <c r="H1638" t="n">
         <v>66587</v>
@@ -47929,7 +47929,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1640" t="n">
-        <v>0.545854508876801</v>
+        <v>0.545854568481445</v>
       </c>
       <c r="H1640" t="n">
         <v>111925</v>
@@ -47987,7 +47987,7 @@
         <v>0.89300000667572</v>
       </c>
       <c r="G1642" t="n">
-        <v>0.547694504261017</v>
+        <v>0.547694563865662</v>
       </c>
       <c r="H1642" t="n">
         <v>149572</v>
@@ -48016,7 +48016,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1643" t="n">
-        <v>0.533588171005249</v>
+        <v>0.533588111400604</v>
       </c>
       <c r="H1643" t="n">
         <v>53610</v>
@@ -48045,7 +48045,7 @@
         <v>0.869000017642975</v>
       </c>
       <c r="G1644" t="n">
-        <v>0.53297483921051</v>
+        <v>0.532974898815155</v>
       </c>
       <c r="H1644" t="n">
         <v>95805</v>
@@ -48103,7 +48103,7 @@
         <v>0.887000024318695</v>
       </c>
       <c r="G1646" t="n">
-        <v>0.544014573097229</v>
+        <v>0.544014632701874</v>
       </c>
       <c r="H1646" t="n">
         <v>120588</v>
@@ -48132,7 +48132,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G1647" t="n">
-        <v>0.554441034793854</v>
+        <v>0.554441094398499</v>
       </c>
       <c r="H1647" t="n">
         <v>152234</v>
@@ -48161,7 +48161,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G1648" t="n">
-        <v>0.547081232070923</v>
+        <v>0.547081172466278</v>
       </c>
       <c r="H1648" t="n">
         <v>67414</v>
@@ -48248,7 +48248,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1651" t="n">
-        <v>0.533588171005249</v>
+        <v>0.533588111400604</v>
       </c>
       <c r="H1651" t="n">
         <v>72124</v>
@@ -48277,7 +48277,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1652" t="n">
-        <v>0.527455031871796</v>
+        <v>0.527454972267151</v>
       </c>
       <c r="H1652" t="n">
         <v>15946</v>
@@ -48393,7 +48393,7 @@
         <v>0.792999982833862</v>
       </c>
       <c r="G1656" t="n">
-        <v>0.486362546682358</v>
+        <v>0.486362516880035</v>
       </c>
       <c r="H1656" t="n">
         <v>58475</v>
@@ -48422,7 +48422,7 @@
         <v>0.788999974727631</v>
       </c>
       <c r="G1657" t="n">
-        <v>0.483909219503403</v>
+        <v>0.483909249305725</v>
       </c>
       <c r="H1657" t="n">
         <v>56680</v>
@@ -48451,7 +48451,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G1658" t="n">
-        <v>0.511508643627167</v>
+        <v>0.511508703231812</v>
       </c>
       <c r="H1658" t="n">
         <v>55747</v>
@@ -48625,7 +48625,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1664" t="n">
-        <v>0.482069283723831</v>
+        <v>0.482069313526154</v>
       </c>
       <c r="H1664" t="n">
         <v>41158</v>
@@ -48654,7 +48654,7 @@
         <v>0.785000026226044</v>
       </c>
       <c r="G1665" t="n">
-        <v>0.481456011533737</v>
+        <v>0.481455981731415</v>
       </c>
       <c r="H1665" t="n">
         <v>33125</v>
@@ -48683,7 +48683,7 @@
         <v>0.787000000476837</v>
       </c>
       <c r="G1666" t="n">
-        <v>0.48268261551857</v>
+        <v>0.482682675123215</v>
       </c>
       <c r="H1666" t="n">
         <v>86039</v>
@@ -48741,7 +48741,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1668" t="n">
-        <v>0.480842649936676</v>
+        <v>0.480842679738998</v>
       </c>
       <c r="H1668" t="n">
         <v>18752</v>
@@ -48857,7 +48857,7 @@
         <v>0.930999994277954</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.571000635623932</v>
+        <v>0.571000695228577</v>
       </c>
       <c r="H1672" t="n">
         <v>119126</v>
@@ -48886,7 +48886,7 @@
         <v>0.922999978065491</v>
       </c>
       <c r="G1673" t="n">
-        <v>0.566094160079956</v>
+        <v>0.566094100475311</v>
       </c>
       <c r="H1673" t="n">
         <v>42938</v>
@@ -49031,7 +49031,7 @@
         <v>0.922999978065491</v>
       </c>
       <c r="G1678" t="n">
-        <v>0.566094160079956</v>
+        <v>0.566094100475311</v>
       </c>
       <c r="H1678" t="n">
         <v>38579</v>
@@ -49089,7 +49089,7 @@
         <v>0.890999972820282</v>
       </c>
       <c r="G1680" t="n">
-        <v>0.546467900276184</v>
+        <v>0.546467840671539</v>
       </c>
       <c r="H1680" t="n">
         <v>17070</v>
@@ -49118,7 +49118,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G1681" t="n">
-        <v>0.542787969112396</v>
+        <v>0.542787909507751</v>
       </c>
       <c r="H1681" t="n">
         <v>22180</v>
@@ -49147,7 +49147,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G1682" t="n">
-        <v>0.548921167850494</v>
+        <v>0.54892110824585</v>
       </c>
       <c r="H1682" t="n">
         <v>7867</v>
@@ -49263,7 +49263,7 @@
         <v>0.880999982357025</v>
       </c>
       <c r="G1686" t="n">
-        <v>0.540334701538086</v>
+        <v>0.540334641933441</v>
       </c>
       <c r="H1686" t="n">
         <v>15422</v>
@@ -49321,7 +49321,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1688" t="n">
-        <v>0.53849470615387</v>
+        <v>0.538494765758514</v>
       </c>
       <c r="H1688" t="n">
         <v>37248</v>
@@ -49408,7 +49408,7 @@
         <v>0.887000024318695</v>
       </c>
       <c r="G1691" t="n">
-        <v>0.544014573097229</v>
+        <v>0.544014632701874</v>
       </c>
       <c r="H1691" t="n">
         <v>9721</v>
@@ -49466,7 +49466,7 @@
         <v>0.870999991893768</v>
       </c>
       <c r="G1693" t="n">
-        <v>0.534201443195343</v>
+        <v>0.534201502799988</v>
       </c>
       <c r="H1693" t="n">
         <v>9319</v>
@@ -49524,7 +49524,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.527455031871796</v>
+        <v>0.527454972267151</v>
       </c>
       <c r="H1695" t="n">
         <v>15843</v>
@@ -49553,7 +49553,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1696" t="n">
-        <v>0.515188574790955</v>
+        <v>0.51518851518631</v>
       </c>
       <c r="H1696" t="n">
         <v>32822</v>
@@ -49640,7 +49640,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1699" t="n">
-        <v>0.506602108478546</v>
+        <v>0.506602048873901</v>
       </c>
       <c r="H1699" t="n">
         <v>6514</v>
@@ -49669,7 +49669,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1700" t="n">
-        <v>0.498015612363815</v>
+        <v>0.498015642166138</v>
       </c>
       <c r="H1700" t="n">
         <v>31394</v>
@@ -49698,7 +49698,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1701" t="n">
-        <v>0.490655779838562</v>
+        <v>0.49065575003624</v>
       </c>
       <c r="H1701" t="n">
         <v>34760</v>
@@ -49727,7 +49727,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1702" t="n">
-        <v>0.485749214887619</v>
+        <v>0.485749244689941</v>
       </c>
       <c r="H1702" t="n">
         <v>38092</v>
@@ -49756,7 +49756,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1703" t="n">
-        <v>0.485749214887619</v>
+        <v>0.485749244689941</v>
       </c>
       <c r="H1703" t="n">
         <v>129729</v>
@@ -49785,7 +49785,7 @@
         <v>0.809000015258789</v>
       </c>
       <c r="G1704" t="n">
-        <v>0.496175676584244</v>
+        <v>0.496175706386566</v>
       </c>
       <c r="H1704" t="n">
         <v>21382</v>
@@ -49843,7 +49843,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1706" t="n">
-        <v>0.486975878477097</v>
+        <v>0.486975938081741</v>
       </c>
       <c r="H1706" t="n">
         <v>180690</v>
@@ -49901,7 +49901,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1708" t="n">
-        <v>0.4747094810009</v>
+        <v>0.474709451198578</v>
       </c>
       <c r="H1708" t="n">
         <v>124386</v>
@@ -49930,7 +49930,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1709" t="n">
-        <v>0.4747094810009</v>
+        <v>0.474709451198578</v>
       </c>
       <c r="H1709" t="n">
         <v>11175</v>
@@ -49959,7 +49959,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1710" t="n">
-        <v>0.472256153821945</v>
+        <v>0.47225621342659</v>
       </c>
       <c r="H1710" t="n">
         <v>25393</v>
@@ -50017,7 +50017,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1712" t="n">
-        <v>0.453243255615234</v>
+        <v>0.453243315219879</v>
       </c>
       <c r="H1712" t="n">
         <v>148619</v>
@@ -50133,7 +50133,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1716" t="n">
-        <v>0.447723418474197</v>
+        <v>0.447723388671875</v>
       </c>
       <c r="H1716" t="n">
         <v>26655</v>
@@ -50162,7 +50162,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G1717" t="n">
-        <v>0.432390421628952</v>
+        <v>0.43239039182663</v>
       </c>
       <c r="H1717" t="n">
         <v>34763</v>
@@ -50249,7 +50249,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G1720" t="n">
-        <v>0.438523590564728</v>
+        <v>0.43852362036705</v>
       </c>
       <c r="H1720" t="n">
         <v>78867</v>
@@ -50307,7 +50307,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1722" t="n">
-        <v>0.42809721827507</v>
+        <v>0.428097188472748</v>
       </c>
       <c r="H1722" t="n">
         <v>9212</v>
@@ -50423,7 +50423,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1726" t="n">
-        <v>0.417057454586029</v>
+        <v>0.417057424783707</v>
       </c>
       <c r="H1726" t="n">
         <v>138955</v>
@@ -50452,7 +50452,7 @@
         <v>0.686999976634979</v>
       </c>
       <c r="G1727" t="n">
-        <v>0.421350628137589</v>
+        <v>0.421350657939911</v>
       </c>
       <c r="H1727" t="n">
         <v>124750</v>
@@ -50510,7 +50510,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1729" t="n">
-        <v>0.431777060031891</v>
+        <v>0.431777089834213</v>
       </c>
       <c r="H1729" t="n">
         <v>113735</v>
@@ -50597,7 +50597,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1732" t="n">
-        <v>0.490655779838562</v>
+        <v>0.49065575003624</v>
       </c>
       <c r="H1732" t="n">
         <v>498028</v>
@@ -50626,7 +50626,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1733" t="n">
-        <v>0.527455031871796</v>
+        <v>0.527454972267151</v>
       </c>
       <c r="H1733" t="n">
         <v>794338</v>
@@ -50974,7 +50974,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1745" t="n">
-        <v>0.515188574790955</v>
+        <v>0.51518851518631</v>
       </c>
       <c r="H1745" t="n">
         <v>39782</v>
@@ -51003,7 +51003,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1746" t="n">
-        <v>0.515188574790955</v>
+        <v>0.51518851518631</v>
       </c>
       <c r="H1746" t="n">
         <v>29578</v>
@@ -51032,7 +51032,7 @@
         <v>0.859000027179718</v>
       </c>
       <c r="G1747" t="n">
-        <v>0.526841640472412</v>
+        <v>0.526841700077057</v>
       </c>
       <c r="H1747" t="n">
         <v>85973</v>
@@ -51090,7 +51090,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G1749" t="n">
-        <v>0.586333632469177</v>
+        <v>0.586333692073822</v>
       </c>
       <c r="H1749" t="n">
         <v>347020</v>
@@ -51119,7 +51119,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1750" t="n">
-        <v>0.575293898582458</v>
+        <v>0.575293958187103</v>
       </c>
       <c r="H1750" t="n">
         <v>90656</v>
@@ -51148,7 +51148,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G1751" t="n">
-        <v>0.567320704460144</v>
+        <v>0.567320764064789</v>
       </c>
       <c r="H1751" t="n">
         <v>28616</v>
@@ -51293,7 +51293,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1756" t="n">
-        <v>0.525001645088196</v>
+        <v>0.525001704692841</v>
       </c>
       <c r="H1756" t="n">
         <v>170491</v>
@@ -51380,7 +51380,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1759" t="n">
-        <v>0.534814774990082</v>
+        <v>0.534814834594727</v>
       </c>
       <c r="H1759" t="n">
         <v>51515</v>
@@ -51438,7 +51438,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1761" t="n">
-        <v>0.545854508876801</v>
+        <v>0.545854568481445</v>
       </c>
       <c r="H1761" t="n">
         <v>29697</v>
@@ -51467,7 +51467,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G1762" t="n">
-        <v>0.542787969112396</v>
+        <v>0.542787909507751</v>
       </c>
       <c r="H1762" t="n">
         <v>69410</v>
@@ -51525,7 +51525,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1764" t="n">
-        <v>0.525001645088196</v>
+        <v>0.525001704692841</v>
       </c>
       <c r="H1764" t="n">
         <v>62102</v>
@@ -51554,7 +51554,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G1765" t="n">
-        <v>0.519481837749481</v>
+        <v>0.519481778144836</v>
       </c>
       <c r="H1765" t="n">
         <v>185940</v>
@@ -51583,7 +51583,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G1766" t="n">
-        <v>0.519481837749481</v>
+        <v>0.519481778144836</v>
       </c>
       <c r="H1766" t="n">
         <v>16972</v>
@@ -51757,7 +51757,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1772" t="n">
-        <v>0.528681576251984</v>
+        <v>0.528681635856628</v>
       </c>
       <c r="H1772" t="n">
         <v>80721</v>
@@ -51786,7 +51786,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1773" t="n">
-        <v>0.527455031871796</v>
+        <v>0.527454972267151</v>
       </c>
       <c r="H1773" t="n">
         <v>26372</v>
@@ -51815,7 +51815,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1774" t="n">
-        <v>0.533588171005249</v>
+        <v>0.533588111400604</v>
       </c>
       <c r="H1774" t="n">
         <v>61411</v>
@@ -51844,7 +51844,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G1775" t="n">
-        <v>0.554441034793854</v>
+        <v>0.554441094398499</v>
       </c>
       <c r="H1775" t="n">
         <v>221808</v>
@@ -51902,7 +51902,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G1777" t="n">
-        <v>0.577747225761414</v>
+        <v>0.577747166156769</v>
       </c>
       <c r="H1777" t="n">
         <v>109525</v>
@@ -51960,7 +51960,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G1779" t="n">
-        <v>0.554441034793854</v>
+        <v>0.554441094398499</v>
       </c>
       <c r="H1779" t="n">
         <v>192322</v>
@@ -52018,7 +52018,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1781" t="n">
-        <v>0.575293898582458</v>
+        <v>0.575293958187103</v>
       </c>
       <c r="H1781" t="n">
         <v>39750</v>
@@ -52134,7 +52134,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G1785" t="n">
-        <v>0.577747225761414</v>
+        <v>0.577747166156769</v>
       </c>
       <c r="H1785" t="n">
         <v>163954</v>
@@ -52192,7 +52192,7 @@
         <v>0.950999975204468</v>
       </c>
       <c r="G1787" t="n">
-        <v>0.583267092704773</v>
+        <v>0.583267033100128</v>
       </c>
       <c r="H1787" t="n">
         <v>12303</v>
@@ -52279,7 +52279,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1790" t="n">
-        <v>0.619452893733978</v>
+        <v>0.619452953338623</v>
       </c>
       <c r="H1790" t="n">
         <v>297236</v>
@@ -52308,7 +52308,7 @@
         <v>1.0460000038147</v>
       </c>
       <c r="G1791" t="n">
-        <v>0.641532480716705</v>
+        <v>0.641532421112061</v>
       </c>
       <c r="H1791" t="n">
         <v>240300</v>
@@ -52337,7 +52337,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1792" t="n">
-        <v>0.656252145767212</v>
+        <v>0.656252205371857</v>
       </c>
       <c r="H1792" t="n">
         <v>246471</v>
@@ -52424,7 +52424,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1795" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1795" t="n">
         <v>83136</v>
@@ -52453,7 +52453,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1796" t="n">
-        <v>0.66238534450531</v>
+        <v>0.662385404109955</v>
       </c>
       <c r="H1796" t="n">
         <v>92197</v>
@@ -52482,7 +52482,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1797" t="n">
-        <v>0.673425018787384</v>
+        <v>0.673425078392029</v>
       </c>
       <c r="H1797" t="n">
         <v>25509</v>
@@ -52511,7 +52511,7 @@
         <v>1.09200000762939</v>
       </c>
       <c r="G1798" t="n">
-        <v>0.669745206832886</v>
+        <v>0.669745147228241</v>
       </c>
       <c r="H1798" t="n">
         <v>77905</v>
@@ -52627,7 +52627,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1802" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1802" t="n">
         <v>89984</v>
@@ -52656,7 +52656,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1803" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1803" t="n">
         <v>24192</v>
@@ -52685,7 +52685,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1804" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1804" t="n">
         <v>49995</v>
@@ -52714,7 +52714,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G1805" t="n">
-        <v>0.688144683837891</v>
+        <v>0.688144743442535</v>
       </c>
       <c r="H1805" t="n">
         <v>128129</v>
@@ -52743,7 +52743,7 @@
         <v>1.13399994373322</v>
       </c>
       <c r="G1806" t="n">
-        <v>0.695504546165466</v>
+        <v>0.695504486560822</v>
       </c>
       <c r="H1806" t="n">
         <v>83356</v>
@@ -52801,7 +52801,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1808" t="n">
-        <v>0.720037341117859</v>
+        <v>0.720037400722504</v>
       </c>
       <c r="H1808" t="n">
         <v>308736</v>
@@ -52859,7 +52859,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1810" t="n">
-        <v>0.723717212677002</v>
+        <v>0.723717272281647</v>
       </c>
       <c r="H1810" t="n">
         <v>66526</v>
@@ -52975,7 +52975,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1814" t="n">
-        <v>0.743343472480774</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H1814" t="n">
         <v>234732</v>
@@ -53004,7 +53004,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1815" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1815" t="n">
         <v>136669</v>
@@ -53149,7 +53149,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1820" t="n">
-        <v>0.724943995475769</v>
+        <v>0.724943935871124</v>
       </c>
       <c r="H1820" t="n">
         <v>326053</v>
@@ -53294,7 +53294,7 @@
         <v>1.09399998188019</v>
       </c>
       <c r="G1825" t="n">
-        <v>0.670971810817719</v>
+        <v>0.670971751213074</v>
       </c>
       <c r="H1825" t="n">
         <v>141594</v>
@@ -53323,7 +53323,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1826" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1826" t="n">
         <v>56323</v>
@@ -53352,7 +53352,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1827" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1827" t="n">
         <v>172559</v>
@@ -53381,7 +53381,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G1828" t="n">
-        <v>0.688144683837891</v>
+        <v>0.688144743442535</v>
       </c>
       <c r="H1828" t="n">
         <v>145815</v>
@@ -53468,7 +53468,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1831" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1831" t="n">
         <v>129863</v>
@@ -53526,7 +53526,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1833" t="n">
-        <v>0.66238534450531</v>
+        <v>0.662385404109955</v>
       </c>
       <c r="H1833" t="n">
         <v>158378</v>
@@ -53555,7 +53555,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1834" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1834" t="n">
         <v>68683</v>
@@ -53584,7 +53584,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1835" t="n">
-        <v>0.643985688686371</v>
+        <v>0.643985629081726</v>
       </c>
       <c r="H1835" t="n">
         <v>341515</v>
@@ -53700,7 +53700,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1839" t="n">
-        <v>0.673425018787384</v>
+        <v>0.673425078392029</v>
       </c>
       <c r="H1839" t="n">
         <v>140803</v>
@@ -53729,7 +53729,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1840" t="n">
-        <v>0.705317735671997</v>
+        <v>0.705317676067352</v>
       </c>
       <c r="H1840" t="n">
         <v>602597</v>
@@ -53758,7 +53758,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1841" t="n">
-        <v>0.705317735671997</v>
+        <v>0.705317676067352</v>
       </c>
       <c r="H1841" t="n">
         <v>102468</v>
@@ -53816,7 +53816,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G1843" t="n">
-        <v>0.696731209754944</v>
+        <v>0.696731269359589</v>
       </c>
       <c r="H1843" t="n">
         <v>56024</v>
@@ -53903,7 +53903,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1846" t="n">
-        <v>0.68078488111496</v>
+        <v>0.680784940719604</v>
       </c>
       <c r="H1846" t="n">
         <v>109832</v>
@@ -53961,7 +53961,7 @@
         <v>1.12399995326996</v>
       </c>
       <c r="G1848" t="n">
-        <v>0.689371407032013</v>
+        <v>0.689371347427368</v>
       </c>
       <c r="H1848" t="n">
         <v>89945</v>
@@ -53990,7 +53990,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1849" t="n">
-        <v>0.686918079853058</v>
+        <v>0.686918139457703</v>
       </c>
       <c r="H1849" t="n">
         <v>154138</v>
@@ -54019,7 +54019,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G1850" t="n">
-        <v>0.697957873344421</v>
+        <v>0.697957813739777</v>
       </c>
       <c r="H1850" t="n">
         <v>31934</v>
@@ -54048,7 +54048,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1851" t="n">
-        <v>0.686918079853058</v>
+        <v>0.686918139457703</v>
       </c>
       <c r="H1851" t="n">
         <v>50692</v>
@@ -54077,7 +54077,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1852" t="n">
-        <v>0.686918079853058</v>
+        <v>0.686918139457703</v>
       </c>
       <c r="H1852" t="n">
         <v>74896</v>
@@ -54106,7 +54106,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G1853" t="n">
-        <v>0.708997666835785</v>
+        <v>0.70899760723114</v>
       </c>
       <c r="H1853" t="n">
         <v>161330</v>
@@ -54193,7 +54193,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1856" t="n">
-        <v>0.754383206367493</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H1856" t="n">
         <v>278182</v>
@@ -54222,7 +54222,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1857" t="n">
-        <v>0.743343472480774</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H1857" t="n">
         <v>119937</v>
@@ -54338,7 +54338,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1861" t="n">
-        <v>0.723717212677002</v>
+        <v>0.723717272281647</v>
       </c>
       <c r="H1861" t="n">
         <v>129795</v>
@@ -54512,7 +54512,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1867" t="n">
-        <v>0.724943995475769</v>
+        <v>0.724943935871124</v>
       </c>
       <c r="H1867" t="n">
         <v>161084</v>
@@ -54541,7 +54541,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G1868" t="n">
-        <v>0.70654433965683</v>
+        <v>0.706544280052185</v>
       </c>
       <c r="H1868" t="n">
         <v>208969</v>
@@ -54628,7 +54628,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G1871" t="n">
-        <v>0.696731209754944</v>
+        <v>0.696731269359589</v>
       </c>
       <c r="H1871" t="n">
         <v>92961</v>
@@ -54686,7 +54686,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1873" t="n">
-        <v>0.711450815200806</v>
+        <v>0.71145087480545</v>
       </c>
       <c r="H1873" t="n">
         <v>50139</v>
@@ -54715,7 +54715,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1874" t="n">
-        <v>0.711450815200806</v>
+        <v>0.71145087480545</v>
       </c>
       <c r="H1874" t="n">
         <v>37118</v>
@@ -54744,7 +54744,7 @@
         <v>1.15400004386902</v>
       </c>
       <c r="G1875" t="n">
-        <v>0.707770943641663</v>
+        <v>0.707771003246307</v>
       </c>
       <c r="H1875" t="n">
         <v>46996</v>
@@ -54773,7 +54773,7 @@
         <v>1.15400004386902</v>
       </c>
       <c r="G1876" t="n">
-        <v>0.707770943641663</v>
+        <v>0.707771003246307</v>
       </c>
       <c r="H1876" t="n">
         <v>41202</v>
@@ -54802,7 +54802,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1877" t="n">
-        <v>0.705317735671997</v>
+        <v>0.705317676067352</v>
       </c>
       <c r="H1877" t="n">
         <v>40683</v>
@@ -54831,7 +54831,7 @@
         <v>1.15400004386902</v>
       </c>
       <c r="G1878" t="n">
-        <v>0.707770943641663</v>
+        <v>0.707771003246307</v>
       </c>
       <c r="H1878" t="n">
         <v>84523</v>
@@ -54860,7 +54860,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1879" t="n">
-        <v>0.711450815200806</v>
+        <v>0.71145087480545</v>
       </c>
       <c r="H1879" t="n">
         <v>110237</v>
@@ -54947,7 +54947,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G1882" t="n">
-        <v>0.688144683837891</v>
+        <v>0.688144743442535</v>
       </c>
       <c r="H1882" t="n">
         <v>112701</v>
@@ -54976,7 +54976,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1883" t="n">
-        <v>0.705317735671997</v>
+        <v>0.705317676067352</v>
       </c>
       <c r="H1883" t="n">
         <v>38864</v>
@@ -55005,7 +55005,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.688144683837891</v>
+        <v>0.688144743442535</v>
       </c>
       <c r="H1884" t="n">
         <v>39378</v>
@@ -55034,7 +55034,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.686918079853058</v>
+        <v>0.686918139457703</v>
       </c>
       <c r="H1885" t="n">
         <v>84022</v>
@@ -55063,7 +55063,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.673425018787384</v>
+        <v>0.673425078392029</v>
       </c>
       <c r="H1886" t="n">
         <v>64482</v>
@@ -55092,7 +55092,7 @@
         <v>1.09399998188019</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.670971810817719</v>
+        <v>0.670971751213074</v>
       </c>
       <c r="H1887" t="n">
         <v>84759</v>
@@ -55150,7 +55150,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.700411081314087</v>
+        <v>0.700411140918732</v>
       </c>
       <c r="H1889" t="n">
         <v>66214</v>
@@ -55208,7 +55208,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1891" t="n">
-        <v>0.711450815200806</v>
+        <v>0.71145087480545</v>
       </c>
       <c r="H1891" t="n">
         <v>33873</v>
@@ -55237,7 +55237,7 @@
         <v>1.15799999237061</v>
       </c>
       <c r="G1892" t="n">
-        <v>0.710224211215973</v>
+        <v>0.710224270820618</v>
       </c>
       <c r="H1892" t="n">
         <v>17771</v>
@@ -55353,7 +55353,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1896" t="n">
-        <v>0.720037341117859</v>
+        <v>0.720037400722504</v>
       </c>
       <c r="H1896" t="n">
         <v>20994</v>
@@ -55382,7 +55382,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G1897" t="n">
-        <v>0.718810737133026</v>
+        <v>0.718810796737671</v>
       </c>
       <c r="H1897" t="n">
         <v>28942</v>
@@ -55469,7 +55469,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1900" t="n">
-        <v>0.720037341117859</v>
+        <v>0.720037400722504</v>
       </c>
       <c r="H1900" t="n">
         <v>36684</v>
@@ -55730,7 +55730,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1909" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1909" t="n">
         <v>60247</v>
@@ -55759,7 +55759,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1910" t="n">
-        <v>0.754383206367493</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H1910" t="n">
         <v>87166</v>
@@ -55875,7 +55875,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1914" t="n">
-        <v>0.759289920330048</v>
+        <v>0.759289860725403</v>
       </c>
       <c r="H1914" t="n">
         <v>30810</v>
@@ -55933,7 +55933,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G1916" t="n">
-        <v>0.767876267433167</v>
+        <v>0.767876327037811</v>
       </c>
       <c r="H1916" t="n">
         <v>111462</v>
@@ -55962,7 +55962,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1917" t="n">
-        <v>0.775236248970032</v>
+        <v>0.775236189365387</v>
       </c>
       <c r="H1917" t="n">
         <v>109012</v>
@@ -56020,7 +56020,7 @@
         <v>1.28799998760223</v>
       </c>
       <c r="G1919" t="n">
-        <v>0.789955854415894</v>
+        <v>0.789955794811249</v>
       </c>
       <c r="H1919" t="n">
         <v>115650</v>
@@ -56049,7 +56049,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1920" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1920" t="n">
         <v>110958</v>
@@ -56078,7 +56078,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1921" t="n">
-        <v>0.78136932849884</v>
+        <v>0.781369388103485</v>
       </c>
       <c r="H1921" t="n">
         <v>136354</v>
@@ -56136,7 +56136,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1923" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1923" t="n">
         <v>186595</v>
@@ -56165,7 +56165,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1924" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1924" t="n">
         <v>93366</v>
@@ -56223,7 +56223,7 @@
         <v>1.28799998760223</v>
       </c>
       <c r="G1926" t="n">
-        <v>0.789955854415894</v>
+        <v>0.789955794811249</v>
       </c>
       <c r="H1926" t="n">
         <v>575030</v>
@@ -56252,7 +56252,7 @@
         <v>1.31200003623962</v>
       </c>
       <c r="G1927" t="n">
-        <v>0.804675459861755</v>
+        <v>0.8046755194664</v>
       </c>
       <c r="H1927" t="n">
         <v>213266</v>
@@ -56339,7 +56339,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G1930" t="n">
-        <v>0.799768924713135</v>
+        <v>0.79976898431778</v>
       </c>
       <c r="H1930" t="n">
         <v>145895</v>
@@ -56368,7 +56368,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1931" t="n">
-        <v>0.78136932849884</v>
+        <v>0.781369388103485</v>
       </c>
       <c r="H1931" t="n">
         <v>151205</v>
@@ -56397,7 +56397,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1932" t="n">
-        <v>0.775236248970032</v>
+        <v>0.775236189365387</v>
       </c>
       <c r="H1932" t="n">
         <v>117911</v>
@@ -56513,7 +56513,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1936" t="n">
-        <v>0.735983729362488</v>
+        <v>0.735983669757843</v>
       </c>
       <c r="H1936" t="n">
         <v>145184</v>
@@ -56571,7 +56571,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1938" t="n">
-        <v>0.759289920330048</v>
+        <v>0.759289860725403</v>
       </c>
       <c r="H1938" t="n">
         <v>76097</v>
@@ -56629,7 +56629,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G1940" t="n">
-        <v>0.767876267433167</v>
+        <v>0.767876327037811</v>
       </c>
       <c r="H1940" t="n">
         <v>97307</v>
@@ -56658,7 +56658,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1941" t="n">
-        <v>0.78136932849884</v>
+        <v>0.781369388103485</v>
       </c>
       <c r="H1941" t="n">
         <v>40081</v>
@@ -56716,7 +56716,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1943" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1943" t="n">
         <v>117184</v>
@@ -57006,7 +57006,7 @@
         <v>1.27600002288818</v>
       </c>
       <c r="G1953" t="n">
-        <v>0.782596051692963</v>
+        <v>0.782595992088318</v>
       </c>
       <c r="H1953" t="n">
         <v>103460</v>
@@ -57035,7 +57035,7 @@
         <v>1.27600002288818</v>
       </c>
       <c r="G1954" t="n">
-        <v>0.782596051692963</v>
+        <v>0.782595992088318</v>
       </c>
       <c r="H1954" t="n">
         <v>122163</v>
@@ -57064,7 +57064,7 @@
         <v>1.28799998760223</v>
       </c>
       <c r="G1955" t="n">
-        <v>0.789955854415894</v>
+        <v>0.789955794811249</v>
       </c>
       <c r="H1955" t="n">
         <v>132398</v>
@@ -57122,7 +57122,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1957" t="n">
-        <v>0.772782862186432</v>
+        <v>0.772782921791077</v>
       </c>
       <c r="H1957" t="n">
         <v>86324</v>
@@ -57151,7 +57151,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1958" t="n">
-        <v>0.775236248970032</v>
+        <v>0.775236189365387</v>
       </c>
       <c r="H1958" t="n">
         <v>59757</v>
@@ -57180,7 +57180,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1959" t="n">
-        <v>0.775236248970032</v>
+        <v>0.775236189365387</v>
       </c>
       <c r="H1959" t="n">
         <v>60924</v>
@@ -57209,7 +57209,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1960" t="n">
-        <v>0.78136932849884</v>
+        <v>0.781369388103485</v>
       </c>
       <c r="H1960" t="n">
         <v>75052</v>
@@ -57296,7 +57296,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G1963" t="n">
-        <v>0.799768924713135</v>
+        <v>0.79976898431778</v>
       </c>
       <c r="H1963" t="n">
         <v>206796</v>
@@ -57528,7 +57528,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1971" t="n">
-        <v>0.907713234424591</v>
+        <v>0.907713174819946</v>
       </c>
       <c r="H1971" t="n">
         <v>262828</v>
@@ -57557,7 +57557,7 @@
         <v>1.46399998664856</v>
       </c>
       <c r="G1972" t="n">
-        <v>0.89790004491806</v>
+        <v>0.897900104522705</v>
       </c>
       <c r="H1972" t="n">
         <v>168691</v>
@@ -57586,7 +57586,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G1973" t="n">
-        <v>0.912619769573212</v>
+        <v>0.912619829177856</v>
       </c>
       <c r="H1973" t="n">
         <v>300698</v>
@@ -57615,7 +57615,7 @@
         <v>1.50399994850159</v>
       </c>
       <c r="G1974" t="n">
-        <v>0.922432899475098</v>
+        <v>0.922432839870453</v>
       </c>
       <c r="H1974" t="n">
         <v>503202</v>
@@ -57702,7 +57702,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1977" t="n">
-        <v>0.928566098213196</v>
+        <v>0.928566157817841</v>
       </c>
       <c r="H1977" t="n">
         <v>2340651</v>
@@ -57760,7 +57760,7 @@
         <v>1.58800005912781</v>
       </c>
       <c r="G1979" t="n">
-        <v>0.973951756954193</v>
+        <v>0.973951876163483</v>
       </c>
       <c r="H1979" t="n">
         <v>372992</v>
@@ -57789,7 +57789,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G1980" t="n">
-        <v>1.04141676425934</v>
+        <v>1.04141700267792</v>
       </c>
       <c r="H1980" t="n">
         <v>635537</v>
@@ -57847,7 +57847,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G1982" t="n">
-        <v>1.0070708990097</v>
+        <v>1.00707101821899</v>
       </c>
       <c r="H1982" t="n">
         <v>351342</v>
@@ -57876,7 +57876,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1983" t="n">
-        <v>0.999711155891418</v>
+        <v>0.999711096286774</v>
       </c>
       <c r="H1983" t="n">
         <v>355798</v>
@@ -57905,7 +57905,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1984" t="n">
-        <v>1.02301728725433</v>
+        <v>1.02301740646362</v>
       </c>
       <c r="H1984" t="n">
         <v>591445</v>
@@ -58021,7 +58021,7 @@
         <v>1.64400005340576</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.00829768180847</v>
+        <v>1.00829756259918</v>
       </c>
       <c r="H1988" t="n">
         <v>364234</v>
@@ -58050,7 +58050,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1989" t="n">
-        <v>0.993578016757965</v>
+        <v>0.99357795715332</v>
       </c>
       <c r="H1989" t="n">
         <v>762902</v>
@@ -58137,7 +58137,7 @@
         <v>1.54799997806549</v>
       </c>
       <c r="G1992" t="n">
-        <v>0.949418962001801</v>
+        <v>0.949418902397156</v>
       </c>
       <c r="H1992" t="n">
         <v>618719</v>
@@ -58166,7 +58166,7 @@
         <v>1.54799997806549</v>
       </c>
       <c r="G1993" t="n">
-        <v>0.949418962001801</v>
+        <v>0.949418902397156</v>
       </c>
       <c r="H1993" t="n">
         <v>164171</v>
@@ -58224,7 +58224,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1995" t="n">
-        <v>0.956778764724731</v>
+        <v>0.956778824329376</v>
       </c>
       <c r="H1995" t="n">
         <v>285758</v>
@@ -58253,7 +58253,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G1996" t="n">
-        <v>0.951872229576111</v>
+        <v>0.951872289180756</v>
       </c>
       <c r="H1996" t="n">
         <v>102119</v>
@@ -58282,7 +58282,7 @@
         <v>1.57799994945526</v>
       </c>
       <c r="G1997" t="n">
-        <v>0.967818439006805</v>
+        <v>0.96781849861145</v>
       </c>
       <c r="H1997" t="n">
         <v>136474</v>
@@ -58311,7 +58311,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1998" t="n">
-        <v>0.96536523103714</v>
+        <v>0.965365350246429</v>
       </c>
       <c r="H1998" t="n">
         <v>115948</v>
@@ -58340,7 +58340,7 @@
         <v>1.5</v>
       </c>
       <c r="G1999" t="n">
-        <v>0.919979572296143</v>
+        <v>0.919979512691498</v>
       </c>
       <c r="H1999" t="n">
         <v>702293</v>
@@ -58369,7 +58369,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G2000" t="n">
-        <v>0.950645625591278</v>
+        <v>0.950645565986633</v>
       </c>
       <c r="H2000" t="n">
         <v>269857</v>
@@ -58398,7 +58398,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G2001" t="n">
-        <v>0.950645625591278</v>
+        <v>0.950645565986633</v>
       </c>
       <c r="H2001" t="n">
         <v>33986</v>
@@ -58427,7 +58427,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G2002" t="n">
-        <v>0.953098893165588</v>
+        <v>0.953098952770233</v>
       </c>
       <c r="H2002" t="n">
         <v>145635</v>
@@ -58456,7 +58456,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G2003" t="n">
-        <v>0.980084896087646</v>
+        <v>0.980085015296936</v>
       </c>
       <c r="H2003" t="n">
         <v>535679</v>
@@ -58485,7 +58485,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G2004" t="n">
-        <v>1.01075088977814</v>
+        <v>1.01075100898743</v>
       </c>
       <c r="H2004" t="n">
         <v>1171917</v>
@@ -58514,7 +58514,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G2005" t="n">
-        <v>0.999711155891418</v>
+        <v>0.999711096286774</v>
       </c>
       <c r="H2005" t="n">
         <v>423686</v>
@@ -58543,7 +58543,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G2006" t="n">
-        <v>0.999711155891418</v>
+        <v>0.999711096286774</v>
       </c>
       <c r="H2006" t="n">
         <v>242068</v>
@@ -58601,7 +58601,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G2008" t="n">
-        <v>1.00461781024933</v>
+        <v>1.00461769104004</v>
       </c>
       <c r="H2008" t="n">
         <v>260872</v>
@@ -58659,7 +58659,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2010" t="n">
-        <v>0.993578016757965</v>
+        <v>0.99357795715332</v>
       </c>
       <c r="H2010" t="n">
         <v>107326</v>
@@ -58717,7 +58717,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G2012" t="n">
-        <v>0.98376476764679</v>
+        <v>0.983764886856079</v>
       </c>
       <c r="H2012" t="n">
         <v>155404</v>
@@ -58775,7 +58775,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G2014" t="n">
-        <v>0.98376476764679</v>
+        <v>0.983764886856079</v>
       </c>
       <c r="H2014" t="n">
         <v>263889</v>
@@ -58833,7 +58833,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G2016" t="n">
-        <v>0.988671362400055</v>
+        <v>0.9886714220047</v>
       </c>
       <c r="H2016" t="n">
         <v>414094</v>
@@ -58862,7 +58862,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G2017" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H2017" t="n">
         <v>184712</v>
@@ -58978,7 +58978,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G2021" t="n">
-        <v>1.11501514911652</v>
+        <v>1.11501526832581</v>
       </c>
       <c r="H2021" t="n">
         <v>1262002</v>
@@ -59094,7 +59094,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G2025" t="n">
-        <v>1.14813458919525</v>
+        <v>1.14813446998596</v>
       </c>
       <c r="H2025" t="n">
         <v>435936</v>
@@ -59123,7 +59123,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G2026" t="n">
-        <v>1.15181457996368</v>
+        <v>1.15181446075439</v>
       </c>
       <c r="H2026" t="n">
         <v>370742</v>
@@ -59268,7 +59268,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2031" t="n">
-        <v>1.26957190036774</v>
+        <v>1.26957178115845</v>
       </c>
       <c r="H2031" t="n">
         <v>342742</v>
@@ -59326,7 +59326,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2033" t="n">
-        <v>1.23277270793915</v>
+        <v>1.23277258872986</v>
       </c>
       <c r="H2033" t="n">
         <v>184193</v>
@@ -59355,7 +59355,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2034" t="n">
-        <v>1.23890578746796</v>
+        <v>1.23890590667725</v>
       </c>
       <c r="H2034" t="n">
         <v>182056</v>
@@ -59384,7 +59384,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G2035" t="n">
-        <v>1.24197256565094</v>
+        <v>1.24197244644165</v>
       </c>
       <c r="H2035" t="n">
         <v>121284</v>
@@ -59442,7 +59442,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G2037" t="n">
-        <v>1.22970616817474</v>
+        <v>1.22970604896545</v>
       </c>
       <c r="H2037" t="n">
         <v>147813</v>
@@ -59471,7 +59471,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2038" t="n">
-        <v>1.20823979377747</v>
+        <v>1.20823991298676</v>
       </c>
       <c r="H2038" t="n">
         <v>347492</v>
@@ -59529,7 +59529,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G2040" t="n">
-        <v>1.18493366241455</v>
+        <v>1.18493378162384</v>
       </c>
       <c r="H2040" t="n">
         <v>419422</v>
@@ -59558,7 +59558,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2041" t="n">
-        <v>1.17757391929626</v>
+        <v>1.17757380008698</v>
       </c>
       <c r="H2041" t="n">
         <v>173482</v>
@@ -59674,7 +59674,7 @@
         <v>2</v>
       </c>
       <c r="G2045" t="n">
-        <v>1.22663938999176</v>
+        <v>1.22663950920105</v>
       </c>
       <c r="H2045" t="n">
         <v>192257</v>
@@ -59703,7 +59703,7 @@
         <v>2</v>
       </c>
       <c r="G2046" t="n">
-        <v>1.22663938999176</v>
+        <v>1.22663950920105</v>
       </c>
       <c r="H2046" t="n">
         <v>143372</v>
@@ -59877,7 +59877,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G2052" t="n">
-        <v>1.14445471763611</v>
+        <v>1.14445459842682</v>
       </c>
       <c r="H2052" t="n">
         <v>273497</v>
@@ -59935,7 +59935,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G2054" t="n">
-        <v>1.13832128047943</v>
+        <v>1.13832139968872</v>
       </c>
       <c r="H2054" t="n">
         <v>321687</v>
@@ -59993,7 +59993,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G2056" t="n">
-        <v>1.13832128047943</v>
+        <v>1.13832139968872</v>
       </c>
       <c r="H2056" t="n">
         <v>67363</v>
@@ -60022,7 +60022,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G2057" t="n">
-        <v>1.14200127124786</v>
+        <v>1.14200139045715</v>
       </c>
       <c r="H2057" t="n">
         <v>174498</v>
@@ -60051,7 +60051,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G2058" t="n">
-        <v>1.15181457996368</v>
+        <v>1.15181446075439</v>
       </c>
       <c r="H2058" t="n">
         <v>68871</v>
@@ -60080,7 +60080,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2059" t="n">
-        <v>1.13464140892029</v>
+        <v>1.13464152812958</v>
       </c>
       <c r="H2059" t="n">
         <v>125743</v>
@@ -60138,7 +60138,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2061" t="n">
-        <v>1.13464140892029</v>
+        <v>1.13464152812958</v>
       </c>
       <c r="H2061" t="n">
         <v>209670</v>
@@ -60225,7 +60225,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2064" t="n">
-        <v>1.12850844860077</v>
+        <v>1.12850832939148</v>
       </c>
       <c r="H2064" t="n">
         <v>58646</v>
@@ -60283,7 +60283,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G2066" t="n">
-        <v>1.1579475402832</v>
+        <v>1.15794765949249</v>
       </c>
       <c r="H2066" t="n">
         <v>230384</v>
@@ -60544,7 +60544,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2075" t="n">
-        <v>1.25730538368225</v>
+        <v>1.25730550289154</v>
       </c>
       <c r="H2075" t="n">
         <v>391092</v>
@@ -60573,7 +60573,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G2076" t="n">
-        <v>1.70502889156342</v>
+        <v>1.70502877235413</v>
       </c>
       <c r="H2076" t="n">
         <v>5087915</v>
@@ -60660,7 +60660,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2079" t="n">
-        <v>1.94422352313995</v>
+        <v>1.94422364234924</v>
       </c>
       <c r="H2079" t="n">
         <v>1370361</v>
@@ -60689,7 +60689,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G2080" t="n">
-        <v>1.89822459220886</v>
+        <v>1.89822471141815</v>
       </c>
       <c r="H2080" t="n">
         <v>851748</v>
@@ -60718,7 +60718,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G2081" t="n">
-        <v>1.87675833702087</v>
+        <v>1.87675857543945</v>
       </c>
       <c r="H2081" t="n">
         <v>677611</v>
@@ -60776,7 +60776,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G2083" t="n">
-        <v>1.83075940608978</v>
+        <v>1.83075928688049</v>
       </c>
       <c r="H2083" t="n">
         <v>364095</v>
@@ -60805,7 +60805,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G2084" t="n">
-        <v>1.7970267534256</v>
+        <v>1.79702687263489</v>
       </c>
       <c r="H2084" t="n">
         <v>366785</v>
@@ -60892,7 +60892,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G2087" t="n">
-        <v>1.84302580356598</v>
+        <v>1.84302592277527</v>
       </c>
       <c r="H2087" t="n">
         <v>693240</v>
@@ -60950,7 +60950,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2089" t="n">
-        <v>1.90129125118256</v>
+        <v>1.90129113197327</v>
       </c>
       <c r="H2089" t="n">
         <v>477509</v>
@@ -60979,7 +60979,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2090" t="n">
-        <v>1.90129125118256</v>
+        <v>1.90129113197327</v>
       </c>
       <c r="H2090" t="n">
         <v>391550</v>
@@ -61008,7 +61008,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2091" t="n">
-        <v>1.91355752944946</v>
+        <v>1.91355764865875</v>
       </c>
       <c r="H2091" t="n">
         <v>668620</v>
@@ -61153,7 +61153,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G2096" t="n">
-        <v>1.92889046669006</v>
+        <v>1.92889058589935</v>
       </c>
       <c r="H2096" t="n">
         <v>185807</v>
@@ -61182,7 +61182,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2097" t="n">
-        <v>1.99942231178284</v>
+        <v>1.99942219257355</v>
       </c>
       <c r="H2097" t="n">
         <v>632586</v>
@@ -61240,7 +61240,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G2099" t="n">
-        <v>1.95955646038055</v>
+        <v>1.95955657958984</v>
       </c>
       <c r="H2099" t="n">
         <v>309057</v>
@@ -61443,7 +61443,7 @@
         <v>3.25</v>
       </c>
       <c r="G2106" t="n">
-        <v>1.99328911304474</v>
+        <v>1.99328923225403</v>
       </c>
       <c r="H2106" t="n">
         <v>313415</v>
@@ -61472,7 +61472,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2107" t="n">
-        <v>2.00555539131165</v>
+        <v>2.00555562973022</v>
       </c>
       <c r="H2107" t="n">
         <v>289188</v>
@@ -61501,7 +61501,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G2108" t="n">
-        <v>1.95342338085175</v>
+        <v>1.95342326164246</v>
       </c>
       <c r="H2108" t="n">
         <v>261617</v>
@@ -61530,7 +61530,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G2109" t="n">
-        <v>1.95342338085175</v>
+        <v>1.95342326164246</v>
       </c>
       <c r="H2109" t="n">
         <v>253803</v>
@@ -61559,7 +61559,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G2110" t="n">
-        <v>1.92889046669006</v>
+        <v>1.92889058589935</v>
       </c>
       <c r="H2110" t="n">
         <v>187344</v>
@@ -61588,7 +61588,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2111" t="n">
-        <v>1.92582404613495</v>
+        <v>1.92582392692566</v>
       </c>
       <c r="H2111" t="n">
         <v>213530</v>
@@ -61646,7 +61646,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2113" t="n">
-        <v>1.88902461528778</v>
+        <v>1.88902485370636</v>
       </c>
       <c r="H2113" t="n">
         <v>498070</v>
@@ -61675,7 +61675,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2114" t="n">
-        <v>1.88902461528778</v>
+        <v>1.88902485370636</v>
       </c>
       <c r="H2114" t="n">
         <v>245321</v>
@@ -61733,7 +61733,7 @@
         <v>3</v>
       </c>
       <c r="G2116" t="n">
-        <v>1.83995914459229</v>
+        <v>1.839959025383</v>
       </c>
       <c r="H2116" t="n">
         <v>604364</v>
@@ -61820,7 +61820,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G2119" t="n">
-        <v>1.80622661113739</v>
+        <v>1.8062264919281</v>
       </c>
       <c r="H2119" t="n">
         <v>193216</v>
@@ -61878,7 +61878,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G2121" t="n">
-        <v>1.7602276802063</v>
+        <v>1.76022756099701</v>
       </c>
       <c r="H2121" t="n">
         <v>400903</v>
@@ -79951,6 +79951,64 @@
         <v>476763</v>
       </c>
       <c r="I2744" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2745">
+      <c r="A2745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2745" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2745" t="n">
+        <v>1.98000001907349</v>
+      </c>
+      <c r="D2745" t="n">
+        <v>1.98000001907349</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>1.93799996376038</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>1.94599997997284</v>
+      </c>
+      <c r="G2745" t="n">
+        <v>1.94599997997284</v>
+      </c>
+      <c r="H2745" t="n">
+        <v>183746</v>
+      </c>
+      <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>1.94599997997284</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>2.00999999046326</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>1.94200003147125</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>272103</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SGF.MI.xlsx
+++ b/data/SGF.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2" t="n">
-        <v>1.25117218494415</v>
+        <v>1.25117230415344</v>
       </c>
       <c r="H2" t="n">
         <v>208771</v>
@@ -456,7 +456,7 @@
         <v>2.00399994850159</v>
       </c>
       <c r="G3" t="n">
-        <v>1.22909259796143</v>
+        <v>1.22909271717072</v>
       </c>
       <c r="H3" t="n">
         <v>161308</v>
@@ -485,7 +485,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G4" t="n">
-        <v>1.20210671424866</v>
+        <v>1.20210659503937</v>
       </c>
       <c r="H4" t="n">
         <v>263865</v>
@@ -514,7 +514,7 @@
         <v>1.93299996852875</v>
       </c>
       <c r="G5" t="n">
-        <v>1.18554711341858</v>
+        <v>1.18554699420929</v>
       </c>
       <c r="H5" t="n">
         <v>335985</v>
@@ -688,7 +688,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0855758190155</v>
+        <v>1.08557593822479</v>
       </c>
       <c r="H11" t="n">
         <v>331594</v>
@@ -717,7 +717,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G12" t="n">
-        <v>1.05613660812378</v>
+        <v>1.05613648891449</v>
       </c>
       <c r="H12" t="n">
         <v>445686</v>
@@ -833,7 +833,7 @@
         <v>1.7610000371933</v>
       </c>
       <c r="G16" t="n">
-        <v>1.08005595207214</v>
+        <v>1.08005607128143</v>
       </c>
       <c r="H16" t="n">
         <v>396007</v>
@@ -949,7 +949,7 @@
         <v>1.692999958992</v>
       </c>
       <c r="G20" t="n">
-        <v>1.03835022449493</v>
+        <v>1.03835034370422</v>
       </c>
       <c r="H20" t="n">
         <v>324056</v>
@@ -978,7 +978,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G21" t="n">
-        <v>1.05613660812378</v>
+        <v>1.05613648891449</v>
       </c>
       <c r="H21" t="n">
         <v>130477</v>
@@ -1065,7 +1065,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G24" t="n">
-        <v>1.01075100898743</v>
+        <v>1.01075088977814</v>
       </c>
       <c r="H24" t="n">
         <v>327325</v>
@@ -1152,7 +1152,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G27" t="n">
-        <v>0.841474652290344</v>
+        <v>0.841474711894989</v>
       </c>
       <c r="H27" t="n">
         <v>327658</v>
@@ -1239,7 +1239,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G30" t="n">
-        <v>0.858647584915161</v>
+        <v>0.858647644519806</v>
       </c>
       <c r="H30" t="n">
         <v>298478</v>
@@ -1297,7 +1297,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G32" t="n">
-        <v>0.981311500072479</v>
+        <v>0.981311619281769</v>
       </c>
       <c r="H32" t="n">
         <v>168307</v>
@@ -1355,7 +1355,7 @@
         <v>1.56099998950958</v>
       </c>
       <c r="G34" t="n">
-        <v>0.957392156124115</v>
+        <v>0.957392036914825</v>
       </c>
       <c r="H34" t="n">
         <v>320159</v>
@@ -1384,7 +1384,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G35" t="n">
-        <v>0.941445708274841</v>
+        <v>0.941445767879486</v>
       </c>
       <c r="H35" t="n">
         <v>350921</v>
@@ -1413,7 +1413,7 @@
         <v>1.50399994850159</v>
       </c>
       <c r="G36" t="n">
-        <v>0.922432839870453</v>
+        <v>0.922432899475098</v>
       </c>
       <c r="H36" t="n">
         <v>200666</v>
@@ -1442,7 +1442,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G37" t="n">
-        <v>0.96291196346283</v>
+        <v>0.962912023067474</v>
       </c>
       <c r="H37" t="n">
         <v>274788</v>
@@ -1471,7 +1471,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G38" t="n">
-        <v>0.941445708274841</v>
+        <v>0.941445767879486</v>
       </c>
       <c r="H38" t="n">
         <v>449707</v>
@@ -1529,7 +1529,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G40" t="n">
-        <v>0.910166501998901</v>
+        <v>0.910166442394257</v>
       </c>
       <c r="H40" t="n">
         <v>482847</v>
@@ -1587,7 +1587,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G42" t="n">
-        <v>0.87214070558548</v>
+        <v>0.872140765190125</v>
       </c>
       <c r="H42" t="n">
         <v>633854</v>
@@ -1616,7 +1616,7 @@
         <v>1.5</v>
       </c>
       <c r="G43" t="n">
-        <v>0.919979512691498</v>
+        <v>0.919979631900787</v>
       </c>
       <c r="H43" t="n">
         <v>841811</v>
@@ -1645,7 +1645,7 @@
         <v>1.5789999961853</v>
       </c>
       <c r="G44" t="n">
-        <v>0.968431830406189</v>
+        <v>0.968431890010834</v>
       </c>
       <c r="H44" t="n">
         <v>563184</v>
@@ -1819,7 +1819,7 @@
         <v>1.54700005054474</v>
       </c>
       <c r="G50" t="n">
-        <v>0.948805630207062</v>
+        <v>0.948805689811707</v>
       </c>
       <c r="H50" t="n">
         <v>402246</v>
@@ -1848,7 +1848,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G51" t="n">
-        <v>0.986218154430389</v>
+        <v>0.986218094825745</v>
       </c>
       <c r="H51" t="n">
         <v>297628</v>
@@ -1935,7 +1935,7 @@
         <v>1.58299994468689</v>
       </c>
       <c r="G54" t="n">
-        <v>0.970885038375854</v>
+        <v>0.970885157585144</v>
       </c>
       <c r="H54" t="n">
         <v>320346</v>
@@ -1993,7 +1993,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G56" t="n">
-        <v>0.917526304721832</v>
+        <v>0.917526364326477</v>
       </c>
       <c r="H56" t="n">
         <v>1000501</v>
@@ -2022,7 +2022,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G57" t="n">
-        <v>0.926112830638885</v>
+        <v>0.926112771034241</v>
       </c>
       <c r="H57" t="n">
         <v>413338</v>
@@ -2051,7 +2051,7 @@
         <v>1.5</v>
       </c>
       <c r="G58" t="n">
-        <v>0.919979512691498</v>
+        <v>0.919979631900787</v>
       </c>
       <c r="H58" t="n">
         <v>214751</v>
@@ -2080,7 +2080,7 @@
         <v>1.4210000038147</v>
       </c>
       <c r="G59" t="n">
-        <v>0.871527373790741</v>
+        <v>0.871527314186096</v>
       </c>
       <c r="H59" t="n">
         <v>857202</v>
@@ -2109,7 +2109,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G60" t="n">
-        <v>0.853741109371185</v>
+        <v>0.853741049766541</v>
       </c>
       <c r="H60" t="n">
         <v>330575</v>
@@ -2138,7 +2138,7 @@
         <v>1.34300005435944</v>
       </c>
       <c r="G61" t="n">
-        <v>0.823688447475433</v>
+        <v>0.823688387870789</v>
       </c>
       <c r="H61" t="n">
         <v>330707</v>
@@ -2196,7 +2196,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G63" t="n">
-        <v>0.867234110832214</v>
+        <v>0.867234170436859</v>
       </c>
       <c r="H63" t="n">
         <v>267980</v>
@@ -2283,7 +2283,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G66" t="n">
-        <v>0.815715253353119</v>
+        <v>0.815715193748474</v>
       </c>
       <c r="H66" t="n">
         <v>496873</v>
@@ -2312,7 +2312,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G67" t="n">
-        <v>0.818781852722168</v>
+        <v>0.818781912326813</v>
       </c>
       <c r="H67" t="n">
         <v>147823</v>
@@ -2341,7 +2341,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G68" t="n">
-        <v>0.794249057769775</v>
+        <v>0.79424911737442</v>
       </c>
       <c r="H68" t="n">
         <v>210357</v>
@@ -2370,7 +2370,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G69" t="n">
-        <v>0.832888185977936</v>
+        <v>0.832888245582581</v>
       </c>
       <c r="H69" t="n">
         <v>207067</v>
@@ -2486,7 +2486,7 @@
         <v>1.43299996852875</v>
       </c>
       <c r="G73" t="n">
-        <v>0.878887236118317</v>
+        <v>0.878887116909027</v>
       </c>
       <c r="H73" t="n">
         <v>194805</v>
@@ -2544,7 +2544,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G75" t="n">
-        <v>0.89544677734375</v>
+        <v>0.895446836948395</v>
       </c>
       <c r="H75" t="n">
         <v>124767</v>
@@ -2573,7 +2573,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G76" t="n">
-        <v>0.852514386177063</v>
+        <v>0.852514445781708</v>
       </c>
       <c r="H76" t="n">
         <v>774434</v>
@@ -2602,7 +2602,7 @@
         <v>1.43099999427795</v>
       </c>
       <c r="G77" t="n">
-        <v>0.877660512924194</v>
+        <v>0.877660632133484</v>
       </c>
       <c r="H77" t="n">
         <v>342413</v>
@@ -2631,7 +2631,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G78" t="n">
-        <v>0.875207304954529</v>
+        <v>0.875207364559174</v>
       </c>
       <c r="H78" t="n">
         <v>207294</v>
@@ -2689,7 +2689,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G80" t="n">
-        <v>0.87214070558548</v>
+        <v>0.872140765190125</v>
       </c>
       <c r="H80" t="n">
         <v>27237</v>
@@ -2718,7 +2718,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G81" t="n">
-        <v>0.868460774421692</v>
+        <v>0.868460714817047</v>
       </c>
       <c r="H81" t="n">
         <v>105201</v>
@@ -2747,7 +2747,7 @@
         <v>1.5</v>
       </c>
       <c r="G82" t="n">
-        <v>0.919979512691498</v>
+        <v>0.919979631900787</v>
       </c>
       <c r="H82" t="n">
         <v>823016</v>
@@ -2776,7 +2776,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G83" t="n">
-        <v>0.943285763263702</v>
+        <v>0.943285703659058</v>
       </c>
       <c r="H83" t="n">
         <v>666476</v>
@@ -2863,7 +2863,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G86" t="n">
-        <v>0.951258957386017</v>
+        <v>0.951258897781372</v>
       </c>
       <c r="H86" t="n">
         <v>426890</v>
@@ -2892,7 +2892,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G87" t="n">
-        <v>0.951258957386017</v>
+        <v>0.951258897781372</v>
       </c>
       <c r="H87" t="n">
         <v>290985</v>
@@ -2921,7 +2921,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G88" t="n">
-        <v>0.951258957386017</v>
+        <v>0.951258897781372</v>
       </c>
       <c r="H88" t="n">
         <v>302509</v>
@@ -2950,7 +2950,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G89" t="n">
-        <v>0.951258957386017</v>
+        <v>0.951258897781372</v>
       </c>
       <c r="H89" t="n">
         <v>223150</v>
@@ -3008,7 +3008,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G91" t="n">
-        <v>0.938379287719727</v>
+        <v>0.938379108905792</v>
       </c>
       <c r="H91" t="n">
         <v>93150</v>
@@ -3037,7 +3037,7 @@
         <v>1.54700005054474</v>
       </c>
       <c r="G92" t="n">
-        <v>0.948805630207062</v>
+        <v>0.948805689811707</v>
       </c>
       <c r="H92" t="n">
         <v>98852</v>
@@ -3066,7 +3066,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G93" t="n">
-        <v>0.978245079517365</v>
+        <v>0.978244960308075</v>
       </c>
       <c r="H93" t="n">
         <v>347619</v>
@@ -3095,7 +3095,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G94" t="n">
-        <v>0.992351412773132</v>
+        <v>0.992351353168488</v>
       </c>
       <c r="H94" t="n">
         <v>320086</v>
@@ -3211,7 +3211,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G98" t="n">
-        <v>0.943285763263702</v>
+        <v>0.943285703659058</v>
       </c>
       <c r="H98" t="n">
         <v>263085</v>
@@ -3240,7 +3240,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G99" t="n">
-        <v>0.935312569141388</v>
+        <v>0.935312628746033</v>
       </c>
       <c r="H99" t="n">
         <v>196453</v>
@@ -3269,7 +3269,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G100" t="n">
-        <v>0.927339434623718</v>
+        <v>0.927339375019073</v>
       </c>
       <c r="H100" t="n">
         <v>141573</v>
@@ -3298,7 +3298,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G101" t="n">
-        <v>0.953712105751038</v>
+        <v>0.953712165355682</v>
       </c>
       <c r="H101" t="n">
         <v>438231</v>
@@ -3414,7 +3414,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G105" t="n">
-        <v>1.12360179424286</v>
+        <v>1.12360167503357</v>
       </c>
       <c r="H105" t="n">
         <v>517266</v>
@@ -3501,7 +3501,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G108" t="n">
-        <v>1.03037703037262</v>
+        <v>1.03037714958191</v>
       </c>
       <c r="H108" t="n">
         <v>290532</v>
@@ -3530,7 +3530,7 @@
         <v>1.64900004863739</v>
       </c>
       <c r="G109" t="n">
-        <v>1.01136434078217</v>
+        <v>1.01136422157288</v>
       </c>
       <c r="H109" t="n">
         <v>279197</v>
@@ -3559,7 +3559,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G110" t="n">
-        <v>0.999711096286774</v>
+        <v>0.999711155891418</v>
       </c>
       <c r="H110" t="n">
         <v>236211</v>
@@ -3617,7 +3617,7 @@
         <v>1.625</v>
       </c>
       <c r="G112" t="n">
-        <v>0.996644616127014</v>
+        <v>0.996644556522369</v>
       </c>
       <c r="H112" t="n">
         <v>276657</v>
@@ -3646,7 +3646,7 @@
         <v>1.60099995136261</v>
       </c>
       <c r="G113" t="n">
-        <v>0.981924831867218</v>
+        <v>0.981924891471863</v>
       </c>
       <c r="H113" t="n">
         <v>124731</v>
@@ -3675,7 +3675,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G114" t="n">
-        <v>0.935312569141388</v>
+        <v>0.935312628746033</v>
       </c>
       <c r="H114" t="n">
         <v>354806</v>
@@ -3704,7 +3704,7 @@
         <v>1.39300000667572</v>
       </c>
       <c r="G115" t="n">
-        <v>0.854354381561279</v>
+        <v>0.854354321956635</v>
       </c>
       <c r="H115" t="n">
         <v>1016663</v>
@@ -3733,7 +3733,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G116" t="n">
-        <v>0.806515514850616</v>
+        <v>0.806515455245972</v>
       </c>
       <c r="H116" t="n">
         <v>596787</v>
@@ -3820,7 +3820,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G119" t="n">
-        <v>0.792409062385559</v>
+        <v>0.792409121990204</v>
       </c>
       <c r="H119" t="n">
         <v>527410</v>
@@ -3849,7 +3849,7 @@
         <v>1.36899995803833</v>
       </c>
       <c r="G120" t="n">
-        <v>0.839634656906128</v>
+        <v>0.839634716510773</v>
       </c>
       <c r="H120" t="n">
         <v>513418</v>
@@ -3907,7 +3907,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G122" t="n">
-        <v>0.875207304954529</v>
+        <v>0.875207364559174</v>
       </c>
       <c r="H122" t="n">
         <v>340422</v>
@@ -3994,7 +3994,7 @@
         <v>1.24800002574921</v>
       </c>
       <c r="G125" t="n">
-        <v>0.765422999858856</v>
+        <v>0.765422940254211</v>
       </c>
       <c r="H125" t="n">
         <v>532951</v>
@@ -4052,7 +4052,7 @@
         <v>1.25699996948242</v>
       </c>
       <c r="G127" t="n">
-        <v>0.77094292640686</v>
+        <v>0.770942807197571</v>
       </c>
       <c r="H127" t="n">
         <v>355957</v>
@@ -4081,7 +4081,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G128" t="n">
-        <v>0.806515514850616</v>
+        <v>0.806515455245972</v>
       </c>
       <c r="H128" t="n">
         <v>370971</v>
@@ -4168,7 +4168,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G131" t="n">
-        <v>0.725557267665863</v>
+        <v>0.725557208061218</v>
       </c>
       <c r="H131" t="n">
         <v>634478</v>
@@ -4284,7 +4284,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G135" t="n">
-        <v>0.771556198596954</v>
+        <v>0.771556258201599</v>
       </c>
       <c r="H135" t="n">
         <v>325977</v>
@@ -4342,7 +4342,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G137" t="n">
-        <v>0.803448796272278</v>
+        <v>0.803448855876923</v>
       </c>
       <c r="H137" t="n">
         <v>159758</v>
@@ -4429,7 +4429,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G140" t="n">
-        <v>0.858647584915161</v>
+        <v>0.858647644519806</v>
       </c>
       <c r="H140" t="n">
         <v>257624</v>
@@ -4487,7 +4487,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G142" t="n">
-        <v>0.861100912094116</v>
+        <v>0.861101031303406</v>
       </c>
       <c r="H142" t="n">
         <v>133440</v>
@@ -4603,7 +4603,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G146" t="n">
-        <v>0.884407043457031</v>
+        <v>0.884407103061676</v>
       </c>
       <c r="H146" t="n">
         <v>428209</v>
@@ -4661,7 +4661,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G148" t="n">
-        <v>0.935312569141388</v>
+        <v>0.935312628746033</v>
       </c>
       <c r="H148" t="n">
         <v>421354</v>
@@ -4690,7 +4690,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G149" t="n">
-        <v>0.932246029376984</v>
+        <v>0.932245969772339</v>
       </c>
       <c r="H149" t="n">
         <v>325924</v>
@@ -4806,7 +4806,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G153" t="n">
-        <v>0.956778824329376</v>
+        <v>0.956778764724731</v>
       </c>
       <c r="H153" t="n">
         <v>149124</v>
@@ -4864,7 +4864,7 @@
         <v>1.62899994850159</v>
       </c>
       <c r="G155" t="n">
-        <v>0.999097764492035</v>
+        <v>0.99909782409668</v>
       </c>
       <c r="H155" t="n">
         <v>261420</v>
@@ -4980,7 +4980,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G159" t="n">
-        <v>1.01749742031097</v>
+        <v>1.01749753952026</v>
       </c>
       <c r="H159" t="n">
         <v>131636</v>
@@ -5067,7 +5067,7 @@
         <v>1.66100001335144</v>
       </c>
       <c r="G162" t="n">
-        <v>1.01872420310974</v>
+        <v>1.01872408390045</v>
       </c>
       <c r="H162" t="n">
         <v>160844</v>
@@ -5096,7 +5096,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G163" t="n">
-        <v>1.00461769104004</v>
+        <v>1.00461781024933</v>
       </c>
       <c r="H163" t="n">
         <v>76999</v>
@@ -5125,7 +5125,7 @@
         <v>1.66100001335144</v>
       </c>
       <c r="G164" t="n">
-        <v>1.01872420310974</v>
+        <v>1.01872408390045</v>
       </c>
       <c r="H164" t="n">
         <v>78461</v>
@@ -5154,7 +5154,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G165" t="n">
-        <v>1.0365104675293</v>
+        <v>1.03651034832001</v>
       </c>
       <c r="H165" t="n">
         <v>295809</v>
@@ -5415,7 +5415,7 @@
         <v>1.75800001621246</v>
       </c>
       <c r="G174" t="n">
-        <v>1.07821619510651</v>
+        <v>1.07821607589722</v>
       </c>
       <c r="H174" t="n">
         <v>614354</v>
@@ -5502,7 +5502,7 @@
         <v>1.77699995040894</v>
       </c>
       <c r="G177" t="n">
-        <v>1.08986902236938</v>
+        <v>1.08986914157867</v>
       </c>
       <c r="H177" t="n">
         <v>220355</v>
@@ -5560,7 +5560,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G179" t="n">
-        <v>1.08250939846039</v>
+        <v>1.0825092792511</v>
       </c>
       <c r="H179" t="n">
         <v>486372</v>
@@ -5763,7 +5763,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G186" t="n">
-        <v>1.06717622280121</v>
+        <v>1.0671763420105</v>
       </c>
       <c r="H186" t="n">
         <v>130158</v>
@@ -5879,7 +5879,7 @@
         <v>1.78299999237061</v>
       </c>
       <c r="G190" t="n">
-        <v>1.09354901313782</v>
+        <v>1.09354913234711</v>
       </c>
       <c r="H190" t="n">
         <v>136706</v>
@@ -5908,7 +5908,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G191" t="n">
-        <v>1.1101086139679</v>
+        <v>1.11010873317719</v>
       </c>
       <c r="H191" t="n">
         <v>193032</v>
@@ -5937,7 +5937,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G192" t="n">
-        <v>1.10397553443909</v>
+        <v>1.1039754152298</v>
       </c>
       <c r="H192" t="n">
         <v>122359</v>
@@ -5966,7 +5966,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G193" t="n">
-        <v>1.10397553443909</v>
+        <v>1.1039754152298</v>
       </c>
       <c r="H193" t="n">
         <v>198036</v>
@@ -6024,7 +6024,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G195" t="n">
-        <v>1.09416234493256</v>
+        <v>1.09416246414185</v>
       </c>
       <c r="H195" t="n">
         <v>227267</v>
@@ -6082,7 +6082,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G197" t="n">
-        <v>1.10397553443909</v>
+        <v>1.1039754152298</v>
       </c>
       <c r="H197" t="n">
         <v>163067</v>
@@ -6111,7 +6111,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G198" t="n">
-        <v>1.0978422164917</v>
+        <v>1.09784233570099</v>
       </c>
       <c r="H198" t="n">
         <v>97852</v>
@@ -6140,7 +6140,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G199" t="n">
-        <v>1.10152220726013</v>
+        <v>1.10152232646942</v>
       </c>
       <c r="H199" t="n">
         <v>60811</v>
@@ -6169,7 +6169,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>1.0978422164917</v>
+        <v>1.09784233570099</v>
       </c>
       <c r="H200" t="n">
         <v>71260</v>
@@ -6256,7 +6256,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G203" t="n">
-        <v>1.0886424779892</v>
+        <v>1.08864259719849</v>
       </c>
       <c r="H203" t="n">
         <v>66057</v>
@@ -6285,7 +6285,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G204" t="n">
-        <v>1.10090899467468</v>
+        <v>1.10090887546539</v>
       </c>
       <c r="H204" t="n">
         <v>98997</v>
@@ -6343,7 +6343,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G206" t="n">
-        <v>1.09048247337341</v>
+        <v>1.0904825925827</v>
       </c>
       <c r="H206" t="n">
         <v>120993</v>
@@ -6401,7 +6401,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G208" t="n">
-        <v>1.10152220726013</v>
+        <v>1.10152232646942</v>
       </c>
       <c r="H208" t="n">
         <v>71337</v>
@@ -6459,7 +6459,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G210" t="n">
-        <v>1.18370699882507</v>
+        <v>1.18370711803436</v>
       </c>
       <c r="H210" t="n">
         <v>1793350</v>
@@ -6517,7 +6517,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G212" t="n">
-        <v>1.25117218494415</v>
+        <v>1.25117230415344</v>
       </c>
       <c r="H212" t="n">
         <v>455701</v>
@@ -6633,7 +6633,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G216" t="n">
-        <v>1.22050619125366</v>
+        <v>1.22050631046295</v>
       </c>
       <c r="H216" t="n">
         <v>490241</v>
@@ -6662,7 +6662,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G217" t="n">
-        <v>1.28551816940308</v>
+        <v>1.28551805019379</v>
       </c>
       <c r="H217" t="n">
         <v>339279</v>
@@ -6691,7 +6691,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G218" t="n">
-        <v>1.26466524600983</v>
+        <v>1.26466536521912</v>
       </c>
       <c r="H218" t="n">
         <v>379339</v>
@@ -6720,7 +6720,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G219" t="n">
-        <v>1.29165136814117</v>
+        <v>1.29165124893188</v>
       </c>
       <c r="H219" t="n">
         <v>262875</v>
@@ -6749,7 +6749,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G220" t="n">
-        <v>1.24503910541534</v>
+        <v>1.24503898620605</v>
       </c>
       <c r="H220" t="n">
         <v>521123</v>
@@ -6807,7 +6807,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G222" t="n">
-        <v>1.24135899543762</v>
+        <v>1.24135911464691</v>
       </c>
       <c r="H222" t="n">
         <v>447289</v>
@@ -6836,7 +6836,7 @@
         <v>2.07399988174438</v>
       </c>
       <c r="G223" t="n">
-        <v>1.27202498912811</v>
+        <v>1.2720251083374</v>
       </c>
       <c r="H223" t="n">
         <v>256250</v>
@@ -6865,7 +6865,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G224" t="n">
-        <v>1.3075977563858</v>
+        <v>1.30759763717651</v>
       </c>
       <c r="H224" t="n">
         <v>602971</v>
@@ -6952,7 +6952,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G227" t="n">
-        <v>1.32477080821991</v>
+        <v>1.32477056980133</v>
       </c>
       <c r="H227" t="n">
         <v>203471</v>
@@ -6981,7 +6981,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G228" t="n">
-        <v>1.32477080821991</v>
+        <v>1.32477056980133</v>
       </c>
       <c r="H228" t="n">
         <v>299354</v>
@@ -7010,7 +7010,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G229" t="n">
-        <v>1.33090388774872</v>
+        <v>1.33090376853943</v>
       </c>
       <c r="H229" t="n">
         <v>710066</v>
@@ -7039,7 +7039,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G230" t="n">
-        <v>1.32354390621185</v>
+        <v>1.32354402542114</v>
       </c>
       <c r="H230" t="n">
         <v>328805</v>
@@ -7068,7 +7068,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G231" t="n">
-        <v>1.29165136814117</v>
+        <v>1.29165124893188</v>
       </c>
       <c r="H231" t="n">
         <v>425513</v>
@@ -7213,7 +7213,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G236" t="n">
-        <v>1.28797125816345</v>
+        <v>1.28797137737274</v>
       </c>
       <c r="H236" t="n">
         <v>205772</v>
@@ -7242,7 +7242,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G237" t="n">
-        <v>1.28797125816345</v>
+        <v>1.28797137737274</v>
       </c>
       <c r="H237" t="n">
         <v>141863</v>
@@ -7474,7 +7474,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G245" t="n">
-        <v>1.47687387466431</v>
+        <v>1.4768739938736</v>
       </c>
       <c r="H245" t="n">
         <v>477131</v>
@@ -7648,7 +7648,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G251" t="n">
-        <v>1.50263333320618</v>
+        <v>1.50263321399689</v>
       </c>
       <c r="H251" t="n">
         <v>163694</v>
@@ -7677,7 +7677,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G252" t="n">
-        <v>1.49650013446808</v>
+        <v>1.49650025367737</v>
       </c>
       <c r="H252" t="n">
         <v>188904</v>
@@ -7735,7 +7735,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G254" t="n">
-        <v>1.47687387466431</v>
+        <v>1.4768739938736</v>
       </c>
       <c r="H254" t="n">
         <v>139637</v>
@@ -7793,7 +7793,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G256" t="n">
-        <v>1.47810065746307</v>
+        <v>1.47810053825378</v>
       </c>
       <c r="H256" t="n">
         <v>141019</v>
@@ -7909,7 +7909,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G260" t="n">
-        <v>1.58113837242126</v>
+        <v>1.58113825321198</v>
       </c>
       <c r="H260" t="n">
         <v>206628</v>
@@ -8025,7 +8025,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G264" t="n">
-        <v>1.5737783908844</v>
+        <v>1.57377851009369</v>
       </c>
       <c r="H264" t="n">
         <v>102370</v>
@@ -8083,7 +8083,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G266" t="n">
-        <v>1.55169892311096</v>
+        <v>1.55169880390167</v>
       </c>
       <c r="H266" t="n">
         <v>242727</v>
@@ -8141,7 +8141,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G268" t="n">
-        <v>1.57868492603302</v>
+        <v>1.57868504524231</v>
       </c>
       <c r="H268" t="n">
         <v>126004</v>
@@ -8199,7 +8199,7 @@
         <v>2.5</v>
       </c>
       <c r="G270" t="n">
-        <v>1.53329944610596</v>
+        <v>1.53329932689667</v>
       </c>
       <c r="H270" t="n">
         <v>124510</v>
@@ -8228,7 +8228,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G271" t="n">
-        <v>1.5259393453598</v>
+        <v>1.52593958377838</v>
       </c>
       <c r="H271" t="n">
         <v>154741</v>
@@ -8257,7 +8257,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G272" t="n">
-        <v>1.5136730670929</v>
+        <v>1.51367294788361</v>
       </c>
       <c r="H272" t="n">
         <v>102900</v>
@@ -8286,7 +8286,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G273" t="n">
-        <v>1.49527359008789</v>
+        <v>1.4952734708786</v>
       </c>
       <c r="H273" t="n">
         <v>101503</v>
@@ -8315,7 +8315,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G274" t="n">
-        <v>1.53084599971771</v>
+        <v>1.53084588050842</v>
       </c>
       <c r="H274" t="n">
         <v>132938</v>
@@ -8373,7 +8373,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G276" t="n">
-        <v>1.5259393453598</v>
+        <v>1.52593958377838</v>
       </c>
       <c r="H276" t="n">
         <v>121968</v>
@@ -8402,7 +8402,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G277" t="n">
-        <v>1.47687387466431</v>
+        <v>1.4768739938736</v>
       </c>
       <c r="H277" t="n">
         <v>113941</v>
@@ -8460,7 +8460,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G279" t="n">
-        <v>1.34930348396301</v>
+        <v>1.34930336475372</v>
       </c>
       <c r="H279" t="n">
         <v>403808</v>
@@ -8489,7 +8489,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G280" t="n">
-        <v>1.4167685508728</v>
+        <v>1.41676843166351</v>
       </c>
       <c r="H280" t="n">
         <v>233709</v>
@@ -8576,7 +8576,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G283" t="n">
-        <v>1.35543668270111</v>
+        <v>1.35543656349182</v>
       </c>
       <c r="H283" t="n">
         <v>155089</v>
@@ -8605,7 +8605,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G284" t="n">
-        <v>1.27079844474792</v>
+        <v>1.27079856395721</v>
       </c>
       <c r="H284" t="n">
         <v>532104</v>
@@ -8692,7 +8692,7 @@
         <v>2.12400007247925</v>
       </c>
       <c r="G287" t="n">
-        <v>1.30269122123718</v>
+        <v>1.30269110202789</v>
       </c>
       <c r="H287" t="n">
         <v>326183</v>
@@ -8779,7 +8779,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G290" t="n">
-        <v>1.39100897312164</v>
+        <v>1.39100909233093</v>
       </c>
       <c r="H290" t="n">
         <v>208243</v>
@@ -8837,7 +8837,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G292" t="n">
-        <v>1.38732933998108</v>
+        <v>1.38732922077179</v>
       </c>
       <c r="H292" t="n">
         <v>78586</v>
@@ -8866,7 +8866,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G293" t="n">
-        <v>1.39959561824799</v>
+        <v>1.39959573745728</v>
       </c>
       <c r="H293" t="n">
         <v>84346</v>
@@ -8953,7 +8953,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G296" t="n">
-        <v>1.4106353521347</v>
+        <v>1.41063547134399</v>
       </c>
       <c r="H296" t="n">
         <v>197826</v>
@@ -8982,7 +8982,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G297" t="n">
-        <v>1.39591562747955</v>
+        <v>1.39591586589813</v>
       </c>
       <c r="H297" t="n">
         <v>195070</v>
@@ -9040,7 +9040,7 @@
         <v>2.67199993133545</v>
       </c>
       <c r="G299" t="n">
-        <v>1.63879024982452</v>
+        <v>1.63879036903381</v>
       </c>
       <c r="H299" t="n">
         <v>1636915</v>
@@ -9214,7 +9214,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G305" t="n">
-        <v>1.79825329780579</v>
+        <v>1.79825341701508</v>
       </c>
       <c r="H305" t="n">
         <v>673534</v>
@@ -9243,7 +9243,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G306" t="n">
-        <v>1.7540944814682</v>
+        <v>1.75409436225891</v>
       </c>
       <c r="H306" t="n">
         <v>548849</v>
@@ -9272,7 +9272,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G307" t="n">
-        <v>1.7908935546875</v>
+        <v>1.79089367389679</v>
       </c>
       <c r="H307" t="n">
         <v>670021</v>
@@ -9330,7 +9330,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>1.77862727642059</v>
+        <v>1.77862739562988</v>
       </c>
       <c r="H309" t="n">
         <v>373278</v>
@@ -9359,7 +9359,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G310" t="n">
-        <v>1.7908935546875</v>
+        <v>1.79089367389679</v>
       </c>
       <c r="H310" t="n">
         <v>165055</v>
@@ -9388,7 +9388,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G311" t="n">
-        <v>1.8031599521637</v>
+        <v>1.80316007137299</v>
       </c>
       <c r="H311" t="n">
         <v>257588</v>
@@ -9417,7 +9417,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G312" t="n">
-        <v>1.82523965835571</v>
+        <v>1.82523953914642</v>
       </c>
       <c r="H312" t="n">
         <v>318543</v>
@@ -9504,7 +9504,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G315" t="n">
-        <v>2.01046228408813</v>
+        <v>2.01046204566956</v>
       </c>
       <c r="H315" t="n">
         <v>892554</v>
@@ -9562,7 +9562,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G317" t="n">
-        <v>2.152752161026</v>
+        <v>2.15275239944458</v>
       </c>
       <c r="H317" t="n">
         <v>748045</v>
@@ -9591,7 +9591,7 @@
         <v>3.60199999809265</v>
       </c>
       <c r="G318" t="n">
-        <v>2.20917797088623</v>
+        <v>2.20917773246765</v>
       </c>
       <c r="H318" t="n">
         <v>1002453</v>
@@ -9620,7 +9620,7 @@
         <v>3.75</v>
       </c>
       <c r="G319" t="n">
-        <v>2.29994916915894</v>
+        <v>2.29994893074036</v>
       </c>
       <c r="H319" t="n">
         <v>632837</v>
@@ -9678,7 +9678,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G321" t="n">
-        <v>2.26928305625916</v>
+        <v>2.26928281784058</v>
       </c>
       <c r="H321" t="n">
         <v>427642</v>
@@ -9823,7 +9823,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G326" t="n">
-        <v>2.24843001365662</v>
+        <v>2.2484302520752</v>
       </c>
       <c r="H326" t="n">
         <v>356043</v>
@@ -9881,7 +9881,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G328" t="n">
-        <v>2.24843001365662</v>
+        <v>2.2484302520752</v>
       </c>
       <c r="H328" t="n">
         <v>167124</v>
@@ -9997,7 +9997,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G332" t="n">
-        <v>2.20181798934937</v>
+        <v>2.20181775093079</v>
       </c>
       <c r="H332" t="n">
         <v>420981</v>
@@ -10055,7 +10055,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G334" t="n">
-        <v>2.33920121192932</v>
+        <v>2.3392014503479</v>
       </c>
       <c r="H334" t="n">
         <v>497655</v>
@@ -10113,7 +10113,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G336" t="n">
-        <v>2.44101238250732</v>
+        <v>2.4410126209259</v>
       </c>
       <c r="H336" t="n">
         <v>688744</v>
@@ -10200,7 +10200,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G339" t="n">
-        <v>2.72681975364685</v>
+        <v>2.72681951522827</v>
       </c>
       <c r="H339" t="n">
         <v>909516</v>
@@ -10229,7 +10229,7 @@
         <v>4.71799993515015</v>
       </c>
       <c r="G340" t="n">
-        <v>2.89364242553711</v>
+        <v>2.89364218711853</v>
       </c>
       <c r="H340" t="n">
         <v>1367684</v>
@@ -10316,7 +10316,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G343" t="n">
-        <v>2.76607227325439</v>
+        <v>2.76607203483582</v>
       </c>
       <c r="H343" t="n">
         <v>487349</v>
@@ -10403,7 +10403,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G346" t="n">
-        <v>2.90590882301331</v>
+        <v>2.90590906143188</v>
       </c>
       <c r="H346" t="n">
         <v>574193</v>
@@ -10432,7 +10432,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G347" t="n">
-        <v>2.93780159950256</v>
+        <v>2.93780112266541</v>
       </c>
       <c r="H347" t="n">
         <v>302332</v>
@@ -10548,7 +10548,7 @@
         <v>4.72399997711182</v>
       </c>
       <c r="G351" t="n">
-        <v>2.89732241630554</v>
+        <v>2.89732265472412</v>
       </c>
       <c r="H351" t="n">
         <v>476496</v>
@@ -10606,7 +10606,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G353" t="n">
-        <v>2.79796433448792</v>
+        <v>2.79796457290649</v>
       </c>
       <c r="H353" t="n">
         <v>631744</v>
@@ -10635,7 +10635,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G354" t="n">
-        <v>2.99300026893616</v>
+        <v>2.99300050735474</v>
       </c>
       <c r="H354" t="n">
         <v>1271662</v>
@@ -10693,7 +10693,7 @@
         <v>5.08500003814697</v>
       </c>
       <c r="G356" t="n">
-        <v>3.11873078346252</v>
+        <v>3.11873126029968</v>
       </c>
       <c r="H356" t="n">
         <v>1016304</v>
@@ -10751,7 +10751,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G358" t="n">
-        <v>3.21379518508911</v>
+        <v>3.21379542350769</v>
       </c>
       <c r="H358" t="n">
         <v>471503</v>
@@ -10925,7 +10925,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G364" t="n">
-        <v>3.28432726860046</v>
+        <v>3.28432703018188</v>
       </c>
       <c r="H364" t="n">
         <v>536733</v>
@@ -10954,7 +10954,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G365" t="n">
-        <v>3.1892626285553</v>
+        <v>3.18926239013672</v>
       </c>
       <c r="H365" t="n">
         <v>330140</v>
@@ -11099,7 +11099,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G370" t="n">
-        <v>2.99300026893616</v>
+        <v>2.99300050735474</v>
       </c>
       <c r="H370" t="n">
         <v>709668</v>
@@ -11331,7 +11331,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>3.2321949005127</v>
+        <v>3.23219513893127</v>
       </c>
       <c r="H378" t="n">
         <v>973335</v>
@@ -11389,7 +11389,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G380" t="n">
-        <v>3.18312954902649</v>
+        <v>3.18312931060791</v>
       </c>
       <c r="H380" t="n">
         <v>358113</v>
@@ -11476,7 +11476,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G383" t="n">
-        <v>2.92553496360779</v>
+        <v>2.92553520202637</v>
       </c>
       <c r="H383" t="n">
         <v>468801</v>
@@ -11505,7 +11505,7 @@
         <v>4.68400001525879</v>
       </c>
       <c r="G384" t="n">
-        <v>2.87278938293457</v>
+        <v>2.87278962135315</v>
       </c>
       <c r="H384" t="n">
         <v>628468</v>
@@ -11563,7 +11563,7 @@
         <v>4.5</v>
       </c>
       <c r="G386" t="n">
-        <v>2.75993895530701</v>
+        <v>2.75993871688843</v>
       </c>
       <c r="H386" t="n">
         <v>677082</v>
@@ -11621,7 +11621,7 @@
         <v>4.39799976348877</v>
       </c>
       <c r="G388" t="n">
-        <v>2.69738006591797</v>
+        <v>2.69738030433655</v>
       </c>
       <c r="H388" t="n">
         <v>498795</v>
@@ -11650,7 +11650,7 @@
         <v>4.39799976348877</v>
       </c>
       <c r="G389" t="n">
-        <v>2.69738006591797</v>
+        <v>2.69738030433655</v>
       </c>
       <c r="H389" t="n">
         <v>247421</v>
@@ -11679,7 +11679,7 @@
         <v>4.50600004196167</v>
       </c>
       <c r="G390" t="n">
-        <v>2.76361870765686</v>
+        <v>2.76361894607544</v>
       </c>
       <c r="H390" t="n">
         <v>534555</v>
@@ -11708,7 +11708,7 @@
         <v>4.72399997711182</v>
       </c>
       <c r="G391" t="n">
-        <v>2.89732241630554</v>
+        <v>2.89732265472412</v>
       </c>
       <c r="H391" t="n">
         <v>894334</v>
@@ -11737,7 +11737,7 @@
         <v>4.71799993515015</v>
       </c>
       <c r="G392" t="n">
-        <v>2.89364242553711</v>
+        <v>2.89364218711853</v>
       </c>
       <c r="H392" t="n">
         <v>334494</v>
@@ -11766,7 +11766,7 @@
         <v>4.71799993515015</v>
       </c>
       <c r="G393" t="n">
-        <v>2.89364242553711</v>
+        <v>2.89364218711853</v>
       </c>
       <c r="H393" t="n">
         <v>133281</v>
@@ -11824,7 +11824,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G395" t="n">
-        <v>2.91081547737122</v>
+        <v>2.91081523895264</v>
       </c>
       <c r="H395" t="n">
         <v>1325910</v>
@@ -11882,7 +11882,7 @@
         <v>4.62599992752075</v>
       </c>
       <c r="G397" t="n">
-        <v>2.83721709251404</v>
+        <v>2.83721685409546</v>
       </c>
       <c r="H397" t="n">
         <v>1465113</v>
@@ -11969,7 +11969,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G400" t="n">
-        <v>2.69860696792603</v>
+        <v>2.69860672950745</v>
       </c>
       <c r="H400" t="n">
         <v>689635</v>
@@ -12027,7 +12027,7 @@
         <v>4.47800016403198</v>
       </c>
       <c r="G402" t="n">
-        <v>2.74644565582275</v>
+        <v>2.74644589424133</v>
       </c>
       <c r="H402" t="n">
         <v>1187685</v>
@@ -12114,7 +12114,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G405" t="n">
-        <v>2.62500882148743</v>
+        <v>2.62500858306885</v>
       </c>
       <c r="H405" t="n">
         <v>480173</v>
@@ -12143,7 +12143,7 @@
         <v>4.2480001449585</v>
       </c>
       <c r="G406" t="n">
-        <v>2.60538244247437</v>
+        <v>2.60538220405579</v>
       </c>
       <c r="H406" t="n">
         <v>336551</v>
@@ -12230,7 +12230,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G409" t="n">
-        <v>2.5759425163269</v>
+        <v>2.57594275474548</v>
       </c>
       <c r="H409" t="n">
         <v>222579</v>
@@ -12259,7 +12259,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G410" t="n">
-        <v>2.5759425163269</v>
+        <v>2.57594275474548</v>
       </c>
       <c r="H410" t="n">
         <v>166188</v>
@@ -12346,7 +12346,7 @@
         <v>4.64799976348877</v>
       </c>
       <c r="G413" t="n">
-        <v>2.85070991516113</v>
+        <v>2.85071015357971</v>
       </c>
       <c r="H413" t="n">
         <v>1542581</v>
@@ -12404,7 +12404,7 @@
         <v>4.55800008773804</v>
       </c>
       <c r="G415" t="n">
-        <v>2.79551148414612</v>
+        <v>2.79551124572754</v>
       </c>
       <c r="H415" t="n">
         <v>440882</v>
@@ -12433,7 +12433,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G416" t="n">
-        <v>2.82127070426941</v>
+        <v>2.82127094268799</v>
       </c>
       <c r="H416" t="n">
         <v>398517</v>
@@ -12491,7 +12491,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G418" t="n">
-        <v>2.79428505897522</v>
+        <v>2.79428482055664</v>
       </c>
       <c r="H418" t="n">
         <v>184142</v>
@@ -12520,7 +12520,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G419" t="n">
-        <v>2.77588534355164</v>
+        <v>2.77588510513306</v>
       </c>
       <c r="H419" t="n">
         <v>278092</v>
@@ -12665,7 +12665,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G424" t="n">
-        <v>2.66794085502625</v>
+        <v>2.66794109344482</v>
       </c>
       <c r="H424" t="n">
         <v>323312</v>
@@ -12810,7 +12810,7 @@
         <v>4.28200006484985</v>
       </c>
       <c r="G429" t="n">
-        <v>2.62623500823975</v>
+        <v>2.62623524665833</v>
       </c>
       <c r="H429" t="n">
         <v>411427</v>
@@ -12897,7 +12897,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G432" t="n">
-        <v>2.8274040222168</v>
+        <v>2.82740426063538</v>
       </c>
       <c r="H432" t="n">
         <v>576429</v>
@@ -12926,7 +12926,7 @@
         <v>4.62200021743774</v>
       </c>
       <c r="G433" t="n">
-        <v>2.83476400375366</v>
+        <v>2.83476376533508</v>
       </c>
       <c r="H433" t="n">
         <v>437726</v>
@@ -12984,7 +12984,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G435" t="n">
-        <v>3.06966519355774</v>
+        <v>3.06966543197632</v>
       </c>
       <c r="H435" t="n">
         <v>1556069</v>
@@ -13042,7 +13042,7 @@
         <v>5</v>
       </c>
       <c r="G437" t="n">
-        <v>3.06659889221191</v>
+        <v>3.06659865379333</v>
       </c>
       <c r="H437" t="n">
         <v>542060</v>
@@ -13071,7 +13071,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G438" t="n">
-        <v>3.0727322101593</v>
+        <v>3.07273173332214</v>
       </c>
       <c r="H438" t="n">
         <v>434258</v>
@@ -13100,7 +13100,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G439" t="n">
-        <v>3.17086315155029</v>
+        <v>3.17086291313171</v>
       </c>
       <c r="H439" t="n">
         <v>667518</v>
@@ -13158,7 +13158,7 @@
         <v>5</v>
       </c>
       <c r="G441" t="n">
-        <v>3.06659889221191</v>
+        <v>3.06659865379333</v>
       </c>
       <c r="H441" t="n">
         <v>837961</v>
@@ -13216,7 +13216,7 @@
         <v>5.03499984741211</v>
       </c>
       <c r="G443" t="n">
-        <v>3.08806467056274</v>
+        <v>3.08806490898132</v>
       </c>
       <c r="H443" t="n">
         <v>178529</v>
@@ -13245,7 +13245,7 @@
         <v>5</v>
       </c>
       <c r="G444" t="n">
-        <v>3.06659889221191</v>
+        <v>3.06659865379333</v>
       </c>
       <c r="H444" t="n">
         <v>685848</v>
@@ -13303,7 +13303,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G446" t="n">
-        <v>3.1769962310791</v>
+        <v>3.17699646949768</v>
       </c>
       <c r="H446" t="n">
         <v>911959</v>
@@ -13361,7 +13361,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>3.15552997589111</v>
+        <v>3.15553021430969</v>
       </c>
       <c r="H448" t="n">
         <v>253394</v>
@@ -13419,7 +13419,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G450" t="n">
-        <v>3.12486410140991</v>
+        <v>3.12486386299133</v>
       </c>
       <c r="H450" t="n">
         <v>232538</v>
@@ -13448,7 +13448,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G451" t="n">
-        <v>3.12486410140991</v>
+        <v>3.12486386299133</v>
       </c>
       <c r="H451" t="n">
         <v>425094</v>
@@ -13506,7 +13506,7 @@
         <v>4.95599985122681</v>
       </c>
       <c r="G453" t="n">
-        <v>3.03961253166199</v>
+        <v>3.03961229324341</v>
       </c>
       <c r="H453" t="n">
         <v>256186</v>
@@ -13564,7 +13564,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G455" t="n">
-        <v>2.96233415603638</v>
+        <v>2.96233439445496</v>
       </c>
       <c r="H455" t="n">
         <v>503874</v>
@@ -13593,7 +13593,7 @@
         <v>4.93800020217896</v>
       </c>
       <c r="G456" t="n">
-        <v>3.02857303619385</v>
+        <v>3.02857279777527</v>
       </c>
       <c r="H456" t="n">
         <v>292791</v>
@@ -13622,7 +13622,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G457" t="n">
-        <v>2.99300026893616</v>
+        <v>2.99300050735474</v>
       </c>
       <c r="H457" t="n">
         <v>279277</v>
@@ -13709,7 +13709,7 @@
         <v>4.80600023269653</v>
       </c>
       <c r="G460" t="n">
-        <v>2.94761490821838</v>
+        <v>2.9476146697998</v>
       </c>
       <c r="H460" t="n">
         <v>218811</v>
@@ -13767,7 +13767,7 @@
         <v>4.63199996948242</v>
       </c>
       <c r="G462" t="n">
-        <v>2.84089708328247</v>
+        <v>2.84089732170105</v>
       </c>
       <c r="H462" t="n">
         <v>672804</v>
@@ -13796,7 +13796,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G463" t="n">
-        <v>2.88260269165039</v>
+        <v>2.88260245323181</v>
       </c>
       <c r="H463" t="n">
         <v>389655</v>
@@ -13825,7 +13825,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G464" t="n">
-        <v>2.90100240707397</v>
+        <v>2.9010021686554</v>
       </c>
       <c r="H464" t="n">
         <v>159385</v>
@@ -13854,7 +13854,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G465" t="n">
-        <v>2.90590882301331</v>
+        <v>2.90590906143188</v>
       </c>
       <c r="H465" t="n">
         <v>601976</v>
@@ -13912,7 +13912,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G467" t="n">
-        <v>2.65567421913147</v>
+        <v>2.65567445755005</v>
       </c>
       <c r="H467" t="n">
         <v>2274886</v>
@@ -13999,7 +13999,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G470" t="n">
-        <v>2.5759425163269</v>
+        <v>2.57594275474548</v>
       </c>
       <c r="H470" t="n">
         <v>671006</v>
@@ -14086,7 +14086,7 @@
         <v>4.26399993896484</v>
       </c>
       <c r="G473" t="n">
-        <v>2.61519551277161</v>
+        <v>2.61519527435303</v>
       </c>
       <c r="H473" t="n">
         <v>1086537</v>
@@ -14376,7 +14376,7 @@
         <v>3.86400008201599</v>
       </c>
       <c r="G483" t="n">
-        <v>2.36986756324768</v>
+        <v>2.3698673248291</v>
       </c>
       <c r="H483" t="n">
         <v>818536</v>
@@ -14579,7 +14579,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G490" t="n">
-        <v>2.44346594810486</v>
+        <v>2.44346570968628</v>
       </c>
       <c r="H490" t="n">
         <v>829724</v>
@@ -14608,7 +14608,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G491" t="n">
-        <v>2.66794085502625</v>
+        <v>2.66794109344482</v>
       </c>
       <c r="H491" t="n">
         <v>3608976</v>
@@ -14637,7 +14637,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G492" t="n">
-        <v>2.63482141494751</v>
+        <v>2.63482165336609</v>
       </c>
       <c r="H492" t="n">
         <v>1627474</v>
@@ -14782,7 +14782,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G497" t="n">
-        <v>2.62500882148743</v>
+        <v>2.62500858306885</v>
       </c>
       <c r="H497" t="n">
         <v>426003</v>
@@ -14927,7 +14927,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G502" t="n">
-        <v>2.33061480522156</v>
+        <v>2.33061504364014</v>
       </c>
       <c r="H502" t="n">
         <v>824177</v>
@@ -14985,7 +14985,7 @@
         <v>3.94799995422363</v>
       </c>
       <c r="G504" t="n">
-        <v>2.42138624191284</v>
+        <v>2.42138648033142</v>
       </c>
       <c r="H504" t="n">
         <v>736965</v>
@@ -15072,7 +15072,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G507" t="n">
-        <v>2.47903847694397</v>
+        <v>2.47903823852539</v>
       </c>
       <c r="H507" t="n">
         <v>419637</v>
@@ -15130,7 +15130,7 @@
         <v>3.97399997711182</v>
       </c>
       <c r="G509" t="n">
-        <v>2.43733263015747</v>
+        <v>2.43733239173889</v>
       </c>
       <c r="H509" t="n">
         <v>229193</v>
@@ -15188,7 +15188,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G511" t="n">
-        <v>2.45941209793091</v>
+        <v>2.45941233634949</v>
       </c>
       <c r="H511" t="n">
         <v>303747</v>
@@ -15275,7 +15275,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G514" t="n">
-        <v>2.54527688026428</v>
+        <v>2.54527711868286</v>
       </c>
       <c r="H514" t="n">
         <v>532337</v>
@@ -15304,7 +15304,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G515" t="n">
-        <v>2.54527688026428</v>
+        <v>2.54527711868286</v>
       </c>
       <c r="H515" t="n">
         <v>252816</v>
@@ -15333,7 +15333,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G516" t="n">
-        <v>2.51461100578308</v>
+        <v>2.5146107673645</v>
       </c>
       <c r="H516" t="n">
         <v>279351</v>
@@ -15536,7 +15536,7 @@
         <v>4.21799993515015</v>
       </c>
       <c r="G523" t="n">
-        <v>2.58698272705078</v>
+        <v>2.5869824886322</v>
       </c>
       <c r="H523" t="n">
         <v>348275</v>
@@ -15594,7 +15594,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G525" t="n">
-        <v>2.64954161643982</v>
+        <v>2.64954113960266</v>
       </c>
       <c r="H525" t="n">
         <v>531029</v>
@@ -15623,7 +15623,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G526" t="n">
-        <v>2.64954161643982</v>
+        <v>2.64954113960266</v>
       </c>
       <c r="H526" t="n">
         <v>459494</v>
@@ -15652,7 +15652,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G527" t="n">
-        <v>2.65567421913147</v>
+        <v>2.65567445755005</v>
       </c>
       <c r="H527" t="n">
         <v>263721</v>
@@ -15681,7 +15681,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G528" t="n">
-        <v>2.59311580657959</v>
+        <v>2.59311604499817</v>
       </c>
       <c r="H528" t="n">
         <v>277825</v>
@@ -15826,7 +15826,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G533" t="n">
-        <v>2.46799850463867</v>
+        <v>2.46799874305725</v>
       </c>
       <c r="H533" t="n">
         <v>422014</v>
@@ -15855,7 +15855,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G534" t="n">
-        <v>2.48271799087524</v>
+        <v>2.48271822929382</v>
       </c>
       <c r="H534" t="n">
         <v>309567</v>
@@ -15884,7 +15884,7 @@
         <v>3.86400008201599</v>
       </c>
       <c r="G535" t="n">
-        <v>2.36986756324768</v>
+        <v>2.3698673248291</v>
       </c>
       <c r="H535" t="n">
         <v>527548</v>
@@ -15913,7 +15913,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G536" t="n">
-        <v>2.32325506210327</v>
+        <v>2.32325530052185</v>
       </c>
       <c r="H536" t="n">
         <v>672319</v>
@@ -15942,7 +15942,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G537" t="n">
-        <v>2.35269474983215</v>
+        <v>2.35269451141357</v>
       </c>
       <c r="H537" t="n">
         <v>708296</v>
@@ -16029,7 +16029,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G540" t="n">
-        <v>2.20181798934937</v>
+        <v>2.20181775093079</v>
       </c>
       <c r="H540" t="n">
         <v>932330</v>
@@ -16116,7 +16116,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G543" t="n">
-        <v>2.32325506210327</v>
+        <v>2.32325530052185</v>
       </c>
       <c r="H543" t="n">
         <v>618299</v>
@@ -16145,7 +16145,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G544" t="n">
-        <v>2.27541637420654</v>
+        <v>2.27541613578796</v>
       </c>
       <c r="H544" t="n">
         <v>202220</v>
@@ -16261,7 +16261,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G548" t="n">
-        <v>2.28400278091431</v>
+        <v>2.28400254249573</v>
       </c>
       <c r="H548" t="n">
         <v>586919</v>
@@ -16290,7 +16290,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G549" t="n">
-        <v>2.33061480522156</v>
+        <v>2.33061504364014</v>
       </c>
       <c r="H549" t="n">
         <v>1543552</v>
@@ -16319,7 +16319,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G550" t="n">
-        <v>2.24965667724609</v>
+        <v>2.24965691566467</v>
       </c>
       <c r="H550" t="n">
         <v>1786585</v>
@@ -16406,7 +16406,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G553" t="n">
-        <v>2.03008842468262</v>
+        <v>2.03008818626404</v>
       </c>
       <c r="H553" t="n">
         <v>1306281</v>
@@ -16435,7 +16435,7 @@
         <v>3.18600010871887</v>
       </c>
       <c r="G554" t="n">
-        <v>1.95403659343719</v>
+        <v>1.95403671264648</v>
       </c>
       <c r="H554" t="n">
         <v>1152409</v>
@@ -16522,7 +16522,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G557" t="n">
-        <v>1.87921154499054</v>
+        <v>1.87921166419983</v>
       </c>
       <c r="H557" t="n">
         <v>843821</v>
@@ -16580,7 +16580,7 @@
         <v>3.15799999237061</v>
       </c>
       <c r="G559" t="n">
-        <v>1.93686366081238</v>
+        <v>1.93686378002167</v>
       </c>
       <c r="H559" t="n">
         <v>444170</v>
@@ -16696,7 +16696,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G563" t="n">
-        <v>1.87798511981964</v>
+        <v>1.87798500061035</v>
       </c>
       <c r="H563" t="n">
         <v>1003231</v>
@@ -16725,7 +16725,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G564" t="n">
-        <v>1.87921154499054</v>
+        <v>1.87921166419983</v>
       </c>
       <c r="H564" t="n">
         <v>329963</v>
@@ -16783,7 +16783,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G566" t="n">
-        <v>1.86571860313416</v>
+        <v>1.86571872234344</v>
       </c>
       <c r="H566" t="n">
         <v>421960</v>
@@ -16899,7 +16899,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G570" t="n">
-        <v>1.86571860313416</v>
+        <v>1.86571872234344</v>
       </c>
       <c r="H570" t="n">
         <v>810989</v>
@@ -16957,7 +16957,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G572" t="n">
-        <v>1.8865715265274</v>
+        <v>1.88657140731812</v>
       </c>
       <c r="H572" t="n">
         <v>885470</v>
@@ -17131,7 +17131,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G578" t="n">
-        <v>1.95649015903473</v>
+        <v>1.95648992061615</v>
       </c>
       <c r="H578" t="n">
         <v>584408</v>
@@ -17160,7 +17160,7 @@
         <v>3.12800002098083</v>
       </c>
       <c r="G579" t="n">
-        <v>1.91846418380737</v>
+        <v>1.91846430301666</v>
       </c>
       <c r="H579" t="n">
         <v>655396</v>
@@ -17247,7 +17247,7 @@
         <v>3.14800000190735</v>
       </c>
       <c r="G582" t="n">
-        <v>1.93073070049286</v>
+        <v>1.93073058128357</v>
       </c>
       <c r="H582" t="n">
         <v>436681</v>
@@ -17392,7 +17392,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G587" t="n">
-        <v>1.99083578586578</v>
+        <v>1.99083590507507</v>
       </c>
       <c r="H587" t="n">
         <v>459538</v>
@@ -17421,7 +17421,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G588" t="n">
-        <v>1.96262300014496</v>
+        <v>1.96262323856354</v>
       </c>
       <c r="H588" t="n">
         <v>478776</v>
@@ -17450,7 +17450,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G589" t="n">
-        <v>2.03008842468262</v>
+        <v>2.03008818626404</v>
       </c>
       <c r="H589" t="n">
         <v>1065238</v>
@@ -17537,7 +17537,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G592" t="n">
-        <v>1.97488951683044</v>
+        <v>1.97488963603973</v>
       </c>
       <c r="H592" t="n">
         <v>412074</v>
@@ -17566,7 +17566,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G593" t="n">
-        <v>1.9773428440094</v>
+        <v>1.97734272480011</v>
       </c>
       <c r="H593" t="n">
         <v>256523</v>
@@ -17595,7 +17595,7 @@
         <v>3.25399994850159</v>
       </c>
       <c r="G594" t="n">
-        <v>1.99574255943298</v>
+        <v>1.99574244022369</v>
       </c>
       <c r="H594" t="n">
         <v>241270</v>
@@ -17624,7 +17624,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G595" t="n">
-        <v>2.08283400535583</v>
+        <v>2.08283376693726</v>
       </c>
       <c r="H595" t="n">
         <v>902410</v>
@@ -17653,7 +17653,7 @@
         <v>3.33599996566772</v>
       </c>
       <c r="G596" t="n">
-        <v>2.04603481292725</v>
+        <v>2.04603457450867</v>
       </c>
       <c r="H596" t="n">
         <v>599907</v>
@@ -17740,7 +17740,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G599" t="n">
-        <v>1.99942219257355</v>
+        <v>1.99942231178284</v>
       </c>
       <c r="H599" t="n">
         <v>777043</v>
@@ -17769,7 +17769,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G600" t="n">
-        <v>2.02640819549561</v>
+        <v>2.02640843391418</v>
       </c>
       <c r="H600" t="n">
         <v>719661</v>
@@ -17827,7 +17827,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G602" t="n">
-        <v>1.96017003059387</v>
+        <v>1.96016991138458</v>
       </c>
       <c r="H602" t="n">
         <v>1065883</v>
@@ -17856,7 +17856,7 @@
         <v>3.15199995040894</v>
       </c>
       <c r="G603" t="n">
-        <v>1.93318367004395</v>
+        <v>1.93318378925323</v>
       </c>
       <c r="H603" t="n">
         <v>745062</v>
@@ -17885,7 +17885,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G604" t="n">
-        <v>1.93441033363342</v>
+        <v>1.93441045284271</v>
       </c>
       <c r="H604" t="n">
         <v>347176</v>
@@ -17972,7 +17972,7 @@
         <v>3.10599994659424</v>
       </c>
       <c r="G607" t="n">
-        <v>1.90497100353241</v>
+        <v>1.90497088432312</v>
       </c>
       <c r="H607" t="n">
         <v>240955</v>
@@ -18059,7 +18059,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G610" t="n">
-        <v>1.89515793323517</v>
+        <v>1.89515805244446</v>
       </c>
       <c r="H610" t="n">
         <v>327212</v>
@@ -18117,7 +18117,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G612" t="n">
-        <v>1.87921154499054</v>
+        <v>1.87921166419983</v>
       </c>
       <c r="H612" t="n">
         <v>402149</v>
@@ -18175,7 +18175,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G614" t="n">
-        <v>1.77985382080078</v>
+        <v>1.77985394001007</v>
       </c>
       <c r="H614" t="n">
         <v>666465</v>
@@ -18204,7 +18204,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G615" t="n">
-        <v>1.74182796478271</v>
+        <v>1.741828083992</v>
       </c>
       <c r="H615" t="n">
         <v>919236</v>
@@ -18262,7 +18262,7 @@
         <v>3.05599999427795</v>
       </c>
       <c r="G617" t="n">
-        <v>1.87430500984192</v>
+        <v>1.87430512905121</v>
       </c>
       <c r="H617" t="n">
         <v>883535</v>
@@ -18349,7 +18349,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G620" t="n">
-        <v>1.93441033363342</v>
+        <v>1.93441045284271</v>
       </c>
       <c r="H620" t="n">
         <v>666111</v>
@@ -18378,7 +18378,7 @@
         <v>3.08400011062622</v>
       </c>
       <c r="G621" t="n">
-        <v>1.89147806167603</v>
+        <v>1.89147818088531</v>
       </c>
       <c r="H621" t="n">
         <v>497533</v>
@@ -18407,7 +18407,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G622" t="n">
-        <v>1.82155966758728</v>
+        <v>1.82155954837799</v>
       </c>
       <c r="H622" t="n">
         <v>562723</v>
@@ -18465,7 +18465,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G624" t="n">
-        <v>1.87062513828278</v>
+        <v>1.87062525749207</v>
       </c>
       <c r="H624" t="n">
         <v>269179</v>
@@ -18552,7 +18552,7 @@
         <v>3.01200008392334</v>
       </c>
       <c r="G627" t="n">
-        <v>1.84731912612915</v>
+        <v>1.84731900691986</v>
       </c>
       <c r="H627" t="n">
         <v>540210</v>
@@ -18581,7 +18581,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G628" t="n">
-        <v>1.8031599521637</v>
+        <v>1.80316007137299</v>
       </c>
       <c r="H628" t="n">
         <v>337726</v>
@@ -18639,7 +18639,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G630" t="n">
-        <v>1.80193328857422</v>
+        <v>1.80193340778351</v>
       </c>
       <c r="H630" t="n">
         <v>413305</v>
@@ -18668,7 +18668,7 @@
         <v>2.87599992752075</v>
       </c>
       <c r="G631" t="n">
-        <v>1.76390743255615</v>
+        <v>1.76390755176544</v>
       </c>
       <c r="H631" t="n">
         <v>379228</v>
@@ -18755,7 +18755,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G634" t="n">
-        <v>1.63756370544434</v>
+        <v>1.63756382465363</v>
       </c>
       <c r="H634" t="n">
         <v>381605</v>
@@ -18784,7 +18784,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G635" t="n">
-        <v>1.63020396232605</v>
+        <v>1.63020384311676</v>
       </c>
       <c r="H635" t="n">
         <v>421592</v>
@@ -18900,7 +18900,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G639" t="n">
-        <v>1.55169892311096</v>
+        <v>1.55169880390167</v>
       </c>
       <c r="H639" t="n">
         <v>341019</v>
@@ -18958,7 +18958,7 @@
         <v>2.68600010871887</v>
       </c>
       <c r="G641" t="n">
-        <v>1.64737689495087</v>
+        <v>1.64737677574158</v>
       </c>
       <c r="H641" t="n">
         <v>510074</v>
@@ -18987,7 +18987,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G642" t="n">
-        <v>1.63143050670624</v>
+        <v>1.63143038749695</v>
       </c>
       <c r="H642" t="n">
         <v>142464</v>
@@ -19045,7 +19045,7 @@
         <v>2.74200010299683</v>
       </c>
       <c r="G644" t="n">
-        <v>1.68172287940979</v>
+        <v>1.6817227602005</v>
       </c>
       <c r="H644" t="n">
         <v>253790</v>
@@ -19074,7 +19074,7 @@
         <v>2.66400003433228</v>
       </c>
       <c r="G645" t="n">
-        <v>1.6338837146759</v>
+        <v>1.63388383388519</v>
       </c>
       <c r="H645" t="n">
         <v>200083</v>
@@ -19161,7 +19161,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G648" t="n">
-        <v>1.5737783908844</v>
+        <v>1.57377851009369</v>
       </c>
       <c r="H648" t="n">
         <v>104635</v>
@@ -19190,7 +19190,7 @@
         <v>2.62800002098083</v>
       </c>
       <c r="G649" t="n">
-        <v>1.61180424690247</v>
+        <v>1.61180436611176</v>
       </c>
       <c r="H649" t="n">
         <v>203791</v>
@@ -19248,7 +19248,7 @@
         <v>2.78600001335144</v>
       </c>
       <c r="G651" t="n">
-        <v>1.70870876312256</v>
+        <v>1.70870864391327</v>
       </c>
       <c r="H651" t="n">
         <v>182007</v>
@@ -19277,7 +19277,7 @@
         <v>2.71399998664856</v>
       </c>
       <c r="G652" t="n">
-        <v>1.66454982757568</v>
+        <v>1.66454970836639</v>
       </c>
       <c r="H652" t="n">
         <v>684291</v>
@@ -19306,7 +19306,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G653" t="n">
-        <v>1.63143050670624</v>
+        <v>1.63143038749695</v>
       </c>
       <c r="H653" t="n">
         <v>134571</v>
@@ -19422,7 +19422,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G657" t="n">
-        <v>1.30637109279633</v>
+        <v>1.30637121200562</v>
       </c>
       <c r="H657" t="n">
         <v>948766</v>
@@ -19480,7 +19480,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G659" t="n">
-        <v>1.30637109279633</v>
+        <v>1.30637121200562</v>
       </c>
       <c r="H659" t="n">
         <v>629454</v>
@@ -19538,7 +19538,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G661" t="n">
-        <v>1.24135899543762</v>
+        <v>1.24135911464691</v>
       </c>
       <c r="H661" t="n">
         <v>746110</v>
@@ -19625,7 +19625,7 @@
         <v>2.1340000629425</v>
       </c>
       <c r="G664" t="n">
-        <v>1.30882430076599</v>
+        <v>1.30882441997528</v>
       </c>
       <c r="H664" t="n">
         <v>377252</v>
@@ -19683,7 +19683,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G666" t="n">
-        <v>1.25853204727173</v>
+        <v>1.25853216648102</v>
       </c>
       <c r="H666" t="n">
         <v>514664</v>
@@ -19741,7 +19741,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G668" t="n">
-        <v>1.20946657657623</v>
+        <v>1.20946645736694</v>
       </c>
       <c r="H668" t="n">
         <v>265562</v>
@@ -19770,7 +19770,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G669" t="n">
-        <v>1.20517325401306</v>
+        <v>1.20517337322235</v>
       </c>
       <c r="H669" t="n">
         <v>337600</v>
@@ -19886,7 +19886,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G673" t="n">
-        <v>1.28551816940308</v>
+        <v>1.28551805019379</v>
       </c>
       <c r="H673" t="n">
         <v>372684</v>
@@ -19973,7 +19973,7 @@
         <v>2.00399994850159</v>
       </c>
       <c r="G676" t="n">
-        <v>1.22909259796143</v>
+        <v>1.22909271717072</v>
       </c>
       <c r="H676" t="n">
         <v>261133</v>
@@ -20002,7 +20002,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G677" t="n">
-        <v>1.23154604434967</v>
+        <v>1.23154592514038</v>
       </c>
       <c r="H677" t="n">
         <v>290766</v>
@@ -20031,7 +20031,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G678" t="n">
-        <v>1.24749219417572</v>
+        <v>1.24749231338501</v>
       </c>
       <c r="H678" t="n">
         <v>430500</v>
@@ -20060,7 +20060,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G679" t="n">
-        <v>1.24749219417572</v>
+        <v>1.24749231338501</v>
       </c>
       <c r="H679" t="n">
         <v>198373</v>
@@ -20118,7 +20118,7 @@
         <v>2.00600004196167</v>
       </c>
       <c r="G681" t="n">
-        <v>1.23031949996948</v>
+        <v>1.23031938076019</v>
       </c>
       <c r="H681" t="n">
         <v>692504</v>
@@ -20147,7 +20147,7 @@
         <v>2.04800009727478</v>
       </c>
       <c r="G682" t="n">
-        <v>1.25607883930206</v>
+        <v>1.25607895851135</v>
       </c>
       <c r="H682" t="n">
         <v>281162</v>
@@ -20176,7 +20176,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G683" t="n">
-        <v>1.22602617740631</v>
+        <v>1.22602605819702</v>
       </c>
       <c r="H683" t="n">
         <v>474792</v>
@@ -20205,7 +20205,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G684" t="n">
-        <v>1.23522591590881</v>
+        <v>1.23522579669952</v>
       </c>
       <c r="H684" t="n">
         <v>891148</v>
@@ -20234,7 +20234,7 @@
         <v>2.00399994850159</v>
       </c>
       <c r="G685" t="n">
-        <v>1.22909259796143</v>
+        <v>1.22909271717072</v>
       </c>
       <c r="H685" t="n">
         <v>716738</v>
@@ -20263,7 +20263,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G686" t="n">
-        <v>1.24503910541534</v>
+        <v>1.24503898620605</v>
       </c>
       <c r="H686" t="n">
         <v>484546</v>
@@ -20437,7 +20437,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G692" t="n">
-        <v>1.24381256103516</v>
+        <v>1.24381244182587</v>
       </c>
       <c r="H692" t="n">
         <v>607664</v>
@@ -20466,7 +20466,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G693" t="n">
-        <v>1.24381256103516</v>
+        <v>1.24381244182587</v>
       </c>
       <c r="H693" t="n">
         <v>615775</v>
@@ -20524,7 +20524,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G695" t="n">
-        <v>1.29533135890961</v>
+        <v>1.29533123970032</v>
       </c>
       <c r="H695" t="n">
         <v>1501497</v>
@@ -20553,7 +20553,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G696" t="n">
-        <v>1.31741070747375</v>
+        <v>1.31741082668304</v>
       </c>
       <c r="H696" t="n">
         <v>1602595</v>
@@ -20611,7 +20611,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G698" t="n">
-        <v>1.24381256103516</v>
+        <v>1.24381244182587</v>
       </c>
       <c r="H698" t="n">
         <v>965266</v>
@@ -20669,7 +20669,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G700" t="n">
-        <v>1.24626564979553</v>
+        <v>1.24626576900482</v>
       </c>
       <c r="H700" t="n">
         <v>384853</v>
@@ -20959,7 +20959,7 @@
         <v>1.68700003623962</v>
       </c>
       <c r="G710" t="n">
-        <v>1.03467035293579</v>
+        <v>1.03467047214508</v>
       </c>
       <c r="H710" t="n">
         <v>398616</v>
@@ -20988,7 +20988,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G711" t="n">
-        <v>1.05552327632904</v>
+        <v>1.05552315711975</v>
       </c>
       <c r="H711" t="n">
         <v>442171</v>
@@ -21046,7 +21046,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G713" t="n">
-        <v>1.057976603508</v>
+        <v>1.05797648429871</v>
       </c>
       <c r="H713" t="n">
         <v>478442</v>
@@ -21075,7 +21075,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G714" t="n">
-        <v>1.02792394161224</v>
+        <v>1.02792382240295</v>
       </c>
       <c r="H714" t="n">
         <v>676455</v>
@@ -21104,7 +21104,7 @@
         <v>1.625</v>
       </c>
       <c r="G715" t="n">
-        <v>0.996644616127014</v>
+        <v>0.996644556522369</v>
       </c>
       <c r="H715" t="n">
         <v>423729</v>
@@ -21162,7 +21162,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G717" t="n">
-        <v>0.984991431236267</v>
+        <v>0.984991490840912</v>
       </c>
       <c r="H717" t="n">
         <v>776455</v>
@@ -21191,7 +21191,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G718" t="n">
-        <v>0.91077983379364</v>
+        <v>0.910779774188995</v>
       </c>
       <c r="H718" t="n">
         <v>847433</v>
@@ -21220,7 +21220,7 @@
         <v>1.49300003051758</v>
       </c>
       <c r="G719" t="n">
-        <v>0.915686309337616</v>
+        <v>0.915686368942261</v>
       </c>
       <c r="H719" t="n">
         <v>735567</v>
@@ -21249,7 +21249,7 @@
         <v>1.5110000371933</v>
       </c>
       <c r="G720" t="n">
-        <v>0.926726162433624</v>
+        <v>0.926726102828979</v>
       </c>
       <c r="H720" t="n">
         <v>609534</v>
@@ -21278,7 +21278,7 @@
         <v>1.49399995803833</v>
       </c>
       <c r="G721" t="n">
-        <v>0.916299700737</v>
+        <v>0.916299641132355</v>
       </c>
       <c r="H721" t="n">
         <v>519573</v>
@@ -21307,7 +21307,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G722" t="n">
-        <v>0.951258957386017</v>
+        <v>0.951258897781372</v>
       </c>
       <c r="H722" t="n">
         <v>878851</v>
@@ -21336,7 +21336,7 @@
         <v>1.57599997520447</v>
       </c>
       <c r="G723" t="n">
-        <v>0.966591835021973</v>
+        <v>0.966591894626617</v>
       </c>
       <c r="H723" t="n">
         <v>684711</v>
@@ -21365,7 +21365,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G724" t="n">
-        <v>0.965365350246429</v>
+        <v>0.965365290641785</v>
       </c>
       <c r="H724" t="n">
         <v>453862</v>
@@ -21394,7 +21394,7 @@
         <v>1.59300005435944</v>
       </c>
       <c r="G725" t="n">
-        <v>0.977018296718597</v>
+        <v>0.977018356323242</v>
       </c>
       <c r="H725" t="n">
         <v>492029</v>
@@ -21423,7 +21423,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G726" t="n">
-        <v>0.980085015296936</v>
+        <v>0.980084955692291</v>
       </c>
       <c r="H726" t="n">
         <v>625242</v>
@@ -21452,7 +21452,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G727" t="n">
-        <v>0.958618640899658</v>
+        <v>0.958618700504303</v>
       </c>
       <c r="H727" t="n">
         <v>253732</v>
@@ -21481,7 +21481,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G728" t="n">
-        <v>0.96291196346283</v>
+        <v>0.962912023067474</v>
       </c>
       <c r="H728" t="n">
         <v>546391</v>
@@ -21510,7 +21510,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G729" t="n">
-        <v>0.992351412773132</v>
+        <v>0.992351353168488</v>
       </c>
       <c r="H729" t="n">
         <v>763102</v>
@@ -21568,7 +21568,7 @@
         <v>1.53299999237061</v>
       </c>
       <c r="G731" t="n">
-        <v>0.940219104290009</v>
+        <v>0.940219223499298</v>
       </c>
       <c r="H731" t="n">
         <v>257158</v>
@@ -21626,7 +21626,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G733" t="n">
-        <v>0.904646635055542</v>
+        <v>0.904646575450897</v>
       </c>
       <c r="H733" t="n">
         <v>613085</v>
@@ -21713,7 +21713,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G736" t="n">
-        <v>0.89544677734375</v>
+        <v>0.895446836948395</v>
       </c>
       <c r="H736" t="n">
         <v>253922</v>
@@ -21742,7 +21742,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G737" t="n">
-        <v>0.902193307876587</v>
+        <v>0.902193248271942</v>
       </c>
       <c r="H737" t="n">
         <v>134126</v>
@@ -21771,7 +21771,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G738" t="n">
-        <v>0.867847383022308</v>
+        <v>0.867847442626953</v>
       </c>
       <c r="H738" t="n">
         <v>252282</v>
@@ -21800,7 +21800,7 @@
         <v>1.44400000572205</v>
       </c>
       <c r="G739" t="n">
-        <v>0.885633707046509</v>
+        <v>0.885633647441864</v>
       </c>
       <c r="H739" t="n">
         <v>529303</v>
@@ -21829,7 +21829,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G740" t="n">
-        <v>0.875820577144623</v>
+        <v>0.875820517539978</v>
       </c>
       <c r="H740" t="n">
         <v>327146</v>
@@ -21858,7 +21858,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G741" t="n">
-        <v>0.884407043457031</v>
+        <v>0.884407103061676</v>
       </c>
       <c r="H741" t="n">
         <v>275350</v>
@@ -21887,7 +21887,7 @@
         <v>1.53299999237061</v>
       </c>
       <c r="G742" t="n">
-        <v>0.940219104290009</v>
+        <v>0.940219223499298</v>
       </c>
       <c r="H742" t="n">
         <v>982055</v>
@@ -21916,7 +21916,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G743" t="n">
-        <v>0.956778824329376</v>
+        <v>0.956778764724731</v>
       </c>
       <c r="H743" t="n">
         <v>500398</v>
@@ -21945,7 +21945,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G744" t="n">
-        <v>0.94451242685318</v>
+        <v>0.944512367248535</v>
       </c>
       <c r="H744" t="n">
         <v>249172</v>
@@ -21974,7 +21974,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G745" t="n">
-        <v>0.941445708274841</v>
+        <v>0.941445767879486</v>
       </c>
       <c r="H745" t="n">
         <v>656565</v>
@@ -22003,7 +22003,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G746" t="n">
-        <v>0.938379287719727</v>
+        <v>0.938379108905792</v>
       </c>
       <c r="H746" t="n">
         <v>1898728</v>
@@ -22032,7 +22032,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G747" t="n">
-        <v>0.967205166816711</v>
+        <v>0.967205226421356</v>
       </c>
       <c r="H747" t="n">
         <v>682019</v>
@@ -22090,7 +22090,7 @@
         <v>1.557000041008</v>
       </c>
       <c r="G749" t="n">
-        <v>0.954938769340515</v>
+        <v>0.95493882894516</v>
       </c>
       <c r="H749" t="n">
         <v>131447</v>
@@ -22119,7 +22119,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G750" t="n">
-        <v>0.901579976081848</v>
+        <v>0.901580035686493</v>
       </c>
       <c r="H750" t="n">
         <v>663241</v>
@@ -22177,7 +22177,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G752" t="n">
-        <v>0.870913982391357</v>
+        <v>0.870914041996002</v>
       </c>
       <c r="H752" t="n">
         <v>372259</v>
@@ -22235,7 +22235,7 @@
         <v>1.48699998855591</v>
       </c>
       <c r="G754" t="n">
-        <v>0.912006497383118</v>
+        <v>0.912006437778473</v>
       </c>
       <c r="H754" t="n">
         <v>459581</v>
@@ -22264,7 +22264,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G755" t="n">
-        <v>0.875207304954529</v>
+        <v>0.875207364559174</v>
       </c>
       <c r="H755" t="n">
         <v>856510</v>
@@ -22293,7 +22293,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G756" t="n">
-        <v>0.859874248504639</v>
+        <v>0.859874188899994</v>
       </c>
       <c r="H756" t="n">
         <v>508033</v>
@@ -22351,7 +22351,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G758" t="n">
-        <v>0.837181389331818</v>
+        <v>0.837181448936462</v>
       </c>
       <c r="H758" t="n">
         <v>234713</v>
@@ -22409,7 +22409,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G760" t="n">
-        <v>0.837181389331818</v>
+        <v>0.837181448936462</v>
       </c>
       <c r="H760" t="n">
         <v>270071</v>
@@ -22496,7 +22496,7 @@
         <v>1.43099999427795</v>
       </c>
       <c r="G763" t="n">
-        <v>0.877660512924194</v>
+        <v>0.877660632133484</v>
       </c>
       <c r="H763" t="n">
         <v>76251</v>
@@ -22525,7 +22525,7 @@
         <v>1.45700001716614</v>
       </c>
       <c r="G764" t="n">
-        <v>0.893606901168823</v>
+        <v>0.893606841564178</v>
       </c>
       <c r="H764" t="n">
         <v>309417</v>
@@ -22554,7 +22554,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G765" t="n">
-        <v>0.911392986774445</v>
+        <v>0.911393165588379</v>
       </c>
       <c r="H765" t="n">
         <v>318206</v>
@@ -22612,7 +22612,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G767" t="n">
-        <v>0.951258957386017</v>
+        <v>0.951258897781372</v>
       </c>
       <c r="H767" t="n">
         <v>303463</v>
@@ -22699,7 +22699,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G770" t="n">
-        <v>0.987444758415222</v>
+        <v>0.987444818019867</v>
       </c>
       <c r="H770" t="n">
         <v>399379</v>
@@ -22728,7 +22728,7 @@
         <v>1.61300003528595</v>
       </c>
       <c r="G771" t="n">
-        <v>0.989284753799438</v>
+        <v>0.989284694194794</v>
       </c>
       <c r="H771" t="n">
         <v>301683</v>
@@ -22786,7 +22786,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G773" t="n">
-        <v>0.94451242685318</v>
+        <v>0.944512367248535</v>
       </c>
       <c r="H773" t="n">
         <v>246426</v>
@@ -22844,7 +22844,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G775" t="n">
-        <v>0.982538282871246</v>
+        <v>0.982538223266602</v>
       </c>
       <c r="H775" t="n">
         <v>323658</v>
@@ -22902,7 +22902,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G777" t="n">
-        <v>0.986218154430389</v>
+        <v>0.986218094825745</v>
       </c>
       <c r="H777" t="n">
         <v>142894</v>
@@ -22960,7 +22960,7 @@
         <v>1.5</v>
       </c>
       <c r="G779" t="n">
-        <v>0.919979512691498</v>
+        <v>0.919979631900787</v>
       </c>
       <c r="H779" t="n">
         <v>307567</v>
@@ -23018,7 +23018,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G781" t="n">
-        <v>0.984991431236267</v>
+        <v>0.984991490840912</v>
       </c>
       <c r="H781" t="n">
         <v>583532</v>
@@ -23250,7 +23250,7 @@
         <v>1.7039999961853</v>
       </c>
       <c r="G789" t="n">
-        <v>1.04509687423706</v>
+        <v>1.04509675502777</v>
       </c>
       <c r="H789" t="n">
         <v>244962</v>
@@ -23279,7 +23279,7 @@
         <v>1.625</v>
       </c>
       <c r="G790" t="n">
-        <v>0.996644616127014</v>
+        <v>0.996644556522369</v>
       </c>
       <c r="H790" t="n">
         <v>694373</v>
@@ -23308,7 +23308,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G791" t="n">
-        <v>0.972111821174622</v>
+        <v>0.972111761569977</v>
       </c>
       <c r="H791" t="n">
         <v>381336</v>
@@ -23337,7 +23337,7 @@
         <v>1.59700000286102</v>
       </c>
       <c r="G792" t="n">
-        <v>0.979471564292908</v>
+        <v>0.979471623897552</v>
       </c>
       <c r="H792" t="n">
         <v>263430</v>
@@ -23366,7 +23366,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G793" t="n">
-        <v>0.996031284332275</v>
+        <v>0.996031224727631</v>
       </c>
       <c r="H793" t="n">
         <v>454468</v>
@@ -23424,7 +23424,7 @@
         <v>1.71300005912781</v>
       </c>
       <c r="G795" t="n">
-        <v>1.05061674118042</v>
+        <v>1.05061662197113</v>
       </c>
       <c r="H795" t="n">
         <v>186136</v>
@@ -23482,7 +23482,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G797" t="n">
-        <v>1.05552327632904</v>
+        <v>1.05552315711975</v>
       </c>
       <c r="H797" t="n">
         <v>145140</v>
@@ -23656,7 +23656,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G803" t="n">
-        <v>1.02792394161224</v>
+        <v>1.02792382240295</v>
       </c>
       <c r="H803" t="n">
         <v>1022175</v>
@@ -23743,7 +23743,7 @@
         <v>1.5789999961853</v>
       </c>
       <c r="G806" t="n">
-        <v>0.968431830406189</v>
+        <v>0.968431890010834</v>
       </c>
       <c r="H806" t="n">
         <v>380344</v>
@@ -23917,7 +23917,7 @@
         <v>1.49399995803833</v>
       </c>
       <c r="G812" t="n">
-        <v>0.916299700737</v>
+        <v>0.916299641132355</v>
       </c>
       <c r="H812" t="n">
         <v>389992</v>
@@ -23975,7 +23975,7 @@
         <v>1.50600004196167</v>
       </c>
       <c r="G814" t="n">
-        <v>0.923659563064575</v>
+        <v>0.92365950345993</v>
       </c>
       <c r="H814" t="n">
         <v>219488</v>
@@ -24004,7 +24004,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G815" t="n">
-        <v>0.928566157817841</v>
+        <v>0.928566098213196</v>
       </c>
       <c r="H815" t="n">
         <v>528078</v>
@@ -24062,7 +24062,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G817" t="n">
-        <v>0.926112830638885</v>
+        <v>0.926112771034241</v>
       </c>
       <c r="H817" t="n">
         <v>331576</v>
@@ -24120,7 +24120,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G819" t="n">
-        <v>0.945739030838013</v>
+        <v>0.945739090442657</v>
       </c>
       <c r="H819" t="n">
         <v>1308957</v>
@@ -24207,7 +24207,7 @@
         <v>1.47300004959106</v>
       </c>
       <c r="G822" t="n">
-        <v>0.903419971466064</v>
+        <v>0.903420031070709</v>
       </c>
       <c r="H822" t="n">
         <v>526975</v>
@@ -24236,7 +24236,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G823" t="n">
-        <v>0.899126648902893</v>
+        <v>0.899126708507538</v>
       </c>
       <c r="H823" t="n">
         <v>347418</v>
@@ -24323,7 +24323,7 @@
         <v>1.53699994087219</v>
       </c>
       <c r="G826" t="n">
-        <v>0.942672491073608</v>
+        <v>0.942672431468964</v>
       </c>
       <c r="H826" t="n">
         <v>166399</v>
@@ -24352,7 +24352,7 @@
         <v>1.59300005435944</v>
       </c>
       <c r="G827" t="n">
-        <v>0.977018296718597</v>
+        <v>0.977018356323242</v>
       </c>
       <c r="H827" t="n">
         <v>400075</v>
@@ -24410,7 +24410,7 @@
         <v>1.65299999713898</v>
       </c>
       <c r="G829" t="n">
-        <v>1.01381742954254</v>
+        <v>1.01381754875183</v>
       </c>
       <c r="H829" t="n">
         <v>887503</v>
@@ -24439,7 +24439,7 @@
         <v>1.66100001335144</v>
       </c>
       <c r="G830" t="n">
-        <v>1.01872420310974</v>
+        <v>1.01872408390045</v>
       </c>
       <c r="H830" t="n">
         <v>270311</v>
@@ -24468,7 +24468,7 @@
         <v>1.66299998760223</v>
       </c>
       <c r="G831" t="n">
-        <v>1.01995074748993</v>
+        <v>1.01995062828064</v>
       </c>
       <c r="H831" t="n">
         <v>221352</v>
@@ -24526,7 +24526,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G833" t="n">
-        <v>0.96291196346283</v>
+        <v>0.962912023067474</v>
       </c>
       <c r="H833" t="n">
         <v>950966</v>
@@ -24555,7 +24555,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G834" t="n">
-        <v>0.96291196346283</v>
+        <v>0.962912023067474</v>
       </c>
       <c r="H834" t="n">
         <v>272796</v>
@@ -24584,7 +24584,7 @@
         <v>1.55299997329712</v>
       </c>
       <c r="G835" t="n">
-        <v>0.952485501766205</v>
+        <v>0.95248544216156</v>
       </c>
       <c r="H835" t="n">
         <v>259158</v>
@@ -24613,7 +24613,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G836" t="n">
-        <v>0.965365350246429</v>
+        <v>0.965365290641785</v>
       </c>
       <c r="H836" t="n">
         <v>290487</v>
@@ -24642,7 +24642,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G837" t="n">
-        <v>0.96291196346283</v>
+        <v>0.962912023067474</v>
       </c>
       <c r="H837" t="n">
         <v>135240</v>
@@ -24787,7 +24787,7 @@
         <v>1.5789999961853</v>
       </c>
       <c r="G842" t="n">
-        <v>0.968431830406189</v>
+        <v>0.968431890010834</v>
       </c>
       <c r="H842" t="n">
         <v>498110</v>
@@ -24816,7 +24816,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G843" t="n">
-        <v>0.953098952770233</v>
+        <v>0.953098833560944</v>
       </c>
       <c r="H843" t="n">
         <v>226537</v>
@@ -24874,7 +24874,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G845" t="n">
-        <v>0.902806639671326</v>
+        <v>0.90280669927597</v>
       </c>
       <c r="H845" t="n">
         <v>601706</v>
@@ -24903,7 +24903,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G846" t="n">
-        <v>0.867234110832214</v>
+        <v>0.867234170436859</v>
       </c>
       <c r="H846" t="n">
         <v>884199</v>
@@ -24932,7 +24932,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G847" t="n">
-        <v>0.852514386177063</v>
+        <v>0.852514445781708</v>
       </c>
       <c r="H847" t="n">
         <v>1230354</v>
@@ -24990,7 +24990,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G849" t="n">
-        <v>0.840248048305511</v>
+        <v>0.840247988700867</v>
       </c>
       <c r="H849" t="n">
         <v>747799</v>
@@ -25077,7 +25077,7 @@
         <v>1.27799999713898</v>
       </c>
       <c r="G852" t="n">
-        <v>0.783822596073151</v>
+        <v>0.783822655677795</v>
       </c>
       <c r="H852" t="n">
         <v>775169</v>
@@ -25164,7 +25164,7 @@
         <v>1.18700003623962</v>
       </c>
       <c r="G855" t="n">
-        <v>0.728010594844818</v>
+        <v>0.728010535240173</v>
       </c>
       <c r="H855" t="n">
         <v>567821</v>
@@ -25280,7 +25280,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G859" t="n">
-        <v>0.69611793756485</v>
+        <v>0.69611781835556</v>
       </c>
       <c r="H859" t="n">
         <v>285309</v>
@@ -25338,7 +25338,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G861" t="n">
-        <v>0.705317676067352</v>
+        <v>0.705317735671997</v>
       </c>
       <c r="H861" t="n">
         <v>305816</v>
@@ -25367,7 +25367,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G862" t="n">
-        <v>0.698571264743805</v>
+        <v>0.69857120513916</v>
       </c>
       <c r="H862" t="n">
         <v>581824</v>
@@ -25396,7 +25396,7 @@
         <v>1.13100004196167</v>
       </c>
       <c r="G863" t="n">
-        <v>0.69366466999054</v>
+        <v>0.693664610385895</v>
       </c>
       <c r="H863" t="n">
         <v>193833</v>
@@ -25425,7 +25425,7 @@
         <v>1.17900002002716</v>
       </c>
       <c r="G864" t="n">
-        <v>0.723104000091553</v>
+        <v>0.723103940486908</v>
       </c>
       <c r="H864" t="n">
         <v>869061</v>
@@ -25512,7 +25512,7 @@
         <v>1.17900002002716</v>
       </c>
       <c r="G867" t="n">
-        <v>0.723104000091553</v>
+        <v>0.723103940486908</v>
       </c>
       <c r="H867" t="n">
         <v>203797</v>
@@ -25570,7 +25570,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G869" t="n">
-        <v>0.698571264743805</v>
+        <v>0.69857120513916</v>
       </c>
       <c r="H869" t="n">
         <v>137746</v>
@@ -25657,7 +25657,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G872" t="n">
-        <v>0.705317676067352</v>
+        <v>0.705317735671997</v>
       </c>
       <c r="H872" t="n">
         <v>363288</v>
@@ -25773,7 +25773,7 @@
         <v>1.1710000038147</v>
       </c>
       <c r="G876" t="n">
-        <v>0.718197345733643</v>
+        <v>0.718197405338287</v>
       </c>
       <c r="H876" t="n">
         <v>98716</v>
@@ -25831,7 +25831,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G878" t="n">
-        <v>0.720650672912598</v>
+        <v>0.720650613307953</v>
       </c>
       <c r="H878" t="n">
         <v>167271</v>
@@ -25918,7 +25918,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G881" t="n">
-        <v>0.73475706577301</v>
+        <v>0.734757006168365</v>
       </c>
       <c r="H881" t="n">
         <v>166835</v>
@@ -26179,7 +26179,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G890" t="n">
-        <v>0.770329654216766</v>
+        <v>0.770329535007477</v>
       </c>
       <c r="H890" t="n">
         <v>248918</v>
@@ -26237,7 +26237,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G892" t="n">
-        <v>0.775849461555481</v>
+        <v>0.775849401950836</v>
       </c>
       <c r="H892" t="n">
         <v>153630</v>
@@ -26295,7 +26295,7 @@
         <v>1.25</v>
       </c>
       <c r="G894" t="n">
-        <v>0.766649723052979</v>
+        <v>0.766649663448334</v>
       </c>
       <c r="H894" t="n">
         <v>155968</v>
@@ -26324,7 +26324,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G895" t="n">
-        <v>0.761743128299713</v>
+        <v>0.761743068695068</v>
       </c>
       <c r="H895" t="n">
         <v>419752</v>
@@ -26440,7 +26440,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G899" t="n">
-        <v>0.756836533546448</v>
+        <v>0.756836473941803</v>
       </c>
       <c r="H899" t="n">
         <v>111892</v>
@@ -26614,7 +26614,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G905" t="n">
-        <v>0.788729190826416</v>
+        <v>0.788729250431061</v>
       </c>
       <c r="H905" t="n">
         <v>739169</v>
@@ -26643,7 +26643,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G906" t="n">
-        <v>0.806515514850616</v>
+        <v>0.806515455245972</v>
       </c>
       <c r="H906" t="n">
         <v>571825</v>
@@ -26672,7 +26672,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G907" t="n">
-        <v>0.813261985778809</v>
+        <v>0.813262045383453</v>
       </c>
       <c r="H907" t="n">
         <v>280555</v>
@@ -26759,7 +26759,7 @@
         <v>1.25</v>
       </c>
       <c r="G910" t="n">
-        <v>0.766649723052979</v>
+        <v>0.766649663448334</v>
       </c>
       <c r="H910" t="n">
         <v>92063</v>
@@ -26904,7 +26904,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G915" t="n">
-        <v>0.721264004707336</v>
+        <v>0.721264064311981</v>
       </c>
       <c r="H915" t="n">
         <v>135340</v>
@@ -26933,7 +26933,7 @@
         <v>1.17900002002716</v>
       </c>
       <c r="G916" t="n">
-        <v>0.723104000091553</v>
+        <v>0.723103940486908</v>
       </c>
       <c r="H916" t="n">
         <v>38025</v>
@@ -26962,7 +26962,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G917" t="n">
-        <v>0.726170599460602</v>
+        <v>0.726170539855957</v>
       </c>
       <c r="H917" t="n">
         <v>65620</v>
@@ -27049,7 +27049,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G920" t="n">
-        <v>0.748250067234039</v>
+        <v>0.748250126838684</v>
       </c>
       <c r="H920" t="n">
         <v>337846</v>
@@ -27107,7 +27107,7 @@
         <v>1.18099999427795</v>
       </c>
       <c r="G922" t="n">
-        <v>0.724330604076385</v>
+        <v>0.72433066368103</v>
       </c>
       <c r="H922" t="n">
         <v>22435</v>
@@ -27223,7 +27223,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G926" t="n">
-        <v>0.792409062385559</v>
+        <v>0.792409121990204</v>
       </c>
       <c r="H926" t="n">
         <v>543195</v>
@@ -27281,7 +27281,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G928" t="n">
-        <v>0.770329654216766</v>
+        <v>0.770329535007477</v>
       </c>
       <c r="H928" t="n">
         <v>147741</v>
@@ -27310,7 +27310,7 @@
         <v>1.25</v>
       </c>
       <c r="G929" t="n">
-        <v>0.766649723052979</v>
+        <v>0.766649663448334</v>
       </c>
       <c r="H929" t="n">
         <v>80356</v>
@@ -27339,7 +27339,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G930" t="n">
-        <v>0.760516464710236</v>
+        <v>0.76051652431488</v>
       </c>
       <c r="H930" t="n">
         <v>93013</v>
@@ -27368,7 +27368,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G931" t="n">
-        <v>0.788729190826416</v>
+        <v>0.788729250431061</v>
       </c>
       <c r="H931" t="n">
         <v>296798</v>
@@ -27397,7 +27397,7 @@
         <v>1.25</v>
       </c>
       <c r="G932" t="n">
-        <v>0.766649723052979</v>
+        <v>0.766649663448334</v>
       </c>
       <c r="H932" t="n">
         <v>209670</v>
@@ -27513,7 +27513,7 @@
         <v>1.28400003910065</v>
       </c>
       <c r="G936" t="n">
-        <v>0.787502586841583</v>
+        <v>0.787502527236938</v>
       </c>
       <c r="H936" t="n">
         <v>379697</v>
@@ -27571,7 +27571,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G938" t="n">
-        <v>0.797315657138824</v>
+        <v>0.79731559753418</v>
       </c>
       <c r="H938" t="n">
         <v>317570</v>
@@ -27600,7 +27600,7 @@
         <v>1.33700001239777</v>
       </c>
       <c r="G939" t="n">
-        <v>0.820008456707001</v>
+        <v>0.820008516311646</v>
       </c>
       <c r="H939" t="n">
         <v>628585</v>
@@ -27716,7 +27716,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G943" t="n">
-        <v>0.837181389331818</v>
+        <v>0.837181448936462</v>
       </c>
       <c r="H943" t="n">
         <v>150974</v>
@@ -27745,7 +27745,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G944" t="n">
-        <v>0.832888185977936</v>
+        <v>0.832888245582581</v>
       </c>
       <c r="H944" t="n">
         <v>363471</v>
@@ -27803,7 +27803,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G946" t="n">
-        <v>0.840248048305511</v>
+        <v>0.840247988700867</v>
       </c>
       <c r="H946" t="n">
         <v>120742</v>
@@ -27832,7 +27832,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G947" t="n">
-        <v>0.829208314418793</v>
+        <v>0.829208254814148</v>
       </c>
       <c r="H947" t="n">
         <v>188418</v>
@@ -27919,7 +27919,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G950" t="n">
-        <v>0.754383265972137</v>
+        <v>0.754383325576782</v>
       </c>
       <c r="H950" t="n">
         <v>388069</v>
@@ -27948,7 +27948,7 @@
         <v>1.23099994659424</v>
       </c>
       <c r="G951" t="n">
-        <v>0.754996538162231</v>
+        <v>0.754996597766876</v>
       </c>
       <c r="H951" t="n">
         <v>184190</v>
@@ -27977,7 +27977,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G952" t="n">
-        <v>0.761743128299713</v>
+        <v>0.761743068695068</v>
       </c>
       <c r="H952" t="n">
         <v>112361</v>
@@ -28006,7 +28006,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G953" t="n">
-        <v>0.760516464710236</v>
+        <v>0.76051652431488</v>
       </c>
       <c r="H953" t="n">
         <v>55618</v>
@@ -28122,7 +28122,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G957" t="n">
-        <v>0.733530342578888</v>
+        <v>0.733530402183533</v>
       </c>
       <c r="H957" t="n">
         <v>98928</v>
@@ -28151,7 +28151,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G958" t="n">
-        <v>0.739050328731537</v>
+        <v>0.739050269126892</v>
       </c>
       <c r="H958" t="n">
         <v>114210</v>
@@ -28209,7 +28209,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G960" t="n">
-        <v>0.756836533546448</v>
+        <v>0.756836473941803</v>
       </c>
       <c r="H960" t="n">
         <v>114513</v>
@@ -28238,7 +28238,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G961" t="n">
-        <v>0.754383265972137</v>
+        <v>0.754383325576782</v>
       </c>
       <c r="H961" t="n">
         <v>137429</v>
@@ -28267,7 +28267,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G962" t="n">
-        <v>0.775849461555481</v>
+        <v>0.775849401950836</v>
       </c>
       <c r="H962" t="n">
         <v>214782</v>
@@ -28354,7 +28354,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G965" t="n">
-        <v>0.797315657138824</v>
+        <v>0.79731559753418</v>
       </c>
       <c r="H965" t="n">
         <v>236368</v>
@@ -28441,7 +28441,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G968" t="n">
-        <v>0.771556198596954</v>
+        <v>0.771556258201599</v>
       </c>
       <c r="H968" t="n">
         <v>106279</v>
@@ -28470,7 +28470,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G969" t="n">
-        <v>0.769102871417999</v>
+        <v>0.769102931022644</v>
       </c>
       <c r="H969" t="n">
         <v>152371</v>
@@ -28499,7 +28499,7 @@
         <v>1.25100004673004</v>
       </c>
       <c r="G970" t="n">
-        <v>0.767262995243073</v>
+        <v>0.767263054847717</v>
       </c>
       <c r="H970" t="n">
         <v>27949</v>
@@ -28586,7 +28586,7 @@
         <v>1.31599998474121</v>
       </c>
       <c r="G973" t="n">
-        <v>0.80712878704071</v>
+        <v>0.807128727436066</v>
       </c>
       <c r="H973" t="n">
         <v>703507</v>
@@ -28673,7 +28673,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G976" t="n">
-        <v>0.859874248504639</v>
+        <v>0.859874188899994</v>
       </c>
       <c r="H976" t="n">
         <v>387912</v>
@@ -28702,7 +28702,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G977" t="n">
-        <v>0.845154643058777</v>
+        <v>0.845154583454132</v>
       </c>
       <c r="H977" t="n">
         <v>146518</v>
@@ -28731,7 +28731,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G978" t="n">
-        <v>0.91077983379364</v>
+        <v>0.910779774188995</v>
       </c>
       <c r="H978" t="n">
         <v>814971</v>
@@ -28760,7 +28760,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G979" t="n">
-        <v>0.953712105751038</v>
+        <v>0.953712165355682</v>
       </c>
       <c r="H979" t="n">
         <v>1109248</v>
@@ -28818,7 +28818,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G981" t="n">
-        <v>0.981311500072479</v>
+        <v>0.981311619281769</v>
       </c>
       <c r="H981" t="n">
         <v>380709</v>
@@ -28847,7 +28847,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G982" t="n">
-        <v>0.94451242685318</v>
+        <v>0.944512367248535</v>
       </c>
       <c r="H982" t="n">
         <v>609647</v>
@@ -28876,7 +28876,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G983" t="n">
-        <v>0.937152504920959</v>
+        <v>0.937152564525604</v>
       </c>
       <c r="H983" t="n">
         <v>263445</v>
@@ -29021,7 +29021,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G988" t="n">
-        <v>0.875820577144623</v>
+        <v>0.875820517539978</v>
       </c>
       <c r="H988" t="n">
         <v>694818</v>
@@ -29079,7 +29079,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G990" t="n">
-        <v>0.87214070558548</v>
+        <v>0.872140765190125</v>
       </c>
       <c r="H990" t="n">
         <v>227729</v>
@@ -29137,7 +29137,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G992" t="n">
-        <v>0.884407043457031</v>
+        <v>0.884407103061676</v>
       </c>
       <c r="H992" t="n">
         <v>245509</v>
@@ -29166,7 +29166,7 @@
         <v>1.5</v>
       </c>
       <c r="G993" t="n">
-        <v>0.919979512691498</v>
+        <v>0.919979631900787</v>
       </c>
       <c r="H993" t="n">
         <v>297589</v>
@@ -29195,7 +29195,7 @@
         <v>1.53100001811981</v>
       </c>
       <c r="G994" t="n">
-        <v>0.938992559909821</v>
+        <v>0.938992500305176</v>
       </c>
       <c r="H994" t="n">
         <v>412888</v>
@@ -29224,7 +29224,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G995" t="n">
-        <v>0.954325437545776</v>
+        <v>0.954325556755066</v>
       </c>
       <c r="H995" t="n">
         <v>364299</v>
@@ -29282,7 +29282,7 @@
         <v>1.49300003051758</v>
       </c>
       <c r="G997" t="n">
-        <v>0.915686309337616</v>
+        <v>0.915686368942261</v>
       </c>
       <c r="H997" t="n">
         <v>223364</v>
@@ -29311,7 +29311,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G998" t="n">
-        <v>0.935312569141388</v>
+        <v>0.935312628746033</v>
       </c>
       <c r="H998" t="n">
         <v>1239866</v>
@@ -29340,7 +29340,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G999" t="n">
-        <v>0.918753027915955</v>
+        <v>0.918752908706665</v>
       </c>
       <c r="H999" t="n">
         <v>695778</v>
@@ -29369,7 +29369,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1000" t="n">
-        <v>0.928566157817841</v>
+        <v>0.928566098213196</v>
       </c>
       <c r="H1000" t="n">
         <v>238212</v>
@@ -29427,7 +29427,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G1002" t="n">
-        <v>0.918753027915955</v>
+        <v>0.918752908706665</v>
       </c>
       <c r="H1002" t="n">
         <v>198540</v>
@@ -29456,7 +29456,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G1003" t="n">
-        <v>0.918753027915955</v>
+        <v>0.918752908706665</v>
       </c>
       <c r="H1003" t="n">
         <v>784488</v>
@@ -29485,7 +29485,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1004" t="n">
-        <v>0.96291196346283</v>
+        <v>0.962912023067474</v>
       </c>
       <c r="H1004" t="n">
         <v>1240368</v>
@@ -29514,7 +29514,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.04141700267792</v>
+        <v>1.04141688346863</v>
       </c>
       <c r="H1005" t="n">
         <v>2397908</v>
@@ -29601,7 +29601,7 @@
         <v>1.73099994659424</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.06165647506714</v>
+        <v>1.06165635585785</v>
       </c>
       <c r="H1008" t="n">
         <v>598181</v>
@@ -29688,7 +29688,7 @@
         <v>1.63900005817413</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.00523114204407</v>
+        <v>1.00523102283478</v>
       </c>
       <c r="H1011" t="n">
         <v>927265</v>
@@ -29717,7 +29717,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.00277781486511</v>
+        <v>1.00277769565582</v>
       </c>
       <c r="H1012" t="n">
         <v>2587600</v>
@@ -29746,7 +29746,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1013" t="n">
-        <v>0.987444758415222</v>
+        <v>0.987444818019867</v>
       </c>
       <c r="H1013" t="n">
         <v>1079055</v>
@@ -29775,7 +29775,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1014" t="n">
-        <v>0.980085015296936</v>
+        <v>0.980084955692291</v>
       </c>
       <c r="H1014" t="n">
         <v>523079</v>
@@ -29804,7 +29804,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1015" t="n">
-        <v>0.980085015296936</v>
+        <v>0.980084955692291</v>
       </c>
       <c r="H1015" t="n">
         <v>426514</v>
@@ -29833,7 +29833,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G1016" t="n">
-        <v>0.986218154430389</v>
+        <v>0.986218094825745</v>
       </c>
       <c r="H1016" t="n">
         <v>668830</v>
@@ -29862,7 +29862,7 @@
         <v>1.57599997520447</v>
       </c>
       <c r="G1017" t="n">
-        <v>0.966591835021973</v>
+        <v>0.966591894626617</v>
       </c>
       <c r="H1017" t="n">
         <v>660847</v>
@@ -29891,7 +29891,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1018" t="n">
-        <v>0.94451242685318</v>
+        <v>0.944512367248535</v>
       </c>
       <c r="H1018" t="n">
         <v>455781</v>
@@ -29920,7 +29920,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G1019" t="n">
-        <v>0.958618640899658</v>
+        <v>0.958618700504303</v>
       </c>
       <c r="H1019" t="n">
         <v>288466</v>
@@ -29949,7 +29949,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1020" t="n">
-        <v>0.956778824329376</v>
+        <v>0.956778764724731</v>
       </c>
       <c r="H1020" t="n">
         <v>270776</v>
@@ -30007,7 +30007,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1022" t="n">
-        <v>0.965978682041168</v>
+        <v>0.965978622436523</v>
       </c>
       <c r="H1022" t="n">
         <v>372971</v>
@@ -30036,7 +30036,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G1023" t="n">
-        <v>0.967205166816711</v>
+        <v>0.967205226421356</v>
       </c>
       <c r="H1023" t="n">
         <v>273940</v>
@@ -30065,7 +30065,7 @@
         <v>1.58899998664856</v>
       </c>
       <c r="G1024" t="n">
-        <v>0.974565088748932</v>
+        <v>0.974565029144287</v>
       </c>
       <c r="H1024" t="n">
         <v>315897</v>
@@ -30094,7 +30094,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1025" t="n">
-        <v>0.980085015296936</v>
+        <v>0.980084955692291</v>
       </c>
       <c r="H1025" t="n">
         <v>570459</v>
@@ -30123,7 +30123,7 @@
         <v>1.58700001239777</v>
       </c>
       <c r="G1026" t="n">
-        <v>0.973338305950165</v>
+        <v>0.973338484764099</v>
       </c>
       <c r="H1026" t="n">
         <v>768858</v>
@@ -30210,7 +30210,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1029" t="n">
-        <v>0.858647584915161</v>
+        <v>0.858647644519806</v>
       </c>
       <c r="H1029" t="n">
         <v>586405</v>
@@ -30268,7 +30268,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1031" t="n">
-        <v>0.815715253353119</v>
+        <v>0.815715193748474</v>
       </c>
       <c r="H1031" t="n">
         <v>572298</v>
@@ -30297,7 +30297,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1032" t="n">
-        <v>0.797315657138824</v>
+        <v>0.79731559753418</v>
       </c>
       <c r="H1032" t="n">
         <v>989532</v>
@@ -30442,7 +30442,7 @@
         <v>1.28400003910065</v>
       </c>
       <c r="G1037" t="n">
-        <v>0.787502586841583</v>
+        <v>0.787502527236938</v>
       </c>
       <c r="H1037" t="n">
         <v>524349</v>
@@ -30500,7 +30500,7 @@
         <v>1.2940000295639</v>
       </c>
       <c r="G1039" t="n">
-        <v>0.793635785579681</v>
+        <v>0.793635725975037</v>
       </c>
       <c r="H1039" t="n">
         <v>278799</v>
@@ -30674,7 +30674,7 @@
         <v>1.33700001239777</v>
       </c>
       <c r="G1045" t="n">
-        <v>0.820008456707001</v>
+        <v>0.820008516311646</v>
       </c>
       <c r="H1045" t="n">
         <v>582765</v>
@@ -30703,7 +30703,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G1046" t="n">
-        <v>0.806515514850616</v>
+        <v>0.806515455245972</v>
       </c>
       <c r="H1046" t="n">
         <v>278628</v>
@@ -30761,7 +30761,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G1048" t="n">
-        <v>0.814488530158997</v>
+        <v>0.814488589763641</v>
       </c>
       <c r="H1048" t="n">
         <v>245739</v>
@@ -30790,7 +30790,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1049" t="n">
-        <v>0.813261985778809</v>
+        <v>0.813262045383453</v>
       </c>
       <c r="H1049" t="n">
         <v>258815</v>
@@ -30819,7 +30819,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1050" t="n">
-        <v>0.803448796272278</v>
+        <v>0.803448855876923</v>
       </c>
       <c r="H1050" t="n">
         <v>319934</v>
@@ -30877,7 +30877,7 @@
         <v>1.28699994087219</v>
       </c>
       <c r="G1052" t="n">
-        <v>0.78934246301651</v>
+        <v>0.789342522621155</v>
       </c>
       <c r="H1052" t="n">
         <v>394105</v>
@@ -30935,7 +30935,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G1054" t="n">
-        <v>0.721264004707336</v>
+        <v>0.721264064311981</v>
       </c>
       <c r="H1054" t="n">
         <v>1222841</v>
@@ -31022,7 +31022,7 @@
         <v>1.07299995422363</v>
       </c>
       <c r="G1057" t="n">
-        <v>0.658092081546783</v>
+        <v>0.658092021942139</v>
       </c>
       <c r="H1057" t="n">
         <v>669322</v>
@@ -31312,7 +31312,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.451403319835663</v>
+        <v>0.451403349637985</v>
       </c>
       <c r="H1067" t="n">
         <v>964293</v>
@@ -31370,7 +31370,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.47225621342659</v>
+        <v>0.472256183624268</v>
       </c>
       <c r="H1069" t="n">
         <v>461033</v>
@@ -31399,7 +31399,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.461216419935226</v>
+        <v>0.461216449737549</v>
       </c>
       <c r="H1070" t="n">
         <v>387884</v>
@@ -31428,7 +31428,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.474709451198578</v>
+        <v>0.4747094810009</v>
       </c>
       <c r="H1071" t="n">
         <v>273830</v>
@@ -31457,7 +31457,7 @@
         <v>0.806999981403351</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.494949012994766</v>
+        <v>0.494949042797089</v>
       </c>
       <c r="H1072" t="n">
         <v>544462</v>
@@ -31486,7 +31486,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.49065575003624</v>
+        <v>0.490655809640884</v>
       </c>
       <c r="H1073" t="n">
         <v>143879</v>
@@ -31544,7 +31544,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.469802886247635</v>
+        <v>0.469802916049957</v>
       </c>
       <c r="H1075" t="n">
         <v>576348</v>
@@ -31573,7 +31573,7 @@
         <v>0.732999980449677</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.449563324451447</v>
+        <v>0.449563354253769</v>
       </c>
       <c r="H1076" t="n">
         <v>402235</v>
@@ -31631,7 +31631,7 @@
         <v>0.679000020027161</v>
       </c>
       <c r="G1078" t="n">
-        <v>0.416444092988968</v>
+        <v>0.41644412279129</v>
       </c>
       <c r="H1078" t="n">
         <v>305317</v>
@@ -31718,7 +31718,7 @@
         <v>0.679000020027161</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.416444092988968</v>
+        <v>0.41644412279129</v>
       </c>
       <c r="H1081" t="n">
         <v>566218</v>
@@ -31747,7 +31747,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.434230387210846</v>
+        <v>0.434230357408524</v>
       </c>
       <c r="H1082" t="n">
         <v>718601</v>
@@ -32095,7 +32095,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G1094" t="n">
-        <v>0.559347569942474</v>
+        <v>0.559347629547119</v>
       </c>
       <c r="H1094" t="n">
         <v>255686</v>
@@ -32124,7 +32124,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1095" t="n">
-        <v>0.533588111400604</v>
+        <v>0.533588171005249</v>
       </c>
       <c r="H1095" t="n">
         <v>655537</v>
@@ -32153,7 +32153,7 @@
         <v>0.880999982357025</v>
       </c>
       <c r="G1096" t="n">
-        <v>0.540334641933441</v>
+        <v>0.540334701538086</v>
       </c>
       <c r="H1096" t="n">
         <v>135566</v>
@@ -32182,7 +32182,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1097" t="n">
-        <v>0.543401300907135</v>
+        <v>0.54340124130249</v>
       </c>
       <c r="H1097" t="n">
         <v>178955</v>
@@ -32211,7 +32211,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1098" t="n">
-        <v>0.533588111400604</v>
+        <v>0.533588171005249</v>
       </c>
       <c r="H1098" t="n">
         <v>299617</v>
@@ -32298,7 +32298,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.506602048873901</v>
+        <v>0.506602108478546</v>
       </c>
       <c r="H1101" t="n">
         <v>179925</v>
@@ -32327,7 +32327,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1102" t="n">
-        <v>0.504148781299591</v>
+        <v>0.504148840904236</v>
       </c>
       <c r="H1102" t="n">
         <v>84582</v>
@@ -32559,7 +32559,7 @@
         <v>0.848999977111816</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.520708501338959</v>
+        <v>0.520708441734314</v>
       </c>
       <c r="H1110" t="n">
         <v>181006</v>
@@ -32617,7 +32617,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.493109077215195</v>
+        <v>0.493109047412872</v>
       </c>
       <c r="H1112" t="n">
         <v>413811</v>
@@ -32646,7 +32646,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.49188244342804</v>
+        <v>0.491882383823395</v>
       </c>
       <c r="H1113" t="n">
         <v>111204</v>
@@ -32704,7 +32704,7 @@
         <v>0.805000007152557</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.493722379207611</v>
+        <v>0.493722409009933</v>
       </c>
       <c r="H1115" t="n">
         <v>158477</v>
@@ -32762,7 +32762,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1117" t="n">
-        <v>0.551987767219543</v>
+        <v>0.551987707614899</v>
       </c>
       <c r="H1117" t="n">
         <v>1116754</v>
@@ -32849,7 +32849,7 @@
         <v>0.888999998569489</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.545241236686707</v>
+        <v>0.545241296291351</v>
       </c>
       <c r="H1120" t="n">
         <v>365185</v>
@@ -32907,7 +32907,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G1122" t="n">
-        <v>0.610866487026215</v>
+        <v>0.61086642742157</v>
       </c>
       <c r="H1122" t="n">
         <v>886047</v>
@@ -32936,7 +32936,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1123" t="n">
-        <v>0.637852489948273</v>
+        <v>0.637852549552917</v>
       </c>
       <c r="H1123" t="n">
         <v>763871</v>
@@ -32965,7 +32965,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1124" t="n">
-        <v>0.643985629081726</v>
+        <v>0.643985688686371</v>
       </c>
       <c r="H1124" t="n">
         <v>645259</v>
@@ -32994,7 +32994,7 @@
         <v>1.07400000095367</v>
       </c>
       <c r="G1125" t="n">
-        <v>0.658705353736877</v>
+        <v>0.658705413341522</v>
       </c>
       <c r="H1125" t="n">
         <v>626443</v>
@@ -33052,7 +33052,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G1127" t="n">
-        <v>0.610866487026215</v>
+        <v>0.61086642742157</v>
       </c>
       <c r="H1127" t="n">
         <v>500431</v>
@@ -33168,7 +33168,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G1131" t="n">
-        <v>0.554441094398499</v>
+        <v>0.554441034793854</v>
       </c>
       <c r="H1131" t="n">
         <v>721039</v>
@@ -33197,7 +33197,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1132" t="n">
-        <v>0.551987767219543</v>
+        <v>0.551987707614899</v>
       </c>
       <c r="H1132" t="n">
         <v>204586</v>
@@ -33487,7 +33487,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1142" t="n">
-        <v>0.504148781299591</v>
+        <v>0.504148840904236</v>
       </c>
       <c r="H1142" t="n">
         <v>275625</v>
@@ -33574,7 +33574,7 @@
         <v>0.837000012397766</v>
       </c>
       <c r="G1145" t="n">
-        <v>0.513348579406738</v>
+        <v>0.513348639011383</v>
       </c>
       <c r="H1145" t="n">
         <v>169771</v>
@@ -33603,7 +33603,7 @@
         <v>0.845000028610229</v>
       </c>
       <c r="G1146" t="n">
-        <v>0.518255233764648</v>
+        <v>0.518255174160004</v>
       </c>
       <c r="H1146" t="n">
         <v>86454</v>
@@ -33690,7 +33690,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1149" t="n">
-        <v>0.52254843711853</v>
+        <v>0.522548377513885</v>
       </c>
       <c r="H1149" t="n">
         <v>155783</v>
@@ -33719,7 +33719,7 @@
         <v>0.859000027179718</v>
       </c>
       <c r="G1150" t="n">
-        <v>0.526841700077057</v>
+        <v>0.526841640472412</v>
       </c>
       <c r="H1150" t="n">
         <v>153721</v>
@@ -33806,7 +33806,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.555054306983948</v>
+        <v>0.555054366588593</v>
       </c>
       <c r="H1153" t="n">
         <v>178213</v>
@@ -33835,7 +33835,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G1154" t="n">
-        <v>0.542787909507751</v>
+        <v>0.542787969112396</v>
       </c>
       <c r="H1154" t="n">
         <v>194414</v>
@@ -33864,7 +33864,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1155" t="n">
-        <v>0.538494765758514</v>
+        <v>0.53849470615387</v>
       </c>
       <c r="H1155" t="n">
         <v>65264</v>
@@ -33980,7 +33980,7 @@
         <v>0.879000008106232</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.539108097553253</v>
+        <v>0.539108037948608</v>
       </c>
       <c r="H1159" t="n">
         <v>107708</v>
@@ -34038,7 +34038,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G1161" t="n">
-        <v>0.542787909507751</v>
+        <v>0.542787969112396</v>
       </c>
       <c r="H1161" t="n">
         <v>343997</v>
@@ -34067,7 +34067,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1162" t="n">
-        <v>0.551987767219543</v>
+        <v>0.551987707614899</v>
       </c>
       <c r="H1162" t="n">
         <v>382932</v>
@@ -34125,7 +34125,7 @@
         <v>0.879000008106232</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.539108097553253</v>
+        <v>0.539108037948608</v>
       </c>
       <c r="H1164" t="n">
         <v>179069</v>
@@ -34270,7 +34270,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.567320764064789</v>
+        <v>0.567320704460144</v>
       </c>
       <c r="H1169" t="n">
         <v>120442</v>
@@ -34328,7 +34328,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G1171" t="n">
-        <v>0.604733288288116</v>
+        <v>0.604733228683472</v>
       </c>
       <c r="H1171" t="n">
         <v>233144</v>
@@ -34357,7 +34357,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.601053357124329</v>
+        <v>0.601053297519684</v>
       </c>
       <c r="H1172" t="n">
         <v>119918</v>
@@ -34415,7 +34415,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.582653701305389</v>
+        <v>0.582653760910034</v>
       </c>
       <c r="H1174" t="n">
         <v>159888</v>
@@ -34473,7 +34473,7 @@
         <v>0.930999994277954</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.571000695228577</v>
+        <v>0.571000635623932</v>
       </c>
       <c r="H1176" t="n">
         <v>76615</v>
@@ -34502,7 +34502,7 @@
         <v>0.962999999523163</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.590626955032349</v>
+        <v>0.590626895427704</v>
       </c>
       <c r="H1177" t="n">
         <v>110900</v>
@@ -34531,7 +34531,7 @@
         <v>0.962999999523163</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.590626955032349</v>
+        <v>0.590626895427704</v>
       </c>
       <c r="H1178" t="n">
         <v>48968</v>
@@ -34560,7 +34560,7 @@
         <v>0.964999973773956</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.591853499412537</v>
+        <v>0.591853559017181</v>
       </c>
       <c r="H1179" t="n">
         <v>247116</v>
@@ -34618,7 +34618,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.588786900043488</v>
+        <v>0.588786959648132</v>
       </c>
       <c r="H1181" t="n">
         <v>72156</v>
@@ -34676,7 +34676,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.578973829746246</v>
+        <v>0.578973889350891</v>
       </c>
       <c r="H1183" t="n">
         <v>46587</v>
@@ -34734,7 +34734,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.559347569942474</v>
+        <v>0.559347629547119</v>
       </c>
       <c r="H1185" t="n">
         <v>112566</v>
@@ -34763,7 +34763,7 @@
         <v>0.902999997138977</v>
       </c>
       <c r="G1186" t="n">
-        <v>0.553827702999115</v>
+        <v>0.55382776260376</v>
       </c>
       <c r="H1186" t="n">
         <v>407591</v>
@@ -34792,7 +34792,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.576520502567291</v>
+        <v>0.576520562171936</v>
       </c>
       <c r="H1187" t="n">
         <v>133864</v>
@@ -34879,7 +34879,7 @@
         <v>0.916999995708466</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.562414169311523</v>
+        <v>0.562414228916168</v>
       </c>
       <c r="H1190" t="n">
         <v>129939</v>
@@ -34908,7 +34908,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.547081172466278</v>
+        <v>0.547081232070923</v>
       </c>
       <c r="H1191" t="n">
         <v>73041</v>
@@ -35111,7 +35111,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.59246689081192</v>
+        <v>0.592466831207275</v>
       </c>
       <c r="H1198" t="n">
         <v>237851</v>
@@ -35140,7 +35140,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G1199" t="n">
-        <v>0.561800897121429</v>
+        <v>0.561800837516785</v>
       </c>
       <c r="H1199" t="n">
         <v>183721</v>
@@ -35169,7 +35169,7 @@
         <v>0.89300000667572</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.547694563865662</v>
+        <v>0.547694504261017</v>
       </c>
       <c r="H1200" t="n">
         <v>153127</v>
@@ -35198,7 +35198,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.551987767219543</v>
+        <v>0.551987707614899</v>
       </c>
       <c r="H1201" t="n">
         <v>188883</v>
@@ -35285,7 +35285,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G1204" t="n">
-        <v>0.555054306983948</v>
+        <v>0.555054366588593</v>
       </c>
       <c r="H1204" t="n">
         <v>55490</v>
@@ -35459,7 +35459,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.576520502567291</v>
+        <v>0.576520562171936</v>
       </c>
       <c r="H1210" t="n">
         <v>31625</v>
@@ -35517,7 +35517,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1212" t="n">
-        <v>0.576520502567291</v>
+        <v>0.576520562171936</v>
       </c>
       <c r="H1212" t="n">
         <v>65395</v>
@@ -35546,7 +35546,7 @@
         <v>0.958999991416931</v>
       </c>
       <c r="G1213" t="n">
-        <v>0.588173687458038</v>
+        <v>0.588173627853394</v>
       </c>
       <c r="H1213" t="n">
         <v>77828</v>
@@ -35604,7 +35604,7 @@
         <v>0.953000009059906</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.584493696689606</v>
+        <v>0.58449375629425</v>
       </c>
       <c r="H1215" t="n">
         <v>35577</v>
@@ -35662,7 +35662,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.576520502567291</v>
+        <v>0.576520562171936</v>
       </c>
       <c r="H1217" t="n">
         <v>57725</v>
@@ -35807,7 +35807,7 @@
         <v>0.888999998569489</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.545241236686707</v>
+        <v>0.545241296291351</v>
       </c>
       <c r="H1222" t="n">
         <v>106986</v>
@@ -35894,7 +35894,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.576520502567291</v>
+        <v>0.576520562171936</v>
       </c>
       <c r="H1225" t="n">
         <v>611268</v>
@@ -36039,7 +36039,7 @@
         <v>0.916999995708466</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.562414169311523</v>
+        <v>0.562414228916168</v>
       </c>
       <c r="H1230" t="n">
         <v>70429</v>
@@ -36126,7 +36126,7 @@
         <v>0.967000007629395</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.593080163002014</v>
+        <v>0.593080222606659</v>
       </c>
       <c r="H1233" t="n">
         <v>53370</v>
@@ -36155,7 +36155,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.588786900043488</v>
+        <v>0.588786959648132</v>
       </c>
       <c r="H1234" t="n">
         <v>47192</v>
@@ -36184,7 +36184,7 @@
         <v>1.01600003242493</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.623132824897766</v>
+        <v>0.623132884502411</v>
       </c>
       <c r="H1235" t="n">
         <v>290003</v>
@@ -36242,7 +36242,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.625586092472076</v>
+        <v>0.625586152076721</v>
       </c>
       <c r="H1237" t="n">
         <v>166551</v>
@@ -36271,7 +36271,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1238" t="n">
-        <v>0.625586092472076</v>
+        <v>0.625586152076721</v>
       </c>
       <c r="H1238" t="n">
         <v>72929</v>
@@ -36387,7 +36387,7 @@
         <v>1.15799999237061</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.710224270820618</v>
+        <v>0.710224330425262</v>
       </c>
       <c r="H1242" t="n">
         <v>253980</v>
@@ -36445,7 +36445,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.697957813739777</v>
+        <v>0.697957932949066</v>
       </c>
       <c r="H1244" t="n">
         <v>343735</v>
@@ -36503,7 +36503,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1246" t="n">
-        <v>0.726170599460602</v>
+        <v>0.726170539855957</v>
       </c>
       <c r="H1246" t="n">
         <v>231356</v>
@@ -36532,7 +36532,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1247" t="n">
-        <v>0.788729190826416</v>
+        <v>0.788729250431061</v>
       </c>
       <c r="H1247" t="n">
         <v>694692</v>
@@ -36561,7 +36561,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.775236189365387</v>
+        <v>0.775236129760742</v>
       </c>
       <c r="H1248" t="n">
         <v>177276</v>
@@ -36677,7 +36677,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1252" t="n">
-        <v>0.754383265972137</v>
+        <v>0.754383325576782</v>
       </c>
       <c r="H1252" t="n">
         <v>109391</v>
@@ -36706,7 +36706,7 @@
         <v>1.25</v>
       </c>
       <c r="G1253" t="n">
-        <v>0.766649723052979</v>
+        <v>0.766649663448334</v>
       </c>
       <c r="H1253" t="n">
         <v>88845</v>
@@ -36735,7 +36735,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G1254" t="n">
-        <v>0.756836533546448</v>
+        <v>0.756836473941803</v>
       </c>
       <c r="H1254" t="n">
         <v>67261</v>
@@ -36793,7 +36793,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1256" t="n">
-        <v>0.769102871417999</v>
+        <v>0.769102931022644</v>
       </c>
       <c r="H1256" t="n">
         <v>128864</v>
@@ -36938,7 +36938,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.748250067234039</v>
+        <v>0.748250126838684</v>
       </c>
       <c r="H1261" t="n">
         <v>99221</v>
@@ -36967,7 +36967,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1262" t="n">
-        <v>0.759289860725403</v>
+        <v>0.759289801120758</v>
       </c>
       <c r="H1262" t="n">
         <v>121252</v>
@@ -36996,7 +36996,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1263" t="n">
-        <v>0.764196455478668</v>
+        <v>0.764196395874023</v>
       </c>
       <c r="H1263" t="n">
         <v>90228</v>
@@ -37054,7 +37054,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.712677478790283</v>
+        <v>0.712677538394928</v>
       </c>
       <c r="H1265" t="n">
         <v>252252</v>
@@ -37228,7 +37228,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.73475706577301</v>
+        <v>0.734757006168365</v>
       </c>
       <c r="H1271" t="n">
         <v>87758</v>
@@ -37286,7 +37286,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G1273" t="n">
-        <v>0.737210333347321</v>
+        <v>0.737210273742676</v>
       </c>
       <c r="H1273" t="n">
         <v>45762</v>
@@ -37315,7 +37315,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.761743128299713</v>
+        <v>0.761743068695068</v>
       </c>
       <c r="H1274" t="n">
         <v>257120</v>
@@ -37402,7 +37402,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1277" t="n">
-        <v>0.748250067234039</v>
+        <v>0.748250126838684</v>
       </c>
       <c r="H1277" t="n">
         <v>128905</v>
@@ -37460,7 +37460,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1279" t="n">
-        <v>0.748250067234039</v>
+        <v>0.748250126838684</v>
       </c>
       <c r="H1279" t="n">
         <v>104631</v>
@@ -37489,7 +37489,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G1280" t="n">
-        <v>0.728623867034912</v>
+        <v>0.728623807430267</v>
       </c>
       <c r="H1280" t="n">
         <v>106827</v>
@@ -37518,7 +37518,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1281" t="n">
-        <v>0.720037400722504</v>
+        <v>0.720037341117859</v>
       </c>
       <c r="H1281" t="n">
         <v>71454</v>
@@ -37692,7 +37692,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1287" t="n">
-        <v>0.712677478790283</v>
+        <v>0.712677538394928</v>
       </c>
       <c r="H1287" t="n">
         <v>89003</v>
@@ -37750,7 +37750,7 @@
         <v>1.14800000190735</v>
       </c>
       <c r="G1289" t="n">
-        <v>0.704091012477875</v>
+        <v>0.70409107208252</v>
       </c>
       <c r="H1289" t="n">
         <v>77619</v>
@@ -37837,7 +37837,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.690598011016846</v>
+        <v>0.69059807062149</v>
       </c>
       <c r="H1292" t="n">
         <v>43018</v>
@@ -37866,7 +37866,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1293" t="n">
-        <v>0.693051278591156</v>
+        <v>0.693051338195801</v>
       </c>
       <c r="H1293" t="n">
         <v>114472</v>
@@ -37924,7 +37924,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.720037400722504</v>
+        <v>0.720037341117859</v>
       </c>
       <c r="H1295" t="n">
         <v>130325</v>
@@ -38098,7 +38098,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1301" t="n">
-        <v>0.748250067234039</v>
+        <v>0.748250126838684</v>
       </c>
       <c r="H1301" t="n">
         <v>82491</v>
@@ -38127,7 +38127,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1302" t="n">
-        <v>0.769102871417999</v>
+        <v>0.769102931022644</v>
       </c>
       <c r="H1302" t="n">
         <v>923737</v>
@@ -38156,7 +38156,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1303" t="n">
-        <v>0.760516464710236</v>
+        <v>0.76051652431488</v>
       </c>
       <c r="H1303" t="n">
         <v>59895</v>
@@ -38185,7 +38185,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1304" t="n">
-        <v>0.759289860725403</v>
+        <v>0.759289801120758</v>
       </c>
       <c r="H1304" t="n">
         <v>121379</v>
@@ -38214,7 +38214,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1305" t="n">
-        <v>0.764196455478668</v>
+        <v>0.764196395874023</v>
       </c>
       <c r="H1305" t="n">
         <v>63773</v>
@@ -38243,7 +38243,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1306" t="n">
-        <v>0.762969672679901</v>
+        <v>0.762969791889191</v>
       </c>
       <c r="H1306" t="n">
         <v>43432</v>
@@ -38272,7 +38272,7 @@
         <v>1.24800002574921</v>
       </c>
       <c r="G1307" t="n">
-        <v>0.765422999858856</v>
+        <v>0.765422940254211</v>
       </c>
       <c r="H1307" t="n">
         <v>95806</v>
@@ -38301,7 +38301,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1308" t="n">
-        <v>0.769102871417999</v>
+        <v>0.769102931022644</v>
       </c>
       <c r="H1308" t="n">
         <v>93854</v>
@@ -38330,7 +38330,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.797315657138824</v>
+        <v>0.79731559753418</v>
       </c>
       <c r="H1309" t="n">
         <v>791184</v>
@@ -38417,7 +38417,7 @@
         <v>1.32200002670288</v>
       </c>
       <c r="G1312" t="n">
-        <v>0.810808718204498</v>
+        <v>0.810808777809143</v>
       </c>
       <c r="H1312" t="n">
         <v>328150</v>
@@ -38475,7 +38475,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1314" t="n">
-        <v>0.824301719665527</v>
+        <v>0.824301660060883</v>
       </c>
       <c r="H1314" t="n">
         <v>64998</v>
@@ -38504,7 +38504,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.803448796272278</v>
+        <v>0.803448855876923</v>
       </c>
       <c r="H1315" t="n">
         <v>119343</v>
@@ -38533,7 +38533,7 @@
         <v>1.31400001049042</v>
       </c>
       <c r="G1316" t="n">
-        <v>0.805902123451233</v>
+        <v>0.805902183055878</v>
       </c>
       <c r="H1316" t="n">
         <v>74558</v>
@@ -38562,7 +38562,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1317" t="n">
-        <v>0.769102871417999</v>
+        <v>0.769102931022644</v>
       </c>
       <c r="H1317" t="n">
         <v>567764</v>
@@ -38591,7 +38591,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1318" t="n">
-        <v>0.797315657138824</v>
+        <v>0.79731559753418</v>
       </c>
       <c r="H1318" t="n">
         <v>326078</v>
@@ -38620,7 +38620,7 @@
         <v>1.28400003910065</v>
       </c>
       <c r="G1319" t="n">
-        <v>0.787502586841583</v>
+        <v>0.787502527236938</v>
       </c>
       <c r="H1319" t="n">
         <v>137229</v>
@@ -38649,7 +38649,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1320" t="n">
-        <v>0.792409062385559</v>
+        <v>0.792409121990204</v>
       </c>
       <c r="H1320" t="n">
         <v>90832</v>
@@ -38678,7 +38678,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1321" t="n">
-        <v>0.815715253353119</v>
+        <v>0.815715193748474</v>
       </c>
       <c r="H1321" t="n">
         <v>297429</v>
@@ -38707,7 +38707,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1322" t="n">
-        <v>0.835341513156891</v>
+        <v>0.835341393947601</v>
       </c>
       <c r="H1322" t="n">
         <v>275179</v>
@@ -38736,7 +38736,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G1323" t="n">
-        <v>0.841474652290344</v>
+        <v>0.841474711894989</v>
       </c>
       <c r="H1323" t="n">
         <v>216478</v>
@@ -38765,7 +38765,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1324" t="n">
-        <v>0.858647584915161</v>
+        <v>0.858647644519806</v>
       </c>
       <c r="H1324" t="n">
         <v>364891</v>
@@ -38794,7 +38794,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1325" t="n">
-        <v>0.858647584915161</v>
+        <v>0.858647644519806</v>
       </c>
       <c r="H1325" t="n">
         <v>204003</v>
@@ -38823,7 +38823,7 @@
         <v>1.38399994373322</v>
       </c>
       <c r="G1326" t="n">
-        <v>0.84883451461792</v>
+        <v>0.848834455013275</v>
       </c>
       <c r="H1326" t="n">
         <v>212647</v>
@@ -38852,7 +38852,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G1327" t="n">
-        <v>0.829208314418793</v>
+        <v>0.829208254814148</v>
       </c>
       <c r="H1327" t="n">
         <v>144710</v>
@@ -38881,7 +38881,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1328" t="n">
-        <v>0.840248048305511</v>
+        <v>0.840247988700867</v>
       </c>
       <c r="H1328" t="n">
         <v>87547</v>
@@ -38910,7 +38910,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1329" t="n">
-        <v>0.813261985778809</v>
+        <v>0.813262045383453</v>
       </c>
       <c r="H1329" t="n">
         <v>142351</v>
@@ -38968,7 +38968,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1331" t="n">
-        <v>0.837794840335846</v>
+        <v>0.837794721126556</v>
       </c>
       <c r="H1331" t="n">
         <v>112011</v>
@@ -39026,7 +39026,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1333" t="n">
-        <v>0.813261985778809</v>
+        <v>0.813262045383453</v>
       </c>
       <c r="H1333" t="n">
         <v>89577</v>
@@ -39113,7 +39113,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1336" t="n">
-        <v>0.846381187438965</v>
+        <v>0.84638124704361</v>
       </c>
       <c r="H1336" t="n">
         <v>167091</v>
@@ -39171,7 +39171,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1338" t="n">
-        <v>0.813261985778809</v>
+        <v>0.813262045383453</v>
       </c>
       <c r="H1338" t="n">
         <v>138577</v>
@@ -39287,7 +39287,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G1342" t="n">
-        <v>0.841474652290344</v>
+        <v>0.841474711894989</v>
       </c>
       <c r="H1342" t="n">
         <v>68917</v>
@@ -39316,7 +39316,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G1343" t="n">
-        <v>0.842701315879822</v>
+        <v>0.842701256275177</v>
       </c>
       <c r="H1343" t="n">
         <v>92663</v>
@@ -39345,7 +39345,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G1344" t="n">
-        <v>0.842701315879822</v>
+        <v>0.842701256275177</v>
       </c>
       <c r="H1344" t="n">
         <v>50622</v>
@@ -39374,7 +39374,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1345" t="n">
-        <v>0.815715253353119</v>
+        <v>0.815715193748474</v>
       </c>
       <c r="H1345" t="n">
         <v>121011</v>
@@ -39432,7 +39432,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1347" t="n">
-        <v>0.803448796272278</v>
+        <v>0.803448855876923</v>
       </c>
       <c r="H1347" t="n">
         <v>156487</v>
@@ -39490,7 +39490,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G1349" t="n">
-        <v>0.853741109371185</v>
+        <v>0.853741049766541</v>
       </c>
       <c r="H1349" t="n">
         <v>1336786</v>
@@ -39519,7 +39519,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1350" t="n">
-        <v>0.870913982391357</v>
+        <v>0.870914041996002</v>
       </c>
       <c r="H1350" t="n">
         <v>1164717</v>
@@ -39548,7 +39548,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1351" t="n">
-        <v>0.8770472407341</v>
+        <v>0.877047181129456</v>
       </c>
       <c r="H1351" t="n">
         <v>713545</v>
@@ -39577,7 +39577,7 @@
         <v>1.43799996376038</v>
       </c>
       <c r="G1352" t="n">
-        <v>0.881953716278076</v>
+        <v>0.881953775882721</v>
       </c>
       <c r="H1352" t="n">
         <v>370355</v>
@@ -39606,7 +39606,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G1353" t="n">
-        <v>0.867234110832214</v>
+        <v>0.867234170436859</v>
       </c>
       <c r="H1353" t="n">
         <v>320259</v>
@@ -39751,7 +39751,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G1358" t="n">
-        <v>0.87214070558548</v>
+        <v>0.872140765190125</v>
       </c>
       <c r="H1358" t="n">
         <v>252612</v>
@@ -39780,7 +39780,7 @@
         <v>1.44599997997284</v>
       </c>
       <c r="G1359" t="n">
-        <v>0.886860311031342</v>
+        <v>0.886860370635986</v>
       </c>
       <c r="H1359" t="n">
         <v>147778</v>
@@ -39838,7 +39838,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G1361" t="n">
-        <v>0.875820577144623</v>
+        <v>0.875820517539978</v>
       </c>
       <c r="H1361" t="n">
         <v>121765</v>
@@ -39896,7 +39896,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1363" t="n">
-        <v>0.846381187438965</v>
+        <v>0.84638124704361</v>
       </c>
       <c r="H1363" t="n">
         <v>171352</v>
@@ -40012,7 +40012,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1367" t="n">
-        <v>0.835341513156891</v>
+        <v>0.835341393947601</v>
       </c>
       <c r="H1367" t="n">
         <v>176992</v>
@@ -40070,7 +40070,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1369" t="n">
-        <v>0.837794840335846</v>
+        <v>0.837794721126556</v>
       </c>
       <c r="H1369" t="n">
         <v>104647</v>
@@ -40128,7 +40128,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G1371" t="n">
-        <v>0.826755046844482</v>
+        <v>0.826754987239838</v>
       </c>
       <c r="H1371" t="n">
         <v>82314</v>
@@ -40157,7 +40157,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G1372" t="n">
-        <v>0.826755046844482</v>
+        <v>0.826754987239838</v>
       </c>
       <c r="H1372" t="n">
         <v>167587</v>
@@ -40215,7 +40215,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G1374" t="n">
-        <v>0.861100912094116</v>
+        <v>0.861101031303406</v>
       </c>
       <c r="H1374" t="n">
         <v>158981</v>
@@ -40273,7 +40273,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G1376" t="n">
-        <v>0.861100912094116</v>
+        <v>0.861101031303406</v>
       </c>
       <c r="H1376" t="n">
         <v>98441</v>
@@ -40331,7 +40331,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1378" t="n">
-        <v>0.870913982391357</v>
+        <v>0.870914041996002</v>
       </c>
       <c r="H1378" t="n">
         <v>178932</v>
@@ -40360,7 +40360,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G1379" t="n">
-        <v>0.912619829177856</v>
+        <v>0.912619769573212</v>
       </c>
       <c r="H1379" t="n">
         <v>464389</v>
@@ -40389,7 +40389,7 @@
         <v>1.5</v>
       </c>
       <c r="G1380" t="n">
-        <v>0.919979512691498</v>
+        <v>0.919979631900787</v>
       </c>
       <c r="H1380" t="n">
         <v>1413263</v>
@@ -40505,7 +40505,7 @@
         <v>1.49399995803833</v>
       </c>
       <c r="G1384" t="n">
-        <v>0.916299700737</v>
+        <v>0.916299641132355</v>
       </c>
       <c r="H1384" t="n">
         <v>101556</v>
@@ -40534,7 +40534,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1385" t="n">
-        <v>0.96291196346283</v>
+        <v>0.962912023067474</v>
       </c>
       <c r="H1385" t="n">
         <v>939739</v>
@@ -40563,7 +40563,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G1386" t="n">
-        <v>0.945739030838013</v>
+        <v>0.945739090442657</v>
       </c>
       <c r="H1386" t="n">
         <v>326723</v>
@@ -40592,7 +40592,7 @@
         <v>1.5</v>
       </c>
       <c r="G1387" t="n">
-        <v>0.919979512691498</v>
+        <v>0.919979631900787</v>
       </c>
       <c r="H1387" t="n">
         <v>365772</v>
@@ -40737,7 +40737,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G1392" t="n">
-        <v>0.884407043457031</v>
+        <v>0.884407103061676</v>
       </c>
       <c r="H1392" t="n">
         <v>141898</v>
@@ -40766,7 +40766,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G1393" t="n">
-        <v>0.884407043457031</v>
+        <v>0.884407103061676</v>
       </c>
       <c r="H1393" t="n">
         <v>64747</v>
@@ -40795,7 +40795,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G1394" t="n">
-        <v>0.861100912094116</v>
+        <v>0.861101031303406</v>
       </c>
       <c r="H1394" t="n">
         <v>173193</v>
@@ -40824,7 +40824,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G1395" t="n">
-        <v>0.861100912094116</v>
+        <v>0.861101031303406</v>
       </c>
       <c r="H1395" t="n">
         <v>99567</v>
@@ -40853,7 +40853,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1396" t="n">
-        <v>0.840248048305511</v>
+        <v>0.840247988700867</v>
       </c>
       <c r="H1396" t="n">
         <v>305258</v>
@@ -40882,7 +40882,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1397" t="n">
-        <v>0.835341513156891</v>
+        <v>0.835341393947601</v>
       </c>
       <c r="H1397" t="n">
         <v>217994</v>
@@ -40940,7 +40940,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G1399" t="n">
-        <v>0.839021384716034</v>
+        <v>0.839021444320679</v>
       </c>
       <c r="H1399" t="n">
         <v>130209</v>
@@ -40969,7 +40969,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1400" t="n">
-        <v>0.820621848106384</v>
+        <v>0.82062178850174</v>
       </c>
       <c r="H1400" t="n">
         <v>314902</v>
@@ -41172,7 +41172,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1407" t="n">
-        <v>0.760516464710236</v>
+        <v>0.76051652431488</v>
       </c>
       <c r="H1407" t="n">
         <v>131819</v>
@@ -41201,7 +41201,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1408" t="n">
-        <v>0.754383265972137</v>
+        <v>0.754383325576782</v>
       </c>
       <c r="H1408" t="n">
         <v>366294</v>
@@ -41259,7 +41259,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G1410" t="n">
-        <v>0.737210333347321</v>
+        <v>0.737210273742676</v>
       </c>
       <c r="H1410" t="n">
         <v>156257</v>
@@ -41288,7 +41288,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1411" t="n">
-        <v>0.769102871417999</v>
+        <v>0.769102931022644</v>
       </c>
       <c r="H1411" t="n">
         <v>112866</v>
@@ -41375,7 +41375,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1414" t="n">
-        <v>0.858647584915161</v>
+        <v>0.858647644519806</v>
       </c>
       <c r="H1414" t="n">
         <v>1235294</v>
@@ -41433,7 +41433,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.852514386177063</v>
+        <v>0.852514445781708</v>
       </c>
       <c r="H1416" t="n">
         <v>491957</v>
@@ -41491,7 +41491,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G1418" t="n">
-        <v>0.839021384716034</v>
+        <v>0.839021444320679</v>
       </c>
       <c r="H1418" t="n">
         <v>356975</v>
@@ -41520,7 +41520,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1419" t="n">
-        <v>0.835341513156891</v>
+        <v>0.835341393947601</v>
       </c>
       <c r="H1419" t="n">
         <v>214498</v>
@@ -41549,7 +41549,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1420" t="n">
-        <v>0.846381187438965</v>
+        <v>0.84638124704361</v>
       </c>
       <c r="H1420" t="n">
         <v>163849</v>
@@ -41578,7 +41578,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1421" t="n">
-        <v>0.846381187438965</v>
+        <v>0.84638124704361</v>
       </c>
       <c r="H1421" t="n">
         <v>206853</v>
@@ -41607,7 +41607,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G1422" t="n">
-        <v>0.845154643058777</v>
+        <v>0.845154583454132</v>
       </c>
       <c r="H1422" t="n">
         <v>89185</v>
@@ -41723,7 +41723,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1426" t="n">
-        <v>0.858647584915161</v>
+        <v>0.858647644519806</v>
       </c>
       <c r="H1426" t="n">
         <v>400318</v>
@@ -41781,7 +41781,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G1428" t="n">
-        <v>0.899126648902893</v>
+        <v>0.899126708507538</v>
       </c>
       <c r="H1428" t="n">
         <v>825243</v>
@@ -41897,7 +41897,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G1432" t="n">
-        <v>0.853741109371185</v>
+        <v>0.853741049766541</v>
       </c>
       <c r="H1432" t="n">
         <v>367934</v>
@@ -41984,7 +41984,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G1435" t="n">
-        <v>0.842701315879822</v>
+        <v>0.842701256275177</v>
       </c>
       <c r="H1435" t="n">
         <v>133388</v>
@@ -42071,7 +42071,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1438" t="n">
-        <v>0.852514386177063</v>
+        <v>0.852514445781708</v>
       </c>
       <c r="H1438" t="n">
         <v>170931</v>
@@ -42129,7 +42129,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1440" t="n">
-        <v>0.858647584915161</v>
+        <v>0.858647644519806</v>
       </c>
       <c r="H1440" t="n">
         <v>304587</v>
@@ -42187,7 +42187,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1442" t="n">
-        <v>0.870913982391357</v>
+        <v>0.870914041996002</v>
       </c>
       <c r="H1442" t="n">
         <v>114768</v>
@@ -42245,7 +42245,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1444" t="n">
-        <v>0.852514386177063</v>
+        <v>0.852514445781708</v>
       </c>
       <c r="H1444" t="n">
         <v>122371</v>
@@ -42303,7 +42303,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1446" t="n">
-        <v>0.837794840335846</v>
+        <v>0.837794721126556</v>
       </c>
       <c r="H1446" t="n">
         <v>129072</v>
@@ -42477,7 +42477,7 @@
         <v>1.31400001049042</v>
       </c>
       <c r="G1452" t="n">
-        <v>0.805902123451233</v>
+        <v>0.805902183055878</v>
       </c>
       <c r="H1452" t="n">
         <v>244151</v>
@@ -42506,7 +42506,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1453" t="n">
-        <v>0.813261985778809</v>
+        <v>0.813262045383453</v>
       </c>
       <c r="H1453" t="n">
         <v>114904</v>
@@ -42564,7 +42564,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1455" t="n">
-        <v>0.772782921791077</v>
+        <v>0.772782802581787</v>
       </c>
       <c r="H1455" t="n">
         <v>167953</v>
@@ -42593,7 +42593,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1456" t="n">
-        <v>0.797315657138824</v>
+        <v>0.79731559753418</v>
       </c>
       <c r="H1456" t="n">
         <v>154869</v>
@@ -42622,7 +42622,7 @@
         <v>1.31400001049042</v>
       </c>
       <c r="G1457" t="n">
-        <v>0.805902123451233</v>
+        <v>0.805902183055878</v>
       </c>
       <c r="H1457" t="n">
         <v>100821</v>
@@ -42651,7 +42651,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1458" t="n">
-        <v>0.813261985778809</v>
+        <v>0.813262045383453</v>
       </c>
       <c r="H1458" t="n">
         <v>135410</v>
@@ -42680,7 +42680,7 @@
         <v>1.33200001716614</v>
       </c>
       <c r="G1459" t="n">
-        <v>0.816941857337952</v>
+        <v>0.816941916942596</v>
       </c>
       <c r="H1459" t="n">
         <v>73758</v>
@@ -42738,7 +42738,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1461" t="n">
-        <v>0.803448796272278</v>
+        <v>0.803448855876923</v>
       </c>
       <c r="H1461" t="n">
         <v>54619</v>
@@ -42825,7 +42825,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1464" t="n">
-        <v>0.788729190826416</v>
+        <v>0.788729250431061</v>
       </c>
       <c r="H1464" t="n">
         <v>91651</v>
@@ -42854,7 +42854,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1465" t="n">
-        <v>0.792409062385559</v>
+        <v>0.792409121990204</v>
       </c>
       <c r="H1465" t="n">
         <v>190594</v>
@@ -42970,7 +42970,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1469" t="n">
-        <v>0.788729190826416</v>
+        <v>0.788729250431061</v>
       </c>
       <c r="H1469" t="n">
         <v>41589</v>
@@ -43028,7 +43028,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1471" t="n">
-        <v>0.815715253353119</v>
+        <v>0.815715193748474</v>
       </c>
       <c r="H1471" t="n">
         <v>212372</v>
@@ -43115,7 +43115,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1474" t="n">
-        <v>0.840248048305511</v>
+        <v>0.840247988700867</v>
       </c>
       <c r="H1474" t="n">
         <v>123829</v>
@@ -43144,7 +43144,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G1475" t="n">
-        <v>0.829208314418793</v>
+        <v>0.829208254814148</v>
       </c>
       <c r="H1475" t="n">
         <v>97695</v>
@@ -43173,7 +43173,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1476" t="n">
-        <v>0.824301719665527</v>
+        <v>0.824301660060883</v>
       </c>
       <c r="H1476" t="n">
         <v>93692</v>
@@ -43202,7 +43202,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1477" t="n">
-        <v>0.856194376945496</v>
+        <v>0.85619443655014</v>
       </c>
       <c r="H1477" t="n">
         <v>332826</v>
@@ -43347,7 +43347,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1482" t="n">
-        <v>0.840248048305511</v>
+        <v>0.840247988700867</v>
       </c>
       <c r="H1482" t="n">
         <v>185548</v>
@@ -43376,7 +43376,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1483" t="n">
-        <v>0.840248048305511</v>
+        <v>0.840247988700867</v>
       </c>
       <c r="H1483" t="n">
         <v>140243</v>
@@ -43405,7 +43405,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1484" t="n">
-        <v>0.840248048305511</v>
+        <v>0.840247988700867</v>
       </c>
       <c r="H1484" t="n">
         <v>295922</v>
@@ -43463,7 +43463,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1486" t="n">
-        <v>0.824301719665527</v>
+        <v>0.824301660060883</v>
       </c>
       <c r="H1486" t="n">
         <v>109288</v>
@@ -43492,7 +43492,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G1487" t="n">
-        <v>0.819395124912262</v>
+        <v>0.819395184516907</v>
       </c>
       <c r="H1487" t="n">
         <v>188308</v>
@@ -43550,7 +43550,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1489" t="n">
-        <v>0.824301719665527</v>
+        <v>0.824301660060883</v>
       </c>
       <c r="H1489" t="n">
         <v>73053</v>
@@ -43608,7 +43608,7 @@
         <v>1.31400001049042</v>
       </c>
       <c r="G1491" t="n">
-        <v>0.805902123451233</v>
+        <v>0.805902183055878</v>
       </c>
       <c r="H1491" t="n">
         <v>171192</v>
@@ -43666,7 +43666,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1493" t="n">
-        <v>0.797315657138824</v>
+        <v>0.79731559753418</v>
       </c>
       <c r="H1493" t="n">
         <v>257678</v>
@@ -43695,7 +43695,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1494" t="n">
-        <v>0.824301719665527</v>
+        <v>0.824301660060883</v>
       </c>
       <c r="H1494" t="n">
         <v>265076</v>
@@ -43782,7 +43782,7 @@
         <v>1.33200001716614</v>
       </c>
       <c r="G1497" t="n">
-        <v>0.816941857337952</v>
+        <v>0.816941916942596</v>
       </c>
       <c r="H1497" t="n">
         <v>106759</v>
@@ -43811,7 +43811,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1498" t="n">
-        <v>0.797315657138824</v>
+        <v>0.79731559753418</v>
       </c>
       <c r="H1498" t="n">
         <v>352664</v>
@@ -43898,7 +43898,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1501" t="n">
-        <v>0.797315657138824</v>
+        <v>0.79731559753418</v>
       </c>
       <c r="H1501" t="n">
         <v>164805</v>
@@ -43927,7 +43927,7 @@
         <v>1.2940000295639</v>
       </c>
       <c r="G1502" t="n">
-        <v>0.793635785579681</v>
+        <v>0.793635725975037</v>
       </c>
       <c r="H1502" t="n">
         <v>60756</v>
@@ -43956,7 +43956,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1503" t="n">
-        <v>0.760516464710236</v>
+        <v>0.76051652431488</v>
       </c>
       <c r="H1503" t="n">
         <v>380395</v>
@@ -44014,7 +44014,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1505" t="n">
-        <v>0.735983669757843</v>
+        <v>0.735983729362488</v>
       </c>
       <c r="H1505" t="n">
         <v>147647</v>
@@ -44072,7 +44072,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G1507" t="n">
-        <v>0.733530342578888</v>
+        <v>0.733530402183533</v>
       </c>
       <c r="H1507" t="n">
         <v>126855</v>
@@ -44101,7 +44101,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G1508" t="n">
-        <v>0.728623867034912</v>
+        <v>0.728623807430267</v>
       </c>
       <c r="H1508" t="n">
         <v>78456</v>
@@ -44188,7 +44188,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1511" t="n">
-        <v>0.748250067234039</v>
+        <v>0.748250126838684</v>
       </c>
       <c r="H1511" t="n">
         <v>77419</v>
@@ -44275,7 +44275,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1514" t="n">
-        <v>0.735983669757843</v>
+        <v>0.735983729362488</v>
       </c>
       <c r="H1514" t="n">
         <v>158378</v>
@@ -44333,7 +44333,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1516" t="n">
-        <v>0.735983669757843</v>
+        <v>0.735983729362488</v>
       </c>
       <c r="H1516" t="n">
         <v>141495</v>
@@ -44420,7 +44420,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G1519" t="n">
-        <v>0.728623867034912</v>
+        <v>0.728623807430267</v>
       </c>
       <c r="H1519" t="n">
         <v>188721</v>
@@ -44449,7 +44449,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G1520" t="n">
-        <v>0.738436937332153</v>
+        <v>0.738436996936798</v>
       </c>
       <c r="H1520" t="n">
         <v>51160</v>
@@ -44536,7 +44536,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1523" t="n">
-        <v>0.726170599460602</v>
+        <v>0.726170539855957</v>
       </c>
       <c r="H1523" t="n">
         <v>89361</v>
@@ -44681,7 +44681,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1528" t="n">
-        <v>0.760516464710236</v>
+        <v>0.76051652431488</v>
       </c>
       <c r="H1528" t="n">
         <v>120544</v>
@@ -44710,7 +44710,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1529" t="n">
-        <v>0.760516464710236</v>
+        <v>0.76051652431488</v>
       </c>
       <c r="H1529" t="n">
         <v>82688</v>
@@ -44739,7 +44739,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G1530" t="n">
-        <v>0.758063137531281</v>
+        <v>0.758063197135925</v>
       </c>
       <c r="H1530" t="n">
         <v>114962</v>
@@ -44855,7 +44855,7 @@
         <v>1.26199996471405</v>
       </c>
       <c r="G1534" t="n">
-        <v>0.774009466171265</v>
+        <v>0.774009525775909</v>
       </c>
       <c r="H1534" t="n">
         <v>48060</v>
@@ -44913,7 +44913,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1536" t="n">
-        <v>0.788729190826416</v>
+        <v>0.788729250431061</v>
       </c>
       <c r="H1536" t="n">
         <v>27795</v>
@@ -44942,7 +44942,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1537" t="n">
-        <v>0.772782921791077</v>
+        <v>0.772782802581787</v>
       </c>
       <c r="H1537" t="n">
         <v>36607</v>
@@ -44971,7 +44971,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1538" t="n">
-        <v>0.771556198596954</v>
+        <v>0.771556258201599</v>
       </c>
       <c r="H1538" t="n">
         <v>69625</v>
@@ -45000,7 +45000,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1539" t="n">
-        <v>0.762969672679901</v>
+        <v>0.762969791889191</v>
       </c>
       <c r="H1539" t="n">
         <v>100515</v>
@@ -45029,7 +45029,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1540" t="n">
-        <v>0.775236189365387</v>
+        <v>0.775236129760742</v>
       </c>
       <c r="H1540" t="n">
         <v>42391</v>
@@ -45058,7 +45058,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G1541" t="n">
-        <v>0.756836533546448</v>
+        <v>0.756836473941803</v>
       </c>
       <c r="H1541" t="n">
         <v>128174</v>
@@ -45145,7 +45145,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1544" t="n">
-        <v>0.748250067234039</v>
+        <v>0.748250126838684</v>
       </c>
       <c r="H1544" t="n">
         <v>23434</v>
@@ -45203,7 +45203,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G1546" t="n">
-        <v>0.728623867034912</v>
+        <v>0.728623807430267</v>
       </c>
       <c r="H1546" t="n">
         <v>83407</v>
@@ -45261,7 +45261,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1548" t="n">
-        <v>0.735983669757843</v>
+        <v>0.735983729362488</v>
       </c>
       <c r="H1548" t="n">
         <v>66394</v>
@@ -45290,7 +45290,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1549" t="n">
-        <v>0.735983669757843</v>
+        <v>0.735983729362488</v>
       </c>
       <c r="H1549" t="n">
         <v>85697</v>
@@ -45319,7 +45319,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1550" t="n">
-        <v>0.754383265972137</v>
+        <v>0.754383325576782</v>
       </c>
       <c r="H1550" t="n">
         <v>123629</v>
@@ -45377,7 +45377,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1552" t="n">
-        <v>0.726170599460602</v>
+        <v>0.726170539855957</v>
       </c>
       <c r="H1552" t="n">
         <v>76444</v>
@@ -45406,7 +45406,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G1553" t="n">
-        <v>0.73475706577301</v>
+        <v>0.734757006168365</v>
       </c>
       <c r="H1553" t="n">
         <v>104901</v>
@@ -45464,7 +45464,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G1555" t="n">
-        <v>0.721264004707336</v>
+        <v>0.721264064311981</v>
       </c>
       <c r="H1555" t="n">
         <v>164015</v>
@@ -45493,7 +45493,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G1556" t="n">
-        <v>0.728623867034912</v>
+        <v>0.728623807430267</v>
       </c>
       <c r="H1556" t="n">
         <v>81679</v>
@@ -45551,7 +45551,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1558" t="n">
-        <v>0.720037400722504</v>
+        <v>0.720037341117859</v>
       </c>
       <c r="H1558" t="n">
         <v>49443</v>
@@ -45580,7 +45580,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G1559" t="n">
-        <v>0.728623867034912</v>
+        <v>0.728623807430267</v>
       </c>
       <c r="H1559" t="n">
         <v>88379</v>
@@ -45638,7 +45638,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1561" t="n">
-        <v>0.712677478790283</v>
+        <v>0.712677538394928</v>
       </c>
       <c r="H1561" t="n">
         <v>157256</v>
@@ -45667,7 +45667,7 @@
         <v>1.14800000190735</v>
       </c>
       <c r="G1562" t="n">
-        <v>0.704091012477875</v>
+        <v>0.70409107208252</v>
       </c>
       <c r="H1562" t="n">
         <v>82654</v>
@@ -45696,7 +45696,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G1563" t="n">
-        <v>0.696731269359589</v>
+        <v>0.696731209754944</v>
       </c>
       <c r="H1563" t="n">
         <v>80261</v>
@@ -45725,7 +45725,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1564" t="n">
-        <v>0.705317676067352</v>
+        <v>0.705317735671997</v>
       </c>
       <c r="H1564" t="n">
         <v>161119</v>
@@ -45754,7 +45754,7 @@
         <v>1.06200003623962</v>
       </c>
       <c r="G1565" t="n">
-        <v>0.651345610618591</v>
+        <v>0.651345551013947</v>
       </c>
       <c r="H1565" t="n">
         <v>274347</v>
@@ -45783,7 +45783,7 @@
         <v>1.13199996948242</v>
       </c>
       <c r="G1566" t="n">
-        <v>0.694277942180634</v>
+        <v>0.694277882575989</v>
       </c>
       <c r="H1566" t="n">
         <v>402246</v>
@@ -46015,7 +46015,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G1574" t="n">
-        <v>0.520095109939575</v>
+        <v>0.52009516954422</v>
       </c>
       <c r="H1574" t="n">
         <v>202197</v>
@@ -46044,7 +46044,7 @@
         <v>0.802999973297119</v>
       </c>
       <c r="G1575" t="n">
-        <v>0.492495715618134</v>
+        <v>0.492495745420456</v>
       </c>
       <c r="H1575" t="n">
         <v>323492</v>
@@ -46102,7 +46102,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1577" t="n">
-        <v>0.504148781299591</v>
+        <v>0.504148840904236</v>
       </c>
       <c r="H1577" t="n">
         <v>133955</v>
@@ -46131,7 +46131,7 @@
         <v>0.814999997615814</v>
       </c>
       <c r="G1578" t="n">
-        <v>0.499855548143387</v>
+        <v>0.499855577945709</v>
       </c>
       <c r="H1578" t="n">
         <v>88927</v>
@@ -46160,7 +46160,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1579" t="n">
-        <v>0.538494765758514</v>
+        <v>0.53849470615387</v>
       </c>
       <c r="H1579" t="n">
         <v>227555</v>
@@ -46189,7 +46189,7 @@
         <v>0.888999998569489</v>
       </c>
       <c r="G1580" t="n">
-        <v>0.545241236686707</v>
+        <v>0.545241296291351</v>
       </c>
       <c r="H1580" t="n">
         <v>91587</v>
@@ -46305,7 +46305,7 @@
         <v>0.879000008106232</v>
       </c>
       <c r="G1584" t="n">
-        <v>0.539108097553253</v>
+        <v>0.539108037948608</v>
       </c>
       <c r="H1584" t="n">
         <v>166972</v>
@@ -46392,7 +46392,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G1587" t="n">
-        <v>0.542787909507751</v>
+        <v>0.542787969112396</v>
       </c>
       <c r="H1587" t="n">
         <v>140994</v>
@@ -46479,7 +46479,7 @@
         <v>0.866999983787537</v>
       </c>
       <c r="G1590" t="n">
-        <v>0.531748235225677</v>
+        <v>0.531748175621033</v>
       </c>
       <c r="H1590" t="n">
         <v>167752</v>
@@ -46595,7 +46595,7 @@
         <v>0.861000001430511</v>
       </c>
       <c r="G1594" t="n">
-        <v>0.52806830406189</v>
+        <v>0.528068244457245</v>
       </c>
       <c r="H1594" t="n">
         <v>123522</v>
@@ -46624,7 +46624,7 @@
         <v>0.837000012397766</v>
       </c>
       <c r="G1595" t="n">
-        <v>0.513348579406738</v>
+        <v>0.513348639011383</v>
       </c>
       <c r="H1595" t="n">
         <v>183181</v>
@@ -46653,7 +46653,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1596" t="n">
-        <v>0.510281980037689</v>
+        <v>0.510282039642334</v>
       </c>
       <c r="H1596" t="n">
         <v>140867</v>
@@ -46682,7 +46682,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1597" t="n">
-        <v>0.51518851518631</v>
+        <v>0.515188574790955</v>
       </c>
       <c r="H1597" t="n">
         <v>250652</v>
@@ -46943,7 +46943,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G1606" t="n">
-        <v>0.542787909507751</v>
+        <v>0.542787969112396</v>
       </c>
       <c r="H1606" t="n">
         <v>302675</v>
@@ -47001,7 +47001,7 @@
         <v>0.861000001430511</v>
       </c>
       <c r="G1608" t="n">
-        <v>0.52806830406189</v>
+        <v>0.528068244457245</v>
       </c>
       <c r="H1608" t="n">
         <v>430668</v>
@@ -47030,7 +47030,7 @@
         <v>0.859000027179718</v>
       </c>
       <c r="G1609" t="n">
-        <v>0.526841700077057</v>
+        <v>0.526841640472412</v>
       </c>
       <c r="H1609" t="n">
         <v>270347</v>
@@ -47059,7 +47059,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1610" t="n">
-        <v>0.533588111400604</v>
+        <v>0.533588171005249</v>
       </c>
       <c r="H1610" t="n">
         <v>109591</v>
@@ -47088,7 +47088,7 @@
         <v>0.869000017642975</v>
       </c>
       <c r="G1611" t="n">
-        <v>0.532974898815155</v>
+        <v>0.53297483921051</v>
       </c>
       <c r="H1611" t="n">
         <v>108692</v>
@@ -47204,7 +47204,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1615" t="n">
-        <v>0.509055316448212</v>
+        <v>0.509055376052856</v>
       </c>
       <c r="H1615" t="n">
         <v>102044</v>
@@ -47233,7 +47233,7 @@
         <v>0.824999988079071</v>
       </c>
       <c r="G1616" t="n">
-        <v>0.505988776683807</v>
+        <v>0.505988836288452</v>
       </c>
       <c r="H1616" t="n">
         <v>195866</v>
@@ -47262,7 +47262,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G1617" t="n">
-        <v>0.520095109939575</v>
+        <v>0.52009516954422</v>
       </c>
       <c r="H1617" t="n">
         <v>69792</v>
@@ -47291,7 +47291,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1618" t="n">
-        <v>0.509055316448212</v>
+        <v>0.509055376052856</v>
       </c>
       <c r="H1618" t="n">
         <v>49549</v>
@@ -47320,7 +47320,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1619" t="n">
-        <v>0.509055316448212</v>
+        <v>0.509055376052856</v>
       </c>
       <c r="H1619" t="n">
         <v>95950</v>
@@ -47407,7 +47407,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1622" t="n">
-        <v>0.533588111400604</v>
+        <v>0.533588171005249</v>
       </c>
       <c r="H1622" t="n">
         <v>114805</v>
@@ -47494,7 +47494,7 @@
         <v>0.869000017642975</v>
       </c>
       <c r="G1625" t="n">
-        <v>0.532974898815155</v>
+        <v>0.53297483921051</v>
       </c>
       <c r="H1625" t="n">
         <v>113355</v>
@@ -47668,7 +47668,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G1631" t="n">
-        <v>0.574067234992981</v>
+        <v>0.574067294597626</v>
       </c>
       <c r="H1631" t="n">
         <v>117312</v>
@@ -47726,7 +47726,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G1633" t="n">
-        <v>0.647665679454803</v>
+        <v>0.647665619850159</v>
       </c>
       <c r="H1633" t="n">
         <v>410308</v>
@@ -47784,7 +47784,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1635" t="n">
-        <v>0.625586092472076</v>
+        <v>0.625586152076721</v>
       </c>
       <c r="H1635" t="n">
         <v>75358</v>
@@ -47813,7 +47813,7 @@
         <v>1.01600003242493</v>
       </c>
       <c r="G1636" t="n">
-        <v>0.623132824897766</v>
+        <v>0.623132884502411</v>
       </c>
       <c r="H1636" t="n">
         <v>85942</v>
@@ -47842,7 +47842,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G1637" t="n">
-        <v>0.628039419651031</v>
+        <v>0.628039479255676</v>
       </c>
       <c r="H1637" t="n">
         <v>80758</v>
@@ -47987,7 +47987,7 @@
         <v>0.89300000667572</v>
       </c>
       <c r="G1642" t="n">
-        <v>0.547694563865662</v>
+        <v>0.547694504261017</v>
       </c>
       <c r="H1642" t="n">
         <v>149572</v>
@@ -48016,7 +48016,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1643" t="n">
-        <v>0.533588111400604</v>
+        <v>0.533588171005249</v>
       </c>
       <c r="H1643" t="n">
         <v>53610</v>
@@ -48045,7 +48045,7 @@
         <v>0.869000017642975</v>
       </c>
       <c r="G1644" t="n">
-        <v>0.532974898815155</v>
+        <v>0.53297483921051</v>
       </c>
       <c r="H1644" t="n">
         <v>95805</v>
@@ -48132,7 +48132,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G1647" t="n">
-        <v>0.554441094398499</v>
+        <v>0.554441034793854</v>
       </c>
       <c r="H1647" t="n">
         <v>152234</v>
@@ -48161,7 +48161,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G1648" t="n">
-        <v>0.547081172466278</v>
+        <v>0.547081232070923</v>
       </c>
       <c r="H1648" t="n">
         <v>67414</v>
@@ -48248,7 +48248,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1651" t="n">
-        <v>0.533588111400604</v>
+        <v>0.533588171005249</v>
       </c>
       <c r="H1651" t="n">
         <v>72124</v>
@@ -48306,7 +48306,7 @@
         <v>0.824999988079071</v>
       </c>
       <c r="G1653" t="n">
-        <v>0.505988776683807</v>
+        <v>0.505988836288452</v>
       </c>
       <c r="H1653" t="n">
         <v>167323</v>
@@ -48393,7 +48393,7 @@
         <v>0.792999982833862</v>
       </c>
       <c r="G1656" t="n">
-        <v>0.486362516880035</v>
+        <v>0.486362546682358</v>
       </c>
       <c r="H1656" t="n">
         <v>58475</v>
@@ -48451,7 +48451,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G1658" t="n">
-        <v>0.511508703231812</v>
+        <v>0.511508643627167</v>
       </c>
       <c r="H1658" t="n">
         <v>55747</v>
@@ -48509,7 +48509,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1660" t="n">
-        <v>0.509055316448212</v>
+        <v>0.509055376052856</v>
       </c>
       <c r="H1660" t="n">
         <v>15200</v>
@@ -48596,7 +48596,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1663" t="n">
-        <v>0.479616045951843</v>
+        <v>0.479616075754166</v>
       </c>
       <c r="H1663" t="n">
         <v>84703</v>
@@ -48654,7 +48654,7 @@
         <v>0.785000026226044</v>
       </c>
       <c r="G1665" t="n">
-        <v>0.481455981731415</v>
+        <v>0.481456011533737</v>
       </c>
       <c r="H1665" t="n">
         <v>33125</v>
@@ -48683,7 +48683,7 @@
         <v>0.787000000476837</v>
       </c>
       <c r="G1666" t="n">
-        <v>0.482682675123215</v>
+        <v>0.482682645320892</v>
       </c>
       <c r="H1666" t="n">
         <v>86039</v>
@@ -48770,7 +48770,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1669" t="n">
-        <v>0.509055316448212</v>
+        <v>0.509055376052856</v>
       </c>
       <c r="H1669" t="n">
         <v>54574</v>
@@ -48799,7 +48799,7 @@
         <v>0.861000001430511</v>
       </c>
       <c r="G1670" t="n">
-        <v>0.52806830406189</v>
+        <v>0.528068244457245</v>
       </c>
       <c r="H1670" t="n">
         <v>412769</v>
@@ -48828,7 +48828,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G1671" t="n">
-        <v>0.559347569942474</v>
+        <v>0.559347629547119</v>
       </c>
       <c r="H1671" t="n">
         <v>189010</v>
@@ -48857,7 +48857,7 @@
         <v>0.930999994277954</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.571000695228577</v>
+        <v>0.571000635623932</v>
       </c>
       <c r="H1672" t="n">
         <v>119126</v>
@@ -49118,7 +49118,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G1681" t="n">
-        <v>0.542787909507751</v>
+        <v>0.542787969112396</v>
       </c>
       <c r="H1681" t="n">
         <v>22180</v>
@@ -49147,7 +49147,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G1682" t="n">
-        <v>0.54892110824585</v>
+        <v>0.548921167850494</v>
       </c>
       <c r="H1682" t="n">
         <v>7867</v>
@@ -49176,7 +49176,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1683" t="n">
-        <v>0.551987767219543</v>
+        <v>0.551987707614899</v>
       </c>
       <c r="H1683" t="n">
         <v>11524</v>
@@ -49263,7 +49263,7 @@
         <v>0.880999982357025</v>
       </c>
       <c r="G1686" t="n">
-        <v>0.540334641933441</v>
+        <v>0.540334701538086</v>
       </c>
       <c r="H1686" t="n">
         <v>15422</v>
@@ -49321,7 +49321,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1688" t="n">
-        <v>0.538494765758514</v>
+        <v>0.53849470615387</v>
       </c>
       <c r="H1688" t="n">
         <v>37248</v>
@@ -49553,7 +49553,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1696" t="n">
-        <v>0.51518851518631</v>
+        <v>0.515188574790955</v>
       </c>
       <c r="H1696" t="n">
         <v>32822</v>
@@ -49611,7 +49611,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1698" t="n">
-        <v>0.509055316448212</v>
+        <v>0.509055376052856</v>
       </c>
       <c r="H1698" t="n">
         <v>13347</v>
@@ -49640,7 +49640,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1699" t="n">
-        <v>0.506602048873901</v>
+        <v>0.506602108478546</v>
       </c>
       <c r="H1699" t="n">
         <v>6514</v>
@@ -49669,7 +49669,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1700" t="n">
-        <v>0.498015642166138</v>
+        <v>0.498015612363815</v>
       </c>
       <c r="H1700" t="n">
         <v>31394</v>
@@ -49698,7 +49698,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1701" t="n">
-        <v>0.49065575003624</v>
+        <v>0.490655809640884</v>
       </c>
       <c r="H1701" t="n">
         <v>34760</v>
@@ -49785,7 +49785,7 @@
         <v>0.809000015258789</v>
       </c>
       <c r="G1704" t="n">
-        <v>0.496175706386566</v>
+        <v>0.496175676584244</v>
       </c>
       <c r="H1704" t="n">
         <v>21382</v>
@@ -49814,7 +49814,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1705" t="n">
-        <v>0.484522610902786</v>
+        <v>0.484522581100464</v>
       </c>
       <c r="H1705" t="n">
         <v>232506</v>
@@ -49843,7 +49843,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1706" t="n">
-        <v>0.486975938081741</v>
+        <v>0.486975878477097</v>
       </c>
       <c r="H1706" t="n">
         <v>180690</v>
@@ -49901,7 +49901,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1708" t="n">
-        <v>0.474709451198578</v>
+        <v>0.4747094810009</v>
       </c>
       <c r="H1708" t="n">
         <v>124386</v>
@@ -49930,7 +49930,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1709" t="n">
-        <v>0.474709451198578</v>
+        <v>0.4747094810009</v>
       </c>
       <c r="H1709" t="n">
         <v>11175</v>
@@ -49959,7 +49959,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1710" t="n">
-        <v>0.47225621342659</v>
+        <v>0.472256183624268</v>
       </c>
       <c r="H1710" t="n">
         <v>25393</v>
@@ -49988,7 +49988,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G1711" t="n">
-        <v>0.456923186779022</v>
+        <v>0.456923216581345</v>
       </c>
       <c r="H1711" t="n">
         <v>131826</v>
@@ -50075,7 +50075,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1714" t="n">
-        <v>0.435456991195679</v>
+        <v>0.435457020998001</v>
       </c>
       <c r="H1714" t="n">
         <v>60877</v>
@@ -50104,7 +50104,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1715" t="n">
-        <v>0.437910288572311</v>
+        <v>0.437910258769989</v>
       </c>
       <c r="H1715" t="n">
         <v>34096</v>
@@ -50133,7 +50133,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1716" t="n">
-        <v>0.447723388671875</v>
+        <v>0.447723418474197</v>
       </c>
       <c r="H1716" t="n">
         <v>26655</v>
@@ -50191,7 +50191,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1718" t="n">
-        <v>0.435456991195679</v>
+        <v>0.435457020998001</v>
       </c>
       <c r="H1718" t="n">
         <v>11872</v>
@@ -50249,7 +50249,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G1720" t="n">
-        <v>0.43852362036705</v>
+        <v>0.438523590564728</v>
       </c>
       <c r="H1720" t="n">
         <v>78867</v>
@@ -50307,7 +50307,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1722" t="n">
-        <v>0.428097188472748</v>
+        <v>0.42809721827507</v>
       </c>
       <c r="H1722" t="n">
         <v>9212</v>
@@ -50336,7 +50336,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1723" t="n">
-        <v>0.429323792457581</v>
+        <v>0.429323822259903</v>
       </c>
       <c r="H1723" t="n">
         <v>12024</v>
@@ -50365,7 +50365,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1724" t="n">
-        <v>0.414604157209396</v>
+        <v>0.414604127407074</v>
       </c>
       <c r="H1724" t="n">
         <v>120285</v>
@@ -50394,7 +50394,7 @@
         <v>0.66100001335144</v>
       </c>
       <c r="G1725" t="n">
-        <v>0.405404359102249</v>
+        <v>0.405404388904572</v>
       </c>
       <c r="H1725" t="n">
         <v>212060</v>
@@ -50452,7 +50452,7 @@
         <v>0.686999976634979</v>
       </c>
       <c r="G1727" t="n">
-        <v>0.421350657939911</v>
+        <v>0.421350628137589</v>
       </c>
       <c r="H1727" t="n">
         <v>124750</v>
@@ -50481,7 +50481,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1728" t="n">
-        <v>0.429323792457581</v>
+        <v>0.429323822259903</v>
       </c>
       <c r="H1728" t="n">
         <v>149076</v>
@@ -50597,7 +50597,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1732" t="n">
-        <v>0.49065575003624</v>
+        <v>0.490655809640884</v>
       </c>
       <c r="H1732" t="n">
         <v>498028</v>
@@ -50771,7 +50771,7 @@
         <v>0.837000012397766</v>
       </c>
       <c r="G1738" t="n">
-        <v>0.513348579406738</v>
+        <v>0.513348639011383</v>
       </c>
       <c r="H1738" t="n">
         <v>42431</v>
@@ -50800,7 +50800,7 @@
         <v>0.824999988079071</v>
       </c>
       <c r="G1739" t="n">
-        <v>0.505988776683807</v>
+        <v>0.505988836288452</v>
       </c>
       <c r="H1739" t="n">
         <v>63148</v>
@@ -50858,7 +50858,7 @@
         <v>0.837000012397766</v>
       </c>
       <c r="G1741" t="n">
-        <v>0.513348579406738</v>
+        <v>0.513348639011383</v>
       </c>
       <c r="H1741" t="n">
         <v>43098</v>
@@ -50945,7 +50945,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1744" t="n">
-        <v>0.513961970806122</v>
+        <v>0.513961911201477</v>
       </c>
       <c r="H1744" t="n">
         <v>57467</v>
@@ -50974,7 +50974,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1745" t="n">
-        <v>0.51518851518631</v>
+        <v>0.515188574790955</v>
       </c>
       <c r="H1745" t="n">
         <v>39782</v>
@@ -51003,7 +51003,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1746" t="n">
-        <v>0.51518851518631</v>
+        <v>0.515188574790955</v>
       </c>
       <c r="H1746" t="n">
         <v>29578</v>
@@ -51032,7 +51032,7 @@
         <v>0.859000027179718</v>
       </c>
       <c r="G1747" t="n">
-        <v>0.526841700077057</v>
+        <v>0.526841640472412</v>
       </c>
       <c r="H1747" t="n">
         <v>85973</v>
@@ -51148,7 +51148,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G1751" t="n">
-        <v>0.567320764064789</v>
+        <v>0.567320704460144</v>
       </c>
       <c r="H1751" t="n">
         <v>28616</v>
@@ -51467,7 +51467,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G1762" t="n">
-        <v>0.542787909507751</v>
+        <v>0.542787969112396</v>
       </c>
       <c r="H1762" t="n">
         <v>69410</v>
@@ -51641,7 +51641,7 @@
         <v>0.845000028610229</v>
       </c>
       <c r="G1768" t="n">
-        <v>0.518255233764648</v>
+        <v>0.518255174160004</v>
       </c>
       <c r="H1768" t="n">
         <v>61066</v>
@@ -51815,7 +51815,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1774" t="n">
-        <v>0.533588111400604</v>
+        <v>0.533588171005249</v>
       </c>
       <c r="H1774" t="n">
         <v>61411</v>
@@ -51844,7 +51844,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G1775" t="n">
-        <v>0.554441094398499</v>
+        <v>0.554441034793854</v>
       </c>
       <c r="H1775" t="n">
         <v>221808</v>
@@ -51960,7 +51960,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G1779" t="n">
-        <v>0.554441094398499</v>
+        <v>0.554441034793854</v>
       </c>
       <c r="H1779" t="n">
         <v>192322</v>
@@ -52250,7 +52250,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G1789" t="n">
-        <v>0.624359548091888</v>
+        <v>0.624359488487244</v>
       </c>
       <c r="H1789" t="n">
         <v>244828</v>
@@ -52337,7 +52337,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1792" t="n">
-        <v>0.656252205371857</v>
+        <v>0.656252145767212</v>
       </c>
       <c r="H1792" t="n">
         <v>246471</v>
@@ -52395,7 +52395,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1794" t="n">
-        <v>0.674651741981506</v>
+        <v>0.674651682376862</v>
       </c>
       <c r="H1794" t="n">
         <v>184077</v>
@@ -52453,7 +52453,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1796" t="n">
-        <v>0.662385404109955</v>
+        <v>0.662385284900665</v>
       </c>
       <c r="H1796" t="n">
         <v>92197</v>
@@ -52540,7 +52540,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1799" t="n">
-        <v>0.674651741981506</v>
+        <v>0.674651682376862</v>
       </c>
       <c r="H1799" t="n">
         <v>167768</v>
@@ -52598,7 +52598,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1801" t="n">
-        <v>0.674651741981506</v>
+        <v>0.674651682376862</v>
       </c>
       <c r="H1801" t="n">
         <v>34524</v>
@@ -52743,7 +52743,7 @@
         <v>1.13399994373322</v>
       </c>
       <c r="G1806" t="n">
-        <v>0.695504486560822</v>
+        <v>0.695504546165466</v>
       </c>
       <c r="H1806" t="n">
         <v>83356</v>
@@ -52801,7 +52801,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1808" t="n">
-        <v>0.720037400722504</v>
+        <v>0.720037341117859</v>
       </c>
       <c r="H1808" t="n">
         <v>308736</v>
@@ -52830,7 +52830,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G1809" t="n">
-        <v>0.721264004707336</v>
+        <v>0.721264064311981</v>
       </c>
       <c r="H1809" t="n">
         <v>80314</v>
@@ -52888,7 +52888,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G1811" t="n">
-        <v>0.721264004707336</v>
+        <v>0.721264064311981</v>
       </c>
       <c r="H1811" t="n">
         <v>151667</v>
@@ -52946,7 +52946,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1813" t="n">
-        <v>0.726170599460602</v>
+        <v>0.726170539855957</v>
       </c>
       <c r="H1813" t="n">
         <v>79046</v>
@@ -53004,7 +53004,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1815" t="n">
-        <v>0.748250067234039</v>
+        <v>0.748250126838684</v>
       </c>
       <c r="H1815" t="n">
         <v>136669</v>
@@ -53120,7 +53120,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1819" t="n">
-        <v>0.726170599460602</v>
+        <v>0.726170539855957</v>
       </c>
       <c r="H1819" t="n">
         <v>122752</v>
@@ -53207,7 +53207,7 @@
         <v>1.11800003051758</v>
       </c>
       <c r="G1822" t="n">
-        <v>0.685691475868225</v>
+        <v>0.68569153547287</v>
       </c>
       <c r="H1822" t="n">
         <v>652291</v>
@@ -53236,7 +53236,7 @@
         <v>1.12800002098083</v>
       </c>
       <c r="G1823" t="n">
-        <v>0.691824674606323</v>
+        <v>0.691824615001678</v>
       </c>
       <c r="H1823" t="n">
         <v>384187</v>
@@ -53526,7 +53526,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1833" t="n">
-        <v>0.662385404109955</v>
+        <v>0.662385284900665</v>
       </c>
       <c r="H1833" t="n">
         <v>158378</v>
@@ -53584,7 +53584,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1835" t="n">
-        <v>0.643985629081726</v>
+        <v>0.643985688686371</v>
       </c>
       <c r="H1835" t="n">
         <v>341515</v>
@@ -53613,7 +53613,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G1836" t="n">
-        <v>0.628039419651031</v>
+        <v>0.628039479255676</v>
       </c>
       <c r="H1836" t="n">
         <v>130678</v>
@@ -53671,7 +53671,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G1838" t="n">
-        <v>0.647665679454803</v>
+        <v>0.647665619850159</v>
       </c>
       <c r="H1838" t="n">
         <v>164523</v>
@@ -53729,7 +53729,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1840" t="n">
-        <v>0.705317676067352</v>
+        <v>0.705317735671997</v>
       </c>
       <c r="H1840" t="n">
         <v>602597</v>
@@ -53758,7 +53758,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1841" t="n">
-        <v>0.705317676067352</v>
+        <v>0.705317735671997</v>
       </c>
       <c r="H1841" t="n">
         <v>102468</v>
@@ -53816,7 +53816,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G1843" t="n">
-        <v>0.696731269359589</v>
+        <v>0.696731209754944</v>
       </c>
       <c r="H1843" t="n">
         <v>56024</v>
@@ -53845,7 +53845,7 @@
         <v>1.13199996948242</v>
       </c>
       <c r="G1844" t="n">
-        <v>0.694277942180634</v>
+        <v>0.694277882575989</v>
       </c>
       <c r="H1844" t="n">
         <v>33750</v>
@@ -53874,7 +53874,7 @@
         <v>1.11800003051758</v>
       </c>
       <c r="G1845" t="n">
-        <v>0.685691475868225</v>
+        <v>0.68569153547287</v>
       </c>
       <c r="H1845" t="n">
         <v>15468</v>
@@ -53990,7 +53990,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1849" t="n">
-        <v>0.686918139457703</v>
+        <v>0.686918079853058</v>
       </c>
       <c r="H1849" t="n">
         <v>154138</v>
@@ -54019,7 +54019,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G1850" t="n">
-        <v>0.697957813739777</v>
+        <v>0.697957932949066</v>
       </c>
       <c r="H1850" t="n">
         <v>31934</v>
@@ -54048,7 +54048,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1851" t="n">
-        <v>0.686918139457703</v>
+        <v>0.686918079853058</v>
       </c>
       <c r="H1851" t="n">
         <v>50692</v>
@@ -54077,7 +54077,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1852" t="n">
-        <v>0.686918139457703</v>
+        <v>0.686918079853058</v>
       </c>
       <c r="H1852" t="n">
         <v>74896</v>
@@ -54193,7 +54193,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1856" t="n">
-        <v>0.754383265972137</v>
+        <v>0.754383325576782</v>
       </c>
       <c r="H1856" t="n">
         <v>278182</v>
@@ -54628,7 +54628,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G1871" t="n">
-        <v>0.696731269359589</v>
+        <v>0.696731209754944</v>
       </c>
       <c r="H1871" t="n">
         <v>92961</v>
@@ -54744,7 +54744,7 @@
         <v>1.15400004386902</v>
       </c>
       <c r="G1875" t="n">
-        <v>0.707771003246307</v>
+        <v>0.707771062850952</v>
       </c>
       <c r="H1875" t="n">
         <v>46996</v>
@@ -54773,7 +54773,7 @@
         <v>1.15400004386902</v>
       </c>
       <c r="G1876" t="n">
-        <v>0.707771003246307</v>
+        <v>0.707771062850952</v>
       </c>
       <c r="H1876" t="n">
         <v>41202</v>
@@ -54802,7 +54802,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1877" t="n">
-        <v>0.705317676067352</v>
+        <v>0.705317735671997</v>
       </c>
       <c r="H1877" t="n">
         <v>40683</v>
@@ -54831,7 +54831,7 @@
         <v>1.15400004386902</v>
       </c>
       <c r="G1878" t="n">
-        <v>0.707771003246307</v>
+        <v>0.707771062850952</v>
       </c>
       <c r="H1878" t="n">
         <v>84523</v>
@@ -54976,7 +54976,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1883" t="n">
-        <v>0.705317676067352</v>
+        <v>0.705317735671997</v>
       </c>
       <c r="H1883" t="n">
         <v>38864</v>
@@ -55034,7 +55034,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.686918139457703</v>
+        <v>0.686918079853058</v>
       </c>
       <c r="H1885" t="n">
         <v>84022</v>
@@ -55237,7 +55237,7 @@
         <v>1.15799999237061</v>
       </c>
       <c r="G1892" t="n">
-        <v>0.710224270820618</v>
+        <v>0.710224330425262</v>
       </c>
       <c r="H1892" t="n">
         <v>17771</v>
@@ -55266,7 +55266,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G1893" t="n">
-        <v>0.721264004707336</v>
+        <v>0.721264064311981</v>
       </c>
       <c r="H1893" t="n">
         <v>52903</v>
@@ -55353,7 +55353,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1896" t="n">
-        <v>0.720037400722504</v>
+        <v>0.720037341117859</v>
       </c>
       <c r="H1896" t="n">
         <v>20994</v>
@@ -55411,7 +55411,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G1898" t="n">
-        <v>0.721264004707336</v>
+        <v>0.721264064311981</v>
       </c>
       <c r="H1898" t="n">
         <v>15484</v>
@@ -55469,7 +55469,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1900" t="n">
-        <v>0.720037400722504</v>
+        <v>0.720037341117859</v>
       </c>
       <c r="H1900" t="n">
         <v>36684</v>
@@ -55498,7 +55498,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G1901" t="n">
-        <v>0.721264004707336</v>
+        <v>0.721264064311981</v>
       </c>
       <c r="H1901" t="n">
         <v>10203</v>
@@ -55527,7 +55527,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G1902" t="n">
-        <v>0.721264004707336</v>
+        <v>0.721264064311981</v>
       </c>
       <c r="H1902" t="n">
         <v>89907</v>
@@ -55585,7 +55585,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G1904" t="n">
-        <v>0.721264004707336</v>
+        <v>0.721264064311981</v>
       </c>
       <c r="H1904" t="n">
         <v>20091</v>
@@ -55730,7 +55730,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1909" t="n">
-        <v>0.748250067234039</v>
+        <v>0.748250126838684</v>
       </c>
       <c r="H1909" t="n">
         <v>60247</v>
@@ -55759,7 +55759,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1910" t="n">
-        <v>0.754383265972137</v>
+        <v>0.754383325576782</v>
       </c>
       <c r="H1910" t="n">
         <v>87166</v>
@@ -55817,7 +55817,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1912" t="n">
-        <v>0.764196455478668</v>
+        <v>0.764196395874023</v>
       </c>
       <c r="H1912" t="n">
         <v>89025</v>
@@ -55875,7 +55875,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1914" t="n">
-        <v>0.759289860725403</v>
+        <v>0.759289801120758</v>
       </c>
       <c r="H1914" t="n">
         <v>30810</v>
@@ -55904,7 +55904,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1915" t="n">
-        <v>0.764196455478668</v>
+        <v>0.764196395874023</v>
       </c>
       <c r="H1915" t="n">
         <v>76312</v>
@@ -55962,7 +55962,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1917" t="n">
-        <v>0.775236189365387</v>
+        <v>0.775236129760742</v>
       </c>
       <c r="H1917" t="n">
         <v>109012</v>
@@ -56049,7 +56049,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1920" t="n">
-        <v>0.797315657138824</v>
+        <v>0.79731559753418</v>
       </c>
       <c r="H1920" t="n">
         <v>110958</v>
@@ -56107,7 +56107,7 @@
         <v>1.28400003910065</v>
       </c>
       <c r="G1922" t="n">
-        <v>0.787502586841583</v>
+        <v>0.787502527236938</v>
       </c>
       <c r="H1922" t="n">
         <v>47817</v>
@@ -56136,7 +56136,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1923" t="n">
-        <v>0.797315657138824</v>
+        <v>0.79731559753418</v>
       </c>
       <c r="H1923" t="n">
         <v>186595</v>
@@ -56165,7 +56165,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1924" t="n">
-        <v>0.797315657138824</v>
+        <v>0.79731559753418</v>
       </c>
       <c r="H1924" t="n">
         <v>93366</v>
@@ -56252,7 +56252,7 @@
         <v>1.31200003623962</v>
       </c>
       <c r="G1927" t="n">
-        <v>0.8046755194664</v>
+        <v>0.804675459861755</v>
       </c>
       <c r="H1927" t="n">
         <v>213266</v>
@@ -56281,7 +56281,7 @@
         <v>1.31599998474121</v>
       </c>
       <c r="G1928" t="n">
-        <v>0.80712878704071</v>
+        <v>0.807128727436066</v>
       </c>
       <c r="H1928" t="n">
         <v>284340</v>
@@ -56310,7 +56310,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G1929" t="n">
-        <v>0.819395124912262</v>
+        <v>0.819395184516907</v>
       </c>
       <c r="H1929" t="n">
         <v>243567</v>
@@ -56397,7 +56397,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1932" t="n">
-        <v>0.775236189365387</v>
+        <v>0.775236129760742</v>
       </c>
       <c r="H1932" t="n">
         <v>117911</v>
@@ -56513,7 +56513,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1936" t="n">
-        <v>0.735983669757843</v>
+        <v>0.735983729362488</v>
       </c>
       <c r="H1936" t="n">
         <v>145184</v>
@@ -56571,7 +56571,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1938" t="n">
-        <v>0.759289860725403</v>
+        <v>0.759289801120758</v>
       </c>
       <c r="H1938" t="n">
         <v>76097</v>
@@ -56716,7 +56716,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1943" t="n">
-        <v>0.748250067234039</v>
+        <v>0.748250126838684</v>
       </c>
       <c r="H1943" t="n">
         <v>117184</v>
@@ -56803,7 +56803,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1946" t="n">
-        <v>0.760516464710236</v>
+        <v>0.76051652431488</v>
       </c>
       <c r="H1946" t="n">
         <v>47490</v>
@@ -56832,7 +56832,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G1947" t="n">
-        <v>0.758063137531281</v>
+        <v>0.758063197135925</v>
       </c>
       <c r="H1947" t="n">
         <v>156141</v>
@@ -56977,7 +56977,7 @@
         <v>1.26199996471405</v>
       </c>
       <c r="G1952" t="n">
-        <v>0.774009466171265</v>
+        <v>0.774009525775909</v>
       </c>
       <c r="H1952" t="n">
         <v>252075</v>
@@ -57122,7 +57122,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1957" t="n">
-        <v>0.772782921791077</v>
+        <v>0.772782802581787</v>
       </c>
       <c r="H1957" t="n">
         <v>86324</v>
@@ -57151,7 +57151,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1958" t="n">
-        <v>0.775236189365387</v>
+        <v>0.775236129760742</v>
       </c>
       <c r="H1958" t="n">
         <v>59757</v>
@@ -57180,7 +57180,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1959" t="n">
-        <v>0.775236189365387</v>
+        <v>0.775236129760742</v>
       </c>
       <c r="H1959" t="n">
         <v>60924</v>
@@ -57441,7 +57441,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1968" t="n">
-        <v>0.889313638210297</v>
+        <v>0.889313697814941</v>
       </c>
       <c r="H1968" t="n">
         <v>580634</v>
@@ -57499,7 +57499,7 @@
         <v>1.44400000572205</v>
       </c>
       <c r="G1970" t="n">
-        <v>0.885633707046509</v>
+        <v>0.885633647441864</v>
       </c>
       <c r="H1970" t="n">
         <v>468014</v>
@@ -57586,7 +57586,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G1973" t="n">
-        <v>0.912619829177856</v>
+        <v>0.912619769573212</v>
       </c>
       <c r="H1973" t="n">
         <v>300698</v>
@@ -57615,7 +57615,7 @@
         <v>1.50399994850159</v>
       </c>
       <c r="G1974" t="n">
-        <v>0.922432839870453</v>
+        <v>0.922432899475098</v>
       </c>
       <c r="H1974" t="n">
         <v>503202</v>
@@ -57673,7 +57673,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1976" t="n">
-        <v>0.926112830638885</v>
+        <v>0.926112771034241</v>
       </c>
       <c r="H1976" t="n">
         <v>169088</v>
@@ -57702,7 +57702,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1977" t="n">
-        <v>0.928566157817841</v>
+        <v>0.928566098213196</v>
       </c>
       <c r="H1977" t="n">
         <v>2340651</v>
@@ -57760,7 +57760,7 @@
         <v>1.58800005912781</v>
       </c>
       <c r="G1979" t="n">
-        <v>0.973951876163483</v>
+        <v>0.973951756954193</v>
       </c>
       <c r="H1979" t="n">
         <v>372992</v>
@@ -57789,7 +57789,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G1980" t="n">
-        <v>1.04141700267792</v>
+        <v>1.04141688346863</v>
       </c>
       <c r="H1980" t="n">
         <v>635537</v>
@@ -57818,7 +57818,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G1981" t="n">
-        <v>1.02792394161224</v>
+        <v>1.02792382240295</v>
       </c>
       <c r="H1981" t="n">
         <v>385147</v>
@@ -57876,7 +57876,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1983" t="n">
-        <v>0.999711096286774</v>
+        <v>0.999711155891418</v>
       </c>
       <c r="H1983" t="n">
         <v>355798</v>
@@ -57905,7 +57905,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1984" t="n">
-        <v>1.02301740646362</v>
+        <v>1.02301728725433</v>
       </c>
       <c r="H1984" t="n">
         <v>591445</v>
@@ -57934,7 +57934,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.01197755336761</v>
+        <v>1.0119776725769</v>
       </c>
       <c r="H1985" t="n">
         <v>307422</v>
@@ -58021,7 +58021,7 @@
         <v>1.64400005340576</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.00829756259918</v>
+        <v>1.00829768180847</v>
       </c>
       <c r="H1988" t="n">
         <v>364234</v>
@@ -58079,7 +58079,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G1990" t="n">
-        <v>0.986218154430389</v>
+        <v>0.986218094825745</v>
       </c>
       <c r="H1990" t="n">
         <v>370565</v>
@@ -58108,7 +58108,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G1991" t="n">
-        <v>0.917526304721832</v>
+        <v>0.917526364326477</v>
       </c>
       <c r="H1991" t="n">
         <v>1073810</v>
@@ -58137,7 +58137,7 @@
         <v>1.54799997806549</v>
       </c>
       <c r="G1992" t="n">
-        <v>0.949418902397156</v>
+        <v>0.949418962001801</v>
       </c>
       <c r="H1992" t="n">
         <v>618719</v>
@@ -58166,7 +58166,7 @@
         <v>1.54799997806549</v>
       </c>
       <c r="G1993" t="n">
-        <v>0.949418902397156</v>
+        <v>0.949418962001801</v>
       </c>
       <c r="H1993" t="n">
         <v>164171</v>
@@ -58195,7 +58195,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1994" t="n">
-        <v>0.937152504920959</v>
+        <v>0.937152564525604</v>
       </c>
       <c r="H1994" t="n">
         <v>126527</v>
@@ -58224,7 +58224,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1995" t="n">
-        <v>0.956778824329376</v>
+        <v>0.956778764724731</v>
       </c>
       <c r="H1995" t="n">
         <v>285758</v>
@@ -58311,7 +58311,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1998" t="n">
-        <v>0.965365350246429</v>
+        <v>0.965365290641785</v>
       </c>
       <c r="H1998" t="n">
         <v>115948</v>
@@ -58340,7 +58340,7 @@
         <v>1.5</v>
       </c>
       <c r="G1999" t="n">
-        <v>0.919979512691498</v>
+        <v>0.919979631900787</v>
       </c>
       <c r="H1999" t="n">
         <v>702293</v>
@@ -58427,7 +58427,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G2002" t="n">
-        <v>0.953098952770233</v>
+        <v>0.953098833560944</v>
       </c>
       <c r="H2002" t="n">
         <v>145635</v>
@@ -58456,7 +58456,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G2003" t="n">
-        <v>0.980085015296936</v>
+        <v>0.980084955692291</v>
       </c>
       <c r="H2003" t="n">
         <v>535679</v>
@@ -58485,7 +58485,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G2004" t="n">
-        <v>1.01075100898743</v>
+        <v>1.01075088977814</v>
       </c>
       <c r="H2004" t="n">
         <v>1171917</v>
@@ -58514,7 +58514,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G2005" t="n">
-        <v>0.999711096286774</v>
+        <v>0.999711155891418</v>
       </c>
       <c r="H2005" t="n">
         <v>423686</v>
@@ -58543,7 +58543,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G2006" t="n">
-        <v>0.999711096286774</v>
+        <v>0.999711155891418</v>
       </c>
       <c r="H2006" t="n">
         <v>242068</v>
@@ -58572,7 +58572,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G2007" t="n">
-        <v>0.987444758415222</v>
+        <v>0.987444818019867</v>
       </c>
       <c r="H2007" t="n">
         <v>109945</v>
@@ -58601,7 +58601,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G2008" t="n">
-        <v>1.00461769104004</v>
+        <v>1.00461781024933</v>
       </c>
       <c r="H2008" t="n">
         <v>260872</v>
@@ -58717,7 +58717,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G2012" t="n">
-        <v>0.983764886856079</v>
+        <v>0.98376476764679</v>
       </c>
       <c r="H2012" t="n">
         <v>155404</v>
@@ -58746,7 +58746,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G2013" t="n">
-        <v>0.987444758415222</v>
+        <v>0.987444818019867</v>
       </c>
       <c r="H2013" t="n">
         <v>164498</v>
@@ -58775,7 +58775,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G2014" t="n">
-        <v>0.983764886856079</v>
+        <v>0.98376476764679</v>
       </c>
       <c r="H2014" t="n">
         <v>263889</v>
@@ -58804,7 +58804,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G2015" t="n">
-        <v>0.987444758415222</v>
+        <v>0.987444818019867</v>
       </c>
       <c r="H2015" t="n">
         <v>167544</v>
@@ -58833,7 +58833,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G2016" t="n">
-        <v>0.9886714220047</v>
+        <v>0.988671362400055</v>
       </c>
       <c r="H2016" t="n">
         <v>414094</v>
@@ -58862,7 +58862,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G2017" t="n">
-        <v>0.96291196346283</v>
+        <v>0.962912023067474</v>
       </c>
       <c r="H2017" t="n">
         <v>184712</v>
@@ -58891,7 +58891,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G2018" t="n">
-        <v>0.987444758415222</v>
+        <v>0.987444818019867</v>
       </c>
       <c r="H2018" t="n">
         <v>222854</v>
@@ -59094,7 +59094,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G2025" t="n">
-        <v>1.14813446998596</v>
+        <v>1.14813458919525</v>
       </c>
       <c r="H2025" t="n">
         <v>435936</v>
@@ -59181,7 +59181,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2028" t="n">
-        <v>1.25117218494415</v>
+        <v>1.25117230415344</v>
       </c>
       <c r="H2028" t="n">
         <v>897508</v>
@@ -59297,7 +59297,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2032" t="n">
-        <v>1.25117218494415</v>
+        <v>1.25117230415344</v>
       </c>
       <c r="H2032" t="n">
         <v>146024</v>
@@ -59384,7 +59384,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G2035" t="n">
-        <v>1.24197244644165</v>
+        <v>1.24197256565094</v>
       </c>
       <c r="H2035" t="n">
         <v>121284</v>
@@ -59442,7 +59442,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G2037" t="n">
-        <v>1.22970604896545</v>
+        <v>1.22970616817474</v>
       </c>
       <c r="H2037" t="n">
         <v>147813</v>
@@ -59529,7 +59529,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G2040" t="n">
-        <v>1.18493378162384</v>
+        <v>1.18493366241455</v>
       </c>
       <c r="H2040" t="n">
         <v>419422</v>
@@ -59558,7 +59558,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2041" t="n">
-        <v>1.17757380008698</v>
+        <v>1.17757391929626</v>
       </c>
       <c r="H2041" t="n">
         <v>173482</v>
@@ -59645,7 +59645,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G2044" t="n">
-        <v>1.22173297405243</v>
+        <v>1.22173285484314</v>
       </c>
       <c r="H2044" t="n">
         <v>456560</v>
@@ -59790,7 +59790,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2049" t="n">
-        <v>1.18370699882507</v>
+        <v>1.18370711803436</v>
       </c>
       <c r="H2049" t="n">
         <v>60184</v>
@@ -60022,7 +60022,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G2057" t="n">
-        <v>1.14200139045715</v>
+        <v>1.14200127124786</v>
       </c>
       <c r="H2057" t="n">
         <v>174498</v>
@@ -60080,7 +60080,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2059" t="n">
-        <v>1.13464152812958</v>
+        <v>1.13464140892029</v>
       </c>
       <c r="H2059" t="n">
         <v>125743</v>
@@ -60138,7 +60138,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2061" t="n">
-        <v>1.13464152812958</v>
+        <v>1.13464140892029</v>
       </c>
       <c r="H2061" t="n">
         <v>209670</v>
@@ -60283,7 +60283,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G2066" t="n">
-        <v>1.15794765949249</v>
+        <v>1.15794777870178</v>
       </c>
       <c r="H2066" t="n">
         <v>230384</v>
@@ -60312,7 +60312,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2067" t="n">
-        <v>1.16530740261078</v>
+        <v>1.16530752182007</v>
       </c>
       <c r="H2067" t="n">
         <v>174916</v>
@@ -60370,7 +60370,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G2069" t="n">
-        <v>1.16162753105164</v>
+        <v>1.16162765026093</v>
       </c>
       <c r="H2069" t="n">
         <v>184521</v>
@@ -60515,7 +60515,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G2074" t="n">
-        <v>1.22173297405243</v>
+        <v>1.22173285484314</v>
       </c>
       <c r="H2074" t="n">
         <v>457907</v>
@@ -60544,7 +60544,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2075" t="n">
-        <v>1.25730550289154</v>
+        <v>1.25730538368225</v>
       </c>
       <c r="H2075" t="n">
         <v>391092</v>
@@ -60573,7 +60573,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G2076" t="n">
-        <v>1.70502877235413</v>
+        <v>1.70502889156342</v>
       </c>
       <c r="H2076" t="n">
         <v>5087915</v>
@@ -60602,7 +60602,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G2077" t="n">
-        <v>1.71729516983032</v>
+        <v>1.71729528903961</v>
       </c>
       <c r="H2077" t="n">
         <v>1386670</v>
@@ -60631,7 +60631,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G2078" t="n">
-        <v>1.8184928894043</v>
+        <v>1.81849312782288</v>
       </c>
       <c r="H2078" t="n">
         <v>1688908</v>
@@ -60660,7 +60660,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2079" t="n">
-        <v>1.94422364234924</v>
+        <v>1.94422352313995</v>
       </c>
       <c r="H2079" t="n">
         <v>1370361</v>
@@ -60689,7 +60689,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G2080" t="n">
-        <v>1.89822471141815</v>
+        <v>1.89822459220886</v>
       </c>
       <c r="H2080" t="n">
         <v>851748</v>
@@ -60718,7 +60718,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G2081" t="n">
-        <v>1.87675857543945</v>
+        <v>1.87675821781158</v>
       </c>
       <c r="H2081" t="n">
         <v>677611</v>
@@ -60834,7 +60834,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G2085" t="n">
-        <v>1.74182796478271</v>
+        <v>1.741828083992</v>
       </c>
       <c r="H2085" t="n">
         <v>645162</v>
@@ -60863,7 +60863,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G2086" t="n">
-        <v>1.74489462375641</v>
+        <v>1.7448947429657</v>
       </c>
       <c r="H2086" t="n">
         <v>454908</v>
@@ -60892,7 +60892,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G2087" t="n">
-        <v>1.84302592277527</v>
+        <v>1.84302580356598</v>
       </c>
       <c r="H2087" t="n">
         <v>693240</v>
@@ -61008,7 +61008,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2091" t="n">
-        <v>1.91355764865875</v>
+        <v>1.91355752944946</v>
       </c>
       <c r="H2091" t="n">
         <v>668620</v>
@@ -61182,7 +61182,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2097" t="n">
-        <v>1.99942219257355</v>
+        <v>1.99942231178284</v>
       </c>
       <c r="H2097" t="n">
         <v>632586</v>
@@ -61240,7 +61240,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G2099" t="n">
-        <v>1.95955657958984</v>
+        <v>1.95955646038055</v>
       </c>
       <c r="H2099" t="n">
         <v>309057</v>
@@ -61269,7 +61269,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G2100" t="n">
-        <v>1.92275750637054</v>
+        <v>1.92275738716125</v>
       </c>
       <c r="H2100" t="n">
         <v>593300</v>
@@ -61327,7 +61327,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2102" t="n">
-        <v>1.93809044361115</v>
+        <v>1.93809032440186</v>
       </c>
       <c r="H2102" t="n">
         <v>199370</v>
@@ -61414,7 +61414,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2105" t="n">
-        <v>1.97488951683044</v>
+        <v>1.97488963603973</v>
       </c>
       <c r="H2105" t="n">
         <v>324201</v>
@@ -61443,7 +61443,7 @@
         <v>3.25</v>
       </c>
       <c r="G2106" t="n">
-        <v>1.99328923225403</v>
+        <v>1.99328911304474</v>
       </c>
       <c r="H2106" t="n">
         <v>313415</v>
@@ -61472,7 +61472,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2107" t="n">
-        <v>2.00555562973022</v>
+        <v>2.00555539131165</v>
       </c>
       <c r="H2107" t="n">
         <v>289188</v>
@@ -61588,7 +61588,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2111" t="n">
-        <v>1.92582392692566</v>
+        <v>1.92582404613495</v>
       </c>
       <c r="H2111" t="n">
         <v>213530</v>
@@ -61617,7 +61617,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G2112" t="n">
-        <v>1.92275750637054</v>
+        <v>1.92275738716125</v>
       </c>
       <c r="H2112" t="n">
         <v>150439</v>
@@ -61646,7 +61646,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2113" t="n">
-        <v>1.88902485370636</v>
+        <v>1.88902473449707</v>
       </c>
       <c r="H2113" t="n">
         <v>498070</v>
@@ -61675,7 +61675,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2114" t="n">
-        <v>1.88902485370636</v>
+        <v>1.88902473449707</v>
       </c>
       <c r="H2114" t="n">
         <v>245321</v>
@@ -61704,7 +61704,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G2115" t="n">
-        <v>1.89515793323517</v>
+        <v>1.89515805244446</v>
       </c>
       <c r="H2115" t="n">
         <v>279894</v>
@@ -61733,7 +61733,7 @@
         <v>3</v>
       </c>
       <c r="G2116" t="n">
-        <v>1.839959025383</v>
+        <v>1.83995926380157</v>
       </c>
       <c r="H2116" t="n">
         <v>604364</v>
@@ -61762,7 +61762,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G2117" t="n">
-        <v>1.7724940776825</v>
+        <v>1.77249419689178</v>
       </c>
       <c r="H2117" t="n">
         <v>350773</v>
@@ -61820,7 +61820,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G2119" t="n">
-        <v>1.8062264919281</v>
+        <v>1.80622661113739</v>
       </c>
       <c r="H2119" t="n">
         <v>193216</v>
@@ -61907,7 +61907,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G2122" t="n">
-        <v>1.8184928894043</v>
+        <v>1.81849312782288</v>
       </c>
       <c r="H2122" t="n">
         <v>874006</v>
@@ -61965,7 +61965,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G2124" t="n">
-        <v>2.01250958442688</v>
+        <v>2.0125093460083</v>
       </c>
       <c r="H2124" t="n">
         <v>1836606</v>
@@ -61994,7 +61994,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G2125" t="n">
-        <v>1.96318304538727</v>
+        <v>1.96318316459656</v>
       </c>
       <c r="H2125" t="n">
         <v>691906</v>
@@ -62052,7 +62052,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G2127" t="n">
-        <v>1.79218566417694</v>
+        <v>1.79218554496765</v>
       </c>
       <c r="H2127" t="n">
         <v>741856</v>
@@ -62197,7 +62197,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G2132" t="n">
-        <v>1.8316468000412</v>
+        <v>1.83164668083191</v>
       </c>
       <c r="H2132" t="n">
         <v>448052</v>
@@ -62284,7 +62284,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G2135" t="n">
-        <v>1.79218566417694</v>
+        <v>1.79218554496765</v>
       </c>
       <c r="H2135" t="n">
         <v>224205</v>
@@ -62313,7 +62313,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G2136" t="n">
-        <v>1.79218566417694</v>
+        <v>1.79218554496765</v>
       </c>
       <c r="H2136" t="n">
         <v>245245</v>
@@ -62371,7 +62371,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G2138" t="n">
-        <v>1.95660638809204</v>
+        <v>1.95660626888275</v>
       </c>
       <c r="H2138" t="n">
         <v>672942</v>
@@ -62400,7 +62400,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G2139" t="n">
-        <v>1.95002949237823</v>
+        <v>1.95002961158752</v>
       </c>
       <c r="H2139" t="n">
         <v>521188</v>
@@ -62429,7 +62429,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G2140" t="n">
-        <v>1.92043375968933</v>
+        <v>1.92043387889862</v>
       </c>
       <c r="H2140" t="n">
         <v>334815</v>
@@ -62458,7 +62458,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G2141" t="n">
-        <v>1.93358743190765</v>
+        <v>1.93358755111694</v>
       </c>
       <c r="H2141" t="n">
         <v>370967</v>
@@ -62487,7 +62487,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G2142" t="n">
-        <v>1.92372214794159</v>
+        <v>1.92372226715088</v>
       </c>
       <c r="H2142" t="n">
         <v>298873</v>
@@ -62545,7 +62545,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G2144" t="n">
-        <v>1.9072802066803</v>
+        <v>1.90728032588959</v>
       </c>
       <c r="H2144" t="n">
         <v>620199</v>
@@ -62603,7 +62603,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G2146" t="n">
-        <v>1.9138571023941</v>
+        <v>1.91385698318481</v>
       </c>
       <c r="H2146" t="n">
         <v>226554</v>
@@ -62632,7 +62632,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G2147" t="n">
-        <v>1.91056847572327</v>
+        <v>1.91056859493256</v>
       </c>
       <c r="H2147" t="n">
         <v>187722</v>
@@ -62661,7 +62661,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G2148" t="n">
-        <v>1.91056847572327</v>
+        <v>1.91056859493256</v>
       </c>
       <c r="H2148" t="n">
         <v>164909</v>
@@ -62690,7 +62690,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G2149" t="n">
-        <v>1.91714549064636</v>
+        <v>1.91714537143707</v>
       </c>
       <c r="H2149" t="n">
         <v>412284</v>
@@ -62748,7 +62748,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G2151" t="n">
-        <v>1.87110757827759</v>
+        <v>1.87110769748688</v>
       </c>
       <c r="H2151" t="n">
         <v>587531</v>
@@ -62835,7 +62835,7 @@
         <v>3</v>
       </c>
       <c r="G2154" t="n">
-        <v>1.97304832935333</v>
+        <v>1.97304844856262</v>
       </c>
       <c r="H2154" t="n">
         <v>2848260</v>
@@ -63096,7 +63096,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2163" t="n">
-        <v>2.22296810150146</v>
+        <v>2.22296786308289</v>
       </c>
       <c r="H2163" t="n">
         <v>1428310</v>
@@ -63125,7 +63125,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G2164" t="n">
-        <v>2.17693018913269</v>
+        <v>2.17692995071411</v>
       </c>
       <c r="H2164" t="n">
         <v>991592</v>
@@ -63154,7 +63154,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G2165" t="n">
-        <v>2.20981407165527</v>
+        <v>2.20981431007385</v>
       </c>
       <c r="H2165" t="n">
         <v>535197</v>
@@ -63183,7 +63183,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2166" t="n">
-        <v>2.22296810150146</v>
+        <v>2.22296786308289</v>
       </c>
       <c r="H2166" t="n">
         <v>543161</v>
@@ -63270,7 +63270,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G2169" t="n">
-        <v>2.17693018913269</v>
+        <v>2.17692995071411</v>
       </c>
       <c r="H2169" t="n">
         <v>544446</v>
@@ -80009,6 +80009,35 @@
         <v>272103</v>
       </c>
       <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>2.02500009536743</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>1.98000001907349</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>2.02500009536743</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>2.02500009536743</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>327904</v>
+      </c>
+      <c r="I2747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SGF.MI.xlsx
+++ b/data/SGF.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2" t="n">
-        <v>1.25117230415344</v>
+        <v>1.25117218494415</v>
       </c>
       <c r="H2" t="n">
         <v>208771</v>
@@ -456,7 +456,7 @@
         <v>2.00399994850159</v>
       </c>
       <c r="G3" t="n">
-        <v>1.22909271717072</v>
+        <v>1.22909259796143</v>
       </c>
       <c r="H3" t="n">
         <v>161308</v>
@@ -485,7 +485,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G4" t="n">
-        <v>1.20210659503937</v>
+        <v>1.20210671424866</v>
       </c>
       <c r="H4" t="n">
         <v>263865</v>
@@ -543,7 +543,7 @@
         <v>1.91299998760223</v>
       </c>
       <c r="G6" t="n">
-        <v>1.17328059673309</v>
+        <v>1.17328071594238</v>
       </c>
       <c r="H6" t="n">
         <v>373482</v>
@@ -601,7 +601,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G8" t="n">
-        <v>1.17389392852783</v>
+        <v>1.17389404773712</v>
       </c>
       <c r="H8" t="n">
         <v>255301</v>
@@ -717,7 +717,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G12" t="n">
-        <v>1.05613648891449</v>
+        <v>1.05613660812378</v>
       </c>
       <c r="H12" t="n">
         <v>445686</v>
@@ -775,7 +775,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>1.00891089439392</v>
+        <v>1.00891101360321</v>
       </c>
       <c r="H14" t="n">
         <v>229916</v>
@@ -891,7 +891,7 @@
         <v>1.77400004863739</v>
       </c>
       <c r="G18" t="n">
-        <v>1.08802926540375</v>
+        <v>1.08802914619446</v>
       </c>
       <c r="H18" t="n">
         <v>242295</v>
@@ -978,7 +978,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G21" t="n">
-        <v>1.05613648891449</v>
+        <v>1.05613660812378</v>
       </c>
       <c r="H21" t="n">
         <v>130477</v>
@@ -1065,7 +1065,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G24" t="n">
-        <v>1.01075088977814</v>
+        <v>1.01075100898743</v>
       </c>
       <c r="H24" t="n">
         <v>327325</v>
@@ -1239,7 +1239,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G30" t="n">
-        <v>0.858647644519806</v>
+        <v>0.858647584915161</v>
       </c>
       <c r="H30" t="n">
         <v>298478</v>
@@ -1268,7 +1268,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G31" t="n">
-        <v>0.916913032531738</v>
+        <v>0.916912972927094</v>
       </c>
       <c r="H31" t="n">
         <v>204119</v>
@@ -1297,7 +1297,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G32" t="n">
-        <v>0.981311619281769</v>
+        <v>0.981311559677124</v>
       </c>
       <c r="H32" t="n">
         <v>168307</v>
@@ -1326,7 +1326,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G33" t="n">
-        <v>0.950645565986633</v>
+        <v>0.950645625591278</v>
       </c>
       <c r="H33" t="n">
         <v>252019</v>
@@ -1355,7 +1355,7 @@
         <v>1.56099998950958</v>
       </c>
       <c r="G34" t="n">
-        <v>0.957392036914825</v>
+        <v>0.95739209651947</v>
       </c>
       <c r="H34" t="n">
         <v>320159</v>
@@ -1413,7 +1413,7 @@
         <v>1.50399994850159</v>
       </c>
       <c r="G36" t="n">
-        <v>0.922432899475098</v>
+        <v>0.922432839870453</v>
       </c>
       <c r="H36" t="n">
         <v>200666</v>
@@ -1442,7 +1442,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G37" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H37" t="n">
         <v>274788</v>
@@ -1500,7 +1500,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G39" t="n">
-        <v>0.924886167049408</v>
+        <v>0.924886226654053</v>
       </c>
       <c r="H39" t="n">
         <v>291804</v>
@@ -1529,7 +1529,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G40" t="n">
-        <v>0.910166442394257</v>
+        <v>0.910166501998901</v>
       </c>
       <c r="H40" t="n">
         <v>482847</v>
@@ -1558,7 +1558,7 @@
         <v>1.52699995040894</v>
       </c>
       <c r="G41" t="n">
-        <v>0.936539232730865</v>
+        <v>0.93653929233551</v>
       </c>
       <c r="H41" t="n">
         <v>374615</v>
@@ -1587,7 +1587,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G42" t="n">
-        <v>0.872140765190125</v>
+        <v>0.872140645980835</v>
       </c>
       <c r="H42" t="n">
         <v>633854</v>
@@ -1616,7 +1616,7 @@
         <v>1.5</v>
       </c>
       <c r="G43" t="n">
-        <v>0.919979631900787</v>
+        <v>0.919979512691498</v>
       </c>
       <c r="H43" t="n">
         <v>841811</v>
@@ -1761,7 +1761,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G48" t="n">
-        <v>1.0040043592453</v>
+        <v>1.00400447845459</v>
       </c>
       <c r="H48" t="n">
         <v>312388</v>
@@ -1790,7 +1790,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G49" t="n">
-        <v>1.00891089439392</v>
+        <v>1.00891101360321</v>
       </c>
       <c r="H49" t="n">
         <v>192494</v>
@@ -1819,7 +1819,7 @@
         <v>1.54700005054474</v>
       </c>
       <c r="G50" t="n">
-        <v>0.948805689811707</v>
+        <v>0.948805630207062</v>
       </c>
       <c r="H50" t="n">
         <v>402246</v>
@@ -1848,7 +1848,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G51" t="n">
-        <v>0.986218094825745</v>
+        <v>0.986218154430389</v>
       </c>
       <c r="H51" t="n">
         <v>297628</v>
@@ -1906,7 +1906,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G53" t="n">
-        <v>0.960458695888519</v>
+        <v>0.960458636283875</v>
       </c>
       <c r="H53" t="n">
         <v>389718</v>
@@ -1935,7 +1935,7 @@
         <v>1.58299994468689</v>
       </c>
       <c r="G54" t="n">
-        <v>0.970885157585144</v>
+        <v>0.970885097980499</v>
       </c>
       <c r="H54" t="n">
         <v>320346</v>
@@ -1964,7 +1964,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G55" t="n">
-        <v>0.956165492534637</v>
+        <v>0.956165432929993</v>
       </c>
       <c r="H55" t="n">
         <v>282072</v>
@@ -1993,7 +1993,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G56" t="n">
-        <v>0.917526364326477</v>
+        <v>0.917526304721832</v>
       </c>
       <c r="H56" t="n">
         <v>1000501</v>
@@ -2022,7 +2022,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G57" t="n">
-        <v>0.926112771034241</v>
+        <v>0.92611289024353</v>
       </c>
       <c r="H57" t="n">
         <v>413338</v>
@@ -2051,7 +2051,7 @@
         <v>1.5</v>
       </c>
       <c r="G58" t="n">
-        <v>0.919979631900787</v>
+        <v>0.919979512691498</v>
       </c>
       <c r="H58" t="n">
         <v>214751</v>
@@ -2138,7 +2138,7 @@
         <v>1.34300005435944</v>
       </c>
       <c r="G61" t="n">
-        <v>0.823688387870789</v>
+        <v>0.823688447475433</v>
       </c>
       <c r="H61" t="n">
         <v>330707</v>
@@ -2196,7 +2196,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G63" t="n">
-        <v>0.867234170436859</v>
+        <v>0.867234110832214</v>
       </c>
       <c r="H63" t="n">
         <v>267980</v>
@@ -2283,7 +2283,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G66" t="n">
-        <v>0.815715193748474</v>
+        <v>0.815715253353119</v>
       </c>
       <c r="H66" t="n">
         <v>496873</v>
@@ -2312,7 +2312,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G67" t="n">
-        <v>0.818781912326813</v>
+        <v>0.818781852722168</v>
       </c>
       <c r="H67" t="n">
         <v>147823</v>
@@ -2341,7 +2341,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G68" t="n">
-        <v>0.79424911737442</v>
+        <v>0.794249057769775</v>
       </c>
       <c r="H68" t="n">
         <v>210357</v>
@@ -2399,7 +2399,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G70" t="n">
-        <v>0.849447846412659</v>
+        <v>0.849447786808014</v>
       </c>
       <c r="H70" t="n">
         <v>138948</v>
@@ -2486,7 +2486,7 @@
         <v>1.43299996852875</v>
       </c>
       <c r="G73" t="n">
-        <v>0.878887116909027</v>
+        <v>0.878887236118317</v>
       </c>
       <c r="H73" t="n">
         <v>194805</v>
@@ -2544,7 +2544,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G75" t="n">
-        <v>0.895446836948395</v>
+        <v>0.89544677734375</v>
       </c>
       <c r="H75" t="n">
         <v>124767</v>
@@ -2573,7 +2573,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G76" t="n">
-        <v>0.852514445781708</v>
+        <v>0.852514386177063</v>
       </c>
       <c r="H76" t="n">
         <v>774434</v>
@@ -2602,7 +2602,7 @@
         <v>1.43099999427795</v>
       </c>
       <c r="G77" t="n">
-        <v>0.877660632133484</v>
+        <v>0.877660572528839</v>
       </c>
       <c r="H77" t="n">
         <v>342413</v>
@@ -2660,7 +2660,7 @@
         <v>1.42299997806549</v>
       </c>
       <c r="G79" t="n">
-        <v>0.872754037380219</v>
+        <v>0.872753977775574</v>
       </c>
       <c r="H79" t="n">
         <v>99483</v>
@@ -2689,7 +2689,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G80" t="n">
-        <v>0.872140765190125</v>
+        <v>0.872140645980835</v>
       </c>
       <c r="H80" t="n">
         <v>27237</v>
@@ -2718,7 +2718,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G81" t="n">
-        <v>0.868460714817047</v>
+        <v>0.868460774421692</v>
       </c>
       <c r="H81" t="n">
         <v>105201</v>
@@ -2747,7 +2747,7 @@
         <v>1.5</v>
       </c>
       <c r="G82" t="n">
-        <v>0.919979631900787</v>
+        <v>0.919979512691498</v>
       </c>
       <c r="H82" t="n">
         <v>823016</v>
@@ -2776,7 +2776,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G83" t="n">
-        <v>0.943285703659058</v>
+        <v>0.943285763263702</v>
       </c>
       <c r="H83" t="n">
         <v>666476</v>
@@ -2805,7 +2805,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G84" t="n">
-        <v>0.977631628513336</v>
+        <v>0.977631688117981</v>
       </c>
       <c r="H84" t="n">
         <v>875820</v>
@@ -2834,7 +2834,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G85" t="n">
-        <v>0.99357795715332</v>
+        <v>0.993577897548676</v>
       </c>
       <c r="H85" t="n">
         <v>550524</v>
@@ -2863,7 +2863,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G86" t="n">
-        <v>0.951258897781372</v>
+        <v>0.951258957386017</v>
       </c>
       <c r="H86" t="n">
         <v>426890</v>
@@ -2892,7 +2892,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G87" t="n">
-        <v>0.951258897781372</v>
+        <v>0.951258957386017</v>
       </c>
       <c r="H87" t="n">
         <v>290985</v>
@@ -2921,7 +2921,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G88" t="n">
-        <v>0.951258897781372</v>
+        <v>0.951258957386017</v>
       </c>
       <c r="H88" t="n">
         <v>302509</v>
@@ -2950,7 +2950,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G89" t="n">
-        <v>0.951258897781372</v>
+        <v>0.951258957386017</v>
       </c>
       <c r="H89" t="n">
         <v>223150</v>
@@ -3008,7 +3008,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G91" t="n">
-        <v>0.938379108905792</v>
+        <v>0.938379287719727</v>
       </c>
       <c r="H91" t="n">
         <v>93150</v>
@@ -3037,7 +3037,7 @@
         <v>1.54700005054474</v>
       </c>
       <c r="G92" t="n">
-        <v>0.948805689811707</v>
+        <v>0.948805630207062</v>
       </c>
       <c r="H92" t="n">
         <v>98852</v>
@@ -3066,7 +3066,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G93" t="n">
-        <v>0.978244960308075</v>
+        <v>0.97824501991272</v>
       </c>
       <c r="H93" t="n">
         <v>347619</v>
@@ -3211,7 +3211,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G98" t="n">
-        <v>0.943285703659058</v>
+        <v>0.943285763263702</v>
       </c>
       <c r="H98" t="n">
         <v>263085</v>
@@ -3269,7 +3269,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G100" t="n">
-        <v>0.927339375019073</v>
+        <v>0.927339434623718</v>
       </c>
       <c r="H100" t="n">
         <v>141573</v>
@@ -3298,7 +3298,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G101" t="n">
-        <v>0.953712165355682</v>
+        <v>0.953712105751038</v>
       </c>
       <c r="H101" t="n">
         <v>438231</v>
@@ -3327,7 +3327,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G102" t="n">
-        <v>1.02424395084381</v>
+        <v>1.02424383163452</v>
       </c>
       <c r="H102" t="n">
         <v>930519</v>
@@ -3356,7 +3356,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G103" t="n">
-        <v>1.09170913696289</v>
+        <v>1.0917090177536</v>
       </c>
       <c r="H103" t="n">
         <v>2561297</v>
@@ -3414,7 +3414,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G105" t="n">
-        <v>1.12360167503357</v>
+        <v>1.12360179424286</v>
       </c>
       <c r="H105" t="n">
         <v>517266</v>
@@ -3501,7 +3501,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G108" t="n">
-        <v>1.03037714958191</v>
+        <v>1.03037703037262</v>
       </c>
       <c r="H108" t="n">
         <v>290532</v>
@@ -3530,7 +3530,7 @@
         <v>1.64900004863739</v>
       </c>
       <c r="G109" t="n">
-        <v>1.01136422157288</v>
+        <v>1.01136434078217</v>
       </c>
       <c r="H109" t="n">
         <v>279197</v>
@@ -3704,7 +3704,7 @@
         <v>1.39300000667572</v>
       </c>
       <c r="G115" t="n">
-        <v>0.854354321956635</v>
+        <v>0.854354381561279</v>
       </c>
       <c r="H115" t="n">
         <v>1016663</v>
@@ -3733,7 +3733,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G116" t="n">
-        <v>0.806515455245972</v>
+        <v>0.806515514850616</v>
       </c>
       <c r="H116" t="n">
         <v>596787</v>
@@ -3994,7 +3994,7 @@
         <v>1.24800002574921</v>
       </c>
       <c r="G125" t="n">
-        <v>0.765422940254211</v>
+        <v>0.765422999858856</v>
       </c>
       <c r="H125" t="n">
         <v>532951</v>
@@ -4052,7 +4052,7 @@
         <v>1.25699996948242</v>
       </c>
       <c r="G127" t="n">
-        <v>0.770942807197571</v>
+        <v>0.77094292640686</v>
       </c>
       <c r="H127" t="n">
         <v>355957</v>
@@ -4081,7 +4081,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G128" t="n">
-        <v>0.806515455245972</v>
+        <v>0.806515514850616</v>
       </c>
       <c r="H128" t="n">
         <v>370971</v>
@@ -4110,7 +4110,7 @@
         <v>1.30900001525879</v>
       </c>
       <c r="G129" t="n">
-        <v>0.802835583686829</v>
+        <v>0.802835524082184</v>
       </c>
       <c r="H129" t="n">
         <v>198549</v>
@@ -4168,7 +4168,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G131" t="n">
-        <v>0.725557208061218</v>
+        <v>0.725557267665863</v>
       </c>
       <c r="H131" t="n">
         <v>634478</v>
@@ -4342,7 +4342,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G137" t="n">
-        <v>0.803448855876923</v>
+        <v>0.803448796272278</v>
       </c>
       <c r="H137" t="n">
         <v>159758</v>
@@ -4429,7 +4429,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G140" t="n">
-        <v>0.858647644519806</v>
+        <v>0.858647584915161</v>
       </c>
       <c r="H140" t="n">
         <v>257624</v>
@@ -4458,7 +4458,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G141" t="n">
-        <v>0.851287841796875</v>
+        <v>0.85128778219223</v>
       </c>
       <c r="H141" t="n">
         <v>149242</v>
@@ -4487,7 +4487,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G142" t="n">
-        <v>0.861101031303406</v>
+        <v>0.861100912094116</v>
       </c>
       <c r="H142" t="n">
         <v>133440</v>
@@ -4603,7 +4603,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G146" t="n">
-        <v>0.884407103061676</v>
+        <v>0.884407043457031</v>
       </c>
       <c r="H146" t="n">
         <v>428209</v>
@@ -4690,7 +4690,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G149" t="n">
-        <v>0.932245969772339</v>
+        <v>0.932246029376984</v>
       </c>
       <c r="H149" t="n">
         <v>325924</v>
@@ -4719,7 +4719,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G150" t="n">
-        <v>0.935925900936127</v>
+        <v>0.935925960540771</v>
       </c>
       <c r="H150" t="n">
         <v>228664</v>
@@ -4777,7 +4777,7 @@
         <v>1.54900002479553</v>
       </c>
       <c r="G152" t="n">
-        <v>0.950032234191895</v>
+        <v>0.950032293796539</v>
       </c>
       <c r="H152" t="n">
         <v>547010</v>
@@ -4951,7 +4951,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G158" t="n">
-        <v>1.02424395084381</v>
+        <v>1.02424383163452</v>
       </c>
       <c r="H158" t="n">
         <v>164073</v>
@@ -4980,7 +4980,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G159" t="n">
-        <v>1.01749753952026</v>
+        <v>1.01749742031097</v>
       </c>
       <c r="H159" t="n">
         <v>131636</v>
@@ -5009,7 +5009,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G160" t="n">
-        <v>1.03344368934631</v>
+        <v>1.0334438085556</v>
       </c>
       <c r="H160" t="n">
         <v>177788</v>
@@ -5154,7 +5154,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G165" t="n">
-        <v>1.03651034832001</v>
+        <v>1.0365104675293</v>
       </c>
       <c r="H165" t="n">
         <v>295809</v>
@@ -5183,7 +5183,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G166" t="n">
-        <v>1.03896355628967</v>
+        <v>1.03896367549896</v>
       </c>
       <c r="H166" t="n">
         <v>150712</v>
@@ -5241,7 +5241,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G168" t="n">
-        <v>1.03405702114105</v>
+        <v>1.03405714035034</v>
       </c>
       <c r="H168" t="n">
         <v>51800</v>
@@ -5357,7 +5357,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G172" t="n">
-        <v>1.02363073825836</v>
+        <v>1.02363061904907</v>
       </c>
       <c r="H172" t="n">
         <v>236960</v>
@@ -5415,7 +5415,7 @@
         <v>1.75800001621246</v>
       </c>
       <c r="G174" t="n">
-        <v>1.07821607589722</v>
+        <v>1.07821619510651</v>
       </c>
       <c r="H174" t="n">
         <v>614354</v>
@@ -5473,7 +5473,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G176" t="n">
-        <v>1.09170913696289</v>
+        <v>1.0917090177536</v>
       </c>
       <c r="H176" t="n">
         <v>233304</v>
@@ -5502,7 +5502,7 @@
         <v>1.77699995040894</v>
       </c>
       <c r="G177" t="n">
-        <v>1.08986914157867</v>
+        <v>1.08986902236938</v>
       </c>
       <c r="H177" t="n">
         <v>220355</v>
@@ -5560,7 +5560,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G179" t="n">
-        <v>1.0825092792511</v>
+        <v>1.08250939846039</v>
       </c>
       <c r="H179" t="n">
         <v>486372</v>
@@ -5589,7 +5589,7 @@
         <v>1.73699998855591</v>
       </c>
       <c r="G180" t="n">
-        <v>1.06533634662628</v>
+        <v>1.06533622741699</v>
       </c>
       <c r="H180" t="n">
         <v>112477</v>
@@ -5618,7 +5618,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G181" t="n">
-        <v>1.06472301483154</v>
+        <v>1.06472289562225</v>
       </c>
       <c r="H181" t="n">
         <v>121177</v>
@@ -5647,7 +5647,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G182" t="n">
-        <v>1.06410980224609</v>
+        <v>1.0641096830368</v>
       </c>
       <c r="H182" t="n">
         <v>104640</v>
@@ -5734,7 +5734,7 @@
         <v>1.68900001049042</v>
       </c>
       <c r="G185" t="n">
-        <v>1.03589701652527</v>
+        <v>1.03589713573456</v>
       </c>
       <c r="H185" t="n">
         <v>97005</v>
@@ -5763,7 +5763,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G186" t="n">
-        <v>1.0671763420105</v>
+        <v>1.06717622280121</v>
       </c>
       <c r="H186" t="n">
         <v>130158</v>
@@ -5792,7 +5792,7 @@
         <v>1.77400004863739</v>
       </c>
       <c r="G187" t="n">
-        <v>1.08802926540375</v>
+        <v>1.08802914619446</v>
       </c>
       <c r="H187" t="n">
         <v>705957</v>
@@ -5850,7 +5850,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G189" t="n">
-        <v>1.09170913696289</v>
+        <v>1.0917090177536</v>
       </c>
       <c r="H189" t="n">
         <v>140051</v>
@@ -5879,7 +5879,7 @@
         <v>1.78299999237061</v>
       </c>
       <c r="G190" t="n">
-        <v>1.09354913234711</v>
+        <v>1.09354901313782</v>
       </c>
       <c r="H190" t="n">
         <v>136706</v>
@@ -5937,7 +5937,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G192" t="n">
-        <v>1.1039754152298</v>
+        <v>1.10397553443909</v>
       </c>
       <c r="H192" t="n">
         <v>122359</v>
@@ -5966,7 +5966,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G193" t="n">
-        <v>1.1039754152298</v>
+        <v>1.10397553443909</v>
       </c>
       <c r="H193" t="n">
         <v>198036</v>
@@ -5995,7 +5995,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G194" t="n">
-        <v>1.09170913696289</v>
+        <v>1.0917090177536</v>
       </c>
       <c r="H194" t="n">
         <v>147290</v>
@@ -6024,7 +6024,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G195" t="n">
-        <v>1.09416246414185</v>
+        <v>1.09416234493256</v>
       </c>
       <c r="H195" t="n">
         <v>227267</v>
@@ -6082,7 +6082,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G197" t="n">
-        <v>1.1039754152298</v>
+        <v>1.10397553443909</v>
       </c>
       <c r="H197" t="n">
         <v>163067</v>
@@ -6111,7 +6111,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G198" t="n">
-        <v>1.09784233570099</v>
+        <v>1.0978422164917</v>
       </c>
       <c r="H198" t="n">
         <v>97852</v>
@@ -6140,7 +6140,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G199" t="n">
-        <v>1.10152232646942</v>
+        <v>1.10152220726013</v>
       </c>
       <c r="H199" t="n">
         <v>60811</v>
@@ -6169,7 +6169,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>1.09784233570099</v>
+        <v>1.0978422164917</v>
       </c>
       <c r="H200" t="n">
         <v>71260</v>
@@ -6256,7 +6256,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G203" t="n">
-        <v>1.08864259719849</v>
+        <v>1.0886424779892</v>
       </c>
       <c r="H203" t="n">
         <v>66057</v>
@@ -6343,7 +6343,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G206" t="n">
-        <v>1.0904825925827</v>
+        <v>1.09048247337341</v>
       </c>
       <c r="H206" t="n">
         <v>120993</v>
@@ -6372,7 +6372,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G207" t="n">
-        <v>1.10274887084961</v>
+        <v>1.1027489900589</v>
       </c>
       <c r="H207" t="n">
         <v>147930</v>
@@ -6401,7 +6401,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G208" t="n">
-        <v>1.10152232646942</v>
+        <v>1.10152220726013</v>
       </c>
       <c r="H208" t="n">
         <v>71337</v>
@@ -6459,7 +6459,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G210" t="n">
-        <v>1.18370711803436</v>
+        <v>1.18370699882507</v>
       </c>
       <c r="H210" t="n">
         <v>1793350</v>
@@ -6517,7 +6517,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G212" t="n">
-        <v>1.25117230415344</v>
+        <v>1.25117218494415</v>
       </c>
       <c r="H212" t="n">
         <v>455701</v>
@@ -6662,7 +6662,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G217" t="n">
-        <v>1.28551805019379</v>
+        <v>1.28551816940308</v>
       </c>
       <c r="H217" t="n">
         <v>339279</v>
@@ -6691,7 +6691,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G218" t="n">
-        <v>1.26466536521912</v>
+        <v>1.26466524600983</v>
       </c>
       <c r="H218" t="n">
         <v>379339</v>
@@ -6720,7 +6720,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G219" t="n">
-        <v>1.29165124893188</v>
+        <v>1.29165136814117</v>
       </c>
       <c r="H219" t="n">
         <v>262875</v>
@@ -6749,7 +6749,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G220" t="n">
-        <v>1.24503898620605</v>
+        <v>1.24503910541534</v>
       </c>
       <c r="H220" t="n">
         <v>521123</v>
@@ -6865,7 +6865,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G224" t="n">
-        <v>1.30759763717651</v>
+        <v>1.3075977563858</v>
       </c>
       <c r="H224" t="n">
         <v>602971</v>
@@ -6894,7 +6894,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G225" t="n">
-        <v>1.31495749950409</v>
+        <v>1.31495761871338</v>
       </c>
       <c r="H225" t="n">
         <v>292475</v>
@@ -6952,7 +6952,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G227" t="n">
-        <v>1.32477056980133</v>
+        <v>1.32477068901062</v>
       </c>
       <c r="H227" t="n">
         <v>203471</v>
@@ -6981,7 +6981,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G228" t="n">
-        <v>1.32477056980133</v>
+        <v>1.32477068901062</v>
       </c>
       <c r="H228" t="n">
         <v>299354</v>
@@ -7010,7 +7010,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G229" t="n">
-        <v>1.33090376853943</v>
+        <v>1.33090388774872</v>
       </c>
       <c r="H229" t="n">
         <v>710066</v>
@@ -7039,7 +7039,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G230" t="n">
-        <v>1.32354402542114</v>
+        <v>1.32354390621185</v>
       </c>
       <c r="H230" t="n">
         <v>328805</v>
@@ -7068,7 +7068,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G231" t="n">
-        <v>1.29165124893188</v>
+        <v>1.29165136814117</v>
       </c>
       <c r="H231" t="n">
         <v>425513</v>
@@ -7097,7 +7097,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G232" t="n">
-        <v>1.30023777484894</v>
+        <v>1.30023765563965</v>
       </c>
       <c r="H232" t="n">
         <v>267103</v>
@@ -7126,7 +7126,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G233" t="n">
-        <v>1.29901123046875</v>
+        <v>1.29901111125946</v>
       </c>
       <c r="H233" t="n">
         <v>173166</v>
@@ -7329,7 +7329,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G240" t="n">
-        <v>1.30023777484894</v>
+        <v>1.30023765563965</v>
       </c>
       <c r="H240" t="n">
         <v>384899</v>
@@ -7532,7 +7532,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G247" t="n">
-        <v>1.45970106124878</v>
+        <v>1.45970094203949</v>
       </c>
       <c r="H247" t="n">
         <v>391093</v>
@@ -7590,7 +7590,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G249" t="n">
-        <v>1.47932708263397</v>
+        <v>1.47932720184326</v>
       </c>
       <c r="H249" t="n">
         <v>163664</v>
@@ -7648,7 +7648,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G251" t="n">
-        <v>1.50263321399689</v>
+        <v>1.50263333320618</v>
       </c>
       <c r="H251" t="n">
         <v>163694</v>
@@ -7677,7 +7677,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G252" t="n">
-        <v>1.49650025367737</v>
+        <v>1.49650013446808</v>
       </c>
       <c r="H252" t="n">
         <v>188904</v>
@@ -7793,7 +7793,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G256" t="n">
-        <v>1.47810053825378</v>
+        <v>1.47810065746307</v>
       </c>
       <c r="H256" t="n">
         <v>141019</v>
@@ -7909,7 +7909,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G260" t="n">
-        <v>1.58113825321198</v>
+        <v>1.58113837242126</v>
       </c>
       <c r="H260" t="n">
         <v>206628</v>
@@ -8025,7 +8025,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G264" t="n">
-        <v>1.57377851009369</v>
+        <v>1.5737783908844</v>
       </c>
       <c r="H264" t="n">
         <v>102370</v>
@@ -8083,7 +8083,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G266" t="n">
-        <v>1.55169880390167</v>
+        <v>1.55169904232025</v>
       </c>
       <c r="H266" t="n">
         <v>242727</v>
@@ -8141,7 +8141,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G268" t="n">
-        <v>1.57868504524231</v>
+        <v>1.57868492603302</v>
       </c>
       <c r="H268" t="n">
         <v>126004</v>
@@ -8228,7 +8228,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G271" t="n">
-        <v>1.52593958377838</v>
+        <v>1.52593946456909</v>
       </c>
       <c r="H271" t="n">
         <v>154741</v>
@@ -8257,7 +8257,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G272" t="n">
-        <v>1.51367294788361</v>
+        <v>1.5136730670929</v>
       </c>
       <c r="H272" t="n">
         <v>102900</v>
@@ -8315,7 +8315,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G274" t="n">
-        <v>1.53084588050842</v>
+        <v>1.53084599971771</v>
       </c>
       <c r="H274" t="n">
         <v>132938</v>
@@ -8373,7 +8373,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G276" t="n">
-        <v>1.52593958377838</v>
+        <v>1.52593946456909</v>
       </c>
       <c r="H276" t="n">
         <v>121968</v>
@@ -8460,7 +8460,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G279" t="n">
-        <v>1.34930336475372</v>
+        <v>1.34930348396301</v>
       </c>
       <c r="H279" t="n">
         <v>403808</v>
@@ -8489,7 +8489,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G280" t="n">
-        <v>1.41676843166351</v>
+        <v>1.4167685508728</v>
       </c>
       <c r="H280" t="n">
         <v>233709</v>
@@ -8518,7 +8518,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G281" t="n">
-        <v>1.41308856010437</v>
+        <v>1.41308867931366</v>
       </c>
       <c r="H281" t="n">
         <v>67393</v>
@@ -8576,7 +8576,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G283" t="n">
-        <v>1.35543656349182</v>
+        <v>1.35543668270111</v>
       </c>
       <c r="H283" t="n">
         <v>155089</v>
@@ -8750,7 +8750,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G289" t="n">
-        <v>1.40940880775452</v>
+        <v>1.40940892696381</v>
       </c>
       <c r="H289" t="n">
         <v>287135</v>
@@ -8837,7 +8837,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G292" t="n">
-        <v>1.38732922077179</v>
+        <v>1.38732933998108</v>
       </c>
       <c r="H292" t="n">
         <v>78586</v>
@@ -8866,7 +8866,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G293" t="n">
-        <v>1.39959573745728</v>
+        <v>1.39959561824799</v>
       </c>
       <c r="H293" t="n">
         <v>84346</v>
@@ -8982,7 +8982,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G297" t="n">
-        <v>1.39591586589813</v>
+        <v>1.39591562747955</v>
       </c>
       <c r="H297" t="n">
         <v>195070</v>
@@ -9040,7 +9040,7 @@
         <v>2.67199993133545</v>
       </c>
       <c r="G299" t="n">
-        <v>1.63879036903381</v>
+        <v>1.63879024982452</v>
       </c>
       <c r="H299" t="n">
         <v>1636915</v>
@@ -9214,7 +9214,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G305" t="n">
-        <v>1.79825341701508</v>
+        <v>1.79825329780579</v>
       </c>
       <c r="H305" t="n">
         <v>673534</v>
@@ -9243,7 +9243,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G306" t="n">
-        <v>1.75409436225891</v>
+        <v>1.7540944814682</v>
       </c>
       <c r="H306" t="n">
         <v>548849</v>
@@ -9272,7 +9272,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G307" t="n">
-        <v>1.79089367389679</v>
+        <v>1.7908935546875</v>
       </c>
       <c r="H307" t="n">
         <v>670021</v>
@@ -9330,7 +9330,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>1.77862739562988</v>
+        <v>1.7786271572113</v>
       </c>
       <c r="H309" t="n">
         <v>373278</v>
@@ -9359,7 +9359,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G310" t="n">
-        <v>1.79089367389679</v>
+        <v>1.7908935546875</v>
       </c>
       <c r="H310" t="n">
         <v>165055</v>
@@ -9388,7 +9388,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G311" t="n">
-        <v>1.80316007137299</v>
+        <v>1.8031599521637</v>
       </c>
       <c r="H311" t="n">
         <v>257588</v>
@@ -9417,7 +9417,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G312" t="n">
-        <v>1.82523953914642</v>
+        <v>1.82523965835571</v>
       </c>
       <c r="H312" t="n">
         <v>318543</v>
@@ -9446,7 +9446,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G313" t="n">
-        <v>1.95526325702667</v>
+        <v>1.95526337623596</v>
       </c>
       <c r="H313" t="n">
         <v>926523</v>
@@ -9475,7 +9475,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G314" t="n">
-        <v>1.9356369972229</v>
+        <v>1.93563711643219</v>
       </c>
       <c r="H314" t="n">
         <v>1008378</v>
@@ -9504,7 +9504,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G315" t="n">
-        <v>2.01046204566956</v>
+        <v>2.01046228408813</v>
       </c>
       <c r="H315" t="n">
         <v>892554</v>
@@ -9591,7 +9591,7 @@
         <v>3.60199999809265</v>
       </c>
       <c r="G318" t="n">
-        <v>2.20917773246765</v>
+        <v>2.20917797088623</v>
       </c>
       <c r="H318" t="n">
         <v>1002453</v>
@@ -9620,7 +9620,7 @@
         <v>3.75</v>
       </c>
       <c r="G319" t="n">
-        <v>2.29994893074036</v>
+        <v>2.29994916915894</v>
       </c>
       <c r="H319" t="n">
         <v>632837</v>
@@ -9649,7 +9649,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G320" t="n">
-        <v>2.2974956035614</v>
+        <v>2.29749584197998</v>
       </c>
       <c r="H320" t="n">
         <v>576179</v>
@@ -9707,7 +9707,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G322" t="n">
-        <v>2.26805639266968</v>
+        <v>2.2680561542511</v>
       </c>
       <c r="H322" t="n">
         <v>763540</v>
@@ -9823,7 +9823,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G326" t="n">
-        <v>2.2484302520752</v>
+        <v>2.24843001365662</v>
       </c>
       <c r="H326" t="n">
         <v>356043</v>
@@ -9881,7 +9881,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G328" t="n">
-        <v>2.2484302520752</v>
+        <v>2.24843001365662</v>
       </c>
       <c r="H328" t="n">
         <v>167124</v>
@@ -9968,7 +9968,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G331" t="n">
-        <v>2.26805639266968</v>
+        <v>2.2680561542511</v>
       </c>
       <c r="H331" t="n">
         <v>213985</v>
@@ -10200,7 +10200,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G339" t="n">
-        <v>2.72681951522827</v>
+        <v>2.72681975364685</v>
       </c>
       <c r="H339" t="n">
         <v>909516</v>
@@ -10229,7 +10229,7 @@
         <v>4.71799993515015</v>
       </c>
       <c r="G340" t="n">
-        <v>2.89364218711853</v>
+        <v>2.89364242553711</v>
       </c>
       <c r="H340" t="n">
         <v>1367684</v>
@@ -10287,7 +10287,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>2.73540616035461</v>
+        <v>2.73540592193604</v>
       </c>
       <c r="H342" t="n">
         <v>1177654</v>
@@ -10316,7 +10316,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G343" t="n">
-        <v>2.76607203483582</v>
+        <v>2.76607227325439</v>
       </c>
       <c r="H343" t="n">
         <v>487349</v>
@@ -10345,7 +10345,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G344" t="n">
-        <v>2.72927260398865</v>
+        <v>2.72927284240723</v>
       </c>
       <c r="H344" t="n">
         <v>500433</v>
@@ -10403,7 +10403,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G346" t="n">
-        <v>2.90590906143188</v>
+        <v>2.90590882301331</v>
       </c>
       <c r="H346" t="n">
         <v>574193</v>
@@ -10432,7 +10432,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G347" t="n">
-        <v>2.93780112266541</v>
+        <v>2.93780136108398</v>
       </c>
       <c r="H347" t="n">
         <v>302332</v>
@@ -10461,7 +10461,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G348" t="n">
-        <v>2.88996243476868</v>
+        <v>2.88996267318726</v>
       </c>
       <c r="H348" t="n">
         <v>336089</v>
@@ -10490,7 +10490,7 @@
         <v>4.60799980163574</v>
       </c>
       <c r="G349" t="n">
-        <v>2.82617712020874</v>
+        <v>2.82617735862732</v>
       </c>
       <c r="H349" t="n">
         <v>339119</v>
@@ -10548,7 +10548,7 @@
         <v>4.72399997711182</v>
       </c>
       <c r="G351" t="n">
-        <v>2.89732265472412</v>
+        <v>2.89732241630554</v>
       </c>
       <c r="H351" t="n">
         <v>476496</v>
@@ -10606,7 +10606,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G353" t="n">
-        <v>2.79796457290649</v>
+        <v>2.79796433448792</v>
       </c>
       <c r="H353" t="n">
         <v>631744</v>
@@ -10635,7 +10635,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G354" t="n">
-        <v>2.99300050735474</v>
+        <v>2.99300026893616</v>
       </c>
       <c r="H354" t="n">
         <v>1271662</v>
@@ -10693,7 +10693,7 @@
         <v>5.08500003814697</v>
       </c>
       <c r="G356" t="n">
-        <v>3.11873126029968</v>
+        <v>3.1187310218811</v>
       </c>
       <c r="H356" t="n">
         <v>1016304</v>
@@ -10751,7 +10751,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G358" t="n">
-        <v>3.21379542350769</v>
+        <v>3.21379518508911</v>
       </c>
       <c r="H358" t="n">
         <v>471503</v>
@@ -10838,7 +10838,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G361" t="n">
-        <v>3.18619608879089</v>
+        <v>3.18619585037231</v>
       </c>
       <c r="H361" t="n">
         <v>342743</v>
@@ -10896,7 +10896,7 @@
         <v>5.125</v>
       </c>
       <c r="G363" t="n">
-        <v>3.1432638168335</v>
+        <v>3.14326357841492</v>
       </c>
       <c r="H363" t="n">
         <v>592954</v>
@@ -10925,7 +10925,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G364" t="n">
-        <v>3.28432703018188</v>
+        <v>3.28432726860046</v>
       </c>
       <c r="H364" t="n">
         <v>536733</v>
@@ -10954,7 +10954,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G365" t="n">
-        <v>3.18926239013672</v>
+        <v>3.1892626285553</v>
       </c>
       <c r="H365" t="n">
         <v>330140</v>
@@ -11099,7 +11099,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G370" t="n">
-        <v>2.99300050735474</v>
+        <v>2.99300026893616</v>
       </c>
       <c r="H370" t="n">
         <v>709668</v>
@@ -11186,7 +11186,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G373" t="n">
-        <v>3.03470587730408</v>
+        <v>3.03470611572266</v>
       </c>
       <c r="H373" t="n">
         <v>703525</v>
@@ -11389,7 +11389,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G380" t="n">
-        <v>3.18312931060791</v>
+        <v>3.18312954902649</v>
       </c>
       <c r="H380" t="n">
         <v>358113</v>
@@ -11418,7 +11418,7 @@
         <v>4.93400001525879</v>
       </c>
       <c r="G381" t="n">
-        <v>3.02611947059631</v>
+        <v>3.02611970901489</v>
       </c>
       <c r="H381" t="n">
         <v>560077</v>
@@ -11476,7 +11476,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G383" t="n">
-        <v>2.92553520202637</v>
+        <v>2.92553496360779</v>
       </c>
       <c r="H383" t="n">
         <v>468801</v>
@@ -11563,7 +11563,7 @@
         <v>4.5</v>
       </c>
       <c r="G386" t="n">
-        <v>2.75993871688843</v>
+        <v>2.75993895530701</v>
       </c>
       <c r="H386" t="n">
         <v>677082</v>
@@ -11621,7 +11621,7 @@
         <v>4.39799976348877</v>
       </c>
       <c r="G388" t="n">
-        <v>2.69738030433655</v>
+        <v>2.69738006591797</v>
       </c>
       <c r="H388" t="n">
         <v>498795</v>
@@ -11650,7 +11650,7 @@
         <v>4.39799976348877</v>
       </c>
       <c r="G389" t="n">
-        <v>2.69738030433655</v>
+        <v>2.69738006591797</v>
       </c>
       <c r="H389" t="n">
         <v>247421</v>
@@ -11708,7 +11708,7 @@
         <v>4.72399997711182</v>
       </c>
       <c r="G391" t="n">
-        <v>2.89732265472412</v>
+        <v>2.89732241630554</v>
       </c>
       <c r="H391" t="n">
         <v>894334</v>
@@ -11737,7 +11737,7 @@
         <v>4.71799993515015</v>
       </c>
       <c r="G392" t="n">
-        <v>2.89364218711853</v>
+        <v>2.89364242553711</v>
       </c>
       <c r="H392" t="n">
         <v>334494</v>
@@ -11766,7 +11766,7 @@
         <v>4.71799993515015</v>
       </c>
       <c r="G393" t="n">
-        <v>2.89364218711853</v>
+        <v>2.89364242553711</v>
       </c>
       <c r="H393" t="n">
         <v>133281</v>
@@ -11795,7 +11795,7 @@
         <v>4.69199991226196</v>
       </c>
       <c r="G394" t="n">
-        <v>2.87769627571106</v>
+        <v>2.87769603729248</v>
       </c>
       <c r="H394" t="n">
         <v>136890</v>
@@ -11824,7 +11824,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G395" t="n">
-        <v>2.91081523895264</v>
+        <v>2.91081547737122</v>
       </c>
       <c r="H395" t="n">
         <v>1325910</v>
@@ -11882,7 +11882,7 @@
         <v>4.62599992752075</v>
       </c>
       <c r="G397" t="n">
-        <v>2.83721685409546</v>
+        <v>2.83721709251404</v>
       </c>
       <c r="H397" t="n">
         <v>1465113</v>
@@ -11940,7 +11940,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G399" t="n">
-        <v>2.67898058891296</v>
+        <v>2.67898082733154</v>
       </c>
       <c r="H399" t="n">
         <v>762725</v>
@@ -11969,7 +11969,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G400" t="n">
-        <v>2.69860672950745</v>
+        <v>2.69860696792603</v>
       </c>
       <c r="H400" t="n">
         <v>689635</v>
@@ -11998,7 +11998,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G401" t="n">
-        <v>2.62746167182922</v>
+        <v>2.6274619102478</v>
       </c>
       <c r="H401" t="n">
         <v>1387370</v>
@@ -12027,7 +12027,7 @@
         <v>4.47800016403198</v>
       </c>
       <c r="G402" t="n">
-        <v>2.74644589424133</v>
+        <v>2.74644565582275</v>
       </c>
       <c r="H402" t="n">
         <v>1187685</v>
@@ -12114,7 +12114,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G405" t="n">
-        <v>2.62500858306885</v>
+        <v>2.62500882148743</v>
       </c>
       <c r="H405" t="n">
         <v>480173</v>
@@ -12317,7 +12317,7 @@
         <v>4.27400016784668</v>
       </c>
       <c r="G412" t="n">
-        <v>2.62132859230042</v>
+        <v>2.62132883071899</v>
       </c>
       <c r="H412" t="n">
         <v>485494</v>
@@ -12346,7 +12346,7 @@
         <v>4.64799976348877</v>
       </c>
       <c r="G413" t="n">
-        <v>2.85071015357971</v>
+        <v>2.85070991516113</v>
       </c>
       <c r="H413" t="n">
         <v>1542581</v>
@@ -12462,7 +12462,7 @@
         <v>4.60400009155273</v>
       </c>
       <c r="G417" t="n">
-        <v>2.82372403144836</v>
+        <v>2.82372426986694</v>
       </c>
       <c r="H417" t="n">
         <v>268282</v>
@@ -12520,7 +12520,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G419" t="n">
-        <v>2.77588510513306</v>
+        <v>2.77588534355164</v>
       </c>
       <c r="H419" t="n">
         <v>278092</v>
@@ -12549,7 +12549,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G420" t="n">
-        <v>2.73540616035461</v>
+        <v>2.73540592193604</v>
       </c>
       <c r="H420" t="n">
         <v>222228</v>
@@ -12665,7 +12665,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G424" t="n">
-        <v>2.66794109344482</v>
+        <v>2.66794061660767</v>
       </c>
       <c r="H424" t="n">
         <v>323312</v>
@@ -12694,7 +12694,7 @@
         <v>4.24599981307983</v>
       </c>
       <c r="G425" t="n">
-        <v>2.60415554046631</v>
+        <v>2.60415530204773</v>
       </c>
       <c r="H425" t="n">
         <v>469148</v>
@@ -12723,7 +12723,7 @@
         <v>4.23400020599365</v>
       </c>
       <c r="G426" t="n">
-        <v>2.5967960357666</v>
+        <v>2.59679579734802</v>
       </c>
       <c r="H426" t="n">
         <v>653160</v>
@@ -12752,7 +12752,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G427" t="n">
-        <v>2.67898058891296</v>
+        <v>2.67898082733154</v>
       </c>
       <c r="H427" t="n">
         <v>1331409</v>
@@ -12781,7 +12781,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G428" t="n">
-        <v>2.62991499900818</v>
+        <v>2.62991523742676</v>
       </c>
       <c r="H428" t="n">
         <v>528651</v>
@@ -12897,7 +12897,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G432" t="n">
-        <v>2.82740426063538</v>
+        <v>2.8274040222168</v>
       </c>
       <c r="H432" t="n">
         <v>576429</v>
@@ -12926,7 +12926,7 @@
         <v>4.62200021743774</v>
       </c>
       <c r="G433" t="n">
-        <v>2.83476376533508</v>
+        <v>2.83476400375366</v>
       </c>
       <c r="H433" t="n">
         <v>437726</v>
@@ -12955,7 +12955,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G434" t="n">
-        <v>3.05065226554871</v>
+        <v>3.05065250396729</v>
       </c>
       <c r="H434" t="n">
         <v>1204033</v>
@@ -13071,7 +13071,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G438" t="n">
-        <v>3.07273173332214</v>
+        <v>3.07273197174072</v>
       </c>
       <c r="H438" t="n">
         <v>434258</v>
@@ -13100,7 +13100,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G439" t="n">
-        <v>3.17086291313171</v>
+        <v>3.17086315155029</v>
       </c>
       <c r="H439" t="n">
         <v>667518</v>
@@ -13187,7 +13187,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G442" t="n">
-        <v>3.10033130645752</v>
+        <v>3.10033106803894</v>
       </c>
       <c r="H442" t="n">
         <v>607313</v>
@@ -13216,7 +13216,7 @@
         <v>5.03499984741211</v>
       </c>
       <c r="G443" t="n">
-        <v>3.08806490898132</v>
+        <v>3.08806467056274</v>
       </c>
       <c r="H443" t="n">
         <v>178529</v>
@@ -13303,7 +13303,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G446" t="n">
-        <v>3.17699646949768</v>
+        <v>3.1769962310791</v>
       </c>
       <c r="H446" t="n">
         <v>911959</v>
@@ -13361,7 +13361,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>3.15553021430969</v>
+        <v>3.15552997589111</v>
       </c>
       <c r="H448" t="n">
         <v>253394</v>
@@ -13419,7 +13419,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G450" t="n">
-        <v>3.12486386299133</v>
+        <v>3.12486410140991</v>
       </c>
       <c r="H450" t="n">
         <v>232538</v>
@@ -13448,7 +13448,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G451" t="n">
-        <v>3.12486386299133</v>
+        <v>3.12486410140991</v>
       </c>
       <c r="H451" t="n">
         <v>425094</v>
@@ -13506,7 +13506,7 @@
         <v>4.95599985122681</v>
       </c>
       <c r="G453" t="n">
-        <v>3.03961229324341</v>
+        <v>3.03961253166199</v>
       </c>
       <c r="H453" t="n">
         <v>256186</v>
@@ -13593,7 +13593,7 @@
         <v>4.93800020217896</v>
       </c>
       <c r="G456" t="n">
-        <v>3.02857279777527</v>
+        <v>3.02857303619385</v>
       </c>
       <c r="H456" t="n">
         <v>292791</v>
@@ -13622,7 +13622,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G457" t="n">
-        <v>2.99300050735474</v>
+        <v>2.99300026893616</v>
       </c>
       <c r="H457" t="n">
         <v>279277</v>
@@ -13767,7 +13767,7 @@
         <v>4.63199996948242</v>
       </c>
       <c r="G462" t="n">
-        <v>2.84089732170105</v>
+        <v>2.84089708328247</v>
       </c>
       <c r="H462" t="n">
         <v>672804</v>
@@ -13796,7 +13796,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G463" t="n">
-        <v>2.88260245323181</v>
+        <v>2.88260269165039</v>
       </c>
       <c r="H463" t="n">
         <v>389655</v>
@@ -13825,7 +13825,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G464" t="n">
-        <v>2.9010021686554</v>
+        <v>2.90100240707397</v>
       </c>
       <c r="H464" t="n">
         <v>159385</v>
@@ -13854,7 +13854,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G465" t="n">
-        <v>2.90590906143188</v>
+        <v>2.90590882301331</v>
       </c>
       <c r="H465" t="n">
         <v>601976</v>
@@ -13912,7 +13912,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G467" t="n">
-        <v>2.65567445755005</v>
+        <v>2.65567421913147</v>
       </c>
       <c r="H467" t="n">
         <v>2274886</v>
@@ -14086,7 +14086,7 @@
         <v>4.26399993896484</v>
       </c>
       <c r="G473" t="n">
-        <v>2.61519527435303</v>
+        <v>2.61519551277161</v>
       </c>
       <c r="H473" t="n">
         <v>1086537</v>
@@ -14318,7 +14318,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G481" t="n">
-        <v>2.26805639266968</v>
+        <v>2.2680561542511</v>
       </c>
       <c r="H481" t="n">
         <v>919203</v>
@@ -14347,7 +14347,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G482" t="n">
-        <v>2.34165477752686</v>
+        <v>2.34165501594543</v>
       </c>
       <c r="H482" t="n">
         <v>702888</v>
@@ -14376,7 +14376,7 @@
         <v>3.86400008201599</v>
       </c>
       <c r="G483" t="n">
-        <v>2.3698673248291</v>
+        <v>2.36986756324768</v>
       </c>
       <c r="H483" t="n">
         <v>818536</v>
@@ -14434,7 +14434,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G485" t="n">
-        <v>2.49375796318054</v>
+        <v>2.49375820159912</v>
       </c>
       <c r="H485" t="n">
         <v>644388</v>
@@ -14579,7 +14579,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G490" t="n">
-        <v>2.44346570968628</v>
+        <v>2.44346594810486</v>
       </c>
       <c r="H490" t="n">
         <v>829724</v>
@@ -14608,7 +14608,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G491" t="n">
-        <v>2.66794109344482</v>
+        <v>2.66794061660767</v>
       </c>
       <c r="H491" t="n">
         <v>3608976</v>
@@ -14666,7 +14666,7 @@
         <v>4.23199987411499</v>
       </c>
       <c r="G493" t="n">
-        <v>2.59556913375854</v>
+        <v>2.59556889533997</v>
       </c>
       <c r="H493" t="n">
         <v>749802</v>
@@ -14695,7 +14695,7 @@
         <v>4.25600004196167</v>
       </c>
       <c r="G494" t="n">
-        <v>2.61028861999512</v>
+        <v>2.6102888584137</v>
       </c>
       <c r="H494" t="n">
         <v>274888</v>
@@ -14782,7 +14782,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G497" t="n">
-        <v>2.62500858306885</v>
+        <v>2.62500882148743</v>
       </c>
       <c r="H497" t="n">
         <v>426003</v>
@@ -14840,7 +14840,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G499" t="n">
-        <v>2.60047554969788</v>
+        <v>2.6004753112793</v>
       </c>
       <c r="H499" t="n">
         <v>400389</v>
@@ -14927,7 +14927,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G502" t="n">
-        <v>2.33061504364014</v>
+        <v>2.33061480522156</v>
       </c>
       <c r="H502" t="n">
         <v>824177</v>
@@ -14985,7 +14985,7 @@
         <v>3.94799995422363</v>
       </c>
       <c r="G504" t="n">
-        <v>2.42138648033142</v>
+        <v>2.42138624191284</v>
       </c>
       <c r="H504" t="n">
         <v>736965</v>
@@ -15043,7 +15043,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G506" t="n">
-        <v>2.43242597579956</v>
+        <v>2.43242621421814</v>
       </c>
       <c r="H506" t="n">
         <v>463093</v>
@@ -15072,7 +15072,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G507" t="n">
-        <v>2.47903823852539</v>
+        <v>2.47903847694397</v>
       </c>
       <c r="H507" t="n">
         <v>419637</v>
@@ -15130,7 +15130,7 @@
         <v>3.97399997711182</v>
       </c>
       <c r="G509" t="n">
-        <v>2.43733239173889</v>
+        <v>2.43733263015747</v>
       </c>
       <c r="H509" t="n">
         <v>229193</v>
@@ -15188,7 +15188,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G511" t="n">
-        <v>2.45941233634949</v>
+        <v>2.45941209793091</v>
       </c>
       <c r="H511" t="n">
         <v>303747</v>
@@ -15275,7 +15275,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G514" t="n">
-        <v>2.54527711868286</v>
+        <v>2.54527688026428</v>
       </c>
       <c r="H514" t="n">
         <v>532337</v>
@@ -15304,7 +15304,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G515" t="n">
-        <v>2.54527711868286</v>
+        <v>2.54527688026428</v>
       </c>
       <c r="H515" t="n">
         <v>252816</v>
@@ -15478,7 +15478,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G521" t="n">
-        <v>2.62991499900818</v>
+        <v>2.62991523742676</v>
       </c>
       <c r="H521" t="n">
         <v>220252</v>
@@ -15507,7 +15507,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G522" t="n">
-        <v>2.62746167182922</v>
+        <v>2.6274619102478</v>
       </c>
       <c r="H522" t="n">
         <v>284746</v>
@@ -15536,7 +15536,7 @@
         <v>4.21799993515015</v>
       </c>
       <c r="G523" t="n">
-        <v>2.5869824886322</v>
+        <v>2.58698272705078</v>
       </c>
       <c r="H523" t="n">
         <v>348275</v>
@@ -15594,7 +15594,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G525" t="n">
-        <v>2.64954113960266</v>
+        <v>2.64954137802124</v>
       </c>
       <c r="H525" t="n">
         <v>531029</v>
@@ -15623,7 +15623,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G526" t="n">
-        <v>2.64954113960266</v>
+        <v>2.64954137802124</v>
       </c>
       <c r="H526" t="n">
         <v>459494</v>
@@ -15652,7 +15652,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G527" t="n">
-        <v>2.65567445755005</v>
+        <v>2.65567421913147</v>
       </c>
       <c r="H527" t="n">
         <v>263721</v>
@@ -15681,7 +15681,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G528" t="n">
-        <v>2.59311604499817</v>
+        <v>2.59311580657959</v>
       </c>
       <c r="H528" t="n">
         <v>277825</v>
@@ -15768,7 +15768,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G531" t="n">
-        <v>2.60047554969788</v>
+        <v>2.6004753112793</v>
       </c>
       <c r="H531" t="n">
         <v>368114</v>
@@ -15826,7 +15826,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G533" t="n">
-        <v>2.46799874305725</v>
+        <v>2.46799850463867</v>
       </c>
       <c r="H533" t="n">
         <v>422014</v>
@@ -15884,7 +15884,7 @@
         <v>3.86400008201599</v>
       </c>
       <c r="G535" t="n">
-        <v>2.3698673248291</v>
+        <v>2.36986756324768</v>
       </c>
       <c r="H535" t="n">
         <v>527548</v>
@@ -15913,7 +15913,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G536" t="n">
-        <v>2.32325530052185</v>
+        <v>2.32325506210327</v>
       </c>
       <c r="H536" t="n">
         <v>672319</v>
@@ -15942,7 +15942,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G537" t="n">
-        <v>2.35269451141357</v>
+        <v>2.35269474983215</v>
       </c>
       <c r="H537" t="n">
         <v>708296</v>
@@ -16058,7 +16058,7 @@
         <v>3.60599994659424</v>
       </c>
       <c r="G541" t="n">
-        <v>2.21163082122803</v>
+        <v>2.21163105964661</v>
       </c>
       <c r="H541" t="n">
         <v>539338</v>
@@ -16087,7 +16087,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G542" t="n">
-        <v>2.18341827392578</v>
+        <v>2.1834180355072</v>
       </c>
       <c r="H542" t="n">
         <v>383193</v>
@@ -16116,7 +16116,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G543" t="n">
-        <v>2.32325530052185</v>
+        <v>2.32325506210327</v>
       </c>
       <c r="H543" t="n">
         <v>618299</v>
@@ -16145,7 +16145,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G544" t="n">
-        <v>2.27541613578796</v>
+        <v>2.27541637420654</v>
       </c>
       <c r="H544" t="n">
         <v>202220</v>
@@ -16261,7 +16261,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G548" t="n">
-        <v>2.28400254249573</v>
+        <v>2.28400278091431</v>
       </c>
       <c r="H548" t="n">
         <v>586919</v>
@@ -16290,7 +16290,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G549" t="n">
-        <v>2.33061504364014</v>
+        <v>2.33061480522156</v>
       </c>
       <c r="H549" t="n">
         <v>1543552</v>
@@ -16319,7 +16319,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G550" t="n">
-        <v>2.24965691566467</v>
+        <v>2.24965667724609</v>
       </c>
       <c r="H550" t="n">
         <v>1786585</v>
@@ -16406,7 +16406,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G553" t="n">
-        <v>2.03008818626404</v>
+        <v>2.03008842468262</v>
       </c>
       <c r="H553" t="n">
         <v>1306281</v>
@@ -16464,7 +16464,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G555" t="n">
-        <v>1.90129113197327</v>
+        <v>1.90129125118256</v>
       </c>
       <c r="H555" t="n">
         <v>1443403</v>
@@ -16493,7 +16493,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G556" t="n">
-        <v>1.84609246253967</v>
+        <v>1.84609234333038</v>
       </c>
       <c r="H556" t="n">
         <v>675663</v>
@@ -16609,7 +16609,7 @@
         <v>3.11800003051758</v>
       </c>
       <c r="G560" t="n">
-        <v>1.91233098506927</v>
+        <v>1.91233086585999</v>
       </c>
       <c r="H560" t="n">
         <v>430921</v>
@@ -16638,7 +16638,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G561" t="n">
-        <v>1.84609246253967</v>
+        <v>1.84609234333038</v>
       </c>
       <c r="H561" t="n">
         <v>656155</v>
@@ -16696,7 +16696,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G563" t="n">
-        <v>1.87798500061035</v>
+        <v>1.87798523902893</v>
       </c>
       <c r="H563" t="n">
         <v>1003231</v>
@@ -16783,7 +16783,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G566" t="n">
-        <v>1.86571872234344</v>
+        <v>1.86571860313416</v>
       </c>
       <c r="H566" t="n">
         <v>421960</v>
@@ -16812,7 +16812,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G567" t="n">
-        <v>1.90129113197327</v>
+        <v>1.90129125118256</v>
       </c>
       <c r="H567" t="n">
         <v>594160</v>
@@ -16841,7 +16841,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G568" t="n">
-        <v>1.98715591430664</v>
+        <v>1.98715579509735</v>
       </c>
       <c r="H568" t="n">
         <v>1455013</v>
@@ -16899,7 +16899,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G570" t="n">
-        <v>1.86571872234344</v>
+        <v>1.86571860313416</v>
       </c>
       <c r="H570" t="n">
         <v>810989</v>
@@ -16928,7 +16928,7 @@
         <v>3.08200001716614</v>
       </c>
       <c r="G571" t="n">
-        <v>1.89025139808655</v>
+        <v>1.89025151729584</v>
       </c>
       <c r="H571" t="n">
         <v>528910</v>
@@ -16957,7 +16957,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G572" t="n">
-        <v>1.88657140731812</v>
+        <v>1.8865715265274</v>
       </c>
       <c r="H572" t="n">
         <v>885470</v>
@@ -17102,7 +17102,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G577" t="n">
-        <v>1.92091739177704</v>
+        <v>1.92091727256775</v>
       </c>
       <c r="H577" t="n">
         <v>1128337</v>
@@ -17131,7 +17131,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G578" t="n">
-        <v>1.95648992061615</v>
+        <v>1.95649003982544</v>
       </c>
       <c r="H578" t="n">
         <v>584408</v>
@@ -17160,7 +17160,7 @@
         <v>3.12800002098083</v>
       </c>
       <c r="G579" t="n">
-        <v>1.91846430301666</v>
+        <v>1.91846418380737</v>
       </c>
       <c r="H579" t="n">
         <v>655396</v>
@@ -17218,7 +17218,7 @@
         <v>3.11800003051758</v>
       </c>
       <c r="G581" t="n">
-        <v>1.91233098506927</v>
+        <v>1.91233086585999</v>
       </c>
       <c r="H581" t="n">
         <v>350643</v>
@@ -17247,7 +17247,7 @@
         <v>3.14800000190735</v>
       </c>
       <c r="G582" t="n">
-        <v>1.93073058128357</v>
+        <v>1.93073046207428</v>
       </c>
       <c r="H582" t="n">
         <v>436681</v>
@@ -17305,7 +17305,7 @@
         <v>3.32399988174438</v>
       </c>
       <c r="G584" t="n">
-        <v>2.03867483139038</v>
+        <v>2.0386745929718</v>
       </c>
       <c r="H584" t="n">
         <v>692299</v>
@@ -17334,7 +17334,7 @@
         <v>3.37199997901917</v>
       </c>
       <c r="G585" t="n">
-        <v>2.0681140422821</v>
+        <v>2.06811428070068</v>
       </c>
       <c r="H585" t="n">
         <v>393469</v>
@@ -17392,7 +17392,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G587" t="n">
-        <v>1.99083590507507</v>
+        <v>1.99083578586578</v>
       </c>
       <c r="H587" t="n">
         <v>459538</v>
@@ -17421,7 +17421,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G588" t="n">
-        <v>1.96262323856354</v>
+        <v>1.96262311935425</v>
       </c>
       <c r="H588" t="n">
         <v>478776</v>
@@ -17450,7 +17450,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G589" t="n">
-        <v>2.03008818626404</v>
+        <v>2.03008842468262</v>
       </c>
       <c r="H589" t="n">
         <v>1065238</v>
@@ -17508,7 +17508,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G591" t="n">
-        <v>1.9712096452713</v>
+        <v>1.97120976448059</v>
       </c>
       <c r="H591" t="n">
         <v>772312</v>
@@ -17537,7 +17537,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G592" t="n">
-        <v>1.97488963603973</v>
+        <v>1.97488951683044</v>
       </c>
       <c r="H592" t="n">
         <v>412074</v>
@@ -17798,7 +17798,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G601" t="n">
-        <v>1.9712096452713</v>
+        <v>1.97120976448059</v>
       </c>
       <c r="H601" t="n">
         <v>1259936</v>
@@ -17827,7 +17827,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G602" t="n">
-        <v>1.96016991138458</v>
+        <v>1.96017003059387</v>
       </c>
       <c r="H602" t="n">
         <v>1065883</v>
@@ -17914,7 +17914,7 @@
         <v>3.08200001716614</v>
       </c>
       <c r="G605" t="n">
-        <v>1.89025139808655</v>
+        <v>1.89025151729584</v>
       </c>
       <c r="H605" t="n">
         <v>380241</v>
@@ -17972,7 +17972,7 @@
         <v>3.10599994659424</v>
       </c>
       <c r="G607" t="n">
-        <v>1.90497088432312</v>
+        <v>1.90497100353241</v>
       </c>
       <c r="H607" t="n">
         <v>240955</v>
@@ -18001,7 +18001,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G608" t="n">
-        <v>1.88411831855774</v>
+        <v>1.88411819934845</v>
       </c>
       <c r="H608" t="n">
         <v>255709</v>
@@ -18030,7 +18030,7 @@
         <v>3.13599991798401</v>
       </c>
       <c r="G609" t="n">
-        <v>1.92337071895599</v>
+        <v>1.9233705997467</v>
       </c>
       <c r="H609" t="n">
         <v>161247</v>
@@ -18059,7 +18059,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G610" t="n">
-        <v>1.89515805244446</v>
+        <v>1.89515793323517</v>
       </c>
       <c r="H610" t="n">
         <v>327212</v>
@@ -18204,7 +18204,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G615" t="n">
-        <v>1.741828083992</v>
+        <v>1.74182796478271</v>
       </c>
       <c r="H615" t="n">
         <v>919236</v>
@@ -18233,7 +18233,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G616" t="n">
-        <v>1.7663608789444</v>
+        <v>1.76636075973511</v>
       </c>
       <c r="H616" t="n">
         <v>727846</v>
@@ -18262,7 +18262,7 @@
         <v>3.05599999427795</v>
       </c>
       <c r="G617" t="n">
-        <v>1.87430512905121</v>
+        <v>1.8743052482605</v>
       </c>
       <c r="H617" t="n">
         <v>883535</v>
@@ -18291,7 +18291,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G618" t="n">
-        <v>1.86939871311188</v>
+        <v>1.86939883232117</v>
       </c>
       <c r="H618" t="n">
         <v>268999</v>
@@ -18320,7 +18320,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G619" t="n">
-        <v>1.87307846546173</v>
+        <v>1.87307858467102</v>
       </c>
       <c r="H619" t="n">
         <v>336325</v>
@@ -18407,7 +18407,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G622" t="n">
-        <v>1.82155954837799</v>
+        <v>1.82155966758728</v>
       </c>
       <c r="H622" t="n">
         <v>562723</v>
@@ -18436,7 +18436,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G623" t="n">
-        <v>1.84609246253967</v>
+        <v>1.84609234333038</v>
       </c>
       <c r="H623" t="n">
         <v>249537</v>
@@ -18494,7 +18494,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G625" t="n">
-        <v>1.84609246253967</v>
+        <v>1.84609234333038</v>
       </c>
       <c r="H625" t="n">
         <v>286623</v>
@@ -18581,7 +18581,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G628" t="n">
-        <v>1.80316007137299</v>
+        <v>1.8031599521637</v>
       </c>
       <c r="H628" t="n">
         <v>337726</v>
@@ -18639,7 +18639,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G630" t="n">
-        <v>1.80193340778351</v>
+        <v>1.80193328857422</v>
       </c>
       <c r="H630" t="n">
         <v>413305</v>
@@ -18755,7 +18755,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G634" t="n">
-        <v>1.63756382465363</v>
+        <v>1.63756370544434</v>
       </c>
       <c r="H634" t="n">
         <v>381605</v>
@@ -18900,7 +18900,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G639" t="n">
-        <v>1.55169880390167</v>
+        <v>1.55169904232025</v>
       </c>
       <c r="H639" t="n">
         <v>341019</v>
@@ -18958,7 +18958,7 @@
         <v>2.68600010871887</v>
       </c>
       <c r="G641" t="n">
-        <v>1.64737677574158</v>
+        <v>1.64737689495087</v>
       </c>
       <c r="H641" t="n">
         <v>510074</v>
@@ -18987,7 +18987,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G642" t="n">
-        <v>1.63143038749695</v>
+        <v>1.63143050670624</v>
       </c>
       <c r="H642" t="n">
         <v>142464</v>
@@ -19016,7 +19016,7 @@
         <v>2.75799989700317</v>
       </c>
       <c r="G643" t="n">
-        <v>1.69153571128845</v>
+        <v>1.69153583049774</v>
       </c>
       <c r="H643" t="n">
         <v>185397</v>
@@ -19045,7 +19045,7 @@
         <v>2.74200010299683</v>
       </c>
       <c r="G644" t="n">
-        <v>1.6817227602005</v>
+        <v>1.68172287940979</v>
       </c>
       <c r="H644" t="n">
         <v>253790</v>
@@ -19074,7 +19074,7 @@
         <v>2.66400003433228</v>
       </c>
       <c r="G645" t="n">
-        <v>1.63388383388519</v>
+        <v>1.6338837146759</v>
       </c>
       <c r="H645" t="n">
         <v>200083</v>
@@ -19103,7 +19103,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G646" t="n">
-        <v>1.60567116737366</v>
+        <v>1.60567104816437</v>
       </c>
       <c r="H646" t="n">
         <v>247013</v>
@@ -19161,7 +19161,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G648" t="n">
-        <v>1.57377851009369</v>
+        <v>1.5737783908844</v>
       </c>
       <c r="H648" t="n">
         <v>104635</v>
@@ -19248,7 +19248,7 @@
         <v>2.78600001335144</v>
       </c>
       <c r="G651" t="n">
-        <v>1.70870864391327</v>
+        <v>1.70870876312256</v>
       </c>
       <c r="H651" t="n">
         <v>182007</v>
@@ -19277,7 +19277,7 @@
         <v>2.71399998664856</v>
       </c>
       <c r="G652" t="n">
-        <v>1.66454970836639</v>
+        <v>1.66454982757568</v>
       </c>
       <c r="H652" t="n">
         <v>684291</v>
@@ -19306,7 +19306,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G653" t="n">
-        <v>1.63143038749695</v>
+        <v>1.63143050670624</v>
       </c>
       <c r="H653" t="n">
         <v>134571</v>
@@ -19422,7 +19422,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G657" t="n">
-        <v>1.30637121200562</v>
+        <v>1.30637109279633</v>
       </c>
       <c r="H657" t="n">
         <v>948766</v>
@@ -19480,7 +19480,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G659" t="n">
-        <v>1.30637121200562</v>
+        <v>1.30637109279633</v>
       </c>
       <c r="H659" t="n">
         <v>629454</v>
@@ -19683,7 +19683,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G666" t="n">
-        <v>1.25853216648102</v>
+        <v>1.25853204727173</v>
       </c>
       <c r="H666" t="n">
         <v>514664</v>
@@ -19712,7 +19712,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G667" t="n">
-        <v>1.23645269870758</v>
+        <v>1.23645257949829</v>
       </c>
       <c r="H667" t="n">
         <v>462440</v>
@@ -19741,7 +19741,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G668" t="n">
-        <v>1.20946645736694</v>
+        <v>1.20946657657623</v>
       </c>
       <c r="H668" t="n">
         <v>265562</v>
@@ -19770,7 +19770,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G669" t="n">
-        <v>1.20517337322235</v>
+        <v>1.20517325401306</v>
       </c>
       <c r="H669" t="n">
         <v>337600</v>
@@ -19886,7 +19886,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G673" t="n">
-        <v>1.28551805019379</v>
+        <v>1.28551816940308</v>
       </c>
       <c r="H673" t="n">
         <v>372684</v>
@@ -19973,7 +19973,7 @@
         <v>2.00399994850159</v>
       </c>
       <c r="G676" t="n">
-        <v>1.22909271717072</v>
+        <v>1.22909259796143</v>
       </c>
       <c r="H676" t="n">
         <v>261133</v>
@@ -20147,7 +20147,7 @@
         <v>2.04800009727478</v>
       </c>
       <c r="G682" t="n">
-        <v>1.25607895851135</v>
+        <v>1.25607883930206</v>
       </c>
       <c r="H682" t="n">
         <v>281162</v>
@@ -20176,7 +20176,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G683" t="n">
-        <v>1.22602605819702</v>
+        <v>1.22602617740631</v>
       </c>
       <c r="H683" t="n">
         <v>474792</v>
@@ -20234,7 +20234,7 @@
         <v>2.00399994850159</v>
       </c>
       <c r="G685" t="n">
-        <v>1.22909271717072</v>
+        <v>1.22909259796143</v>
       </c>
       <c r="H685" t="n">
         <v>716738</v>
@@ -20263,7 +20263,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G686" t="n">
-        <v>1.24503898620605</v>
+        <v>1.24503910541534</v>
       </c>
       <c r="H686" t="n">
         <v>484546</v>
@@ -20292,7 +20292,7 @@
         <v>2</v>
       </c>
       <c r="G687" t="n">
-        <v>1.22663950920105</v>
+        <v>1.22663938999176</v>
       </c>
       <c r="H687" t="n">
         <v>624287</v>
@@ -20350,7 +20350,7 @@
         <v>1.98300004005432</v>
       </c>
       <c r="G689" t="n">
-        <v>1.21621298789978</v>
+        <v>1.21621310710907</v>
       </c>
       <c r="H689" t="n">
         <v>330913</v>
@@ -20408,7 +20408,7 @@
         <v>2</v>
       </c>
       <c r="G691" t="n">
-        <v>1.22663950920105</v>
+        <v>1.22663938999176</v>
       </c>
       <c r="H691" t="n">
         <v>605384</v>
@@ -20437,7 +20437,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G692" t="n">
-        <v>1.24381244182587</v>
+        <v>1.24381256103516</v>
       </c>
       <c r="H692" t="n">
         <v>607664</v>
@@ -20466,7 +20466,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G693" t="n">
-        <v>1.24381244182587</v>
+        <v>1.24381256103516</v>
       </c>
       <c r="H693" t="n">
         <v>615775</v>
@@ -20524,7 +20524,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G695" t="n">
-        <v>1.29533123970032</v>
+        <v>1.29533135890961</v>
       </c>
       <c r="H695" t="n">
         <v>1501497</v>
@@ -20582,7 +20582,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G697" t="n">
-        <v>1.30023777484894</v>
+        <v>1.30023765563965</v>
       </c>
       <c r="H697" t="n">
         <v>729989</v>
@@ -20611,7 +20611,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G698" t="n">
-        <v>1.24381244182587</v>
+        <v>1.24381256103516</v>
       </c>
       <c r="H698" t="n">
         <v>965266</v>
@@ -20756,7 +20756,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G703" t="n">
-        <v>1.17389392852783</v>
+        <v>1.17389404773712</v>
       </c>
       <c r="H703" t="n">
         <v>1026206</v>
@@ -20814,7 +20814,7 @@
         <v>1.92299997806549</v>
       </c>
       <c r="G705" t="n">
-        <v>1.17941379547119</v>
+        <v>1.17941391468048</v>
       </c>
       <c r="H705" t="n">
         <v>288525</v>
@@ -20901,7 +20901,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G708" t="n">
-        <v>1.08434927463531</v>
+        <v>1.0843493938446</v>
       </c>
       <c r="H708" t="n">
         <v>456610</v>
@@ -20930,7 +20930,7 @@
         <v>1.7389999628067</v>
       </c>
       <c r="G709" t="n">
-        <v>1.06656301021576</v>
+        <v>1.06656289100647</v>
       </c>
       <c r="H709" t="n">
         <v>332239</v>
@@ -20988,7 +20988,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G711" t="n">
-        <v>1.05552315711975</v>
+        <v>1.05552327632904</v>
       </c>
       <c r="H711" t="n">
         <v>442171</v>
@@ -21046,7 +21046,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G713" t="n">
-        <v>1.05797648429871</v>
+        <v>1.057976603508</v>
       </c>
       <c r="H713" t="n">
         <v>478442</v>
@@ -21162,7 +21162,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G717" t="n">
-        <v>0.984991490840912</v>
+        <v>0.984991431236267</v>
       </c>
       <c r="H717" t="n">
         <v>776455</v>
@@ -21191,7 +21191,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G718" t="n">
-        <v>0.910779774188995</v>
+        <v>0.91077983379364</v>
       </c>
       <c r="H718" t="n">
         <v>847433</v>
@@ -21249,7 +21249,7 @@
         <v>1.5110000371933</v>
       </c>
       <c r="G720" t="n">
-        <v>0.926726102828979</v>
+        <v>0.926726222038269</v>
       </c>
       <c r="H720" t="n">
         <v>609534</v>
@@ -21278,7 +21278,7 @@
         <v>1.49399995803833</v>
       </c>
       <c r="G721" t="n">
-        <v>0.916299641132355</v>
+        <v>0.916299700737</v>
       </c>
       <c r="H721" t="n">
         <v>519573</v>
@@ -21307,7 +21307,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G722" t="n">
-        <v>0.951258897781372</v>
+        <v>0.951258957386017</v>
       </c>
       <c r="H722" t="n">
         <v>878851</v>
@@ -21365,7 +21365,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G724" t="n">
-        <v>0.965365290641785</v>
+        <v>0.96536523103714</v>
       </c>
       <c r="H724" t="n">
         <v>453862</v>
@@ -21423,7 +21423,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G726" t="n">
-        <v>0.980084955692291</v>
+        <v>0.980085015296936</v>
       </c>
       <c r="H726" t="n">
         <v>625242</v>
@@ -21452,7 +21452,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G727" t="n">
-        <v>0.958618700504303</v>
+        <v>0.958618640899658</v>
       </c>
       <c r="H727" t="n">
         <v>253732</v>
@@ -21481,7 +21481,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G728" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H728" t="n">
         <v>546391</v>
@@ -21539,7 +21539,7 @@
         <v>1.57200002670288</v>
       </c>
       <c r="G730" t="n">
-        <v>0.964138627052307</v>
+        <v>0.964138567447662</v>
       </c>
       <c r="H730" t="n">
         <v>464016</v>
@@ -21568,7 +21568,7 @@
         <v>1.53299999237061</v>
       </c>
       <c r="G731" t="n">
-        <v>0.940219223499298</v>
+        <v>0.940219163894653</v>
       </c>
       <c r="H731" t="n">
         <v>257158</v>
@@ -21626,7 +21626,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G733" t="n">
-        <v>0.904646575450897</v>
+        <v>0.904646635055542</v>
       </c>
       <c r="H733" t="n">
         <v>613085</v>
@@ -21684,7 +21684,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G735" t="n">
-        <v>0.924886167049408</v>
+        <v>0.924886226654053</v>
       </c>
       <c r="H735" t="n">
         <v>327275</v>
@@ -21713,7 +21713,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G736" t="n">
-        <v>0.895446836948395</v>
+        <v>0.89544677734375</v>
       </c>
       <c r="H736" t="n">
         <v>253922</v>
@@ -21742,7 +21742,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G737" t="n">
-        <v>0.902193248271942</v>
+        <v>0.902193307876587</v>
       </c>
       <c r="H737" t="n">
         <v>134126</v>
@@ -21771,7 +21771,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G738" t="n">
-        <v>0.867847442626953</v>
+        <v>0.867847383022308</v>
       </c>
       <c r="H738" t="n">
         <v>252282</v>
@@ -21800,7 +21800,7 @@
         <v>1.44400000572205</v>
       </c>
       <c r="G739" t="n">
-        <v>0.885633647441864</v>
+        <v>0.885633707046509</v>
       </c>
       <c r="H739" t="n">
         <v>529303</v>
@@ -21829,7 +21829,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G740" t="n">
-        <v>0.875820517539978</v>
+        <v>0.875820577144623</v>
       </c>
       <c r="H740" t="n">
         <v>327146</v>
@@ -21858,7 +21858,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G741" t="n">
-        <v>0.884407103061676</v>
+        <v>0.884407043457031</v>
       </c>
       <c r="H741" t="n">
         <v>275350</v>
@@ -21887,7 +21887,7 @@
         <v>1.53299999237061</v>
       </c>
       <c r="G742" t="n">
-        <v>0.940219223499298</v>
+        <v>0.940219163894653</v>
       </c>
       <c r="H742" t="n">
         <v>982055</v>
@@ -21945,7 +21945,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G744" t="n">
-        <v>0.944512367248535</v>
+        <v>0.94451242685318</v>
       </c>
       <c r="H744" t="n">
         <v>249172</v>
@@ -22003,7 +22003,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G746" t="n">
-        <v>0.938379108905792</v>
+        <v>0.938379287719727</v>
       </c>
       <c r="H746" t="n">
         <v>1898728</v>
@@ -22061,7 +22061,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G748" t="n">
-        <v>0.956165492534637</v>
+        <v>0.956165432929993</v>
       </c>
       <c r="H748" t="n">
         <v>267818</v>
@@ -22090,7 +22090,7 @@
         <v>1.557000041008</v>
       </c>
       <c r="G749" t="n">
-        <v>0.95493882894516</v>
+        <v>0.954938769340515</v>
       </c>
       <c r="H749" t="n">
         <v>131447</v>
@@ -22119,7 +22119,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G750" t="n">
-        <v>0.901580035686493</v>
+        <v>0.901579976081848</v>
       </c>
       <c r="H750" t="n">
         <v>663241</v>
@@ -22177,7 +22177,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G752" t="n">
-        <v>0.870914041996002</v>
+        <v>0.870913982391357</v>
       </c>
       <c r="H752" t="n">
         <v>372259</v>
@@ -22235,7 +22235,7 @@
         <v>1.48699998855591</v>
       </c>
       <c r="G754" t="n">
-        <v>0.912006437778473</v>
+        <v>0.912006497383118</v>
       </c>
       <c r="H754" t="n">
         <v>459581</v>
@@ -22293,7 +22293,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G756" t="n">
-        <v>0.859874188899994</v>
+        <v>0.859874248504639</v>
       </c>
       <c r="H756" t="n">
         <v>508033</v>
@@ -22322,7 +22322,7 @@
         <v>1.37899994850159</v>
       </c>
       <c r="G757" t="n">
-        <v>0.845767855644226</v>
+        <v>0.845767915248871</v>
       </c>
       <c r="H757" t="n">
         <v>507600</v>
@@ -22351,7 +22351,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G758" t="n">
-        <v>0.837181448936462</v>
+        <v>0.837181389331818</v>
       </c>
       <c r="H758" t="n">
         <v>234713</v>
@@ -22380,7 +22380,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G759" t="n">
-        <v>0.849447846412659</v>
+        <v>0.849447786808014</v>
       </c>
       <c r="H759" t="n">
         <v>349314</v>
@@ -22409,7 +22409,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G760" t="n">
-        <v>0.837181448936462</v>
+        <v>0.837181389331818</v>
       </c>
       <c r="H760" t="n">
         <v>270071</v>
@@ -22496,7 +22496,7 @@
         <v>1.43099999427795</v>
       </c>
       <c r="G763" t="n">
-        <v>0.877660632133484</v>
+        <v>0.877660572528839</v>
       </c>
       <c r="H763" t="n">
         <v>76251</v>
@@ -22525,7 +22525,7 @@
         <v>1.45700001716614</v>
       </c>
       <c r="G764" t="n">
-        <v>0.893606841564178</v>
+        <v>0.893606901168823</v>
       </c>
       <c r="H764" t="n">
         <v>309417</v>
@@ -22554,7 +22554,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G765" t="n">
-        <v>0.911393165588379</v>
+        <v>0.911393046379089</v>
       </c>
       <c r="H765" t="n">
         <v>318206</v>
@@ -22612,7 +22612,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G767" t="n">
-        <v>0.951258897781372</v>
+        <v>0.951258957386017</v>
       </c>
       <c r="H767" t="n">
         <v>303463</v>
@@ -22641,7 +22641,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G768" t="n">
-        <v>0.951872289180756</v>
+        <v>0.951872229576111</v>
       </c>
       <c r="H768" t="n">
         <v>554719</v>
@@ -22670,7 +22670,7 @@
         <v>1.60699999332428</v>
       </c>
       <c r="G769" t="n">
-        <v>0.985604822635651</v>
+        <v>0.985604882240295</v>
       </c>
       <c r="H769" t="n">
         <v>1218675</v>
@@ -22699,7 +22699,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G770" t="n">
-        <v>0.987444818019867</v>
+        <v>0.987444758415222</v>
       </c>
       <c r="H770" t="n">
         <v>399379</v>
@@ -22786,7 +22786,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G773" t="n">
-        <v>0.944512367248535</v>
+        <v>0.94451242685318</v>
       </c>
       <c r="H773" t="n">
         <v>246426</v>
@@ -22873,7 +22873,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G776" t="n">
-        <v>0.99357795715332</v>
+        <v>0.993577897548676</v>
       </c>
       <c r="H776" t="n">
         <v>368874</v>
@@ -22902,7 +22902,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G777" t="n">
-        <v>0.986218094825745</v>
+        <v>0.986218154430389</v>
       </c>
       <c r="H777" t="n">
         <v>142894</v>
@@ -22931,7 +22931,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G778" t="n">
-        <v>0.940832495689392</v>
+        <v>0.940832555294037</v>
       </c>
       <c r="H778" t="n">
         <v>302240</v>
@@ -22960,7 +22960,7 @@
         <v>1.5</v>
       </c>
       <c r="G779" t="n">
-        <v>0.919979631900787</v>
+        <v>0.919979512691498</v>
       </c>
       <c r="H779" t="n">
         <v>307567</v>
@@ -23018,7 +23018,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G781" t="n">
-        <v>0.984991490840912</v>
+        <v>0.984991431236267</v>
       </c>
       <c r="H781" t="n">
         <v>583532</v>
@@ -23105,7 +23105,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G784" t="n">
-        <v>1.06472301483154</v>
+        <v>1.06472289562225</v>
       </c>
       <c r="H784" t="n">
         <v>414554</v>
@@ -23221,7 +23221,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G788" t="n">
-        <v>1.03221714496613</v>
+        <v>1.03221702575684</v>
       </c>
       <c r="H788" t="n">
         <v>548765</v>
@@ -23250,7 +23250,7 @@
         <v>1.7039999961853</v>
       </c>
       <c r="G789" t="n">
-        <v>1.04509675502777</v>
+        <v>1.04509687423706</v>
       </c>
       <c r="H789" t="n">
         <v>244962</v>
@@ -23308,7 +23308,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G791" t="n">
-        <v>0.972111761569977</v>
+        <v>0.972111880779266</v>
       </c>
       <c r="H791" t="n">
         <v>381336</v>
@@ -23337,7 +23337,7 @@
         <v>1.59700000286102</v>
       </c>
       <c r="G792" t="n">
-        <v>0.979471623897552</v>
+        <v>0.979471564292908</v>
       </c>
       <c r="H792" t="n">
         <v>263430</v>
@@ -23424,7 +23424,7 @@
         <v>1.71300005912781</v>
       </c>
       <c r="G795" t="n">
-        <v>1.05061662197113</v>
+        <v>1.05061674118042</v>
       </c>
       <c r="H795" t="n">
         <v>186136</v>
@@ -23482,7 +23482,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G797" t="n">
-        <v>1.05552315711975</v>
+        <v>1.05552327632904</v>
       </c>
       <c r="H797" t="n">
         <v>145140</v>
@@ -23714,7 +23714,7 @@
         <v>1.56700003147125</v>
       </c>
       <c r="G805" t="n">
-        <v>0.961072027683258</v>
+        <v>0.961071968078613</v>
       </c>
       <c r="H805" t="n">
         <v>514716</v>
@@ -23859,7 +23859,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G810" t="n">
-        <v>0.92120623588562</v>
+        <v>0.921206176280975</v>
       </c>
       <c r="H810" t="n">
         <v>897101</v>
@@ -23917,7 +23917,7 @@
         <v>1.49399995803833</v>
       </c>
       <c r="G812" t="n">
-        <v>0.916299641132355</v>
+        <v>0.916299700737</v>
       </c>
       <c r="H812" t="n">
         <v>389992</v>
@@ -24004,7 +24004,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G815" t="n">
-        <v>0.928566098213196</v>
+        <v>0.928566157817841</v>
       </c>
       <c r="H815" t="n">
         <v>528078</v>
@@ -24033,7 +24033,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G816" t="n">
-        <v>0.923046231269836</v>
+        <v>0.923046171665192</v>
       </c>
       <c r="H816" t="n">
         <v>409925</v>
@@ -24062,7 +24062,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G817" t="n">
-        <v>0.926112771034241</v>
+        <v>0.92611289024353</v>
       </c>
       <c r="H817" t="n">
         <v>331576</v>
@@ -24091,7 +24091,7 @@
         <v>1.54100000858307</v>
       </c>
       <c r="G818" t="n">
-        <v>0.945125699043274</v>
+        <v>0.945125758647919</v>
       </c>
       <c r="H818" t="n">
         <v>478848</v>
@@ -24207,7 +24207,7 @@
         <v>1.47300004959106</v>
       </c>
       <c r="G822" t="n">
-        <v>0.903420031070709</v>
+        <v>0.903419971466064</v>
       </c>
       <c r="H822" t="n">
         <v>526975</v>
@@ -24236,7 +24236,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G823" t="n">
-        <v>0.899126708507538</v>
+        <v>0.899126648902893</v>
       </c>
       <c r="H823" t="n">
         <v>347418</v>
@@ -24381,7 +24381,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G828" t="n">
-        <v>0.960458695888519</v>
+        <v>0.960458636283875</v>
       </c>
       <c r="H828" t="n">
         <v>496001</v>
@@ -24526,7 +24526,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G833" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H833" t="n">
         <v>950966</v>
@@ -24555,7 +24555,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G834" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H834" t="n">
         <v>272796</v>
@@ -24584,7 +24584,7 @@
         <v>1.55299997329712</v>
       </c>
       <c r="G835" t="n">
-        <v>0.95248544216156</v>
+        <v>0.952485501766205</v>
       </c>
       <c r="H835" t="n">
         <v>259158</v>
@@ -24613,7 +24613,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G836" t="n">
-        <v>0.965365290641785</v>
+        <v>0.96536523103714</v>
       </c>
       <c r="H836" t="n">
         <v>290487</v>
@@ -24642,7 +24642,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G837" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H837" t="n">
         <v>135240</v>
@@ -24700,7 +24700,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G839" t="n">
-        <v>0.977631628513336</v>
+        <v>0.977631688117981</v>
       </c>
       <c r="H839" t="n">
         <v>557684</v>
@@ -24816,7 +24816,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G843" t="n">
-        <v>0.953098833560944</v>
+        <v>0.953098893165588</v>
       </c>
       <c r="H843" t="n">
         <v>226537</v>
@@ -24874,7 +24874,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G845" t="n">
-        <v>0.90280669927597</v>
+        <v>0.902806639671326</v>
       </c>
       <c r="H845" t="n">
         <v>601706</v>
@@ -24903,7 +24903,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G846" t="n">
-        <v>0.867234170436859</v>
+        <v>0.867234110832214</v>
       </c>
       <c r="H846" t="n">
         <v>884199</v>
@@ -24932,7 +24932,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G847" t="n">
-        <v>0.852514445781708</v>
+        <v>0.852514386177063</v>
       </c>
       <c r="H847" t="n">
         <v>1230354</v>
@@ -24990,7 +24990,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G849" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H849" t="n">
         <v>747799</v>
@@ -25077,7 +25077,7 @@
         <v>1.27799999713898</v>
       </c>
       <c r="G852" t="n">
-        <v>0.783822655677795</v>
+        <v>0.783822596073151</v>
       </c>
       <c r="H852" t="n">
         <v>775169</v>
@@ -25164,7 +25164,7 @@
         <v>1.18700003623962</v>
       </c>
       <c r="G855" t="n">
-        <v>0.728010535240173</v>
+        <v>0.728010594844818</v>
       </c>
       <c r="H855" t="n">
         <v>567821</v>
@@ -25193,7 +25193,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G856" t="n">
-        <v>0.743343591690063</v>
+        <v>0.743343532085419</v>
       </c>
       <c r="H856" t="n">
         <v>866584</v>
@@ -25280,7 +25280,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G859" t="n">
-        <v>0.69611781835556</v>
+        <v>0.696117877960205</v>
       </c>
       <c r="H859" t="n">
         <v>285309</v>
@@ -25309,7 +25309,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G860" t="n">
-        <v>0.718810796737671</v>
+        <v>0.718810737133026</v>
       </c>
       <c r="H860" t="n">
         <v>601635</v>
@@ -25396,7 +25396,7 @@
         <v>1.13100004196167</v>
       </c>
       <c r="G863" t="n">
-        <v>0.693664610385895</v>
+        <v>0.69366466999054</v>
       </c>
       <c r="H863" t="n">
         <v>193833</v>
@@ -25425,7 +25425,7 @@
         <v>1.17900002002716</v>
       </c>
       <c r="G864" t="n">
-        <v>0.723103940486908</v>
+        <v>0.723104000091553</v>
       </c>
       <c r="H864" t="n">
         <v>869061</v>
@@ -25483,7 +25483,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G866" t="n">
-        <v>0.72985053062439</v>
+        <v>0.729850471019745</v>
       </c>
       <c r="H866" t="n">
         <v>419879</v>
@@ -25512,7 +25512,7 @@
         <v>1.17900002002716</v>
       </c>
       <c r="G867" t="n">
-        <v>0.723103940486908</v>
+        <v>0.723104000091553</v>
       </c>
       <c r="H867" t="n">
         <v>203797</v>
@@ -25599,7 +25599,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G870" t="n">
-        <v>0.722490608692169</v>
+        <v>0.722490668296814</v>
       </c>
       <c r="H870" t="n">
         <v>551645</v>
@@ -25686,7 +25686,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G873" t="n">
-        <v>0.709610939025879</v>
+        <v>0.709610879421234</v>
       </c>
       <c r="H873" t="n">
         <v>47164</v>
@@ -25831,7 +25831,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G878" t="n">
-        <v>0.720650613307953</v>
+        <v>0.720650672912598</v>
       </c>
       <c r="H878" t="n">
         <v>167271</v>
@@ -25860,7 +25860,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G879" t="n">
-        <v>0.718810796737671</v>
+        <v>0.718810737133026</v>
       </c>
       <c r="H879" t="n">
         <v>103212</v>
@@ -25889,7 +25889,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G880" t="n">
-        <v>0.722490608692169</v>
+        <v>0.722490668296814</v>
       </c>
       <c r="H880" t="n">
         <v>278772</v>
@@ -26121,7 +26121,7 @@
         <v>1.24699997901917</v>
       </c>
       <c r="G888" t="n">
-        <v>0.764809668064117</v>
+        <v>0.764809727668762</v>
       </c>
       <c r="H888" t="n">
         <v>84093</v>
@@ -26179,7 +26179,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G890" t="n">
-        <v>0.770329535007477</v>
+        <v>0.770329594612122</v>
       </c>
       <c r="H890" t="n">
         <v>248918</v>
@@ -26208,7 +26208,7 @@
         <v>1.25300002098083</v>
       </c>
       <c r="G891" t="n">
-        <v>0.76848965883255</v>
+        <v>0.768489599227905</v>
       </c>
       <c r="H891" t="n">
         <v>235609</v>
@@ -26237,7 +26237,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G892" t="n">
-        <v>0.775849401950836</v>
+        <v>0.775849521160126</v>
       </c>
       <c r="H892" t="n">
         <v>153630</v>
@@ -26324,7 +26324,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G895" t="n">
-        <v>0.761743068695068</v>
+        <v>0.761743128299713</v>
       </c>
       <c r="H895" t="n">
         <v>419752</v>
@@ -26353,7 +26353,7 @@
         <v>1.25300002098083</v>
       </c>
       <c r="G896" t="n">
-        <v>0.76848965883255</v>
+        <v>0.768489599227905</v>
       </c>
       <c r="H896" t="n">
         <v>158402</v>
@@ -26411,7 +26411,7 @@
         <v>1.24699997901917</v>
       </c>
       <c r="G898" t="n">
-        <v>0.764809668064117</v>
+        <v>0.764809727668762</v>
       </c>
       <c r="H898" t="n">
         <v>106980</v>
@@ -26440,7 +26440,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G899" t="n">
-        <v>0.756836473941803</v>
+        <v>0.756836533546448</v>
       </c>
       <c r="H899" t="n">
         <v>111892</v>
@@ -26614,7 +26614,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G905" t="n">
-        <v>0.788729250431061</v>
+        <v>0.788729190826416</v>
       </c>
       <c r="H905" t="n">
         <v>739169</v>
@@ -26643,7 +26643,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G906" t="n">
-        <v>0.806515455245972</v>
+        <v>0.806515514850616</v>
       </c>
       <c r="H906" t="n">
         <v>571825</v>
@@ -26672,7 +26672,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G907" t="n">
-        <v>0.813262045383453</v>
+        <v>0.813261926174164</v>
       </c>
       <c r="H907" t="n">
         <v>280555</v>
@@ -26846,7 +26846,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G913" t="n">
-        <v>0.724943935871124</v>
+        <v>0.724943995475769</v>
       </c>
       <c r="H913" t="n">
         <v>255453</v>
@@ -26875,7 +26875,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G914" t="n">
-        <v>0.7323037981987</v>
+        <v>0.732303738594055</v>
       </c>
       <c r="H914" t="n">
         <v>47796</v>
@@ -26904,7 +26904,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G915" t="n">
-        <v>0.721264064311981</v>
+        <v>0.721264004707336</v>
       </c>
       <c r="H915" t="n">
         <v>135340</v>
@@ -26933,7 +26933,7 @@
         <v>1.17900002002716</v>
       </c>
       <c r="G916" t="n">
-        <v>0.723103940486908</v>
+        <v>0.723104000091553</v>
       </c>
       <c r="H916" t="n">
         <v>38025</v>
@@ -26962,7 +26962,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G917" t="n">
-        <v>0.726170539855957</v>
+        <v>0.726170599460602</v>
       </c>
       <c r="H917" t="n">
         <v>65620</v>
@@ -27049,7 +27049,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G920" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H920" t="n">
         <v>337846</v>
@@ -27078,7 +27078,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G921" t="n">
-        <v>0.7323037981987</v>
+        <v>0.732303738594055</v>
       </c>
       <c r="H921" t="n">
         <v>112754</v>
@@ -27107,7 +27107,7 @@
         <v>1.18099999427795</v>
       </c>
       <c r="G922" t="n">
-        <v>0.72433066368103</v>
+        <v>0.724330604076385</v>
       </c>
       <c r="H922" t="n">
         <v>22435</v>
@@ -27281,7 +27281,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G928" t="n">
-        <v>0.770329535007477</v>
+        <v>0.770329594612122</v>
       </c>
       <c r="H928" t="n">
         <v>147741</v>
@@ -27339,7 +27339,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G930" t="n">
-        <v>0.76051652431488</v>
+        <v>0.760516464710236</v>
       </c>
       <c r="H930" t="n">
         <v>93013</v>
@@ -27368,7 +27368,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G931" t="n">
-        <v>0.788729250431061</v>
+        <v>0.788729190826416</v>
       </c>
       <c r="H931" t="n">
         <v>296798</v>
@@ -27455,7 +27455,7 @@
         <v>1.23699998855591</v>
       </c>
       <c r="G934" t="n">
-        <v>0.758676469326019</v>
+        <v>0.758676528930664</v>
       </c>
       <c r="H934" t="n">
         <v>75972</v>
@@ -27513,7 +27513,7 @@
         <v>1.28400003910065</v>
       </c>
       <c r="G936" t="n">
-        <v>0.787502527236938</v>
+        <v>0.787502586841583</v>
       </c>
       <c r="H936" t="n">
         <v>379697</v>
@@ -27571,7 +27571,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G938" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H938" t="n">
         <v>317570</v>
@@ -27600,7 +27600,7 @@
         <v>1.33700001239777</v>
       </c>
       <c r="G939" t="n">
-        <v>0.820008516311646</v>
+        <v>0.820008456707001</v>
       </c>
       <c r="H939" t="n">
         <v>628585</v>
@@ -27629,7 +27629,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G940" t="n">
-        <v>0.849447846412659</v>
+        <v>0.849447786808014</v>
       </c>
       <c r="H940" t="n">
         <v>636692</v>
@@ -27716,7 +27716,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G943" t="n">
-        <v>0.837181448936462</v>
+        <v>0.837181389331818</v>
       </c>
       <c r="H943" t="n">
         <v>150974</v>
@@ -27803,7 +27803,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G946" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H946" t="n">
         <v>120742</v>
@@ -27832,7 +27832,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G947" t="n">
-        <v>0.829208254814148</v>
+        <v>0.829208314418793</v>
       </c>
       <c r="H947" t="n">
         <v>188418</v>
@@ -27919,7 +27919,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G950" t="n">
-        <v>0.754383325576782</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H950" t="n">
         <v>388069</v>
@@ -27948,7 +27948,7 @@
         <v>1.23099994659424</v>
       </c>
       <c r="G951" t="n">
-        <v>0.754996597766876</v>
+        <v>0.754996538162231</v>
       </c>
       <c r="H951" t="n">
         <v>184190</v>
@@ -27977,7 +27977,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G952" t="n">
-        <v>0.761743068695068</v>
+        <v>0.761743128299713</v>
       </c>
       <c r="H952" t="n">
         <v>112361</v>
@@ -28006,7 +28006,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G953" t="n">
-        <v>0.76051652431488</v>
+        <v>0.760516464710236</v>
       </c>
       <c r="H953" t="n">
         <v>55618</v>
@@ -28122,7 +28122,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G957" t="n">
-        <v>0.733530402183533</v>
+        <v>0.733530342578888</v>
       </c>
       <c r="H957" t="n">
         <v>98928</v>
@@ -28151,7 +28151,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G958" t="n">
-        <v>0.739050269126892</v>
+        <v>0.739050328731537</v>
       </c>
       <c r="H958" t="n">
         <v>114210</v>
@@ -28209,7 +28209,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G960" t="n">
-        <v>0.756836473941803</v>
+        <v>0.756836533546448</v>
       </c>
       <c r="H960" t="n">
         <v>114513</v>
@@ -28238,7 +28238,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G961" t="n">
-        <v>0.754383325576782</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H961" t="n">
         <v>137429</v>
@@ -28267,7 +28267,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G962" t="n">
-        <v>0.775849401950836</v>
+        <v>0.775849521160126</v>
       </c>
       <c r="H962" t="n">
         <v>214782</v>
@@ -28354,7 +28354,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G965" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H965" t="n">
         <v>236368</v>
@@ -28383,7 +28383,7 @@
         <v>1.29900002479553</v>
       </c>
       <c r="G966" t="n">
-        <v>0.796702325344086</v>
+        <v>0.79670238494873</v>
       </c>
       <c r="H966" t="n">
         <v>218158</v>
@@ -28412,7 +28412,7 @@
         <v>1.25300002098083</v>
       </c>
       <c r="G967" t="n">
-        <v>0.76848965883255</v>
+        <v>0.768489599227905</v>
       </c>
       <c r="H967" t="n">
         <v>275593</v>
@@ -28470,7 +28470,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G969" t="n">
-        <v>0.769102931022644</v>
+        <v>0.769102871417999</v>
       </c>
       <c r="H969" t="n">
         <v>152371</v>
@@ -28499,7 +28499,7 @@
         <v>1.25100004673004</v>
       </c>
       <c r="G970" t="n">
-        <v>0.767263054847717</v>
+        <v>0.767262995243073</v>
       </c>
       <c r="H970" t="n">
         <v>27949</v>
@@ -28586,7 +28586,7 @@
         <v>1.31599998474121</v>
       </c>
       <c r="G973" t="n">
-        <v>0.807128727436066</v>
+        <v>0.80712878704071</v>
       </c>
       <c r="H973" t="n">
         <v>703507</v>
@@ -28673,7 +28673,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G976" t="n">
-        <v>0.859874188899994</v>
+        <v>0.859874248504639</v>
       </c>
       <c r="H976" t="n">
         <v>387912</v>
@@ -28702,7 +28702,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G977" t="n">
-        <v>0.845154583454132</v>
+        <v>0.845154643058777</v>
       </c>
       <c r="H977" t="n">
         <v>146518</v>
@@ -28731,7 +28731,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G978" t="n">
-        <v>0.910779774188995</v>
+        <v>0.91077983379364</v>
       </c>
       <c r="H978" t="n">
         <v>814971</v>
@@ -28760,7 +28760,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G979" t="n">
-        <v>0.953712165355682</v>
+        <v>0.953712105751038</v>
       </c>
       <c r="H979" t="n">
         <v>1109248</v>
@@ -28818,7 +28818,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G981" t="n">
-        <v>0.981311619281769</v>
+        <v>0.981311559677124</v>
       </c>
       <c r="H981" t="n">
         <v>380709</v>
@@ -28847,7 +28847,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G982" t="n">
-        <v>0.944512367248535</v>
+        <v>0.94451242685318</v>
       </c>
       <c r="H982" t="n">
         <v>609647</v>
@@ -28876,7 +28876,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G983" t="n">
-        <v>0.937152564525604</v>
+        <v>0.937152624130249</v>
       </c>
       <c r="H983" t="n">
         <v>263445</v>
@@ -28905,7 +28905,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G984" t="n">
-        <v>0.961685359477997</v>
+        <v>0.961685299873352</v>
       </c>
       <c r="H984" t="n">
         <v>669708</v>
@@ -29021,7 +29021,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G988" t="n">
-        <v>0.875820517539978</v>
+        <v>0.875820577144623</v>
       </c>
       <c r="H988" t="n">
         <v>694818</v>
@@ -29079,7 +29079,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G990" t="n">
-        <v>0.872140765190125</v>
+        <v>0.872140645980835</v>
       </c>
       <c r="H990" t="n">
         <v>227729</v>
@@ -29137,7 +29137,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G992" t="n">
-        <v>0.884407103061676</v>
+        <v>0.884407043457031</v>
       </c>
       <c r="H992" t="n">
         <v>245509</v>
@@ -29166,7 +29166,7 @@
         <v>1.5</v>
       </c>
       <c r="G993" t="n">
-        <v>0.919979631900787</v>
+        <v>0.919979512691498</v>
       </c>
       <c r="H993" t="n">
         <v>297589</v>
@@ -29195,7 +29195,7 @@
         <v>1.53100001811981</v>
       </c>
       <c r="G994" t="n">
-        <v>0.938992500305176</v>
+        <v>0.938992619514465</v>
       </c>
       <c r="H994" t="n">
         <v>412888</v>
@@ -29224,7 +29224,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G995" t="n">
-        <v>0.954325556755066</v>
+        <v>0.954325437545776</v>
       </c>
       <c r="H995" t="n">
         <v>364299</v>
@@ -29253,7 +29253,7 @@
         <v>1.52699995040894</v>
       </c>
       <c r="G996" t="n">
-        <v>0.936539232730865</v>
+        <v>0.93653929233551</v>
       </c>
       <c r="H996" t="n">
         <v>279676</v>
@@ -29340,7 +29340,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G999" t="n">
-        <v>0.918752908706665</v>
+        <v>0.91875296831131</v>
       </c>
       <c r="H999" t="n">
         <v>695778</v>
@@ -29369,7 +29369,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1000" t="n">
-        <v>0.928566098213196</v>
+        <v>0.928566157817841</v>
       </c>
       <c r="H1000" t="n">
         <v>238212</v>
@@ -29398,7 +29398,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G1001" t="n">
-        <v>0.916913032531738</v>
+        <v>0.916912972927094</v>
       </c>
       <c r="H1001" t="n">
         <v>566221</v>
@@ -29427,7 +29427,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G1002" t="n">
-        <v>0.918752908706665</v>
+        <v>0.91875296831131</v>
       </c>
       <c r="H1002" t="n">
         <v>198540</v>
@@ -29456,7 +29456,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G1003" t="n">
-        <v>0.918752908706665</v>
+        <v>0.91875296831131</v>
       </c>
       <c r="H1003" t="n">
         <v>784488</v>
@@ -29485,7 +29485,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1004" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H1004" t="n">
         <v>1240368</v>
@@ -29543,7 +29543,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1006" t="n">
-        <v>1.03344368934631</v>
+        <v>1.0334438085556</v>
       </c>
       <c r="H1006" t="n">
         <v>1431295</v>
@@ -29601,7 +29601,7 @@
         <v>1.73099994659424</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.06165635585785</v>
+        <v>1.06165647506714</v>
       </c>
       <c r="H1008" t="n">
         <v>598181</v>
@@ -29659,7 +29659,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.01933741569519</v>
+        <v>1.0193372964859</v>
       </c>
       <c r="H1010" t="n">
         <v>906453</v>
@@ -29688,7 +29688,7 @@
         <v>1.63900005817413</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.00523102283478</v>
+        <v>1.00523114204407</v>
       </c>
       <c r="H1011" t="n">
         <v>927265</v>
@@ -29717,7 +29717,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.00277769565582</v>
+        <v>1.00277781486511</v>
       </c>
       <c r="H1012" t="n">
         <v>2587600</v>
@@ -29746,7 +29746,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1013" t="n">
-        <v>0.987444818019867</v>
+        <v>0.987444758415222</v>
       </c>
       <c r="H1013" t="n">
         <v>1079055</v>
@@ -29775,7 +29775,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1014" t="n">
-        <v>0.980084955692291</v>
+        <v>0.980085015296936</v>
       </c>
       <c r="H1014" t="n">
         <v>523079</v>
@@ -29804,7 +29804,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1015" t="n">
-        <v>0.980084955692291</v>
+        <v>0.980085015296936</v>
       </c>
       <c r="H1015" t="n">
         <v>426514</v>
@@ -29833,7 +29833,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G1016" t="n">
-        <v>0.986218094825745</v>
+        <v>0.986218154430389</v>
       </c>
       <c r="H1016" t="n">
         <v>668830</v>
@@ -29891,7 +29891,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1018" t="n">
-        <v>0.944512367248535</v>
+        <v>0.94451242685318</v>
       </c>
       <c r="H1018" t="n">
         <v>455781</v>
@@ -29920,7 +29920,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G1019" t="n">
-        <v>0.958618700504303</v>
+        <v>0.958618640899658</v>
       </c>
       <c r="H1019" t="n">
         <v>288466</v>
@@ -30007,7 +30007,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1022" t="n">
-        <v>0.965978622436523</v>
+        <v>0.965978562831879</v>
       </c>
       <c r="H1022" t="n">
         <v>372971</v>
@@ -30065,7 +30065,7 @@
         <v>1.58899998664856</v>
       </c>
       <c r="G1024" t="n">
-        <v>0.974565029144287</v>
+        <v>0.974565088748932</v>
       </c>
       <c r="H1024" t="n">
         <v>315897</v>
@@ -30094,7 +30094,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1025" t="n">
-        <v>0.980084955692291</v>
+        <v>0.980085015296936</v>
       </c>
       <c r="H1025" t="n">
         <v>570459</v>
@@ -30123,7 +30123,7 @@
         <v>1.58700001239777</v>
       </c>
       <c r="G1026" t="n">
-        <v>0.973338484764099</v>
+        <v>0.973338425159454</v>
       </c>
       <c r="H1026" t="n">
         <v>768858</v>
@@ -30152,7 +30152,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G1027" t="n">
-        <v>0.906486630439758</v>
+        <v>0.906486570835114</v>
       </c>
       <c r="H1027" t="n">
         <v>1879056</v>
@@ -30210,7 +30210,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1029" t="n">
-        <v>0.858647644519806</v>
+        <v>0.858647584915161</v>
       </c>
       <c r="H1029" t="n">
         <v>586405</v>
@@ -30239,7 +30239,7 @@
         <v>1.36699998378754</v>
       </c>
       <c r="G1030" t="n">
-        <v>0.83840811252594</v>
+        <v>0.838408052921295</v>
       </c>
       <c r="H1030" t="n">
         <v>744323</v>
@@ -30268,7 +30268,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1031" t="n">
-        <v>0.815715193748474</v>
+        <v>0.815715253353119</v>
       </c>
       <c r="H1031" t="n">
         <v>572298</v>
@@ -30297,7 +30297,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1032" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1032" t="n">
         <v>989532</v>
@@ -30326,7 +30326,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G1033" t="n">
-        <v>0.767876327037811</v>
+        <v>0.767876267433167</v>
       </c>
       <c r="H1033" t="n">
         <v>878332</v>
@@ -30355,7 +30355,7 @@
         <v>1.26699995994568</v>
       </c>
       <c r="G1034" t="n">
-        <v>0.777076125144958</v>
+        <v>0.777076065540314</v>
       </c>
       <c r="H1034" t="n">
         <v>1684681</v>
@@ -30384,7 +30384,7 @@
         <v>1.32099997997284</v>
       </c>
       <c r="G1035" t="n">
-        <v>0.810195326805115</v>
+        <v>0.81019538640976</v>
       </c>
       <c r="H1035" t="n">
         <v>1370386</v>
@@ -30442,7 +30442,7 @@
         <v>1.28400003910065</v>
       </c>
       <c r="G1037" t="n">
-        <v>0.787502527236938</v>
+        <v>0.787502586841583</v>
       </c>
       <c r="H1037" t="n">
         <v>524349</v>
@@ -30500,7 +30500,7 @@
         <v>1.2940000295639</v>
       </c>
       <c r="G1039" t="n">
-        <v>0.793635725975037</v>
+        <v>0.793635785579681</v>
       </c>
       <c r="H1039" t="n">
         <v>278799</v>
@@ -30529,7 +30529,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G1040" t="n">
-        <v>0.79976898431778</v>
+        <v>0.799768924713135</v>
       </c>
       <c r="H1040" t="n">
         <v>413001</v>
@@ -30674,7 +30674,7 @@
         <v>1.33700001239777</v>
       </c>
       <c r="G1045" t="n">
-        <v>0.820008516311646</v>
+        <v>0.820008456707001</v>
       </c>
       <c r="H1045" t="n">
         <v>582765</v>
@@ -30703,7 +30703,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G1046" t="n">
-        <v>0.806515455245972</v>
+        <v>0.806515514850616</v>
       </c>
       <c r="H1046" t="n">
         <v>278628</v>
@@ -30761,7 +30761,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G1048" t="n">
-        <v>0.814488589763641</v>
+        <v>0.814488530158997</v>
       </c>
       <c r="H1048" t="n">
         <v>245739</v>
@@ -30790,7 +30790,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1049" t="n">
-        <v>0.813262045383453</v>
+        <v>0.813261926174164</v>
       </c>
       <c r="H1049" t="n">
         <v>258815</v>
@@ -30819,7 +30819,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1050" t="n">
-        <v>0.803448855876923</v>
+        <v>0.803448796272278</v>
       </c>
       <c r="H1050" t="n">
         <v>319934</v>
@@ -30877,7 +30877,7 @@
         <v>1.28699994087219</v>
       </c>
       <c r="G1052" t="n">
-        <v>0.789342522621155</v>
+        <v>0.78934246301651</v>
       </c>
       <c r="H1052" t="n">
         <v>394105</v>
@@ -30935,7 +30935,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G1054" t="n">
-        <v>0.721264064311981</v>
+        <v>0.721264004707336</v>
       </c>
       <c r="H1054" t="n">
         <v>1222841</v>
@@ -31022,7 +31022,7 @@
         <v>1.07299995422363</v>
       </c>
       <c r="G1057" t="n">
-        <v>0.658092021942139</v>
+        <v>0.658092081546783</v>
       </c>
       <c r="H1057" t="n">
         <v>669322</v>
@@ -31167,7 +31167,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.572227299213409</v>
+        <v>0.572227358818054</v>
       </c>
       <c r="H1062" t="n">
         <v>1024504</v>
@@ -31254,7 +31254,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.49678897857666</v>
+        <v>0.496788948774338</v>
       </c>
       <c r="H1065" t="n">
         <v>713971</v>
@@ -31312,7 +31312,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.451403349637985</v>
+        <v>0.451403319835663</v>
       </c>
       <c r="H1067" t="n">
         <v>964293</v>
@@ -31370,7 +31370,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.472256183624268</v>
+        <v>0.47225621342659</v>
       </c>
       <c r="H1069" t="n">
         <v>461033</v>
@@ -31399,7 +31399,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.461216449737549</v>
+        <v>0.461216419935226</v>
       </c>
       <c r="H1070" t="n">
         <v>387884</v>
@@ -31457,7 +31457,7 @@
         <v>0.806999981403351</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.494949042797089</v>
+        <v>0.494949012994766</v>
       </c>
       <c r="H1072" t="n">
         <v>544462</v>
@@ -31486,7 +31486,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.490655809640884</v>
+        <v>0.490655779838562</v>
       </c>
       <c r="H1073" t="n">
         <v>143879</v>
@@ -31573,7 +31573,7 @@
         <v>0.732999980449677</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.449563354253769</v>
+        <v>0.449563324451447</v>
       </c>
       <c r="H1076" t="n">
         <v>402235</v>
@@ -31660,7 +31660,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.39988449215889</v>
+        <v>0.399884462356567</v>
       </c>
       <c r="H1079" t="n">
         <v>1104968</v>
@@ -31747,7 +31747,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.434230357408524</v>
+        <v>0.434230387210846</v>
       </c>
       <c r="H1082" t="n">
         <v>718601</v>
@@ -31863,7 +31863,7 @@
         <v>0.901000022888184</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.552601099014282</v>
+        <v>0.552601158618927</v>
       </c>
       <c r="H1086" t="n">
         <v>1092450</v>
@@ -31921,7 +31921,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.49678897857666</v>
+        <v>0.496788948774338</v>
       </c>
       <c r="H1088" t="n">
         <v>488572</v>
@@ -32095,7 +32095,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G1094" t="n">
-        <v>0.559347629547119</v>
+        <v>0.559347569942474</v>
       </c>
       <c r="H1094" t="n">
         <v>255686</v>
@@ -32124,7 +32124,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1095" t="n">
-        <v>0.533588171005249</v>
+        <v>0.533588111400604</v>
       </c>
       <c r="H1095" t="n">
         <v>655537</v>
@@ -32211,7 +32211,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1098" t="n">
-        <v>0.533588171005249</v>
+        <v>0.533588111400604</v>
       </c>
       <c r="H1098" t="n">
         <v>299617</v>
@@ -32240,7 +32240,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G1099" t="n">
-        <v>0.536041438579559</v>
+        <v>0.536041498184204</v>
       </c>
       <c r="H1099" t="n">
         <v>126540</v>
@@ -32269,7 +32269,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G1100" t="n">
-        <v>0.512121975421906</v>
+        <v>0.512121915817261</v>
       </c>
       <c r="H1100" t="n">
         <v>217518</v>
@@ -32385,7 +32385,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1104" t="n">
-        <v>0.518868505954742</v>
+        <v>0.518868565559387</v>
       </c>
       <c r="H1104" t="n">
         <v>58819</v>
@@ -32472,7 +32472,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1107" t="n">
-        <v>0.518868505954742</v>
+        <v>0.518868565559387</v>
       </c>
       <c r="H1107" t="n">
         <v>472495</v>
@@ -32501,7 +32501,7 @@
         <v>0.830999970436096</v>
       </c>
       <c r="G1108" t="n">
-        <v>0.509668707847595</v>
+        <v>0.50966864824295</v>
       </c>
       <c r="H1108" t="n">
         <v>91813</v>
@@ -32617,7 +32617,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.493109047412872</v>
+        <v>0.493109077215195</v>
       </c>
       <c r="H1112" t="n">
         <v>413811</v>
@@ -32646,7 +32646,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.491882383823395</v>
+        <v>0.49188244342804</v>
       </c>
       <c r="H1113" t="n">
         <v>111204</v>
@@ -32704,7 +32704,7 @@
         <v>0.805000007152557</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.493722409009933</v>
+        <v>0.493722379207611</v>
       </c>
       <c r="H1115" t="n">
         <v>158477</v>
@@ -32733,7 +32733,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1116" t="n">
-        <v>0.518868505954742</v>
+        <v>0.518868565559387</v>
       </c>
       <c r="H1116" t="n">
         <v>359020</v>
@@ -32762,7 +32762,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1117" t="n">
-        <v>0.551987707614899</v>
+        <v>0.551987767219543</v>
       </c>
       <c r="H1117" t="n">
         <v>1116754</v>
@@ -32791,7 +32791,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1118" t="n">
-        <v>0.545854568481445</v>
+        <v>0.545854508876801</v>
       </c>
       <c r="H1118" t="n">
         <v>579211</v>
@@ -32849,7 +32849,7 @@
         <v>0.888999998569489</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.545241296291351</v>
+        <v>0.545241236686707</v>
       </c>
       <c r="H1120" t="n">
         <v>365185</v>
@@ -32907,7 +32907,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G1122" t="n">
-        <v>0.61086642742157</v>
+        <v>0.610866487026215</v>
       </c>
       <c r="H1122" t="n">
         <v>886047</v>
@@ -32936,7 +32936,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1123" t="n">
-        <v>0.637852549552917</v>
+        <v>0.637852489948273</v>
       </c>
       <c r="H1123" t="n">
         <v>763871</v>
@@ -33023,7 +33023,7 @@
         <v>1</v>
       </c>
       <c r="G1126" t="n">
-        <v>0.613319754600525</v>
+        <v>0.61331969499588</v>
       </c>
       <c r="H1126" t="n">
         <v>511212</v>
@@ -33052,7 +33052,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G1127" t="n">
-        <v>0.61086642742157</v>
+        <v>0.610866487026215</v>
       </c>
       <c r="H1127" t="n">
         <v>500431</v>
@@ -33110,7 +33110,7 @@
         <v>0.949000000953674</v>
       </c>
       <c r="G1129" t="n">
-        <v>0.582040429115295</v>
+        <v>0.582040369510651</v>
       </c>
       <c r="H1129" t="n">
         <v>271755</v>
@@ -33197,7 +33197,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1132" t="n">
-        <v>0.551987707614899</v>
+        <v>0.551987767219543</v>
       </c>
       <c r="H1132" t="n">
         <v>204586</v>
@@ -33255,7 +33255,7 @@
         <v>0.876999974250793</v>
       </c>
       <c r="G1134" t="n">
-        <v>0.537881374359131</v>
+        <v>0.537881433963776</v>
       </c>
       <c r="H1134" t="n">
         <v>352691</v>
@@ -33400,7 +33400,7 @@
         <v>0.842999994754791</v>
       </c>
       <c r="G1139" t="n">
-        <v>0.517028510570526</v>
+        <v>0.517028570175171</v>
       </c>
       <c r="H1139" t="n">
         <v>186704</v>
@@ -33545,7 +33545,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.516415238380432</v>
+        <v>0.516415178775787</v>
       </c>
       <c r="H1144" t="n">
         <v>471211</v>
@@ -33574,7 +33574,7 @@
         <v>0.837000012397766</v>
       </c>
       <c r="G1145" t="n">
-        <v>0.513348639011383</v>
+        <v>0.513348579406738</v>
       </c>
       <c r="H1145" t="n">
         <v>169771</v>
@@ -33603,7 +33603,7 @@
         <v>0.845000028610229</v>
       </c>
       <c r="G1146" t="n">
-        <v>0.518255174160004</v>
+        <v>0.518255233764648</v>
       </c>
       <c r="H1146" t="n">
         <v>86454</v>
@@ -33690,7 +33690,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1149" t="n">
-        <v>0.522548377513885</v>
+        <v>0.52254843711853</v>
       </c>
       <c r="H1149" t="n">
         <v>155783</v>
@@ -33719,7 +33719,7 @@
         <v>0.859000027179718</v>
       </c>
       <c r="G1150" t="n">
-        <v>0.526841640472412</v>
+        <v>0.526841700077057</v>
       </c>
       <c r="H1150" t="n">
         <v>153721</v>
@@ -33864,7 +33864,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1155" t="n">
-        <v>0.53849470615387</v>
+        <v>0.538494765758514</v>
       </c>
       <c r="H1155" t="n">
         <v>65264</v>
@@ -33893,7 +33893,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1156" t="n">
-        <v>0.542174637317657</v>
+        <v>0.542174696922302</v>
       </c>
       <c r="H1156" t="n">
         <v>144213</v>
@@ -33922,7 +33922,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1157" t="n">
-        <v>0.545854568481445</v>
+        <v>0.545854508876801</v>
       </c>
       <c r="H1157" t="n">
         <v>71533</v>
@@ -33951,7 +33951,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1158" t="n">
-        <v>0.545854568481445</v>
+        <v>0.545854508876801</v>
       </c>
       <c r="H1158" t="n">
         <v>127025</v>
@@ -33980,7 +33980,7 @@
         <v>0.879000008106232</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.539108037948608</v>
+        <v>0.539108097553253</v>
       </c>
       <c r="H1159" t="n">
         <v>107708</v>
@@ -34067,7 +34067,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1162" t="n">
-        <v>0.551987707614899</v>
+        <v>0.551987767219543</v>
       </c>
       <c r="H1162" t="n">
         <v>382932</v>
@@ -34096,7 +34096,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.542174637317657</v>
+        <v>0.542174696922302</v>
       </c>
       <c r="H1163" t="n">
         <v>210006</v>
@@ -34125,7 +34125,7 @@
         <v>0.879000008106232</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.539108037948608</v>
+        <v>0.539108097553253</v>
       </c>
       <c r="H1164" t="n">
         <v>179069</v>
@@ -34328,7 +34328,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G1171" t="n">
-        <v>0.604733228683472</v>
+        <v>0.604733288288116</v>
       </c>
       <c r="H1171" t="n">
         <v>233144</v>
@@ -34357,7 +34357,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.601053297519684</v>
+        <v>0.601053357124329</v>
       </c>
       <c r="H1172" t="n">
         <v>119918</v>
@@ -34415,7 +34415,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.582653760910034</v>
+        <v>0.582653701305389</v>
       </c>
       <c r="H1174" t="n">
         <v>159888</v>
@@ -34473,7 +34473,7 @@
         <v>0.930999994277954</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.571000635623932</v>
+        <v>0.571000695228577</v>
       </c>
       <c r="H1176" t="n">
         <v>76615</v>
@@ -34560,7 +34560,7 @@
         <v>0.964999973773956</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.591853559017181</v>
+        <v>0.591853499412537</v>
       </c>
       <c r="H1179" t="n">
         <v>247116</v>
@@ -34647,7 +34647,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.587560296058655</v>
+        <v>0.5875603556633</v>
       </c>
       <c r="H1182" t="n">
         <v>98391</v>
@@ -34676,7 +34676,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.578973889350891</v>
+        <v>0.578973770141602</v>
       </c>
       <c r="H1183" t="n">
         <v>46587</v>
@@ -34734,7 +34734,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.559347629547119</v>
+        <v>0.559347569942474</v>
       </c>
       <c r="H1185" t="n">
         <v>112566</v>
@@ -34821,7 +34821,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.572227299213409</v>
+        <v>0.572227358818054</v>
       </c>
       <c r="H1188" t="n">
         <v>463536</v>
@@ -34879,7 +34879,7 @@
         <v>0.916999995708466</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.562414228916168</v>
+        <v>0.562414169311523</v>
       </c>
       <c r="H1190" t="n">
         <v>129939</v>
@@ -34908,7 +34908,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.547081232070923</v>
+        <v>0.547081172466278</v>
       </c>
       <c r="H1191" t="n">
         <v>73041</v>
@@ -35111,7 +35111,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.592466831207275</v>
+        <v>0.59246689081192</v>
       </c>
       <c r="H1198" t="n">
         <v>237851</v>
@@ -35140,7 +35140,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G1199" t="n">
-        <v>0.561800837516785</v>
+        <v>0.561800897121429</v>
       </c>
       <c r="H1199" t="n">
         <v>183721</v>
@@ -35198,7 +35198,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.551987707614899</v>
+        <v>0.551987767219543</v>
       </c>
       <c r="H1201" t="n">
         <v>188883</v>
@@ -35401,7 +35401,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.572227299213409</v>
+        <v>0.572227358818054</v>
       </c>
       <c r="H1208" t="n">
         <v>45202</v>
@@ -35488,7 +35488,7 @@
         <v>0.944999992847443</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.579587161540985</v>
+        <v>0.57958710193634</v>
       </c>
       <c r="H1211" t="n">
         <v>145714</v>
@@ -35546,7 +35546,7 @@
         <v>0.958999991416931</v>
       </c>
       <c r="G1213" t="n">
-        <v>0.588173627853394</v>
+        <v>0.588173687458038</v>
       </c>
       <c r="H1213" t="n">
         <v>77828</v>
@@ -35604,7 +35604,7 @@
         <v>0.953000009059906</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.58449375629425</v>
+        <v>0.584493696689606</v>
       </c>
       <c r="H1215" t="n">
         <v>35577</v>
@@ -35807,7 +35807,7 @@
         <v>0.888999998569489</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.545241296291351</v>
+        <v>0.545241236686707</v>
       </c>
       <c r="H1222" t="n">
         <v>106986</v>
@@ -36039,7 +36039,7 @@
         <v>0.916999995708466</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.562414228916168</v>
+        <v>0.562414169311523</v>
       </c>
       <c r="H1230" t="n">
         <v>70429</v>
@@ -36068,7 +36068,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.572227299213409</v>
+        <v>0.572227358818054</v>
       </c>
       <c r="H1231" t="n">
         <v>77919</v>
@@ -36097,7 +36097,7 @@
         <v>0.944999992847443</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.579587161540985</v>
+        <v>0.57958710193634</v>
       </c>
       <c r="H1232" t="n">
         <v>109876</v>
@@ -36126,7 +36126,7 @@
         <v>0.967000007629395</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.593080222606659</v>
+        <v>0.593080163002014</v>
       </c>
       <c r="H1233" t="n">
         <v>53370</v>
@@ -36242,7 +36242,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.625586152076721</v>
+        <v>0.625586092472076</v>
       </c>
       <c r="H1237" t="n">
         <v>166551</v>
@@ -36271,7 +36271,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1238" t="n">
-        <v>0.625586152076721</v>
+        <v>0.625586092472076</v>
       </c>
       <c r="H1238" t="n">
         <v>72929</v>
@@ -36300,7 +36300,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.648892283439636</v>
+        <v>0.648892223834991</v>
       </c>
       <c r="H1239" t="n">
         <v>338804</v>
@@ -36387,7 +36387,7 @@
         <v>1.15799999237061</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.710224330425262</v>
+        <v>0.710224270820618</v>
       </c>
       <c r="H1242" t="n">
         <v>253980</v>
@@ -36445,7 +36445,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.697957932949066</v>
+        <v>0.697957813739777</v>
       </c>
       <c r="H1244" t="n">
         <v>343735</v>
@@ -36503,7 +36503,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1246" t="n">
-        <v>0.726170539855957</v>
+        <v>0.726170599460602</v>
       </c>
       <c r="H1246" t="n">
         <v>231356</v>
@@ -36532,7 +36532,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1247" t="n">
-        <v>0.788729250431061</v>
+        <v>0.788729190826416</v>
       </c>
       <c r="H1247" t="n">
         <v>694692</v>
@@ -36561,7 +36561,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.775236129760742</v>
+        <v>0.775236248970032</v>
       </c>
       <c r="H1248" t="n">
         <v>177276</v>
@@ -36590,7 +36590,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1249" t="n">
-        <v>0.821848511695862</v>
+        <v>0.821848452091217</v>
       </c>
       <c r="H1249" t="n">
         <v>385304</v>
@@ -36677,7 +36677,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1252" t="n">
-        <v>0.754383325576782</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H1252" t="n">
         <v>109391</v>
@@ -36735,7 +36735,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G1254" t="n">
-        <v>0.756836473941803</v>
+        <v>0.756836533546448</v>
       </c>
       <c r="H1254" t="n">
         <v>67261</v>
@@ -36793,7 +36793,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1256" t="n">
-        <v>0.769102931022644</v>
+        <v>0.769102871417999</v>
       </c>
       <c r="H1256" t="n">
         <v>128864</v>
@@ -36880,7 +36880,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.743343591690063</v>
+        <v>0.743343532085419</v>
       </c>
       <c r="H1259" t="n">
         <v>192421</v>
@@ -36909,7 +36909,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.739663541316986</v>
+        <v>0.739663600921631</v>
       </c>
       <c r="H1260" t="n">
         <v>143028</v>
@@ -36938,7 +36938,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1261" t="n">
         <v>99221</v>
@@ -36967,7 +36967,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1262" t="n">
-        <v>0.759289801120758</v>
+        <v>0.759289860725403</v>
       </c>
       <c r="H1262" t="n">
         <v>121252</v>
@@ -36996,7 +36996,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1263" t="n">
-        <v>0.764196395874023</v>
+        <v>0.764196455478668</v>
       </c>
       <c r="H1263" t="n">
         <v>90228</v>
@@ -37054,7 +37054,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.712677538394928</v>
+        <v>0.712677478790283</v>
       </c>
       <c r="H1265" t="n">
         <v>252252</v>
@@ -37199,7 +37199,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1270" t="n">
-        <v>0.724943935871124</v>
+        <v>0.724943995475769</v>
       </c>
       <c r="H1270" t="n">
         <v>100068</v>
@@ -37257,7 +37257,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1272" t="n">
-        <v>0.743343591690063</v>
+        <v>0.743343532085419</v>
       </c>
       <c r="H1272" t="n">
         <v>66956</v>
@@ -37286,7 +37286,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G1273" t="n">
-        <v>0.737210273742676</v>
+        <v>0.737210333347321</v>
       </c>
       <c r="H1273" t="n">
         <v>45762</v>
@@ -37315,7 +37315,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.761743068695068</v>
+        <v>0.761743128299713</v>
       </c>
       <c r="H1274" t="n">
         <v>257120</v>
@@ -37402,7 +37402,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1277" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1277" t="n">
         <v>128905</v>
@@ -37460,7 +37460,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1279" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1279" t="n">
         <v>104631</v>
@@ -37489,7 +37489,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G1280" t="n">
-        <v>0.728623807430267</v>
+        <v>0.728623867034912</v>
       </c>
       <c r="H1280" t="n">
         <v>106827</v>
@@ -37663,7 +37663,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G1286" t="n">
-        <v>0.702864468097687</v>
+        <v>0.702864408493042</v>
       </c>
       <c r="H1286" t="n">
         <v>99700</v>
@@ -37692,7 +37692,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1287" t="n">
-        <v>0.712677538394928</v>
+        <v>0.712677478790283</v>
       </c>
       <c r="H1287" t="n">
         <v>89003</v>
@@ -37721,7 +37721,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G1288" t="n">
-        <v>0.706544280052185</v>
+        <v>0.70654433965683</v>
       </c>
       <c r="H1288" t="n">
         <v>55804</v>
@@ -38040,7 +38040,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1299" t="n">
-        <v>0.743343591690063</v>
+        <v>0.743343532085419</v>
       </c>
       <c r="H1299" t="n">
         <v>114513</v>
@@ -38098,7 +38098,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1301" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1301" t="n">
         <v>82491</v>
@@ -38127,7 +38127,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1302" t="n">
-        <v>0.769102931022644</v>
+        <v>0.769102871417999</v>
       </c>
       <c r="H1302" t="n">
         <v>923737</v>
@@ -38156,7 +38156,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1303" t="n">
-        <v>0.76051652431488</v>
+        <v>0.760516464710236</v>
       </c>
       <c r="H1303" t="n">
         <v>59895</v>
@@ -38185,7 +38185,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1304" t="n">
-        <v>0.759289801120758</v>
+        <v>0.759289860725403</v>
       </c>
       <c r="H1304" t="n">
         <v>121379</v>
@@ -38214,7 +38214,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1305" t="n">
-        <v>0.764196395874023</v>
+        <v>0.764196455478668</v>
       </c>
       <c r="H1305" t="n">
         <v>63773</v>
@@ -38243,7 +38243,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1306" t="n">
-        <v>0.762969791889191</v>
+        <v>0.762969732284546</v>
       </c>
       <c r="H1306" t="n">
         <v>43432</v>
@@ -38272,7 +38272,7 @@
         <v>1.24800002574921</v>
       </c>
       <c r="G1307" t="n">
-        <v>0.765422940254211</v>
+        <v>0.765422999858856</v>
       </c>
       <c r="H1307" t="n">
         <v>95806</v>
@@ -38301,7 +38301,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1308" t="n">
-        <v>0.769102931022644</v>
+        <v>0.769102871417999</v>
       </c>
       <c r="H1308" t="n">
         <v>93854</v>
@@ -38330,7 +38330,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1309" t="n">
         <v>791184</v>
@@ -38417,7 +38417,7 @@
         <v>1.32200002670288</v>
       </c>
       <c r="G1312" t="n">
-        <v>0.810808777809143</v>
+        <v>0.810808718204498</v>
       </c>
       <c r="H1312" t="n">
         <v>328150</v>
@@ -38475,7 +38475,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1314" t="n">
-        <v>0.824301660060883</v>
+        <v>0.824301719665527</v>
       </c>
       <c r="H1314" t="n">
         <v>64998</v>
@@ -38504,7 +38504,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.803448855876923</v>
+        <v>0.803448796272278</v>
       </c>
       <c r="H1315" t="n">
         <v>119343</v>
@@ -38562,7 +38562,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1317" t="n">
-        <v>0.769102931022644</v>
+        <v>0.769102871417999</v>
       </c>
       <c r="H1317" t="n">
         <v>567764</v>
@@ -38591,7 +38591,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1318" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1318" t="n">
         <v>326078</v>
@@ -38620,7 +38620,7 @@
         <v>1.28400003910065</v>
       </c>
       <c r="G1319" t="n">
-        <v>0.787502527236938</v>
+        <v>0.787502586841583</v>
       </c>
       <c r="H1319" t="n">
         <v>137229</v>
@@ -38678,7 +38678,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1321" t="n">
-        <v>0.815715193748474</v>
+        <v>0.815715253353119</v>
       </c>
       <c r="H1321" t="n">
         <v>297429</v>
@@ -38707,7 +38707,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1322" t="n">
-        <v>0.835341393947601</v>
+        <v>0.835341453552246</v>
       </c>
       <c r="H1322" t="n">
         <v>275179</v>
@@ -38765,7 +38765,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1324" t="n">
-        <v>0.858647644519806</v>
+        <v>0.858647584915161</v>
       </c>
       <c r="H1324" t="n">
         <v>364891</v>
@@ -38794,7 +38794,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1325" t="n">
-        <v>0.858647644519806</v>
+        <v>0.858647584915161</v>
       </c>
       <c r="H1325" t="n">
         <v>204003</v>
@@ -38852,7 +38852,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G1327" t="n">
-        <v>0.829208254814148</v>
+        <v>0.829208314418793</v>
       </c>
       <c r="H1327" t="n">
         <v>144710</v>
@@ -38881,7 +38881,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1328" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H1328" t="n">
         <v>87547</v>
@@ -38910,7 +38910,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1329" t="n">
-        <v>0.813262045383453</v>
+        <v>0.813261926174164</v>
       </c>
       <c r="H1329" t="n">
         <v>142351</v>
@@ -38939,7 +38939,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1330" t="n">
-        <v>0.843927979469299</v>
+        <v>0.843928039073944</v>
       </c>
       <c r="H1330" t="n">
         <v>259824</v>
@@ -38968,7 +38968,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1331" t="n">
-        <v>0.837794721126556</v>
+        <v>0.837794780731201</v>
       </c>
       <c r="H1331" t="n">
         <v>112011</v>
@@ -39026,7 +39026,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1333" t="n">
-        <v>0.813262045383453</v>
+        <v>0.813261926174164</v>
       </c>
       <c r="H1333" t="n">
         <v>89577</v>
@@ -39055,7 +39055,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1334" t="n">
-        <v>0.851287841796875</v>
+        <v>0.85128778219223</v>
       </c>
       <c r="H1334" t="n">
         <v>98128</v>
@@ -39171,7 +39171,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1338" t="n">
-        <v>0.813262045383453</v>
+        <v>0.813261926174164</v>
       </c>
       <c r="H1338" t="n">
         <v>138577</v>
@@ -39229,7 +39229,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1340" t="n">
-        <v>0.843927979469299</v>
+        <v>0.843928039073944</v>
       </c>
       <c r="H1340" t="n">
         <v>106788</v>
@@ -39316,7 +39316,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G1343" t="n">
-        <v>0.842701256275177</v>
+        <v>0.842701315879822</v>
       </c>
       <c r="H1343" t="n">
         <v>92663</v>
@@ -39345,7 +39345,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G1344" t="n">
-        <v>0.842701256275177</v>
+        <v>0.842701315879822</v>
       </c>
       <c r="H1344" t="n">
         <v>50622</v>
@@ -39374,7 +39374,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1345" t="n">
-        <v>0.815715193748474</v>
+        <v>0.815715253353119</v>
       </c>
       <c r="H1345" t="n">
         <v>121011</v>
@@ -39432,7 +39432,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1347" t="n">
-        <v>0.803448855876923</v>
+        <v>0.803448796272278</v>
       </c>
       <c r="H1347" t="n">
         <v>156487</v>
@@ -39519,7 +39519,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1350" t="n">
-        <v>0.870914041996002</v>
+        <v>0.870913982391357</v>
       </c>
       <c r="H1350" t="n">
         <v>1164717</v>
@@ -39548,7 +39548,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1351" t="n">
-        <v>0.877047181129456</v>
+        <v>0.8770472407341</v>
       </c>
       <c r="H1351" t="n">
         <v>713545</v>
@@ -39606,7 +39606,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G1353" t="n">
-        <v>0.867234170436859</v>
+        <v>0.867234110832214</v>
       </c>
       <c r="H1353" t="n">
         <v>320259</v>
@@ -39635,7 +39635,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1354" t="n">
-        <v>0.890540242195129</v>
+        <v>0.890540301799774</v>
       </c>
       <c r="H1354" t="n">
         <v>435360</v>
@@ -39722,7 +39722,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1357" t="n">
-        <v>0.890540242195129</v>
+        <v>0.890540301799774</v>
       </c>
       <c r="H1357" t="n">
         <v>356070</v>
@@ -39751,7 +39751,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G1358" t="n">
-        <v>0.872140765190125</v>
+        <v>0.872140645980835</v>
       </c>
       <c r="H1358" t="n">
         <v>252612</v>
@@ -39780,7 +39780,7 @@
         <v>1.44599997997284</v>
       </c>
       <c r="G1359" t="n">
-        <v>0.886860370635986</v>
+        <v>0.886860251426697</v>
       </c>
       <c r="H1359" t="n">
         <v>147778</v>
@@ -39838,7 +39838,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G1361" t="n">
-        <v>0.875820517539978</v>
+        <v>0.875820577144623</v>
       </c>
       <c r="H1361" t="n">
         <v>121765</v>
@@ -39867,7 +39867,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1362" t="n">
-        <v>0.851287841796875</v>
+        <v>0.85128778219223</v>
       </c>
       <c r="H1362" t="n">
         <v>179758</v>
@@ -39983,7 +39983,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1366" t="n">
-        <v>0.843927979469299</v>
+        <v>0.843928039073944</v>
       </c>
       <c r="H1366" t="n">
         <v>141918</v>
@@ -40012,7 +40012,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1367" t="n">
-        <v>0.835341393947601</v>
+        <v>0.835341453552246</v>
       </c>
       <c r="H1367" t="n">
         <v>176992</v>
@@ -40070,7 +40070,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1369" t="n">
-        <v>0.837794721126556</v>
+        <v>0.837794780731201</v>
       </c>
       <c r="H1369" t="n">
         <v>104647</v>
@@ -40128,7 +40128,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G1371" t="n">
-        <v>0.826754987239838</v>
+        <v>0.826755046844482</v>
       </c>
       <c r="H1371" t="n">
         <v>82314</v>
@@ -40157,7 +40157,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G1372" t="n">
-        <v>0.826754987239838</v>
+        <v>0.826755046844482</v>
       </c>
       <c r="H1372" t="n">
         <v>167587</v>
@@ -40215,7 +40215,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G1374" t="n">
-        <v>0.861101031303406</v>
+        <v>0.861100912094116</v>
       </c>
       <c r="H1374" t="n">
         <v>158981</v>
@@ -40273,7 +40273,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G1376" t="n">
-        <v>0.861101031303406</v>
+        <v>0.861100912094116</v>
       </c>
       <c r="H1376" t="n">
         <v>98441</v>
@@ -40331,7 +40331,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1378" t="n">
-        <v>0.870914041996002</v>
+        <v>0.870913982391357</v>
       </c>
       <c r="H1378" t="n">
         <v>178932</v>
@@ -40360,7 +40360,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G1379" t="n">
-        <v>0.912619769573212</v>
+        <v>0.912619829177856</v>
       </c>
       <c r="H1379" t="n">
         <v>464389</v>
@@ -40389,7 +40389,7 @@
         <v>1.5</v>
       </c>
       <c r="G1380" t="n">
-        <v>0.919979631900787</v>
+        <v>0.919979512691498</v>
       </c>
       <c r="H1380" t="n">
         <v>1413263</v>
@@ -40418,7 +40418,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G1381" t="n">
-        <v>0.940832495689392</v>
+        <v>0.940832555294037</v>
       </c>
       <c r="H1381" t="n">
         <v>367278</v>
@@ -40447,7 +40447,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G1382" t="n">
-        <v>0.929792761802673</v>
+        <v>0.929792702198029</v>
       </c>
       <c r="H1382" t="n">
         <v>243296</v>
@@ -40505,7 +40505,7 @@
         <v>1.49399995803833</v>
       </c>
       <c r="G1384" t="n">
-        <v>0.916299641132355</v>
+        <v>0.916299700737</v>
       </c>
       <c r="H1384" t="n">
         <v>101556</v>
@@ -40534,7 +40534,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1385" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H1385" t="n">
         <v>939739</v>
@@ -40592,7 +40592,7 @@
         <v>1.5</v>
       </c>
       <c r="G1387" t="n">
-        <v>0.919979631900787</v>
+        <v>0.919979512691498</v>
       </c>
       <c r="H1387" t="n">
         <v>365772</v>
@@ -40621,7 +40621,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1388" t="n">
-        <v>0.890540242195129</v>
+        <v>0.890540301799774</v>
       </c>
       <c r="H1388" t="n">
         <v>318780</v>
@@ -40650,7 +40650,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G1389" t="n">
-        <v>0.92120623588562</v>
+        <v>0.921206176280975</v>
       </c>
       <c r="H1389" t="n">
         <v>395299</v>
@@ -40708,7 +40708,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1391" t="n">
-        <v>0.890540242195129</v>
+        <v>0.890540301799774</v>
       </c>
       <c r="H1391" t="n">
         <v>134123</v>
@@ -40737,7 +40737,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G1392" t="n">
-        <v>0.884407103061676</v>
+        <v>0.884407043457031</v>
       </c>
       <c r="H1392" t="n">
         <v>141898</v>
@@ -40766,7 +40766,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G1393" t="n">
-        <v>0.884407103061676</v>
+        <v>0.884407043457031</v>
       </c>
       <c r="H1393" t="n">
         <v>64747</v>
@@ -40795,7 +40795,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G1394" t="n">
-        <v>0.861101031303406</v>
+        <v>0.861100912094116</v>
       </c>
       <c r="H1394" t="n">
         <v>173193</v>
@@ -40824,7 +40824,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G1395" t="n">
-        <v>0.861101031303406</v>
+        <v>0.861100912094116</v>
       </c>
       <c r="H1395" t="n">
         <v>99567</v>
@@ -40853,7 +40853,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1396" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H1396" t="n">
         <v>305258</v>
@@ -40882,7 +40882,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1397" t="n">
-        <v>0.835341393947601</v>
+        <v>0.835341453552246</v>
       </c>
       <c r="H1397" t="n">
         <v>217994</v>
@@ -40940,7 +40940,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G1399" t="n">
-        <v>0.839021444320679</v>
+        <v>0.839021384716034</v>
       </c>
       <c r="H1399" t="n">
         <v>130209</v>
@@ -40969,7 +40969,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1400" t="n">
-        <v>0.82062178850174</v>
+        <v>0.820621848106384</v>
       </c>
       <c r="H1400" t="n">
         <v>314902</v>
@@ -41172,7 +41172,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1407" t="n">
-        <v>0.76051652431488</v>
+        <v>0.760516464710236</v>
       </c>
       <c r="H1407" t="n">
         <v>131819</v>
@@ -41201,7 +41201,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1408" t="n">
-        <v>0.754383325576782</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H1408" t="n">
         <v>366294</v>
@@ -41259,7 +41259,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G1410" t="n">
-        <v>0.737210273742676</v>
+        <v>0.737210333347321</v>
       </c>
       <c r="H1410" t="n">
         <v>156257</v>
@@ -41288,7 +41288,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1411" t="n">
-        <v>0.769102931022644</v>
+        <v>0.769102871417999</v>
       </c>
       <c r="H1411" t="n">
         <v>112866</v>
@@ -41375,7 +41375,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1414" t="n">
-        <v>0.858647644519806</v>
+        <v>0.858647584915161</v>
       </c>
       <c r="H1414" t="n">
         <v>1235294</v>
@@ -41433,7 +41433,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.852514445781708</v>
+        <v>0.852514386177063</v>
       </c>
       <c r="H1416" t="n">
         <v>491957</v>
@@ -41491,7 +41491,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G1418" t="n">
-        <v>0.839021444320679</v>
+        <v>0.839021384716034</v>
       </c>
       <c r="H1418" t="n">
         <v>356975</v>
@@ -41520,7 +41520,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1419" t="n">
-        <v>0.835341393947601</v>
+        <v>0.835341453552246</v>
       </c>
       <c r="H1419" t="n">
         <v>214498</v>
@@ -41607,7 +41607,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G1422" t="n">
-        <v>0.845154583454132</v>
+        <v>0.845154643058777</v>
       </c>
       <c r="H1422" t="n">
         <v>89185</v>
@@ -41636,7 +41636,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1423" t="n">
-        <v>0.851287841796875</v>
+        <v>0.85128778219223</v>
       </c>
       <c r="H1423" t="n">
         <v>61204</v>
@@ -41694,7 +41694,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G1425" t="n">
-        <v>0.857420980930328</v>
+        <v>0.857421040534973</v>
       </c>
       <c r="H1425" t="n">
         <v>391972</v>
@@ -41723,7 +41723,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1426" t="n">
-        <v>0.858647644519806</v>
+        <v>0.858647584915161</v>
       </c>
       <c r="H1426" t="n">
         <v>400318</v>
@@ -41781,7 +41781,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G1428" t="n">
-        <v>0.899126708507538</v>
+        <v>0.899126648902893</v>
       </c>
       <c r="H1428" t="n">
         <v>825243</v>
@@ -41868,7 +41868,7 @@
         <v>1.43400001525879</v>
       </c>
       <c r="G1431" t="n">
-        <v>0.879500508308411</v>
+        <v>0.879500567913055</v>
       </c>
       <c r="H1431" t="n">
         <v>165321</v>
@@ -41984,7 +41984,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G1435" t="n">
-        <v>0.842701256275177</v>
+        <v>0.842701315879822</v>
       </c>
       <c r="H1435" t="n">
         <v>133388</v>
@@ -42042,7 +42042,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1437" t="n">
-        <v>0.843927979469299</v>
+        <v>0.843928039073944</v>
       </c>
       <c r="H1437" t="n">
         <v>135208</v>
@@ -42071,7 +42071,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1438" t="n">
-        <v>0.852514445781708</v>
+        <v>0.852514386177063</v>
       </c>
       <c r="H1438" t="n">
         <v>170931</v>
@@ -42129,7 +42129,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1440" t="n">
-        <v>0.858647644519806</v>
+        <v>0.858647584915161</v>
       </c>
       <c r="H1440" t="n">
         <v>304587</v>
@@ -42158,7 +42158,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G1441" t="n">
-        <v>0.857420980930328</v>
+        <v>0.857421040534973</v>
       </c>
       <c r="H1441" t="n">
         <v>224445</v>
@@ -42187,7 +42187,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1442" t="n">
-        <v>0.870914041996002</v>
+        <v>0.870913982391357</v>
       </c>
       <c r="H1442" t="n">
         <v>114768</v>
@@ -42245,7 +42245,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1444" t="n">
-        <v>0.852514445781708</v>
+        <v>0.852514386177063</v>
       </c>
       <c r="H1444" t="n">
         <v>122371</v>
@@ -42303,7 +42303,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1446" t="n">
-        <v>0.837794721126556</v>
+        <v>0.837794780731201</v>
       </c>
       <c r="H1446" t="n">
         <v>129072</v>
@@ -42332,7 +42332,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G1447" t="n">
-        <v>0.82307505607605</v>
+        <v>0.823075115680695</v>
       </c>
       <c r="H1447" t="n">
         <v>145648</v>
@@ -42448,7 +42448,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G1451" t="n">
-        <v>0.82307505607605</v>
+        <v>0.823075115680695</v>
       </c>
       <c r="H1451" t="n">
         <v>132905</v>
@@ -42506,7 +42506,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1453" t="n">
-        <v>0.813262045383453</v>
+        <v>0.813261926174164</v>
       </c>
       <c r="H1453" t="n">
         <v>114904</v>
@@ -42564,7 +42564,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1455" t="n">
-        <v>0.772782802581787</v>
+        <v>0.772782921791077</v>
       </c>
       <c r="H1455" t="n">
         <v>167953</v>
@@ -42593,7 +42593,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1456" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1456" t="n">
         <v>154869</v>
@@ -42651,7 +42651,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1458" t="n">
-        <v>0.813262045383453</v>
+        <v>0.813261926174164</v>
       </c>
       <c r="H1458" t="n">
         <v>135410</v>
@@ -42680,7 +42680,7 @@
         <v>1.33200001716614</v>
       </c>
       <c r="G1459" t="n">
-        <v>0.816941916942596</v>
+        <v>0.816941857337952</v>
       </c>
       <c r="H1459" t="n">
         <v>73758</v>
@@ -42709,7 +42709,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G1460" t="n">
-        <v>0.79976898431778</v>
+        <v>0.799768924713135</v>
       </c>
       <c r="H1460" t="n">
         <v>158559</v>
@@ -42738,7 +42738,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1461" t="n">
-        <v>0.803448855876923</v>
+        <v>0.803448796272278</v>
       </c>
       <c r="H1461" t="n">
         <v>54619</v>
@@ -42825,7 +42825,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1464" t="n">
-        <v>0.788729250431061</v>
+        <v>0.788729190826416</v>
       </c>
       <c r="H1464" t="n">
         <v>91651</v>
@@ -42970,7 +42970,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1469" t="n">
-        <v>0.788729250431061</v>
+        <v>0.788729190826416</v>
       </c>
       <c r="H1469" t="n">
         <v>41589</v>
@@ -42999,7 +42999,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1470" t="n">
-        <v>0.809582054615021</v>
+        <v>0.809582114219666</v>
       </c>
       <c r="H1470" t="n">
         <v>109019</v>
@@ -43028,7 +43028,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1471" t="n">
-        <v>0.815715193748474</v>
+        <v>0.815715253353119</v>
       </c>
       <c r="H1471" t="n">
         <v>212372</v>
@@ -43115,7 +43115,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1474" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H1474" t="n">
         <v>123829</v>
@@ -43144,7 +43144,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G1475" t="n">
-        <v>0.829208254814148</v>
+        <v>0.829208314418793</v>
       </c>
       <c r="H1475" t="n">
         <v>97695</v>
@@ -43173,7 +43173,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1476" t="n">
-        <v>0.824301660060883</v>
+        <v>0.824301719665527</v>
       </c>
       <c r="H1476" t="n">
         <v>93692</v>
@@ -43202,7 +43202,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1477" t="n">
-        <v>0.85619443655014</v>
+        <v>0.856194376945496</v>
       </c>
       <c r="H1477" t="n">
         <v>332826</v>
@@ -43231,7 +43231,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1478" t="n">
-        <v>0.851287841796875</v>
+        <v>0.85128778219223</v>
       </c>
       <c r="H1478" t="n">
         <v>1035445</v>
@@ -43260,7 +43260,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1479" t="n">
-        <v>0.883180439472198</v>
+        <v>0.883180379867554</v>
       </c>
       <c r="H1479" t="n">
         <v>900272</v>
@@ -43347,7 +43347,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1482" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H1482" t="n">
         <v>185548</v>
@@ -43376,7 +43376,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1483" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H1483" t="n">
         <v>140243</v>
@@ -43405,7 +43405,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1484" t="n">
-        <v>0.840247988700867</v>
+        <v>0.840248048305511</v>
       </c>
       <c r="H1484" t="n">
         <v>295922</v>
@@ -43463,7 +43463,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1486" t="n">
-        <v>0.824301660060883</v>
+        <v>0.824301719665527</v>
       </c>
       <c r="H1486" t="n">
         <v>109288</v>
@@ -43492,7 +43492,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G1487" t="n">
-        <v>0.819395184516907</v>
+        <v>0.819395124912262</v>
       </c>
       <c r="H1487" t="n">
         <v>188308</v>
@@ -43550,7 +43550,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1489" t="n">
-        <v>0.824301660060883</v>
+        <v>0.824301719665527</v>
       </c>
       <c r="H1489" t="n">
         <v>73053</v>
@@ -43666,7 +43666,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1493" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1493" t="n">
         <v>257678</v>
@@ -43695,7 +43695,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1494" t="n">
-        <v>0.824301660060883</v>
+        <v>0.824301719665527</v>
       </c>
       <c r="H1494" t="n">
         <v>265076</v>
@@ -43724,7 +43724,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G1495" t="n">
-        <v>0.82307505607605</v>
+        <v>0.823075115680695</v>
       </c>
       <c r="H1495" t="n">
         <v>151385</v>
@@ -43753,7 +43753,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1496" t="n">
-        <v>0.821848511695862</v>
+        <v>0.821848452091217</v>
       </c>
       <c r="H1496" t="n">
         <v>80356</v>
@@ -43782,7 +43782,7 @@
         <v>1.33200001716614</v>
       </c>
       <c r="G1497" t="n">
-        <v>0.816941916942596</v>
+        <v>0.816941857337952</v>
       </c>
       <c r="H1497" t="n">
         <v>106759</v>
@@ -43811,7 +43811,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1498" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1498" t="n">
         <v>352664</v>
@@ -43840,7 +43840,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1499" t="n">
-        <v>0.809582054615021</v>
+        <v>0.809582114219666</v>
       </c>
       <c r="H1499" t="n">
         <v>101101</v>
@@ -43869,7 +43869,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G1500" t="n">
-        <v>0.79976898431778</v>
+        <v>0.799768924713135</v>
       </c>
       <c r="H1500" t="n">
         <v>70839</v>
@@ -43898,7 +43898,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1501" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1501" t="n">
         <v>164805</v>
@@ -43927,7 +43927,7 @@
         <v>1.2940000295639</v>
       </c>
       <c r="G1502" t="n">
-        <v>0.793635725975037</v>
+        <v>0.793635785579681</v>
       </c>
       <c r="H1502" t="n">
         <v>60756</v>
@@ -43956,7 +43956,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1503" t="n">
-        <v>0.76051652431488</v>
+        <v>0.760516464710236</v>
       </c>
       <c r="H1503" t="n">
         <v>380395</v>
@@ -44014,7 +44014,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1505" t="n">
-        <v>0.735983729362488</v>
+        <v>0.735983669757843</v>
       </c>
       <c r="H1505" t="n">
         <v>147647</v>
@@ -44043,7 +44043,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1506" t="n">
-        <v>0.743343591690063</v>
+        <v>0.743343532085419</v>
       </c>
       <c r="H1506" t="n">
         <v>53247</v>
@@ -44072,7 +44072,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G1507" t="n">
-        <v>0.733530402183533</v>
+        <v>0.733530342578888</v>
       </c>
       <c r="H1507" t="n">
         <v>126855</v>
@@ -44101,7 +44101,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G1508" t="n">
-        <v>0.728623807430267</v>
+        <v>0.728623867034912</v>
       </c>
       <c r="H1508" t="n">
         <v>78456</v>
@@ -44130,7 +44130,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G1509" t="n">
-        <v>0.722490608692169</v>
+        <v>0.722490668296814</v>
       </c>
       <c r="H1509" t="n">
         <v>119287</v>
@@ -44188,7 +44188,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1511" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1511" t="n">
         <v>77419</v>
@@ -44217,7 +44217,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1512" t="n">
-        <v>0.743343591690063</v>
+        <v>0.743343532085419</v>
       </c>
       <c r="H1512" t="n">
         <v>124927</v>
@@ -44246,7 +44246,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1513" t="n">
-        <v>0.743343591690063</v>
+        <v>0.743343532085419</v>
       </c>
       <c r="H1513" t="n">
         <v>67036</v>
@@ -44275,7 +44275,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1514" t="n">
-        <v>0.735983729362488</v>
+        <v>0.735983669757843</v>
       </c>
       <c r="H1514" t="n">
         <v>158378</v>
@@ -44333,7 +44333,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1516" t="n">
-        <v>0.735983729362488</v>
+        <v>0.735983669757843</v>
       </c>
       <c r="H1516" t="n">
         <v>141495</v>
@@ -44420,7 +44420,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G1519" t="n">
-        <v>0.728623807430267</v>
+        <v>0.728623867034912</v>
       </c>
       <c r="H1519" t="n">
         <v>188721</v>
@@ -44507,7 +44507,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1522" t="n">
-        <v>0.724943935871124</v>
+        <v>0.724943995475769</v>
       </c>
       <c r="H1522" t="n">
         <v>49440</v>
@@ -44536,7 +44536,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1523" t="n">
-        <v>0.726170539855957</v>
+        <v>0.726170599460602</v>
       </c>
       <c r="H1523" t="n">
         <v>89361</v>
@@ -44623,7 +44623,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1526" t="n">
-        <v>0.724943935871124</v>
+        <v>0.724943995475769</v>
       </c>
       <c r="H1526" t="n">
         <v>112221</v>
@@ -44681,7 +44681,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1528" t="n">
-        <v>0.76051652431488</v>
+        <v>0.760516464710236</v>
       </c>
       <c r="H1528" t="n">
         <v>120544</v>
@@ -44710,7 +44710,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1529" t="n">
-        <v>0.76051652431488</v>
+        <v>0.760516464710236</v>
       </c>
       <c r="H1529" t="n">
         <v>82688</v>
@@ -44739,7 +44739,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G1530" t="n">
-        <v>0.758063197135925</v>
+        <v>0.758063137531281</v>
       </c>
       <c r="H1530" t="n">
         <v>114962</v>
@@ -44913,7 +44913,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1536" t="n">
-        <v>0.788729250431061</v>
+        <v>0.788729190826416</v>
       </c>
       <c r="H1536" t="n">
         <v>27795</v>
@@ -44942,7 +44942,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1537" t="n">
-        <v>0.772782802581787</v>
+        <v>0.772782921791077</v>
       </c>
       <c r="H1537" t="n">
         <v>36607</v>
@@ -45000,7 +45000,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1539" t="n">
-        <v>0.762969791889191</v>
+        <v>0.762969732284546</v>
       </c>
       <c r="H1539" t="n">
         <v>100515</v>
@@ -45029,7 +45029,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1540" t="n">
-        <v>0.775236129760742</v>
+        <v>0.775236248970032</v>
       </c>
       <c r="H1540" t="n">
         <v>42391</v>
@@ -45058,7 +45058,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G1541" t="n">
-        <v>0.756836473941803</v>
+        <v>0.756836533546448</v>
       </c>
       <c r="H1541" t="n">
         <v>128174</v>
@@ -45116,7 +45116,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1543" t="n">
-        <v>0.72985053062439</v>
+        <v>0.729850471019745</v>
       </c>
       <c r="H1543" t="n">
         <v>155144</v>
@@ -45145,7 +45145,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1544" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1544" t="n">
         <v>23434</v>
@@ -45203,7 +45203,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G1546" t="n">
-        <v>0.728623807430267</v>
+        <v>0.728623867034912</v>
       </c>
       <c r="H1546" t="n">
         <v>83407</v>
@@ -45232,7 +45232,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1547" t="n">
-        <v>0.7323037981987</v>
+        <v>0.732303738594055</v>
       </c>
       <c r="H1547" t="n">
         <v>79230</v>
@@ -45261,7 +45261,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1548" t="n">
-        <v>0.735983729362488</v>
+        <v>0.735983669757843</v>
       </c>
       <c r="H1548" t="n">
         <v>66394</v>
@@ -45290,7 +45290,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1549" t="n">
-        <v>0.735983729362488</v>
+        <v>0.735983669757843</v>
       </c>
       <c r="H1549" t="n">
         <v>85697</v>
@@ -45319,7 +45319,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1550" t="n">
-        <v>0.754383325576782</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H1550" t="n">
         <v>123629</v>
@@ -45377,7 +45377,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1552" t="n">
-        <v>0.726170539855957</v>
+        <v>0.726170599460602</v>
       </c>
       <c r="H1552" t="n">
         <v>76444</v>
@@ -45435,7 +45435,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1554" t="n">
-        <v>0.739663541316986</v>
+        <v>0.739663600921631</v>
       </c>
       <c r="H1554" t="n">
         <v>60612</v>
@@ -45464,7 +45464,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G1555" t="n">
-        <v>0.721264064311981</v>
+        <v>0.721264004707336</v>
       </c>
       <c r="H1555" t="n">
         <v>164015</v>
@@ -45493,7 +45493,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G1556" t="n">
-        <v>0.728623807430267</v>
+        <v>0.728623867034912</v>
       </c>
       <c r="H1556" t="n">
         <v>81679</v>
@@ -45580,7 +45580,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G1559" t="n">
-        <v>0.728623807430267</v>
+        <v>0.728623867034912</v>
       </c>
       <c r="H1559" t="n">
         <v>88379</v>
@@ -45638,7 +45638,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1561" t="n">
-        <v>0.712677538394928</v>
+        <v>0.712677478790283</v>
       </c>
       <c r="H1561" t="n">
         <v>157256</v>
@@ -45783,7 +45783,7 @@
         <v>1.13199996948242</v>
       </c>
       <c r="G1566" t="n">
-        <v>0.694277882575989</v>
+        <v>0.694277942180634</v>
       </c>
       <c r="H1566" t="n">
         <v>402246</v>
@@ -45928,7 +45928,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1571" t="n">
-        <v>0.517641842365265</v>
+        <v>0.51764190196991</v>
       </c>
       <c r="H1571" t="n">
         <v>472172</v>
@@ -45957,7 +45957,7 @@
         <v>0.788999974727631</v>
       </c>
       <c r="G1572" t="n">
-        <v>0.483909249305725</v>
+        <v>0.483909279108047</v>
       </c>
       <c r="H1572" t="n">
         <v>431253</v>
@@ -45986,7 +45986,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1573" t="n">
-        <v>0.480842679738998</v>
+        <v>0.480842649936676</v>
       </c>
       <c r="H1573" t="n">
         <v>174707</v>
@@ -46015,7 +46015,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G1574" t="n">
-        <v>0.52009516954422</v>
+        <v>0.520095109939575</v>
       </c>
       <c r="H1574" t="n">
         <v>202197</v>
@@ -46044,7 +46044,7 @@
         <v>0.802999973297119</v>
       </c>
       <c r="G1575" t="n">
-        <v>0.492495745420456</v>
+        <v>0.492495715618134</v>
       </c>
       <c r="H1575" t="n">
         <v>323492</v>
@@ -46160,7 +46160,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1579" t="n">
-        <v>0.53849470615387</v>
+        <v>0.538494765758514</v>
       </c>
       <c r="H1579" t="n">
         <v>227555</v>
@@ -46189,7 +46189,7 @@
         <v>0.888999998569489</v>
       </c>
       <c r="G1580" t="n">
-        <v>0.545241296291351</v>
+        <v>0.545241236686707</v>
       </c>
       <c r="H1580" t="n">
         <v>91587</v>
@@ -46247,7 +46247,7 @@
         <v>0.897000014781952</v>
       </c>
       <c r="G1582" t="n">
-        <v>0.550147831439972</v>
+        <v>0.550147771835327</v>
       </c>
       <c r="H1582" t="n">
         <v>225480</v>
@@ -46305,7 +46305,7 @@
         <v>0.879000008106232</v>
       </c>
       <c r="G1584" t="n">
-        <v>0.539108037948608</v>
+        <v>0.539108097553253</v>
       </c>
       <c r="H1584" t="n">
         <v>166972</v>
@@ -46566,7 +46566,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G1593" t="n">
-        <v>0.536041438579559</v>
+        <v>0.536041498184204</v>
       </c>
       <c r="H1593" t="n">
         <v>57617</v>
@@ -46595,7 +46595,7 @@
         <v>0.861000001430511</v>
       </c>
       <c r="G1594" t="n">
-        <v>0.528068244457245</v>
+        <v>0.52806830406189</v>
       </c>
       <c r="H1594" t="n">
         <v>123522</v>
@@ -46624,7 +46624,7 @@
         <v>0.837000012397766</v>
       </c>
       <c r="G1595" t="n">
-        <v>0.513348639011383</v>
+        <v>0.513348579406738</v>
       </c>
       <c r="H1595" t="n">
         <v>183181</v>
@@ -46653,7 +46653,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1596" t="n">
-        <v>0.510282039642334</v>
+        <v>0.510281980037689</v>
       </c>
       <c r="H1596" t="n">
         <v>140867</v>
@@ -46682,7 +46682,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1597" t="n">
-        <v>0.515188574790955</v>
+        <v>0.51518851518631</v>
       </c>
       <c r="H1597" t="n">
         <v>250652</v>
@@ -46711,7 +46711,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1598" t="n">
-        <v>0.517641842365265</v>
+        <v>0.51764190196991</v>
       </c>
       <c r="H1598" t="n">
         <v>186829</v>
@@ -47001,7 +47001,7 @@
         <v>0.861000001430511</v>
       </c>
       <c r="G1608" t="n">
-        <v>0.528068244457245</v>
+        <v>0.52806830406189</v>
       </c>
       <c r="H1608" t="n">
         <v>430668</v>
@@ -47030,7 +47030,7 @@
         <v>0.859000027179718</v>
       </c>
       <c r="G1609" t="n">
-        <v>0.526841640472412</v>
+        <v>0.526841700077057</v>
       </c>
       <c r="H1609" t="n">
         <v>270347</v>
@@ -47059,7 +47059,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1610" t="n">
-        <v>0.533588171005249</v>
+        <v>0.533588111400604</v>
       </c>
       <c r="H1610" t="n">
         <v>109591</v>
@@ -47146,7 +47146,7 @@
         <v>0.830999970436096</v>
       </c>
       <c r="G1613" t="n">
-        <v>0.509668707847595</v>
+        <v>0.50966864824295</v>
       </c>
       <c r="H1613" t="n">
         <v>203802</v>
@@ -47175,7 +47175,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1614" t="n">
-        <v>0.517641842365265</v>
+        <v>0.51764190196991</v>
       </c>
       <c r="H1614" t="n">
         <v>160874</v>
@@ -47204,7 +47204,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1615" t="n">
-        <v>0.509055376052856</v>
+        <v>0.509055316448212</v>
       </c>
       <c r="H1615" t="n">
         <v>102044</v>
@@ -47233,7 +47233,7 @@
         <v>0.824999988079071</v>
       </c>
       <c r="G1616" t="n">
-        <v>0.505988836288452</v>
+        <v>0.505988776683807</v>
       </c>
       <c r="H1616" t="n">
         <v>195866</v>
@@ -47262,7 +47262,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G1617" t="n">
-        <v>0.52009516954422</v>
+        <v>0.520095109939575</v>
       </c>
       <c r="H1617" t="n">
         <v>69792</v>
@@ -47291,7 +47291,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1618" t="n">
-        <v>0.509055376052856</v>
+        <v>0.509055316448212</v>
       </c>
       <c r="H1618" t="n">
         <v>49549</v>
@@ -47320,7 +47320,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1619" t="n">
-        <v>0.509055376052856</v>
+        <v>0.509055316448212</v>
       </c>
       <c r="H1619" t="n">
         <v>95950</v>
@@ -47349,7 +47349,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G1620" t="n">
-        <v>0.519481778144836</v>
+        <v>0.519481837749481</v>
       </c>
       <c r="H1620" t="n">
         <v>106747</v>
@@ -47407,7 +47407,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1622" t="n">
-        <v>0.533588171005249</v>
+        <v>0.533588111400604</v>
       </c>
       <c r="H1622" t="n">
         <v>114805</v>
@@ -47610,7 +47610,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1629" t="n">
-        <v>0.572227299213409</v>
+        <v>0.572227358818054</v>
       </c>
       <c r="H1629" t="n">
         <v>80085</v>
@@ -47726,7 +47726,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G1633" t="n">
-        <v>0.647665619850159</v>
+        <v>0.647665679454803</v>
       </c>
       <c r="H1633" t="n">
         <v>410308</v>
@@ -47784,7 +47784,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1635" t="n">
-        <v>0.625586152076721</v>
+        <v>0.625586092472076</v>
       </c>
       <c r="H1635" t="n">
         <v>75358</v>
@@ -47842,7 +47842,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G1637" t="n">
-        <v>0.628039479255676</v>
+        <v>0.628039419651031</v>
       </c>
       <c r="H1637" t="n">
         <v>80758</v>
@@ -47929,7 +47929,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1640" t="n">
-        <v>0.545854568481445</v>
+        <v>0.545854508876801</v>
       </c>
       <c r="H1640" t="n">
         <v>111925</v>
@@ -48016,7 +48016,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1643" t="n">
-        <v>0.533588171005249</v>
+        <v>0.533588111400604</v>
       </c>
       <c r="H1643" t="n">
         <v>53610</v>
@@ -48074,7 +48074,7 @@
         <v>0.898999989032745</v>
       </c>
       <c r="G1645" t="n">
-        <v>0.551374435424805</v>
+        <v>0.551374495029449</v>
       </c>
       <c r="H1645" t="n">
         <v>61905</v>
@@ -48103,7 +48103,7 @@
         <v>0.887000024318695</v>
       </c>
       <c r="G1646" t="n">
-        <v>0.544014632701874</v>
+        <v>0.544014573097229</v>
       </c>
       <c r="H1646" t="n">
         <v>120588</v>
@@ -48161,7 +48161,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G1648" t="n">
-        <v>0.547081232070923</v>
+        <v>0.547081172466278</v>
       </c>
       <c r="H1648" t="n">
         <v>67414</v>
@@ -48190,7 +48190,7 @@
         <v>0.898999989032745</v>
       </c>
       <c r="G1649" t="n">
-        <v>0.551374435424805</v>
+        <v>0.551374495029449</v>
       </c>
       <c r="H1649" t="n">
         <v>7510</v>
@@ -48248,7 +48248,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1651" t="n">
-        <v>0.533588171005249</v>
+        <v>0.533588111400604</v>
       </c>
       <c r="H1651" t="n">
         <v>72124</v>
@@ -48306,7 +48306,7 @@
         <v>0.824999988079071</v>
       </c>
       <c r="G1653" t="n">
-        <v>0.505988836288452</v>
+        <v>0.505988776683807</v>
       </c>
       <c r="H1653" t="n">
         <v>167323</v>
@@ -48364,7 +48364,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G1655" t="n">
-        <v>0.512121975421906</v>
+        <v>0.512121915817261</v>
       </c>
       <c r="H1655" t="n">
         <v>31287</v>
@@ -48422,7 +48422,7 @@
         <v>0.788999974727631</v>
       </c>
       <c r="G1657" t="n">
-        <v>0.483909249305725</v>
+        <v>0.483909279108047</v>
       </c>
       <c r="H1657" t="n">
         <v>56680</v>
@@ -48509,7 +48509,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1660" t="n">
-        <v>0.509055376052856</v>
+        <v>0.509055316448212</v>
       </c>
       <c r="H1660" t="n">
         <v>15200</v>
@@ -48596,7 +48596,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1663" t="n">
-        <v>0.479616075754166</v>
+        <v>0.479616045951843</v>
       </c>
       <c r="H1663" t="n">
         <v>84703</v>
@@ -48625,7 +48625,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1664" t="n">
-        <v>0.482069313526154</v>
+        <v>0.482069283723831</v>
       </c>
       <c r="H1664" t="n">
         <v>41158</v>
@@ -48654,7 +48654,7 @@
         <v>0.785000026226044</v>
       </c>
       <c r="G1665" t="n">
-        <v>0.481456011533737</v>
+        <v>0.481455981731415</v>
       </c>
       <c r="H1665" t="n">
         <v>33125</v>
@@ -48683,7 +48683,7 @@
         <v>0.787000000476837</v>
       </c>
       <c r="G1666" t="n">
-        <v>0.482682645320892</v>
+        <v>0.48268261551857</v>
       </c>
       <c r="H1666" t="n">
         <v>86039</v>
@@ -48741,7 +48741,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1668" t="n">
-        <v>0.480842679738998</v>
+        <v>0.480842649936676</v>
       </c>
       <c r="H1668" t="n">
         <v>18752</v>
@@ -48770,7 +48770,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1669" t="n">
-        <v>0.509055376052856</v>
+        <v>0.509055316448212</v>
       </c>
       <c r="H1669" t="n">
         <v>54574</v>
@@ -48799,7 +48799,7 @@
         <v>0.861000001430511</v>
       </c>
       <c r="G1670" t="n">
-        <v>0.528068244457245</v>
+        <v>0.52806830406189</v>
       </c>
       <c r="H1670" t="n">
         <v>412769</v>
@@ -48828,7 +48828,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G1671" t="n">
-        <v>0.559347629547119</v>
+        <v>0.559347569942474</v>
       </c>
       <c r="H1671" t="n">
         <v>189010</v>
@@ -48857,7 +48857,7 @@
         <v>0.930999994277954</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.571000635623932</v>
+        <v>0.571000695228577</v>
       </c>
       <c r="H1672" t="n">
         <v>119126</v>
@@ -49147,7 +49147,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G1682" t="n">
-        <v>0.548921167850494</v>
+        <v>0.54892110824585</v>
       </c>
       <c r="H1682" t="n">
         <v>7867</v>
@@ -49176,7 +49176,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1683" t="n">
-        <v>0.551987707614899</v>
+        <v>0.551987767219543</v>
       </c>
       <c r="H1683" t="n">
         <v>11524</v>
@@ -49292,7 +49292,7 @@
         <v>0.898999989032745</v>
       </c>
       <c r="G1687" t="n">
-        <v>0.551374435424805</v>
+        <v>0.551374495029449</v>
       </c>
       <c r="H1687" t="n">
         <v>12702</v>
@@ -49321,7 +49321,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1688" t="n">
-        <v>0.53849470615387</v>
+        <v>0.538494765758514</v>
       </c>
       <c r="H1688" t="n">
         <v>37248</v>
@@ -49379,7 +49379,7 @@
         <v>0.898999989032745</v>
       </c>
       <c r="G1690" t="n">
-        <v>0.551374435424805</v>
+        <v>0.551374495029449</v>
       </c>
       <c r="H1690" t="n">
         <v>65957</v>
@@ -49408,7 +49408,7 @@
         <v>0.887000024318695</v>
       </c>
       <c r="G1691" t="n">
-        <v>0.544014632701874</v>
+        <v>0.544014573097229</v>
       </c>
       <c r="H1691" t="n">
         <v>9721</v>
@@ -49553,7 +49553,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1696" t="n">
-        <v>0.515188574790955</v>
+        <v>0.51518851518631</v>
       </c>
       <c r="H1696" t="n">
         <v>32822</v>
@@ -49611,7 +49611,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1698" t="n">
-        <v>0.509055376052856</v>
+        <v>0.509055316448212</v>
       </c>
       <c r="H1698" t="n">
         <v>13347</v>
@@ -49698,7 +49698,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1701" t="n">
-        <v>0.490655809640884</v>
+        <v>0.490655779838562</v>
       </c>
       <c r="H1701" t="n">
         <v>34760</v>
@@ -49727,7 +49727,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1702" t="n">
-        <v>0.485749244689941</v>
+        <v>0.485749274492264</v>
       </c>
       <c r="H1702" t="n">
         <v>38092</v>
@@ -49756,7 +49756,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1703" t="n">
-        <v>0.485749244689941</v>
+        <v>0.485749274492264</v>
       </c>
       <c r="H1703" t="n">
         <v>129729</v>
@@ -49814,7 +49814,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1705" t="n">
-        <v>0.484522581100464</v>
+        <v>0.484522610902786</v>
       </c>
       <c r="H1705" t="n">
         <v>232506</v>
@@ -49843,7 +49843,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1706" t="n">
-        <v>0.486975878477097</v>
+        <v>0.486975908279419</v>
       </c>
       <c r="H1706" t="n">
         <v>180690</v>
@@ -49959,7 +49959,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1710" t="n">
-        <v>0.472256183624268</v>
+        <v>0.47225621342659</v>
       </c>
       <c r="H1710" t="n">
         <v>25393</v>
@@ -49988,7 +49988,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G1711" t="n">
-        <v>0.456923216581345</v>
+        <v>0.456923186779022</v>
       </c>
       <c r="H1711" t="n">
         <v>131826</v>
@@ -50017,7 +50017,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1712" t="n">
-        <v>0.453243315219879</v>
+        <v>0.453243285417557</v>
       </c>
       <c r="H1712" t="n">
         <v>148619</v>
@@ -50075,7 +50075,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1714" t="n">
-        <v>0.435457020998001</v>
+        <v>0.435456991195679</v>
       </c>
       <c r="H1714" t="n">
         <v>60877</v>
@@ -50104,7 +50104,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1715" t="n">
-        <v>0.437910258769989</v>
+        <v>0.437910288572311</v>
       </c>
       <c r="H1715" t="n">
         <v>34096</v>
@@ -50133,7 +50133,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1716" t="n">
-        <v>0.447723418474197</v>
+        <v>0.447723388671875</v>
       </c>
       <c r="H1716" t="n">
         <v>26655</v>
@@ -50191,7 +50191,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1718" t="n">
-        <v>0.435457020998001</v>
+        <v>0.435456991195679</v>
       </c>
       <c r="H1718" t="n">
         <v>11872</v>
@@ -50249,7 +50249,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G1720" t="n">
-        <v>0.438523590564728</v>
+        <v>0.43852362036705</v>
       </c>
       <c r="H1720" t="n">
         <v>78867</v>
@@ -50307,7 +50307,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1722" t="n">
-        <v>0.42809721827507</v>
+        <v>0.428097188472748</v>
       </c>
       <c r="H1722" t="n">
         <v>9212</v>
@@ -50336,7 +50336,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1723" t="n">
-        <v>0.429323822259903</v>
+        <v>0.429323792457581</v>
       </c>
       <c r="H1723" t="n">
         <v>12024</v>
@@ -50365,7 +50365,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1724" t="n">
-        <v>0.414604127407074</v>
+        <v>0.414604157209396</v>
       </c>
       <c r="H1724" t="n">
         <v>120285</v>
@@ -50394,7 +50394,7 @@
         <v>0.66100001335144</v>
       </c>
       <c r="G1725" t="n">
-        <v>0.405404388904572</v>
+        <v>0.405404359102249</v>
       </c>
       <c r="H1725" t="n">
         <v>212060</v>
@@ -50452,7 +50452,7 @@
         <v>0.686999976634979</v>
       </c>
       <c r="G1727" t="n">
-        <v>0.421350628137589</v>
+        <v>0.421350657939911</v>
       </c>
       <c r="H1727" t="n">
         <v>124750</v>
@@ -50481,7 +50481,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1728" t="n">
-        <v>0.429323822259903</v>
+        <v>0.429323792457581</v>
       </c>
       <c r="H1728" t="n">
         <v>149076</v>
@@ -50597,7 +50597,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1732" t="n">
-        <v>0.490655809640884</v>
+        <v>0.490655779838562</v>
       </c>
       <c r="H1732" t="n">
         <v>498028</v>
@@ -50742,7 +50742,7 @@
         <v>0.842999994754791</v>
       </c>
       <c r="G1737" t="n">
-        <v>0.517028510570526</v>
+        <v>0.517028570175171</v>
       </c>
       <c r="H1737" t="n">
         <v>94738</v>
@@ -50771,7 +50771,7 @@
         <v>0.837000012397766</v>
       </c>
       <c r="G1738" t="n">
-        <v>0.513348639011383</v>
+        <v>0.513348579406738</v>
       </c>
       <c r="H1738" t="n">
         <v>42431</v>
@@ -50800,7 +50800,7 @@
         <v>0.824999988079071</v>
       </c>
       <c r="G1739" t="n">
-        <v>0.505988836288452</v>
+        <v>0.505988776683807</v>
       </c>
       <c r="H1739" t="n">
         <v>63148</v>
@@ -50858,7 +50858,7 @@
         <v>0.837000012397766</v>
       </c>
       <c r="G1741" t="n">
-        <v>0.513348639011383</v>
+        <v>0.513348579406738</v>
       </c>
       <c r="H1741" t="n">
         <v>43098</v>
@@ -50974,7 +50974,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1745" t="n">
-        <v>0.515188574790955</v>
+        <v>0.51518851518631</v>
       </c>
       <c r="H1745" t="n">
         <v>39782</v>
@@ -51003,7 +51003,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1746" t="n">
-        <v>0.515188574790955</v>
+        <v>0.51518851518631</v>
       </c>
       <c r="H1746" t="n">
         <v>29578</v>
@@ -51032,7 +51032,7 @@
         <v>0.859000027179718</v>
       </c>
       <c r="G1747" t="n">
-        <v>0.526841640472412</v>
+        <v>0.526841700077057</v>
       </c>
       <c r="H1747" t="n">
         <v>85973</v>
@@ -51235,7 +51235,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1754" t="n">
-        <v>0.542174637317657</v>
+        <v>0.542174696922302</v>
       </c>
       <c r="H1754" t="n">
         <v>75730</v>
@@ -51438,7 +51438,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1761" t="n">
-        <v>0.545854568481445</v>
+        <v>0.545854508876801</v>
       </c>
       <c r="H1761" t="n">
         <v>29697</v>
@@ -51554,7 +51554,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G1765" t="n">
-        <v>0.519481778144836</v>
+        <v>0.519481837749481</v>
       </c>
       <c r="H1765" t="n">
         <v>185940</v>
@@ -51583,7 +51583,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G1766" t="n">
-        <v>0.519481778144836</v>
+        <v>0.519481837749481</v>
       </c>
       <c r="H1766" t="n">
         <v>16972</v>
@@ -51641,7 +51641,7 @@
         <v>0.845000028610229</v>
       </c>
       <c r="G1768" t="n">
-        <v>0.518255174160004</v>
+        <v>0.518255233764648</v>
       </c>
       <c r="H1768" t="n">
         <v>61066</v>
@@ -51670,7 +51670,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1769" t="n">
-        <v>0.518868505954742</v>
+        <v>0.518868565559387</v>
       </c>
       <c r="H1769" t="n">
         <v>228286</v>
@@ -51815,7 +51815,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1774" t="n">
-        <v>0.533588171005249</v>
+        <v>0.533588111400604</v>
       </c>
       <c r="H1774" t="n">
         <v>61411</v>
@@ -51931,7 +51931,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G1778" t="n">
-        <v>0.567934095859528</v>
+        <v>0.567934036254883</v>
       </c>
       <c r="H1778" t="n">
         <v>118464</v>
@@ -52163,7 +52163,7 @@
         <v>0.944999992847443</v>
       </c>
       <c r="G1786" t="n">
-        <v>0.579587161540985</v>
+        <v>0.57958710193634</v>
       </c>
       <c r="H1786" t="n">
         <v>65962</v>
@@ -52250,7 +52250,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G1789" t="n">
-        <v>0.624359488487244</v>
+        <v>0.624359548091888</v>
       </c>
       <c r="H1789" t="n">
         <v>244828</v>
@@ -52337,7 +52337,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1792" t="n">
-        <v>0.656252145767212</v>
+        <v>0.656252205371857</v>
       </c>
       <c r="H1792" t="n">
         <v>246471</v>
@@ -52395,7 +52395,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1794" t="n">
-        <v>0.674651682376862</v>
+        <v>0.674651741981506</v>
       </c>
       <c r="H1794" t="n">
         <v>184077</v>
@@ -52453,7 +52453,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1796" t="n">
-        <v>0.662385284900665</v>
+        <v>0.66238534450531</v>
       </c>
       <c r="H1796" t="n">
         <v>92197</v>
@@ -52511,7 +52511,7 @@
         <v>1.09200000762939</v>
       </c>
       <c r="G1798" t="n">
-        <v>0.669745147228241</v>
+        <v>0.669745206832886</v>
       </c>
       <c r="H1798" t="n">
         <v>77905</v>
@@ -52540,7 +52540,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1799" t="n">
-        <v>0.674651682376862</v>
+        <v>0.674651741981506</v>
       </c>
       <c r="H1799" t="n">
         <v>167768</v>
@@ -52598,7 +52598,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1801" t="n">
-        <v>0.674651682376862</v>
+        <v>0.674651741981506</v>
       </c>
       <c r="H1801" t="n">
         <v>34524</v>
@@ -52772,7 +52772,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G1807" t="n">
-        <v>0.702864468097687</v>
+        <v>0.702864408493042</v>
       </c>
       <c r="H1807" t="n">
         <v>166355</v>
@@ -52830,7 +52830,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G1809" t="n">
-        <v>0.721264064311981</v>
+        <v>0.721264004707336</v>
       </c>
       <c r="H1809" t="n">
         <v>80314</v>
@@ -52888,7 +52888,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G1811" t="n">
-        <v>0.721264064311981</v>
+        <v>0.721264004707336</v>
       </c>
       <c r="H1811" t="n">
         <v>151667</v>
@@ -52917,7 +52917,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1812" t="n">
-        <v>0.7323037981987</v>
+        <v>0.732303738594055</v>
       </c>
       <c r="H1812" t="n">
         <v>306421</v>
@@ -52946,7 +52946,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1813" t="n">
-        <v>0.726170539855957</v>
+        <v>0.726170599460602</v>
       </c>
       <c r="H1813" t="n">
         <v>79046</v>
@@ -52975,7 +52975,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1814" t="n">
-        <v>0.743343591690063</v>
+        <v>0.743343532085419</v>
       </c>
       <c r="H1814" t="n">
         <v>234732</v>
@@ -53004,7 +53004,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1815" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1815" t="n">
         <v>136669</v>
@@ -53120,7 +53120,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1819" t="n">
-        <v>0.726170539855957</v>
+        <v>0.726170599460602</v>
       </c>
       <c r="H1819" t="n">
         <v>122752</v>
@@ -53149,7 +53149,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1820" t="n">
-        <v>0.724943935871124</v>
+        <v>0.724943995475769</v>
       </c>
       <c r="H1820" t="n">
         <v>326053</v>
@@ -53207,7 +53207,7 @@
         <v>1.11800003051758</v>
       </c>
       <c r="G1822" t="n">
-        <v>0.68569153547287</v>
+        <v>0.68569141626358</v>
       </c>
       <c r="H1822" t="n">
         <v>652291</v>
@@ -53236,7 +53236,7 @@
         <v>1.12800002098083</v>
       </c>
       <c r="G1823" t="n">
-        <v>0.691824615001678</v>
+        <v>0.691824674606323</v>
       </c>
       <c r="H1823" t="n">
         <v>384187</v>
@@ -53294,7 +53294,7 @@
         <v>1.09399998188019</v>
       </c>
       <c r="G1825" t="n">
-        <v>0.670971751213074</v>
+        <v>0.670971810817719</v>
       </c>
       <c r="H1825" t="n">
         <v>141594</v>
@@ -53526,7 +53526,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1833" t="n">
-        <v>0.662385284900665</v>
+        <v>0.66238534450531</v>
       </c>
       <c r="H1833" t="n">
         <v>158378</v>
@@ -53613,7 +53613,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G1836" t="n">
-        <v>0.628039479255676</v>
+        <v>0.628039419651031</v>
       </c>
       <c r="H1836" t="n">
         <v>130678</v>
@@ -53671,7 +53671,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G1838" t="n">
-        <v>0.647665619850159</v>
+        <v>0.647665679454803</v>
       </c>
       <c r="H1838" t="n">
         <v>164523</v>
@@ -53845,7 +53845,7 @@
         <v>1.13199996948242</v>
       </c>
       <c r="G1844" t="n">
-        <v>0.694277882575989</v>
+        <v>0.694277942180634</v>
       </c>
       <c r="H1844" t="n">
         <v>33750</v>
@@ -53874,7 +53874,7 @@
         <v>1.11800003051758</v>
       </c>
       <c r="G1845" t="n">
-        <v>0.68569153547287</v>
+        <v>0.68569141626358</v>
       </c>
       <c r="H1845" t="n">
         <v>15468</v>
@@ -53990,7 +53990,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1849" t="n">
-        <v>0.686918079853058</v>
+        <v>0.686918139457703</v>
       </c>
       <c r="H1849" t="n">
         <v>154138</v>
@@ -54019,7 +54019,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G1850" t="n">
-        <v>0.697957932949066</v>
+        <v>0.697957813739777</v>
       </c>
       <c r="H1850" t="n">
         <v>31934</v>
@@ -54048,7 +54048,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1851" t="n">
-        <v>0.686918079853058</v>
+        <v>0.686918139457703</v>
       </c>
       <c r="H1851" t="n">
         <v>50692</v>
@@ -54077,7 +54077,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1852" t="n">
-        <v>0.686918079853058</v>
+        <v>0.686918139457703</v>
       </c>
       <c r="H1852" t="n">
         <v>74896</v>
@@ -54193,7 +54193,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1856" t="n">
-        <v>0.754383325576782</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H1856" t="n">
         <v>278182</v>
@@ -54222,7 +54222,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1857" t="n">
-        <v>0.743343591690063</v>
+        <v>0.743343532085419</v>
       </c>
       <c r="H1857" t="n">
         <v>119937</v>
@@ -54309,7 +54309,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1860" t="n">
-        <v>0.7323037981987</v>
+        <v>0.732303738594055</v>
       </c>
       <c r="H1860" t="n">
         <v>371175</v>
@@ -54512,7 +54512,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1867" t="n">
-        <v>0.724943935871124</v>
+        <v>0.724943995475769</v>
       </c>
       <c r="H1867" t="n">
         <v>161084</v>
@@ -54541,7 +54541,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G1868" t="n">
-        <v>0.706544280052185</v>
+        <v>0.70654433965683</v>
       </c>
       <c r="H1868" t="n">
         <v>208969</v>
@@ -54744,7 +54744,7 @@
         <v>1.15400004386902</v>
       </c>
       <c r="G1875" t="n">
-        <v>0.707771062850952</v>
+        <v>0.707771003246307</v>
       </c>
       <c r="H1875" t="n">
         <v>46996</v>
@@ -54773,7 +54773,7 @@
         <v>1.15400004386902</v>
       </c>
       <c r="G1876" t="n">
-        <v>0.707771062850952</v>
+        <v>0.707771003246307</v>
       </c>
       <c r="H1876" t="n">
         <v>41202</v>
@@ -54831,7 +54831,7 @@
         <v>1.15400004386902</v>
       </c>
       <c r="G1878" t="n">
-        <v>0.707771062850952</v>
+        <v>0.707771003246307</v>
       </c>
       <c r="H1878" t="n">
         <v>84523</v>
@@ -55034,7 +55034,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.686918079853058</v>
+        <v>0.686918139457703</v>
       </c>
       <c r="H1885" t="n">
         <v>84022</v>
@@ -55092,7 +55092,7 @@
         <v>1.09399998188019</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.670971751213074</v>
+        <v>0.670971810817719</v>
       </c>
       <c r="H1887" t="n">
         <v>84759</v>
@@ -55150,7 +55150,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.700411140918732</v>
+        <v>0.700411081314087</v>
       </c>
       <c r="H1889" t="n">
         <v>66214</v>
@@ -55237,7 +55237,7 @@
         <v>1.15799999237061</v>
       </c>
       <c r="G1892" t="n">
-        <v>0.710224330425262</v>
+        <v>0.710224270820618</v>
       </c>
       <c r="H1892" t="n">
         <v>17771</v>
@@ -55266,7 +55266,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G1893" t="n">
-        <v>0.721264064311981</v>
+        <v>0.721264004707336</v>
       </c>
       <c r="H1893" t="n">
         <v>52903</v>
@@ -55382,7 +55382,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G1897" t="n">
-        <v>0.718810796737671</v>
+        <v>0.718810737133026</v>
       </c>
       <c r="H1897" t="n">
         <v>28942</v>
@@ -55411,7 +55411,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G1898" t="n">
-        <v>0.721264064311981</v>
+        <v>0.721264004707336</v>
       </c>
       <c r="H1898" t="n">
         <v>15484</v>
@@ -55498,7 +55498,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G1901" t="n">
-        <v>0.721264064311981</v>
+        <v>0.721264004707336</v>
       </c>
       <c r="H1901" t="n">
         <v>10203</v>
@@ -55527,7 +55527,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G1902" t="n">
-        <v>0.721264064311981</v>
+        <v>0.721264004707336</v>
       </c>
       <c r="H1902" t="n">
         <v>89907</v>
@@ -55585,7 +55585,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G1904" t="n">
-        <v>0.721264064311981</v>
+        <v>0.721264004707336</v>
       </c>
       <c r="H1904" t="n">
         <v>20091</v>
@@ -55730,7 +55730,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1909" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1909" t="n">
         <v>60247</v>
@@ -55759,7 +55759,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1910" t="n">
-        <v>0.754383325576782</v>
+        <v>0.754383265972137</v>
       </c>
       <c r="H1910" t="n">
         <v>87166</v>
@@ -55817,7 +55817,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1912" t="n">
-        <v>0.764196395874023</v>
+        <v>0.764196455478668</v>
       </c>
       <c r="H1912" t="n">
         <v>89025</v>
@@ -55875,7 +55875,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1914" t="n">
-        <v>0.759289801120758</v>
+        <v>0.759289860725403</v>
       </c>
       <c r="H1914" t="n">
         <v>30810</v>
@@ -55904,7 +55904,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1915" t="n">
-        <v>0.764196395874023</v>
+        <v>0.764196455478668</v>
       </c>
       <c r="H1915" t="n">
         <v>76312</v>
@@ -55933,7 +55933,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G1916" t="n">
-        <v>0.767876327037811</v>
+        <v>0.767876267433167</v>
       </c>
       <c r="H1916" t="n">
         <v>111462</v>
@@ -55962,7 +55962,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1917" t="n">
-        <v>0.775236129760742</v>
+        <v>0.775236248970032</v>
       </c>
       <c r="H1917" t="n">
         <v>109012</v>
@@ -56049,7 +56049,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1920" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1920" t="n">
         <v>110958</v>
@@ -56107,7 +56107,7 @@
         <v>1.28400003910065</v>
       </c>
       <c r="G1922" t="n">
-        <v>0.787502527236938</v>
+        <v>0.787502586841583</v>
       </c>
       <c r="H1922" t="n">
         <v>47817</v>
@@ -56136,7 +56136,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1923" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1923" t="n">
         <v>186595</v>
@@ -56165,7 +56165,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1924" t="n">
-        <v>0.79731559753418</v>
+        <v>0.797315657138824</v>
       </c>
       <c r="H1924" t="n">
         <v>93366</v>
@@ -56194,7 +56194,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1925" t="n">
-        <v>0.821848511695862</v>
+        <v>0.821848452091217</v>
       </c>
       <c r="H1925" t="n">
         <v>314752</v>
@@ -56281,7 +56281,7 @@
         <v>1.31599998474121</v>
       </c>
       <c r="G1928" t="n">
-        <v>0.807128727436066</v>
+        <v>0.80712878704071</v>
       </c>
       <c r="H1928" t="n">
         <v>284340</v>
@@ -56310,7 +56310,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G1929" t="n">
-        <v>0.819395184516907</v>
+        <v>0.819395124912262</v>
       </c>
       <c r="H1929" t="n">
         <v>243567</v>
@@ -56339,7 +56339,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G1930" t="n">
-        <v>0.79976898431778</v>
+        <v>0.799768924713135</v>
       </c>
       <c r="H1930" t="n">
         <v>145895</v>
@@ -56397,7 +56397,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1932" t="n">
-        <v>0.775236129760742</v>
+        <v>0.775236248970032</v>
       </c>
       <c r="H1932" t="n">
         <v>117911</v>
@@ -56513,7 +56513,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1936" t="n">
-        <v>0.735983729362488</v>
+        <v>0.735983669757843</v>
       </c>
       <c r="H1936" t="n">
         <v>145184</v>
@@ -56571,7 +56571,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1938" t="n">
-        <v>0.759289801120758</v>
+        <v>0.759289860725403</v>
       </c>
       <c r="H1938" t="n">
         <v>76097</v>
@@ -56629,7 +56629,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G1940" t="n">
-        <v>0.767876327037811</v>
+        <v>0.767876267433167</v>
       </c>
       <c r="H1940" t="n">
         <v>97307</v>
@@ -56716,7 +56716,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1943" t="n">
-        <v>0.748250126838684</v>
+        <v>0.748250067234039</v>
       </c>
       <c r="H1943" t="n">
         <v>117184</v>
@@ -56803,7 +56803,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1946" t="n">
-        <v>0.76051652431488</v>
+        <v>0.760516464710236</v>
       </c>
       <c r="H1946" t="n">
         <v>47490</v>
@@ -56832,7 +56832,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G1947" t="n">
-        <v>0.758063197135925</v>
+        <v>0.758063137531281</v>
       </c>
       <c r="H1947" t="n">
         <v>156141</v>
@@ -57122,7 +57122,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1957" t="n">
-        <v>0.772782802581787</v>
+        <v>0.772782921791077</v>
       </c>
       <c r="H1957" t="n">
         <v>86324</v>
@@ -57151,7 +57151,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1958" t="n">
-        <v>0.775236129760742</v>
+        <v>0.775236248970032</v>
       </c>
       <c r="H1958" t="n">
         <v>59757</v>
@@ -57180,7 +57180,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1959" t="n">
-        <v>0.775236129760742</v>
+        <v>0.775236248970032</v>
       </c>
       <c r="H1959" t="n">
         <v>60924</v>
@@ -57296,7 +57296,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G1963" t="n">
-        <v>0.79976898431778</v>
+        <v>0.799768924713135</v>
       </c>
       <c r="H1963" t="n">
         <v>206796</v>
@@ -57354,7 +57354,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1965" t="n">
-        <v>0.821848511695862</v>
+        <v>0.821848452091217</v>
       </c>
       <c r="H1965" t="n">
         <v>369054</v>
@@ -57441,7 +57441,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1968" t="n">
-        <v>0.889313697814941</v>
+        <v>0.889313578605652</v>
       </c>
       <c r="H1968" t="n">
         <v>580634</v>
@@ -57470,7 +57470,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G1969" t="n">
-        <v>0.924886167049408</v>
+        <v>0.924886226654053</v>
       </c>
       <c r="H1969" t="n">
         <v>590769</v>
@@ -57499,7 +57499,7 @@
         <v>1.44400000572205</v>
       </c>
       <c r="G1970" t="n">
-        <v>0.885633647441864</v>
+        <v>0.885633707046509</v>
       </c>
       <c r="H1970" t="n">
         <v>468014</v>
@@ -57586,7 +57586,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G1973" t="n">
-        <v>0.912619769573212</v>
+        <v>0.912619829177856</v>
       </c>
       <c r="H1973" t="n">
         <v>300698</v>
@@ -57615,7 +57615,7 @@
         <v>1.50399994850159</v>
       </c>
       <c r="G1974" t="n">
-        <v>0.922432899475098</v>
+        <v>0.922432839870453</v>
       </c>
       <c r="H1974" t="n">
         <v>503202</v>
@@ -57673,7 +57673,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1976" t="n">
-        <v>0.926112771034241</v>
+        <v>0.92611289024353</v>
       </c>
       <c r="H1976" t="n">
         <v>169088</v>
@@ -57702,7 +57702,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1977" t="n">
-        <v>0.928566098213196</v>
+        <v>0.928566157817841</v>
       </c>
       <c r="H1977" t="n">
         <v>2340651</v>
@@ -57760,7 +57760,7 @@
         <v>1.58800005912781</v>
       </c>
       <c r="G1979" t="n">
-        <v>0.973951756954193</v>
+        <v>0.973951816558838</v>
       </c>
       <c r="H1979" t="n">
         <v>372992</v>
@@ -57934,7 +57934,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.0119776725769</v>
+        <v>1.01197755336761</v>
       </c>
       <c r="H1985" t="n">
         <v>307422</v>
@@ -58050,7 +58050,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1989" t="n">
-        <v>0.99357795715332</v>
+        <v>0.993577897548676</v>
       </c>
       <c r="H1989" t="n">
         <v>762902</v>
@@ -58079,7 +58079,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G1990" t="n">
-        <v>0.986218094825745</v>
+        <v>0.986218154430389</v>
       </c>
       <c r="H1990" t="n">
         <v>370565</v>
@@ -58108,7 +58108,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G1991" t="n">
-        <v>0.917526364326477</v>
+        <v>0.917526304721832</v>
       </c>
       <c r="H1991" t="n">
         <v>1073810</v>
@@ -58195,7 +58195,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1994" t="n">
-        <v>0.937152564525604</v>
+        <v>0.937152624130249</v>
       </c>
       <c r="H1994" t="n">
         <v>126527</v>
@@ -58253,7 +58253,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G1996" t="n">
-        <v>0.951872289180756</v>
+        <v>0.951872229576111</v>
       </c>
       <c r="H1996" t="n">
         <v>102119</v>
@@ -58282,7 +58282,7 @@
         <v>1.57799994945526</v>
       </c>
       <c r="G1997" t="n">
-        <v>0.96781849861145</v>
+        <v>0.967818558216095</v>
       </c>
       <c r="H1997" t="n">
         <v>136474</v>
@@ -58311,7 +58311,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1998" t="n">
-        <v>0.965365290641785</v>
+        <v>0.96536523103714</v>
       </c>
       <c r="H1998" t="n">
         <v>115948</v>
@@ -58340,7 +58340,7 @@
         <v>1.5</v>
       </c>
       <c r="G1999" t="n">
-        <v>0.919979631900787</v>
+        <v>0.919979512691498</v>
       </c>
       <c r="H1999" t="n">
         <v>702293</v>
@@ -58369,7 +58369,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G2000" t="n">
-        <v>0.950645565986633</v>
+        <v>0.950645625591278</v>
       </c>
       <c r="H2000" t="n">
         <v>269857</v>
@@ -58398,7 +58398,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G2001" t="n">
-        <v>0.950645565986633</v>
+        <v>0.950645625591278</v>
       </c>
       <c r="H2001" t="n">
         <v>33986</v>
@@ -58427,7 +58427,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G2002" t="n">
-        <v>0.953098833560944</v>
+        <v>0.953098893165588</v>
       </c>
       <c r="H2002" t="n">
         <v>145635</v>
@@ -58456,7 +58456,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G2003" t="n">
-        <v>0.980084955692291</v>
+        <v>0.980085015296936</v>
       </c>
       <c r="H2003" t="n">
         <v>535679</v>
@@ -58485,7 +58485,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G2004" t="n">
-        <v>1.01075088977814</v>
+        <v>1.01075100898743</v>
       </c>
       <c r="H2004" t="n">
         <v>1171917</v>
@@ -58572,7 +58572,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G2007" t="n">
-        <v>0.987444818019867</v>
+        <v>0.987444758415222</v>
       </c>
       <c r="H2007" t="n">
         <v>109945</v>
@@ -58659,7 +58659,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2010" t="n">
-        <v>0.99357795715332</v>
+        <v>0.993577897548676</v>
       </c>
       <c r="H2010" t="n">
         <v>107326</v>
@@ -58717,7 +58717,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G2012" t="n">
-        <v>0.98376476764679</v>
+        <v>0.983764886856079</v>
       </c>
       <c r="H2012" t="n">
         <v>155404</v>
@@ -58746,7 +58746,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G2013" t="n">
-        <v>0.987444818019867</v>
+        <v>0.987444758415222</v>
       </c>
       <c r="H2013" t="n">
         <v>164498</v>
@@ -58775,7 +58775,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G2014" t="n">
-        <v>0.98376476764679</v>
+        <v>0.983764886856079</v>
       </c>
       <c r="H2014" t="n">
         <v>263889</v>
@@ -58804,7 +58804,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G2015" t="n">
-        <v>0.987444818019867</v>
+        <v>0.987444758415222</v>
       </c>
       <c r="H2015" t="n">
         <v>167544</v>
@@ -58862,7 +58862,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G2017" t="n">
-        <v>0.962912023067474</v>
+        <v>0.96291196346283</v>
       </c>
       <c r="H2017" t="n">
         <v>184712</v>
@@ -58891,7 +58891,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G2018" t="n">
-        <v>0.987444818019867</v>
+        <v>0.987444758415222</v>
       </c>
       <c r="H2018" t="n">
         <v>222854</v>
@@ -59181,7 +59181,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2028" t="n">
-        <v>1.25117230415344</v>
+        <v>1.25117218494415</v>
       </c>
       <c r="H2028" t="n">
         <v>897508</v>
@@ -59297,7 +59297,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2032" t="n">
-        <v>1.25117230415344</v>
+        <v>1.25117218494415</v>
       </c>
       <c r="H2032" t="n">
         <v>146024</v>
@@ -59442,7 +59442,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G2037" t="n">
-        <v>1.22970616817474</v>
+        <v>1.22970604896545</v>
       </c>
       <c r="H2037" t="n">
         <v>147813</v>
@@ -59529,7 +59529,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G2040" t="n">
-        <v>1.18493366241455</v>
+        <v>1.18493378162384</v>
       </c>
       <c r="H2040" t="n">
         <v>419422</v>
@@ -59645,7 +59645,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G2044" t="n">
-        <v>1.22173285484314</v>
+        <v>1.22173297405243</v>
       </c>
       <c r="H2044" t="n">
         <v>456560</v>
@@ -59674,7 +59674,7 @@
         <v>2</v>
       </c>
       <c r="G2045" t="n">
-        <v>1.22663950920105</v>
+        <v>1.22663938999176</v>
       </c>
       <c r="H2045" t="n">
         <v>192257</v>
@@ -59703,7 +59703,7 @@
         <v>2</v>
       </c>
       <c r="G2046" t="n">
-        <v>1.22663950920105</v>
+        <v>1.22663938999176</v>
       </c>
       <c r="H2046" t="n">
         <v>143372</v>
@@ -59790,7 +59790,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2049" t="n">
-        <v>1.18370711803436</v>
+        <v>1.18370699882507</v>
       </c>
       <c r="H2049" t="n">
         <v>60184</v>
@@ -59877,7 +59877,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G2052" t="n">
-        <v>1.14445459842682</v>
+        <v>1.14445471763611</v>
       </c>
       <c r="H2052" t="n">
         <v>273497</v>
@@ -60022,7 +60022,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G2057" t="n">
-        <v>1.14200127124786</v>
+        <v>1.14200139045715</v>
       </c>
       <c r="H2057" t="n">
         <v>174498</v>
@@ -60109,7 +60109,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G2060" t="n">
-        <v>1.10274887084961</v>
+        <v>1.1027489900589</v>
       </c>
       <c r="H2060" t="n">
         <v>180510</v>
@@ -60283,7 +60283,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G2066" t="n">
-        <v>1.15794777870178</v>
+        <v>1.1579475402832</v>
       </c>
       <c r="H2066" t="n">
         <v>230384</v>
@@ -60312,7 +60312,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2067" t="n">
-        <v>1.16530752182007</v>
+        <v>1.16530740261078</v>
       </c>
       <c r="H2067" t="n">
         <v>174916</v>
@@ -60370,7 +60370,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G2069" t="n">
-        <v>1.16162765026093</v>
+        <v>1.16162753105164</v>
       </c>
       <c r="H2069" t="n">
         <v>184521</v>
@@ -60515,7 +60515,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G2074" t="n">
-        <v>1.22173285484314</v>
+        <v>1.22173297405243</v>
       </c>
       <c r="H2074" t="n">
         <v>457907</v>
@@ -60573,7 +60573,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G2076" t="n">
-        <v>1.70502889156342</v>
+        <v>1.70502877235413</v>
       </c>
       <c r="H2076" t="n">
         <v>5087915</v>
@@ -60602,7 +60602,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G2077" t="n">
-        <v>1.71729528903961</v>
+        <v>1.71729516983032</v>
       </c>
       <c r="H2077" t="n">
         <v>1386670</v>
@@ -60631,7 +60631,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G2078" t="n">
-        <v>1.81849312782288</v>
+        <v>1.8184928894043</v>
       </c>
       <c r="H2078" t="n">
         <v>1688908</v>
@@ -60660,7 +60660,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2079" t="n">
-        <v>1.94422352313995</v>
+        <v>1.94422376155853</v>
       </c>
       <c r="H2079" t="n">
         <v>1370361</v>
@@ -60718,7 +60718,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G2081" t="n">
-        <v>1.87675821781158</v>
+        <v>1.87675857543945</v>
       </c>
       <c r="H2081" t="n">
         <v>677611</v>
@@ -60834,7 +60834,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G2085" t="n">
-        <v>1.741828083992</v>
+        <v>1.74182796478271</v>
       </c>
       <c r="H2085" t="n">
         <v>645162</v>
@@ -60863,7 +60863,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G2086" t="n">
-        <v>1.7448947429657</v>
+        <v>1.74489462375641</v>
       </c>
       <c r="H2086" t="n">
         <v>454908</v>
@@ -60921,7 +60921,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G2088" t="n">
-        <v>1.83689260482788</v>
+        <v>1.83689248561859</v>
       </c>
       <c r="H2088" t="n">
         <v>219354</v>
@@ -60950,7 +60950,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2089" t="n">
-        <v>1.90129113197327</v>
+        <v>1.90129125118256</v>
       </c>
       <c r="H2089" t="n">
         <v>477509</v>
@@ -60979,7 +60979,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2090" t="n">
-        <v>1.90129113197327</v>
+        <v>1.90129125118256</v>
       </c>
       <c r="H2090" t="n">
         <v>391550</v>
@@ -61153,7 +61153,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G2096" t="n">
-        <v>1.92889058589935</v>
+        <v>1.92889046669006</v>
       </c>
       <c r="H2096" t="n">
         <v>185807</v>
@@ -61269,7 +61269,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G2100" t="n">
-        <v>1.92275738716125</v>
+        <v>1.92275750637054</v>
       </c>
       <c r="H2100" t="n">
         <v>593300</v>
@@ -61327,7 +61327,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2102" t="n">
-        <v>1.93809032440186</v>
+        <v>1.93809044361115</v>
       </c>
       <c r="H2102" t="n">
         <v>199370</v>
@@ -61414,7 +61414,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2105" t="n">
-        <v>1.97488963603973</v>
+        <v>1.97488951683044</v>
       </c>
       <c r="H2105" t="n">
         <v>324201</v>
@@ -61472,7 +61472,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2107" t="n">
-        <v>2.00555539131165</v>
+        <v>2.00555562973022</v>
       </c>
       <c r="H2107" t="n">
         <v>289188</v>
@@ -61501,7 +61501,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G2108" t="n">
-        <v>1.95342326164246</v>
+        <v>1.95342314243317</v>
       </c>
       <c r="H2108" t="n">
         <v>261617</v>
@@ -61530,7 +61530,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G2109" t="n">
-        <v>1.95342326164246</v>
+        <v>1.95342314243317</v>
       </c>
       <c r="H2109" t="n">
         <v>253803</v>
@@ -61559,7 +61559,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G2110" t="n">
-        <v>1.92889058589935</v>
+        <v>1.92889046669006</v>
       </c>
       <c r="H2110" t="n">
         <v>187344</v>
@@ -61588,7 +61588,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2111" t="n">
-        <v>1.92582404613495</v>
+        <v>1.92582392692566</v>
       </c>
       <c r="H2111" t="n">
         <v>213530</v>
@@ -61617,7 +61617,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G2112" t="n">
-        <v>1.92275738716125</v>
+        <v>1.92275750637054</v>
       </c>
       <c r="H2112" t="n">
         <v>150439</v>
@@ -61646,7 +61646,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2113" t="n">
-        <v>1.88902473449707</v>
+        <v>1.88902485370636</v>
       </c>
       <c r="H2113" t="n">
         <v>498070</v>
@@ -61675,7 +61675,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2114" t="n">
-        <v>1.88902473449707</v>
+        <v>1.88902485370636</v>
       </c>
       <c r="H2114" t="n">
         <v>245321</v>
@@ -61704,7 +61704,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G2115" t="n">
-        <v>1.89515805244446</v>
+        <v>1.89515793323517</v>
       </c>
       <c r="H2115" t="n">
         <v>279894</v>
@@ -61733,7 +61733,7 @@
         <v>3</v>
       </c>
       <c r="G2116" t="n">
-        <v>1.83995926380157</v>
+        <v>1.839959025383</v>
       </c>
       <c r="H2116" t="n">
         <v>604364</v>
@@ -61762,7 +61762,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G2117" t="n">
-        <v>1.77249419689178</v>
+        <v>1.7724940776825</v>
       </c>
       <c r="H2117" t="n">
         <v>350773</v>
@@ -61820,7 +61820,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G2119" t="n">
-        <v>1.80622661113739</v>
+        <v>1.8062264919281</v>
       </c>
       <c r="H2119" t="n">
         <v>193216</v>
@@ -61849,7 +61849,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G2120" t="n">
-        <v>1.7694274187088</v>
+        <v>1.76942729949951</v>
       </c>
       <c r="H2120" t="n">
         <v>294872</v>
@@ -61907,7 +61907,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G2122" t="n">
-        <v>1.81849312782288</v>
+        <v>1.8184928894043</v>
       </c>
       <c r="H2122" t="n">
         <v>874006</v>
@@ -61965,7 +61965,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G2124" t="n">
-        <v>2.0125093460083</v>
+        <v>2.01250958442688</v>
       </c>
       <c r="H2124" t="n">
         <v>1836606</v>
@@ -61994,7 +61994,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G2125" t="n">
-        <v>1.96318316459656</v>
+        <v>1.96318304538727</v>
       </c>
       <c r="H2125" t="n">
         <v>691906</v>
@@ -62052,7 +62052,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G2127" t="n">
-        <v>1.79218554496765</v>
+        <v>1.79218566417694</v>
       </c>
       <c r="H2127" t="n">
         <v>741856</v>
@@ -62197,7 +62197,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G2132" t="n">
-        <v>1.83164668083191</v>
+        <v>1.8316468000412</v>
       </c>
       <c r="H2132" t="n">
         <v>448052</v>
@@ -62284,7 +62284,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G2135" t="n">
-        <v>1.79218554496765</v>
+        <v>1.79218566417694</v>
       </c>
       <c r="H2135" t="n">
         <v>224205</v>
@@ -62313,7 +62313,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G2136" t="n">
-        <v>1.79218554496765</v>
+        <v>1.79218566417694</v>
       </c>
       <c r="H2136" t="n">
         <v>245245</v>
@@ -62371,7 +62371,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G2138" t="n">
-        <v>1.95660626888275</v>
+        <v>1.95660638809204</v>
       </c>
       <c r="H2138" t="n">
         <v>672942</v>
@@ -62400,7 +62400,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G2139" t="n">
-        <v>1.95002961158752</v>
+        <v>1.95002949237823</v>
       </c>
       <c r="H2139" t="n">
         <v>521188</v>
@@ -62429,7 +62429,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G2140" t="n">
-        <v>1.92043387889862</v>
+        <v>1.92043375968933</v>
       </c>
       <c r="H2140" t="n">
         <v>334815</v>
@@ -62458,7 +62458,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G2141" t="n">
-        <v>1.93358755111694</v>
+        <v>1.93358743190765</v>
       </c>
       <c r="H2141" t="n">
         <v>370967</v>
@@ -62487,7 +62487,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G2142" t="n">
-        <v>1.92372226715088</v>
+        <v>1.92372214794159</v>
       </c>
       <c r="H2142" t="n">
         <v>298873</v>
@@ -62545,7 +62545,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G2144" t="n">
-        <v>1.90728032588959</v>
+        <v>1.9072802066803</v>
       </c>
       <c r="H2144" t="n">
         <v>620199</v>
@@ -62603,7 +62603,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G2146" t="n">
-        <v>1.91385698318481</v>
+        <v>1.9138571023941</v>
       </c>
       <c r="H2146" t="n">
         <v>226554</v>
@@ -62632,7 +62632,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G2147" t="n">
-        <v>1.91056859493256</v>
+        <v>1.91056847572327</v>
       </c>
       <c r="H2147" t="n">
         <v>187722</v>
@@ -62661,7 +62661,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G2148" t="n">
-        <v>1.91056859493256</v>
+        <v>1.91056847572327</v>
       </c>
       <c r="H2148" t="n">
         <v>164909</v>
@@ -62690,7 +62690,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G2149" t="n">
-        <v>1.91714537143707</v>
+        <v>1.91714549064636</v>
       </c>
       <c r="H2149" t="n">
         <v>412284</v>
@@ -62748,7 +62748,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G2151" t="n">
-        <v>1.87110769748688</v>
+        <v>1.87110757827759</v>
       </c>
       <c r="H2151" t="n">
         <v>587531</v>
@@ -62835,7 +62835,7 @@
         <v>3</v>
       </c>
       <c r="G2154" t="n">
-        <v>1.97304844856262</v>
+        <v>1.97304832935333</v>
       </c>
       <c r="H2154" t="n">
         <v>2848260</v>
@@ -63096,7 +63096,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2163" t="n">
-        <v>2.22296786308289</v>
+        <v>2.22296810150146</v>
       </c>
       <c r="H2163" t="n">
         <v>1428310</v>
@@ -63125,7 +63125,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G2164" t="n">
-        <v>2.17692995071411</v>
+        <v>2.17693018913269</v>
       </c>
       <c r="H2164" t="n">
         <v>991592</v>
@@ -63154,7 +63154,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G2165" t="n">
-        <v>2.20981431007385</v>
+        <v>2.20981407165527</v>
       </c>
       <c r="H2165" t="n">
         <v>535197</v>
@@ -63183,7 +63183,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2166" t="n">
-        <v>2.22296786308289</v>
+        <v>2.22296810150146</v>
       </c>
       <c r="H2166" t="n">
         <v>543161</v>
@@ -63270,7 +63270,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G2169" t="n">
-        <v>2.17692995071411</v>
+        <v>2.17693018913269</v>
       </c>
       <c r="H2169" t="n">
         <v>544446</v>
@@ -80038,6 +80038,35 @@
         <v>327904</v>
       </c>
       <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>2.01500010490417</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>2.01500010490417</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>1.92200005054474</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>1.92200005054474</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>1.92200005054474</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>416070</v>
+      </c>
+      <c r="I2748" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SGF.MI.xlsx
+++ b/data/SGF.MI.xlsx
@@ -514,7 +514,7 @@
         <v>1.93299996852875</v>
       </c>
       <c r="G5" t="n">
-        <v>1.18554699420929</v>
+        <v>1.18554711341858</v>
       </c>
       <c r="H5" t="n">
         <v>335985</v>
@@ -543,7 +543,7 @@
         <v>1.91299998760223</v>
       </c>
       <c r="G6" t="n">
-        <v>1.17328071594238</v>
+        <v>1.17328059673309</v>
       </c>
       <c r="H6" t="n">
         <v>373482</v>
@@ -601,7 +601,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G8" t="n">
-        <v>1.17389404773712</v>
+        <v>1.17389392852783</v>
       </c>
       <c r="H8" t="n">
         <v>255301</v>
@@ -688,7 +688,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G11" t="n">
-        <v>1.08557593822479</v>
+        <v>1.0855758190155</v>
       </c>
       <c r="H11" t="n">
         <v>331594</v>
@@ -775,7 +775,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>1.00891101360321</v>
+        <v>1.00891089439392</v>
       </c>
       <c r="H14" t="n">
         <v>229916</v>
@@ -833,7 +833,7 @@
         <v>1.7610000371933</v>
       </c>
       <c r="G16" t="n">
-        <v>1.08005607128143</v>
+        <v>1.08005595207214</v>
       </c>
       <c r="H16" t="n">
         <v>396007</v>
@@ -891,7 +891,7 @@
         <v>1.77400004863739</v>
       </c>
       <c r="G18" t="n">
-        <v>1.08802914619446</v>
+        <v>1.08802926540375</v>
       </c>
       <c r="H18" t="n">
         <v>242295</v>
@@ -949,7 +949,7 @@
         <v>1.692999958992</v>
       </c>
       <c r="G20" t="n">
-        <v>1.03835034370422</v>
+        <v>1.03835022449493</v>
       </c>
       <c r="H20" t="n">
         <v>324056</v>
@@ -1152,7 +1152,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G27" t="n">
-        <v>0.841474711894989</v>
+        <v>0.841474652290344</v>
       </c>
       <c r="H27" t="n">
         <v>327658</v>
@@ -1268,7 +1268,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G31" t="n">
-        <v>0.916912972927094</v>
+        <v>0.916913032531738</v>
       </c>
       <c r="H31" t="n">
         <v>204119</v>
@@ -1297,7 +1297,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G32" t="n">
-        <v>0.981311559677124</v>
+        <v>0.981311500072479</v>
       </c>
       <c r="H32" t="n">
         <v>168307</v>
@@ -1326,7 +1326,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G33" t="n">
-        <v>0.950645625591278</v>
+        <v>0.950645565986633</v>
       </c>
       <c r="H33" t="n">
         <v>252019</v>
@@ -1355,7 +1355,7 @@
         <v>1.56099998950958</v>
       </c>
       <c r="G34" t="n">
-        <v>0.95739209651947</v>
+        <v>0.957392156124115</v>
       </c>
       <c r="H34" t="n">
         <v>320159</v>
@@ -1384,7 +1384,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G35" t="n">
-        <v>0.941445767879486</v>
+        <v>0.941445708274841</v>
       </c>
       <c r="H35" t="n">
         <v>350921</v>
@@ -1471,7 +1471,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G38" t="n">
-        <v>0.941445767879486</v>
+        <v>0.941445708274841</v>
       </c>
       <c r="H38" t="n">
         <v>449707</v>
@@ -1500,7 +1500,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G39" t="n">
-        <v>0.924886226654053</v>
+        <v>0.924886167049408</v>
       </c>
       <c r="H39" t="n">
         <v>291804</v>
@@ -1558,7 +1558,7 @@
         <v>1.52699995040894</v>
       </c>
       <c r="G41" t="n">
-        <v>0.93653929233551</v>
+        <v>0.936539232730865</v>
       </c>
       <c r="H41" t="n">
         <v>374615</v>
@@ -1587,7 +1587,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G42" t="n">
-        <v>0.872140645980835</v>
+        <v>0.87214070558548</v>
       </c>
       <c r="H42" t="n">
         <v>633854</v>
@@ -1645,7 +1645,7 @@
         <v>1.5789999961853</v>
       </c>
       <c r="G44" t="n">
-        <v>0.968431890010834</v>
+        <v>0.968431830406189</v>
       </c>
       <c r="H44" t="n">
         <v>563184</v>
@@ -1761,7 +1761,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G48" t="n">
-        <v>1.00400447845459</v>
+        <v>1.0040043592453</v>
       </c>
       <c r="H48" t="n">
         <v>312388</v>
@@ -1790,7 +1790,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G49" t="n">
-        <v>1.00891101360321</v>
+        <v>1.00891089439392</v>
       </c>
       <c r="H49" t="n">
         <v>192494</v>
@@ -1906,7 +1906,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G53" t="n">
-        <v>0.960458636283875</v>
+        <v>0.960458695888519</v>
       </c>
       <c r="H53" t="n">
         <v>389718</v>
@@ -1935,7 +1935,7 @@
         <v>1.58299994468689</v>
       </c>
       <c r="G54" t="n">
-        <v>0.970885097980499</v>
+        <v>0.970885038375854</v>
       </c>
       <c r="H54" t="n">
         <v>320346</v>
@@ -1964,7 +1964,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G55" t="n">
-        <v>0.956165432929993</v>
+        <v>0.956165492534637</v>
       </c>
       <c r="H55" t="n">
         <v>282072</v>
@@ -2022,7 +2022,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G57" t="n">
-        <v>0.92611289024353</v>
+        <v>0.926112830638885</v>
       </c>
       <c r="H57" t="n">
         <v>413338</v>
@@ -2080,7 +2080,7 @@
         <v>1.4210000038147</v>
       </c>
       <c r="G59" t="n">
-        <v>0.871527314186096</v>
+        <v>0.871527373790741</v>
       </c>
       <c r="H59" t="n">
         <v>857202</v>
@@ -2109,7 +2109,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G60" t="n">
-        <v>0.853741049766541</v>
+        <v>0.853741109371185</v>
       </c>
       <c r="H60" t="n">
         <v>330575</v>
@@ -2370,7 +2370,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G69" t="n">
-        <v>0.832888245582581</v>
+        <v>0.832888185977936</v>
       </c>
       <c r="H69" t="n">
         <v>207067</v>
@@ -2399,7 +2399,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G70" t="n">
-        <v>0.849447786808014</v>
+        <v>0.849447846412659</v>
       </c>
       <c r="H70" t="n">
         <v>138948</v>
@@ -2602,7 +2602,7 @@
         <v>1.43099999427795</v>
       </c>
       <c r="G77" t="n">
-        <v>0.877660572528839</v>
+        <v>0.877660512924194</v>
       </c>
       <c r="H77" t="n">
         <v>342413</v>
@@ -2631,7 +2631,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G78" t="n">
-        <v>0.875207364559174</v>
+        <v>0.875207304954529</v>
       </c>
       <c r="H78" t="n">
         <v>207294</v>
@@ -2660,7 +2660,7 @@
         <v>1.42299997806549</v>
       </c>
       <c r="G79" t="n">
-        <v>0.872753977775574</v>
+        <v>0.872754037380219</v>
       </c>
       <c r="H79" t="n">
         <v>99483</v>
@@ -2689,7 +2689,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G80" t="n">
-        <v>0.872140645980835</v>
+        <v>0.87214070558548</v>
       </c>
       <c r="H80" t="n">
         <v>27237</v>
@@ -2805,7 +2805,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G84" t="n">
-        <v>0.977631688117981</v>
+        <v>0.977631628513336</v>
       </c>
       <c r="H84" t="n">
         <v>875820</v>
@@ -2834,7 +2834,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G85" t="n">
-        <v>0.993577897548676</v>
+        <v>0.99357795715332</v>
       </c>
       <c r="H85" t="n">
         <v>550524</v>
@@ -3066,7 +3066,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G93" t="n">
-        <v>0.97824501991272</v>
+        <v>0.978245079517365</v>
       </c>
       <c r="H93" t="n">
         <v>347619</v>
@@ -3095,7 +3095,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G94" t="n">
-        <v>0.992351353168488</v>
+        <v>0.992351412773132</v>
       </c>
       <c r="H94" t="n">
         <v>320086</v>
@@ -3240,7 +3240,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G99" t="n">
-        <v>0.935312628746033</v>
+        <v>0.935312569141388</v>
       </c>
       <c r="H99" t="n">
         <v>196453</v>
@@ -3327,7 +3327,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G102" t="n">
-        <v>1.02424383163452</v>
+        <v>1.02424395084381</v>
       </c>
       <c r="H102" t="n">
         <v>930519</v>
@@ -3356,7 +3356,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G103" t="n">
-        <v>1.0917090177536</v>
+        <v>1.09170913696289</v>
       </c>
       <c r="H103" t="n">
         <v>2561297</v>
@@ -3559,7 +3559,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G110" t="n">
-        <v>0.999711155891418</v>
+        <v>0.999711096286774</v>
       </c>
       <c r="H110" t="n">
         <v>236211</v>
@@ -3617,7 +3617,7 @@
         <v>1.625</v>
       </c>
       <c r="G112" t="n">
-        <v>0.996644556522369</v>
+        <v>0.996644616127014</v>
       </c>
       <c r="H112" t="n">
         <v>276657</v>
@@ -3646,7 +3646,7 @@
         <v>1.60099995136261</v>
       </c>
       <c r="G113" t="n">
-        <v>0.981924891471863</v>
+        <v>0.981924831867218</v>
       </c>
       <c r="H113" t="n">
         <v>124731</v>
@@ -3675,7 +3675,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G114" t="n">
-        <v>0.935312628746033</v>
+        <v>0.935312569141388</v>
       </c>
       <c r="H114" t="n">
         <v>354806</v>
@@ -3820,7 +3820,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G119" t="n">
-        <v>0.792409121990204</v>
+        <v>0.792409062385559</v>
       </c>
       <c r="H119" t="n">
         <v>527410</v>
@@ -3849,7 +3849,7 @@
         <v>1.36899995803833</v>
       </c>
       <c r="G120" t="n">
-        <v>0.839634716510773</v>
+        <v>0.839634656906128</v>
       </c>
       <c r="H120" t="n">
         <v>513418</v>
@@ -3907,7 +3907,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G122" t="n">
-        <v>0.875207364559174</v>
+        <v>0.875207304954529</v>
       </c>
       <c r="H122" t="n">
         <v>340422</v>
@@ -4110,7 +4110,7 @@
         <v>1.30900001525879</v>
       </c>
       <c r="G129" t="n">
-        <v>0.802835524082184</v>
+        <v>0.802835583686829</v>
       </c>
       <c r="H129" t="n">
         <v>198549</v>
@@ -4284,7 +4284,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G135" t="n">
-        <v>0.771556258201599</v>
+        <v>0.771556198596954</v>
       </c>
       <c r="H135" t="n">
         <v>325977</v>
@@ -4458,7 +4458,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G141" t="n">
-        <v>0.85128778219223</v>
+        <v>0.851287841796875</v>
       </c>
       <c r="H141" t="n">
         <v>149242</v>
@@ -4661,7 +4661,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G148" t="n">
-        <v>0.935312628746033</v>
+        <v>0.935312569141388</v>
       </c>
       <c r="H148" t="n">
         <v>421354</v>
@@ -4719,7 +4719,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G150" t="n">
-        <v>0.935925960540771</v>
+        <v>0.935925900936127</v>
       </c>
       <c r="H150" t="n">
         <v>228664</v>
@@ -4777,7 +4777,7 @@
         <v>1.54900002479553</v>
       </c>
       <c r="G152" t="n">
-        <v>0.950032293796539</v>
+        <v>0.950032234191895</v>
       </c>
       <c r="H152" t="n">
         <v>547010</v>
@@ -4806,7 +4806,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G153" t="n">
-        <v>0.956778764724731</v>
+        <v>0.956778824329376</v>
       </c>
       <c r="H153" t="n">
         <v>149124</v>
@@ -4864,7 +4864,7 @@
         <v>1.62899994850159</v>
       </c>
       <c r="G155" t="n">
-        <v>0.99909782409668</v>
+        <v>0.999097764492035</v>
       </c>
       <c r="H155" t="n">
         <v>261420</v>
@@ -4951,7 +4951,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G158" t="n">
-        <v>1.02424383163452</v>
+        <v>1.02424395084381</v>
       </c>
       <c r="H158" t="n">
         <v>164073</v>
@@ -5009,7 +5009,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G160" t="n">
-        <v>1.0334438085556</v>
+        <v>1.03344368934631</v>
       </c>
       <c r="H160" t="n">
         <v>177788</v>
@@ -5067,7 +5067,7 @@
         <v>1.66100001335144</v>
       </c>
       <c r="G162" t="n">
-        <v>1.01872408390045</v>
+        <v>1.01872420310974</v>
       </c>
       <c r="H162" t="n">
         <v>160844</v>
@@ -5096,7 +5096,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G163" t="n">
-        <v>1.00461781024933</v>
+        <v>1.00461769104004</v>
       </c>
       <c r="H163" t="n">
         <v>76999</v>
@@ -5125,7 +5125,7 @@
         <v>1.66100001335144</v>
       </c>
       <c r="G164" t="n">
-        <v>1.01872408390045</v>
+        <v>1.01872420310974</v>
       </c>
       <c r="H164" t="n">
         <v>78461</v>
@@ -5183,7 +5183,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G166" t="n">
-        <v>1.03896367549896</v>
+        <v>1.03896355628967</v>
       </c>
       <c r="H166" t="n">
         <v>150712</v>
@@ -5241,7 +5241,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G168" t="n">
-        <v>1.03405714035034</v>
+        <v>1.03405702114105</v>
       </c>
       <c r="H168" t="n">
         <v>51800</v>
@@ -5357,7 +5357,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G172" t="n">
-        <v>1.02363061904907</v>
+        <v>1.02363073825836</v>
       </c>
       <c r="H172" t="n">
         <v>236960</v>
@@ -5473,7 +5473,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G176" t="n">
-        <v>1.0917090177536</v>
+        <v>1.09170913696289</v>
       </c>
       <c r="H176" t="n">
         <v>233304</v>
@@ -5589,7 +5589,7 @@
         <v>1.73699998855591</v>
       </c>
       <c r="G180" t="n">
-        <v>1.06533622741699</v>
+        <v>1.06533634662628</v>
       </c>
       <c r="H180" t="n">
         <v>112477</v>
@@ -5618,7 +5618,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G181" t="n">
-        <v>1.06472289562225</v>
+        <v>1.06472301483154</v>
       </c>
       <c r="H181" t="n">
         <v>121177</v>
@@ -5647,7 +5647,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G182" t="n">
-        <v>1.0641096830368</v>
+        <v>1.06410980224609</v>
       </c>
       <c r="H182" t="n">
         <v>104640</v>
@@ -5734,7 +5734,7 @@
         <v>1.68900001049042</v>
       </c>
       <c r="G185" t="n">
-        <v>1.03589713573456</v>
+        <v>1.03589701652527</v>
       </c>
       <c r="H185" t="n">
         <v>97005</v>
@@ -5792,7 +5792,7 @@
         <v>1.77400004863739</v>
       </c>
       <c r="G187" t="n">
-        <v>1.08802914619446</v>
+        <v>1.08802926540375</v>
       </c>
       <c r="H187" t="n">
         <v>705957</v>
@@ -5850,7 +5850,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G189" t="n">
-        <v>1.0917090177536</v>
+        <v>1.09170913696289</v>
       </c>
       <c r="H189" t="n">
         <v>140051</v>
@@ -5908,7 +5908,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G191" t="n">
-        <v>1.11010873317719</v>
+        <v>1.1101086139679</v>
       </c>
       <c r="H191" t="n">
         <v>193032</v>
@@ -5995,7 +5995,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G194" t="n">
-        <v>1.0917090177536</v>
+        <v>1.09170913696289</v>
       </c>
       <c r="H194" t="n">
         <v>147290</v>
@@ -6285,7 +6285,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G204" t="n">
-        <v>1.10090887546539</v>
+        <v>1.10090899467468</v>
       </c>
       <c r="H204" t="n">
         <v>98997</v>
@@ -6372,7 +6372,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G207" t="n">
-        <v>1.1027489900589</v>
+        <v>1.10274887084961</v>
       </c>
       <c r="H207" t="n">
         <v>147930</v>
@@ -6633,7 +6633,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G216" t="n">
-        <v>1.22050631046295</v>
+        <v>1.22050619125366</v>
       </c>
       <c r="H216" t="n">
         <v>490241</v>
@@ -6807,7 +6807,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G222" t="n">
-        <v>1.24135911464691</v>
+        <v>1.24135899543762</v>
       </c>
       <c r="H222" t="n">
         <v>447289</v>
@@ -6836,7 +6836,7 @@
         <v>2.07399988174438</v>
       </c>
       <c r="G223" t="n">
-        <v>1.2720251083374</v>
+        <v>1.27202498912811</v>
       </c>
       <c r="H223" t="n">
         <v>256250</v>
@@ -6894,7 +6894,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G225" t="n">
-        <v>1.31495761871338</v>
+        <v>1.31495749950409</v>
       </c>
       <c r="H225" t="n">
         <v>292475</v>
@@ -6952,7 +6952,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G227" t="n">
-        <v>1.32477068901062</v>
+        <v>1.32477080821991</v>
       </c>
       <c r="H227" t="n">
         <v>203471</v>
@@ -6981,7 +6981,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G228" t="n">
-        <v>1.32477068901062</v>
+        <v>1.32477080821991</v>
       </c>
       <c r="H228" t="n">
         <v>299354</v>
@@ -7097,7 +7097,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G232" t="n">
-        <v>1.30023765563965</v>
+        <v>1.30023777484894</v>
       </c>
       <c r="H232" t="n">
         <v>267103</v>
@@ -7126,7 +7126,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G233" t="n">
-        <v>1.29901111125946</v>
+        <v>1.29901123046875</v>
       </c>
       <c r="H233" t="n">
         <v>173166</v>
@@ -7213,7 +7213,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G236" t="n">
-        <v>1.28797137737274</v>
+        <v>1.28797125816345</v>
       </c>
       <c r="H236" t="n">
         <v>205772</v>
@@ -7242,7 +7242,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G237" t="n">
-        <v>1.28797137737274</v>
+        <v>1.28797125816345</v>
       </c>
       <c r="H237" t="n">
         <v>141863</v>
@@ -7329,7 +7329,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G240" t="n">
-        <v>1.30023765563965</v>
+        <v>1.30023777484894</v>
       </c>
       <c r="H240" t="n">
         <v>384899</v>
@@ -7474,7 +7474,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G245" t="n">
-        <v>1.4768739938736</v>
+        <v>1.47687387466431</v>
       </c>
       <c r="H245" t="n">
         <v>477131</v>
@@ -7532,7 +7532,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G247" t="n">
-        <v>1.45970094203949</v>
+        <v>1.45970106124878</v>
       </c>
       <c r="H247" t="n">
         <v>391093</v>
@@ -7590,7 +7590,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G249" t="n">
-        <v>1.47932720184326</v>
+        <v>1.47932708263397</v>
       </c>
       <c r="H249" t="n">
         <v>163664</v>
@@ -7735,7 +7735,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G254" t="n">
-        <v>1.4768739938736</v>
+        <v>1.47687387466431</v>
       </c>
       <c r="H254" t="n">
         <v>139637</v>
@@ -8083,7 +8083,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G266" t="n">
-        <v>1.55169904232025</v>
+        <v>1.55169892311096</v>
       </c>
       <c r="H266" t="n">
         <v>242727</v>
@@ -8199,7 +8199,7 @@
         <v>2.5</v>
       </c>
       <c r="G270" t="n">
-        <v>1.53329932689667</v>
+        <v>1.53329944610596</v>
       </c>
       <c r="H270" t="n">
         <v>124510</v>
@@ -8228,7 +8228,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G271" t="n">
-        <v>1.52593946456909</v>
+        <v>1.5259393453598</v>
       </c>
       <c r="H271" t="n">
         <v>154741</v>
@@ -8286,7 +8286,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G273" t="n">
-        <v>1.4952734708786</v>
+        <v>1.49527359008789</v>
       </c>
       <c r="H273" t="n">
         <v>101503</v>
@@ -8373,7 +8373,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G276" t="n">
-        <v>1.52593946456909</v>
+        <v>1.5259393453598</v>
       </c>
       <c r="H276" t="n">
         <v>121968</v>
@@ -8402,7 +8402,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G277" t="n">
-        <v>1.4768739938736</v>
+        <v>1.47687387466431</v>
       </c>
       <c r="H277" t="n">
         <v>113941</v>
@@ -8518,7 +8518,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G281" t="n">
-        <v>1.41308867931366</v>
+        <v>1.41308856010437</v>
       </c>
       <c r="H281" t="n">
         <v>67393</v>
@@ -8605,7 +8605,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G284" t="n">
-        <v>1.27079856395721</v>
+        <v>1.27079844474792</v>
       </c>
       <c r="H284" t="n">
         <v>532104</v>
@@ -8692,7 +8692,7 @@
         <v>2.12400007247925</v>
       </c>
       <c r="G287" t="n">
-        <v>1.30269110202789</v>
+        <v>1.30269122123718</v>
       </c>
       <c r="H287" t="n">
         <v>326183</v>
@@ -8750,7 +8750,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G289" t="n">
-        <v>1.40940892696381</v>
+        <v>1.40940880775452</v>
       </c>
       <c r="H289" t="n">
         <v>287135</v>
@@ -8779,7 +8779,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G290" t="n">
-        <v>1.39100909233093</v>
+        <v>1.39100897312164</v>
       </c>
       <c r="H290" t="n">
         <v>208243</v>
@@ -8953,7 +8953,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G296" t="n">
-        <v>1.41063547134399</v>
+        <v>1.4106353521347</v>
       </c>
       <c r="H296" t="n">
         <v>197826</v>
@@ -9330,7 +9330,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>1.7786271572113</v>
+        <v>1.77862727642059</v>
       </c>
       <c r="H309" t="n">
         <v>373278</v>
@@ -9446,7 +9446,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G313" t="n">
-        <v>1.95526337623596</v>
+        <v>1.95526325702667</v>
       </c>
       <c r="H313" t="n">
         <v>926523</v>
@@ -9475,7 +9475,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G314" t="n">
-        <v>1.93563711643219</v>
+        <v>1.9356369972229</v>
       </c>
       <c r="H314" t="n">
         <v>1008378</v>
@@ -9562,7 +9562,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G317" t="n">
-        <v>2.15275239944458</v>
+        <v>2.152752161026</v>
       </c>
       <c r="H317" t="n">
         <v>748045</v>
@@ -9649,7 +9649,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G320" t="n">
-        <v>2.29749584197998</v>
+        <v>2.2974956035614</v>
       </c>
       <c r="H320" t="n">
         <v>576179</v>
@@ -9678,7 +9678,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G321" t="n">
-        <v>2.26928281784058</v>
+        <v>2.26928305625916</v>
       </c>
       <c r="H321" t="n">
         <v>427642</v>
@@ -9707,7 +9707,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G322" t="n">
-        <v>2.2680561542511</v>
+        <v>2.26805639266968</v>
       </c>
       <c r="H322" t="n">
         <v>763540</v>
@@ -9968,7 +9968,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G331" t="n">
-        <v>2.2680561542511</v>
+        <v>2.26805639266968</v>
       </c>
       <c r="H331" t="n">
         <v>213985</v>
@@ -9997,7 +9997,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G332" t="n">
-        <v>2.20181775093079</v>
+        <v>2.20181798934937</v>
       </c>
       <c r="H332" t="n">
         <v>420981</v>
@@ -10055,7 +10055,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G334" t="n">
-        <v>2.3392014503479</v>
+        <v>2.33920121192932</v>
       </c>
       <c r="H334" t="n">
         <v>497655</v>
@@ -10113,7 +10113,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G336" t="n">
-        <v>2.4410126209259</v>
+        <v>2.44101238250732</v>
       </c>
       <c r="H336" t="n">
         <v>688744</v>
@@ -10287,7 +10287,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>2.73540592193604</v>
+        <v>2.73540616035461</v>
       </c>
       <c r="H342" t="n">
         <v>1177654</v>
@@ -10345,7 +10345,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G344" t="n">
-        <v>2.72927284240723</v>
+        <v>2.72927260398865</v>
       </c>
       <c r="H344" t="n">
         <v>500433</v>
@@ -10432,7 +10432,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G347" t="n">
-        <v>2.93780136108398</v>
+        <v>2.93780159950256</v>
       </c>
       <c r="H347" t="n">
         <v>302332</v>
@@ -10461,7 +10461,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G348" t="n">
-        <v>2.88996267318726</v>
+        <v>2.88996243476868</v>
       </c>
       <c r="H348" t="n">
         <v>336089</v>
@@ -10490,7 +10490,7 @@
         <v>4.60799980163574</v>
       </c>
       <c r="G349" t="n">
-        <v>2.82617735862732</v>
+        <v>2.82617712020874</v>
       </c>
       <c r="H349" t="n">
         <v>339119</v>
@@ -10693,7 +10693,7 @@
         <v>5.08500003814697</v>
       </c>
       <c r="G356" t="n">
-        <v>3.1187310218811</v>
+        <v>3.11873078346252</v>
       </c>
       <c r="H356" t="n">
         <v>1016304</v>
@@ -10838,7 +10838,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G361" t="n">
-        <v>3.18619585037231</v>
+        <v>3.18619608879089</v>
       </c>
       <c r="H361" t="n">
         <v>342743</v>
@@ -10896,7 +10896,7 @@
         <v>5.125</v>
       </c>
       <c r="G363" t="n">
-        <v>3.14326357841492</v>
+        <v>3.1432638168335</v>
       </c>
       <c r="H363" t="n">
         <v>592954</v>
@@ -11186,7 +11186,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G373" t="n">
-        <v>3.03470611572266</v>
+        <v>3.03470587730408</v>
       </c>
       <c r="H373" t="n">
         <v>703525</v>
@@ -11331,7 +11331,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>3.23219513893127</v>
+        <v>3.2321949005127</v>
       </c>
       <c r="H378" t="n">
         <v>973335</v>
@@ -11418,7 +11418,7 @@
         <v>4.93400001525879</v>
       </c>
       <c r="G381" t="n">
-        <v>3.02611970901489</v>
+        <v>3.02611947059631</v>
       </c>
       <c r="H381" t="n">
         <v>560077</v>
@@ -11505,7 +11505,7 @@
         <v>4.68400001525879</v>
       </c>
       <c r="G384" t="n">
-        <v>2.87278962135315</v>
+        <v>2.87278938293457</v>
       </c>
       <c r="H384" t="n">
         <v>628468</v>
@@ -11679,7 +11679,7 @@
         <v>4.50600004196167</v>
       </c>
       <c r="G390" t="n">
-        <v>2.76361894607544</v>
+        <v>2.76361870765686</v>
       </c>
       <c r="H390" t="n">
         <v>534555</v>
@@ -11795,7 +11795,7 @@
         <v>4.69199991226196</v>
       </c>
       <c r="G394" t="n">
-        <v>2.87769603729248</v>
+        <v>2.87769627571106</v>
       </c>
       <c r="H394" t="n">
         <v>136890</v>
@@ -11940,7 +11940,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G399" t="n">
-        <v>2.67898082733154</v>
+        <v>2.67898058891296</v>
       </c>
       <c r="H399" t="n">
         <v>762725</v>
@@ -11998,7 +11998,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G401" t="n">
-        <v>2.6274619102478</v>
+        <v>2.62746167182922</v>
       </c>
       <c r="H401" t="n">
         <v>1387370</v>
@@ -12143,7 +12143,7 @@
         <v>4.2480001449585</v>
       </c>
       <c r="G406" t="n">
-        <v>2.60538220405579</v>
+        <v>2.60538244247437</v>
       </c>
       <c r="H406" t="n">
         <v>336551</v>
@@ -12230,7 +12230,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G409" t="n">
-        <v>2.57594275474548</v>
+        <v>2.5759425163269</v>
       </c>
       <c r="H409" t="n">
         <v>222579</v>
@@ -12259,7 +12259,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G410" t="n">
-        <v>2.57594275474548</v>
+        <v>2.5759425163269</v>
       </c>
       <c r="H410" t="n">
         <v>166188</v>
@@ -12317,7 +12317,7 @@
         <v>4.27400016784668</v>
       </c>
       <c r="G412" t="n">
-        <v>2.62132883071899</v>
+        <v>2.62132859230042</v>
       </c>
       <c r="H412" t="n">
         <v>485494</v>
@@ -12404,7 +12404,7 @@
         <v>4.55800008773804</v>
       </c>
       <c r="G415" t="n">
-        <v>2.79551124572754</v>
+        <v>2.79551148414612</v>
       </c>
       <c r="H415" t="n">
         <v>440882</v>
@@ -12433,7 +12433,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G416" t="n">
-        <v>2.82127094268799</v>
+        <v>2.82127070426941</v>
       </c>
       <c r="H416" t="n">
         <v>398517</v>
@@ -12462,7 +12462,7 @@
         <v>4.60400009155273</v>
       </c>
       <c r="G417" t="n">
-        <v>2.82372426986694</v>
+        <v>2.82372403144836</v>
       </c>
       <c r="H417" t="n">
         <v>268282</v>
@@ -12491,7 +12491,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G418" t="n">
-        <v>2.79428482055664</v>
+        <v>2.79428505897522</v>
       </c>
       <c r="H418" t="n">
         <v>184142</v>
@@ -12549,7 +12549,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G420" t="n">
-        <v>2.73540592193604</v>
+        <v>2.73540616035461</v>
       </c>
       <c r="H420" t="n">
         <v>222228</v>
@@ -12665,7 +12665,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G424" t="n">
-        <v>2.66794061660767</v>
+        <v>2.66794085502625</v>
       </c>
       <c r="H424" t="n">
         <v>323312</v>
@@ -12694,7 +12694,7 @@
         <v>4.24599981307983</v>
       </c>
       <c r="G425" t="n">
-        <v>2.60415530204773</v>
+        <v>2.60415554046631</v>
       </c>
       <c r="H425" t="n">
         <v>469148</v>
@@ -12723,7 +12723,7 @@
         <v>4.23400020599365</v>
       </c>
       <c r="G426" t="n">
-        <v>2.59679579734802</v>
+        <v>2.5967960357666</v>
       </c>
       <c r="H426" t="n">
         <v>653160</v>
@@ -12752,7 +12752,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G427" t="n">
-        <v>2.67898082733154</v>
+        <v>2.67898058891296</v>
       </c>
       <c r="H427" t="n">
         <v>1331409</v>
@@ -12781,7 +12781,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G428" t="n">
-        <v>2.62991523742676</v>
+        <v>2.62991499900818</v>
       </c>
       <c r="H428" t="n">
         <v>528651</v>
@@ -12810,7 +12810,7 @@
         <v>4.28200006484985</v>
       </c>
       <c r="G429" t="n">
-        <v>2.62623524665833</v>
+        <v>2.62623500823975</v>
       </c>
       <c r="H429" t="n">
         <v>411427</v>
@@ -12955,7 +12955,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G434" t="n">
-        <v>3.05065250396729</v>
+        <v>3.05065226554871</v>
       </c>
       <c r="H434" t="n">
         <v>1204033</v>
@@ -12984,7 +12984,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G435" t="n">
-        <v>3.06966543197632</v>
+        <v>3.06966519355774</v>
       </c>
       <c r="H435" t="n">
         <v>1556069</v>
@@ -13042,7 +13042,7 @@
         <v>5</v>
       </c>
       <c r="G437" t="n">
-        <v>3.06659865379333</v>
+        <v>3.06659889221191</v>
       </c>
       <c r="H437" t="n">
         <v>542060</v>
@@ -13071,7 +13071,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G438" t="n">
-        <v>3.07273197174072</v>
+        <v>3.0727322101593</v>
       </c>
       <c r="H438" t="n">
         <v>434258</v>
@@ -13158,7 +13158,7 @@
         <v>5</v>
       </c>
       <c r="G441" t="n">
-        <v>3.06659865379333</v>
+        <v>3.06659889221191</v>
       </c>
       <c r="H441" t="n">
         <v>837961</v>
@@ -13187,7 +13187,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G442" t="n">
-        <v>3.10033106803894</v>
+        <v>3.10033130645752</v>
       </c>
       <c r="H442" t="n">
         <v>607313</v>
@@ -13245,7 +13245,7 @@
         <v>5</v>
       </c>
       <c r="G444" t="n">
-        <v>3.06659865379333</v>
+        <v>3.06659889221191</v>
       </c>
       <c r="H444" t="n">
         <v>685848</v>
@@ -13564,7 +13564,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G455" t="n">
-        <v>2.96233439445496</v>
+        <v>2.96233415603638</v>
       </c>
       <c r="H455" t="n">
         <v>503874</v>
@@ -13709,7 +13709,7 @@
         <v>4.80600023269653</v>
       </c>
       <c r="G460" t="n">
-        <v>2.9476146697998</v>
+        <v>2.94761490821838</v>
       </c>
       <c r="H460" t="n">
         <v>218811</v>
@@ -13999,7 +13999,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G470" t="n">
-        <v>2.57594275474548</v>
+        <v>2.5759425163269</v>
       </c>
       <c r="H470" t="n">
         <v>671006</v>
@@ -14318,7 +14318,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G481" t="n">
-        <v>2.2680561542511</v>
+        <v>2.26805639266968</v>
       </c>
       <c r="H481" t="n">
         <v>919203</v>
@@ -14347,7 +14347,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G482" t="n">
-        <v>2.34165501594543</v>
+        <v>2.34165477752686</v>
       </c>
       <c r="H482" t="n">
         <v>702888</v>
@@ -14434,7 +14434,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G485" t="n">
-        <v>2.49375820159912</v>
+        <v>2.49375796318054</v>
       </c>
       <c r="H485" t="n">
         <v>644388</v>
@@ -14608,7 +14608,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G491" t="n">
-        <v>2.66794061660767</v>
+        <v>2.66794085502625</v>
       </c>
       <c r="H491" t="n">
         <v>3608976</v>
@@ -14637,7 +14637,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G492" t="n">
-        <v>2.63482165336609</v>
+        <v>2.63482141494751</v>
       </c>
       <c r="H492" t="n">
         <v>1627474</v>
@@ -14666,7 +14666,7 @@
         <v>4.23199987411499</v>
       </c>
       <c r="G493" t="n">
-        <v>2.59556889533997</v>
+        <v>2.59556913375854</v>
       </c>
       <c r="H493" t="n">
         <v>749802</v>
@@ -14695,7 +14695,7 @@
         <v>4.25600004196167</v>
       </c>
       <c r="G494" t="n">
-        <v>2.6102888584137</v>
+        <v>2.61028861999512</v>
       </c>
       <c r="H494" t="n">
         <v>274888</v>
@@ -14840,7 +14840,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G499" t="n">
-        <v>2.6004753112793</v>
+        <v>2.60047554969788</v>
       </c>
       <c r="H499" t="n">
         <v>400389</v>
@@ -15043,7 +15043,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G506" t="n">
-        <v>2.43242621421814</v>
+        <v>2.43242597579956</v>
       </c>
       <c r="H506" t="n">
         <v>463093</v>
@@ -15333,7 +15333,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G516" t="n">
-        <v>2.5146107673645</v>
+        <v>2.51461100578308</v>
       </c>
       <c r="H516" t="n">
         <v>279351</v>
@@ -15478,7 +15478,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G521" t="n">
-        <v>2.62991523742676</v>
+        <v>2.62991499900818</v>
       </c>
       <c r="H521" t="n">
         <v>220252</v>
@@ -15507,7 +15507,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G522" t="n">
-        <v>2.6274619102478</v>
+        <v>2.62746167182922</v>
       </c>
       <c r="H522" t="n">
         <v>284746</v>
@@ -15594,7 +15594,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G525" t="n">
-        <v>2.64954137802124</v>
+        <v>2.64954161643982</v>
       </c>
       <c r="H525" t="n">
         <v>531029</v>
@@ -15623,7 +15623,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G526" t="n">
-        <v>2.64954137802124</v>
+        <v>2.64954161643982</v>
       </c>
       <c r="H526" t="n">
         <v>459494</v>
@@ -15768,7 +15768,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G531" t="n">
-        <v>2.6004753112793</v>
+        <v>2.60047554969788</v>
       </c>
       <c r="H531" t="n">
         <v>368114</v>
@@ -15855,7 +15855,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G534" t="n">
-        <v>2.48271822929382</v>
+        <v>2.48271799087524</v>
       </c>
       <c r="H534" t="n">
         <v>309567</v>
@@ -16029,7 +16029,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G540" t="n">
-        <v>2.20181775093079</v>
+        <v>2.20181798934937</v>
       </c>
       <c r="H540" t="n">
         <v>932330</v>
@@ -16058,7 +16058,7 @@
         <v>3.60599994659424</v>
       </c>
       <c r="G541" t="n">
-        <v>2.21163105964661</v>
+        <v>2.21163082122803</v>
       </c>
       <c r="H541" t="n">
         <v>539338</v>
@@ -16087,7 +16087,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G542" t="n">
-        <v>2.1834180355072</v>
+        <v>2.18341827392578</v>
       </c>
       <c r="H542" t="n">
         <v>383193</v>
@@ -16435,7 +16435,7 @@
         <v>3.18600010871887</v>
       </c>
       <c r="G554" t="n">
-        <v>1.95403671264648</v>
+        <v>1.95403659343719</v>
       </c>
       <c r="H554" t="n">
         <v>1152409</v>
@@ -16464,7 +16464,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G555" t="n">
-        <v>1.90129125118256</v>
+        <v>1.90129113197327</v>
       </c>
       <c r="H555" t="n">
         <v>1443403</v>
@@ -16493,7 +16493,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G556" t="n">
-        <v>1.84609234333038</v>
+        <v>1.84609246253967</v>
       </c>
       <c r="H556" t="n">
         <v>675663</v>
@@ -16522,7 +16522,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G557" t="n">
-        <v>1.87921166419983</v>
+        <v>1.87921154499054</v>
       </c>
       <c r="H557" t="n">
         <v>843821</v>
@@ -16580,7 +16580,7 @@
         <v>3.15799999237061</v>
       </c>
       <c r="G559" t="n">
-        <v>1.93686378002167</v>
+        <v>1.93686366081238</v>
       </c>
       <c r="H559" t="n">
         <v>444170</v>
@@ -16609,7 +16609,7 @@
         <v>3.11800003051758</v>
       </c>
       <c r="G560" t="n">
-        <v>1.91233086585999</v>
+        <v>1.91233098506927</v>
       </c>
       <c r="H560" t="n">
         <v>430921</v>
@@ -16638,7 +16638,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G561" t="n">
-        <v>1.84609234333038</v>
+        <v>1.84609246253967</v>
       </c>
       <c r="H561" t="n">
         <v>656155</v>
@@ -16696,7 +16696,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G563" t="n">
-        <v>1.87798523902893</v>
+        <v>1.87798511981964</v>
       </c>
       <c r="H563" t="n">
         <v>1003231</v>
@@ -16725,7 +16725,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G564" t="n">
-        <v>1.87921166419983</v>
+        <v>1.87921154499054</v>
       </c>
       <c r="H564" t="n">
         <v>329963</v>
@@ -16812,7 +16812,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G567" t="n">
-        <v>1.90129125118256</v>
+        <v>1.90129113197327</v>
       </c>
       <c r="H567" t="n">
         <v>594160</v>
@@ -16841,7 +16841,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G568" t="n">
-        <v>1.98715579509735</v>
+        <v>1.98715591430664</v>
       </c>
       <c r="H568" t="n">
         <v>1455013</v>
@@ -16928,7 +16928,7 @@
         <v>3.08200001716614</v>
       </c>
       <c r="G571" t="n">
-        <v>1.89025151729584</v>
+        <v>1.89025139808655</v>
       </c>
       <c r="H571" t="n">
         <v>528910</v>
@@ -17102,7 +17102,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G577" t="n">
-        <v>1.92091727256775</v>
+        <v>1.92091739177704</v>
       </c>
       <c r="H577" t="n">
         <v>1128337</v>
@@ -17131,7 +17131,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G578" t="n">
-        <v>1.95649003982544</v>
+        <v>1.95649015903473</v>
       </c>
       <c r="H578" t="n">
         <v>584408</v>
@@ -17218,7 +17218,7 @@
         <v>3.11800003051758</v>
       </c>
       <c r="G581" t="n">
-        <v>1.91233086585999</v>
+        <v>1.91233098506927</v>
       </c>
       <c r="H581" t="n">
         <v>350643</v>
@@ -17247,7 +17247,7 @@
         <v>3.14800000190735</v>
       </c>
       <c r="G582" t="n">
-        <v>1.93073046207428</v>
+        <v>1.93073070049286</v>
       </c>
       <c r="H582" t="n">
         <v>436681</v>
@@ -17305,7 +17305,7 @@
         <v>3.32399988174438</v>
       </c>
       <c r="G584" t="n">
-        <v>2.0386745929718</v>
+        <v>2.03867483139038</v>
       </c>
       <c r="H584" t="n">
         <v>692299</v>
@@ -17334,7 +17334,7 @@
         <v>3.37199997901917</v>
       </c>
       <c r="G585" t="n">
-        <v>2.06811428070068</v>
+        <v>2.0681140422821</v>
       </c>
       <c r="H585" t="n">
         <v>393469</v>
@@ -17421,7 +17421,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G588" t="n">
-        <v>1.96262311935425</v>
+        <v>1.96262300014496</v>
       </c>
       <c r="H588" t="n">
         <v>478776</v>
@@ -17508,7 +17508,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G591" t="n">
-        <v>1.97120976448059</v>
+        <v>1.9712096452713</v>
       </c>
       <c r="H591" t="n">
         <v>772312</v>
@@ -17566,7 +17566,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G593" t="n">
-        <v>1.97734272480011</v>
+        <v>1.9773428440094</v>
       </c>
       <c r="H593" t="n">
         <v>256523</v>
@@ -17595,7 +17595,7 @@
         <v>3.25399994850159</v>
       </c>
       <c r="G594" t="n">
-        <v>1.99574244022369</v>
+        <v>1.99574255943298</v>
       </c>
       <c r="H594" t="n">
         <v>241270</v>
@@ -17624,7 +17624,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G595" t="n">
-        <v>2.08283376693726</v>
+        <v>2.08283400535583</v>
       </c>
       <c r="H595" t="n">
         <v>902410</v>
@@ -17653,7 +17653,7 @@
         <v>3.33599996566772</v>
       </c>
       <c r="G596" t="n">
-        <v>2.04603457450867</v>
+        <v>2.04603481292725</v>
       </c>
       <c r="H596" t="n">
         <v>599907</v>
@@ -17740,7 +17740,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G599" t="n">
-        <v>1.99942231178284</v>
+        <v>1.99942219257355</v>
       </c>
       <c r="H599" t="n">
         <v>777043</v>
@@ -17769,7 +17769,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G600" t="n">
-        <v>2.02640843391418</v>
+        <v>2.02640819549561</v>
       </c>
       <c r="H600" t="n">
         <v>719661</v>
@@ -17798,7 +17798,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G601" t="n">
-        <v>1.97120976448059</v>
+        <v>1.9712096452713</v>
       </c>
       <c r="H601" t="n">
         <v>1259936</v>
@@ -17856,7 +17856,7 @@
         <v>3.15199995040894</v>
       </c>
       <c r="G603" t="n">
-        <v>1.93318378925323</v>
+        <v>1.93318367004395</v>
       </c>
       <c r="H603" t="n">
         <v>745062</v>
@@ -17885,7 +17885,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G604" t="n">
-        <v>1.93441045284271</v>
+        <v>1.93441033363342</v>
       </c>
       <c r="H604" t="n">
         <v>347176</v>
@@ -17914,7 +17914,7 @@
         <v>3.08200001716614</v>
       </c>
       <c r="G605" t="n">
-        <v>1.89025151729584</v>
+        <v>1.89025139808655</v>
       </c>
       <c r="H605" t="n">
         <v>380241</v>
@@ -18001,7 +18001,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G608" t="n">
-        <v>1.88411819934845</v>
+        <v>1.88411831855774</v>
       </c>
       <c r="H608" t="n">
         <v>255709</v>
@@ -18030,7 +18030,7 @@
         <v>3.13599991798401</v>
       </c>
       <c r="G609" t="n">
-        <v>1.9233705997467</v>
+        <v>1.92337071895599</v>
       </c>
       <c r="H609" t="n">
         <v>161247</v>
@@ -18117,7 +18117,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G612" t="n">
-        <v>1.87921166419983</v>
+        <v>1.87921154499054</v>
       </c>
       <c r="H612" t="n">
         <v>402149</v>
@@ -18175,7 +18175,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G614" t="n">
-        <v>1.77985394001007</v>
+        <v>1.77985382080078</v>
       </c>
       <c r="H614" t="n">
         <v>666465</v>
@@ -18233,7 +18233,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G616" t="n">
-        <v>1.76636075973511</v>
+        <v>1.7663608789444</v>
       </c>
       <c r="H616" t="n">
         <v>727846</v>
@@ -18262,7 +18262,7 @@
         <v>3.05599999427795</v>
       </c>
       <c r="G617" t="n">
-        <v>1.8743052482605</v>
+        <v>1.87430500984192</v>
       </c>
       <c r="H617" t="n">
         <v>883535</v>
@@ -18291,7 +18291,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G618" t="n">
-        <v>1.86939883232117</v>
+        <v>1.86939871311188</v>
       </c>
       <c r="H618" t="n">
         <v>268999</v>
@@ -18320,7 +18320,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G619" t="n">
-        <v>1.87307858467102</v>
+        <v>1.87307846546173</v>
       </c>
       <c r="H619" t="n">
         <v>336325</v>
@@ -18349,7 +18349,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G620" t="n">
-        <v>1.93441045284271</v>
+        <v>1.93441033363342</v>
       </c>
       <c r="H620" t="n">
         <v>666111</v>
@@ -18378,7 +18378,7 @@
         <v>3.08400011062622</v>
       </c>
       <c r="G621" t="n">
-        <v>1.89147818088531</v>
+        <v>1.89147806167603</v>
       </c>
       <c r="H621" t="n">
         <v>497533</v>
@@ -18436,7 +18436,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G623" t="n">
-        <v>1.84609234333038</v>
+        <v>1.84609246253967</v>
       </c>
       <c r="H623" t="n">
         <v>249537</v>
@@ -18465,7 +18465,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G624" t="n">
-        <v>1.87062525749207</v>
+        <v>1.87062513828278</v>
       </c>
       <c r="H624" t="n">
         <v>269179</v>
@@ -18494,7 +18494,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G625" t="n">
-        <v>1.84609234333038</v>
+        <v>1.84609246253967</v>
       </c>
       <c r="H625" t="n">
         <v>286623</v>
@@ -18552,7 +18552,7 @@
         <v>3.01200008392334</v>
       </c>
       <c r="G627" t="n">
-        <v>1.84731900691986</v>
+        <v>1.84731912612915</v>
       </c>
       <c r="H627" t="n">
         <v>540210</v>
@@ -18668,7 +18668,7 @@
         <v>2.87599992752075</v>
       </c>
       <c r="G631" t="n">
-        <v>1.76390755176544</v>
+        <v>1.76390743255615</v>
       </c>
       <c r="H631" t="n">
         <v>379228</v>
@@ -18784,7 +18784,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G635" t="n">
-        <v>1.63020384311676</v>
+        <v>1.63020396232605</v>
       </c>
       <c r="H635" t="n">
         <v>421592</v>
@@ -18900,7 +18900,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G639" t="n">
-        <v>1.55169904232025</v>
+        <v>1.55169892311096</v>
       </c>
       <c r="H639" t="n">
         <v>341019</v>
@@ -19016,7 +19016,7 @@
         <v>2.75799989700317</v>
       </c>
       <c r="G643" t="n">
-        <v>1.69153583049774</v>
+        <v>1.69153571128845</v>
       </c>
       <c r="H643" t="n">
         <v>185397</v>
@@ -19103,7 +19103,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G646" t="n">
-        <v>1.60567104816437</v>
+        <v>1.60567116737366</v>
       </c>
       <c r="H646" t="n">
         <v>247013</v>
@@ -19190,7 +19190,7 @@
         <v>2.62800002098083</v>
       </c>
       <c r="G649" t="n">
-        <v>1.61180436611176</v>
+        <v>1.61180424690247</v>
       </c>
       <c r="H649" t="n">
         <v>203791</v>
@@ -19538,7 +19538,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G661" t="n">
-        <v>1.24135911464691</v>
+        <v>1.24135899543762</v>
       </c>
       <c r="H661" t="n">
         <v>746110</v>
@@ -19625,7 +19625,7 @@
         <v>2.1340000629425</v>
       </c>
       <c r="G664" t="n">
-        <v>1.30882441997528</v>
+        <v>1.30882430076599</v>
       </c>
       <c r="H664" t="n">
         <v>377252</v>
@@ -19712,7 +19712,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G667" t="n">
-        <v>1.23645257949829</v>
+        <v>1.23645269870758</v>
       </c>
       <c r="H667" t="n">
         <v>462440</v>
@@ -20002,7 +20002,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G677" t="n">
-        <v>1.23154592514038</v>
+        <v>1.23154604434967</v>
       </c>
       <c r="H677" t="n">
         <v>290766</v>
@@ -20031,7 +20031,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G678" t="n">
-        <v>1.24749231338501</v>
+        <v>1.24749219417572</v>
       </c>
       <c r="H678" t="n">
         <v>430500</v>
@@ -20060,7 +20060,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G679" t="n">
-        <v>1.24749231338501</v>
+        <v>1.24749219417572</v>
       </c>
       <c r="H679" t="n">
         <v>198373</v>
@@ -20118,7 +20118,7 @@
         <v>2.00600004196167</v>
       </c>
       <c r="G681" t="n">
-        <v>1.23031938076019</v>
+        <v>1.23031949996948</v>
       </c>
       <c r="H681" t="n">
         <v>692504</v>
@@ -20205,7 +20205,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G684" t="n">
-        <v>1.23522579669952</v>
+        <v>1.23522591590881</v>
       </c>
       <c r="H684" t="n">
         <v>891148</v>
@@ -20292,7 +20292,7 @@
         <v>2</v>
       </c>
       <c r="G687" t="n">
-        <v>1.22663938999176</v>
+        <v>1.22663950920105</v>
       </c>
       <c r="H687" t="n">
         <v>624287</v>
@@ -20350,7 +20350,7 @@
         <v>1.98300004005432</v>
       </c>
       <c r="G689" t="n">
-        <v>1.21621310710907</v>
+        <v>1.21621298789978</v>
       </c>
       <c r="H689" t="n">
         <v>330913</v>
@@ -20408,7 +20408,7 @@
         <v>2</v>
       </c>
       <c r="G691" t="n">
-        <v>1.22663938999176</v>
+        <v>1.22663950920105</v>
       </c>
       <c r="H691" t="n">
         <v>605384</v>
@@ -20553,7 +20553,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G696" t="n">
-        <v>1.31741082668304</v>
+        <v>1.31741070747375</v>
       </c>
       <c r="H696" t="n">
         <v>1602595</v>
@@ -20582,7 +20582,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G697" t="n">
-        <v>1.30023765563965</v>
+        <v>1.30023777484894</v>
       </c>
       <c r="H697" t="n">
         <v>729989</v>
@@ -20669,7 +20669,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G700" t="n">
-        <v>1.24626576900482</v>
+        <v>1.24626564979553</v>
       </c>
       <c r="H700" t="n">
         <v>384853</v>
@@ -20756,7 +20756,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G703" t="n">
-        <v>1.17389404773712</v>
+        <v>1.17389392852783</v>
       </c>
       <c r="H703" t="n">
         <v>1026206</v>
@@ -20814,7 +20814,7 @@
         <v>1.92299997806549</v>
       </c>
       <c r="G705" t="n">
-        <v>1.17941391468048</v>
+        <v>1.17941379547119</v>
       </c>
       <c r="H705" t="n">
         <v>288525</v>
@@ -20901,7 +20901,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G708" t="n">
-        <v>1.0843493938446</v>
+        <v>1.08434927463531</v>
       </c>
       <c r="H708" t="n">
         <v>456610</v>
@@ -20930,7 +20930,7 @@
         <v>1.7389999628067</v>
       </c>
       <c r="G709" t="n">
-        <v>1.06656289100647</v>
+        <v>1.06656301021576</v>
       </c>
       <c r="H709" t="n">
         <v>332239</v>
@@ -20959,7 +20959,7 @@
         <v>1.68700003623962</v>
       </c>
       <c r="G710" t="n">
-        <v>1.03467047214508</v>
+        <v>1.03467035293579</v>
       </c>
       <c r="H710" t="n">
         <v>398616</v>
@@ -21075,7 +21075,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G714" t="n">
-        <v>1.02792382240295</v>
+        <v>1.02792394161224</v>
       </c>
       <c r="H714" t="n">
         <v>676455</v>
@@ -21104,7 +21104,7 @@
         <v>1.625</v>
       </c>
       <c r="G715" t="n">
-        <v>0.996644556522369</v>
+        <v>0.996644616127014</v>
       </c>
       <c r="H715" t="n">
         <v>423729</v>
@@ -21220,7 +21220,7 @@
         <v>1.49300003051758</v>
       </c>
       <c r="G719" t="n">
-        <v>0.915686368942261</v>
+        <v>0.915686309337616</v>
       </c>
       <c r="H719" t="n">
         <v>735567</v>
@@ -21249,7 +21249,7 @@
         <v>1.5110000371933</v>
       </c>
       <c r="G720" t="n">
-        <v>0.926726222038269</v>
+        <v>0.926726162433624</v>
       </c>
       <c r="H720" t="n">
         <v>609534</v>
@@ -21336,7 +21336,7 @@
         <v>1.57599997520447</v>
       </c>
       <c r="G723" t="n">
-        <v>0.966591894626617</v>
+        <v>0.966591835021973</v>
       </c>
       <c r="H723" t="n">
         <v>684711</v>
@@ -21365,7 +21365,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G724" t="n">
-        <v>0.96536523103714</v>
+        <v>0.965365350246429</v>
       </c>
       <c r="H724" t="n">
         <v>453862</v>
@@ -21394,7 +21394,7 @@
         <v>1.59300005435944</v>
       </c>
       <c r="G725" t="n">
-        <v>0.977018356323242</v>
+        <v>0.977018296718597</v>
       </c>
       <c r="H725" t="n">
         <v>492029</v>
@@ -21510,7 +21510,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G729" t="n">
-        <v>0.992351353168488</v>
+        <v>0.992351412773132</v>
       </c>
       <c r="H729" t="n">
         <v>763102</v>
@@ -21539,7 +21539,7 @@
         <v>1.57200002670288</v>
       </c>
       <c r="G730" t="n">
-        <v>0.964138567447662</v>
+        <v>0.964138627052307</v>
       </c>
       <c r="H730" t="n">
         <v>464016</v>
@@ -21568,7 +21568,7 @@
         <v>1.53299999237061</v>
       </c>
       <c r="G731" t="n">
-        <v>0.940219163894653</v>
+        <v>0.940219104290009</v>
       </c>
       <c r="H731" t="n">
         <v>257158</v>
@@ -21684,7 +21684,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G735" t="n">
-        <v>0.924886226654053</v>
+        <v>0.924886167049408</v>
       </c>
       <c r="H735" t="n">
         <v>327275</v>
@@ -21887,7 +21887,7 @@
         <v>1.53299999237061</v>
       </c>
       <c r="G742" t="n">
-        <v>0.940219163894653</v>
+        <v>0.940219104290009</v>
       </c>
       <c r="H742" t="n">
         <v>982055</v>
@@ -21916,7 +21916,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G743" t="n">
-        <v>0.956778764724731</v>
+        <v>0.956778824329376</v>
       </c>
       <c r="H743" t="n">
         <v>500398</v>
@@ -21974,7 +21974,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G745" t="n">
-        <v>0.941445767879486</v>
+        <v>0.941445708274841</v>
       </c>
       <c r="H745" t="n">
         <v>656565</v>
@@ -22032,7 +22032,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G747" t="n">
-        <v>0.967205226421356</v>
+        <v>0.967205166816711</v>
       </c>
       <c r="H747" t="n">
         <v>682019</v>
@@ -22061,7 +22061,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G748" t="n">
-        <v>0.956165432929993</v>
+        <v>0.956165492534637</v>
       </c>
       <c r="H748" t="n">
         <v>267818</v>
@@ -22264,7 +22264,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G755" t="n">
-        <v>0.875207364559174</v>
+        <v>0.875207304954529</v>
       </c>
       <c r="H755" t="n">
         <v>856510</v>
@@ -22322,7 +22322,7 @@
         <v>1.37899994850159</v>
       </c>
       <c r="G757" t="n">
-        <v>0.845767915248871</v>
+        <v>0.845767855644226</v>
       </c>
       <c r="H757" t="n">
         <v>507600</v>
@@ -22380,7 +22380,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G759" t="n">
-        <v>0.849447786808014</v>
+        <v>0.849447846412659</v>
       </c>
       <c r="H759" t="n">
         <v>349314</v>
@@ -22496,7 +22496,7 @@
         <v>1.43099999427795</v>
       </c>
       <c r="G763" t="n">
-        <v>0.877660572528839</v>
+        <v>0.877660512924194</v>
       </c>
       <c r="H763" t="n">
         <v>76251</v>
@@ -22554,7 +22554,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G765" t="n">
-        <v>0.911393046379089</v>
+        <v>0.911392986774445</v>
       </c>
       <c r="H765" t="n">
         <v>318206</v>
@@ -22641,7 +22641,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G768" t="n">
-        <v>0.951872229576111</v>
+        <v>0.951872289180756</v>
       </c>
       <c r="H768" t="n">
         <v>554719</v>
@@ -22670,7 +22670,7 @@
         <v>1.60699999332428</v>
       </c>
       <c r="G769" t="n">
-        <v>0.985604882240295</v>
+        <v>0.985604822635651</v>
       </c>
       <c r="H769" t="n">
         <v>1218675</v>
@@ -22728,7 +22728,7 @@
         <v>1.61300003528595</v>
       </c>
       <c r="G771" t="n">
-        <v>0.989284694194794</v>
+        <v>0.989284753799438</v>
       </c>
       <c r="H771" t="n">
         <v>301683</v>
@@ -22844,7 +22844,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G775" t="n">
-        <v>0.982538223266602</v>
+        <v>0.982538282871246</v>
       </c>
       <c r="H775" t="n">
         <v>323658</v>
@@ -22873,7 +22873,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G776" t="n">
-        <v>0.993577897548676</v>
+        <v>0.99357795715332</v>
       </c>
       <c r="H776" t="n">
         <v>368874</v>
@@ -22931,7 +22931,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G778" t="n">
-        <v>0.940832555294037</v>
+        <v>0.940832495689392</v>
       </c>
       <c r="H778" t="n">
         <v>302240</v>
@@ -23105,7 +23105,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G784" t="n">
-        <v>1.06472289562225</v>
+        <v>1.06472301483154</v>
       </c>
       <c r="H784" t="n">
         <v>414554</v>
@@ -23221,7 +23221,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G788" t="n">
-        <v>1.03221702575684</v>
+        <v>1.03221714496613</v>
       </c>
       <c r="H788" t="n">
         <v>548765</v>
@@ -23279,7 +23279,7 @@
         <v>1.625</v>
       </c>
       <c r="G790" t="n">
-        <v>0.996644556522369</v>
+        <v>0.996644616127014</v>
       </c>
       <c r="H790" t="n">
         <v>694373</v>
@@ -23308,7 +23308,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G791" t="n">
-        <v>0.972111880779266</v>
+        <v>0.972111821174622</v>
       </c>
       <c r="H791" t="n">
         <v>381336</v>
@@ -23366,7 +23366,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G793" t="n">
-        <v>0.996031224727631</v>
+        <v>0.996031284332275</v>
       </c>
       <c r="H793" t="n">
         <v>454468</v>
@@ -23656,7 +23656,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G803" t="n">
-        <v>1.02792382240295</v>
+        <v>1.02792394161224</v>
       </c>
       <c r="H803" t="n">
         <v>1022175</v>
@@ -23714,7 +23714,7 @@
         <v>1.56700003147125</v>
       </c>
       <c r="G805" t="n">
-        <v>0.961071968078613</v>
+        <v>0.961072027683258</v>
       </c>
       <c r="H805" t="n">
         <v>514716</v>
@@ -23743,7 +23743,7 @@
         <v>1.5789999961853</v>
       </c>
       <c r="G806" t="n">
-        <v>0.968431890010834</v>
+        <v>0.968431830406189</v>
       </c>
       <c r="H806" t="n">
         <v>380344</v>
@@ -23859,7 +23859,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G810" t="n">
-        <v>0.921206176280975</v>
+        <v>0.92120623588562</v>
       </c>
       <c r="H810" t="n">
         <v>897101</v>
@@ -23975,7 +23975,7 @@
         <v>1.50600004196167</v>
       </c>
       <c r="G814" t="n">
-        <v>0.92365950345993</v>
+        <v>0.923659563064575</v>
       </c>
       <c r="H814" t="n">
         <v>219488</v>
@@ -24033,7 +24033,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G816" t="n">
-        <v>0.923046171665192</v>
+        <v>0.923046231269836</v>
       </c>
       <c r="H816" t="n">
         <v>409925</v>
@@ -24062,7 +24062,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G817" t="n">
-        <v>0.92611289024353</v>
+        <v>0.926112830638885</v>
       </c>
       <c r="H817" t="n">
         <v>331576</v>
@@ -24091,7 +24091,7 @@
         <v>1.54100000858307</v>
       </c>
       <c r="G818" t="n">
-        <v>0.945125758647919</v>
+        <v>0.945125699043274</v>
       </c>
       <c r="H818" t="n">
         <v>478848</v>
@@ -24120,7 +24120,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G819" t="n">
-        <v>0.945739090442657</v>
+        <v>0.945739030838013</v>
       </c>
       <c r="H819" t="n">
         <v>1308957</v>
@@ -24323,7 +24323,7 @@
         <v>1.53699994087219</v>
       </c>
       <c r="G826" t="n">
-        <v>0.942672431468964</v>
+        <v>0.942672491073608</v>
       </c>
       <c r="H826" t="n">
         <v>166399</v>
@@ -24352,7 +24352,7 @@
         <v>1.59300005435944</v>
       </c>
       <c r="G827" t="n">
-        <v>0.977018356323242</v>
+        <v>0.977018296718597</v>
       </c>
       <c r="H827" t="n">
         <v>400075</v>
@@ -24381,7 +24381,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G828" t="n">
-        <v>0.960458636283875</v>
+        <v>0.960458695888519</v>
       </c>
       <c r="H828" t="n">
         <v>496001</v>
@@ -24410,7 +24410,7 @@
         <v>1.65299999713898</v>
       </c>
       <c r="G829" t="n">
-        <v>1.01381754875183</v>
+        <v>1.01381742954254</v>
       </c>
       <c r="H829" t="n">
         <v>887503</v>
@@ -24439,7 +24439,7 @@
         <v>1.66100001335144</v>
       </c>
       <c r="G830" t="n">
-        <v>1.01872408390045</v>
+        <v>1.01872420310974</v>
       </c>
       <c r="H830" t="n">
         <v>270311</v>
@@ -24468,7 +24468,7 @@
         <v>1.66299998760223</v>
       </c>
       <c r="G831" t="n">
-        <v>1.01995062828064</v>
+        <v>1.01995074748993</v>
       </c>
       <c r="H831" t="n">
         <v>221352</v>
@@ -24613,7 +24613,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G836" t="n">
-        <v>0.96536523103714</v>
+        <v>0.965365350246429</v>
       </c>
       <c r="H836" t="n">
         <v>290487</v>
@@ -24700,7 +24700,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G839" t="n">
-        <v>0.977631688117981</v>
+        <v>0.977631628513336</v>
       </c>
       <c r="H839" t="n">
         <v>557684</v>
@@ -24787,7 +24787,7 @@
         <v>1.5789999961853</v>
       </c>
       <c r="G842" t="n">
-        <v>0.968431890010834</v>
+        <v>0.968431830406189</v>
       </c>
       <c r="H842" t="n">
         <v>498110</v>
@@ -24816,7 +24816,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G843" t="n">
-        <v>0.953098893165588</v>
+        <v>0.953098952770233</v>
       </c>
       <c r="H843" t="n">
         <v>226537</v>
@@ -25193,7 +25193,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G856" t="n">
-        <v>0.743343532085419</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H856" t="n">
         <v>866584</v>
@@ -25280,7 +25280,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G859" t="n">
-        <v>0.696117877960205</v>
+        <v>0.69611793756485</v>
       </c>
       <c r="H859" t="n">
         <v>285309</v>
@@ -25309,7 +25309,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G860" t="n">
-        <v>0.718810737133026</v>
+        <v>0.718810796737671</v>
       </c>
       <c r="H860" t="n">
         <v>601635</v>
@@ -25338,7 +25338,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G861" t="n">
-        <v>0.705317735671997</v>
+        <v>0.705317676067352</v>
       </c>
       <c r="H861" t="n">
         <v>305816</v>
@@ -25367,7 +25367,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G862" t="n">
-        <v>0.69857120513916</v>
+        <v>0.698571264743805</v>
       </c>
       <c r="H862" t="n">
         <v>581824</v>
@@ -25483,7 +25483,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G866" t="n">
-        <v>0.729850471019745</v>
+        <v>0.72985053062439</v>
       </c>
       <c r="H866" t="n">
         <v>419879</v>
@@ -25570,7 +25570,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G869" t="n">
-        <v>0.69857120513916</v>
+        <v>0.698571264743805</v>
       </c>
       <c r="H869" t="n">
         <v>137746</v>
@@ -25599,7 +25599,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G870" t="n">
-        <v>0.722490668296814</v>
+        <v>0.722490608692169</v>
       </c>
       <c r="H870" t="n">
         <v>551645</v>
@@ -25657,7 +25657,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G872" t="n">
-        <v>0.705317735671997</v>
+        <v>0.705317676067352</v>
       </c>
       <c r="H872" t="n">
         <v>363288</v>
@@ -25686,7 +25686,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G873" t="n">
-        <v>0.709610879421234</v>
+        <v>0.709610939025879</v>
       </c>
       <c r="H873" t="n">
         <v>47164</v>
@@ -25773,7 +25773,7 @@
         <v>1.1710000038147</v>
       </c>
       <c r="G876" t="n">
-        <v>0.718197405338287</v>
+        <v>0.718197345733643</v>
       </c>
       <c r="H876" t="n">
         <v>98716</v>
@@ -25860,7 +25860,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G879" t="n">
-        <v>0.718810737133026</v>
+        <v>0.718810796737671</v>
       </c>
       <c r="H879" t="n">
         <v>103212</v>
@@ -25889,7 +25889,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G880" t="n">
-        <v>0.722490668296814</v>
+        <v>0.722490608692169</v>
       </c>
       <c r="H880" t="n">
         <v>278772</v>
@@ -25918,7 +25918,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G881" t="n">
-        <v>0.734757006168365</v>
+        <v>0.73475706577301</v>
       </c>
       <c r="H881" t="n">
         <v>166835</v>
@@ -26121,7 +26121,7 @@
         <v>1.24699997901917</v>
       </c>
       <c r="G888" t="n">
-        <v>0.764809727668762</v>
+        <v>0.764809668064117</v>
       </c>
       <c r="H888" t="n">
         <v>84093</v>
@@ -26179,7 +26179,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G890" t="n">
-        <v>0.770329594612122</v>
+        <v>0.770329654216766</v>
       </c>
       <c r="H890" t="n">
         <v>248918</v>
@@ -26208,7 +26208,7 @@
         <v>1.25300002098083</v>
       </c>
       <c r="G891" t="n">
-        <v>0.768489599227905</v>
+        <v>0.76848965883255</v>
       </c>
       <c r="H891" t="n">
         <v>235609</v>
@@ -26237,7 +26237,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G892" t="n">
-        <v>0.775849521160126</v>
+        <v>0.775849461555481</v>
       </c>
       <c r="H892" t="n">
         <v>153630</v>
@@ -26295,7 +26295,7 @@
         <v>1.25</v>
       </c>
       <c r="G894" t="n">
-        <v>0.766649663448334</v>
+        <v>0.766649723052979</v>
       </c>
       <c r="H894" t="n">
         <v>155968</v>
@@ -26353,7 +26353,7 @@
         <v>1.25300002098083</v>
       </c>
       <c r="G896" t="n">
-        <v>0.768489599227905</v>
+        <v>0.76848965883255</v>
       </c>
       <c r="H896" t="n">
         <v>158402</v>
@@ -26411,7 +26411,7 @@
         <v>1.24699997901917</v>
       </c>
       <c r="G898" t="n">
-        <v>0.764809727668762</v>
+        <v>0.764809668064117</v>
       </c>
       <c r="H898" t="n">
         <v>106980</v>
@@ -26672,7 +26672,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G907" t="n">
-        <v>0.813261926174164</v>
+        <v>0.813261985778809</v>
       </c>
       <c r="H907" t="n">
         <v>280555</v>
@@ -26759,7 +26759,7 @@
         <v>1.25</v>
       </c>
       <c r="G910" t="n">
-        <v>0.766649663448334</v>
+        <v>0.766649723052979</v>
       </c>
       <c r="H910" t="n">
         <v>92063</v>
@@ -26846,7 +26846,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G913" t="n">
-        <v>0.724943995475769</v>
+        <v>0.724943935871124</v>
       </c>
       <c r="H913" t="n">
         <v>255453</v>
@@ -26875,7 +26875,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G914" t="n">
-        <v>0.732303738594055</v>
+        <v>0.7323037981987</v>
       </c>
       <c r="H914" t="n">
         <v>47796</v>
@@ -27078,7 +27078,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G921" t="n">
-        <v>0.732303738594055</v>
+        <v>0.7323037981987</v>
       </c>
       <c r="H921" t="n">
         <v>112754</v>
@@ -27223,7 +27223,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G926" t="n">
-        <v>0.792409121990204</v>
+        <v>0.792409062385559</v>
       </c>
       <c r="H926" t="n">
         <v>543195</v>
@@ -27281,7 +27281,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G928" t="n">
-        <v>0.770329594612122</v>
+        <v>0.770329654216766</v>
       </c>
       <c r="H928" t="n">
         <v>147741</v>
@@ -27310,7 +27310,7 @@
         <v>1.25</v>
       </c>
       <c r="G929" t="n">
-        <v>0.766649663448334</v>
+        <v>0.766649723052979</v>
       </c>
       <c r="H929" t="n">
         <v>80356</v>
@@ -27397,7 +27397,7 @@
         <v>1.25</v>
       </c>
       <c r="G932" t="n">
-        <v>0.766649663448334</v>
+        <v>0.766649723052979</v>
       </c>
       <c r="H932" t="n">
         <v>209670</v>
@@ -27455,7 +27455,7 @@
         <v>1.23699998855591</v>
       </c>
       <c r="G934" t="n">
-        <v>0.758676528930664</v>
+        <v>0.758676469326019</v>
       </c>
       <c r="H934" t="n">
         <v>75972</v>
@@ -27629,7 +27629,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G940" t="n">
-        <v>0.849447786808014</v>
+        <v>0.849447846412659</v>
       </c>
       <c r="H940" t="n">
         <v>636692</v>
@@ -27745,7 +27745,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G944" t="n">
-        <v>0.832888245582581</v>
+        <v>0.832888185977936</v>
       </c>
       <c r="H944" t="n">
         <v>363471</v>
@@ -28267,7 +28267,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G962" t="n">
-        <v>0.775849521160126</v>
+        <v>0.775849461555481</v>
       </c>
       <c r="H962" t="n">
         <v>214782</v>
@@ -28383,7 +28383,7 @@
         <v>1.29900002479553</v>
       </c>
       <c r="G966" t="n">
-        <v>0.79670238494873</v>
+        <v>0.796702325344086</v>
       </c>
       <c r="H966" t="n">
         <v>218158</v>
@@ -28412,7 +28412,7 @@
         <v>1.25300002098083</v>
       </c>
       <c r="G967" t="n">
-        <v>0.768489599227905</v>
+        <v>0.76848965883255</v>
       </c>
       <c r="H967" t="n">
         <v>275593</v>
@@ -28441,7 +28441,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G968" t="n">
-        <v>0.771556258201599</v>
+        <v>0.771556198596954</v>
       </c>
       <c r="H968" t="n">
         <v>106279</v>
@@ -28818,7 +28818,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G981" t="n">
-        <v>0.981311559677124</v>
+        <v>0.981311500072479</v>
       </c>
       <c r="H981" t="n">
         <v>380709</v>
@@ -28876,7 +28876,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G983" t="n">
-        <v>0.937152624130249</v>
+        <v>0.937152504920959</v>
       </c>
       <c r="H983" t="n">
         <v>263445</v>
@@ -28905,7 +28905,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G984" t="n">
-        <v>0.961685299873352</v>
+        <v>0.961685359477997</v>
       </c>
       <c r="H984" t="n">
         <v>669708</v>
@@ -29079,7 +29079,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G990" t="n">
-        <v>0.872140645980835</v>
+        <v>0.87214070558548</v>
       </c>
       <c r="H990" t="n">
         <v>227729</v>
@@ -29195,7 +29195,7 @@
         <v>1.53100001811981</v>
       </c>
       <c r="G994" t="n">
-        <v>0.938992619514465</v>
+        <v>0.938992559909821</v>
       </c>
       <c r="H994" t="n">
         <v>412888</v>
@@ -29253,7 +29253,7 @@
         <v>1.52699995040894</v>
       </c>
       <c r="G996" t="n">
-        <v>0.93653929233551</v>
+        <v>0.936539232730865</v>
       </c>
       <c r="H996" t="n">
         <v>279676</v>
@@ -29282,7 +29282,7 @@
         <v>1.49300003051758</v>
       </c>
       <c r="G997" t="n">
-        <v>0.915686368942261</v>
+        <v>0.915686309337616</v>
       </c>
       <c r="H997" t="n">
         <v>223364</v>
@@ -29311,7 +29311,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G998" t="n">
-        <v>0.935312628746033</v>
+        <v>0.935312569141388</v>
       </c>
       <c r="H998" t="n">
         <v>1239866</v>
@@ -29340,7 +29340,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G999" t="n">
-        <v>0.91875296831131</v>
+        <v>0.918753027915955</v>
       </c>
       <c r="H999" t="n">
         <v>695778</v>
@@ -29398,7 +29398,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G1001" t="n">
-        <v>0.916912972927094</v>
+        <v>0.916913032531738</v>
       </c>
       <c r="H1001" t="n">
         <v>566221</v>
@@ -29427,7 +29427,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G1002" t="n">
-        <v>0.91875296831131</v>
+        <v>0.918753027915955</v>
       </c>
       <c r="H1002" t="n">
         <v>198540</v>
@@ -29456,7 +29456,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G1003" t="n">
-        <v>0.91875296831131</v>
+        <v>0.918753027915955</v>
       </c>
       <c r="H1003" t="n">
         <v>784488</v>
@@ -29514,7 +29514,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.04141688346863</v>
+        <v>1.04141700267792</v>
       </c>
       <c r="H1005" t="n">
         <v>2397908</v>
@@ -29543,7 +29543,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1006" t="n">
-        <v>1.0334438085556</v>
+        <v>1.03344368934631</v>
       </c>
       <c r="H1006" t="n">
         <v>1431295</v>
@@ -29659,7 +29659,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.0193372964859</v>
+        <v>1.01933741569519</v>
       </c>
       <c r="H1010" t="n">
         <v>906453</v>
@@ -29862,7 +29862,7 @@
         <v>1.57599997520447</v>
       </c>
       <c r="G1017" t="n">
-        <v>0.966591894626617</v>
+        <v>0.966591835021973</v>
       </c>
       <c r="H1017" t="n">
         <v>660847</v>
@@ -29949,7 +29949,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1020" t="n">
-        <v>0.956778764724731</v>
+        <v>0.956778824329376</v>
       </c>
       <c r="H1020" t="n">
         <v>270776</v>
@@ -30007,7 +30007,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1022" t="n">
-        <v>0.965978562831879</v>
+        <v>0.965978682041168</v>
       </c>
       <c r="H1022" t="n">
         <v>372971</v>
@@ -30036,7 +30036,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G1023" t="n">
-        <v>0.967205226421356</v>
+        <v>0.967205166816711</v>
       </c>
       <c r="H1023" t="n">
         <v>273940</v>
@@ -30123,7 +30123,7 @@
         <v>1.58700001239777</v>
       </c>
       <c r="G1026" t="n">
-        <v>0.973338425159454</v>
+        <v>0.973338305950165</v>
       </c>
       <c r="H1026" t="n">
         <v>768858</v>
@@ -30152,7 +30152,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G1027" t="n">
-        <v>0.906486570835114</v>
+        <v>0.906486630439758</v>
       </c>
       <c r="H1027" t="n">
         <v>1879056</v>
@@ -30239,7 +30239,7 @@
         <v>1.36699998378754</v>
       </c>
       <c r="G1030" t="n">
-        <v>0.838408052921295</v>
+        <v>0.83840811252594</v>
       </c>
       <c r="H1030" t="n">
         <v>744323</v>
@@ -30326,7 +30326,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G1033" t="n">
-        <v>0.767876267433167</v>
+        <v>0.767876327037811</v>
       </c>
       <c r="H1033" t="n">
         <v>878332</v>
@@ -30355,7 +30355,7 @@
         <v>1.26699995994568</v>
       </c>
       <c r="G1034" t="n">
-        <v>0.777076065540314</v>
+        <v>0.777076125144958</v>
       </c>
       <c r="H1034" t="n">
         <v>1684681</v>
@@ -30384,7 +30384,7 @@
         <v>1.32099997997284</v>
       </c>
       <c r="G1035" t="n">
-        <v>0.81019538640976</v>
+        <v>0.810195326805115</v>
       </c>
       <c r="H1035" t="n">
         <v>1370386</v>
@@ -30529,7 +30529,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G1040" t="n">
-        <v>0.799768924713135</v>
+        <v>0.79976898431778</v>
       </c>
       <c r="H1040" t="n">
         <v>413001</v>
@@ -30790,7 +30790,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1049" t="n">
-        <v>0.813261926174164</v>
+        <v>0.813261985778809</v>
       </c>
       <c r="H1049" t="n">
         <v>258815</v>
@@ -31167,7 +31167,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.572227358818054</v>
+        <v>0.572227299213409</v>
       </c>
       <c r="H1062" t="n">
         <v>1024504</v>
@@ -31254,7 +31254,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.496788948774338</v>
+        <v>0.49678897857666</v>
       </c>
       <c r="H1065" t="n">
         <v>713971</v>
@@ -31428,7 +31428,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.4747094810009</v>
+        <v>0.474709451198578</v>
       </c>
       <c r="H1071" t="n">
         <v>273830</v>
@@ -31486,7 +31486,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.490655779838562</v>
+        <v>0.49065575003624</v>
       </c>
       <c r="H1073" t="n">
         <v>143879</v>
@@ -31544,7 +31544,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.469802916049957</v>
+        <v>0.469802886247635</v>
       </c>
       <c r="H1075" t="n">
         <v>576348</v>
@@ -31631,7 +31631,7 @@
         <v>0.679000020027161</v>
       </c>
       <c r="G1078" t="n">
-        <v>0.41644412279129</v>
+        <v>0.416444092988968</v>
       </c>
       <c r="H1078" t="n">
         <v>305317</v>
@@ -31660,7 +31660,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.399884462356567</v>
+        <v>0.39988449215889</v>
       </c>
       <c r="H1079" t="n">
         <v>1104968</v>
@@ -31718,7 +31718,7 @@
         <v>0.679000020027161</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.41644412279129</v>
+        <v>0.416444092988968</v>
       </c>
       <c r="H1081" t="n">
         <v>566218</v>
@@ -31863,7 +31863,7 @@
         <v>0.901000022888184</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.552601158618927</v>
+        <v>0.552601099014282</v>
       </c>
       <c r="H1086" t="n">
         <v>1092450</v>
@@ -31921,7 +31921,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.496788948774338</v>
+        <v>0.49678897857666</v>
       </c>
       <c r="H1088" t="n">
         <v>488572</v>
@@ -32153,7 +32153,7 @@
         <v>0.880999982357025</v>
       </c>
       <c r="G1096" t="n">
-        <v>0.540334701538086</v>
+        <v>0.540334641933441</v>
       </c>
       <c r="H1096" t="n">
         <v>135566</v>
@@ -32182,7 +32182,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1097" t="n">
-        <v>0.54340124130249</v>
+        <v>0.543401300907135</v>
       </c>
       <c r="H1097" t="n">
         <v>178955</v>
@@ -32240,7 +32240,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G1099" t="n">
-        <v>0.536041498184204</v>
+        <v>0.536041438579559</v>
       </c>
       <c r="H1099" t="n">
         <v>126540</v>
@@ -32269,7 +32269,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G1100" t="n">
-        <v>0.512121915817261</v>
+        <v>0.512121975421906</v>
       </c>
       <c r="H1100" t="n">
         <v>217518</v>
@@ -32298,7 +32298,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.506602108478546</v>
+        <v>0.506602048873901</v>
       </c>
       <c r="H1101" t="n">
         <v>179925</v>
@@ -32327,7 +32327,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1102" t="n">
-        <v>0.504148840904236</v>
+        <v>0.504148781299591</v>
       </c>
       <c r="H1102" t="n">
         <v>84582</v>
@@ -32385,7 +32385,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1104" t="n">
-        <v>0.518868565559387</v>
+        <v>0.518868505954742</v>
       </c>
       <c r="H1104" t="n">
         <v>58819</v>
@@ -32472,7 +32472,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1107" t="n">
-        <v>0.518868565559387</v>
+        <v>0.518868505954742</v>
       </c>
       <c r="H1107" t="n">
         <v>472495</v>
@@ -32501,7 +32501,7 @@
         <v>0.830999970436096</v>
       </c>
       <c r="G1108" t="n">
-        <v>0.50966864824295</v>
+        <v>0.509668707847595</v>
       </c>
       <c r="H1108" t="n">
         <v>91813</v>
@@ -32559,7 +32559,7 @@
         <v>0.848999977111816</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.520708441734314</v>
+        <v>0.520708501338959</v>
       </c>
       <c r="H1110" t="n">
         <v>181006</v>
@@ -32733,7 +32733,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1116" t="n">
-        <v>0.518868565559387</v>
+        <v>0.518868505954742</v>
       </c>
       <c r="H1116" t="n">
         <v>359020</v>
@@ -32791,7 +32791,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1118" t="n">
-        <v>0.545854508876801</v>
+        <v>0.545854568481445</v>
       </c>
       <c r="H1118" t="n">
         <v>579211</v>
@@ -32965,7 +32965,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1124" t="n">
-        <v>0.643985688686371</v>
+        <v>0.643985629081726</v>
       </c>
       <c r="H1124" t="n">
         <v>645259</v>
@@ -32994,7 +32994,7 @@
         <v>1.07400000095367</v>
       </c>
       <c r="G1125" t="n">
-        <v>0.658705413341522</v>
+        <v>0.658705353736877</v>
       </c>
       <c r="H1125" t="n">
         <v>626443</v>
@@ -33023,7 +33023,7 @@
         <v>1</v>
       </c>
       <c r="G1126" t="n">
-        <v>0.61331969499588</v>
+        <v>0.613319754600525</v>
       </c>
       <c r="H1126" t="n">
         <v>511212</v>
@@ -33110,7 +33110,7 @@
         <v>0.949000000953674</v>
       </c>
       <c r="G1129" t="n">
-        <v>0.582040369510651</v>
+        <v>0.582040429115295</v>
       </c>
       <c r="H1129" t="n">
         <v>271755</v>
@@ -33168,7 +33168,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G1131" t="n">
-        <v>0.554441034793854</v>
+        <v>0.554441094398499</v>
       </c>
       <c r="H1131" t="n">
         <v>721039</v>
@@ -33255,7 +33255,7 @@
         <v>0.876999974250793</v>
       </c>
       <c r="G1134" t="n">
-        <v>0.537881433963776</v>
+        <v>0.537881374359131</v>
       </c>
       <c r="H1134" t="n">
         <v>352691</v>
@@ -33400,7 +33400,7 @@
         <v>0.842999994754791</v>
       </c>
       <c r="G1139" t="n">
-        <v>0.517028570175171</v>
+        <v>0.517028510570526</v>
       </c>
       <c r="H1139" t="n">
         <v>186704</v>
@@ -33487,7 +33487,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1142" t="n">
-        <v>0.504148840904236</v>
+        <v>0.504148781299591</v>
       </c>
       <c r="H1142" t="n">
         <v>275625</v>
@@ -33545,7 +33545,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.516415178775787</v>
+        <v>0.516415238380432</v>
       </c>
       <c r="H1144" t="n">
         <v>471211</v>
@@ -33806,7 +33806,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.555054366588593</v>
+        <v>0.555054306983948</v>
       </c>
       <c r="H1153" t="n">
         <v>178213</v>
@@ -33835,7 +33835,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G1154" t="n">
-        <v>0.542787969112396</v>
+        <v>0.542787909507751</v>
       </c>
       <c r="H1154" t="n">
         <v>194414</v>
@@ -33893,7 +33893,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1156" t="n">
-        <v>0.542174696922302</v>
+        <v>0.542174637317657</v>
       </c>
       <c r="H1156" t="n">
         <v>144213</v>
@@ -33922,7 +33922,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1157" t="n">
-        <v>0.545854508876801</v>
+        <v>0.545854568481445</v>
       </c>
       <c r="H1157" t="n">
         <v>71533</v>
@@ -33951,7 +33951,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1158" t="n">
-        <v>0.545854508876801</v>
+        <v>0.545854568481445</v>
       </c>
       <c r="H1158" t="n">
         <v>127025</v>
@@ -34038,7 +34038,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G1161" t="n">
-        <v>0.542787969112396</v>
+        <v>0.542787909507751</v>
       </c>
       <c r="H1161" t="n">
         <v>343997</v>
@@ -34096,7 +34096,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.542174696922302</v>
+        <v>0.542174637317657</v>
       </c>
       <c r="H1163" t="n">
         <v>210006</v>
@@ -34270,7 +34270,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.567320704460144</v>
+        <v>0.567320764064789</v>
       </c>
       <c r="H1169" t="n">
         <v>120442</v>
@@ -34502,7 +34502,7 @@
         <v>0.962999999523163</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.590626895427704</v>
+        <v>0.590626955032349</v>
       </c>
       <c r="H1177" t="n">
         <v>110900</v>
@@ -34531,7 +34531,7 @@
         <v>0.962999999523163</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.590626895427704</v>
+        <v>0.590626955032349</v>
       </c>
       <c r="H1178" t="n">
         <v>48968</v>
@@ -34618,7 +34618,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.588786959648132</v>
+        <v>0.588786900043488</v>
       </c>
       <c r="H1181" t="n">
         <v>72156</v>
@@ -34647,7 +34647,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.5875603556633</v>
+        <v>0.587560296058655</v>
       </c>
       <c r="H1182" t="n">
         <v>98391</v>
@@ -34676,7 +34676,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.578973770141602</v>
+        <v>0.578973829746246</v>
       </c>
       <c r="H1183" t="n">
         <v>46587</v>
@@ -34763,7 +34763,7 @@
         <v>0.902999997138977</v>
       </c>
       <c r="G1186" t="n">
-        <v>0.55382776260376</v>
+        <v>0.553827702999115</v>
       </c>
       <c r="H1186" t="n">
         <v>407591</v>
@@ -34792,7 +34792,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.576520562171936</v>
+        <v>0.576520502567291</v>
       </c>
       <c r="H1187" t="n">
         <v>133864</v>
@@ -34821,7 +34821,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.572227358818054</v>
+        <v>0.572227299213409</v>
       </c>
       <c r="H1188" t="n">
         <v>463536</v>
@@ -35169,7 +35169,7 @@
         <v>0.89300000667572</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.547694504261017</v>
+        <v>0.547694563865662</v>
       </c>
       <c r="H1200" t="n">
         <v>153127</v>
@@ -35285,7 +35285,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G1204" t="n">
-        <v>0.555054366588593</v>
+        <v>0.555054306983948</v>
       </c>
       <c r="H1204" t="n">
         <v>55490</v>
@@ -35401,7 +35401,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.572227358818054</v>
+        <v>0.572227299213409</v>
       </c>
       <c r="H1208" t="n">
         <v>45202</v>
@@ -35459,7 +35459,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.576520562171936</v>
+        <v>0.576520502567291</v>
       </c>
       <c r="H1210" t="n">
         <v>31625</v>
@@ -35488,7 +35488,7 @@
         <v>0.944999992847443</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.57958710193634</v>
+        <v>0.579587161540985</v>
       </c>
       <c r="H1211" t="n">
         <v>145714</v>
@@ -35517,7 +35517,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1212" t="n">
-        <v>0.576520562171936</v>
+        <v>0.576520502567291</v>
       </c>
       <c r="H1212" t="n">
         <v>65395</v>
@@ -35662,7 +35662,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.576520562171936</v>
+        <v>0.576520502567291</v>
       </c>
       <c r="H1217" t="n">
         <v>57725</v>
@@ -35894,7 +35894,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.576520562171936</v>
+        <v>0.576520502567291</v>
       </c>
       <c r="H1225" t="n">
         <v>611268</v>
@@ -36068,7 +36068,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.572227358818054</v>
+        <v>0.572227299213409</v>
       </c>
       <c r="H1231" t="n">
         <v>77919</v>
@@ -36097,7 +36097,7 @@
         <v>0.944999992847443</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.57958710193634</v>
+        <v>0.579587161540985</v>
       </c>
       <c r="H1232" t="n">
         <v>109876</v>
@@ -36155,7 +36155,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.588786959648132</v>
+        <v>0.588786900043488</v>
       </c>
       <c r="H1234" t="n">
         <v>47192</v>
@@ -36184,7 +36184,7 @@
         <v>1.01600003242493</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.623132884502411</v>
+        <v>0.623132824897766</v>
       </c>
       <c r="H1235" t="n">
         <v>290003</v>
@@ -36300,7 +36300,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.648892223834991</v>
+        <v>0.648892283439636</v>
       </c>
       <c r="H1239" t="n">
         <v>338804</v>
@@ -36561,7 +36561,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.775236248970032</v>
+        <v>0.775236189365387</v>
       </c>
       <c r="H1248" t="n">
         <v>177276</v>
@@ -36590,7 +36590,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1249" t="n">
-        <v>0.821848452091217</v>
+        <v>0.821848511695862</v>
       </c>
       <c r="H1249" t="n">
         <v>385304</v>
@@ -36706,7 +36706,7 @@
         <v>1.25</v>
       </c>
       <c r="G1253" t="n">
-        <v>0.766649663448334</v>
+        <v>0.766649723052979</v>
       </c>
       <c r="H1253" t="n">
         <v>88845</v>
@@ -36880,7 +36880,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.743343532085419</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H1259" t="n">
         <v>192421</v>
@@ -36909,7 +36909,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.739663600921631</v>
+        <v>0.739663541316986</v>
       </c>
       <c r="H1260" t="n">
         <v>143028</v>
@@ -37199,7 +37199,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1270" t="n">
-        <v>0.724943995475769</v>
+        <v>0.724943935871124</v>
       </c>
       <c r="H1270" t="n">
         <v>100068</v>
@@ -37228,7 +37228,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.734757006168365</v>
+        <v>0.73475706577301</v>
       </c>
       <c r="H1271" t="n">
         <v>87758</v>
@@ -37257,7 +37257,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1272" t="n">
-        <v>0.743343532085419</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H1272" t="n">
         <v>66956</v>
@@ -37518,7 +37518,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1281" t="n">
-        <v>0.720037341117859</v>
+        <v>0.720037400722504</v>
       </c>
       <c r="H1281" t="n">
         <v>71454</v>
@@ -37663,7 +37663,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G1286" t="n">
-        <v>0.702864408493042</v>
+        <v>0.702864468097687</v>
       </c>
       <c r="H1286" t="n">
         <v>99700</v>
@@ -37721,7 +37721,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G1288" t="n">
-        <v>0.70654433965683</v>
+        <v>0.706544280052185</v>
       </c>
       <c r="H1288" t="n">
         <v>55804</v>
@@ -37750,7 +37750,7 @@
         <v>1.14800000190735</v>
       </c>
       <c r="G1289" t="n">
-        <v>0.70409107208252</v>
+        <v>0.704091012477875</v>
       </c>
       <c r="H1289" t="n">
         <v>77619</v>
@@ -37837,7 +37837,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.69059807062149</v>
+        <v>0.690598011016846</v>
       </c>
       <c r="H1292" t="n">
         <v>43018</v>
@@ -37866,7 +37866,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1293" t="n">
-        <v>0.693051338195801</v>
+        <v>0.693051278591156</v>
       </c>
       <c r="H1293" t="n">
         <v>114472</v>
@@ -37924,7 +37924,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.720037341117859</v>
+        <v>0.720037400722504</v>
       </c>
       <c r="H1295" t="n">
         <v>130325</v>
@@ -38040,7 +38040,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1299" t="n">
-        <v>0.743343532085419</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H1299" t="n">
         <v>114513</v>
@@ -38243,7 +38243,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1306" t="n">
-        <v>0.762969732284546</v>
+        <v>0.762969672679901</v>
       </c>
       <c r="H1306" t="n">
         <v>43432</v>
@@ -38533,7 +38533,7 @@
         <v>1.31400001049042</v>
       </c>
       <c r="G1316" t="n">
-        <v>0.805902183055878</v>
+        <v>0.805902123451233</v>
       </c>
       <c r="H1316" t="n">
         <v>74558</v>
@@ -38649,7 +38649,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1320" t="n">
-        <v>0.792409121990204</v>
+        <v>0.792409062385559</v>
       </c>
       <c r="H1320" t="n">
         <v>90832</v>
@@ -38707,7 +38707,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1322" t="n">
-        <v>0.835341453552246</v>
+        <v>0.835341513156891</v>
       </c>
       <c r="H1322" t="n">
         <v>275179</v>
@@ -38736,7 +38736,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G1323" t="n">
-        <v>0.841474711894989</v>
+        <v>0.841474652290344</v>
       </c>
       <c r="H1323" t="n">
         <v>216478</v>
@@ -38823,7 +38823,7 @@
         <v>1.38399994373322</v>
       </c>
       <c r="G1326" t="n">
-        <v>0.848834455013275</v>
+        <v>0.84883451461792</v>
       </c>
       <c r="H1326" t="n">
         <v>212647</v>
@@ -38910,7 +38910,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1329" t="n">
-        <v>0.813261926174164</v>
+        <v>0.813261985778809</v>
       </c>
       <c r="H1329" t="n">
         <v>142351</v>
@@ -38939,7 +38939,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1330" t="n">
-        <v>0.843928039073944</v>
+        <v>0.843927979469299</v>
       </c>
       <c r="H1330" t="n">
         <v>259824</v>
@@ -38968,7 +38968,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1331" t="n">
-        <v>0.837794780731201</v>
+        <v>0.837794840335846</v>
       </c>
       <c r="H1331" t="n">
         <v>112011</v>
@@ -39026,7 +39026,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1333" t="n">
-        <v>0.813261926174164</v>
+        <v>0.813261985778809</v>
       </c>
       <c r="H1333" t="n">
         <v>89577</v>
@@ -39055,7 +39055,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1334" t="n">
-        <v>0.85128778219223</v>
+        <v>0.851287841796875</v>
       </c>
       <c r="H1334" t="n">
         <v>98128</v>
@@ -39113,7 +39113,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1336" t="n">
-        <v>0.84638124704361</v>
+        <v>0.846381187438965</v>
       </c>
       <c r="H1336" t="n">
         <v>167091</v>
@@ -39171,7 +39171,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1338" t="n">
-        <v>0.813261926174164</v>
+        <v>0.813261985778809</v>
       </c>
       <c r="H1338" t="n">
         <v>138577</v>
@@ -39229,7 +39229,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1340" t="n">
-        <v>0.843928039073944</v>
+        <v>0.843927979469299</v>
       </c>
       <c r="H1340" t="n">
         <v>106788</v>
@@ -39287,7 +39287,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G1342" t="n">
-        <v>0.841474711894989</v>
+        <v>0.841474652290344</v>
       </c>
       <c r="H1342" t="n">
         <v>68917</v>
@@ -39490,7 +39490,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G1349" t="n">
-        <v>0.853741049766541</v>
+        <v>0.853741109371185</v>
       </c>
       <c r="H1349" t="n">
         <v>1336786</v>
@@ -39577,7 +39577,7 @@
         <v>1.43799996376038</v>
       </c>
       <c r="G1352" t="n">
-        <v>0.881953775882721</v>
+        <v>0.881953716278076</v>
       </c>
       <c r="H1352" t="n">
         <v>370355</v>
@@ -39635,7 +39635,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1354" t="n">
-        <v>0.890540301799774</v>
+        <v>0.890540242195129</v>
       </c>
       <c r="H1354" t="n">
         <v>435360</v>
@@ -39722,7 +39722,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1357" t="n">
-        <v>0.890540301799774</v>
+        <v>0.890540242195129</v>
       </c>
       <c r="H1357" t="n">
         <v>356070</v>
@@ -39751,7 +39751,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G1358" t="n">
-        <v>0.872140645980835</v>
+        <v>0.87214070558548</v>
       </c>
       <c r="H1358" t="n">
         <v>252612</v>
@@ -39780,7 +39780,7 @@
         <v>1.44599997997284</v>
       </c>
       <c r="G1359" t="n">
-        <v>0.886860251426697</v>
+        <v>0.886860311031342</v>
       </c>
       <c r="H1359" t="n">
         <v>147778</v>
@@ -39867,7 +39867,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1362" t="n">
-        <v>0.85128778219223</v>
+        <v>0.851287841796875</v>
       </c>
       <c r="H1362" t="n">
         <v>179758</v>
@@ -39896,7 +39896,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1363" t="n">
-        <v>0.84638124704361</v>
+        <v>0.846381187438965</v>
       </c>
       <c r="H1363" t="n">
         <v>171352</v>
@@ -39983,7 +39983,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1366" t="n">
-        <v>0.843928039073944</v>
+        <v>0.843927979469299</v>
       </c>
       <c r="H1366" t="n">
         <v>141918</v>
@@ -40012,7 +40012,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1367" t="n">
-        <v>0.835341453552246</v>
+        <v>0.835341513156891</v>
       </c>
       <c r="H1367" t="n">
         <v>176992</v>
@@ -40070,7 +40070,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1369" t="n">
-        <v>0.837794780731201</v>
+        <v>0.837794840335846</v>
       </c>
       <c r="H1369" t="n">
         <v>104647</v>
@@ -40418,7 +40418,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G1381" t="n">
-        <v>0.940832555294037</v>
+        <v>0.940832495689392</v>
       </c>
       <c r="H1381" t="n">
         <v>367278</v>
@@ -40447,7 +40447,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G1382" t="n">
-        <v>0.929792702198029</v>
+        <v>0.929792761802673</v>
       </c>
       <c r="H1382" t="n">
         <v>243296</v>
@@ -40563,7 +40563,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G1386" t="n">
-        <v>0.945739090442657</v>
+        <v>0.945739030838013</v>
       </c>
       <c r="H1386" t="n">
         <v>326723</v>
@@ -40621,7 +40621,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1388" t="n">
-        <v>0.890540301799774</v>
+        <v>0.890540242195129</v>
       </c>
       <c r="H1388" t="n">
         <v>318780</v>
@@ -40650,7 +40650,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G1389" t="n">
-        <v>0.921206176280975</v>
+        <v>0.92120623588562</v>
       </c>
       <c r="H1389" t="n">
         <v>395299</v>
@@ -40708,7 +40708,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1391" t="n">
-        <v>0.890540301799774</v>
+        <v>0.890540242195129</v>
       </c>
       <c r="H1391" t="n">
         <v>134123</v>
@@ -40882,7 +40882,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1397" t="n">
-        <v>0.835341453552246</v>
+        <v>0.835341513156891</v>
       </c>
       <c r="H1397" t="n">
         <v>217994</v>
@@ -41520,7 +41520,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1419" t="n">
-        <v>0.835341453552246</v>
+        <v>0.835341513156891</v>
       </c>
       <c r="H1419" t="n">
         <v>214498</v>
@@ -41549,7 +41549,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1420" t="n">
-        <v>0.84638124704361</v>
+        <v>0.846381187438965</v>
       </c>
       <c r="H1420" t="n">
         <v>163849</v>
@@ -41578,7 +41578,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1421" t="n">
-        <v>0.84638124704361</v>
+        <v>0.846381187438965</v>
       </c>
       <c r="H1421" t="n">
         <v>206853</v>
@@ -41636,7 +41636,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1423" t="n">
-        <v>0.85128778219223</v>
+        <v>0.851287841796875</v>
       </c>
       <c r="H1423" t="n">
         <v>61204</v>
@@ -41694,7 +41694,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G1425" t="n">
-        <v>0.857421040534973</v>
+        <v>0.857420980930328</v>
       </c>
       <c r="H1425" t="n">
         <v>391972</v>
@@ -41868,7 +41868,7 @@
         <v>1.43400001525879</v>
       </c>
       <c r="G1431" t="n">
-        <v>0.879500567913055</v>
+        <v>0.879500508308411</v>
       </c>
       <c r="H1431" t="n">
         <v>165321</v>
@@ -41897,7 +41897,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G1432" t="n">
-        <v>0.853741049766541</v>
+        <v>0.853741109371185</v>
       </c>
       <c r="H1432" t="n">
         <v>367934</v>
@@ -42042,7 +42042,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1437" t="n">
-        <v>0.843928039073944</v>
+        <v>0.843927979469299</v>
       </c>
       <c r="H1437" t="n">
         <v>135208</v>
@@ -42158,7 +42158,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G1441" t="n">
-        <v>0.857421040534973</v>
+        <v>0.857420980930328</v>
       </c>
       <c r="H1441" t="n">
         <v>224445</v>
@@ -42303,7 +42303,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1446" t="n">
-        <v>0.837794780731201</v>
+        <v>0.837794840335846</v>
       </c>
       <c r="H1446" t="n">
         <v>129072</v>
@@ -42332,7 +42332,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G1447" t="n">
-        <v>0.823075115680695</v>
+        <v>0.82307505607605</v>
       </c>
       <c r="H1447" t="n">
         <v>145648</v>
@@ -42448,7 +42448,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G1451" t="n">
-        <v>0.823075115680695</v>
+        <v>0.82307505607605</v>
       </c>
       <c r="H1451" t="n">
         <v>132905</v>
@@ -42477,7 +42477,7 @@
         <v>1.31400001049042</v>
       </c>
       <c r="G1452" t="n">
-        <v>0.805902183055878</v>
+        <v>0.805902123451233</v>
       </c>
       <c r="H1452" t="n">
         <v>244151</v>
@@ -42506,7 +42506,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1453" t="n">
-        <v>0.813261926174164</v>
+        <v>0.813261985778809</v>
       </c>
       <c r="H1453" t="n">
         <v>114904</v>
@@ -42622,7 +42622,7 @@
         <v>1.31400001049042</v>
       </c>
       <c r="G1457" t="n">
-        <v>0.805902183055878</v>
+        <v>0.805902123451233</v>
       </c>
       <c r="H1457" t="n">
         <v>100821</v>
@@ -42651,7 +42651,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1458" t="n">
-        <v>0.813261926174164</v>
+        <v>0.813261985778809</v>
       </c>
       <c r="H1458" t="n">
         <v>135410</v>
@@ -42709,7 +42709,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G1460" t="n">
-        <v>0.799768924713135</v>
+        <v>0.79976898431778</v>
       </c>
       <c r="H1460" t="n">
         <v>158559</v>
@@ -42854,7 +42854,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1465" t="n">
-        <v>0.792409121990204</v>
+        <v>0.792409062385559</v>
       </c>
       <c r="H1465" t="n">
         <v>190594</v>
@@ -42999,7 +42999,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1470" t="n">
-        <v>0.809582114219666</v>
+        <v>0.809582054615021</v>
       </c>
       <c r="H1470" t="n">
         <v>109019</v>
@@ -43231,7 +43231,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1478" t="n">
-        <v>0.85128778219223</v>
+        <v>0.851287841796875</v>
       </c>
       <c r="H1478" t="n">
         <v>1035445</v>
@@ -43260,7 +43260,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1479" t="n">
-        <v>0.883180379867554</v>
+        <v>0.883180439472198</v>
       </c>
       <c r="H1479" t="n">
         <v>900272</v>
@@ -43608,7 +43608,7 @@
         <v>1.31400001049042</v>
       </c>
       <c r="G1491" t="n">
-        <v>0.805902183055878</v>
+        <v>0.805902123451233</v>
       </c>
       <c r="H1491" t="n">
         <v>171192</v>
@@ -43724,7 +43724,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G1495" t="n">
-        <v>0.823075115680695</v>
+        <v>0.82307505607605</v>
       </c>
       <c r="H1495" t="n">
         <v>151385</v>
@@ -43753,7 +43753,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1496" t="n">
-        <v>0.821848452091217</v>
+        <v>0.821848511695862</v>
       </c>
       <c r="H1496" t="n">
         <v>80356</v>
@@ -43840,7 +43840,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1499" t="n">
-        <v>0.809582114219666</v>
+        <v>0.809582054615021</v>
       </c>
       <c r="H1499" t="n">
         <v>101101</v>
@@ -43869,7 +43869,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G1500" t="n">
-        <v>0.799768924713135</v>
+        <v>0.79976898431778</v>
       </c>
       <c r="H1500" t="n">
         <v>70839</v>
@@ -44043,7 +44043,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1506" t="n">
-        <v>0.743343532085419</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H1506" t="n">
         <v>53247</v>
@@ -44130,7 +44130,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G1509" t="n">
-        <v>0.722490668296814</v>
+        <v>0.722490608692169</v>
       </c>
       <c r="H1509" t="n">
         <v>119287</v>
@@ -44217,7 +44217,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1512" t="n">
-        <v>0.743343532085419</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H1512" t="n">
         <v>124927</v>
@@ -44246,7 +44246,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1513" t="n">
-        <v>0.743343532085419</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H1513" t="n">
         <v>67036</v>
@@ -44449,7 +44449,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G1520" t="n">
-        <v>0.738436996936798</v>
+        <v>0.738436937332153</v>
       </c>
       <c r="H1520" t="n">
         <v>51160</v>
@@ -44507,7 +44507,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1522" t="n">
-        <v>0.724943995475769</v>
+        <v>0.724943935871124</v>
       </c>
       <c r="H1522" t="n">
         <v>49440</v>
@@ -44623,7 +44623,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1526" t="n">
-        <v>0.724943995475769</v>
+        <v>0.724943935871124</v>
       </c>
       <c r="H1526" t="n">
         <v>112221</v>
@@ -44855,7 +44855,7 @@
         <v>1.26199996471405</v>
       </c>
       <c r="G1534" t="n">
-        <v>0.774009525775909</v>
+        <v>0.774009466171265</v>
       </c>
       <c r="H1534" t="n">
         <v>48060</v>
@@ -44971,7 +44971,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1538" t="n">
-        <v>0.771556258201599</v>
+        <v>0.771556198596954</v>
       </c>
       <c r="H1538" t="n">
         <v>69625</v>
@@ -45000,7 +45000,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1539" t="n">
-        <v>0.762969732284546</v>
+        <v>0.762969672679901</v>
       </c>
       <c r="H1539" t="n">
         <v>100515</v>
@@ -45029,7 +45029,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1540" t="n">
-        <v>0.775236248970032</v>
+        <v>0.775236189365387</v>
       </c>
       <c r="H1540" t="n">
         <v>42391</v>
@@ -45116,7 +45116,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1543" t="n">
-        <v>0.729850471019745</v>
+        <v>0.72985053062439</v>
       </c>
       <c r="H1543" t="n">
         <v>155144</v>
@@ -45232,7 +45232,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1547" t="n">
-        <v>0.732303738594055</v>
+        <v>0.7323037981987</v>
       </c>
       <c r="H1547" t="n">
         <v>79230</v>
@@ -45406,7 +45406,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G1553" t="n">
-        <v>0.734757006168365</v>
+        <v>0.73475706577301</v>
       </c>
       <c r="H1553" t="n">
         <v>104901</v>
@@ -45435,7 +45435,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1554" t="n">
-        <v>0.739663600921631</v>
+        <v>0.739663541316986</v>
       </c>
       <c r="H1554" t="n">
         <v>60612</v>
@@ -45551,7 +45551,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1558" t="n">
-        <v>0.720037341117859</v>
+        <v>0.720037400722504</v>
       </c>
       <c r="H1558" t="n">
         <v>49443</v>
@@ -45667,7 +45667,7 @@
         <v>1.14800000190735</v>
       </c>
       <c r="G1562" t="n">
-        <v>0.70409107208252</v>
+        <v>0.704091012477875</v>
       </c>
       <c r="H1562" t="n">
         <v>82654</v>
@@ -45696,7 +45696,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G1563" t="n">
-        <v>0.696731209754944</v>
+        <v>0.696731269359589</v>
       </c>
       <c r="H1563" t="n">
         <v>80261</v>
@@ -45725,7 +45725,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1564" t="n">
-        <v>0.705317735671997</v>
+        <v>0.705317676067352</v>
       </c>
       <c r="H1564" t="n">
         <v>161119</v>
@@ -45754,7 +45754,7 @@
         <v>1.06200003623962</v>
       </c>
       <c r="G1565" t="n">
-        <v>0.651345551013947</v>
+        <v>0.651345610618591</v>
       </c>
       <c r="H1565" t="n">
         <v>274347</v>
@@ -45928,7 +45928,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1571" t="n">
-        <v>0.51764190196991</v>
+        <v>0.517641842365265</v>
       </c>
       <c r="H1571" t="n">
         <v>472172</v>
@@ -45957,7 +45957,7 @@
         <v>0.788999974727631</v>
       </c>
       <c r="G1572" t="n">
-        <v>0.483909279108047</v>
+        <v>0.483909249305725</v>
       </c>
       <c r="H1572" t="n">
         <v>431253</v>
@@ -45986,7 +45986,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1573" t="n">
-        <v>0.480842649936676</v>
+        <v>0.480842679738998</v>
       </c>
       <c r="H1573" t="n">
         <v>174707</v>
@@ -46102,7 +46102,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1577" t="n">
-        <v>0.504148840904236</v>
+        <v>0.504148781299591</v>
       </c>
       <c r="H1577" t="n">
         <v>133955</v>
@@ -46131,7 +46131,7 @@
         <v>0.814999997615814</v>
       </c>
       <c r="G1578" t="n">
-        <v>0.499855577945709</v>
+        <v>0.499855548143387</v>
       </c>
       <c r="H1578" t="n">
         <v>88927</v>
@@ -46247,7 +46247,7 @@
         <v>0.897000014781952</v>
       </c>
       <c r="G1582" t="n">
-        <v>0.550147771835327</v>
+        <v>0.550147831439972</v>
       </c>
       <c r="H1582" t="n">
         <v>225480</v>
@@ -46392,7 +46392,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G1587" t="n">
-        <v>0.542787969112396</v>
+        <v>0.542787909507751</v>
       </c>
       <c r="H1587" t="n">
         <v>140994</v>
@@ -46479,7 +46479,7 @@
         <v>0.866999983787537</v>
       </c>
       <c r="G1590" t="n">
-        <v>0.531748175621033</v>
+        <v>0.531748235225677</v>
       </c>
       <c r="H1590" t="n">
         <v>167752</v>
@@ -46566,7 +46566,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G1593" t="n">
-        <v>0.536041498184204</v>
+        <v>0.536041438579559</v>
       </c>
       <c r="H1593" t="n">
         <v>57617</v>
@@ -46711,7 +46711,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1598" t="n">
-        <v>0.51764190196991</v>
+        <v>0.517641842365265</v>
       </c>
       <c r="H1598" t="n">
         <v>186829</v>
@@ -46943,7 +46943,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G1606" t="n">
-        <v>0.542787969112396</v>
+        <v>0.542787909507751</v>
       </c>
       <c r="H1606" t="n">
         <v>302675</v>
@@ -47088,7 +47088,7 @@
         <v>0.869000017642975</v>
       </c>
       <c r="G1611" t="n">
-        <v>0.53297483921051</v>
+        <v>0.532974898815155</v>
       </c>
       <c r="H1611" t="n">
         <v>108692</v>
@@ -47146,7 +47146,7 @@
         <v>0.830999970436096</v>
       </c>
       <c r="G1613" t="n">
-        <v>0.50966864824295</v>
+        <v>0.509668707847595</v>
       </c>
       <c r="H1613" t="n">
         <v>203802</v>
@@ -47175,7 +47175,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1614" t="n">
-        <v>0.51764190196991</v>
+        <v>0.517641842365265</v>
       </c>
       <c r="H1614" t="n">
         <v>160874</v>
@@ -47349,7 +47349,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G1620" t="n">
-        <v>0.519481837749481</v>
+        <v>0.519481778144836</v>
       </c>
       <c r="H1620" t="n">
         <v>106747</v>
@@ -47494,7 +47494,7 @@
         <v>0.869000017642975</v>
       </c>
       <c r="G1625" t="n">
-        <v>0.53297483921051</v>
+        <v>0.532974898815155</v>
       </c>
       <c r="H1625" t="n">
         <v>113355</v>
@@ -47610,7 +47610,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1629" t="n">
-        <v>0.572227358818054</v>
+        <v>0.572227299213409</v>
       </c>
       <c r="H1629" t="n">
         <v>80085</v>
@@ -47668,7 +47668,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G1631" t="n">
-        <v>0.574067294597626</v>
+        <v>0.574067234992981</v>
       </c>
       <c r="H1631" t="n">
         <v>117312</v>
@@ -47813,7 +47813,7 @@
         <v>1.01600003242493</v>
       </c>
       <c r="G1636" t="n">
-        <v>0.623132884502411</v>
+        <v>0.623132824897766</v>
       </c>
       <c r="H1636" t="n">
         <v>85942</v>
@@ -47929,7 +47929,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1640" t="n">
-        <v>0.545854508876801</v>
+        <v>0.545854568481445</v>
       </c>
       <c r="H1640" t="n">
         <v>111925</v>
@@ -47987,7 +47987,7 @@
         <v>0.89300000667572</v>
       </c>
       <c r="G1642" t="n">
-        <v>0.547694504261017</v>
+        <v>0.547694563865662</v>
       </c>
       <c r="H1642" t="n">
         <v>149572</v>
@@ -48045,7 +48045,7 @@
         <v>0.869000017642975</v>
       </c>
       <c r="G1644" t="n">
-        <v>0.53297483921051</v>
+        <v>0.532974898815155</v>
       </c>
       <c r="H1644" t="n">
         <v>95805</v>
@@ -48074,7 +48074,7 @@
         <v>0.898999989032745</v>
       </c>
       <c r="G1645" t="n">
-        <v>0.551374495029449</v>
+        <v>0.551374435424805</v>
       </c>
       <c r="H1645" t="n">
         <v>61905</v>
@@ -48103,7 +48103,7 @@
         <v>0.887000024318695</v>
       </c>
       <c r="G1646" t="n">
-        <v>0.544014573097229</v>
+        <v>0.544014632701874</v>
       </c>
       <c r="H1646" t="n">
         <v>120588</v>
@@ -48132,7 +48132,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G1647" t="n">
-        <v>0.554441034793854</v>
+        <v>0.554441094398499</v>
       </c>
       <c r="H1647" t="n">
         <v>152234</v>
@@ -48190,7 +48190,7 @@
         <v>0.898999989032745</v>
       </c>
       <c r="G1649" t="n">
-        <v>0.551374495029449</v>
+        <v>0.551374435424805</v>
       </c>
       <c r="H1649" t="n">
         <v>7510</v>
@@ -48364,7 +48364,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G1655" t="n">
-        <v>0.512121915817261</v>
+        <v>0.512121975421906</v>
       </c>
       <c r="H1655" t="n">
         <v>31287</v>
@@ -48393,7 +48393,7 @@
         <v>0.792999982833862</v>
       </c>
       <c r="G1656" t="n">
-        <v>0.486362546682358</v>
+        <v>0.486362516880035</v>
       </c>
       <c r="H1656" t="n">
         <v>58475</v>
@@ -48422,7 +48422,7 @@
         <v>0.788999974727631</v>
       </c>
       <c r="G1657" t="n">
-        <v>0.483909279108047</v>
+        <v>0.483909249305725</v>
       </c>
       <c r="H1657" t="n">
         <v>56680</v>
@@ -48451,7 +48451,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G1658" t="n">
-        <v>0.511508643627167</v>
+        <v>0.511508703231812</v>
       </c>
       <c r="H1658" t="n">
         <v>55747</v>
@@ -48625,7 +48625,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1664" t="n">
-        <v>0.482069283723831</v>
+        <v>0.482069313526154</v>
       </c>
       <c r="H1664" t="n">
         <v>41158</v>
@@ -48683,7 +48683,7 @@
         <v>0.787000000476837</v>
       </c>
       <c r="G1666" t="n">
-        <v>0.48268261551857</v>
+        <v>0.482682675123215</v>
       </c>
       <c r="H1666" t="n">
         <v>86039</v>
@@ -48741,7 +48741,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1668" t="n">
-        <v>0.480842649936676</v>
+        <v>0.480842679738998</v>
       </c>
       <c r="H1668" t="n">
         <v>18752</v>
@@ -49118,7 +49118,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G1681" t="n">
-        <v>0.542787969112396</v>
+        <v>0.542787909507751</v>
       </c>
       <c r="H1681" t="n">
         <v>22180</v>
@@ -49263,7 +49263,7 @@
         <v>0.880999982357025</v>
       </c>
       <c r="G1686" t="n">
-        <v>0.540334701538086</v>
+        <v>0.540334641933441</v>
       </c>
       <c r="H1686" t="n">
         <v>15422</v>
@@ -49292,7 +49292,7 @@
         <v>0.898999989032745</v>
       </c>
       <c r="G1687" t="n">
-        <v>0.551374495029449</v>
+        <v>0.551374435424805</v>
       </c>
       <c r="H1687" t="n">
         <v>12702</v>
@@ -49379,7 +49379,7 @@
         <v>0.898999989032745</v>
       </c>
       <c r="G1690" t="n">
-        <v>0.551374495029449</v>
+        <v>0.551374435424805</v>
       </c>
       <c r="H1690" t="n">
         <v>65957</v>
@@ -49408,7 +49408,7 @@
         <v>0.887000024318695</v>
       </c>
       <c r="G1691" t="n">
-        <v>0.544014573097229</v>
+        <v>0.544014632701874</v>
       </c>
       <c r="H1691" t="n">
         <v>9721</v>
@@ -49640,7 +49640,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1699" t="n">
-        <v>0.506602108478546</v>
+        <v>0.506602048873901</v>
       </c>
       <c r="H1699" t="n">
         <v>6514</v>
@@ -49669,7 +49669,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1700" t="n">
-        <v>0.498015612363815</v>
+        <v>0.498015642166138</v>
       </c>
       <c r="H1700" t="n">
         <v>31394</v>
@@ -49698,7 +49698,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1701" t="n">
-        <v>0.490655779838562</v>
+        <v>0.49065575003624</v>
       </c>
       <c r="H1701" t="n">
         <v>34760</v>
@@ -49727,7 +49727,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1702" t="n">
-        <v>0.485749274492264</v>
+        <v>0.485749244689941</v>
       </c>
       <c r="H1702" t="n">
         <v>38092</v>
@@ -49756,7 +49756,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1703" t="n">
-        <v>0.485749274492264</v>
+        <v>0.485749244689941</v>
       </c>
       <c r="H1703" t="n">
         <v>129729</v>
@@ -49785,7 +49785,7 @@
         <v>0.809000015258789</v>
       </c>
       <c r="G1704" t="n">
-        <v>0.496175676584244</v>
+        <v>0.496175706386566</v>
       </c>
       <c r="H1704" t="n">
         <v>21382</v>
@@ -49843,7 +49843,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1706" t="n">
-        <v>0.486975908279419</v>
+        <v>0.486975938081741</v>
       </c>
       <c r="H1706" t="n">
         <v>180690</v>
@@ -49901,7 +49901,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1708" t="n">
-        <v>0.4747094810009</v>
+        <v>0.474709451198578</v>
       </c>
       <c r="H1708" t="n">
         <v>124386</v>
@@ -49930,7 +49930,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1709" t="n">
-        <v>0.4747094810009</v>
+        <v>0.474709451198578</v>
       </c>
       <c r="H1709" t="n">
         <v>11175</v>
@@ -50017,7 +50017,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1712" t="n">
-        <v>0.453243285417557</v>
+        <v>0.453243315219879</v>
       </c>
       <c r="H1712" t="n">
         <v>148619</v>
@@ -50597,7 +50597,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1732" t="n">
-        <v>0.490655779838562</v>
+        <v>0.49065575003624</v>
       </c>
       <c r="H1732" t="n">
         <v>498028</v>
@@ -50742,7 +50742,7 @@
         <v>0.842999994754791</v>
       </c>
       <c r="G1737" t="n">
-        <v>0.517028570175171</v>
+        <v>0.517028510570526</v>
       </c>
       <c r="H1737" t="n">
         <v>94738</v>
@@ -50945,7 +50945,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1744" t="n">
-        <v>0.513961911201477</v>
+        <v>0.513961970806122</v>
       </c>
       <c r="H1744" t="n">
         <v>57467</v>
@@ -51148,7 +51148,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G1751" t="n">
-        <v>0.567320704460144</v>
+        <v>0.567320764064789</v>
       </c>
       <c r="H1751" t="n">
         <v>28616</v>
@@ -51235,7 +51235,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1754" t="n">
-        <v>0.542174696922302</v>
+        <v>0.542174637317657</v>
       </c>
       <c r="H1754" t="n">
         <v>75730</v>
@@ -51438,7 +51438,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1761" t="n">
-        <v>0.545854508876801</v>
+        <v>0.545854568481445</v>
       </c>
       <c r="H1761" t="n">
         <v>29697</v>
@@ -51467,7 +51467,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G1762" t="n">
-        <v>0.542787969112396</v>
+        <v>0.542787909507751</v>
       </c>
       <c r="H1762" t="n">
         <v>69410</v>
@@ -51554,7 +51554,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G1765" t="n">
-        <v>0.519481837749481</v>
+        <v>0.519481778144836</v>
       </c>
       <c r="H1765" t="n">
         <v>185940</v>
@@ -51583,7 +51583,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G1766" t="n">
-        <v>0.519481837749481</v>
+        <v>0.519481778144836</v>
       </c>
       <c r="H1766" t="n">
         <v>16972</v>
@@ -51670,7 +51670,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1769" t="n">
-        <v>0.518868565559387</v>
+        <v>0.518868505954742</v>
       </c>
       <c r="H1769" t="n">
         <v>228286</v>
@@ -51844,7 +51844,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G1775" t="n">
-        <v>0.554441034793854</v>
+        <v>0.554441094398499</v>
       </c>
       <c r="H1775" t="n">
         <v>221808</v>
@@ -51931,7 +51931,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G1778" t="n">
-        <v>0.567934036254883</v>
+        <v>0.567934095859528</v>
       </c>
       <c r="H1778" t="n">
         <v>118464</v>
@@ -51960,7 +51960,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G1779" t="n">
-        <v>0.554441034793854</v>
+        <v>0.554441094398499</v>
       </c>
       <c r="H1779" t="n">
         <v>192322</v>
@@ -52163,7 +52163,7 @@
         <v>0.944999992847443</v>
       </c>
       <c r="G1786" t="n">
-        <v>0.57958710193634</v>
+        <v>0.579587161540985</v>
       </c>
       <c r="H1786" t="n">
         <v>65962</v>
@@ -52453,7 +52453,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1796" t="n">
-        <v>0.66238534450531</v>
+        <v>0.662385404109955</v>
       </c>
       <c r="H1796" t="n">
         <v>92197</v>
@@ -52511,7 +52511,7 @@
         <v>1.09200000762939</v>
       </c>
       <c r="G1798" t="n">
-        <v>0.669745206832886</v>
+        <v>0.669745147228241</v>
       </c>
       <c r="H1798" t="n">
         <v>77905</v>
@@ -52743,7 +52743,7 @@
         <v>1.13399994373322</v>
       </c>
       <c r="G1806" t="n">
-        <v>0.695504546165466</v>
+        <v>0.695504486560822</v>
       </c>
       <c r="H1806" t="n">
         <v>83356</v>
@@ -52772,7 +52772,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G1807" t="n">
-        <v>0.702864408493042</v>
+        <v>0.702864468097687</v>
       </c>
       <c r="H1807" t="n">
         <v>166355</v>
@@ -52801,7 +52801,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1808" t="n">
-        <v>0.720037341117859</v>
+        <v>0.720037400722504</v>
       </c>
       <c r="H1808" t="n">
         <v>308736</v>
@@ -52917,7 +52917,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1812" t="n">
-        <v>0.732303738594055</v>
+        <v>0.7323037981987</v>
       </c>
       <c r="H1812" t="n">
         <v>306421</v>
@@ -52975,7 +52975,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1814" t="n">
-        <v>0.743343532085419</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H1814" t="n">
         <v>234732</v>
@@ -53149,7 +53149,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1820" t="n">
-        <v>0.724943995475769</v>
+        <v>0.724943935871124</v>
       </c>
       <c r="H1820" t="n">
         <v>326053</v>
@@ -53207,7 +53207,7 @@
         <v>1.11800003051758</v>
       </c>
       <c r="G1822" t="n">
-        <v>0.68569141626358</v>
+        <v>0.685691475868225</v>
       </c>
       <c r="H1822" t="n">
         <v>652291</v>
@@ -53294,7 +53294,7 @@
         <v>1.09399998188019</v>
       </c>
       <c r="G1825" t="n">
-        <v>0.670971810817719</v>
+        <v>0.670971751213074</v>
       </c>
       <c r="H1825" t="n">
         <v>141594</v>
@@ -53526,7 +53526,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1833" t="n">
-        <v>0.66238534450531</v>
+        <v>0.662385404109955</v>
       </c>
       <c r="H1833" t="n">
         <v>158378</v>
@@ -53584,7 +53584,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1835" t="n">
-        <v>0.643985688686371</v>
+        <v>0.643985629081726</v>
       </c>
       <c r="H1835" t="n">
         <v>341515</v>
@@ -53729,7 +53729,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1840" t="n">
-        <v>0.705317735671997</v>
+        <v>0.705317676067352</v>
       </c>
       <c r="H1840" t="n">
         <v>602597</v>
@@ -53758,7 +53758,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1841" t="n">
-        <v>0.705317735671997</v>
+        <v>0.705317676067352</v>
       </c>
       <c r="H1841" t="n">
         <v>102468</v>
@@ -53816,7 +53816,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G1843" t="n">
-        <v>0.696731209754944</v>
+        <v>0.696731269359589</v>
       </c>
       <c r="H1843" t="n">
         <v>56024</v>
@@ -53874,7 +53874,7 @@
         <v>1.11800003051758</v>
       </c>
       <c r="G1845" t="n">
-        <v>0.68569141626358</v>
+        <v>0.685691475868225</v>
       </c>
       <c r="H1845" t="n">
         <v>15468</v>
@@ -54222,7 +54222,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1857" t="n">
-        <v>0.743343532085419</v>
+        <v>0.743343591690063</v>
       </c>
       <c r="H1857" t="n">
         <v>119937</v>
@@ -54309,7 +54309,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1860" t="n">
-        <v>0.732303738594055</v>
+        <v>0.7323037981987</v>
       </c>
       <c r="H1860" t="n">
         <v>371175</v>
@@ -54512,7 +54512,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1867" t="n">
-        <v>0.724943995475769</v>
+        <v>0.724943935871124</v>
       </c>
       <c r="H1867" t="n">
         <v>161084</v>
@@ -54541,7 +54541,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G1868" t="n">
-        <v>0.70654433965683</v>
+        <v>0.706544280052185</v>
       </c>
       <c r="H1868" t="n">
         <v>208969</v>
@@ -54628,7 +54628,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G1871" t="n">
-        <v>0.696731209754944</v>
+        <v>0.696731269359589</v>
       </c>
       <c r="H1871" t="n">
         <v>92961</v>
@@ -54802,7 +54802,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1877" t="n">
-        <v>0.705317735671997</v>
+        <v>0.705317676067352</v>
       </c>
       <c r="H1877" t="n">
         <v>40683</v>
@@ -54976,7 +54976,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1883" t="n">
-        <v>0.705317735671997</v>
+        <v>0.705317676067352</v>
       </c>
       <c r="H1883" t="n">
         <v>38864</v>
@@ -55092,7 +55092,7 @@
         <v>1.09399998188019</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.670971810817719</v>
+        <v>0.670971751213074</v>
       </c>
       <c r="H1887" t="n">
         <v>84759</v>
@@ -55150,7 +55150,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.700411081314087</v>
+        <v>0.700411140918732</v>
       </c>
       <c r="H1889" t="n">
         <v>66214</v>
@@ -55353,7 +55353,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1896" t="n">
-        <v>0.720037341117859</v>
+        <v>0.720037400722504</v>
       </c>
       <c r="H1896" t="n">
         <v>20994</v>
@@ -55382,7 +55382,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G1897" t="n">
-        <v>0.718810737133026</v>
+        <v>0.718810796737671</v>
       </c>
       <c r="H1897" t="n">
         <v>28942</v>
@@ -55469,7 +55469,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1900" t="n">
-        <v>0.720037341117859</v>
+        <v>0.720037400722504</v>
       </c>
       <c r="H1900" t="n">
         <v>36684</v>
@@ -55933,7 +55933,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G1916" t="n">
-        <v>0.767876267433167</v>
+        <v>0.767876327037811</v>
       </c>
       <c r="H1916" t="n">
         <v>111462</v>
@@ -55962,7 +55962,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1917" t="n">
-        <v>0.775236248970032</v>
+        <v>0.775236189365387</v>
       </c>
       <c r="H1917" t="n">
         <v>109012</v>
@@ -56194,7 +56194,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1925" t="n">
-        <v>0.821848452091217</v>
+        <v>0.821848511695862</v>
       </c>
       <c r="H1925" t="n">
         <v>314752</v>
@@ -56252,7 +56252,7 @@
         <v>1.31200003623962</v>
       </c>
       <c r="G1927" t="n">
-        <v>0.804675459861755</v>
+        <v>0.8046755194664</v>
       </c>
       <c r="H1927" t="n">
         <v>213266</v>
@@ -56339,7 +56339,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G1930" t="n">
-        <v>0.799768924713135</v>
+        <v>0.79976898431778</v>
       </c>
       <c r="H1930" t="n">
         <v>145895</v>
@@ -56397,7 +56397,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1932" t="n">
-        <v>0.775236248970032</v>
+        <v>0.775236189365387</v>
       </c>
       <c r="H1932" t="n">
         <v>117911</v>
@@ -56629,7 +56629,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G1940" t="n">
-        <v>0.767876267433167</v>
+        <v>0.767876327037811</v>
       </c>
       <c r="H1940" t="n">
         <v>97307</v>
@@ -56977,7 +56977,7 @@
         <v>1.26199996471405</v>
       </c>
       <c r="G1952" t="n">
-        <v>0.774009525775909</v>
+        <v>0.774009466171265</v>
       </c>
       <c r="H1952" t="n">
         <v>252075</v>
@@ -57151,7 +57151,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1958" t="n">
-        <v>0.775236248970032</v>
+        <v>0.775236189365387</v>
       </c>
       <c r="H1958" t="n">
         <v>59757</v>
@@ -57180,7 +57180,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1959" t="n">
-        <v>0.775236248970032</v>
+        <v>0.775236189365387</v>
       </c>
       <c r="H1959" t="n">
         <v>60924</v>
@@ -57296,7 +57296,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G1963" t="n">
-        <v>0.799768924713135</v>
+        <v>0.79976898431778</v>
       </c>
       <c r="H1963" t="n">
         <v>206796</v>
@@ -57354,7 +57354,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1965" t="n">
-        <v>0.821848452091217</v>
+        <v>0.821848511695862</v>
       </c>
       <c r="H1965" t="n">
         <v>369054</v>
@@ -57441,7 +57441,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1968" t="n">
-        <v>0.889313578605652</v>
+        <v>0.889313638210297</v>
       </c>
       <c r="H1968" t="n">
         <v>580634</v>
@@ -57470,7 +57470,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G1969" t="n">
-        <v>0.924886226654053</v>
+        <v>0.924886167049408</v>
       </c>
       <c r="H1969" t="n">
         <v>590769</v>
@@ -57673,7 +57673,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1976" t="n">
-        <v>0.92611289024353</v>
+        <v>0.926112830638885</v>
       </c>
       <c r="H1976" t="n">
         <v>169088</v>
@@ -57760,7 +57760,7 @@
         <v>1.58800005912781</v>
       </c>
       <c r="G1979" t="n">
-        <v>0.973951816558838</v>
+        <v>0.973951876163483</v>
       </c>
       <c r="H1979" t="n">
         <v>372992</v>
@@ -57789,7 +57789,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G1980" t="n">
-        <v>1.04141688346863</v>
+        <v>1.04141700267792</v>
       </c>
       <c r="H1980" t="n">
         <v>635537</v>
@@ -57818,7 +57818,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G1981" t="n">
-        <v>1.02792382240295</v>
+        <v>1.02792394161224</v>
       </c>
       <c r="H1981" t="n">
         <v>385147</v>
@@ -57876,7 +57876,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1983" t="n">
-        <v>0.999711155891418</v>
+        <v>0.999711096286774</v>
       </c>
       <c r="H1983" t="n">
         <v>355798</v>
@@ -57905,7 +57905,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1984" t="n">
-        <v>1.02301728725433</v>
+        <v>1.02301740646362</v>
       </c>
       <c r="H1984" t="n">
         <v>591445</v>
@@ -58021,7 +58021,7 @@
         <v>1.64400005340576</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.00829768180847</v>
+        <v>1.00829756259918</v>
       </c>
       <c r="H1988" t="n">
         <v>364234</v>
@@ -58050,7 +58050,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1989" t="n">
-        <v>0.993577897548676</v>
+        <v>0.99357795715332</v>
       </c>
       <c r="H1989" t="n">
         <v>762902</v>
@@ -58137,7 +58137,7 @@
         <v>1.54799997806549</v>
       </c>
       <c r="G1992" t="n">
-        <v>0.949418962001801</v>
+        <v>0.949418902397156</v>
       </c>
       <c r="H1992" t="n">
         <v>618719</v>
@@ -58166,7 +58166,7 @@
         <v>1.54799997806549</v>
       </c>
       <c r="G1993" t="n">
-        <v>0.949418962001801</v>
+        <v>0.949418902397156</v>
       </c>
       <c r="H1993" t="n">
         <v>164171</v>
@@ -58195,7 +58195,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1994" t="n">
-        <v>0.937152624130249</v>
+        <v>0.937152504920959</v>
       </c>
       <c r="H1994" t="n">
         <v>126527</v>
@@ -58224,7 +58224,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1995" t="n">
-        <v>0.956778764724731</v>
+        <v>0.956778824329376</v>
       </c>
       <c r="H1995" t="n">
         <v>285758</v>
@@ -58253,7 +58253,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G1996" t="n">
-        <v>0.951872229576111</v>
+        <v>0.951872289180756</v>
       </c>
       <c r="H1996" t="n">
         <v>102119</v>
@@ -58282,7 +58282,7 @@
         <v>1.57799994945526</v>
       </c>
       <c r="G1997" t="n">
-        <v>0.967818558216095</v>
+        <v>0.96781849861145</v>
       </c>
       <c r="H1997" t="n">
         <v>136474</v>
@@ -58311,7 +58311,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1998" t="n">
-        <v>0.96536523103714</v>
+        <v>0.965365350246429</v>
       </c>
       <c r="H1998" t="n">
         <v>115948</v>
@@ -58369,7 +58369,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G2000" t="n">
-        <v>0.950645625591278</v>
+        <v>0.950645565986633</v>
       </c>
       <c r="H2000" t="n">
         <v>269857</v>
@@ -58398,7 +58398,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G2001" t="n">
-        <v>0.950645625591278</v>
+        <v>0.950645565986633</v>
       </c>
       <c r="H2001" t="n">
         <v>33986</v>
@@ -58427,7 +58427,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G2002" t="n">
-        <v>0.953098893165588</v>
+        <v>0.953098952770233</v>
       </c>
       <c r="H2002" t="n">
         <v>145635</v>
@@ -58514,7 +58514,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G2005" t="n">
-        <v>0.999711155891418</v>
+        <v>0.999711096286774</v>
       </c>
       <c r="H2005" t="n">
         <v>423686</v>
@@ -58543,7 +58543,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G2006" t="n">
-        <v>0.999711155891418</v>
+        <v>0.999711096286774</v>
       </c>
       <c r="H2006" t="n">
         <v>242068</v>
@@ -58601,7 +58601,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G2008" t="n">
-        <v>1.00461781024933</v>
+        <v>1.00461769104004</v>
       </c>
       <c r="H2008" t="n">
         <v>260872</v>
@@ -58659,7 +58659,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2010" t="n">
-        <v>0.993577897548676</v>
+        <v>0.99357795715332</v>
       </c>
       <c r="H2010" t="n">
         <v>107326</v>
@@ -58833,7 +58833,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G2016" t="n">
-        <v>0.988671362400055</v>
+        <v>0.9886714220047</v>
       </c>
       <c r="H2016" t="n">
         <v>414094</v>
@@ -59094,7 +59094,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G2025" t="n">
-        <v>1.14813458919525</v>
+        <v>1.14813446998596</v>
       </c>
       <c r="H2025" t="n">
         <v>435936</v>
@@ -59384,7 +59384,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G2035" t="n">
-        <v>1.24197256565094</v>
+        <v>1.24197244644165</v>
       </c>
       <c r="H2035" t="n">
         <v>121284</v>
@@ -59558,7 +59558,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2041" t="n">
-        <v>1.17757391929626</v>
+        <v>1.17757380008698</v>
       </c>
       <c r="H2041" t="n">
         <v>173482</v>
@@ -59674,7 +59674,7 @@
         <v>2</v>
       </c>
       <c r="G2045" t="n">
-        <v>1.22663938999176</v>
+        <v>1.22663950920105</v>
       </c>
       <c r="H2045" t="n">
         <v>192257</v>
@@ -59703,7 +59703,7 @@
         <v>2</v>
       </c>
       <c r="G2046" t="n">
-        <v>1.22663938999176</v>
+        <v>1.22663950920105</v>
       </c>
       <c r="H2046" t="n">
         <v>143372</v>
@@ -59877,7 +59877,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G2052" t="n">
-        <v>1.14445471763611</v>
+        <v>1.14445459842682</v>
       </c>
       <c r="H2052" t="n">
         <v>273497</v>
@@ -60080,7 +60080,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2059" t="n">
-        <v>1.13464140892029</v>
+        <v>1.13464152812958</v>
       </c>
       <c r="H2059" t="n">
         <v>125743</v>
@@ -60109,7 +60109,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G2060" t="n">
-        <v>1.1027489900589</v>
+        <v>1.10274887084961</v>
       </c>
       <c r="H2060" t="n">
         <v>180510</v>
@@ -60138,7 +60138,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2061" t="n">
-        <v>1.13464140892029</v>
+        <v>1.13464152812958</v>
       </c>
       <c r="H2061" t="n">
         <v>209670</v>
@@ -60283,7 +60283,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G2066" t="n">
-        <v>1.1579475402832</v>
+        <v>1.15794765949249</v>
       </c>
       <c r="H2066" t="n">
         <v>230384</v>
@@ -60544,7 +60544,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2075" t="n">
-        <v>1.25730538368225</v>
+        <v>1.25730550289154</v>
       </c>
       <c r="H2075" t="n">
         <v>391092</v>
@@ -60660,7 +60660,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2079" t="n">
-        <v>1.94422376155853</v>
+        <v>1.94422364234924</v>
       </c>
       <c r="H2079" t="n">
         <v>1370361</v>
@@ -60689,7 +60689,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G2080" t="n">
-        <v>1.89822459220886</v>
+        <v>1.89822471141815</v>
       </c>
       <c r="H2080" t="n">
         <v>851748</v>
@@ -60892,7 +60892,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G2087" t="n">
-        <v>1.84302580356598</v>
+        <v>1.84302592277527</v>
       </c>
       <c r="H2087" t="n">
         <v>693240</v>
@@ -60921,7 +60921,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G2088" t="n">
-        <v>1.83689248561859</v>
+        <v>1.83689260482788</v>
       </c>
       <c r="H2088" t="n">
         <v>219354</v>
@@ -60950,7 +60950,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2089" t="n">
-        <v>1.90129125118256</v>
+        <v>1.90129113197327</v>
       </c>
       <c r="H2089" t="n">
         <v>477509</v>
@@ -60979,7 +60979,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2090" t="n">
-        <v>1.90129125118256</v>
+        <v>1.90129113197327</v>
       </c>
       <c r="H2090" t="n">
         <v>391550</v>
@@ -61008,7 +61008,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2091" t="n">
-        <v>1.91355752944946</v>
+        <v>1.91355764865875</v>
       </c>
       <c r="H2091" t="n">
         <v>668620</v>
@@ -61153,7 +61153,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G2096" t="n">
-        <v>1.92889046669006</v>
+        <v>1.92889058589935</v>
       </c>
       <c r="H2096" t="n">
         <v>185807</v>
@@ -61182,7 +61182,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2097" t="n">
-        <v>1.99942231178284</v>
+        <v>1.99942219257355</v>
       </c>
       <c r="H2097" t="n">
         <v>632586</v>
@@ -61240,7 +61240,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G2099" t="n">
-        <v>1.95955646038055</v>
+        <v>1.95955657958984</v>
       </c>
       <c r="H2099" t="n">
         <v>309057</v>
@@ -61443,7 +61443,7 @@
         <v>3.25</v>
       </c>
       <c r="G2106" t="n">
-        <v>1.99328911304474</v>
+        <v>1.99328923225403</v>
       </c>
       <c r="H2106" t="n">
         <v>313415</v>
@@ -61501,7 +61501,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G2108" t="n">
-        <v>1.95342314243317</v>
+        <v>1.95342326164246</v>
       </c>
       <c r="H2108" t="n">
         <v>261617</v>
@@ -61530,7 +61530,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G2109" t="n">
-        <v>1.95342314243317</v>
+        <v>1.95342326164246</v>
       </c>
       <c r="H2109" t="n">
         <v>253803</v>
@@ -61559,7 +61559,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G2110" t="n">
-        <v>1.92889046669006</v>
+        <v>1.92889058589935</v>
       </c>
       <c r="H2110" t="n">
         <v>187344</v>
@@ -61849,7 +61849,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G2120" t="n">
-        <v>1.76942729949951</v>
+        <v>1.7694274187088</v>
       </c>
       <c r="H2120" t="n">
         <v>294872</v>
@@ -80067,6 +80067,35 @@
         <v>416070</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>1.92999994754791</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>1.94400000572205</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>1.89600002765656</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>1.90799999237061</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>1.90799999237061</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>211618</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SGF.MI.xlsx
+++ b/data/SGF.MI.xlsx
@@ -456,7 +456,7 @@
         <v>2.00399994850159</v>
       </c>
       <c r="G3" t="n">
-        <v>1.22909259796143</v>
+        <v>1.22909271717072</v>
       </c>
       <c r="H3" t="n">
         <v>161308</v>
@@ -514,7 +514,7 @@
         <v>1.93299996852875</v>
       </c>
       <c r="G5" t="n">
-        <v>1.18554711341858</v>
+        <v>1.18554699420929</v>
       </c>
       <c r="H5" t="n">
         <v>335985</v>
@@ -630,7 +630,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G9" t="n">
-        <v>1.15058791637421</v>
+        <v>1.15058779716492</v>
       </c>
       <c r="H9" t="n">
         <v>230740</v>
@@ -688,7 +688,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0855758190155</v>
+        <v>1.08557593822479</v>
       </c>
       <c r="H11" t="n">
         <v>331594</v>
@@ -717,7 +717,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G12" t="n">
-        <v>1.05613660812378</v>
+        <v>1.05613648891449</v>
       </c>
       <c r="H12" t="n">
         <v>445686</v>
@@ -746,7 +746,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G13" t="n">
-        <v>1.09293568134308</v>
+        <v>1.09293580055237</v>
       </c>
       <c r="H13" t="n">
         <v>294153</v>
@@ -833,7 +833,7 @@
         <v>1.7610000371933</v>
       </c>
       <c r="G16" t="n">
-        <v>1.08005595207214</v>
+        <v>1.08005607128143</v>
       </c>
       <c r="H16" t="n">
         <v>396007</v>
@@ -891,7 +891,7 @@
         <v>1.77400004863739</v>
       </c>
       <c r="G18" t="n">
-        <v>1.08802926540375</v>
+        <v>1.08802914619446</v>
       </c>
       <c r="H18" t="n">
         <v>242295</v>
@@ -920,7 +920,7 @@
         <v>1.75699996948242</v>
       </c>
       <c r="G19" t="n">
-        <v>1.07760274410248</v>
+        <v>1.07760286331177</v>
       </c>
       <c r="H19" t="n">
         <v>120899</v>
@@ -949,7 +949,7 @@
         <v>1.692999958992</v>
       </c>
       <c r="G20" t="n">
-        <v>1.03835022449493</v>
+        <v>1.03835034370422</v>
       </c>
       <c r="H20" t="n">
         <v>324056</v>
@@ -978,7 +978,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G21" t="n">
-        <v>1.05613660812378</v>
+        <v>1.05613648891449</v>
       </c>
       <c r="H21" t="n">
         <v>130477</v>
@@ -1007,7 +1007,7 @@
         <v>1.72800004482269</v>
       </c>
       <c r="G22" t="n">
-        <v>1.05981659889221</v>
+        <v>1.05981647968292</v>
       </c>
       <c r="H22" t="n">
         <v>122677</v>
@@ -1065,7 +1065,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G24" t="n">
-        <v>1.01075100898743</v>
+        <v>1.01075088977814</v>
       </c>
       <c r="H24" t="n">
         <v>327325</v>
@@ -1152,7 +1152,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G27" t="n">
-        <v>0.841474652290344</v>
+        <v>0.841474711894989</v>
       </c>
       <c r="H27" t="n">
         <v>327658</v>
@@ -1297,7 +1297,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G32" t="n">
-        <v>0.981311500072479</v>
+        <v>0.981311619281769</v>
       </c>
       <c r="H32" t="n">
         <v>168307</v>
@@ -1384,7 +1384,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G35" t="n">
-        <v>0.941445708274841</v>
+        <v>0.941445827484131</v>
       </c>
       <c r="H35" t="n">
         <v>350921</v>
@@ -1413,7 +1413,7 @@
         <v>1.50399994850159</v>
       </c>
       <c r="G36" t="n">
-        <v>0.922432839870453</v>
+        <v>0.922432899475098</v>
       </c>
       <c r="H36" t="n">
         <v>200666</v>
@@ -1442,7 +1442,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G37" t="n">
-        <v>0.96291196346283</v>
+        <v>0.962912023067474</v>
       </c>
       <c r="H37" t="n">
         <v>274788</v>
@@ -1471,7 +1471,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G38" t="n">
-        <v>0.941445708274841</v>
+        <v>0.941445827484131</v>
       </c>
       <c r="H38" t="n">
         <v>449707</v>
@@ -1529,7 +1529,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G40" t="n">
-        <v>0.910166501998901</v>
+        <v>0.910166442394257</v>
       </c>
       <c r="H40" t="n">
         <v>482847</v>
@@ -1558,7 +1558,7 @@
         <v>1.52699995040894</v>
       </c>
       <c r="G41" t="n">
-        <v>0.936539232730865</v>
+        <v>0.936539173126221</v>
       </c>
       <c r="H41" t="n">
         <v>374615</v>
@@ -1587,7 +1587,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G42" t="n">
-        <v>0.87214070558548</v>
+        <v>0.872140765190125</v>
       </c>
       <c r="H42" t="n">
         <v>633854</v>
@@ -1616,7 +1616,7 @@
         <v>1.5</v>
       </c>
       <c r="G43" t="n">
-        <v>0.919979512691498</v>
+        <v>0.919979631900787</v>
       </c>
       <c r="H43" t="n">
         <v>841811</v>
@@ -1645,7 +1645,7 @@
         <v>1.5789999961853</v>
       </c>
       <c r="G44" t="n">
-        <v>0.968431830406189</v>
+        <v>0.968431770801544</v>
       </c>
       <c r="H44" t="n">
         <v>563184</v>
@@ -1674,7 +1674,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G45" t="n">
-        <v>1.04264354705811</v>
+        <v>1.0426436662674</v>
       </c>
       <c r="H45" t="n">
         <v>1154922</v>
@@ -1819,7 +1819,7 @@
         <v>1.54700005054474</v>
       </c>
       <c r="G50" t="n">
-        <v>0.948805630207062</v>
+        <v>0.948805689811707</v>
       </c>
       <c r="H50" t="n">
         <v>402246</v>
@@ -1848,7 +1848,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G51" t="n">
-        <v>0.986218154430389</v>
+        <v>0.986218214035034</v>
       </c>
       <c r="H51" t="n">
         <v>297628</v>
@@ -1935,7 +1935,7 @@
         <v>1.58299994468689</v>
       </c>
       <c r="G54" t="n">
-        <v>0.970885038375854</v>
+        <v>0.970885157585144</v>
       </c>
       <c r="H54" t="n">
         <v>320346</v>
@@ -1964,7 +1964,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G55" t="n">
-        <v>0.956165492534637</v>
+        <v>0.956165432929993</v>
       </c>
       <c r="H55" t="n">
         <v>282072</v>
@@ -2051,7 +2051,7 @@
         <v>1.5</v>
       </c>
       <c r="G58" t="n">
-        <v>0.919979512691498</v>
+        <v>0.919979631900787</v>
       </c>
       <c r="H58" t="n">
         <v>214751</v>
@@ -2109,7 +2109,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G60" t="n">
-        <v>0.853741109371185</v>
+        <v>0.853741049766541</v>
       </c>
       <c r="H60" t="n">
         <v>330575</v>
@@ -2138,7 +2138,7 @@
         <v>1.34300005435944</v>
       </c>
       <c r="G61" t="n">
-        <v>0.823688447475433</v>
+        <v>0.823688387870789</v>
       </c>
       <c r="H61" t="n">
         <v>330707</v>
@@ -2196,7 +2196,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G63" t="n">
-        <v>0.867234110832214</v>
+        <v>0.86723405122757</v>
       </c>
       <c r="H63" t="n">
         <v>267980</v>
@@ -2254,7 +2254,7 @@
         <v>1.34599995613098</v>
       </c>
       <c r="G65" t="n">
-        <v>0.82552832365036</v>
+        <v>0.825528383255005</v>
       </c>
       <c r="H65" t="n">
         <v>258827</v>
@@ -2283,7 +2283,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G66" t="n">
-        <v>0.815715253353119</v>
+        <v>0.815715312957764</v>
       </c>
       <c r="H66" t="n">
         <v>496873</v>
@@ -2312,7 +2312,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G67" t="n">
-        <v>0.818781852722168</v>
+        <v>0.818781912326813</v>
       </c>
       <c r="H67" t="n">
         <v>147823</v>
@@ -2341,7 +2341,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G68" t="n">
-        <v>0.794249057769775</v>
+        <v>0.79424911737442</v>
       </c>
       <c r="H68" t="n">
         <v>210357</v>
@@ -2370,7 +2370,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G69" t="n">
-        <v>0.832888185977936</v>
+        <v>0.832888245582581</v>
       </c>
       <c r="H69" t="n">
         <v>207067</v>
@@ -2486,7 +2486,7 @@
         <v>1.43299996852875</v>
       </c>
       <c r="G73" t="n">
-        <v>0.878887236118317</v>
+        <v>0.878887116909027</v>
       </c>
       <c r="H73" t="n">
         <v>194805</v>
@@ -2544,7 +2544,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G75" t="n">
-        <v>0.89544677734375</v>
+        <v>0.895446836948395</v>
       </c>
       <c r="H75" t="n">
         <v>124767</v>
@@ -2573,7 +2573,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G76" t="n">
-        <v>0.852514386177063</v>
+        <v>0.852514445781708</v>
       </c>
       <c r="H76" t="n">
         <v>774434</v>
@@ -2631,7 +2631,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G78" t="n">
-        <v>0.875207304954529</v>
+        <v>0.875207245349884</v>
       </c>
       <c r="H78" t="n">
         <v>207294</v>
@@ -2689,7 +2689,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G80" t="n">
-        <v>0.87214070558548</v>
+        <v>0.872140765190125</v>
       </c>
       <c r="H80" t="n">
         <v>27237</v>
@@ -2747,7 +2747,7 @@
         <v>1.5</v>
       </c>
       <c r="G82" t="n">
-        <v>0.919979512691498</v>
+        <v>0.919979631900787</v>
       </c>
       <c r="H82" t="n">
         <v>823016</v>
@@ -2776,7 +2776,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G83" t="n">
-        <v>0.943285763263702</v>
+        <v>0.943285703659058</v>
       </c>
       <c r="H83" t="n">
         <v>666476</v>
@@ -2863,7 +2863,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G86" t="n">
-        <v>0.951258957386017</v>
+        <v>0.951258897781372</v>
       </c>
       <c r="H86" t="n">
         <v>426890</v>
@@ -2892,7 +2892,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G87" t="n">
-        <v>0.951258957386017</v>
+        <v>0.951258897781372</v>
       </c>
       <c r="H87" t="n">
         <v>290985</v>
@@ -2921,7 +2921,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G88" t="n">
-        <v>0.951258957386017</v>
+        <v>0.951258897781372</v>
       </c>
       <c r="H88" t="n">
         <v>302509</v>
@@ -2950,7 +2950,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G89" t="n">
-        <v>0.951258957386017</v>
+        <v>0.951258897781372</v>
       </c>
       <c r="H89" t="n">
         <v>223150</v>
@@ -2979,7 +2979,7 @@
         <v>1.50100004673004</v>
       </c>
       <c r="G90" t="n">
-        <v>0.920592963695526</v>
+        <v>0.920592904090881</v>
       </c>
       <c r="H90" t="n">
         <v>157165</v>
@@ -3008,7 +3008,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G91" t="n">
-        <v>0.938379287719727</v>
+        <v>0.938379228115082</v>
       </c>
       <c r="H91" t="n">
         <v>93150</v>
@@ -3037,7 +3037,7 @@
         <v>1.54700005054474</v>
       </c>
       <c r="G92" t="n">
-        <v>0.948805630207062</v>
+        <v>0.948805689811707</v>
       </c>
       <c r="H92" t="n">
         <v>98852</v>
@@ -3066,7 +3066,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G93" t="n">
-        <v>0.978245079517365</v>
+        <v>0.978244960308075</v>
       </c>
       <c r="H93" t="n">
         <v>347619</v>
@@ -3211,7 +3211,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G98" t="n">
-        <v>0.943285763263702</v>
+        <v>0.943285703659058</v>
       </c>
       <c r="H98" t="n">
         <v>263085</v>
@@ -3240,7 +3240,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G99" t="n">
-        <v>0.935312569141388</v>
+        <v>0.935312628746033</v>
       </c>
       <c r="H99" t="n">
         <v>196453</v>
@@ -3269,7 +3269,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G100" t="n">
-        <v>0.927339434623718</v>
+        <v>0.927339375019073</v>
       </c>
       <c r="H100" t="n">
         <v>141573</v>
@@ -3298,7 +3298,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G101" t="n">
-        <v>0.953712105751038</v>
+        <v>0.953712165355682</v>
       </c>
       <c r="H101" t="n">
         <v>438231</v>
@@ -3414,7 +3414,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G105" t="n">
-        <v>1.12360179424286</v>
+        <v>1.12360167503357</v>
       </c>
       <c r="H105" t="n">
         <v>517266</v>
@@ -3472,7 +3472,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G107" t="n">
-        <v>1.04264354705811</v>
+        <v>1.0426436662674</v>
       </c>
       <c r="H107" t="n">
         <v>337346</v>
@@ -3501,7 +3501,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G108" t="n">
-        <v>1.03037703037262</v>
+        <v>1.03037714958191</v>
       </c>
       <c r="H108" t="n">
         <v>290532</v>
@@ -3559,7 +3559,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G110" t="n">
-        <v>0.999711096286774</v>
+        <v>0.999711155891418</v>
       </c>
       <c r="H110" t="n">
         <v>236211</v>
@@ -3588,7 +3588,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G111" t="n">
-        <v>1.00707101821899</v>
+        <v>1.0070708990097</v>
       </c>
       <c r="H111" t="n">
         <v>230111</v>
@@ -3617,7 +3617,7 @@
         <v>1.625</v>
       </c>
       <c r="G112" t="n">
-        <v>0.996644616127014</v>
+        <v>0.996644556522369</v>
       </c>
       <c r="H112" t="n">
         <v>276657</v>
@@ -3646,7 +3646,7 @@
         <v>1.60099995136261</v>
       </c>
       <c r="G113" t="n">
-        <v>0.981924831867218</v>
+        <v>0.981924891471863</v>
       </c>
       <c r="H113" t="n">
         <v>124731</v>
@@ -3675,7 +3675,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G114" t="n">
-        <v>0.935312569141388</v>
+        <v>0.935312628746033</v>
       </c>
       <c r="H114" t="n">
         <v>354806</v>
@@ -3704,7 +3704,7 @@
         <v>1.39300000667572</v>
       </c>
       <c r="G115" t="n">
-        <v>0.854354381561279</v>
+        <v>0.854354441165924</v>
       </c>
       <c r="H115" t="n">
         <v>1016663</v>
@@ -3820,7 +3820,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G119" t="n">
-        <v>0.792409062385559</v>
+        <v>0.792409121990204</v>
       </c>
       <c r="H119" t="n">
         <v>527410</v>
@@ -3907,7 +3907,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G122" t="n">
-        <v>0.875207304954529</v>
+        <v>0.875207245349884</v>
       </c>
       <c r="H122" t="n">
         <v>340422</v>
@@ -3994,7 +3994,7 @@
         <v>1.24800002574921</v>
       </c>
       <c r="G125" t="n">
-        <v>0.765422999858856</v>
+        <v>0.765423059463501</v>
       </c>
       <c r="H125" t="n">
         <v>532951</v>
@@ -4168,7 +4168,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G131" t="n">
-        <v>0.725557267665863</v>
+        <v>0.725557208061218</v>
       </c>
       <c r="H131" t="n">
         <v>634478</v>
@@ -4284,7 +4284,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G135" t="n">
-        <v>0.771556198596954</v>
+        <v>0.771556258201599</v>
       </c>
       <c r="H135" t="n">
         <v>325977</v>
@@ -4342,7 +4342,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G137" t="n">
-        <v>0.803448796272278</v>
+        <v>0.803448855876923</v>
       </c>
       <c r="H137" t="n">
         <v>159758</v>
@@ -4603,7 +4603,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G146" t="n">
-        <v>0.884407043457031</v>
+        <v>0.884407103061676</v>
       </c>
       <c r="H146" t="n">
         <v>428209</v>
@@ -4661,7 +4661,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G148" t="n">
-        <v>0.935312569141388</v>
+        <v>0.935312628746033</v>
       </c>
       <c r="H148" t="n">
         <v>421354</v>
@@ -4690,7 +4690,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G149" t="n">
-        <v>0.932246029376984</v>
+        <v>0.932245969772339</v>
       </c>
       <c r="H149" t="n">
         <v>325924</v>
@@ -4719,7 +4719,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G150" t="n">
-        <v>0.935925900936127</v>
+        <v>0.935925960540771</v>
       </c>
       <c r="H150" t="n">
         <v>228664</v>
@@ -4748,7 +4748,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G151" t="n">
-        <v>0.907713174819946</v>
+        <v>0.907713294029236</v>
       </c>
       <c r="H151" t="n">
         <v>331548</v>
@@ -4777,7 +4777,7 @@
         <v>1.54900002479553</v>
       </c>
       <c r="G152" t="n">
-        <v>0.950032234191895</v>
+        <v>0.950032293796539</v>
       </c>
       <c r="H152" t="n">
         <v>547010</v>
@@ -4806,7 +4806,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G153" t="n">
-        <v>0.956778824329376</v>
+        <v>0.956778764724731</v>
       </c>
       <c r="H153" t="n">
         <v>149124</v>
@@ -4864,7 +4864,7 @@
         <v>1.62899994850159</v>
       </c>
       <c r="G155" t="n">
-        <v>0.999097764492035</v>
+        <v>0.99909782409668</v>
       </c>
       <c r="H155" t="n">
         <v>261420</v>
@@ -4893,7 +4893,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G156" t="n">
-        <v>1.00707101821899</v>
+        <v>1.0070708990097</v>
       </c>
       <c r="H156" t="n">
         <v>68730</v>
@@ -4980,7 +4980,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G159" t="n">
-        <v>1.01749742031097</v>
+        <v>1.01749753952026</v>
       </c>
       <c r="H159" t="n">
         <v>131636</v>
@@ -5067,7 +5067,7 @@
         <v>1.66100001335144</v>
       </c>
       <c r="G162" t="n">
-        <v>1.01872420310974</v>
+        <v>1.01872408390045</v>
       </c>
       <c r="H162" t="n">
         <v>160844</v>
@@ -5096,7 +5096,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G163" t="n">
-        <v>1.00461769104004</v>
+        <v>1.00461781024933</v>
       </c>
       <c r="H163" t="n">
         <v>76999</v>
@@ -5125,7 +5125,7 @@
         <v>1.66100001335144</v>
       </c>
       <c r="G164" t="n">
-        <v>1.01872420310974</v>
+        <v>1.01872408390045</v>
       </c>
       <c r="H164" t="n">
         <v>78461</v>
@@ -5183,7 +5183,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G166" t="n">
-        <v>1.03896355628967</v>
+        <v>1.03896367549896</v>
       </c>
       <c r="H166" t="n">
         <v>150712</v>
@@ -5212,7 +5212,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G167" t="n">
-        <v>1.02731049060822</v>
+        <v>1.0273106098175</v>
       </c>
       <c r="H167" t="n">
         <v>147312</v>
@@ -5415,7 +5415,7 @@
         <v>1.75800001621246</v>
       </c>
       <c r="G174" t="n">
-        <v>1.07821619510651</v>
+        <v>1.07821607589722</v>
       </c>
       <c r="H174" t="n">
         <v>614354</v>
@@ -5502,7 +5502,7 @@
         <v>1.77699995040894</v>
       </c>
       <c r="G177" t="n">
-        <v>1.08986902236938</v>
+        <v>1.08986914157867</v>
       </c>
       <c r="H177" t="n">
         <v>220355</v>
@@ -5560,7 +5560,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G179" t="n">
-        <v>1.08250939846039</v>
+        <v>1.0825092792511</v>
       </c>
       <c r="H179" t="n">
         <v>486372</v>
@@ -5676,7 +5676,7 @@
         <v>1.64600002765656</v>
       </c>
       <c r="G183" t="n">
-        <v>1.00952434539795</v>
+        <v>1.00952422618866</v>
       </c>
       <c r="H183" t="n">
         <v>198703</v>
@@ -5763,7 +5763,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G186" t="n">
-        <v>1.06717622280121</v>
+        <v>1.0671763420105</v>
       </c>
       <c r="H186" t="n">
         <v>130158</v>
@@ -5792,7 +5792,7 @@
         <v>1.77400004863739</v>
       </c>
       <c r="G187" t="n">
-        <v>1.08802926540375</v>
+        <v>1.08802914619446</v>
       </c>
       <c r="H187" t="n">
         <v>705957</v>
@@ -5937,7 +5937,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G192" t="n">
-        <v>1.10397553443909</v>
+        <v>1.1039754152298</v>
       </c>
       <c r="H192" t="n">
         <v>122359</v>
@@ -5966,7 +5966,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G193" t="n">
-        <v>1.10397553443909</v>
+        <v>1.1039754152298</v>
       </c>
       <c r="H193" t="n">
         <v>198036</v>
@@ -6024,7 +6024,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G195" t="n">
-        <v>1.09416234493256</v>
+        <v>1.09416246414185</v>
       </c>
       <c r="H195" t="n">
         <v>227267</v>
@@ -6082,7 +6082,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G197" t="n">
-        <v>1.10397553443909</v>
+        <v>1.1039754152298</v>
       </c>
       <c r="H197" t="n">
         <v>163067</v>
@@ -6111,7 +6111,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G198" t="n">
-        <v>1.0978422164917</v>
+        <v>1.09784233570099</v>
       </c>
       <c r="H198" t="n">
         <v>97852</v>
@@ -6140,7 +6140,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G199" t="n">
-        <v>1.10152220726013</v>
+        <v>1.10152232646942</v>
       </c>
       <c r="H199" t="n">
         <v>60811</v>
@@ -6169,7 +6169,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>1.0978422164917</v>
+        <v>1.09784233570099</v>
       </c>
       <c r="H200" t="n">
         <v>71260</v>
@@ -6198,7 +6198,7 @@
         <v>1.79100000858307</v>
       </c>
       <c r="G201" t="n">
-        <v>1.09845554828644</v>
+        <v>1.09845566749573</v>
       </c>
       <c r="H201" t="n">
         <v>108906</v>
@@ -6285,7 +6285,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G204" t="n">
-        <v>1.10090899467468</v>
+        <v>1.10090887546539</v>
       </c>
       <c r="H204" t="n">
         <v>98997</v>
@@ -6314,7 +6314,7 @@
         <v>1.79100000858307</v>
       </c>
       <c r="G205" t="n">
-        <v>1.09845554828644</v>
+        <v>1.09845566749573</v>
       </c>
       <c r="H205" t="n">
         <v>130768</v>
@@ -6401,7 +6401,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G208" t="n">
-        <v>1.10152220726013</v>
+        <v>1.10152232646942</v>
       </c>
       <c r="H208" t="n">
         <v>71337</v>
@@ -6459,7 +6459,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G210" t="n">
-        <v>1.18370699882507</v>
+        <v>1.18370711803436</v>
       </c>
       <c r="H210" t="n">
         <v>1793350</v>
@@ -6488,7 +6488,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G211" t="n">
-        <v>1.23890590667725</v>
+        <v>1.23890578746796</v>
       </c>
       <c r="H211" t="n">
         <v>1398955</v>
@@ -6546,7 +6546,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G213" t="n">
-        <v>1.23277258872986</v>
+        <v>1.23277270793915</v>
       </c>
       <c r="H213" t="n">
         <v>488691</v>
@@ -6604,7 +6604,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G215" t="n">
-        <v>1.26343858242035</v>
+        <v>1.26343870162964</v>
       </c>
       <c r="H215" t="n">
         <v>414877</v>
@@ -6691,7 +6691,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G218" t="n">
-        <v>1.26466524600983</v>
+        <v>1.26466536521912</v>
       </c>
       <c r="H218" t="n">
         <v>379339</v>
@@ -6749,7 +6749,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G220" t="n">
-        <v>1.24503910541534</v>
+        <v>1.24503898620605</v>
       </c>
       <c r="H220" t="n">
         <v>521123</v>
@@ -6807,7 +6807,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G222" t="n">
-        <v>1.24135899543762</v>
+        <v>1.24135911464691</v>
       </c>
       <c r="H222" t="n">
         <v>447289</v>
@@ -6836,7 +6836,7 @@
         <v>2.07399988174438</v>
       </c>
       <c r="G223" t="n">
-        <v>1.27202498912811</v>
+        <v>1.2720251083374</v>
       </c>
       <c r="H223" t="n">
         <v>256250</v>
@@ -6952,7 +6952,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G227" t="n">
-        <v>1.32477080821991</v>
+        <v>1.32477068901062</v>
       </c>
       <c r="H227" t="n">
         <v>203471</v>
@@ -6981,7 +6981,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G228" t="n">
-        <v>1.32477080821991</v>
+        <v>1.32477068901062</v>
       </c>
       <c r="H228" t="n">
         <v>299354</v>
@@ -7010,7 +7010,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G229" t="n">
-        <v>1.33090388774872</v>
+        <v>1.33090376853943</v>
       </c>
       <c r="H229" t="n">
         <v>710066</v>
@@ -7213,7 +7213,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G236" t="n">
-        <v>1.28797125816345</v>
+        <v>1.28797137737274</v>
       </c>
       <c r="H236" t="n">
         <v>205772</v>
@@ -7242,7 +7242,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G237" t="n">
-        <v>1.28797125816345</v>
+        <v>1.28797137737274</v>
       </c>
       <c r="H237" t="n">
         <v>141863</v>
@@ -7271,7 +7271,7 @@
         <v>2.09200000762939</v>
       </c>
       <c r="G238" t="n">
-        <v>1.28306484222412</v>
+        <v>1.28306496143341</v>
       </c>
       <c r="H238" t="n">
         <v>268785</v>
@@ -7590,7 +7590,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G249" t="n">
-        <v>1.47932708263397</v>
+        <v>1.47932720184326</v>
       </c>
       <c r="H249" t="n">
         <v>163664</v>
@@ -7648,7 +7648,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G251" t="n">
-        <v>1.50263333320618</v>
+        <v>1.50263345241547</v>
       </c>
       <c r="H251" t="n">
         <v>163694</v>
@@ -7677,7 +7677,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G252" t="n">
-        <v>1.49650013446808</v>
+        <v>1.49650025367737</v>
       </c>
       <c r="H252" t="n">
         <v>188904</v>
@@ -7764,7 +7764,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G255" t="n">
-        <v>1.44743454456329</v>
+        <v>1.447434425354</v>
       </c>
       <c r="H255" t="n">
         <v>237678</v>
@@ -7793,7 +7793,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G256" t="n">
-        <v>1.47810065746307</v>
+        <v>1.47810053825378</v>
       </c>
       <c r="H256" t="n">
         <v>141019</v>
@@ -7880,7 +7880,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G259" t="n">
-        <v>1.5799115896225</v>
+        <v>1.57991170883179</v>
       </c>
       <c r="H259" t="n">
         <v>412317</v>
@@ -7996,7 +7996,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G263" t="n">
-        <v>1.53943252563477</v>
+        <v>1.53943240642548</v>
       </c>
       <c r="H263" t="n">
         <v>458372</v>
@@ -8025,7 +8025,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G264" t="n">
-        <v>1.5737783908844</v>
+        <v>1.57377851009369</v>
       </c>
       <c r="H264" t="n">
         <v>102370</v>
@@ -8083,7 +8083,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G266" t="n">
-        <v>1.55169892311096</v>
+        <v>1.55169880390167</v>
       </c>
       <c r="H266" t="n">
         <v>242727</v>
@@ -8141,7 +8141,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G268" t="n">
-        <v>1.57868492603302</v>
+        <v>1.57868480682373</v>
       </c>
       <c r="H268" t="n">
         <v>126004</v>
@@ -8199,7 +8199,7 @@
         <v>2.5</v>
       </c>
       <c r="G270" t="n">
-        <v>1.53329944610596</v>
+        <v>1.53329932689667</v>
       </c>
       <c r="H270" t="n">
         <v>124510</v>
@@ -8228,7 +8228,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G271" t="n">
-        <v>1.5259393453598</v>
+        <v>1.52593958377838</v>
       </c>
       <c r="H271" t="n">
         <v>154741</v>
@@ -8257,7 +8257,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G272" t="n">
-        <v>1.5136730670929</v>
+        <v>1.51367318630219</v>
       </c>
       <c r="H272" t="n">
         <v>102900</v>
@@ -8286,7 +8286,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G273" t="n">
-        <v>1.49527359008789</v>
+        <v>1.4952734708786</v>
       </c>
       <c r="H273" t="n">
         <v>101503</v>
@@ -8315,7 +8315,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G274" t="n">
-        <v>1.53084599971771</v>
+        <v>1.530846118927</v>
       </c>
       <c r="H274" t="n">
         <v>132938</v>
@@ -8373,7 +8373,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G276" t="n">
-        <v>1.5259393453598</v>
+        <v>1.52593958377838</v>
       </c>
       <c r="H276" t="n">
         <v>121968</v>
@@ -8489,7 +8489,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G280" t="n">
-        <v>1.4167685508728</v>
+        <v>1.41676867008209</v>
       </c>
       <c r="H280" t="n">
         <v>233709</v>
@@ -8518,7 +8518,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G281" t="n">
-        <v>1.41308856010437</v>
+        <v>1.41308867931366</v>
       </c>
       <c r="H281" t="n">
         <v>67393</v>
@@ -8750,7 +8750,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G289" t="n">
-        <v>1.40940880775452</v>
+        <v>1.40940892696381</v>
       </c>
       <c r="H289" t="n">
         <v>287135</v>
@@ -8779,7 +8779,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G290" t="n">
-        <v>1.39100897312164</v>
+        <v>1.39100909233093</v>
       </c>
       <c r="H290" t="n">
         <v>208243</v>
@@ -8953,7 +8953,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G296" t="n">
-        <v>1.4106353521347</v>
+        <v>1.41063547134399</v>
       </c>
       <c r="H296" t="n">
         <v>197826</v>
@@ -8982,7 +8982,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G297" t="n">
-        <v>1.39591562747955</v>
+        <v>1.39591574668884</v>
       </c>
       <c r="H297" t="n">
         <v>195070</v>
@@ -9040,7 +9040,7 @@
         <v>2.67199993133545</v>
       </c>
       <c r="G299" t="n">
-        <v>1.63879024982452</v>
+        <v>1.63879036903381</v>
       </c>
       <c r="H299" t="n">
         <v>1636915</v>
@@ -9214,7 +9214,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G305" t="n">
-        <v>1.79825329780579</v>
+        <v>1.79825341701508</v>
       </c>
       <c r="H305" t="n">
         <v>673534</v>
@@ -9243,7 +9243,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G306" t="n">
-        <v>1.7540944814682</v>
+        <v>1.75409436225891</v>
       </c>
       <c r="H306" t="n">
         <v>548849</v>
@@ -9272,7 +9272,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G307" t="n">
-        <v>1.7908935546875</v>
+        <v>1.79089367389679</v>
       </c>
       <c r="H307" t="n">
         <v>670021</v>
@@ -9301,7 +9301,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G308" t="n">
-        <v>1.77740049362183</v>
+        <v>1.77740061283112</v>
       </c>
       <c r="H308" t="n">
         <v>520725</v>
@@ -9330,7 +9330,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>1.77862727642059</v>
+        <v>1.7786271572113</v>
       </c>
       <c r="H309" t="n">
         <v>373278</v>
@@ -9359,7 +9359,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G310" t="n">
-        <v>1.7908935546875</v>
+        <v>1.79089367389679</v>
       </c>
       <c r="H310" t="n">
         <v>165055</v>
@@ -9388,7 +9388,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G311" t="n">
-        <v>1.8031599521637</v>
+        <v>1.80316007137299</v>
       </c>
       <c r="H311" t="n">
         <v>257588</v>
@@ -9417,7 +9417,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G312" t="n">
-        <v>1.82523965835571</v>
+        <v>1.82523953914642</v>
       </c>
       <c r="H312" t="n">
         <v>318543</v>
@@ -9533,7 +9533,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G316" t="n">
-        <v>2.08528709411621</v>
+        <v>2.08528733253479</v>
       </c>
       <c r="H316" t="n">
         <v>2203772</v>
@@ -9591,7 +9591,7 @@
         <v>3.60199999809265</v>
       </c>
       <c r="G318" t="n">
-        <v>2.20917797088623</v>
+        <v>2.20917773246765</v>
       </c>
       <c r="H318" t="n">
         <v>1002453</v>
@@ -9620,7 +9620,7 @@
         <v>3.75</v>
       </c>
       <c r="G319" t="n">
-        <v>2.29994916915894</v>
+        <v>2.29994893074036</v>
       </c>
       <c r="H319" t="n">
         <v>632837</v>
@@ -9649,7 +9649,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G320" t="n">
-        <v>2.2974956035614</v>
+        <v>2.29749584197998</v>
       </c>
       <c r="H320" t="n">
         <v>576179</v>
@@ -9678,7 +9678,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G321" t="n">
-        <v>2.26928305625916</v>
+        <v>2.26928281784058</v>
       </c>
       <c r="H321" t="n">
         <v>427642</v>
@@ -9823,7 +9823,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G326" t="n">
-        <v>2.24843001365662</v>
+        <v>2.2484302520752</v>
       </c>
       <c r="H326" t="n">
         <v>356043</v>
@@ -9881,7 +9881,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G328" t="n">
-        <v>2.24843001365662</v>
+        <v>2.2484302520752</v>
       </c>
       <c r="H328" t="n">
         <v>167124</v>
@@ -9997,7 +9997,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G332" t="n">
-        <v>2.20181798934937</v>
+        <v>2.20181775093079</v>
       </c>
       <c r="H332" t="n">
         <v>420981</v>
@@ -10026,7 +10026,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G333" t="n">
-        <v>2.28277611732483</v>
+        <v>2.28277587890625</v>
       </c>
       <c r="H333" t="n">
         <v>285695</v>
@@ -10229,7 +10229,7 @@
         <v>4.71799993515015</v>
       </c>
       <c r="G340" t="n">
-        <v>2.89364242553711</v>
+        <v>2.89364218711853</v>
       </c>
       <c r="H340" t="n">
         <v>1367684</v>
@@ -10287,7 +10287,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>2.73540616035461</v>
+        <v>2.73540592193604</v>
       </c>
       <c r="H342" t="n">
         <v>1177654</v>
@@ -10316,7 +10316,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G343" t="n">
-        <v>2.76607227325439</v>
+        <v>2.76607203483582</v>
       </c>
       <c r="H343" t="n">
         <v>487349</v>
@@ -10490,7 +10490,7 @@
         <v>4.60799980163574</v>
       </c>
       <c r="G349" t="n">
-        <v>2.82617712020874</v>
+        <v>2.82617735862732</v>
       </c>
       <c r="H349" t="n">
         <v>339119</v>
@@ -10548,7 +10548,7 @@
         <v>4.72399997711182</v>
       </c>
       <c r="G351" t="n">
-        <v>2.89732241630554</v>
+        <v>2.89732265472412</v>
       </c>
       <c r="H351" t="n">
         <v>476496</v>
@@ -10606,7 +10606,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G353" t="n">
-        <v>2.79796433448792</v>
+        <v>2.79796457290649</v>
       </c>
       <c r="H353" t="n">
         <v>631744</v>
@@ -10635,7 +10635,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G354" t="n">
-        <v>2.99300026893616</v>
+        <v>2.99300050735474</v>
       </c>
       <c r="H354" t="n">
         <v>1271662</v>
@@ -10751,7 +10751,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G358" t="n">
-        <v>3.21379518508911</v>
+        <v>3.21379542350769</v>
       </c>
       <c r="H358" t="n">
         <v>471503</v>
@@ -10954,7 +10954,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G365" t="n">
-        <v>3.1892626285553</v>
+        <v>3.18926239013672</v>
       </c>
       <c r="H365" t="n">
         <v>330140</v>
@@ -11099,7 +11099,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G370" t="n">
-        <v>2.99300026893616</v>
+        <v>2.99300050735474</v>
       </c>
       <c r="H370" t="n">
         <v>709668</v>
@@ -11128,7 +11128,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G371" t="n">
-        <v>3.21072888374329</v>
+        <v>3.21072864532471</v>
       </c>
       <c r="H371" t="n">
         <v>1337692</v>
@@ -11389,7 +11389,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G380" t="n">
-        <v>3.18312954902649</v>
+        <v>3.18312931060791</v>
       </c>
       <c r="H380" t="n">
         <v>358113</v>
@@ -11418,7 +11418,7 @@
         <v>4.93400001525879</v>
       </c>
       <c r="G381" t="n">
-        <v>3.02611947059631</v>
+        <v>3.02611970901489</v>
       </c>
       <c r="H381" t="n">
         <v>560077</v>
@@ -11476,7 +11476,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G383" t="n">
-        <v>2.92553496360779</v>
+        <v>2.92553520202637</v>
       </c>
       <c r="H383" t="n">
         <v>468801</v>
@@ -11505,7 +11505,7 @@
         <v>4.68400001525879</v>
       </c>
       <c r="G384" t="n">
-        <v>2.87278938293457</v>
+        <v>2.87278962135315</v>
       </c>
       <c r="H384" t="n">
         <v>628468</v>
@@ -11563,7 +11563,7 @@
         <v>4.5</v>
       </c>
       <c r="G386" t="n">
-        <v>2.75993895530701</v>
+        <v>2.75993871688843</v>
       </c>
       <c r="H386" t="n">
         <v>677082</v>
@@ -11708,7 +11708,7 @@
         <v>4.72399997711182</v>
       </c>
       <c r="G391" t="n">
-        <v>2.89732241630554</v>
+        <v>2.89732265472412</v>
       </c>
       <c r="H391" t="n">
         <v>894334</v>
@@ -11737,7 +11737,7 @@
         <v>4.71799993515015</v>
       </c>
       <c r="G392" t="n">
-        <v>2.89364242553711</v>
+        <v>2.89364218711853</v>
       </c>
       <c r="H392" t="n">
         <v>334494</v>
@@ -11766,7 +11766,7 @@
         <v>4.71799993515015</v>
       </c>
       <c r="G393" t="n">
-        <v>2.89364242553711</v>
+        <v>2.89364218711853</v>
       </c>
       <c r="H393" t="n">
         <v>133281</v>
@@ -11795,7 +11795,7 @@
         <v>4.69199991226196</v>
       </c>
       <c r="G394" t="n">
-        <v>2.87769627571106</v>
+        <v>2.8776957988739</v>
       </c>
       <c r="H394" t="n">
         <v>136890</v>
@@ -11824,7 +11824,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G395" t="n">
-        <v>2.91081547737122</v>
+        <v>2.91081523895264</v>
       </c>
       <c r="H395" t="n">
         <v>1325910</v>
@@ -11882,7 +11882,7 @@
         <v>4.62599992752075</v>
       </c>
       <c r="G397" t="n">
-        <v>2.83721709251404</v>
+        <v>2.83721733093262</v>
       </c>
       <c r="H397" t="n">
         <v>1465113</v>
@@ -11911,7 +11911,7 @@
         <v>4.51599979400635</v>
       </c>
       <c r="G398" t="n">
-        <v>2.76975178718567</v>
+        <v>2.76975154876709</v>
       </c>
       <c r="H398" t="n">
         <v>784006</v>
@@ -11940,7 +11940,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G399" t="n">
-        <v>2.67898058891296</v>
+        <v>2.67898082733154</v>
       </c>
       <c r="H399" t="n">
         <v>762725</v>
@@ -12027,7 +12027,7 @@
         <v>4.47800016403198</v>
       </c>
       <c r="G402" t="n">
-        <v>2.74644565582275</v>
+        <v>2.74644589424133</v>
       </c>
       <c r="H402" t="n">
         <v>1187685</v>
@@ -12056,7 +12056,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G403" t="n">
-        <v>2.69492697715759</v>
+        <v>2.69492721557617</v>
       </c>
       <c r="H403" t="n">
         <v>765672</v>
@@ -12114,7 +12114,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G405" t="n">
-        <v>2.62500882148743</v>
+        <v>2.62500858306885</v>
       </c>
       <c r="H405" t="n">
         <v>480173</v>
@@ -12230,7 +12230,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G409" t="n">
-        <v>2.5759425163269</v>
+        <v>2.57594275474548</v>
       </c>
       <c r="H409" t="n">
         <v>222579</v>
@@ -12259,7 +12259,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G410" t="n">
-        <v>2.5759425163269</v>
+        <v>2.57594275474548</v>
       </c>
       <c r="H410" t="n">
         <v>166188</v>
@@ -12346,7 +12346,7 @@
         <v>4.64799976348877</v>
       </c>
       <c r="G413" t="n">
-        <v>2.85070991516113</v>
+        <v>2.85071015357971</v>
       </c>
       <c r="H413" t="n">
         <v>1542581</v>
@@ -12433,7 +12433,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G416" t="n">
-        <v>2.82127070426941</v>
+        <v>2.82127094268799</v>
       </c>
       <c r="H416" t="n">
         <v>398517</v>
@@ -12462,7 +12462,7 @@
         <v>4.60400009155273</v>
       </c>
       <c r="G417" t="n">
-        <v>2.82372403144836</v>
+        <v>2.82372426986694</v>
       </c>
       <c r="H417" t="n">
         <v>268282</v>
@@ -12491,7 +12491,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G418" t="n">
-        <v>2.79428505897522</v>
+        <v>2.79428482055664</v>
       </c>
       <c r="H418" t="n">
         <v>184142</v>
@@ -12520,7 +12520,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G419" t="n">
-        <v>2.77588534355164</v>
+        <v>2.77588510513306</v>
       </c>
       <c r="H419" t="n">
         <v>278092</v>
@@ -12549,7 +12549,7 @@
         <v>4.46000003814697</v>
       </c>
      